--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320D950B-B925-4D76-AB7A-168E772B9030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19946B6-841F-4F1F-ABAE-2F99B964A724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="562">
   <si>
     <t>Name</t>
   </si>
@@ -294,129 +294,57 @@
     <t>Painted Slab</t>
   </si>
   <si>
-    <t>&lt;b&gt;Wall of Splendor: &lt;/b&gt;1 AP&lt;br&gt;Place the slab down on an adjacent hex. It extends straight on each side to become a three hex wall, if there is space. This wall blocks vision and is indestructible.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Reclaim: &lt;/b&gt;3 AP or fleshtfleshtfleshT&lt;br&gt;Pick up a deployed painted slab, any adjacent being can do this.</t>
-  </si>
-  <si>
     <t>Pincer Grips</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack -&lt;/i&gt;&lt;b&gt; Nip:&lt;/b&gt; 2 AP&lt;br&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt; , close range.&lt;br&gt;Critical Option:&lt;br&gt;&lt;b&gt;Restrain: &lt;/b&gt;Inflict the &lt;b&gt;Entangled&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
     <t>Projectile Spines</t>
   </si>
   <si>
-    <t>&lt;i&gt;Ranged Attack -&lt;/i&gt;&lt;b&gt; Volley:&lt;/b&gt; 2 AP&lt;br&gt;Damage = 4. &lt;br&gt;You take 1 damage when you use this attack, this damage cannot be reduced.</t>
-  </si>
-  <si>
     <t>Pulsing Heartstone</t>
   </si>
   <si>
-    <t>&lt;b&gt;Embed:&lt;/b&gt; weirdt&lt;br&gt;Place a 1 hex sized heartstone on an adjacent hex. It will break if it takes damage.</t>
-  </si>
-  <si>
     <t>Quartz Seed</t>
   </si>
   <si>
-    <t>&lt;b&gt;Sprout Spire:&lt;/b&gt; 2 AP + (weirdt or charget)&lt;br&gt;Place a &lt;b&gt;crystal spire&lt;/b&gt; on an adjacent hex, it has a two hex radius aura, blocks line of sight, and is &lt;b&gt;destructible&lt;/b&gt;.&lt;br&gt;Whiskey_Xplo</t>
-  </si>
-  <si>
-    <t>Other beings that start their turn inside a &lt;b&gt;crystal spire&lt;/b&gt; aura or enter it their turn take 3 damage.</t>
-  </si>
-  <si>
     <t>Rock Pouch</t>
   </si>
   <si>
-    <t>&lt;i&gt;Ranged Attack - &lt;/i&gt;&lt;b&gt;Throw: &lt;/b&gt;1 AP + charget&lt;br&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Rummage:&lt;/b&gt; 3 AP + fleshT&lt;br&gt;Recharge this item.</t>
-  </si>
-  <si>
     <t>Shovelling talons</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack -&lt;/i&gt; &lt;b&gt;Thump: &lt;/b&gt;2 AP&lt;br&gt;Damage =4, close range.&lt;br&gt;Crit Option:&lt;br&gt;&lt;b&gt;Concuss:&lt;/b&gt; Inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Dig:&lt;/b&gt; 1 AP or fleshT&lt;br&gt;Clear an adjacent hex of any terrain. This can cause beings to fall if they were on top of it.</t>
-  </si>
-  <si>
     <t>Sineuous Lash</t>
   </si>
   <si>
-    <t>&lt;i&gt;Ranged Attack&lt;/i&gt; -&lt;b&gt; Yoink:&lt;/b&gt; 1 AP&lt;br&gt;Damage = 0.&lt;br&gt;Pull the target to an adjacent hex on a hit&lt;br&gt;Crit Option:&lt;br&gt;&lt;b&gt;Entangle:&lt;/b&gt; Inflict the &lt;b&gt;Entangled&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
     <t>Sneak Spurs</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack -&lt;/i&gt;&lt;b&gt; Ping!: &lt;/b&gt;1 AP&lt;br&gt;Damage = 1, reach.&lt;br&gt;Crit Options:&lt;br&gt;&lt;b&gt;Dash:&lt;/b&gt; Take a move action for free.&lt;br&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage.</t>
-  </si>
-  <si>
     <t>Stalagmite</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Prod:&lt;/b&gt; 2 AP&lt;br&gt;Damage = 4, reach.&lt;br&gt;This can only target non-adjacent beings.&lt;br&gt;Crit Option:&lt;br&gt;&lt;b&gt;Strike:&lt;/b&gt; +1 damage.</t>
-  </si>
-  <si>
     <t>Steam Vent</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Geyser:&lt;/b&gt; 2 AP&lt;br&gt;Damage = 2, reach.&lt;br&gt;On a hit, remove all &lt;b&gt;temporary composure&lt;/b&gt; from the target before dealing damage.&lt;br&gt;Crit Option:&lt;br&gt;&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack cannot be reduced.</t>
-  </si>
-  <si>
     <t>Stone-Swivel Hinge</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Smash:&lt;/b&gt; 3 AP + 2 composure&lt;br&gt;Damage = 7, reach.&lt;br&gt;</t>
-  </si>
-  <si>
     <t>Thermal Funnel</t>
   </si>
   <si>
-    <t>&lt;i&gt;Ranged Attack - &lt;/i&gt;&lt;b&gt;Flameball:&lt;/b&gt; 3 AP&lt;br&gt;Damage = 5&lt;br&gt;On a hit, inflict the &lt;b&gt;burning&lt;/b&gt; status effect.&lt;br&gt;On a miss, inflict the &lt;b&gt;burning&lt;/b&gt; status effect on you.</t>
-  </si>
-  <si>
     <t>Torsion Ribs</t>
   </si>
   <si>
-    <t>&lt;i&gt;Ranged Attack - &lt;/i&gt;&lt;b&gt;Release:&lt;/b&gt; 5 x chargeT&lt;br&gt;Automatically activates upon reaching 5 charget.&lt;br&gt;Deal 8 damage to all beings in a straight line from you. No attack roll required.</t>
-  </si>
-  <si>
     <t>Twitching Talons</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Scour:&lt;/b&gt; 2 AP&lt;br&gt;Damage = 4 , close range.</t>
-  </si>
-  <si>
     <t>Venemous Tail</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Lance: &lt;/b&gt;2 AP&lt;br&gt;Damage = 3 , reach.&lt;br&gt;Crit Option:&lt;br&gt;&lt;b&gt;Venom: &lt;/b&gt;Inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Jab: &lt;/b&gt;jazzt&lt;br&gt;Use the Lance attack on a being that has entered your attack range for the first time on their turn.</t>
-  </si>
-  <si>
     <t>Willow Parasite</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Lash Out:&lt;/b&gt; 2 AP&lt;br&gt;Damage = 4 , reach.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Summon Saplings:&lt;/b&gt; weirdtweirdT&lt;br&gt;Fill 3 target connected empty hexes with a willow tree which blocks movement and vision. Each hex can be individually destroyed by dealing damage.</t>
-  </si>
-  <si>
     <t>Withered Hand</t>
   </si>
   <si>
-    <t>&lt;i&gt;Melee Attack - &lt;/i&gt;&lt;b&gt;Anhidonia:&lt;/b&gt; 3 AP&lt;br&gt;Damage = 5, close range.&lt;br&gt;Inflict the &lt;b&gt;Exhausted&lt;/b&gt; status effect on a hit.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Create Sigil: &lt;/b&gt;1 AP</t>
   </si>
   <si>
@@ -435,9 +363,6 @@
     <t>&lt;b&gt;Flail: automatic&lt;/b&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 4, close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Draw a sigil on an adjacent tile. You may have a maximum of 3 sigils. Other players may spend 3AP to destroy an adjacent sigil</t>
   </si>
   <si>
@@ -486,9 +411,6 @@
     <t>&lt;b&gt;Drive-Power: &lt;/b&gt;weirdt</t>
   </si>
   <si>
-    <t>Inflict the &lt;b&gt;Cursed&lt;/b&gt; status effect on a target in close range.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Smear:&lt;/b&gt; 2 AP + weirdT weirdT</t>
   </si>
   <si>
@@ -513,15 +435,9 @@
     <t>&lt;b&gt;Crush:&lt;/b&gt; 4 AP or (2 AP + fleshT fleshT)</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 5 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Bludgeon:&lt;/b&gt; 3 AP</t>
   </si>
   <si>
-    <t>Damage = 3 , close range.&lt;br&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Whelm:&lt;/b&gt; 1 AP + weirdT</t>
   </si>
   <si>
@@ -531,9 +447,6 @@
     <t>&lt;b&gt; Charge!:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 6 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt; Shove :&lt;/b&gt; 1 AP + fleshT</t>
   </si>
   <si>
@@ -558,18 +471,9 @@
     <t>&lt;b&gt; Bite:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 4 , close range.&lt;br&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 3 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Flurry:&lt;/b&gt;Your next attack costs 1 less AP.&lt;br&gt;&lt;b&gt;Strike:&lt;/b&gt; +1 Damage.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 4 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Dash:&lt;/b&gt; Take a move action.&lt;br&gt;&lt;b&gt;Mighty Shove:&lt;/b&gt; Push the target 2 hexes.</t>
   </si>
   <si>
@@ -585,18 +489,12 @@
     <t>The boss does not consider you a target unless you are the last alive.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 1 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Omen:&lt;/b&gt; Inflict the &lt;b&gt;Cursed&lt;/b&gt; status effect.</t>
   </si>
   <si>
     <t>&lt;b&gt;Burn:&lt;/b&gt; Inflict the &lt;b&gt;Burning&lt;/b&gt; status effect.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 8 , close range.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Concuss:&lt;/b&gt; Inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect.</t>
   </si>
   <si>
@@ -669,9 +567,6 @@
     <t>Wounds inflicted by this limb's attacks always target the stat of your choice.</t>
   </si>
   <si>
-    <t>&lt;i&gt;&lt;b&gt;Precise:&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Strike:&lt;/b&gt; +1 damage.</t>
   </si>
   <si>
@@ -732,9 +627,6 @@
     <t>Coward</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Flee:&lt;/b&gt; jazzT&lt;br&gt;When an enemy moves into an adjacent tile, you may take a free move action immediately.</t>
-  </si>
-  <si>
     <t>Creative</t>
   </si>
   <si>
@@ -753,15 +645,9 @@
     <t>chargemidchargemidchargemid</t>
   </si>
   <si>
-    <t>&lt;b&gt;Burst:&lt;/b&gt; chargeT or weirdT&lt;br&gt;Replenish a jazzt or flesht</t>
-  </si>
-  <si>
     <t>Grandiose</t>
   </si>
   <si>
-    <t>Pillars can be climbed by spending 3 AP or jazzT.</t>
-  </si>
-  <si>
     <t>Hardy</t>
   </si>
   <si>
@@ -771,18 +657,9 @@
     <t>I'm Normal</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;What?:&lt;/b&gt; 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;Ignore the effects of an ability with weirdt in its cost. (Even if no weirdT was spent).</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;A cup of tea:&lt;/b&gt; 1 AP + 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;Gain the &lt;b&gt;Well rested&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
     <t>Kind</t>
   </si>
   <si>
-    <t>&lt;b&gt;Alliance:&lt;/b&gt; 3 AP&lt;br&gt;Declare target being your ally (if they consent), you both win if you are the only beings left in the room. You may only use this ability if 4 players are alive.</t>
-  </si>
-  <si>
     <t>You may only use Kind in a 4 or more player game, if drawn in a 3 player game replace immediately.</t>
   </si>
   <si>
@@ -801,65 +678,36 @@
     <t>Malevolent</t>
   </si>
   <si>
-    <t>&lt;b&gt;Cackle:&lt;/b&gt; WeirdT&lt;br&gt;Give yourself and an ally up to 1 temporary composure</t>
-  </si>
-  <si>
     <t>Melancholic</t>
   </si>
   <si>
-    <t>&lt;b&gt;Apathy&lt;/b&gt;: WeirdT&lt;br&gt;Put a counter on a limb of target being. The next time that limb deals damage, it deals 2 less. This doesn't stack.</t>
-  </si>
-  <si>
     <t>Morbid</t>
   </si>
   <si>
     <t>Musical</t>
   </si>
   <si>
-    <t>&lt;b&gt;Rally Song:&lt;/b&gt; 2 AP or weirdT&lt;br&gt;You and any number of target allies gain up to 3 temporary composure.</t>
-  </si>
-  <si>
     <t>Negotiator</t>
   </si>
   <si>
-    <t>&lt;b&gt;Pact&lt;/b&gt;: 1 AP + WeirdT
-&lt;br&gt;Offer a deal to a player. If they accept they gain one temporary stat token. &lt;br&gt;If they then break the deal, they take 8 damage.
-&lt;br&gt;If they reject the deal, you gain the temporary stat token.</t>
-  </si>
-  <si>
     <t>Nimble</t>
   </si>
   <si>
-    <t>&lt;b&gt;Dash: jazzt&lt;br&gt;&lt;/b&gt;Take a move action.</t>
-  </si>
-  <si>
     <t>Obscene</t>
   </si>
   <si>
-    <t>&lt;b&gt;Slander:&lt;/b&gt; 1AP + WeirdT&lt;br&gt;Mark a target, your attacks against marked target deal +1 damage.</t>
-  </si>
-  <si>
     <t>Pathetic</t>
   </si>
   <si>
     <t>Patient</t>
   </si>
   <si>
-    <t>&lt;b&gt;Exhale:&lt;/b&gt; Remove all counters&lt;br&gt;Gain 1 AP for each counter removed. This turn inhale won't trigger.</t>
-  </si>
-  <si>
     <t>Protector</t>
   </si>
   <si>
-    <t>&lt;b&gt;Good Clay:&lt;/b&gt; weirdtweirdt or 2 AP + weirdT&lt;br&gt;You and up to 1 adjacent being restore 1 wound.</t>
-  </si>
-  <si>
     <t>Relentless</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;b&gt;Double down:&lt;/b&gt;&lt;/i&gt; jazzTjazzT&lt;br&gt;Re-roll an attack roll you have made.</t>
-  </si>
-  <si>
     <t>Restless</t>
   </si>
   <si>
@@ -872,46 +720,24 @@
     <t>Stalwart</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Protect&lt;/b&gt;: FleshT or WeirdT
-&lt;br&gt;When target ally takes damage, reduce that damage by 2, activate only once per instance of damage.</t>
-  </si>
-  <si>
     <t>Stoic</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - Unfazed&lt;/i&gt;: WeirdT
-&lt;br&gt;When you would take a status effect (except exhausted), ignore it instead.</t>
-  </si>
-  <si>
     <t>Strange</t>
   </si>
   <si>
-    <t>&lt;b&gt;Secret Technique:&lt;/b&gt; 1AP or weirdT&lt;br&gt;Add your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt; to the range of your next melee attack this turn.</t>
-  </si>
-  <si>
     <t>Strong Heartbeat</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Snigger:&lt;/b&gt; 1 AP or WeirdT
-&lt;br&gt;Whenever you see a being take damage from a source other than you, increase that damage by 2. This does not stack.</t>
-  </si>
-  <si>
     <t>Trickster</t>
   </si>
   <si>
     <t>Wanderer</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Push Through the Pain:&lt;/b&gt; JazzT + FleshT + weirdT&lt;br&gt;When you are non-lethally wounded, ignore the wound.</t>
-  </si>
-  <si>
     <t>Wilful</t>
   </si>
   <si>
-    <t>&lt;b&gt;Overexert&lt;/b&gt;: Gain the &lt;b&gt;Exhausted&lt;/b&gt; status effect
-&lt;br&gt;Gain the &lt;b&gt;Well Rested&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
     <t>Ancient One</t>
   </si>
   <si>
@@ -963,9 +789,6 @@
     <t>Phantom</t>
   </si>
   <si>
-    <t>Quilled</t>
-  </si>
-  <si>
     <t>Serpentine</t>
   </si>
   <si>
@@ -1002,16 +825,7 @@
     <t>chargeBig</t>
   </si>
   <si>
-    <t>&lt;b&gt;Breathe Fire: &lt;/b&gt;3 AP + weirdT
-&lt;br&gt;Emit an inferno of fire, all other beings within 3 hexes take 7 damage.
-&lt;br&gt;You and all adjacent beings suffer the &lt;b&gt;Burning&lt;/b&gt; status.</t>
-  </si>
-  <si>
     <t>You may destroy an equipped limb to replenish a spent token.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Feast&lt;/b&gt;
-Remove an infected token from a being, and use one of your abilities spending their tokens.</t>
   </si>
   <si>
     <t>Whenever you take damage, refresh 1 WeirdT.</t>
@@ -1085,15 +899,6 @@
     <t>At the start of your turn, gain &lt;br&gt;tempct tempct. Temporary composure can stack from any source up to a cap of 5.</t>
   </si>
   <si>
-    <t>&lt;i&gt;&lt;b&gt;Charger:&lt;br&gt;&lt;/i&gt;&lt;/b&gt;When you make an attack, you may move 2 tiles before attacking</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Inhale:&lt;br&gt;&lt;/i&gt;&lt;/b&gt;At the end of your turn, for each unspent action point add a counter to this card, up to max of your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Relish in battle:&lt;br&gt;&lt;/i&gt;&lt;/b&gt;Whenever you critically hit, restore 2 composure or gain up to 2 temporary composure.</t>
-  </si>
-  <si>
     <t>&lt;i&gt;&lt;b&gt;Decrepit&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
@@ -1103,9 +908,6 @@
     <t>&lt;i&gt;&lt;b&gt;Immense&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t>&lt;i&gt;Reaction - &lt;b&gt;Switcheroo&lt;/i&gt;&lt;/b&gt; 1 AP + weirdT&lt;br&gt;After taking damage, you may activate this to swap places with any being.</t>
-  </si>
-  <si>
     <t>&lt;i&gt;&lt;b&gt;Two Legs&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
@@ -1134,15 +936,6 @@
   </si>
   <si>
     <t>Make a 2 tile wall Hex2wide of Crystal. It can not be climbed and is &lt;b&gt;destructible.&lt;/b&gt;Gain up to two tempct.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Mimic: WeirdT + 1AP&lt;/b&gt;Adaptive becomes a copy of any Limb or Impression in play, except it also retains the &lt;b&gt;Mimic&lt;/b&gt; ability. If it would be destroyed, so is Adaptive.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Mold Earth: weirdTweirdT&lt;/b&gt;Create a large pillar Hex1b in target empty location.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;Reaction - &lt;/i&gt;&lt;b&gt;Change of Luck: chargeT&lt;/b&gt;After any die is rolled by any being you can see, you may force it to be re-rolled after seeing the result.</t>
   </si>
   <si>
     <t>&lt;b&gt;Damage = 4, ranged.&lt;/b&gt;This attack can only target your hated target.</t>
@@ -1152,96 +945,7 @@
 This damage cannot be reduced.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 2 , close range.&lt;/b&gt;On a hit, you may destroy this card to destroy any equipped Limb or Impression from the target.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = hexes moved, close range.&lt;/b&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br&gt; hornshexes</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 2 , close range.&lt;/b&gt;On a hit, the target is pushed back hexes equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Damage = 7, ranged.&lt;/b&gt;Throw this limb at your target as part of the attack, regardless of attack outcome, they now have Hungering Hand equipped .</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 1 , close range.&lt;/b&gt;This attack always hits, do not roll.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 4 , Ranged&lt;/b&gt;Ignores damage reduction effects.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 8, close range.&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 2, reach.&lt;/b&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Winch: 1 AP&lt;/b&gt;Add a chargeT to this card. Activate only once each turn.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Uncanny: &lt;/i&gt;&lt;/b&gt;At the beginning of combat secretly choose the next being to die and write it down. If you are correct, gain the &lt;b&gt;Portent&lt;/b&gt; status and repeat this ability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;i&gt; &lt;b&gt;Sure Footed: &lt;/i&gt;&lt;/b&gt;Effects from enemy abilities and terrain cannot reduce your movement speed. </t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Furnace&lt;/i&gt;&lt;/b&gt;Your move speed is reduced by 1.
-&lt;br&gt;You take 1 less damage from all sources.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Magic Touch&lt;/i&gt;&lt;/b&gt;Your attacks have the crit option&lt;br&gt;&lt;b&gt;Imbue:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Aura of Earth&lt;/i&gt;&lt;/b&gt;Whenever you spend weirdt, you and up to 1 target ally gain up to 1 temporary composure.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Creature of the Shadows&lt;/i&gt;&lt;/b&gt;Terrain that does not block movement does not block your line of sight.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Living Rythm&lt;/i&gt;&lt;/b&gt;While there is at least 1 heartstone on the map, you gain up to 3 temporary composure at the end of your turn.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Snatch&lt;/i&gt;&lt;/b&gt;Whenever a being leaves your attack range, you may spend jazzT to make an attack with any limb against them. If the attack would cost 3 or more AP, become &lt;b&gt;exhausted&lt;/b&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; World Sculptor&lt;/i&gt;&lt;/b&gt;Whenever you spend weirdt, create a small pillar Hex1a in target empty hex.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Normality&lt;/i&gt;&lt;/b&gt;Replace your  &lt;span style="color:#3366cc"&gt;&lt;strong&gt;Weird&lt;/strong&gt;&lt;/span&gt; with &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;. You cannot spend weirdt any more.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Vulgarity&lt;/i&gt;&lt;/b&gt;Whenever you spend a weirdt, all marked targets lose 1 composure, down to a minimum of 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;i&gt;&lt;b&gt;Stone Flesh&lt;/i&gt;&lt;/b&gt;
-Reduce damage taken by 1 and your move speed by 2. </t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Impervious Plates&lt;/i&gt;&lt;/b&gt;
-Reduce damage from non-adjacent beings to 0.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Behemoth&lt;/i&gt;&lt;/b&gt;
-Effects cannot move you, only the move action will cause you to move.
-&lt;br&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Infect&lt;/b&gt;
-Gain the crit option:
-&lt;br&gt;&lt;b&gt;Infect:&lt;/b&gt; Spend one chargeT, and give it to your target. While they have this token, they are infected.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;
-At the start of your turn, gain 1 temporary composure for each infected being including you.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Flame geysers&lt;/i&gt;&lt;/b&gt;
-At the start of each turn, gain the &lt;b&gt;Burning&lt;/b&gt; status effect</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Through fire&lt;/i&gt;&lt;/b&gt;
-Your attacks gain the crit option:
-&lt;br&gt;&lt;b&gt;Purification:&lt;/b&gt;Remove one of your status effects and inflict it.</t>
   </si>
   <si>
     <t>&lt;i&gt;&lt;b&gt; Flow State&lt;/b&gt;&lt;/i&gt;</t>
@@ -1267,76 +971,9 @@
     </r>
   </si>
   <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;The first time a being dies in combat, draw 4 impressions and equip 2 of them.</t>
-  </si>
-  <si>
     <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t>&lt;i&gt;Passive- &lt;b&gt;Enflamed:&lt;/b&gt;&lt;/i&gt;Fire and Burning give you temporary composure instead of dealing damage.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;Passive- &lt;b&gt;Generative:&lt;/b&gt;&lt;/i&gt;At the start of your turn, if you have less than 4 limbs equipped, draw and equip a limb.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Dual Wielder&lt;/i&gt;&lt;/b&gt;Your second attack each turn costs 1 less AP</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Creative Duellist&lt;/i&gt;&lt;/b&gt;You may use crit options available to any of your limbs on all attacks.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;At the start of your turn, if you have an equal number of unspent tokens in each stat, refresh two spent stat tokens.
-&lt;br&gt;&lt;br&gt;They must be different tokens.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;Once per turn you may suffer a wound to a stat of your choice to refresh 2 spent tokens in that stat.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;While you are unwounded, gain 1 additional AP at the start of each turn.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;At the start of your first turn, draw an impression and equip it over creative. &lt;br&gt;At the end of your each turn, you &lt;b&gt;may&lt;/b&gt; discard that impression to draw and equip a new impression over creative.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; On the Move:&lt;/b&gt;&lt;/i&gt;Whenever you gain temporary composure, you may move that many hexes.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;You can't be affected by the &lt;b&gt;Targeted Strike&lt;/b&gt; critical effect.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;Your attacks have the crit option:&lt;br&gt;&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to 1 temporary composure.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt; Treasure!:&lt;/b&gt;&lt;/i&gt;During map creation, search the boons deck for any card. You may place this on the map in addition to your allotted terrain cards.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;Whenever a 12 is rolled by any being during the game, replenish 1 spent stat token of your choice.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Twisted Kindness&lt;/b&gt;&lt;/i&gt;Whenever you would give another creature temporary composure, you may deal that much damage instead</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Fatebender: &lt;/b&gt;&lt;/i&gt;At the stat of combat, gain the &lt;b&gt;Portent&lt;/b&gt; status effect.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;When you take the &lt;b&gt;cower&lt;/b&gt; reaction, you can reduce damage taken by 2 instead of 1</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;When you take the &lt;b&gt;reposition&lt;/b&gt; reaction you can move your speed instead of 1 hex.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;Your attacks deal bonus damage equal to the number of &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt; wounds you have.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Pressure Points&lt;/b&gt;&lt;/i&gt;Your attacks have the crit option:&lt;br&gt;&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;i&gt;&lt;b&gt;Passive&lt;/i&gt;&lt;/b&gt;Whenever you would heal or refresh a token, heal or refresh twice as many. </t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Minion:&lt;/b&gt;&lt;/i&gt;The boss does not consider you a target unless you are the last alive</t>
-  </si>
-  <si>
     <t>Your attacks that inflict a wound have the crit option&lt;br&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
   </si>
   <si>
@@ -1370,9 +1007,6 @@
     <t>At the start of your turn, put a counter on an empty mode then use that effect</t>
   </si>
   <si>
-    <t>&lt;b&gt;Billowing Dark:&lt;/b&gt; 1 AP + weirdT&lt;br&gt;Create a 3 hex area of darkness Hex1b&lt;br&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only crit on a 12.</t>
-  </si>
-  <si>
     <t>&lt;i&gt;&lt;b&gt;Very Fast&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
@@ -1392,9 +1026,6 @@
   </si>
   <si>
     <t>Prevent all damage from an attack that would kill you.</t>
-  </si>
-  <si>
-    <t>You may clear a status effect (except exhausted) to refresh a token of your choice</t>
   </si>
   <si>
     <t>Your melee and reach attacks have the crit option:
@@ -1431,12 +1062,6 @@
     <t>When you take a wound, replenish a spent token of the same stat.</t>
   </si>
   <si>
-    <t>You take 1 less damage from all sources.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Tough&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>While you have at most 1 limb equipped, you refresh 1 WeirdT at the start of each of your turns.</t>
   </si>
   <si>
@@ -1465,12 +1090,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Chilling presence: &lt;/b&gt;weirdT</t>
-  </si>
-  <si>
-    <t>Whenever you are struck by a melee attack, deal 3 damage back to the attacker.</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;&lt;b&gt;Thorny&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Your move speed is increased by 1.</t>
@@ -1532,6 +1151,607 @@
   </si>
   <si>
     <t>At the end of your turn, if you did not move, gain up to 4 tempct.</t>
+  </si>
+  <si>
+    <t>Emit an inferno of fire, all other beings within 3 hexes take 7 damage.
+&lt;br&gt;You and all adjacent beings suffer the &lt;b&gt;Burning&lt;/b&gt; status.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Breathe Fire: &lt;/b&gt;3 AP + weirdT</t>
+  </si>
+  <si>
+    <t>Your move speed is reduced by 1.
+&lt;br&gt;You take 1 less damage from all sources.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Furnace&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduce damage taken by 1 and your move speed by 2. </t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Stone Flesh&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Reduce damage from non-adjacent beings to 0.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Impervious Plates&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Effects cannot move you, only the move action will cause you to move.
+&lt;br&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Behemoth&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Remove an infected token from a being, and use one of your abilities spending their tokens.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Feast&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Through fire&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Fire and Burning give you temporary composure instead of dealing damage.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;Passive- &lt;b&gt;Enflamed:&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Infect&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>At the start of your turn, gain 1 temporary composure for each infected being including you.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Flame geysers&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>At the start of each turn, gain the &lt;b&gt;Burning&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>At the start of your turn, if you have less than 4 limbs equipped, draw and equip a limb.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Generative&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Adaptive becomes a copy of any Limb or Impression in play, except it also retains the &lt;b&gt;Mimic&lt;/b&gt; ability. If it would be destroyed, so is Adaptive.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Mimic: WeirdT + 1AP&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Your attacks gain the crit option:
+&lt;br&gt;&lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
+  </si>
+  <si>
+    <t>Gain the crit option:
+&lt;br&gt;&lt;b&gt;Infect:&lt;/b&gt; Spend one chargeT, target takes the chargeT and is infected.</t>
+  </si>
+  <si>
+    <t>chargebig X 4</t>
+  </si>
+  <si>
+    <t>You may clear a status effect (except exhausted) to refresh a token of your choice.</t>
+  </si>
+  <si>
+    <t>Your second attack each turn costs 1 less AP</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Dual Wielder&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>You may use crit options available to any of your limbs on all attacks.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Creative Duellist&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>When you make an attack, you may move 2 tiles before attacking</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Charger&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>At the start of your turn, if you have an equal number of unspent tokens in each stat, refresh two spent stat tokens.
+&lt;br&gt;&lt;br&gt;They must be different tokens.</t>
+  </si>
+  <si>
+    <t>Once per turn you may suffer a wound to a stat of your choice to refresh 2 spent tokens in that stat.</t>
+  </si>
+  <si>
+    <t>While you are unwounded, gain 1 additional AP at the start of each turn.</t>
+  </si>
+  <si>
+    <t>When an enemy moves into an adjacent tile, you may take a free move action immediately.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Flee:&lt;/b&gt; jazzT</t>
+  </si>
+  <si>
+    <t>Whenever you gain temporary composure, you may move that many hexes.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; On the Move&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>At the start of your first turn, draw an impression and equip it over creative. &lt;br&gt;At the end of your each turn, you &lt;b&gt;may&lt;/b&gt; discard that impression to draw and equip a new impression over creative.</t>
+  </si>
+  <si>
+    <t>The first time a being dies in combat, draw 4 impressions and equip 2 of them.</t>
+  </si>
+  <si>
+    <t>Replenish a jazzt or flesht</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Burst:&lt;/b&gt; chargeT or weirdT</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Mold Earth: weirdTweirdT&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Create a large pillar Hex1b in target empty location.&lt;br&gt;&lt;br&gt;Pillars can be climbed by spending 3 AP or jazzT.</t>
+  </si>
+  <si>
+    <t>Whenever you spend weirdt, create a small pillar Hex1a in target empty hex.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; World Sculptor&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Ignore the effects of an ability with weirdt in its cost. (Even if no weirdT was spent).</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;What?:&lt;/b&gt; 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Replace your  &lt;span style="color:#3366cc"&gt;&lt;strong&gt;Weird&lt;/strong&gt;&lt;/span&gt; with &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;. You cannot spend weirdt any more.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; Normality&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>You can't be affected by the &lt;b&gt;Targeted Strike&lt;/b&gt; critical effect.</t>
+  </si>
+  <si>
+    <t>Your attacks have the crit option:&lt;br&gt;&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to 1 temporary composure.</t>
+  </si>
+  <si>
+    <t>Gain the &lt;b&gt;Well rested&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;A cup of tea:&lt;/b&gt; 1 AP + 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Declare target being your ally (if they consent), you both win if you are the only beings left in the room. You may only use this ability if 4 players are alive.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Alliance:&lt;/b&gt; 3 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;i&gt;No standoffs&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>After any die is rolled by any being you can see, you may force it to be re-rolled after seeing the result.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Change of Luck: chargeT&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Your attacks have the crit option&lt;br&gt;&lt;b&gt;Imbue:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; Magic Touch&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>During map creation, search the boons deck for any card. You may place this on the map in addition to your allotted terrain cards.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; Treasure!&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Whenever a 12 is rolled by any being during the game, replenish 1 spent stat token of your choice.</t>
+  </si>
+  <si>
+    <t>Whenever you would give another creature temporary composure, you may deal that much damage instead</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Twisted Kindness&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Give yourself and an ally up to 1 temporary composure</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Cackle:&lt;/b&gt; WeirdT</t>
+  </si>
+  <si>
+    <t>Put a counter on a limb of target being. The next time that limb deals damage, it deals 2 less. This doesn't stack.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Apathy&lt;/b&gt;: WeirdT</t>
+  </si>
+  <si>
+    <t>At the stat of combat, gain the &lt;b&gt;Portent&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Fatebender&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>At the beginning of combat secretly choose the next being to die and write it down. If you are correct, gain the &lt;b&gt;Portent&lt;/b&gt; status and repeat this ability</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Uncanny&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>You and any number of target allies gain up to 3 temporary composure.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Rally Song:&lt;/b&gt; 2 AP or weirdT</t>
+  </si>
+  <si>
+    <t>Offer a deal to a player. If they accept they gain one temporary stat token. &lt;br&gt;If they then break the deal, they take 8 damage.
+&lt;br&gt;If they reject the deal, you gain the temporary stat token.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Pact&lt;/b&gt;: 1 AP + WeirdT</t>
+  </si>
+  <si>
+    <t>Take a move action.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Dash: jazzt&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Mark a target, your attacks against marked target deal +1 damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Slander:&lt;/b&gt; 1AP + WeirdT</t>
+  </si>
+  <si>
+    <t>Whenever you spend a weirdt, all marked targets lose 1 composure, down to a minimum of 1.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; Vulgarity&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>When you take the &lt;b&gt;cower&lt;/b&gt; reaction, you can reduce damage taken by 2 instead of 1</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Inhale&lt;br&gt;&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exhale:&lt;/b&gt; Remove all charget</t>
+  </si>
+  <si>
+    <t>At the end of your turn, for each unspent action point add charget to this card, up to max of your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt;.</t>
+  </si>
+  <si>
+    <t>Gain 1 AP for each charget removed. This turn inhale won't trigger.</t>
+  </si>
+  <si>
+    <t>You and up to 1 adjacent being restore 1 wound.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Good Clay:&lt;/b&gt; weirdtweirdt or 2 AP + weirdT</t>
+  </si>
+  <si>
+    <t>Whenever you critically hit, restore 2 composure or gain up to 2 temporary composure.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Relish in battle&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Whenever you spend weirdt, you and up to 1 target ally gain up to 1 temporary composure.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Aura of Earth&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Re-roll an attack roll you have made.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Double down:&lt;/b&gt; jazzTjazzT</t>
+  </si>
+  <si>
+    <t>When you take the &lt;b&gt;reposition&lt;/b&gt; reaction you can move your speed instead of 1 hex.</t>
+  </si>
+  <si>
+    <t>Create a 3 hex area of darkness Hex1b&lt;br&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only crit on a 12.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Billowing Dark:&lt;/b&gt; 1 AP + weirdT</t>
+  </si>
+  <si>
+    <t>Your attacks deal bonus damage equal to the number of &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt; wounds you have.</t>
+  </si>
+  <si>
+    <t>When target ally takes damage, reduce that damage by 2, activate only once per instance of damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Protect&lt;/b&gt;: FleshT or WeirdT</t>
+  </si>
+  <si>
+    <t>Terrain that does not block movement does not block your line of sight.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Creature of the Shadows&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>When you would take a status effect (except exhausted), ignore it instead.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Unfazed:&lt;/b&gt; WeirdT</t>
+  </si>
+  <si>
+    <t>Add your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt; to the range of your next melee attack this turn.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Secret Technique:&lt;/b&gt; 1AP or weirdT</t>
+  </si>
+  <si>
+    <t>Your attacks have the crit option:&lt;br&gt;&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Pressure Points&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whenever you would heal or refresh a token, heal or refresh twice as many. </t>
+  </si>
+  <si>
+    <t>After taking damage, you may activate this to swap places with any being.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Switcheroo:&lt;/b&gt; 1 AP + weirdT</t>
+  </si>
+  <si>
+    <t>When you are non-lethally wounded, ignore the wound.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects from enemy abilities and terrain cannot reduce your movement speed. </t>
+  </si>
+  <si>
+    <t>&lt;i&gt; &lt;b&gt;Sure Footed&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Gain the &lt;b&gt;Well Rested&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Overexert:&lt;/b&gt; Gain &lt;b&gt;Exhausted&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Push Through Pain:&lt;/b&gt; JazzT +FleshT +weirdT</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Precise&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4 , Ranged&lt;/b&gt;&lt;br&gt;Ignores damage reduction effects.</t>
+  </si>
+  <si>
+    <t>Place the slab down on an adjacent hex. It extends straight on each side to become a three hex wall, if there is space. This wall blocks vision and is indestructible.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Wall of Splendor: &lt;/b&gt;1 AP</t>
+  </si>
+  <si>
+    <t>Pick up a deployed painted slab, any adjacent being can do this.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Reclaim: &lt;/b&gt;3 AP or fleshtfleshtfleshT</t>
+  </si>
+  <si>
+    <t>&lt;b&gt; Nip:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Restrain: &lt;/b&gt;Inflict the &lt;b&gt;Entangled&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Volley: 2 AP &lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;&lt;br&gt;You take 1 damage when you use this attack, this damage cannot be reduced.</t>
+  </si>
+  <si>
+    <t>Place a 1 hex sized heartstone on an adjacent hex. It will break if it takes damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Embed:&lt;/b&gt; weirdt</t>
+  </si>
+  <si>
+    <t>While there is at least 1 heartstone on the map, you gain up to 3 temporary composure at the end of your turn.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt;Living Rythm&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Place a &lt;b&gt;crystal spire&lt;/b&gt; on an adjacent hex, it has a two hex radius aura, blocks line of sight, and is &lt;b&gt;destructible&lt;/b&gt;.&lt;br&gt;Whiskey_Xplo</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sprout Spire:&lt;/b&gt; 2 AP + (weirdt or charget)</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Throw: &lt;/b&gt;1 AP + charget</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;, Ranged.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Recharge this item.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Rummage:&lt;/b&gt; 3 AP + fleshT</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Thump: &lt;/b&gt;2 AP</t>
+  </si>
+  <si>
+    <t>Clear an adjacent hex of any terrain. This can cause beings to fall if they were on top of it.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Dig:&lt;/b&gt; 1 AP or fleshT</t>
+  </si>
+  <si>
+    <t>Other beings that start their turn inside a &lt;b&gt;crystal spire&lt;/b&gt; aura or enter it take 3 damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt; Yoink:&lt;/b&gt; 1 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 0, Ranged.&lt;/b&gt;&lt;br&gt;Pull the target to an adjacent hex on a hit</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Entangle:&lt;/b&gt; Inflict the &lt;b&gt;Entangled&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Ping!: &lt;/b&gt;1 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 2, Reach.&lt;/b&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 1, Reach.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Dash:&lt;/b&gt; Take a move action for free.&lt;br&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Prod:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4, Reach.&lt;/b&gt;&lt;br&gt;This can only target non-adjacent beings.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Geyser:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 2, Reach.&lt;/b&gt;&lt;br&gt;On a hit, remove all &lt;b&gt;temporary composure&lt;/b&gt; from the target before dealing damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack cannot be reduced.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 7, Reach.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Flameball:&lt;/b&gt; 3 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Winch: 1 AP&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Add chargeT to this card. Activate only once each turn.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Scour:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 3 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4, Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 5 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 1 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Inflict the &lt;b&gt;Cursed&lt;/b&gt; status effect on a target in Melee.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 8 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 6 , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Damage = 3 , Melee.&lt;br&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 2 , Melee.&lt;/b&gt;On a hit, you may destroy this card to destroy any equipped Limb or Impression from the target.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = hexes moved, Melee.&lt;/b&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br&gt; hornshexes</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 2 , Melee.&lt;/b&gt;On a hit, the target is pushed back hexes equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4 , Melee.&lt;br&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 1 , Melee.&lt;/b&gt;This attack always hits, do not roll.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 8, Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt; , Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Damage =4, Melee.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Lance: &lt;/b&gt;2 AP</t>
+  </si>
+  <si>
+    <t>Whenever a being leaves your attack range, you may spend jazzT to make an attack with any limb against them. If the attack would cost 3 or more AP, become &lt;b&gt;exhausted&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;&lt;b&gt; Snatch&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Release:&lt;/b&gt; 5 x chargeT</t>
+  </si>
+  <si>
+    <t>Automatically activates upon reaching 5 charget.&lt;br&gt;Deal 8 damage to all beings in a straight line from you. No attack roll required.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Smash:&lt;/b&gt; 3 AP + comptcompt</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 5, Ranged.&lt;/b&gt;&lt;br&gt;On a hit, inflict the &lt;b&gt;burning&lt;/b&gt; status effect.&lt;br&gt;On a miss, inflict the &lt;b&gt;burning&lt;/b&gt; status effect on you.</t>
+  </si>
+  <si>
+    <t>Damage = 3 , Reach.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Venom: &lt;/b&gt;Inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect.</t>
+  </si>
+  <si>
+    <t>Use the Lance attack on a being that has entered your attack range for the first time on their turn.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Jab: &lt;/b&gt;jazzt</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4 , Reach.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Lash Out:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t>Fill 3 target connected empty hexes with a willow tree which blocks movement and vision. Each hex can be individually destroyed by dealing damage.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 5, Melee.&lt;/b&gt;&lt;br&gt;Inflict the &lt;b&gt;Exhausted&lt;/b&gt; status effect on a hit.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Anhidonia:&lt;/b&gt; 3 AP</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Summon Saplings:&lt;/b&gt; weirdtweirdT</t>
   </si>
 </sst>
 </file>
@@ -2345,10 +2565,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:AC198" totalsRowShown="0" dataDxfId="44">
-  <autoFilter ref="A1:AC198" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC198">
-    <sortCondition ref="B1:B198"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:AC196" totalsRowShown="0" dataDxfId="44">
+  <autoFilter ref="A1:AC196" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC196">
+    <sortCondition ref="B1:B196"/>
   </sortState>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name" dataDxfId="43"/>
@@ -2583,7 +2803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC198"/>
+  <dimension ref="A1:AC196"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2698,7 +2918,7 @@
     </row>
     <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>47</v>
@@ -2711,10 +2931,10 @@
         <v>36</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="H2" s="7">
         <v>4</v>
@@ -2723,10 +2943,10 @@
         <v>36</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="17"/>
@@ -2786,7 +3006,7 @@
     </row>
     <row r="3" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>47</v>
@@ -2799,10 +3019,10 @@
         <v>36</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2811,10 +3031,10 @@
         <v>36</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>325</v>
+        <v>266</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="L3" s="7">
         <v>9</v>
@@ -2823,10 +3043,10 @@
         <v>36</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>328</v>
+        <v>269</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -2872,13 +3092,13 @@
     </row>
     <row r="4" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -2887,10 +3107,10 @@
         <v>36</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>331</v>
+        <v>272</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>330</v>
+        <v>271</v>
       </c>
       <c r="H4" s="7">
         <v>3</v>
@@ -2899,10 +3119,10 @@
         <v>11</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>332</v>
+        <v>273</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="17"/>
@@ -2910,7 +3130,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="12" t="s">
-        <v>426</v>
+        <v>312</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -2952,15 +3172,15 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>291</v>
+        <v>235</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -2969,22 +3189,22 @@
         <v>11</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>334</v>
+        <v>275</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>336</v>
+        <v>277</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="17"/>
@@ -2992,7 +3212,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="13" t="s">
-        <v>425</v>
+        <v>311</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -3011,15 +3231,15 @@
       </c>
       <c r="X5" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>5.0100000000000007</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y5" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.8900000000000006</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z5" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.61</v>
+        <v>5.12</v>
       </c>
       <c r="AA5" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -3036,7 +3256,7 @@
     </row>
     <row r="6" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
@@ -3049,10 +3269,10 @@
         <v>36</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="17"/>
@@ -3064,7 +3284,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="14" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -3108,7 +3328,7 @@
     </row>
     <row r="7" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>47</v>
@@ -3121,10 +3341,10 @@
         <v>36</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="H7" s="7">
         <v>6</v>
@@ -3133,10 +3353,10 @@
         <v>11</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="17"/>
@@ -3186,7 +3406,7 @@
     </row>
     <row r="8" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>47</v>
@@ -3199,10 +3419,10 @@
         <v>36</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>346</v>
+        <v>284</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>441</v>
+        <v>325</v>
       </c>
       <c r="H8" s="7">
         <v>5</v>
@@ -3211,10 +3431,10 @@
         <v>36</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>354</v>
+        <v>291</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>423</v>
+        <v>309</v>
       </c>
       <c r="L8" s="7">
         <v>9</v>
@@ -3223,10 +3443,10 @@
         <v>36</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>436</v>
+        <v>321</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
@@ -3272,7 +3492,7 @@
     </row>
     <row r="9" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>47</v>
@@ -3285,10 +3505,10 @@
         <v>36</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>347</v>
+        <v>285</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="H9" s="7">
         <v>4</v>
@@ -3297,10 +3517,10 @@
         <v>36</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>355</v>
+        <v>292</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>424</v>
+        <v>310</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="17"/>
@@ -3350,13 +3570,13 @@
     </row>
     <row r="10" spans="1:29" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="D10" s="7">
         <v>1</v>
@@ -3365,10 +3585,10 @@
         <v>36</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>440</v>
+        <v>324</v>
       </c>
       <c r="H10" s="7">
         <v>5</v>
@@ -3377,10 +3597,10 @@
         <v>36</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>356</v>
+        <v>293</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>439</v>
+        <v>323</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="17"/>
@@ -3428,15 +3648,15 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="D11" s="7">
         <v>1</v>
@@ -3445,10 +3665,10 @@
         <v>36</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>442</v>
+        <v>326</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
@@ -3457,10 +3677,10 @@
         <v>36</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>443</v>
+        <v>327</v>
       </c>
       <c r="L11" s="7">
         <v>7</v>
@@ -3469,10 +3689,10 @@
         <v>11</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>437</v>
+        <v>322</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -3518,7 +3738,7 @@
     </row>
     <row r="12" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>47</v>
@@ -3531,10 +3751,10 @@
         <v>36</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>419</v>
+        <v>305</v>
       </c>
       <c r="H12" s="7">
         <v>6</v>
@@ -3543,10 +3763,10 @@
         <v>36</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>444</v>
+        <v>328</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="17"/>
@@ -3596,7 +3816,7 @@
     </row>
     <row r="13" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>47</v>
@@ -3609,10 +3829,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>352</v>
+        <v>289</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>420</v>
+        <v>306</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
@@ -3621,10 +3841,10 @@
         <v>36</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>447</v>
+        <v>331</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>448</v>
+        <v>332</v>
       </c>
       <c r="L13" s="7">
         <v>8</v>
@@ -3633,10 +3853,10 @@
         <v>36</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>473</v>
+        <v>353</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>472</v>
+        <v>352</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -3682,13 +3902,13 @@
     </row>
     <row r="14" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="D14" s="7">
         <v>1</v>
@@ -3697,10 +3917,10 @@
         <v>11</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>421</v>
+        <v>307</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
@@ -3709,10 +3929,10 @@
         <v>11</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>446</v>
+        <v>330</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>445</v>
+        <v>329</v>
       </c>
       <c r="L14" s="7">
         <v>7</v>
@@ -3721,10 +3941,10 @@
         <v>36</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>471</v>
+        <v>351</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>470</v>
+        <v>350</v>
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -3770,7 +3990,7 @@
     </row>
     <row r="15" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>47</v>
@@ -3783,10 +4003,10 @@
         <v>36</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>422</v>
+        <v>308</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>429</v>
+        <v>315</v>
       </c>
       <c r="H15" s="7">
         <v>4</v>
@@ -3842,13 +4062,13 @@
     </row>
     <row r="16" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>476</v>
+        <v>356</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -3857,10 +4077,10 @@
         <v>36</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>431</v>
+        <v>316</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="H16" s="7">
         <v>3</v>
@@ -3869,10 +4089,10 @@
         <v>36</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>457</v>
+        <v>339</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>475</v>
+        <v>355</v>
       </c>
       <c r="L16" s="7">
         <v>9</v>
@@ -3881,10 +4101,10 @@
         <v>36</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>469</v>
+        <v>349</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>468</v>
+        <v>348</v>
       </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -3930,7 +4150,7 @@
     </row>
     <row r="17" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>47</v>
@@ -3943,10 +4163,10 @@
         <v>11</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>433</v>
+        <v>318</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>432</v>
+        <v>317</v>
       </c>
       <c r="H17" s="7">
         <v>3</v>
@@ -3955,10 +4175,10 @@
         <v>11</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>459</v>
+        <v>341</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>458</v>
+        <v>340</v>
       </c>
       <c r="L17" s="7">
         <v>6</v>
@@ -3967,10 +4187,10 @@
         <v>36</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>467</v>
+        <v>347</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>466</v>
+        <v>346</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -4016,7 +4236,7 @@
     </row>
     <row r="18" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>47</v>
@@ -4029,10 +4249,10 @@
         <v>36</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>435</v>
+        <v>320</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>434</v>
+        <v>319</v>
       </c>
       <c r="H18" s="7">
         <v>8</v>
@@ -4041,10 +4261,10 @@
         <v>11</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>461</v>
+        <v>343</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>460</v>
+        <v>342</v>
       </c>
       <c r="L18" s="7"/>
       <c r="M18" s="17"/>
@@ -4094,7 +4314,7 @@
     </row>
     <row r="19" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>47</v>
@@ -4107,22 +4327,22 @@
         <v>36</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>450</v>
+        <v>335</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>334</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>462</v>
+        <v>345</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="17"/>
@@ -4147,15 +4367,15 @@
       </c>
       <c r="X19" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.03</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y19" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.91</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z19" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.63</v>
+        <v>5.12</v>
       </c>
       <c r="AA19" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4170,37 +4390,39 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="D20" s="7">
         <v>1</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>36</v>
+      <c r="E20" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>453</v>
+        <v>336</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>452</v>
+        <v>357</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>36</v>
+        <v>9.6</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>465</v>
+        <v>337</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>464</v>
+        <v>338</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="17"/>
@@ -4225,15 +4447,15 @@
       </c>
       <c r="X20" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>6.774</v>
       </c>
       <c r="Y20" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>6.6539999999999999</v>
       </c>
       <c r="Z20" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>7.3739999999999997</v>
       </c>
       <c r="AA20" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4248,44 +4470,50 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="135" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="7">
         <v>1</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>11</v>
+      <c r="E21" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>454</v>
+        <v>359</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>477</v>
+        <v>358</v>
       </c>
       <c r="H21" s="7">
-        <v>9.6</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>455</v>
+        <v>361</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="7"/>
+        <v>360</v>
+      </c>
+      <c r="L21" s="7">
+        <v>6</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>363</v>
+      </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
@@ -4305,37 +4533,39 @@
       </c>
       <c r="X21" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.774</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y21" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.6539999999999999</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z21" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>7.3739999999999997</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA21" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>5.2100000000000009</v>
       </c>
       <c r="AB21" s="11">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>5.0900000000000007</v>
       </c>
       <c r="AC21" s="19">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>5.8100000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="7"/>
+      <c r="C22" s="7" t="s">
+        <v>259</v>
+      </c>
       <c r="D22" s="7">
         <v>1</v>
       </c>
@@ -4343,34 +4573,34 @@
         <v>36</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>479</v>
+        <v>369</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>478</v>
+        <v>368</v>
       </c>
       <c r="H22" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>481</v>
+        <v>371</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>480</v>
+        <v>370</v>
       </c>
       <c r="L22" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" s="17" t="s">
         <v>36</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>482</v>
+        <v>373</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>483</v>
+        <v>372</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -4391,70 +4621,80 @@
       </c>
       <c r="X22" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>4.03</v>
       </c>
       <c r="Y22" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>3.91</v>
       </c>
       <c r="Z22" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>4.63</v>
       </c>
       <c r="AA22" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>5.2100000000000009</v>
+        <v>5.7000000000000011</v>
       </c>
       <c r="AB22" s="11">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>5.0900000000000007</v>
+        <v>5.580000000000001</v>
       </c>
       <c r="AC22" s="19">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>5.8100000000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>309</v>
+        <v>6.3000000000000007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>316</v>
-      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="7">
         <v>1</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="H23" s="7"/>
+      <c r="F23" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="7">
+        <v>4</v>
+      </c>
       <c r="I23" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="17"/>
+      <c r="J23" s="17" t="s">
+        <v>179</v>
+      </c>
       <c r="K23" s="7" t="s">
-        <v>386</v>
+        <v>49</v>
       </c>
       <c r="L23" s="7"/>
-      <c r="M23" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="17"/>
-      <c r="O23" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7">
+        <v>2.96</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="R23" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="S23" s="7">
+        <v>-0.12</v>
+      </c>
+      <c r="T23" s="7">
+        <v>-0.6</v>
+      </c>
       <c r="U23" s="11">
         <f>Table3[[#This Row],[E1Y]]+T$2</f>
         <v>2.36</v>
@@ -4469,15 +4709,15 @@
       </c>
       <c r="X23" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y23" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z23" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA23" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4492,9 +4732,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>46</v>
+    <row r="24" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>47</v>
@@ -4504,45 +4744,35 @@
         <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>50</v>
+        <v>11</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>364</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>214</v>
+        <v>367</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>49</v>
+        <v>366</v>
       </c>
       <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="7">
-        <v>2.96</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="R24" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="S24" s="7">
-        <v>-0.12</v>
-      </c>
-      <c r="T24" s="7">
-        <v>-0.6</v>
-      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
       <c r="U24" s="11">
         <f>Table3[[#This Row],[E1Y]]+T$2</f>
         <v>2.36</v>
@@ -4557,15 +4787,15 @@
       </c>
       <c r="X24" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.03</v>
+        <v>5.5000000000000009</v>
       </c>
       <c r="Y24" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.91</v>
+        <v>5.3800000000000008</v>
       </c>
       <c r="Z24" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.63</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="AA24" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4580,34 +4810,52 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7" t="s">
+        <v>390</v>
+      </c>
       <c r="D25" s="7">
         <v>1</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="17"/>
+      <c r="F25" s="17" t="s">
+        <v>379</v>
+      </c>
       <c r="G25" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
+        <v>389</v>
+      </c>
+      <c r="H25" s="7">
+        <v>5</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>380</v>
+      </c>
       <c r="K25" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="7"/>
+        <v>381</v>
+      </c>
+      <c r="L25" s="7">
+        <v>9</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>374</v>
+      </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -4627,32 +4875,32 @@
       </c>
       <c r="X25" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y25" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z25" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA25" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.6800000000000006</v>
       </c>
       <c r="AB25" s="11">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.5600000000000005</v>
       </c>
       <c r="AC25" s="19">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>47</v>
@@ -4661,26 +4909,38 @@
       <c r="D26" s="7">
         <v>1</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="17"/>
+      <c r="E26" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>378</v>
+      </c>
       <c r="G26" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="H26" s="7">
+        <v>5</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="L26" s="7">
+        <v>8</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="O26" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N26" s="17"/>
-      <c r="O26" s="7" t="s">
-        <v>320</v>
       </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
@@ -4701,32 +4961,32 @@
       </c>
       <c r="X26" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y26" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z26" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA26" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.19</v>
       </c>
       <c r="AB26" s="11">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.07</v>
       </c>
       <c r="AC26" s="19">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>47</v>
@@ -4738,22 +4998,28 @@
       <c r="E27" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="17" t="s">
+        <v>385</v>
+      </c>
       <c r="G27" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
+        <v>384</v>
+      </c>
+      <c r="H27" s="7">
+        <v>6</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>328</v>
+      </c>
       <c r="K27" s="7" t="s">
-        <v>390</v>
+        <v>261</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
-      <c r="O27" s="7" t="s">
-        <v>391</v>
-      </c>
+      <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
@@ -4773,15 +5039,15 @@
       </c>
       <c r="X27" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y27" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z27" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.61</v>
       </c>
       <c r="AA27" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4796,35 +5062,33 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>312</v>
+    <row r="28" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7">
         <v>1</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="17"/>
+      <c r="E28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>387</v>
+      </c>
       <c r="G28" s="17" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J28" s="17"/>
-      <c r="K28" s="7" t="s">
-        <v>319</v>
-      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
       <c r="L28" s="7"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
@@ -4868,28 +5132,38 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="7"/>
+      <c r="C29" s="17"/>
       <c r="D29" s="7">
         <v>1</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="17"/>
+      <c r="E29" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>393</v>
+      </c>
       <c r="G29" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
+        <v>392</v>
+      </c>
+      <c r="H29" s="7">
+        <v>4</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>394</v>
+      </c>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
@@ -4913,15 +5187,15 @@
       </c>
       <c r="X29" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y29" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z29" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA29" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -4936,30 +5210,30 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="17"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="7">
         <v>1</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17" t="s">
-        <v>400</v>
+      <c r="F30" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>396</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
-      <c r="K30" s="7" t="s">
-        <v>401</v>
-      </c>
+      <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -5006,9 +5280,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>53</v>
@@ -5020,9 +5294,11 @@
       <c r="E31" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="7"/>
+      <c r="F31" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="G31" s="7" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5074,9 +5350,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>53</v>
@@ -5088,9 +5364,11 @@
       <c r="E32" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="G32" s="7" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5142,9 +5420,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>53</v>
@@ -5156,9 +5434,11 @@
       <c r="E33" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="7"/>
+      <c r="F33" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="G33" s="7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5210,9 +5490,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>53</v>
@@ -5222,19 +5502,21 @@
         <v>1</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7" t="s">
-        <v>404</v>
+        <v>56</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>401</v>
       </c>
       <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
@@ -5278,9 +5560,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>53</v>
@@ -5289,10 +5571,14 @@
       <c r="D35" s="7">
         <v>1</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="E35" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G35" s="17" t="s">
-        <v>230</v>
+        <v>405</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="17"/>
@@ -5346,7 +5632,7 @@
     </row>
     <row r="36" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>53</v>
@@ -5358,14 +5644,24 @@
       <c r="E36" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="17"/>
+      <c r="F36" s="17" t="s">
+        <v>300</v>
+      </c>
       <c r="G36" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="7"/>
+        <v>301</v>
+      </c>
+      <c r="H36" s="7">
+        <v>6</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="L36" s="7"/>
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
@@ -5389,15 +5685,15 @@
       </c>
       <c r="X36" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y36" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z36" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.61</v>
       </c>
       <c r="AA36" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -5412,9 +5708,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>53</v>
@@ -5427,17 +5723,15 @@
         <v>36</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>393</v>
+        <v>302</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
-      <c r="K37" s="7" t="s">
-        <v>406</v>
-      </c>
+      <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
@@ -5486,7 +5780,7 @@
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>53</v>
@@ -5499,10 +5793,10 @@
         <v>36</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>395</v>
+        <v>304</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="17"/>
@@ -5554,25 +5848,27 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="7"/>
+      <c r="C39" s="7" t="s">
+        <v>200</v>
+      </c>
       <c r="D39" s="7">
         <v>1</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>36</v>
+      <c r="E39" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="17"/>
@@ -5624,30 +5920,38 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="120" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="C40" s="7"/>
       <c r="D40" s="7">
         <v>1</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="17"/>
+      <c r="F40" s="17" t="s">
+        <v>409</v>
+      </c>
       <c r="G40" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="7"/>
+        <v>410</v>
+      </c>
+      <c r="H40" s="7">
+        <v>7</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="L40" s="7"/>
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
@@ -5671,15 +5975,15 @@
       </c>
       <c r="X40" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.5000000000000009</v>
       </c>
       <c r="Y40" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>5.3800000000000008</v>
       </c>
       <c r="Z40" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="AA40" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -5694,9 +5998,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>53</v>
@@ -5705,25 +6009,23 @@
       <c r="D41" s="7">
         <v>1</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="17"/>
+      <c r="E41" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G41" s="17" t="s">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
-      <c r="K41" s="7" t="s">
-        <v>239</v>
-      </c>
+      <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
-      <c r="O41" s="7" t="s">
-        <v>382</v>
-      </c>
+      <c r="O41" s="7"/>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
@@ -5766,9 +6068,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>240</v>
+    <row r="42" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>53</v>
@@ -5780,9 +6082,11 @@
       <c r="E42" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17" t="s">
-        <v>407</v>
+      <c r="F42" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>418</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="17"/>
@@ -5834,9 +6138,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>53</v>
@@ -5848,18 +6152,36 @@
       <c r="E43" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="17"/>
-      <c r="G43" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="7"/>
+      <c r="F43" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="H43" s="7">
+        <v>5</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="L43" s="7">
+        <v>9</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
@@ -5879,32 +6201,32 @@
       </c>
       <c r="X43" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y43" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z43" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA43" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.6800000000000006</v>
       </c>
       <c r="AB43" s="11">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.5600000000000005</v>
       </c>
       <c r="AC43" s="19">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>53</v>
@@ -5913,27 +6235,31 @@
       <c r="D44" s="7">
         <v>1</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="H44" s="7">
+        <v>7</v>
+      </c>
+      <c r="I44" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="7" t="s">
-        <v>243</v>
+      <c r="J44" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="L44" s="7"/>
-      <c r="M44" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="M44" s="17"/>
       <c r="N44" s="17"/>
-      <c r="O44" s="7" t="s">
-        <v>244</v>
-      </c>
+      <c r="O44" s="7"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
@@ -5953,15 +6279,15 @@
       </c>
       <c r="X44" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.5000000000000009</v>
       </c>
       <c r="Y44" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>5.3800000000000008</v>
       </c>
       <c r="Z44" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>6.1000000000000005</v>
       </c>
       <c r="AA44" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -5976,30 +6302,32 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="7"/>
+      <c r="C45" s="7" t="s">
+        <v>208</v>
+      </c>
       <c r="D45" s="7">
         <v>1</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="17"/>
+      <c r="E45" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>425</v>
+      </c>
       <c r="G45" s="17" t="s">
-        <v>246</v>
+        <v>424</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
-      <c r="K45" s="7" t="s">
-        <v>247</v>
-      </c>
+      <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
@@ -6046,30 +6374,38 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>249</v>
-      </c>
+      <c r="C46" s="7"/>
       <c r="D46" s="7">
         <v>1</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="H46" s="7">
+        <v>5</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>428</v>
+      </c>
       <c r="L46" s="7"/>
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
@@ -6093,15 +6429,15 @@
       </c>
       <c r="X46" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y46" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z46" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA46" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6116,9 +6452,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>53</v>
@@ -6130,18 +6466,16 @@
       <c r="E47" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="17"/>
-      <c r="G47" s="16" t="s">
-        <v>377</v>
+      <c r="F47" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>430</v>
       </c>
       <c r="H47" s="7"/>
-      <c r="I47" s="17" t="s">
-        <v>36</v>
-      </c>
+      <c r="I47" s="17"/>
       <c r="J47" s="17"/>
-      <c r="K47" s="9" t="s">
-        <v>409</v>
-      </c>
+      <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
@@ -6190,7 +6524,7 @@
     </row>
     <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>53</v>
@@ -6202,14 +6536,24 @@
       <c r="E48" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="17"/>
+      <c r="F48" s="17" t="s">
+        <v>432</v>
+      </c>
       <c r="G48" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="7"/>
+        <v>431</v>
+      </c>
+      <c r="H48" s="7">
+        <v>6</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="L48" s="7"/>
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
@@ -6233,15 +6577,15 @@
       </c>
       <c r="X48" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y48" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z48" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.61</v>
       </c>
       <c r="AA48" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6256,9 +6600,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>53</v>
@@ -6267,21 +6611,19 @@
       <c r="D49" s="7">
         <v>1</v>
       </c>
-      <c r="E49" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17" t="s">
-        <v>411</v>
+      <c r="E49" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>435</v>
       </c>
       <c r="H49" s="7"/>
-      <c r="I49" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="I49" s="17"/>
       <c r="J49" s="17"/>
-      <c r="K49" s="7" t="s">
-        <v>253</v>
-      </c>
+      <c r="K49" s="9"/>
       <c r="L49" s="7"/>
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
@@ -6328,32 +6670,42 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="7"/>
+      <c r="C50" s="9"/>
       <c r="D50" s="7">
         <v>1</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="17"/>
+      <c r="E50" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>438</v>
+      </c>
       <c r="G50" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="9"/>
+        <v>437</v>
+      </c>
+      <c r="H50" s="7">
+        <v>4</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>439</v>
+      </c>
       <c r="L50" s="7"/>
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
-      <c r="O50" s="7"/>
+      <c r="O50" s="9"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
@@ -6373,15 +6725,15 @@
       </c>
       <c r="X50" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y50" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z50" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA50" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6396,9 +6748,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>53</v>
@@ -6407,21 +6759,19 @@
       <c r="D51" s="7">
         <v>1</v>
       </c>
-      <c r="E51" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="17"/>
+      <c r="E51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>442</v>
+      </c>
       <c r="G51" s="16" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="H51" s="7"/>
-      <c r="I51" s="17" t="s">
-        <v>36</v>
-      </c>
+      <c r="I51" s="17"/>
       <c r="J51" s="17"/>
-      <c r="K51" s="9" t="s">
-        <v>374</v>
-      </c>
+      <c r="K51" s="9"/>
       <c r="L51" s="7"/>
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
@@ -6468,9 +6818,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>53</v>
@@ -6482,9 +6832,11 @@
       <c r="E52" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="17"/>
+      <c r="F52" s="17" t="s">
+        <v>444</v>
+      </c>
       <c r="G52" s="16" t="s">
-        <v>258</v>
+        <v>443</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="17"/>
@@ -6536,9 +6888,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>53</v>
@@ -6550,9 +6902,11 @@
       <c r="E53" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="17"/>
+      <c r="F53" s="17" t="s">
+        <v>446</v>
+      </c>
       <c r="G53" s="16" t="s">
-        <v>260</v>
+        <v>445</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="17"/>
@@ -6604,9 +6958,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>53</v>
@@ -6618,14 +6972,24 @@
       <c r="E54" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="17"/>
+      <c r="F54" s="17" t="s">
+        <v>448</v>
+      </c>
       <c r="G54" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="9"/>
+        <v>447</v>
+      </c>
+      <c r="H54" s="7">
+        <v>5</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>449</v>
+      </c>
       <c r="L54" s="7"/>
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
@@ -6649,15 +7013,15 @@
       </c>
       <c r="X54" s="11">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y54" s="11">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z54" s="11">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA54" s="11">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6674,7 +7038,7 @@
     </row>
     <row r="55" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>53</v>
@@ -6683,30 +7047,28 @@
       <c r="D55" s="7">
         <v>1</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="17"/>
+      <c r="E55" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G55" s="16" t="s">
-        <v>264</v>
+        <v>451</v>
       </c>
       <c r="H55" s="7"/>
-      <c r="I55" s="17" t="s">
-        <v>36</v>
-      </c>
+      <c r="I55" s="17"/>
       <c r="J55" s="17"/>
-      <c r="K55" s="9" t="s">
-        <v>384</v>
-      </c>
+      <c r="K55" s="9"/>
       <c r="L55" s="7"/>
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
       <c r="O55" s="9"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="R55" s="15"/>
+      <c r="S55" s="15"/>
+      <c r="T55" s="15"/>
       <c r="U55" s="11">
         <f>Table3[[#This Row],[E1Y]]+T$2</f>
         <v>2.36</v>
@@ -6744,9 +7106,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>53</v>
@@ -6758,63 +7120,73 @@
       <c r="E56" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F56" s="17"/>
+      <c r="F56" s="17" t="s">
+        <v>452</v>
+      </c>
       <c r="G56" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="9"/>
+        <v>454</v>
+      </c>
+      <c r="H56" s="7">
+        <v>6</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>455</v>
+      </c>
       <c r="L56" s="7"/>
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
       <c r="O56" s="9"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15"/>
-      <c r="S56" s="15"/>
-      <c r="T56" s="15"/>
-      <c r="U56" s="11">
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
+      <c r="U56" s="7">
         <f>Table3[[#This Row],[E1Y]]+T$2</f>
         <v>2.36</v>
       </c>
-      <c r="V56" s="11">
+      <c r="V56" s="7">
         <f>Table3[[#This Row],[E1TY]]+S$2</f>
         <v>2.2399999999999998</v>
       </c>
-      <c r="W56" s="11">
+      <c r="W56" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
         <v>2.96</v>
       </c>
-      <c r="X56" s="11">
+      <c r="X56" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="Y56" s="11">
+        <v>5.0100000000000007</v>
+      </c>
+      <c r="Y56" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
-      </c>
-      <c r="Z56" s="11">
+        <v>4.8900000000000006</v>
+      </c>
+      <c r="Z56" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
-      </c>
-      <c r="AA56" s="11">
+        <v>5.61</v>
+      </c>
+      <c r="AA56" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
         <v>2.2699999999999996</v>
       </c>
-      <c r="AB56" s="11">
+      <c r="AB56" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
         <v>2.1499999999999995</v>
       </c>
-      <c r="AC56" s="19">
+      <c r="AC56" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>53</v>
@@ -6823,20 +7195,26 @@
       <c r="D57" s="7">
         <v>1</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="H57" s="7">
+        <v>4</v>
+      </c>
+      <c r="I57" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="17"/>
-      <c r="G57" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J57" s="16"/>
+      <c r="J57" s="16" t="s">
+        <v>461</v>
+      </c>
       <c r="K57" s="9" t="s">
-        <v>267</v>
+        <v>460</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="17"/>
@@ -6861,15 +7239,15 @@
       </c>
       <c r="X57" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y57" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z57" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA57" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6886,7 +7264,7 @@
     </row>
     <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>53</v>
@@ -6895,20 +7273,26 @@
       <c r="D58" s="7">
         <v>1</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="17"/>
+      <c r="E58" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>459</v>
+      </c>
       <c r="G58" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J58" s="16"/>
+        <v>458</v>
+      </c>
+      <c r="H58" s="7">
+        <v>5</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>463</v>
+      </c>
       <c r="K58" s="9" t="s">
-        <v>378</v>
+        <v>462</v>
       </c>
       <c r="L58" s="7"/>
       <c r="M58" s="17"/>
@@ -6933,15 +7317,15 @@
       </c>
       <c r="X58" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y58" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z58" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA58" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -6956,9 +7340,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>53</v>
@@ -6970,18 +7354,16 @@
       <c r="E59" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F59" s="17"/>
+      <c r="F59" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G59" s="16" t="s">
-        <v>345</v>
+        <v>464</v>
       </c>
       <c r="H59" s="7"/>
-      <c r="I59" s="16" t="s">
-        <v>56</v>
-      </c>
+      <c r="I59" s="16"/>
       <c r="J59" s="16"/>
-      <c r="K59" s="9" t="s">
-        <v>271</v>
-      </c>
+      <c r="K59" s="9"/>
       <c r="L59" s="7"/>
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
@@ -7028,9 +7410,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>53</v>
@@ -7039,17 +7421,27 @@
       <c r="D60" s="7">
         <v>1</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="H60" s="7">
+        <v>9</v>
+      </c>
+      <c r="I60" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="9"/>
+      <c r="J60" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>470</v>
+      </c>
       <c r="L60" s="7"/>
       <c r="M60" s="17"/>
       <c r="N60" s="17"/>
@@ -7073,15 +7465,15 @@
       </c>
       <c r="X60" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.48</v>
       </c>
       <c r="Y60" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.36</v>
       </c>
       <c r="Z60" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.08</v>
       </c>
       <c r="AA60" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -7096,9 +7488,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>53</v>
@@ -7107,21 +7499,19 @@
       <c r="D61" s="7">
         <v>1</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="17"/>
+      <c r="E61" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G61" s="16" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="H61" s="7"/>
-      <c r="I61" s="16" t="s">
-        <v>36</v>
-      </c>
+      <c r="I61" s="16"/>
       <c r="J61" s="16"/>
-      <c r="K61" s="9" t="s">
-        <v>379</v>
-      </c>
+      <c r="K61" s="9"/>
       <c r="L61" s="7"/>
       <c r="M61" s="17"/>
       <c r="N61" s="17"/>
@@ -7168,9 +7558,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>53</v>
@@ -7180,11 +7570,13 @@
         <v>1</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F62" s="17"/>
+        <v>56</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>469</v>
+      </c>
       <c r="G62" s="16" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="16"/>
@@ -7236,9 +7628,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>53</v>
@@ -7250,9 +7642,11 @@
       <c r="E63" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F63" s="17"/>
+      <c r="F63" s="17" t="s">
+        <v>473</v>
+      </c>
       <c r="G63" s="16" t="s">
-        <v>276</v>
+        <v>472</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="16"/>
@@ -7306,7 +7700,7 @@
     </row>
     <row r="64" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>53</v>
@@ -7315,17 +7709,27 @@
       <c r="D64" s="7">
         <v>1</v>
       </c>
-      <c r="E64" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F64" s="17"/>
+      <c r="E64" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>475</v>
+      </c>
       <c r="G64" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="H64" s="7"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="9"/>
+        <v>474</v>
+      </c>
+      <c r="H64" s="7">
+        <v>4</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>476</v>
+      </c>
       <c r="L64" s="7"/>
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
@@ -7349,15 +7753,15 @@
       </c>
       <c r="X64" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y64" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z64" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA64" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -7372,9 +7776,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>53</v>
@@ -7383,21 +7787,19 @@
       <c r="D65" s="7">
         <v>1</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="17"/>
+      <c r="E65" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>304</v>
+      </c>
       <c r="G65" s="16" t="s">
-        <v>280</v>
+        <v>478</v>
       </c>
       <c r="H65" s="7"/>
-      <c r="I65" s="16" t="s">
-        <v>36</v>
-      </c>
+      <c r="I65" s="16"/>
       <c r="J65" s="16"/>
-      <c r="K65" s="9" t="s">
-        <v>416</v>
-      </c>
+      <c r="K65" s="9"/>
       <c r="L65" s="7"/>
       <c r="M65" s="17"/>
       <c r="N65" s="17"/>
@@ -7446,7 +7848,7 @@
     </row>
     <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>281</v>
+        <v>52</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>53</v>
@@ -7455,20 +7857,30 @@
       <c r="D66" s="7">
         <v>1</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H66" s="7">
+        <v>6</v>
+      </c>
+      <c r="I66" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="H66" s="7"/>
-      <c r="I66" s="16"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="9"/>
+      <c r="J66" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>148</v>
+      </c>
       <c r="L66" s="7"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="7"/>
       <c r="O66" s="9"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="7"/>
@@ -7489,15 +7901,15 @@
       </c>
       <c r="X66" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y66" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z66" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.61</v>
       </c>
       <c r="AA66" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -7512,9 +7924,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>52</v>
+        <v>229</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>53</v>
@@ -7523,30 +7935,22 @@
       <c r="D67" s="7">
         <v>1</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="17" t="s">
         <v>56</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>54</v>
+        <v>480</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H67" s="7">
-        <v>6</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>180</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="9"/>
       <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-      <c r="N67" s="7"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
       <c r="O67" s="9"/>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
@@ -7567,15 +7971,15 @@
       </c>
       <c r="X67" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>5.0100000000000007</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y67" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.8900000000000006</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="Z67" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.61</v>
+        <v>2.67</v>
       </c>
       <c r="AA67" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -7590,9 +7994,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>52</v>
+        <v>230</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>53</v>
@@ -7604,17 +8008,23 @@
       <c r="E68" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F68" s="17"/>
+      <c r="F68" s="17" t="s">
+        <v>486</v>
+      </c>
       <c r="G68" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="H68" s="7"/>
+        <v>481</v>
+      </c>
+      <c r="H68" s="7">
+        <v>4</v>
+      </c>
       <c r="I68" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J68" s="16"/>
+      <c r="J68" s="16" t="s">
+        <v>483</v>
+      </c>
       <c r="K68" s="9" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="L68" s="7"/>
       <c r="M68" s="17"/>
@@ -7639,15 +8049,15 @@
       </c>
       <c r="X68" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y68" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z68" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA68" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -7662,9 +8072,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>283</v>
+        <v>231</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>53</v>
@@ -7673,12 +8083,14 @@
       <c r="D69" s="7">
         <v>1</v>
       </c>
-      <c r="E69" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F69" s="17"/>
+      <c r="E69" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>485</v>
+      </c>
       <c r="G69" s="16" t="s">
-        <v>349</v>
+        <v>484</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="16"/>
@@ -7730,36 +8142,50 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="7">
         <v>1</v>
       </c>
-      <c r="E70" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F70" s="17"/>
-      <c r="G70" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J70" s="16"/>
+      <c r="E70" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="7">
+        <v>5</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K70" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="L70" s="7"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="17"/>
-      <c r="O70" s="9"/>
+        <v>297</v>
+      </c>
+      <c r="L70" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O70" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="P70" s="7"/>
       <c r="Q70" s="7"/>
       <c r="R70" s="7"/>
@@ -7779,54 +8205,66 @@
       </c>
       <c r="X70" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y70" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z70" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA70" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.9250000000000007</v>
       </c>
       <c r="AB70" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.8050000000000006</v>
       </c>
       <c r="AC70" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>7.5250000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>286</v>
+        <v>39</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="7">
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="17"/>
-      <c r="G71" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="H71" s="7"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="H71" s="7">
+        <v>9</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="L71" s="7">
+        <v>5</v>
+      </c>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
       <c r="O71" s="9"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
@@ -7847,32 +8285,32 @@
       </c>
       <c r="X71" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.48</v>
       </c>
       <c r="Y71" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.36</v>
       </c>
       <c r="Z71" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.08</v>
       </c>
       <c r="AA71" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>4.7200000000000006</v>
       </c>
       <c r="AB71" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AC71" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>6</v>
@@ -7881,39 +8319,31 @@
       <c r="D72" s="7">
         <v>1</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>9</v>
+      <c r="F72" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="H72" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="L72" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="M72" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="N72" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>169</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="9"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="7"/>
       <c r="R72" s="7"/>
@@ -7933,32 +8363,32 @@
       </c>
       <c r="X72" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y72" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z72" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>5.61</v>
       </c>
       <c r="AA72" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>6.9250000000000007</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB72" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>6.8050000000000006</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC72" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>7.5250000000000004</v>
+        <v>2.8699999999999997</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>6</v>
@@ -7968,25 +8398,25 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="H73" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>174</v>
+        <v>45</v>
       </c>
       <c r="L73" s="7">
         <v>5</v>
@@ -8013,15 +8443,15 @@
       </c>
       <c r="X73" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.48</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y73" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.36</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z73" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>7.08</v>
+        <v>5.12</v>
       </c>
       <c r="AA73" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8036,9 +8466,9 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>6</v>
@@ -8051,22 +8481,22 @@
         <v>11</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="H74" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
@@ -8091,15 +8521,15 @@
       </c>
       <c r="X74" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>5.0100000000000007</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y74" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.8900000000000006</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z74" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.61</v>
+        <v>5.12</v>
       </c>
       <c r="AA74" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8114,9 +8544,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>6</v>
@@ -8125,30 +8555,28 @@
       <c r="D75" s="7">
         <v>1</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>43</v>
+      <c r="E75" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>530</v>
       </c>
       <c r="H75" s="7">
-        <v>5</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>44</v>
+        <v>3</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>182</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L75" s="7">
-        <v>5</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
       <c r="O75" s="9"/>
@@ -8171,32 +8599,32 @@
       </c>
       <c r="X75" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y75" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z75" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA75" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>4.7200000000000006</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB75" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>4.6000000000000005</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC75" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>2.8699999999999997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>6</v>
@@ -8206,25 +8634,25 @@
         <v>1</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>128</v>
+        <v>527</v>
       </c>
       <c r="H76" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
@@ -8249,15 +8677,15 @@
       </c>
       <c r="X76" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>6.48</v>
       </c>
       <c r="Y76" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>6.36</v>
       </c>
       <c r="Z76" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>7.08</v>
       </c>
       <c r="AA76" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8274,7 +8702,7 @@
     </row>
     <row r="77" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>6</v>
@@ -8287,22 +8715,22 @@
         <v>34</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>131</v>
+        <v>298</v>
       </c>
       <c r="H77" s="7">
-        <v>3</v>
-      </c>
-      <c r="I77" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I77" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J77" s="16" t="s">
-        <v>217</v>
+      <c r="J77" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
@@ -8327,15 +8755,15 @@
       </c>
       <c r="X77" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y77" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z77" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>5.12</v>
       </c>
       <c r="AA77" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8350,9 +8778,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>6</v>
@@ -8362,25 +8790,25 @@
         <v>1</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="H78" s="7">
-        <v>9</v>
+        <v>114</v>
+      </c>
+      <c r="H78" s="17">
+        <v>5</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
@@ -8405,15 +8833,15 @@
       </c>
       <c r="X78" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.48</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y78" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.36</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z78" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>7.08</v>
+        <v>5.12</v>
       </c>
       <c r="AA78" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8428,9 +8856,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>6</v>
@@ -8443,22 +8871,22 @@
         <v>34</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>364</v>
+        <v>531</v>
       </c>
       <c r="H79" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
@@ -8483,15 +8911,15 @@
       </c>
       <c r="X79" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y79" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z79" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA79" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8506,9 +8934,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>6</v>
@@ -8518,30 +8946,38 @@
         <v>1</v>
       </c>
       <c r="E80" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="H80" s="17">
+        <v>3</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F80" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G80" s="16" t="s">
+      <c r="J80" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="L80" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="M80" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="H80" s="17">
-        <v>5</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J80" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="K80" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="9"/>
+      <c r="N80" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="P80" s="7"/>
       <c r="Q80" s="7"/>
       <c r="R80" s="7"/>
@@ -8561,32 +8997,32 @@
       </c>
       <c r="X80" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y80" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z80" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA80" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.9250000000000007</v>
       </c>
       <c r="AB80" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.8050000000000006</v>
       </c>
       <c r="AC80" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>7.5250000000000004</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>6</v>
@@ -8599,10 +9035,10 @@
         <v>34</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>157</v>
+        <v>529</v>
       </c>
       <c r="H81" s="7">
         <v>3</v>
@@ -8611,15 +9047,23 @@
         <v>11</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="K81" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L81" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="M81" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="N81" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="9"/>
+      <c r="O81" s="9" t="s">
+        <v>150</v>
+      </c>
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7"/>
@@ -8651,20 +9095,20 @@
       </c>
       <c r="AA81" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>6.9250000000000007</v>
       </c>
       <c r="AB81" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>6.8050000000000006</v>
       </c>
       <c r="AC81" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
+        <v>7.5250000000000004</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>6</v>
@@ -8674,38 +9118,22 @@
         <v>1</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="H82" s="17">
-        <v>3</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K82" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="L82" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="M82" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="N82" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O82" s="9" t="s">
-        <v>182</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="H82" s="7"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="9"/>
       <c r="P82" s="7"/>
       <c r="Q82" s="7"/>
       <c r="R82" s="7"/>
@@ -8725,73 +9153,67 @@
       </c>
       <c r="X82" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y82" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="Z82" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>2.67</v>
       </c>
       <c r="AA82" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>6.9250000000000007</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB82" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>6.8050000000000006</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC82" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>7.5250000000000004</v>
+        <v>2.8699999999999997</v>
       </c>
     </row>
     <row r="83" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="9" t="s">
+        <v>160</v>
+      </c>
       <c r="D83" s="7">
         <v>1</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="H83" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="K83" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="L83" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="M83" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="N83" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>183</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="9"/>
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7"/>
@@ -8811,32 +9233,32 @@
       </c>
       <c r="X83" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>4.03</v>
       </c>
       <c r="Y83" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>3.91</v>
       </c>
       <c r="Z83" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>4.63</v>
       </c>
       <c r="AA83" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>6.9250000000000007</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB83" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>6.8050000000000006</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC83" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>7.5250000000000004</v>
+        <v>2.8699999999999997</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>6</v>
@@ -8846,18 +9268,26 @@
         <v>1</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="H84" s="7"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9"/>
-      <c r="K84" s="9"/>
+        <v>534</v>
+      </c>
+      <c r="H84" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K84" s="9" t="s">
+        <v>151</v>
+      </c>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
@@ -8881,15 +9311,15 @@
       </c>
       <c r="X84" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.7250000000000005</v>
       </c>
       <c r="Y84" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.6050000000000004</v>
       </c>
       <c r="Z84" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.3250000000000002</v>
       </c>
       <c r="AA84" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8904,39 +9334,37 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>194</v>
-      </c>
+      <c r="C85" s="9"/>
       <c r="D85" s="7">
         <v>1</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>152</v>
+        <v>535</v>
       </c>
       <c r="H85" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="K85" s="9" t="s">
-        <v>155</v>
+        <v>536</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
@@ -8961,15 +9389,15 @@
       </c>
       <c r="X85" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.03</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y85" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.91</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z85" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.63</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA85" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -8984,14 +9412,14 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B86" s="7" t="s">
+    <row r="86" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="9"/>
+      <c r="C86" s="16"/>
       <c r="D86" s="7">
         <v>1</v>
       </c>
@@ -8999,27 +9427,19 @@
         <v>34</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H86" s="17">
-        <v>9.5</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="J86" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="K86" s="9" t="s">
-        <v>185</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="16"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
-      <c r="O86" s="9"/>
+      <c r="O86" s="16"/>
       <c r="P86" s="7"/>
       <c r="Q86" s="7"/>
       <c r="R86" s="7"/>
@@ -9039,15 +9459,15 @@
       </c>
       <c r="X86" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.7250000000000005</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y86" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.6050000000000004</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="Z86" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>7.3250000000000002</v>
+        <v>2.67</v>
       </c>
       <c r="AA86" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9062,9 +9482,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>6</v>
@@ -9077,22 +9497,22 @@
         <v>34</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>163</v>
+        <v>538</v>
       </c>
       <c r="H87" s="7">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="I87" s="9" t="s">
         <v>34</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>159</v>
+        <v>135</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>539</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
@@ -9117,15 +9537,15 @@
       </c>
       <c r="X87" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>6.2350000000000003</v>
       </c>
       <c r="Y87" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>6.1150000000000002</v>
       </c>
       <c r="Z87" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>6.835</v>
       </c>
       <c r="AA87" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9140,11 +9560,11 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B88" s="17" t="s">
+    <row r="88" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A88" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="16"/>
@@ -9155,15 +9575,23 @@
         <v>34</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="H88" s="7"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="H88" s="7">
+        <v>3</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K88" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -9187,15 +9615,15 @@
       </c>
       <c r="X88" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y88" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z88" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA88" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9210,9 +9638,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>6</v>
@@ -9225,22 +9653,22 @@
         <v>34</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>366</v>
+        <v>540</v>
       </c>
       <c r="H89" s="7">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>34</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="K89" s="18" t="s">
-        <v>367</v>
+        <v>141</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
@@ -9265,15 +9693,15 @@
       </c>
       <c r="X89" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.2350000000000003</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y89" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.1150000000000002</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z89" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>6.835</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA89" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9290,12 +9718,12 @@
     </row>
     <row r="90" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="16"/>
+      <c r="C90" s="9"/>
       <c r="D90" s="7">
         <v>1</v>
       </c>
@@ -9303,27 +9731,27 @@
         <v>34</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="H90" s="7">
         <v>3</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="K90" s="9" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
-      <c r="O90" s="16"/>
+      <c r="O90" s="9"/>
       <c r="P90" s="7"/>
       <c r="Q90" s="7"/>
       <c r="R90" s="7"/>
@@ -9366,42 +9794,44 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
-        <v>73</v>
+    <row r="91" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="7" t="s">
+        <v>161</v>
+      </c>
       <c r="D91" s="7">
         <v>1</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>172</v>
+        <v>157</v>
+      </c>
+      <c r="G91" s="17" t="s">
+        <v>156</v>
       </c>
       <c r="H91" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="K91" s="9" t="s">
-        <v>368</v>
+        <v>159</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="9"/>
+      <c r="O91" s="7"/>
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7"/>
@@ -9421,15 +9851,15 @@
       </c>
       <c r="X91" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y91" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z91" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>5.12</v>
       </c>
       <c r="AA91" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9444,14 +9874,14 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
-        <v>74</v>
+    <row r="92" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C92" s="9"/>
+      <c r="C92" s="17"/>
       <c r="D92" s="7">
         <v>1</v>
       </c>
@@ -9459,27 +9889,27 @@
         <v>34</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>187</v>
+        <v>163</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>527</v>
       </c>
       <c r="H92" s="7">
         <v>3</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="K92" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="9"/>
+      <c r="O92" s="17"/>
       <c r="P92" s="7"/>
       <c r="Q92" s="7"/>
       <c r="R92" s="7"/>
@@ -9522,39 +9952,37 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C93" s="7" t="s">
-        <v>195</v>
-      </c>
+      <c r="C93" s="7"/>
       <c r="D93" s="7">
         <v>1</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>190</v>
+        <v>541</v>
       </c>
       <c r="H93" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
@@ -9579,15 +10007,15 @@
       </c>
       <c r="X93" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>4.03</v>
       </c>
       <c r="Y93" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>3.91</v>
       </c>
       <c r="Z93" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>4.63</v>
       </c>
       <c r="AA93" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9602,14 +10030,14 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A94" s="17" t="s">
-        <v>76</v>
+    <row r="94" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="17"/>
+      <c r="C94" s="7"/>
       <c r="D94" s="7">
         <v>1</v>
       </c>
@@ -9617,27 +10045,27 @@
         <v>34</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>175</v>
+        <v>535</v>
       </c>
       <c r="H94" s="7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="J94" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="K94" s="17" t="s">
-        <v>198</v>
+        <v>146</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
-      <c r="O94" s="17"/>
+      <c r="O94" s="7"/>
       <c r="P94" s="7"/>
       <c r="Q94" s="7"/>
       <c r="R94" s="7"/>
@@ -9657,15 +10085,15 @@
       </c>
       <c r="X94" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="Y94" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>6.8500000000000005</v>
       </c>
       <c r="Z94" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>7.57</v>
       </c>
       <c r="AA94" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9682,7 +10110,7 @@
     </row>
     <row r="95" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>6</v>
@@ -9692,25 +10120,25 @@
         <v>1</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>369</v>
+        <v>169</v>
       </c>
       <c r="H95" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I95" s="9" t="s">
         <v>36</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
@@ -9735,15 +10163,15 @@
       </c>
       <c r="X95" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>5.0100000000000007</v>
       </c>
       <c r="Y95" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>4.8900000000000006</v>
       </c>
       <c r="Z95" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>5.61</v>
       </c>
       <c r="AA95" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9760,7 +10188,7 @@
     </row>
     <row r="96" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>6</v>
@@ -9773,27 +10201,35 @@
         <v>34</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>163</v>
+        <v>529</v>
       </c>
       <c r="H96" s="7">
+        <v>3</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="L96" s="7">
         <v>10</v>
       </c>
-      <c r="I96" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="J96" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="K96" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
+      <c r="M96" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="N96" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O96" s="7" t="s">
+        <v>175</v>
+      </c>
       <c r="P96" s="7"/>
       <c r="Q96" s="7"/>
       <c r="R96" s="7"/>
@@ -9813,32 +10249,32 @@
       </c>
       <c r="X96" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>6.9700000000000006</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y96" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>6.8500000000000005</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z96" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>7.57</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA96" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>7.1700000000000008</v>
       </c>
       <c r="AB96" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>7.0500000000000007</v>
       </c>
       <c r="AC96" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>7.7700000000000005</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>6</v>
@@ -9848,26 +10284,18 @@
         <v>1</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="H97" s="7">
-        <v>6</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J97" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>205</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
@@ -9891,15 +10319,15 @@
       </c>
       <c r="X97" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>5.0100000000000007</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y97" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.8900000000000006</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="Z97" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.61</v>
+        <v>2.67</v>
       </c>
       <c r="AA97" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -9915,13 +10343,13 @@
       </c>
     </row>
     <row r="98" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B98" s="7" t="s">
+      <c r="A98" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B98" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="7"/>
+      <c r="C98" s="17"/>
       <c r="D98" s="7">
         <v>1</v>
       </c>
@@ -9929,35 +10357,19 @@
         <v>34</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="H98" s="7">
-        <v>3</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J98" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="L98" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="M98" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="N98" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="O98" s="7" t="s">
-        <v>210</v>
-      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="17"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="17"/>
       <c r="P98" s="7"/>
       <c r="Q98" s="7"/>
       <c r="R98" s="7"/>
@@ -9977,32 +10389,32 @@
       </c>
       <c r="X98" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>3.5399999999999996</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y98" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>3.4199999999999995</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="Z98" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>4.1399999999999997</v>
+        <v>2.67</v>
       </c>
       <c r="AA98" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>7.4150000000000009</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB98" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>7.2950000000000008</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC98" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>8.0150000000000006</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>2.8699999999999997</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>6</v>
@@ -10015,19 +10427,35 @@
         <v>34</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="H99" s="7"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
-      <c r="K99" s="7"/>
-      <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
+        <v>542</v>
+      </c>
+      <c r="H99" s="7">
+        <v>3</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="L99" s="7">
+        <v>10</v>
+      </c>
+      <c r="M99" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N99" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>491</v>
+      </c>
       <c r="P99" s="7"/>
       <c r="Q99" s="7"/>
       <c r="R99" s="7"/>
@@ -10047,37 +10475,37 @@
       </c>
       <c r="X99" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y99" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z99" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA99" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>7.1700000000000008</v>
       </c>
       <c r="AB99" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>7.0500000000000007</v>
       </c>
       <c r="AC99" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B100" s="17" t="s">
+        <v>7.7700000000000005</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B100" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C100" s="17"/>
+      <c r="C100" s="7"/>
       <c r="D100" s="7">
         <v>1</v>
       </c>
@@ -10085,19 +10513,27 @@
         <v>34</v>
       </c>
       <c r="F100" s="17" t="s">
-        <v>212</v>
+        <v>493</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="H100" s="7"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="17"/>
+        <v>543</v>
+      </c>
+      <c r="H100" s="7">
+        <v>10</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>494</v>
+      </c>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
-      <c r="O100" s="17"/>
+      <c r="O100" s="7"/>
       <c r="P100" s="7"/>
       <c r="Q100" s="7"/>
       <c r="R100" s="7"/>
@@ -10117,15 +10553,15 @@
       </c>
       <c r="X100" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="Y100" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.8500000000000005</v>
       </c>
       <c r="Z100" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.57</v>
       </c>
       <c r="AA100" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10140,9 +10576,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>6</v>
@@ -10155,25 +10591,19 @@
         <v>34</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>371</v>
+        <v>496</v>
       </c>
       <c r="H101" s="7"/>
-      <c r="I101" s="9" t="s">
-        <v>11</v>
-      </c>
+      <c r="I101" s="9"/>
       <c r="J101" s="9"/>
-      <c r="K101" s="7" t="s">
-        <v>84</v>
-      </c>
+      <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
-      <c r="O101" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="O101" s="7"/>
       <c r="P101" s="7"/>
       <c r="Q101" s="7"/>
       <c r="R101" s="7"/>
@@ -10216,7 +10646,7 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>86</v>
       </c>
@@ -10228,16 +10658,26 @@
         <v>1</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F102" s="17"/>
+        <v>11</v>
+      </c>
+      <c r="F102" s="17" t="s">
+        <v>498</v>
+      </c>
       <c r="G102" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H102" s="7"/>
-      <c r="I102" s="9"/>
-      <c r="J102" s="9"/>
-      <c r="K102" s="7"/>
+        <v>497</v>
+      </c>
+      <c r="H102" s="7">
+        <v>5</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="K102" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -10261,15 +10701,15 @@
       </c>
       <c r="X102" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.5200000000000005</v>
       </c>
       <c r="Y102" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z102" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>5.12</v>
       </c>
       <c r="AA102" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10285,31 +10725,43 @@
       </c>
     </row>
     <row r="103" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B103" s="7" t="s">
+      <c r="A103" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B103" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C103" s="7"/>
+      <c r="C103" s="17" t="s">
+        <v>162</v>
+      </c>
       <c r="D103" s="7">
         <v>1</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F103" s="17"/>
+        <v>11</v>
+      </c>
+      <c r="F103" s="17" t="s">
+        <v>502</v>
+      </c>
       <c r="G103" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="H103" s="7"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="7"/>
+        <v>501</v>
+      </c>
+      <c r="H103" s="7">
+        <v>9</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>510</v>
+      </c>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
+      <c r="O103" s="17"/>
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
       <c r="R103" s="7"/>
@@ -10329,15 +10781,15 @@
       </c>
       <c r="X103" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.48</v>
       </c>
       <c r="Y103" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.36</v>
       </c>
       <c r="Z103" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.08</v>
       </c>
       <c r="AA103" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10352,31 +10804,39 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="7"/>
+      <c r="C104" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="D104" s="7">
         <v>1</v>
       </c>
       <c r="E104" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="G104" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="H104" s="7">
+        <v>3</v>
+      </c>
+      <c r="I104" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F104" s="17"/>
-      <c r="G104" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="H104" s="7"/>
-      <c r="I104" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J104" s="9"/>
+      <c r="J104" s="9" t="s">
+        <v>506</v>
+      </c>
       <c r="K104" s="7" t="s">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
@@ -10401,15 +10861,15 @@
       </c>
       <c r="X104" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y104" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z104" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA104" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10424,38 +10884,50 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" s="17" t="s">
+    <row r="105" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A105" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C105" s="17" t="s">
-        <v>196</v>
-      </c>
+      <c r="C105" s="7"/>
       <c r="D105" s="7">
         <v>1</v>
       </c>
       <c r="E105" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H105" s="7">
+        <v>3</v>
+      </c>
+      <c r="I105" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F105" s="17"/>
-      <c r="G105" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H105" s="7"/>
-      <c r="I105" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J105" s="9"/>
-      <c r="K105" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
-      <c r="N105" s="7"/>
-      <c r="O105" s="17"/>
+      <c r="J105" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L105" s="7">
+        <v>10</v>
+      </c>
+      <c r="M105" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="N105" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>151</v>
+      </c>
       <c r="P105" s="7"/>
       <c r="Q105" s="7"/>
       <c r="R105" s="7"/>
@@ -10475,56 +10947,60 @@
       </c>
       <c r="X105" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y105" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z105" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA105" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>7.1700000000000008</v>
       </c>
       <c r="AB105" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>7.0500000000000007</v>
       </c>
       <c r="AC105" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>7.7700000000000005</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C106" s="7" t="s">
-        <v>196</v>
-      </c>
+      <c r="C106" s="7"/>
       <c r="D106" s="7">
         <v>1</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F106" s="17"/>
+      <c r="F106" s="17" t="s">
+        <v>511</v>
+      </c>
       <c r="G106" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H106" s="7"/>
-      <c r="I106" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J106" s="9"/>
+        <v>512</v>
+      </c>
+      <c r="H106" s="7">
+        <v>10</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>146</v>
+      </c>
       <c r="K106" s="7" t="s">
-        <v>97</v>
+        <v>513</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -10549,15 +11025,15 @@
       </c>
       <c r="X106" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="Y106" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.8500000000000005</v>
       </c>
       <c r="Z106" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.57</v>
       </c>
       <c r="AA106" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10574,7 +11050,7 @@
     </row>
     <row r="107" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>6</v>
@@ -10583,27 +11059,35 @@
       <c r="D107" s="7">
         <v>1</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F107" s="17"/>
-      <c r="G107" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H107" s="7"/>
+      <c r="F107" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="H107" s="7">
+        <v>4</v>
+      </c>
       <c r="I107" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J107" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="K107" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="L107" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="L107" s="7">
+        <v>5</v>
+      </c>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
       <c r="O107" s="7"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="7"/>
+      <c r="P107" s="17"/>
+      <c r="Q107" s="17"/>
       <c r="R107" s="7"/>
       <c r="S107" s="7"/>
       <c r="T107" s="7"/>
@@ -10621,55 +11105,65 @@
       </c>
       <c r="X107" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y107" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z107" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA107" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>4.7200000000000006</v>
       </c>
       <c r="AB107" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AC107" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="108" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>101</v>
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C108" s="7"/>
+      <c r="C108" s="17"/>
       <c r="D108" s="7">
         <v>1</v>
       </c>
       <c r="E108" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F108" s="17"/>
+      <c r="F108" s="17" t="s">
+        <v>514</v>
+      </c>
       <c r="G108" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="H108" s="7"/>
-      <c r="I108" s="9"/>
-      <c r="J108" s="9"/>
-      <c r="K108" s="7"/>
+        <v>516</v>
+      </c>
+      <c r="H108" s="7">
+        <v>9</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K108" s="17" t="s">
+        <v>517</v>
+      </c>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
+      <c r="O108" s="17"/>
       <c r="P108" s="7"/>
       <c r="Q108" s="7"/>
       <c r="R108" s="7"/>
@@ -10689,15 +11183,15 @@
       </c>
       <c r="X108" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.48</v>
       </c>
       <c r="Y108" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.36</v>
       </c>
       <c r="Z108" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.08</v>
       </c>
       <c r="AA108" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10712,46 +11206,44 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C109" s="7"/>
+      <c r="C109" s="17"/>
       <c r="D109" s="7">
         <v>1</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>372</v>
+      <c r="F109" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="G109" s="17" t="s">
+        <v>519</v>
       </c>
       <c r="H109" s="7">
-        <v>5</v>
-      </c>
-      <c r="I109" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J109" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K109" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L109" s="7">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="L109" s="7"/>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="17"/>
-      <c r="Q109" s="17"/>
+      <c r="O109" s="17"/>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
       <c r="R109" s="7"/>
       <c r="S109" s="7"/>
       <c r="T109" s="7"/>
@@ -10769,32 +11261,32 @@
       </c>
       <c r="X109" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>4.5200000000000005</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="Y109" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>4.4000000000000004</v>
+        <v>6.8500000000000005</v>
       </c>
       <c r="Z109" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>5.12</v>
+        <v>7.57</v>
       </c>
       <c r="AA109" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>4.7200000000000006</v>
+        <v>2.2699999999999996</v>
       </c>
       <c r="AB109" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>4.6000000000000005</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AC109" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="110" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>2.8699999999999997</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>6</v>
@@ -10806,14 +11298,24 @@
       <c r="E110" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F110" s="17"/>
+      <c r="F110" s="17" t="s">
+        <v>520</v>
+      </c>
       <c r="G110" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H110" s="7"/>
-      <c r="I110" s="9"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="17"/>
+        <v>521</v>
+      </c>
+      <c r="H110" s="7">
+        <v>9</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J110" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>522</v>
+      </c>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -10837,15 +11339,15 @@
       </c>
       <c r="X110" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>6.48</v>
       </c>
       <c r="Y110" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>6.36</v>
       </c>
       <c r="Z110" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>7.08</v>
       </c>
       <c r="AA110" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -10860,9 +11362,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
-        <v>105</v>
+    <row r="111" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A111" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>6</v>
@@ -10874,9 +11376,11 @@
       <c r="E111" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F111" s="17"/>
+      <c r="F111" s="17" t="s">
+        <v>550</v>
+      </c>
       <c r="G111" s="17" t="s">
-        <v>106</v>
+        <v>523</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="9"/>
@@ -10928,9 +11432,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>6</v>
@@ -10942,9 +11446,11 @@
       <c r="E112" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F112" s="17"/>
+      <c r="F112" s="17" t="s">
+        <v>524</v>
+      </c>
       <c r="G112" s="17" t="s">
-        <v>108</v>
+        <v>551</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="9"/>
@@ -10996,9 +11502,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>6</v>
@@ -11008,16 +11514,26 @@
         <v>1</v>
       </c>
       <c r="E113" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="G113" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="H113" s="7">
+        <v>4</v>
+      </c>
+      <c r="I113" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F113" s="17"/>
-      <c r="G113" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H113" s="7"/>
-      <c r="I113" s="9"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="17"/>
+      <c r="J113" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>549</v>
+      </c>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
@@ -11041,15 +11557,15 @@
       </c>
       <c r="X113" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>4.03</v>
       </c>
       <c r="Y113" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.91</v>
       </c>
       <c r="Z113" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="AA113" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -11064,9 +11580,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>6</v>
@@ -11078,14 +11594,24 @@
       <c r="E114" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F114" s="17"/>
+      <c r="F114" s="17" t="s">
+        <v>528</v>
+      </c>
       <c r="G114" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H114" s="7"/>
-      <c r="I114" s="9"/>
-      <c r="J114" s="9"/>
-      <c r="K114" s="17"/>
+        <v>527</v>
+      </c>
+      <c r="H114" s="7">
+        <v>3</v>
+      </c>
+      <c r="I114" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J114" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>546</v>
+      </c>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
@@ -11109,15 +11635,15 @@
       </c>
       <c r="X114" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y114" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z114" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA114" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -11132,9 +11658,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
-        <v>113</v>
+    <row r="115" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>6</v>
@@ -11144,24 +11670,38 @@
         <v>1</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="F115" s="17" t="s">
+        <v>545</v>
+      </c>
       <c r="G115" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="H115" s="7"/>
+        <v>552</v>
+      </c>
+      <c r="H115" s="7">
+        <v>3</v>
+      </c>
       <c r="I115" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J115" s="9"/>
-      <c r="K115" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
-      <c r="O115" s="17"/>
+        <v>56</v>
+      </c>
+      <c r="J115" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="L115" s="7">
+        <v>10</v>
+      </c>
+      <c r="M115" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="N115" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O115" s="17" t="s">
+        <v>553</v>
+      </c>
       <c r="P115" s="7"/>
       <c r="Q115" s="7"/>
       <c r="R115" s="7"/>
@@ -11181,32 +11721,32 @@
       </c>
       <c r="X115" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y115" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z115" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA115" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
+        <v>7.1700000000000008</v>
       </c>
       <c r="AB115" s="7">
         <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
+        <v>7.0500000000000007</v>
       </c>
       <c r="AC115" s="17">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="116" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A116" s="17" t="s">
-        <v>115</v>
+        <v>7.7700000000000005</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+      <c r="A116" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>6</v>
@@ -11218,17 +11758,23 @@
       <c r="E116" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F116" s="17"/>
+      <c r="F116" s="17" t="s">
+        <v>557</v>
+      </c>
       <c r="G116" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H116" s="7"/>
+        <v>556</v>
+      </c>
+      <c r="H116" s="7">
+        <v>3</v>
+      </c>
       <c r="I116" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J116" s="9"/>
-      <c r="K116" s="17" t="s">
-        <v>381</v>
+        <v>11</v>
+      </c>
+      <c r="J116" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>558</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
@@ -11253,15 +11799,15 @@
       </c>
       <c r="X116" s="7">
         <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
+        <v>3.5399999999999996</v>
       </c>
       <c r="Y116" s="7">
         <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
+        <v>3.4199999999999995</v>
       </c>
       <c r="Z116" s="7">
         <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AA116" s="7">
         <f>Table3[[#This Row],[E3Y]]+T$2</f>
@@ -11276,9 +11822,9 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
-        <v>117</v>
+    <row r="117" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>6</v>
@@ -11290,18 +11836,16 @@
       <c r="E117" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F117" s="17"/>
+      <c r="F117" s="17" t="s">
+        <v>560</v>
+      </c>
       <c r="G117" s="17" t="s">
-        <v>118</v>
+        <v>559</v>
       </c>
       <c r="H117" s="7"/>
-      <c r="I117" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="I117" s="9"/>
       <c r="J117" s="9"/>
-      <c r="K117" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="K117" s="17"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
@@ -11348,145 +11892,67 @@
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="17"/>
-      <c r="D118" s="7">
-        <v>1</v>
-      </c>
-      <c r="E118" s="17" t="s">
-        <v>34</v>
-      </c>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A118" s="9"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="17"/>
       <c r="F118" s="17"/>
-      <c r="G118" s="17" t="s">
-        <v>121</v>
-      </c>
+      <c r="G118" s="9"/>
       <c r="H118" s="7"/>
-      <c r="I118" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J118" s="9"/>
-      <c r="K118" s="7" t="s">
-        <v>122</v>
-      </c>
+      <c r="I118" s="16"/>
+      <c r="J118" s="16"/>
+      <c r="K118" s="9"/>
       <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="17"/>
+      <c r="M118" s="17"/>
+      <c r="N118" s="17"/>
+      <c r="O118" s="9"/>
       <c r="P118" s="7"/>
       <c r="Q118" s="7"/>
       <c r="R118" s="7"/>
       <c r="S118" s="7"/>
       <c r="T118" s="7"/>
-      <c r="U118" s="7">
-        <f>Table3[[#This Row],[E1Y]]+T$2</f>
-        <v>2.36</v>
-      </c>
-      <c r="V118" s="7">
-        <f>Table3[[#This Row],[E1TY]]+S$2</f>
-        <v>2.2399999999999998</v>
-      </c>
-      <c r="W118" s="7">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
-        <v>2.96</v>
-      </c>
-      <c r="X118" s="7">
-        <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="Y118" s="7">
-        <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
-      </c>
-      <c r="Z118" s="7">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
-      </c>
-      <c r="AA118" s="7">
-        <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
-      </c>
-      <c r="AB118" s="7">
-        <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
-      </c>
-      <c r="AC118" s="17">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
-    </row>
-    <row r="119" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A119" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="7">
-        <v>1</v>
-      </c>
-      <c r="E119" s="17" t="s">
-        <v>34</v>
-      </c>
+      <c r="U118" s="7"/>
+      <c r="V118" s="7"/>
+      <c r="W118" s="7"/>
+      <c r="X118" s="7"/>
+      <c r="Y118" s="7"/>
+      <c r="Z118" s="7"/>
+      <c r="AA118" s="7"/>
+      <c r="AB118" s="7"/>
+      <c r="AC118" s="17"/>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A119" s="9"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="17"/>
       <c r="F119" s="17"/>
-      <c r="G119" s="17" t="s">
-        <v>124</v>
-      </c>
+      <c r="G119" s="9"/>
       <c r="H119" s="7"/>
-      <c r="I119" s="9"/>
-      <c r="J119" s="9"/>
-      <c r="K119" s="17"/>
+      <c r="I119" s="16"/>
+      <c r="J119" s="16"/>
+      <c r="K119" s="9"/>
       <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="17"/>
+      <c r="M119" s="17"/>
+      <c r="N119" s="17"/>
+      <c r="O119" s="9"/>
       <c r="P119" s="7"/>
       <c r="Q119" s="7"/>
       <c r="R119" s="7"/>
       <c r="S119" s="7"/>
       <c r="T119" s="7"/>
-      <c r="U119" s="7">
-        <f>Table3[[#This Row],[E1Y]]+T$2</f>
-        <v>2.36</v>
-      </c>
-      <c r="V119" s="7">
-        <f>Table3[[#This Row],[E1TY]]+S$2</f>
-        <v>2.2399999999999998</v>
-      </c>
-      <c r="W119" s="7">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
-        <v>2.96</v>
-      </c>
-      <c r="X119" s="7">
-        <f>Table3[[#This Row],[E2Y]]+T$2</f>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="Y119" s="7">
-        <f>Table3[[#This Row],[E2TY]]+S$2</f>
-        <v>1.9499999999999997</v>
-      </c>
-      <c r="Z119" s="7">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 2 Y]]-1)+R$2</f>
-        <v>2.67</v>
-      </c>
-      <c r="AA119" s="7">
-        <f>Table3[[#This Row],[E3Y]]+T$2</f>
-        <v>2.2699999999999996</v>
-      </c>
-      <c r="AB119" s="7">
-        <f>Table3[[#This Row],[E3TY]]+S$2</f>
-        <v>2.1499999999999995</v>
-      </c>
-      <c r="AC119" s="17">
-        <f>P$2+Q$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*R$2</f>
-        <v>2.8699999999999997</v>
-      </c>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="7"/>
+      <c r="Z119" s="7"/>
+      <c r="AA119" s="7"/>
+      <c r="AB119" s="7"/>
+      <c r="AC119" s="17"/>
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="9"/>
@@ -13875,71 +14341,9 @@
       <c r="AB196" s="7"/>
       <c r="AC196" s="17"/>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A197" s="9"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="9"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="17"/>
-      <c r="F197" s="17"/>
-      <c r="G197" s="9"/>
-      <c r="H197" s="7"/>
-      <c r="I197" s="16"/>
-      <c r="J197" s="16"/>
-      <c r="K197" s="9"/>
-      <c r="L197" s="7"/>
-      <c r="M197" s="17"/>
-      <c r="N197" s="17"/>
-      <c r="O197" s="9"/>
-      <c r="P197" s="7"/>
-      <c r="Q197" s="7"/>
-      <c r="R197" s="7"/>
-      <c r="S197" s="7"/>
-      <c r="T197" s="7"/>
-      <c r="U197" s="7"/>
-      <c r="V197" s="7"/>
-      <c r="W197" s="7"/>
-      <c r="X197" s="7"/>
-      <c r="Y197" s="7"/>
-      <c r="Z197" s="7"/>
-      <c r="AA197" s="7"/>
-      <c r="AB197" s="7"/>
-      <c r="AC197" s="17"/>
-    </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A198" s="9"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="17"/>
-      <c r="F198" s="17"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="7"/>
-      <c r="I198" s="16"/>
-      <c r="J198" s="16"/>
-      <c r="K198" s="9"/>
-      <c r="L198" s="7"/>
-      <c r="M198" s="17"/>
-      <c r="N198" s="17"/>
-      <c r="O198" s="9"/>
-      <c r="P198" s="7"/>
-      <c r="Q198" s="7"/>
-      <c r="R198" s="7"/>
-      <c r="S198" s="7"/>
-      <c r="T198" s="7"/>
-      <c r="U198" s="7"/>
-      <c r="V198" s="7"/>
-      <c r="W198" s="7"/>
-      <c r="X198" s="7"/>
-      <c r="Y198" s="7"/>
-      <c r="Z198" s="7"/>
-      <c r="AA198" s="7"/>
-      <c r="AB198" s="7"/>
-      <c r="AC198" s="17"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B95">
+  <conditionalFormatting sqref="B1:B93">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Accessory">
       <formula>NOT(ISERROR(SEARCH("Accessory",B1)))</formula>
     </cfRule>
@@ -13956,21 +14360,21 @@
       <formula>NOT(ISERROR(SEARCH("Spell",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120:B198">
+  <conditionalFormatting sqref="B118:B196">
     <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Accessory">
-      <formula>NOT(ISERROR(SEARCH("Accessory",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Accessory",B118)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="Armour">
-      <formula>NOT(ISERROR(SEARCH("Armour",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Armour",B118)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="Equipment">
-      <formula>NOT(ISERROR(SEARCH("Equipment",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Equipment",B118)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="Impression">
-      <formula>NOT(ISERROR(SEARCH("Impression",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Impression",B118)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="Spell">
-      <formula>NOT(ISERROR(SEARCH("Spell",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Spell",B118)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19946B6-841F-4F1F-ABAE-2F99B964A724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454C7DAC-B721-40C9-987A-F198D0037EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="561">
   <si>
     <t>Name</t>
   </si>
@@ -499,9 +499,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Impale: &lt;/b&gt;2 AP</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 4 , reach.&lt;/b&gt;</t>
   </si>
   <si>
     <t>Destroy this card to completely block an incoming attack.</t>
@@ -1532,9 +1529,6 @@
     <t>&lt;i&gt;&lt;b&gt;Precise&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 4 , Ranged&lt;/b&gt;&lt;br&gt;Ignores damage reduction effects.</t>
-  </si>
-  <si>
     <t>Place the slab down on an adjacent hex. It extends straight on each side to become a three hex wall, if there is space. This wall blocks vision and is indestructible.</t>
   </si>
   <si>
@@ -1682,9 +1676,6 @@
     <t>&lt;b&gt;Damage = 2 , Melee.&lt;/b&gt;On a hit, you may destroy this card to destroy any equipped Limb or Impression from the target.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = hexes moved, Melee.&lt;/b&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br&gt; hornshexes</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Damage = 2 , Melee.&lt;/b&gt;On a hit, the target is pushed back hexes equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
   </si>
   <si>
@@ -1697,9 +1688,6 @@
     <t>&lt;b&gt;Damage = 8, Melee.&lt;/b&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt; , Melee.&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Damage =4, Melee.</t>
   </si>
   <si>
@@ -1724,9 +1712,6 @@
     <t>&lt;b&gt;Damage = 5, Ranged.&lt;/b&gt;&lt;br&gt;On a hit, inflict the &lt;b&gt;burning&lt;/b&gt; status effect.&lt;br&gt;On a miss, inflict the &lt;b&gt;burning&lt;/b&gt; status effect on you.</t>
   </si>
   <si>
-    <t>Damage = 3 , Reach.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Venom: &lt;/b&gt;Inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect.</t>
   </si>
   <si>
@@ -1752,6 +1737,18 @@
   </si>
   <si>
     <t>&lt;b&gt;Summon Saplings:&lt;/b&gt; weirdtweirdT</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt; ,&lt;b&gt; Melee.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = hexes moved, Melee.&lt;/b&gt;&lt;br&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br&gt; hornshexes</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4 , Ranged.&lt;/b&gt;&lt;br&gt;Ignores damage reduction effects.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 3 , Reach.&lt;/b&gt;</t>
   </si>
 </sst>
 </file>
@@ -2918,7 +2915,7 @@
     </row>
     <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>47</v>
@@ -2931,10 +2928,10 @@
         <v>36</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H2" s="7">
         <v>4</v>
@@ -2943,10 +2940,10 @@
         <v>36</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="17"/>
@@ -3006,7 +3003,7 @@
     </row>
     <row r="3" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>47</v>
@@ -3019,10 +3016,10 @@
         <v>36</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -3031,10 +3028,10 @@
         <v>36</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L3" s="7">
         <v>9</v>
@@ -3043,10 +3040,10 @@
         <v>36</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -3092,13 +3089,13 @@
     </row>
     <row r="4" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -3107,10 +3104,10 @@
         <v>36</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H4" s="7">
         <v>3</v>
@@ -3119,10 +3116,10 @@
         <v>11</v>
       </c>
       <c r="J4" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>274</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="17"/>
@@ -3130,7 +3127,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -3174,13 +3171,13 @@
     </row>
     <row r="5" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -3189,10 +3186,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H5" s="7">
         <v>5</v>
@@ -3201,10 +3198,10 @@
         <v>36</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="17"/>
@@ -3212,7 +3209,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -3256,7 +3253,7 @@
     </row>
     <row r="6" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
@@ -3269,10 +3266,10 @@
         <v>36</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>278</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>279</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="17"/>
@@ -3284,7 +3281,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -3328,7 +3325,7 @@
     </row>
     <row r="7" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>47</v>
@@ -3341,10 +3338,10 @@
         <v>36</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H7" s="7">
         <v>6</v>
@@ -3353,10 +3350,10 @@
         <v>11</v>
       </c>
       <c r="J7" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>282</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="17"/>
@@ -3406,7 +3403,7 @@
     </row>
     <row r="8" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>47</v>
@@ -3419,10 +3416,10 @@
         <v>36</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H8" s="7">
         <v>5</v>
@@ -3431,10 +3428,10 @@
         <v>36</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L8" s="7">
         <v>9</v>
@@ -3443,10 +3440,10 @@
         <v>36</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
@@ -3492,7 +3489,7 @@
     </row>
     <row r="9" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>47</v>
@@ -3505,10 +3502,10 @@
         <v>36</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H9" s="7">
         <v>4</v>
@@ -3517,10 +3514,10 @@
         <v>36</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="17"/>
@@ -3570,13 +3567,13 @@
     </row>
     <row r="10" spans="1:29" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D10" s="7">
         <v>1</v>
@@ -3585,10 +3582,10 @@
         <v>36</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H10" s="7">
         <v>5</v>
@@ -3597,10 +3594,10 @@
         <v>36</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="17"/>
@@ -3650,13 +3647,13 @@
     </row>
     <row r="11" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D11" s="7">
         <v>1</v>
@@ -3665,10 +3662,10 @@
         <v>36</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
@@ -3677,10 +3674,10 @@
         <v>36</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L11" s="7">
         <v>7</v>
@@ -3689,10 +3686,10 @@
         <v>11</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -3738,7 +3735,7 @@
     </row>
     <row r="12" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>47</v>
@@ -3751,10 +3748,10 @@
         <v>36</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H12" s="7">
         <v>6</v>
@@ -3763,10 +3760,10 @@
         <v>36</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="17"/>
@@ -3816,7 +3813,7 @@
     </row>
     <row r="13" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>47</v>
@@ -3829,10 +3826,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
@@ -3841,10 +3838,10 @@
         <v>36</v>
       </c>
       <c r="J13" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>332</v>
       </c>
       <c r="L13" s="7">
         <v>8</v>
@@ -3853,10 +3850,10 @@
         <v>36</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -3902,13 +3899,13 @@
     </row>
     <row r="14" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D14" s="7">
         <v>1</v>
@@ -3917,10 +3914,10 @@
         <v>11</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
@@ -3929,10 +3926,10 @@
         <v>11</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L14" s="7">
         <v>7</v>
@@ -3941,10 +3938,10 @@
         <v>36</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -3990,7 +3987,7 @@
     </row>
     <row r="15" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>47</v>
@@ -4003,10 +4000,10 @@
         <v>36</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H15" s="7">
         <v>4</v>
@@ -4062,13 +4059,13 @@
     </row>
     <row r="16" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -4077,10 +4074,10 @@
         <v>36</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H16" s="7">
         <v>3</v>
@@ -4089,10 +4086,10 @@
         <v>36</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L16" s="7">
         <v>9</v>
@@ -4101,10 +4098,10 @@
         <v>36</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -4150,7 +4147,7 @@
     </row>
     <row r="17" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>47</v>
@@ -4163,10 +4160,10 @@
         <v>11</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H17" s="7">
         <v>3</v>
@@ -4175,10 +4172,10 @@
         <v>11</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L17" s="7">
         <v>6</v>
@@ -4187,10 +4184,10 @@
         <v>36</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -4236,7 +4233,7 @@
     </row>
     <row r="18" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>47</v>
@@ -4249,10 +4246,10 @@
         <v>36</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H18" s="7">
         <v>8</v>
@@ -4261,10 +4258,10 @@
         <v>11</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L18" s="7"/>
       <c r="M18" s="17"/>
@@ -4314,7 +4311,7 @@
     </row>
     <row r="19" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>47</v>
@@ -4327,10 +4324,10 @@
         <v>36</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H19" s="7">
         <v>5</v>
@@ -4339,10 +4336,10 @@
         <v>36</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="17"/>
@@ -4392,13 +4389,13 @@
     </row>
     <row r="20" spans="1:29" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D20" s="7">
         <v>1</v>
@@ -4407,10 +4404,10 @@
         <v>11</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H20" s="7">
         <v>9.6</v>
@@ -4419,10 +4416,10 @@
         <v>11</v>
       </c>
       <c r="J20" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>338</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="17"/>
@@ -4472,7 +4469,7 @@
     </row>
     <row r="21" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>47</v>
@@ -4485,10 +4482,10 @@
         <v>36</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H21" s="7">
         <v>3</v>
@@ -4497,10 +4494,10 @@
         <v>36</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L21" s="7">
         <v>6</v>
@@ -4509,10 +4506,10 @@
         <v>36</v>
       </c>
       <c r="N21" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
@@ -4558,13 +4555,13 @@
     </row>
     <row r="22" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D22" s="7">
         <v>1</v>
@@ -4573,10 +4570,10 @@
         <v>36</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H22" s="7">
         <v>4</v>
@@ -4585,10 +4582,10 @@
         <v>36</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L22" s="7">
         <v>7</v>
@@ -4597,10 +4594,10 @@
         <v>36</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -4671,7 +4668,7 @@
         <v>36</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>49</v>
@@ -4734,7 +4731,7 @@
     </row>
     <row r="24" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>47</v>
@@ -4747,10 +4744,10 @@
         <v>11</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H24" s="7">
         <v>7</v>
@@ -4759,10 +4756,10 @@
         <v>36</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="17"/>
@@ -4812,13 +4809,13 @@
     </row>
     <row r="25" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D25" s="7">
         <v>1</v>
@@ -4827,10 +4824,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H25" s="7">
         <v>5</v>
@@ -4839,10 +4836,10 @@
         <v>36</v>
       </c>
       <c r="J25" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>381</v>
       </c>
       <c r="L25" s="7">
         <v>9</v>
@@ -4851,10 +4848,10 @@
         <v>11</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
@@ -4900,7 +4897,7 @@
     </row>
     <row r="26" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>47</v>
@@ -4913,10 +4910,10 @@
         <v>36</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H26" s="7">
         <v>5</v>
@@ -4925,10 +4922,10 @@
         <v>36</v>
       </c>
       <c r="J26" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>383</v>
       </c>
       <c r="L26" s="7">
         <v>8</v>
@@ -4937,10 +4934,10 @@
         <v>36</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="27" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>47</v>
@@ -4999,10 +4996,10 @@
         <v>36</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H27" s="7">
         <v>6</v>
@@ -5011,10 +5008,10 @@
         <v>11</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="17"/>
@@ -5064,7 +5061,7 @@
     </row>
     <row r="28" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>53</v>
@@ -5077,10 +5074,10 @@
         <v>11</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5134,7 +5131,7 @@
     </row>
     <row r="29" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>53</v>
@@ -5147,10 +5144,10 @@
         <v>36</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H29" s="7">
         <v>4</v>
@@ -5159,10 +5156,10 @@
         <v>36</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
@@ -5212,7 +5209,7 @@
     </row>
     <row r="30" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>53</v>
@@ -5225,10 +5222,10 @@
         <v>36</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5282,7 +5279,7 @@
     </row>
     <row r="31" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>53</v>
@@ -5295,10 +5292,10 @@
         <v>36</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5352,7 +5349,7 @@
     </row>
     <row r="32" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>53</v>
@@ -5365,10 +5362,10 @@
         <v>36</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -5422,7 +5419,7 @@
     </row>
     <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>53</v>
@@ -5435,10 +5432,10 @@
         <v>36</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="34" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>53</v>
@@ -5505,10 +5502,10 @@
         <v>56</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="17"/>
@@ -5562,7 +5559,7 @@
     </row>
     <row r="35" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>53</v>
@@ -5575,10 +5572,10 @@
         <v>36</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="17"/>
@@ -5632,7 +5629,7 @@
     </row>
     <row r="36" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>53</v>
@@ -5645,10 +5642,10 @@
         <v>36</v>
       </c>
       <c r="F36" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="G36" s="17" t="s">
         <v>300</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>301</v>
       </c>
       <c r="H36" s="7">
         <v>6</v>
@@ -5657,10 +5654,10 @@
         <v>36</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L36" s="7"/>
       <c r="M36" s="17"/>
@@ -5710,7 +5707,7 @@
     </row>
     <row r="37" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>53</v>
@@ -5723,10 +5720,10 @@
         <v>36</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="17"/>
@@ -5780,7 +5777,7 @@
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>53</v>
@@ -5793,10 +5790,10 @@
         <v>36</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="17"/>
@@ -5850,13 +5847,13 @@
     </row>
     <row r="39" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D39" s="7">
         <v>1</v>
@@ -5865,10 +5862,10 @@
         <v>11</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="17"/>
@@ -5922,7 +5919,7 @@
     </row>
     <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>53</v>
@@ -5935,10 +5932,10 @@
         <v>11</v>
       </c>
       <c r="F40" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="G40" s="17" t="s">
         <v>409</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>410</v>
       </c>
       <c r="H40" s="7">
         <v>7</v>
@@ -5947,10 +5944,10 @@
         <v>36</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L40" s="7"/>
       <c r="M40" s="17"/>
@@ -6000,7 +5997,7 @@
     </row>
     <row r="41" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>53</v>
@@ -6013,10 +6010,10 @@
         <v>36</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="17"/>
@@ -6070,7 +6067,7 @@
     </row>
     <row r="42" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>53</v>
@@ -6083,10 +6080,10 @@
         <v>36</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="17"/>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="43" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>53</v>
@@ -6153,10 +6150,10 @@
         <v>36</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H43" s="7">
         <v>5</v>
@@ -6165,10 +6162,10 @@
         <v>11</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L43" s="7">
         <v>9</v>
@@ -6177,10 +6174,10 @@
         <v>11</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
@@ -6226,7 +6223,7 @@
     </row>
     <row r="44" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>53</v>
@@ -6239,10 +6236,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H44" s="7">
         <v>7</v>
@@ -6251,10 +6248,10 @@
         <v>36</v>
       </c>
       <c r="J44" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L44" s="7"/>
       <c r="M44" s="17"/>
@@ -6304,13 +6301,13 @@
     </row>
     <row r="45" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D45" s="7">
         <v>1</v>
@@ -6319,10 +6316,10 @@
         <v>56</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="17"/>
@@ -6376,7 +6373,7 @@
     </row>
     <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>53</v>
@@ -6389,10 +6386,10 @@
         <v>36</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H46" s="7">
         <v>5</v>
@@ -6401,10 +6398,10 @@
         <v>36</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L46" s="7"/>
       <c r="M46" s="17"/>
@@ -6454,7 +6451,7 @@
     </row>
     <row r="47" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>53</v>
@@ -6467,10 +6464,10 @@
         <v>36</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="17"/>
@@ -6524,7 +6521,7 @@
     </row>
     <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>53</v>
@@ -6537,10 +6534,10 @@
         <v>36</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H48" s="7">
         <v>6</v>
@@ -6549,10 +6546,10 @@
         <v>11</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L48" s="7"/>
       <c r="M48" s="17"/>
@@ -6602,7 +6599,7 @@
     </row>
     <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>53</v>
@@ -6615,10 +6612,10 @@
         <v>11</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="17"/>
@@ -6672,7 +6669,7 @@
     </row>
     <row r="50" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>53</v>
@@ -6685,10 +6682,10 @@
         <v>36</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H50" s="7">
         <v>4</v>
@@ -6697,10 +6694,10 @@
         <v>36</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L50" s="7"/>
       <c r="M50" s="17"/>
@@ -6750,7 +6747,7 @@
     </row>
     <row r="51" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>53</v>
@@ -6763,10 +6760,10 @@
         <v>11</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="17"/>
@@ -6820,7 +6817,7 @@
     </row>
     <row r="52" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>53</v>
@@ -6833,10 +6830,10 @@
         <v>11</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="17"/>
@@ -6890,7 +6887,7 @@
     </row>
     <row r="53" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>53</v>
@@ -6903,10 +6900,10 @@
         <v>11</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="17"/>
@@ -6960,7 +6957,7 @@
     </row>
     <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>53</v>
@@ -6973,10 +6970,10 @@
         <v>11</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H54" s="7">
         <v>5</v>
@@ -6985,10 +6982,10 @@
         <v>36</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="17"/>
@@ -7038,7 +7035,7 @@
     </row>
     <row r="55" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>53</v>
@@ -7051,10 +7048,10 @@
         <v>36</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="17"/>
@@ -7108,7 +7105,7 @@
     </row>
     <row r="56" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>53</v>
@@ -7121,10 +7118,10 @@
         <v>36</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H56" s="7">
         <v>6</v>
@@ -7133,10 +7130,10 @@
         <v>11</v>
       </c>
       <c r="J56" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L56" s="7"/>
       <c r="M56" s="17"/>
@@ -7186,7 +7183,7 @@
     </row>
     <row r="57" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>53</v>
@@ -7199,10 +7196,10 @@
         <v>11</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H57" s="7">
         <v>4</v>
@@ -7211,10 +7208,10 @@
         <v>36</v>
       </c>
       <c r="J57" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="17"/>
@@ -7264,7 +7261,7 @@
     </row>
     <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>53</v>
@@ -7277,10 +7274,10 @@
         <v>36</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H58" s="7">
         <v>5</v>
@@ -7289,10 +7286,10 @@
         <v>56</v>
       </c>
       <c r="J58" s="16" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L58" s="7"/>
       <c r="M58" s="17"/>
@@ -7342,7 +7339,7 @@
     </row>
     <row r="59" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>53</v>
@@ -7355,10 +7352,10 @@
         <v>36</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="16"/>
@@ -7412,7 +7409,7 @@
     </row>
     <row r="60" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>53</v>
@@ -7425,10 +7422,10 @@
         <v>11</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H60" s="7">
         <v>9</v>
@@ -7437,10 +7434,10 @@
         <v>36</v>
       </c>
       <c r="J60" s="16" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="17"/>
@@ -7490,7 +7487,7 @@
     </row>
     <row r="61" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>53</v>
@@ -7503,10 +7500,10 @@
         <v>36</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="16"/>
@@ -7560,7 +7557,7 @@
     </row>
     <row r="62" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>53</v>
@@ -7573,10 +7570,10 @@
         <v>56</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="16"/>
@@ -7630,7 +7627,7 @@
     </row>
     <row r="63" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>53</v>
@@ -7643,10 +7640,10 @@
         <v>56</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="16"/>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="64" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>53</v>
@@ -7713,10 +7710,10 @@
         <v>11</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H64" s="7">
         <v>4</v>
@@ -7725,10 +7722,10 @@
         <v>36</v>
       </c>
       <c r="J64" s="16" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L64" s="7"/>
       <c r="M64" s="17"/>
@@ -7778,7 +7775,7 @@
     </row>
     <row r="65" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>53</v>
@@ -7791,10 +7788,10 @@
         <v>36</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="16"/>
@@ -7873,7 +7870,7 @@
         <v>36</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K66" s="9" t="s">
         <v>148</v>
@@ -7926,7 +7923,7 @@
     </row>
     <row r="67" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>53</v>
@@ -7939,10 +7936,10 @@
         <v>56</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="16"/>
@@ -7996,7 +7993,7 @@
     </row>
     <row r="68" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>53</v>
@@ -8009,10 +8006,10 @@
         <v>56</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H68" s="7">
         <v>4</v>
@@ -8021,10 +8018,10 @@
         <v>36</v>
       </c>
       <c r="J68" s="16" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L68" s="7"/>
       <c r="M68" s="17"/>
@@ -8074,7 +8071,7 @@
     </row>
     <row r="69" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>53</v>
@@ -8087,10 +8084,10 @@
         <v>11</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="16"/>
@@ -8172,7 +8169,7 @@
         <v>16</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L70" s="7">
         <v>9.5</v>
@@ -8246,7 +8243,7 @@
         <v>41</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H71" s="7">
         <v>9</v>
@@ -8493,7 +8490,7 @@
         <v>36</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K74" s="9" t="s">
         <v>105</v>
@@ -8562,7 +8559,7 @@
         <v>106</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H75" s="7">
         <v>3</v>
@@ -8571,7 +8568,7 @@
         <v>36</v>
       </c>
       <c r="J75" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>108</v>
@@ -8640,7 +8637,7 @@
         <v>111</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H76" s="7">
         <v>9</v>
@@ -8718,7 +8715,7 @@
         <v>110</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H77" s="7">
         <v>5</v>
@@ -8727,7 +8724,7 @@
         <v>36</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K77" s="9" t="s">
         <v>109</v>
@@ -8805,7 +8802,7 @@
         <v>36</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K78" s="9" t="s">
         <v>120</v>
@@ -8874,7 +8871,7 @@
         <v>115</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H79" s="7">
         <v>3</v>
@@ -8952,7 +8949,7 @@
         <v>116</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H80" s="17">
         <v>3</v>
@@ -8964,7 +8961,7 @@
         <v>123</v>
       </c>
       <c r="K80" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="L80" s="7">
         <v>9.5</v>
@@ -9038,7 +9035,7 @@
         <v>117</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H81" s="7">
         <v>3</v>
@@ -9184,7 +9181,7 @@
         <v>6</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D83" s="7">
         <v>1</v>
@@ -9274,7 +9271,7 @@
         <v>130</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H84" s="17">
         <v>9.5</v>
@@ -9352,7 +9349,7 @@
         <v>131</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H85" s="7">
         <v>3</v>
@@ -9364,7 +9361,7 @@
         <v>132</v>
       </c>
       <c r="K85" s="9" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
@@ -9430,7 +9427,7 @@
         <v>133</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H86" s="7"/>
       <c r="I86" s="9"/>
@@ -9500,7 +9497,7 @@
         <v>134</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="H87" s="7">
         <v>8.5</v>
@@ -9512,7 +9509,7 @@
         <v>135</v>
       </c>
       <c r="K87" s="18" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
@@ -9578,7 +9575,7 @@
         <v>136</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H88" s="7">
         <v>3</v>
@@ -9656,7 +9653,7 @@
         <v>142</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H89" s="7">
         <v>3</v>
@@ -9668,7 +9665,7 @@
         <v>141</v>
       </c>
       <c r="K89" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
@@ -9734,7 +9731,7 @@
         <v>152</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>153</v>
+        <v>551</v>
       </c>
       <c r="H90" s="7">
         <v>3</v>
@@ -9743,10 +9740,10 @@
         <v>56</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K90" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
@@ -9802,7 +9799,7 @@
         <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D91" s="7">
         <v>1</v>
@@ -9811,10 +9808,10 @@
         <v>11</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H91" s="7">
         <v>5</v>
@@ -9823,10 +9820,10 @@
         <v>11</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
@@ -9889,10 +9886,10 @@
         <v>34</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H92" s="7">
         <v>3</v>
@@ -9901,10 +9898,10 @@
         <v>36</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
@@ -9967,10 +9964,10 @@
         <v>34</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H93" s="7">
         <v>4</v>
@@ -9979,10 +9976,10 @@
         <v>36</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
@@ -10045,10 +10042,10 @@
         <v>34</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H94" s="7">
         <v>10</v>
@@ -10060,7 +10057,7 @@
         <v>146</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
@@ -10123,10 +10120,10 @@
         <v>56</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H95" s="7">
         <v>6</v>
@@ -10135,10 +10132,10 @@
         <v>36</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
@@ -10201,10 +10198,10 @@
         <v>34</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H96" s="7">
         <v>3</v>
@@ -10213,10 +10210,10 @@
         <v>36</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L96" s="7">
         <v>10</v>
@@ -10228,7 +10225,7 @@
         <v>146</v>
       </c>
       <c r="O96" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P96" s="7"/>
       <c r="Q96" s="7"/>
@@ -10287,10 +10284,10 @@
         <v>34</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>488</v>
+        <v>559</v>
       </c>
       <c r="H97" s="7"/>
       <c r="I97" s="9"/>
@@ -10357,10 +10354,10 @@
         <v>34</v>
       </c>
       <c r="F98" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G98" s="17" t="s">
         <v>177</v>
-      </c>
-      <c r="G98" s="17" t="s">
-        <v>178</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="9"/>
@@ -10427,10 +10424,10 @@
         <v>34</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H99" s="7">
         <v>3</v>
@@ -10439,10 +10436,10 @@
         <v>11</v>
       </c>
       <c r="J99" s="9" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L99" s="7">
         <v>10</v>
@@ -10451,10 +10448,10 @@
         <v>11</v>
       </c>
       <c r="N99" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P99" s="7"/>
       <c r="Q99" s="7"/>
@@ -10513,10 +10510,10 @@
         <v>34</v>
       </c>
       <c r="F100" s="17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="H100" s="7">
         <v>10</v>
@@ -10528,7 +10525,7 @@
         <v>146</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
@@ -10591,10 +10588,10 @@
         <v>34</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="9"/>
@@ -10661,10 +10658,10 @@
         <v>11</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H102" s="7">
         <v>5</v>
@@ -10673,10 +10670,10 @@
         <v>36</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
@@ -10732,7 +10729,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D103" s="7">
         <v>1</v>
@@ -10741,10 +10738,10 @@
         <v>11</v>
       </c>
       <c r="F103" s="17" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H103" s="7">
         <v>9</v>
@@ -10753,10 +10750,10 @@
         <v>36</v>
       </c>
       <c r="J103" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K103" s="17" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
@@ -10812,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D104" s="7">
         <v>1</v>
@@ -10821,10 +10818,10 @@
         <v>34</v>
       </c>
       <c r="F104" s="17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H104" s="7">
         <v>3</v>
@@ -10833,10 +10830,10 @@
         <v>11</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
@@ -10899,10 +10896,10 @@
         <v>34</v>
       </c>
       <c r="F105" s="17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H105" s="7">
         <v>3</v>
@@ -10911,10 +10908,10 @@
         <v>11</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L105" s="7">
         <v>10</v>
@@ -10985,10 +10982,10 @@
         <v>34</v>
       </c>
       <c r="F106" s="17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H106" s="7">
         <v>10</v>
@@ -11000,7 +10997,7 @@
         <v>146</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -11066,7 +11063,7 @@
         <v>38</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H107" s="7">
         <v>4</v>
@@ -11143,10 +11140,10 @@
         <v>34</v>
       </c>
       <c r="F108" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="G108" s="17" t="s">
         <v>514</v>
-      </c>
-      <c r="G108" s="17" t="s">
-        <v>516</v>
       </c>
       <c r="H108" s="7">
         <v>9</v>
@@ -11158,7 +11155,7 @@
         <v>146</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
@@ -11221,10 +11218,10 @@
         <v>34</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H109" s="7">
         <v>10</v>
@@ -11236,7 +11233,7 @@
         <v>146</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
@@ -11299,10 +11296,10 @@
         <v>34</v>
       </c>
       <c r="F110" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H110" s="7">
         <v>9</v>
@@ -11314,7 +11311,7 @@
         <v>146</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
@@ -11377,10 +11374,10 @@
         <v>34</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="9"/>
@@ -11447,10 +11444,10 @@
         <v>34</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="9"/>
@@ -11517,10 +11514,10 @@
         <v>11</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H113" s="7">
         <v>4</v>
@@ -11529,10 +11526,10 @@
         <v>34</v>
       </c>
       <c r="J113" s="9" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
@@ -11595,10 +11592,10 @@
         <v>34</v>
       </c>
       <c r="F114" s="17" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H114" s="7">
         <v>3</v>
@@ -11607,10 +11604,10 @@
         <v>36</v>
       </c>
       <c r="J114" s="9" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="K114" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
@@ -11673,10 +11670,10 @@
         <v>34</v>
       </c>
       <c r="F115" s="17" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="H115" s="7">
         <v>3</v>
@@ -11685,10 +11682,10 @@
         <v>56</v>
       </c>
       <c r="J115" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="L115" s="7">
         <v>10</v>
@@ -11700,7 +11697,7 @@
         <v>146</v>
       </c>
       <c r="O115" s="17" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="P115" s="7"/>
       <c r="Q115" s="7"/>
@@ -11759,10 +11756,10 @@
         <v>34</v>
       </c>
       <c r="F116" s="17" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H116" s="7">
         <v>3</v>
@@ -11771,10 +11768,10 @@
         <v>11</v>
       </c>
       <c r="J116" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
@@ -11837,10 +11834,10 @@
         <v>34</v>
       </c>
       <c r="F117" s="17" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H117" s="7"/>
       <c r="I117" s="9"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntk\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75A692D-16E7-4894-8DCF-11600110915F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A16E7FA-3275-429B-93F6-A05018BD16A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -247,27 +247,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>&lt;i&gt;Chiten&lt;/i&gt;&lt;/b&gt;</t>
-    </r>
-  </si>
-  <si>
     <t>Reduce damage taken by 2.</t>
   </si>
   <si>
@@ -593,9 +572,6 @@
     <t>&lt;b&gt;&lt;i&gt;Two Arms&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t>Terrain interactions cost 1 less AP</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Plot Armour:&lt;/b&gt; chargeT</t>
   </si>
   <si>
@@ -626,10 +602,6 @@
     </r>
   </si>
   <si>
-    <t>Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;&lt;i&gt;Regenerative&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
@@ -730,10 +702,6 @@
       </rPr>
       <t>&lt;i&gt;Recharge&lt;/i&gt;&lt;/b&gt;</t>
     </r>
-  </si>
-  <si>
-    <t>Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
   </si>
   <si>
     <t>Mechanical</t>
@@ -2612,6 +2580,32 @@
   </si>
   <si>
     <t>&lt;span style="color:#27ae60"&gt;&lt;b&gt;Jazz&lt;/b&gt;&lt;/span&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>&lt;i&gt;Chiton&lt;/i&gt;&lt;/b&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Terrain interactions cost 1 less AP.</t>
+  </si>
+  <si>
+    <t>Your attacks have the Crit option:
+&lt;br&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
+  </si>
+  <si>
+    <t>Your attacks have the Crit option:
+&lt;br&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
   </si>
 </sst>
 </file>
@@ -3323,33 +3317,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG196"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="1.42578125" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="1.44140625" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="42.42578125" customWidth="1"/>
-    <col min="9" max="9" width="1.42578125" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
-    <col min="12" max="12" width="31.7109375" customWidth="1"/>
-    <col min="13" max="13" width="37.85546875" style="25" customWidth="1"/>
-    <col min="14" max="14" width="1.42578125" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" customWidth="1"/>
-    <col min="17" max="17" width="25.5703125" customWidth="1"/>
-    <col min="18" max="18" width="35.140625" customWidth="1"/>
-    <col min="19" max="19" width="1.42578125" customWidth="1"/>
+    <col min="8" max="8" width="42.44140625" customWidth="1"/>
+    <col min="9" max="9" width="1.44140625" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="12" max="12" width="31.6640625" customWidth="1"/>
+    <col min="13" max="13" width="37.88671875" style="25" customWidth="1"/>
+    <col min="14" max="14" width="1.44140625" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" customWidth="1"/>
+    <col min="17" max="17" width="25.5546875" customWidth="1"/>
+    <col min="18" max="18" width="35.109375" customWidth="1"/>
+    <col min="19" max="19" width="1.44140625" customWidth="1"/>
     <col min="20" max="20" width="10" customWidth="1"/>
     <col min="21" max="21" width="38" customWidth="1"/>
-    <col min="24" max="31" width="10.5703125" customWidth="1"/>
+    <col min="24" max="31" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3360,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -3375,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>7</v>
@@ -3390,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>11</v>
@@ -3405,7 +3399,7 @@
         <v>14</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>15</v>
@@ -3450,7 +3444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3494,10 +3488,10 @@
         <v>2.96</v>
       </c>
       <c r="U2" s="6">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="V2" s="6">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="W2" s="6">
         <v>-0.12</v>
@@ -3519,30 +3513,30 @@
       </c>
       <c r="AB2" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC2" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD2" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE2" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF2" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG2" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
@@ -3561,7 +3555,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="6">
@@ -3609,30 +3603,30 @@
       </c>
       <c r="AB3" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC3" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD3" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE3" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.0600000000000005</v>
+        <v>6.25</v>
       </c>
       <c r="AF3" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.94</v>
+        <v>6.13</v>
       </c>
       <c r="AG3" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
@@ -3650,23 +3644,23 @@
         <v>31</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="6">
         <v>3</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="6"/>
@@ -3676,7 +3670,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="6"/>
       <c r="U4" s="11" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -3695,51 +3689,51 @@
       </c>
       <c r="AB4" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC4" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD4" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF4" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG4" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="6">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="6">
@@ -3749,10 +3743,10 @@
         <v>31</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="6"/>
@@ -3762,7 +3756,7 @@
       <c r="S5" s="7"/>
       <c r="T5" s="6"/>
       <c r="U5" s="12" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -3781,32 +3775,32 @@
       </c>
       <c r="AB5" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC5" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD5" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE5" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF5" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG5" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -3820,10 +3814,10 @@
         <v>31</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="6"/>
@@ -3838,7 +3832,7 @@
       <c r="S6" s="7"/>
       <c r="T6" s="6"/>
       <c r="U6" s="13" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -3857,32 +3851,32 @@
       </c>
       <c r="AB6" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC6" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD6" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE6" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF6" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG6" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>30</v>
@@ -3896,23 +3890,23 @@
         <v>31</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
         <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="N7" s="22"/>
       <c r="O7" s="6"/>
@@ -3939,32 +3933,32 @@
       </c>
       <c r="AB7" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC7" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD7" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE7" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF7" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG7" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
@@ -3978,10 +3972,10 @@
         <v>31</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6">
@@ -3991,10 +3985,10 @@
         <v>31</v>
       </c>
       <c r="L8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="N8" s="22"/>
       <c r="O8" s="6">
@@ -4004,10 +3998,10 @@
         <v>31</v>
       </c>
       <c r="Q8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="6"/>
@@ -4029,32 +4023,32 @@
       </c>
       <c r="AB8" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC8" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE8" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.0600000000000005</v>
+        <v>6.25</v>
       </c>
       <c r="AF8" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.94</v>
+        <v>6.13</v>
       </c>
       <c r="AG8" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>30</v>
@@ -4068,10 +4062,10 @@
         <v>31</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -4081,10 +4075,10 @@
         <v>31</v>
       </c>
       <c r="L9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="N9" s="22"/>
       <c r="O9" s="6"/>
@@ -4111,38 +4105,38 @@
       </c>
       <c r="AB9" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC9" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD9" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE9" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF9" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG9" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="6">
@@ -4152,10 +4146,10 @@
         <v>31</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
@@ -4165,10 +4159,10 @@
         <v>31</v>
       </c>
       <c r="L10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="N10" s="22"/>
       <c r="O10" s="6"/>
@@ -4195,38 +4189,38 @@
       </c>
       <c r="AB10" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC10" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD10" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE10" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF10" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG10" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="6">
@@ -4236,10 +4230,10 @@
         <v>31</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
@@ -4249,23 +4243,23 @@
         <v>31</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>84</v>
+        <v>558</v>
       </c>
       <c r="N11" s="22"/>
       <c r="O11" s="6">
         <v>6</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="6"/>
@@ -4287,32 +4281,32 @@
       </c>
       <c r="AB11" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD11" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE11" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.1400000000000006</v>
+        <v>5.31</v>
       </c>
       <c r="AF11" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.0200000000000005</v>
+        <v>5.1899999999999995</v>
       </c>
       <c r="AG11" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>5.9099999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
@@ -4326,10 +4320,10 @@
         <v>31</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>89</v>
+        <v>559</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="6">
@@ -4339,10 +4333,10 @@
         <v>31</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N12" s="22"/>
       <c r="O12" s="6"/>
@@ -4369,32 +4363,32 @@
       </c>
       <c r="AB12" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC12" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD12" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE12" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF12" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG12" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
@@ -4408,10 +4402,10 @@
         <v>31</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="6">
@@ -4421,10 +4415,10 @@
         <v>31</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N13" s="22"/>
       <c r="O13" s="6">
@@ -4434,10 +4428,10 @@
         <v>31</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S13" s="7"/>
       <c r="T13" s="6"/>
@@ -4459,64 +4453,64 @@
       </c>
       <c r="AB13" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC13" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD13" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE13" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.0600000000000005</v>
+        <v>6.25</v>
       </c>
       <c r="AF13" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.94</v>
+        <v>6.13</v>
       </c>
       <c r="AG13" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="6">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="6">
         <v>4</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N14" s="22"/>
       <c r="O14" s="6">
@@ -4526,10 +4520,10 @@
         <v>31</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>106</v>
+        <v>560</v>
       </c>
       <c r="S14" s="7"/>
       <c r="T14" s="6"/>
@@ -4551,38 +4545,38 @@
       </c>
       <c r="AB14" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC14" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD14" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE14" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.6000000000000014</v>
+        <v>5.7799999999999994</v>
       </c>
       <c r="AF14" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.4800000000000013</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AG14" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.2000000000000011</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>6.379999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="6">
@@ -4592,10 +4586,10 @@
         <v>31</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="6">
@@ -4629,38 +4623,38 @@
       </c>
       <c r="AB15" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC15" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD15" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE15" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF15" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG15" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="6">
@@ -4670,10 +4664,10 @@
         <v>31</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="6">
@@ -4683,10 +4677,10 @@
         <v>31</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N16" s="22"/>
       <c r="O16" s="6">
@@ -4696,10 +4690,10 @@
         <v>31</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="S16" s="7"/>
       <c r="T16" s="6"/>
@@ -4721,32 +4715,32 @@
       </c>
       <c r="AB16" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC16" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD16" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE16" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.5200000000000014</v>
+        <v>6.72</v>
       </c>
       <c r="AF16" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.4000000000000012</v>
+        <v>6.6</v>
       </c>
       <c r="AG16" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.120000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>7.3199999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>30</v>
@@ -4757,26 +4751,26 @@
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6">
         <v>3</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N17" s="22"/>
       <c r="O17" s="6">
@@ -4786,10 +4780,10 @@
         <v>31</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="6"/>
@@ -4811,32 +4805,32 @@
       </c>
       <c r="AB17" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC17" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.1400000000000006</v>
+        <v>5.31</v>
       </c>
       <c r="AF17" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.0200000000000005</v>
+        <v>5.1899999999999995</v>
       </c>
       <c r="AG17" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>5.9099999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>30</v>
@@ -4850,23 +4844,23 @@
         <v>31</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="6">
         <v>8</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N18" s="22"/>
       <c r="O18" s="6"/>
@@ -4893,32 +4887,32 @@
       </c>
       <c r="AB18" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.82</v>
+        <v>5.95</v>
       </c>
       <c r="AC18" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.7</v>
+        <v>5.83</v>
       </c>
       <c r="AD18" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
       <c r="AE18" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF18" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>30</v>
@@ -4932,10 +4926,10 @@
         <v>31</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="6">
@@ -4945,10 +4939,10 @@
         <v>31</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N19" s="22"/>
       <c r="O19" s="6"/>
@@ -4975,64 +4969,64 @@
       </c>
       <c r="AB19" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC19" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD19" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE19" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF19" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" ht="135" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="6">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N20" s="22"/>
       <c r="O20" s="6"/>
@@ -5059,32 +5053,32 @@
       </c>
       <c r="AB20" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.5560000000000009</v>
+        <v>7.3599999999999994</v>
       </c>
       <c r="AC20" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.4360000000000008</v>
+        <v>7.2399999999999993</v>
       </c>
       <c r="AD20" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.1560000000000006</v>
+        <v>7.9599999999999991</v>
       </c>
       <c r="AE20" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF20" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>30</v>
@@ -5098,10 +5092,10 @@
         <v>31</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6">
@@ -5111,10 +5105,10 @@
         <v>31</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N21" s="22"/>
       <c r="O21" s="6">
@@ -5124,10 +5118,10 @@
         <v>31</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="S21" s="7"/>
       <c r="T21" s="6"/>
@@ -5149,38 +5143,38 @@
       </c>
       <c r="AB21" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC21" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD21" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE21" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.1400000000000006</v>
+        <v>5.31</v>
       </c>
       <c r="AF21" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.0200000000000005</v>
+        <v>5.1899999999999995</v>
       </c>
       <c r="AG21" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>5.9099999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="6">
@@ -5190,10 +5184,10 @@
         <v>31</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6">
@@ -5203,10 +5197,10 @@
         <v>31</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N22" s="22"/>
       <c r="O22" s="6">
@@ -5216,10 +5210,10 @@
         <v>31</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S22" s="7"/>
       <c r="T22" s="6"/>
@@ -5241,32 +5235,32 @@
       </c>
       <c r="AB22" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC22" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD22" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE22" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.6000000000000014</v>
+        <v>5.7799999999999994</v>
       </c>
       <c r="AF22" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.4800000000000013</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AG22" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.2000000000000011</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>6.379999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>30</v>
@@ -5280,10 +5274,10 @@
         <v>31</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="6">
@@ -5293,10 +5287,10 @@
         <v>31</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N23" s="23"/>
       <c r="O23" s="6"/>
@@ -5333,32 +5327,32 @@
       </c>
       <c r="AB23" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC23" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD23" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE23" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF23" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG23" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>30</v>
@@ -5372,23 +5366,23 @@
         <v>31</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N24" s="22"/>
       <c r="O24" s="8"/>
@@ -5415,51 +5409,51 @@
       </c>
       <c r="AB24" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.07</v>
       </c>
       <c r="AC24" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>3.95</v>
       </c>
       <c r="AD24" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>4.67</v>
       </c>
       <c r="AE24" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF24" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG24" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="6">
         <v>1</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="6">
@@ -5469,23 +5463,23 @@
         <v>31</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="N25" s="22"/>
       <c r="O25" s="6">
         <v>9</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="6"/>
@@ -5507,32 +5501,32 @@
       </c>
       <c r="AB25" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC25" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD25" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE25" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.5200000000000014</v>
+        <v>6.72</v>
       </c>
       <c r="AF25" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.4000000000000012</v>
+        <v>6.6</v>
       </c>
       <c r="AG25" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.120000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>7.3199999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>30</v>
@@ -5546,10 +5540,10 @@
         <v>31</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="6">
@@ -5559,10 +5553,10 @@
         <v>31</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N26" s="22"/>
       <c r="O26" s="6">
@@ -5572,10 +5566,10 @@
         <v>31</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="S26" s="7"/>
       <c r="T26" s="6"/>
@@ -5597,32 +5591,32 @@
       </c>
       <c r="AB26" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC26" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD26" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE26" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.0600000000000005</v>
+        <v>6.25</v>
       </c>
       <c r="AF26" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.94</v>
+        <v>6.13</v>
       </c>
       <c r="AG26" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>30</v>
@@ -5636,23 +5630,23 @@
         <v>31</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N27" s="22"/>
       <c r="O27" s="6"/>
@@ -5679,35 +5673,35 @@
       </c>
       <c r="AB27" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC27" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
       <c r="AD27" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="AE27" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF27" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG27" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="7"/>
@@ -5715,13 +5709,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="6"/>
@@ -5753,35 +5747,35 @@
       </c>
       <c r="AB28" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC28" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD28" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE28" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF28" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG28" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
@@ -5792,10 +5786,10 @@
         <v>31</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="6">
@@ -5805,10 +5799,10 @@
         <v>31</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N29" s="22"/>
       <c r="O29" s="6"/>
@@ -5835,35 +5829,35 @@
       </c>
       <c r="AB29" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC29" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD29" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE29" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF29" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG29" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="15"/>
@@ -5874,10 +5868,10 @@
         <v>31</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="6"/>
@@ -5909,35 +5903,35 @@
       </c>
       <c r="AB30" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC30" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD30" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE30" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF30" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG30" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="15"/>
@@ -5948,10 +5942,10 @@
         <v>31</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="6"/>
@@ -5983,35 +5977,35 @@
       </c>
       <c r="AB31" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC31" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD31" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE31" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF31" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG31" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="15"/>
@@ -6022,10 +6016,10 @@
         <v>31</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="6"/>
@@ -6057,35 +6051,35 @@
       </c>
       <c r="AB32" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC32" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD32" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE32" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF32" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG32" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="15"/>
@@ -6096,10 +6090,10 @@
         <v>31</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="6"/>
@@ -6131,35 +6125,35 @@
       </c>
       <c r="AB33" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC33" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD33" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE33" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF33" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG33" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7"/>
@@ -6167,13 +6161,13 @@
         <v>1</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="6"/>
@@ -6205,35 +6199,35 @@
       </c>
       <c r="AB34" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC34" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD34" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE34" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF34" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG34" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
@@ -6244,10 +6238,10 @@
         <v>31</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="6"/>
@@ -6279,35 +6273,35 @@
       </c>
       <c r="AB35" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC35" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD35" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE35" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF35" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG35" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="7"/>
@@ -6318,10 +6312,10 @@
         <v>31</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="6">
@@ -6331,10 +6325,10 @@
         <v>31</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N36" s="22"/>
       <c r="O36" s="6"/>
@@ -6361,35 +6355,35 @@
       </c>
       <c r="AB36" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC36" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD36" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE36" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF36" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG36" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="7"/>
@@ -6400,10 +6394,10 @@
         <v>31</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6"/>
@@ -6435,35 +6429,35 @@
       </c>
       <c r="AB37" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC37" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD37" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE37" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF37" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG37" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
@@ -6474,10 +6468,10 @@
         <v>31</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="6"/>
@@ -6509,51 +6503,51 @@
       </c>
       <c r="AB38" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC38" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD38" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE38" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF38" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG38" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="6">
         <v>1</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="6"/>
@@ -6585,35 +6579,35 @@
       </c>
       <c r="AB39" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC39" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD39" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE39" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF39" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG39" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
@@ -6621,13 +6615,13 @@
         <v>1</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="6">
@@ -6637,10 +6631,10 @@
         <v>31</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N40" s="22"/>
       <c r="O40" s="6"/>
@@ -6667,35 +6661,35 @@
       </c>
       <c r="AB40" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.3600000000000012</v>
+        <v>5.4799999999999995</v>
       </c>
       <c r="AC40" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.2400000000000011</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AD40" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.9600000000000009</v>
+        <v>6.0799999999999992</v>
       </c>
       <c r="AE40" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF40" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG40" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="7"/>
@@ -6706,10 +6700,10 @@
         <v>31</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="6"/>
@@ -6741,35 +6735,35 @@
       </c>
       <c r="AB41" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC41" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD41" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE41" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF41" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG41" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="7"/>
@@ -6780,10 +6774,10 @@
         <v>31</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="6"/>
@@ -6815,35 +6809,35 @@
       </c>
       <c r="AB42" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC42" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD42" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE42" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF42" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG42" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="7"/>
@@ -6854,36 +6848,36 @@
         <v>31</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="6">
         <v>5</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N43" s="22"/>
       <c r="O43" s="6">
         <v>9</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="6"/>
@@ -6905,35 +6899,35 @@
       </c>
       <c r="AB43" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC43" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD43" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE43" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.5200000000000014</v>
+        <v>6.72</v>
       </c>
       <c r="AF43" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.4000000000000012</v>
+        <v>6.6</v>
       </c>
       <c r="AG43" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.120000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>7.3199999999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="7"/>
@@ -6941,13 +6935,13 @@
         <v>1</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6">
@@ -6957,10 +6951,10 @@
         <v>31</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N44" s="22"/>
       <c r="O44" s="6"/>
@@ -6987,51 +6981,51 @@
       </c>
       <c r="AB44" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.3600000000000012</v>
+        <v>5.4799999999999995</v>
       </c>
       <c r="AC44" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.2400000000000011</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AD44" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.9600000000000009</v>
+        <v>6.0799999999999992</v>
       </c>
       <c r="AE44" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF44" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG44" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="6">
         <v>1</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
@@ -7063,35 +7057,35 @@
       </c>
       <c r="AB45" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC45" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD45" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE45" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF45" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG45" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
@@ -7102,10 +7096,10 @@
         <v>31</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="6">
@@ -7115,10 +7109,10 @@
         <v>31</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N46" s="22"/>
       <c r="O46" s="6"/>
@@ -7145,35 +7139,35 @@
       </c>
       <c r="AB46" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC46" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD46" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE46" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF46" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG46" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="47" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="7"/>
@@ -7184,10 +7178,10 @@
         <v>31</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="6"/>
@@ -7219,35 +7213,35 @@
       </c>
       <c r="AB47" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC47" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD47" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE47" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF47" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG47" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
@@ -7258,23 +7252,23 @@
         <v>31</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="6">
         <v>6</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="N48" s="22"/>
       <c r="O48" s="6"/>
@@ -7301,35 +7295,35 @@
       </c>
       <c r="AB48" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC48" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD48" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE48" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF48" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG48" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
@@ -7337,13 +7331,13 @@
         <v>1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="6"/>
@@ -7375,35 +7369,35 @@
       </c>
       <c r="AB49" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC49" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD49" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE49" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF49" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG49" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
@@ -7414,10 +7408,10 @@
         <v>31</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="6">
@@ -7427,10 +7421,10 @@
         <v>31</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N50" s="22"/>
       <c r="O50" s="6"/>
@@ -7457,35 +7451,35 @@
       </c>
       <c r="AB50" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC50" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD50" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE50" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF50" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG50" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
@@ -7493,13 +7487,13 @@
         <v>1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="6"/>
@@ -7531,35 +7525,35 @@
       </c>
       <c r="AB51" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC51" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD51" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE51" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF51" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG51" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
@@ -7567,13 +7561,13 @@
         <v>1</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
@@ -7605,35 +7599,35 @@
       </c>
       <c r="AB52" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC52" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD52" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE52" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF52" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG52" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
@@ -7641,13 +7635,13 @@
         <v>1</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="6"/>
@@ -7679,35 +7673,35 @@
       </c>
       <c r="AB53" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC53" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD53" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE53" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF53" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG53" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="7"/>
@@ -7715,13 +7709,13 @@
         <v>1</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="6">
@@ -7731,10 +7725,10 @@
         <v>31</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="N54" s="22"/>
       <c r="O54" s="6"/>
@@ -7761,35 +7755,35 @@
       </c>
       <c r="AB54" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC54" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD54" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE54" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF54" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG54" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="7"/>
@@ -7800,10 +7794,10 @@
         <v>31</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="6"/>
@@ -7835,35 +7829,35 @@
       </c>
       <c r="AB55" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC55" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD55" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE55" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF55" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG55" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="7"/>
@@ -7874,23 +7868,23 @@
         <v>31</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="6">
         <v>6</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N56" s="22"/>
       <c r="O56" s="6"/>
@@ -7917,35 +7911,35 @@
       </c>
       <c r="AB56" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC56" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD56" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE56" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF56" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG56" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="7"/>
@@ -7953,13 +7947,13 @@
         <v>1</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="6">
@@ -7969,10 +7963,10 @@
         <v>31</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N57" s="22"/>
       <c r="O57" s="6"/>
@@ -7999,35 +7993,35 @@
       </c>
       <c r="AB57" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC57" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD57" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE57" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF57" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG57" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="7"/>
@@ -8038,23 +8032,23 @@
         <v>31</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="6">
         <v>5</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N58" s="22"/>
       <c r="O58" s="6"/>
@@ -8081,35 +8075,35 @@
       </c>
       <c r="AB58" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC58" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD58" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE58" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF58" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG58" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="7"/>
@@ -8120,10 +8114,10 @@
         <v>31</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="6"/>
@@ -8155,35 +8149,35 @@
       </c>
       <c r="AB59" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC59" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD59" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE59" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF59" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG59" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="7"/>
@@ -8191,13 +8185,13 @@
         <v>1</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="6">
@@ -8207,10 +8201,10 @@
         <v>31</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N60" s="22"/>
       <c r="O60" s="6"/>
@@ -8237,35 +8231,35 @@
       </c>
       <c r="AB60" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC60" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD60" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE60" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF60" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG60" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="61" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="7"/>
@@ -8276,10 +8270,10 @@
         <v>31</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="6"/>
@@ -8311,35 +8305,35 @@
       </c>
       <c r="AB61" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC61" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD61" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE61" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF61" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG61" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="7"/>
@@ -8347,13 +8341,13 @@
         <v>1</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="6"/>
@@ -8385,35 +8379,35 @@
       </c>
       <c r="AB62" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC62" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD62" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE62" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF62" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG62" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="7"/>
@@ -8421,13 +8415,13 @@
         <v>1</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="6"/>
@@ -8459,35 +8453,35 @@
       </c>
       <c r="AB63" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC63" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD63" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE63" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF63" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG63" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="7"/>
@@ -8495,13 +8489,13 @@
         <v>1</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="6">
@@ -8511,10 +8505,10 @@
         <v>31</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N64" s="22"/>
       <c r="O64" s="6"/>
@@ -8541,35 +8535,35 @@
       </c>
       <c r="AB64" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC64" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD64" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE64" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF64" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG64" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="7"/>
@@ -8580,10 +8574,10 @@
         <v>31</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="6"/>
@@ -8615,35 +8609,35 @@
       </c>
       <c r="AB65" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC65" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD65" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE65" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF65" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG65" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="7"/>
@@ -8651,13 +8645,13 @@
         <v>1</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="6">
@@ -8667,10 +8661,10 @@
         <v>31</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N66" s="22"/>
       <c r="O66" s="6"/>
@@ -8697,35 +8691,35 @@
       </c>
       <c r="AB66" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.3600000000000012</v>
+        <v>5.4799999999999995</v>
       </c>
       <c r="AC66" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.2400000000000011</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AD66" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.9600000000000009</v>
+        <v>6.0799999999999992</v>
       </c>
       <c r="AE66" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF66" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG66" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="67" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="7"/>
@@ -8733,13 +8727,13 @@
         <v>1</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="6"/>
@@ -8771,35 +8765,35 @@
       </c>
       <c r="AB67" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC67" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD67" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE67" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF67" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG67" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="7"/>
@@ -8807,13 +8801,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="6">
@@ -8823,10 +8817,10 @@
         <v>31</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="N68" s="22"/>
       <c r="O68" s="6"/>
@@ -8853,35 +8847,35 @@
       </c>
       <c r="AB68" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC68" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD68" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE68" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF68" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG68" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="7"/>
@@ -8889,13 +8883,13 @@
         <v>1</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="6"/>
@@ -8927,35 +8921,35 @@
       </c>
       <c r="AB69" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC69" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD69" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE69" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF69" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG69" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="15"/>
@@ -8963,39 +8957,39 @@
         <v>1</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I70" s="15"/>
       <c r="J70" s="6">
         <v>5</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N70" s="23"/>
       <c r="O70" s="6">
         <v>9.5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="S70" s="15"/>
       <c r="T70" s="6"/>
@@ -9017,35 +9011,35 @@
       </c>
       <c r="AB70" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC70" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD70" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE70" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.75</v>
+        <v>6.9550000000000001</v>
       </c>
       <c r="AF70" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.63</v>
+        <v>6.835</v>
       </c>
       <c r="AG70" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>7.5549999999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="15"/>
@@ -9053,26 +9047,26 @@
         <v>1</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="6">
         <v>9</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N71" s="23"/>
       <c r="O71" s="6">
@@ -9101,35 +9095,35 @@
       </c>
       <c r="AB71" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC71" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD71" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE71" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.68</v>
+        <v>4.84</v>
       </c>
       <c r="AF71" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.5599999999999996</v>
+        <v>4.72</v>
       </c>
       <c r="AG71" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.2799999999999994</v>
-      </c>
-    </row>
-    <row r="72" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>5.4399999999999995</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="7"/>
@@ -9137,26 +9131,26 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="6">
         <v>6</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N72" s="22"/>
       <c r="O72" s="6"/>
@@ -9183,35 +9177,35 @@
       </c>
       <c r="AB72" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC72" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD72" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE72" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF72" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG72" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="73" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="15"/>
@@ -9219,26 +9213,26 @@
         <v>1</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I73" s="15"/>
       <c r="J73" s="6">
         <v>5</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="N73" s="23"/>
       <c r="O73" s="6">
@@ -9267,35 +9261,35 @@
       </c>
       <c r="AB73" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC73" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD73" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE73" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.68</v>
+        <v>4.84</v>
       </c>
       <c r="AF73" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.5599999999999996</v>
+        <v>4.72</v>
       </c>
       <c r="AG73" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.2799999999999994</v>
-      </c>
-    </row>
-    <row r="74" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>5.4399999999999995</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="7"/>
@@ -9303,13 +9297,13 @@
         <v>1</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="6">
@@ -9319,10 +9313,10 @@
         <v>31</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N74" s="22"/>
       <c r="O74" s="6"/>
@@ -9349,35 +9343,35 @@
       </c>
       <c r="AB74" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC74" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD74" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE74" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF74" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG74" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="7"/>
@@ -9385,13 +9379,13 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="6">
@@ -9401,10 +9395,10 @@
         <v>31</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="N75" s="22"/>
       <c r="O75" s="6"/>
@@ -9431,35 +9425,35 @@
       </c>
       <c r="AB75" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC75" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD75" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE75" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF75" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG75" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="7"/>
@@ -9467,26 +9461,26 @@
         <v>1</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="6">
         <v>9</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N76" s="22"/>
       <c r="O76" s="6"/>
@@ -9513,35 +9507,35 @@
       </c>
       <c r="AB76" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC76" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD76" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE76" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF76" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG76" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="7"/>
@@ -9549,13 +9543,13 @@
         <v>1</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="6">
@@ -9565,10 +9559,10 @@
         <v>31</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="N77" s="22"/>
       <c r="O77" s="6"/>
@@ -9595,35 +9589,35 @@
       </c>
       <c r="AB77" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC77" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD77" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE77" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF77" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG77" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="78" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="7"/>
@@ -9631,13 +9625,13 @@
         <v>1</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="8">
@@ -9647,10 +9641,10 @@
         <v>31</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N78" s="22"/>
       <c r="O78" s="6"/>
@@ -9677,35 +9671,35 @@
       </c>
       <c r="AB78" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC78" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD78" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE78" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF78" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG78" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="79" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="7"/>
@@ -9713,26 +9707,26 @@
         <v>1</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="6">
         <v>3</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="N79" s="22"/>
       <c r="O79" s="6"/>
@@ -9759,35 +9753,35 @@
       </c>
       <c r="AB79" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC79" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD79" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE79" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF79" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG79" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="80" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="7"/>
@@ -9795,39 +9789,39 @@
         <v>1</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="8">
         <v>3</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N80" s="22"/>
       <c r="O80" s="6">
         <v>9.5</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="S80" s="7"/>
       <c r="T80" s="6"/>
@@ -9849,35 +9843,35 @@
       </c>
       <c r="AB80" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC80" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD80" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE80" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.75</v>
+        <v>6.9550000000000001</v>
       </c>
       <c r="AF80" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.63</v>
+        <v>6.835</v>
       </c>
       <c r="AG80" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="81" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>7.5549999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C81" s="6"/>
       <c r="D81" s="7"/>
@@ -9885,39 +9879,39 @@
         <v>1</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="6">
         <v>3</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="N81" s="22"/>
       <c r="O81" s="6">
         <v>9.5</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="6"/>
@@ -9939,35 +9933,35 @@
       </c>
       <c r="AB81" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC81" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD81" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE81" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.75</v>
+        <v>6.9550000000000001</v>
       </c>
       <c r="AF81" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.63</v>
+        <v>6.835</v>
       </c>
       <c r="AG81" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="82" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>7.5549999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="7"/>
@@ -9975,13 +9969,13 @@
         <v>1</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="6"/>
@@ -10013,64 +10007,64 @@
       </c>
       <c r="AB82" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC82" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD82" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE82" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF82" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG82" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="83" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="6">
         <v>1</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="6">
         <v>4</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="N83" s="22"/>
       <c r="O83" s="6"/>
@@ -10097,35 +10091,35 @@
       </c>
       <c r="AB83" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC83" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD83" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE83" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF83" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG83" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="84" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="7"/>
@@ -10133,26 +10127,26 @@
         <v>1</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
         <v>9.5</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N84" s="22"/>
       <c r="O84" s="6"/>
@@ -10179,35 +10173,35 @@
       </c>
       <c r="AB84" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.5100000000000007</v>
+        <v>6.6550000000000002</v>
       </c>
       <c r="AC84" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3900000000000006</v>
+        <v>6.5350000000000001</v>
       </c>
       <c r="AD84" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.11</v>
+        <v>7.2549999999999999</v>
       </c>
       <c r="AE84" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF84" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG84" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="85" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="7"/>
@@ -10215,26 +10209,26 @@
         <v>1</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="6">
         <v>3</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="N85" s="22"/>
       <c r="O85" s="6"/>
@@ -10261,35 +10255,35 @@
       </c>
       <c r="AB85" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC85" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD85" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE85" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF85" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG85" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="7"/>
@@ -10297,13 +10291,13 @@
         <v>1</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="6"/>
@@ -10335,35 +10329,35 @@
       </c>
       <c r="AB86" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC86" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD86" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE86" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF86" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG86" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="87" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="7"/>
@@ -10371,26 +10365,26 @@
         <v>1</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="6">
         <v>8.5</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M87" s="18" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N87" s="22"/>
       <c r="O87" s="6"/>
@@ -10417,35 +10411,35 @@
       </c>
       <c r="AB87" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.0500000000000007</v>
+        <v>6.1849999999999996</v>
       </c>
       <c r="AC87" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.9300000000000006</v>
+        <v>6.0649999999999995</v>
       </c>
       <c r="AD87" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.65</v>
+        <v>6.7849999999999993</v>
       </c>
       <c r="AE87" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF87" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG87" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="7"/>
@@ -10453,26 +10447,26 @@
         <v>1</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="6">
         <v>3</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="N88" s="22"/>
       <c r="O88" s="6"/>
@@ -10499,35 +10493,35 @@
       </c>
       <c r="AB88" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC88" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD88" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE88" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF88" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG88" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="7"/>
@@ -10535,26 +10529,26 @@
         <v>1</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="6">
         <v>3</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="N89" s="22"/>
       <c r="O89" s="6"/>
@@ -10581,35 +10575,35 @@
       </c>
       <c r="AB89" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC89" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD89" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE89" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF89" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG89" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="90" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="7"/>
@@ -10617,26 +10611,26 @@
         <v>1</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="6">
         <v>3</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N90" s="22"/>
       <c r="O90" s="6"/>
@@ -10663,64 +10657,64 @@
       </c>
       <c r="AB90" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC90" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD90" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE90" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF90" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG90" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="91" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="6">
         <v>1</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="6">
         <v>5</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="N91" s="22"/>
       <c r="O91" s="6"/>
@@ -10747,35 +10741,35 @@
       </c>
       <c r="AB91" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC91" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD91" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE91" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF91" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG91" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
@@ -10783,13 +10777,13 @@
         <v>1</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="6">
@@ -10799,10 +10793,10 @@
         <v>31</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="N92" s="22"/>
       <c r="O92" s="6"/>
@@ -10829,35 +10823,35 @@
       </c>
       <c r="AB92" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC92" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD92" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE92" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF92" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG92" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="93" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="7"/>
@@ -10865,13 +10859,13 @@
         <v>1</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="6">
@@ -10881,10 +10875,10 @@
         <v>31</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="N93" s="22"/>
       <c r="O93" s="6"/>
@@ -10911,35 +10905,35 @@
       </c>
       <c r="AB93" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC93" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD93" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE93" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF93" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG93" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="7"/>
@@ -10947,26 +10941,26 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="6">
         <v>10</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="N94" s="22"/>
       <c r="O94" s="6"/>
@@ -10993,35 +10987,35 @@
       </c>
       <c r="AB94" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.7400000000000011</v>
+        <v>6.89</v>
       </c>
       <c r="AC94" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.620000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="AD94" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.3400000000000007</v>
+        <v>7.4899999999999993</v>
       </c>
       <c r="AE94" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF94" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG94" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="95" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="7"/>
@@ -11029,13 +11023,13 @@
         <v>1</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="6">
@@ -11045,10 +11039,10 @@
         <v>31</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="N95" s="22"/>
       <c r="O95" s="6"/>
@@ -11075,35 +11069,35 @@
       </c>
       <c r="AB95" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.9000000000000004</v>
+        <v>5.01</v>
       </c>
       <c r="AC95" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.78</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AD95" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.5</v>
+        <v>5.6099999999999994</v>
       </c>
       <c r="AE95" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF95" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG95" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="7"/>
@@ -11111,13 +11105,13 @@
         <v>1</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="6">
@@ -11127,23 +11121,23 @@
         <v>31</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="N96" s="22"/>
       <c r="O96" s="6">
         <v>11</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="S96" s="7"/>
       <c r="T96" s="6"/>
@@ -11165,35 +11159,35 @@
       </c>
       <c r="AB96" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC96" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD96" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE96" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>7.4400000000000013</v>
+        <v>7.66</v>
       </c>
       <c r="AF96" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>7.3200000000000012</v>
+        <v>7.54</v>
       </c>
       <c r="AG96" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>8.0400000000000009</v>
-      </c>
-    </row>
-    <row r="97" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="7"/>
@@ -11201,13 +11195,13 @@
         <v>1</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="6"/>
@@ -11239,35 +11233,35 @@
       </c>
       <c r="AB97" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC97" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD97" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE97" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF97" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG97" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="98" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="7"/>
@@ -11275,13 +11269,13 @@
         <v>1</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="6"/>
@@ -11313,35 +11307,35 @@
       </c>
       <c r="AB98" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC98" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD98" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE98" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF98" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG98" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C99" s="6"/>
       <c r="D99" s="7"/>
@@ -11349,39 +11343,39 @@
         <v>1</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="6">
         <v>3</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N99" s="22"/>
       <c r="O99" s="6">
         <v>10</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="S99" s="7"/>
       <c r="T99" s="6"/>
@@ -11403,35 +11397,35 @@
       </c>
       <c r="AB99" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC99" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD99" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE99" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.98</v>
+        <v>7.1899999999999995</v>
       </c>
       <c r="AF99" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.86</v>
+        <v>7.0699999999999994</v>
       </c>
       <c r="AG99" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>7.7899999999999991</v>
+      </c>
+    </row>
+    <row r="100" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="7"/>
@@ -11439,26 +11433,26 @@
         <v>1</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="6">
         <v>10</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N100" s="22"/>
       <c r="O100" s="6"/>
@@ -11485,35 +11479,35 @@
       </c>
       <c r="AB100" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.7400000000000011</v>
+        <v>6.89</v>
       </c>
       <c r="AC100" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.620000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="AD100" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.3400000000000007</v>
+        <v>7.4899999999999993</v>
       </c>
       <c r="AE100" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF100" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG100" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C101" s="6"/>
       <c r="D101" s="7"/>
@@ -11521,13 +11515,13 @@
         <v>1</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="6"/>
@@ -11559,35 +11553,35 @@
       </c>
       <c r="AB101" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC101" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD101" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE101" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF101" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG101" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="102" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="7"/>
@@ -11595,13 +11589,13 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="6">
@@ -11611,10 +11605,10 @@
         <v>31</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N102" s="22"/>
       <c r="O102" s="6"/>
@@ -11641,51 +11635,51 @@
       </c>
       <c r="AB102" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.4400000000000004</v>
+        <v>4.54</v>
       </c>
       <c r="AC102" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="AD102" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="AE102" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF102" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG102" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="103" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="6">
         <v>1</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="6">
@@ -11695,10 +11689,10 @@
         <v>31</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="N103" s="22"/>
       <c r="O103" s="6"/>
@@ -11725,64 +11719,64 @@
       </c>
       <c r="AB103" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC103" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD103" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE103" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF103" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG103" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="104" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="6">
         <v>1</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="6">
         <v>3</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="N104" s="22"/>
       <c r="O104" s="6"/>
@@ -11809,35 +11803,35 @@
       </c>
       <c r="AB104" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC104" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD104" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE104" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF104" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG104" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="105" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="105" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C105" s="6"/>
       <c r="D105" s="7"/>
@@ -11845,39 +11839,39 @@
         <v>1</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="6">
         <v>3</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="N105" s="22"/>
       <c r="O105" s="6">
         <v>10</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q105" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="S105" s="7"/>
       <c r="T105" s="6"/>
@@ -11899,35 +11893,35 @@
       </c>
       <c r="AB105" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC105" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD105" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE105" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.98</v>
+        <v>7.1899999999999995</v>
       </c>
       <c r="AF105" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.86</v>
+        <v>7.0699999999999994</v>
       </c>
       <c r="AG105" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.58</v>
-      </c>
-    </row>
-    <row r="106" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>7.7899999999999991</v>
+      </c>
+    </row>
+    <row r="106" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="7"/>
@@ -11935,26 +11929,26 @@
         <v>1</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="6">
         <v>10</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N106" s="22"/>
       <c r="O106" s="6"/>
@@ -11981,35 +11975,35 @@
       </c>
       <c r="AB106" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.7400000000000011</v>
+        <v>6.89</v>
       </c>
       <c r="AC106" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.620000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="AD106" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.3400000000000007</v>
+        <v>7.4899999999999993</v>
       </c>
       <c r="AE106" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF106" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG106" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="107" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C107" s="6"/>
       <c r="D107" s="15"/>
@@ -12017,13 +12011,13 @@
         <v>1</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I107" s="15"/>
       <c r="J107" s="6">
@@ -12033,10 +12027,10 @@
         <v>31</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="N107" s="23"/>
       <c r="O107" s="6">
@@ -12065,35 +12059,35 @@
       </c>
       <c r="AB107" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC107" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD107" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE107" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.68</v>
+        <v>4.84</v>
       </c>
       <c r="AF107" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.5599999999999996</v>
+        <v>4.72</v>
       </c>
       <c r="AG107" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.2799999999999994</v>
-      </c>
-    </row>
-    <row r="108" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>5.4399999999999995</v>
+      </c>
+    </row>
+    <row r="108" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="7"/>
@@ -12101,26 +12095,26 @@
         <v>1</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="6">
         <v>9</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N108" s="22"/>
       <c r="O108" s="6"/>
@@ -12147,35 +12141,35 @@
       </c>
       <c r="AB108" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC108" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD108" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE108" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF108" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG108" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="109" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
@@ -12183,26 +12177,26 @@
         <v>1</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="6">
         <v>10</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="N109" s="22"/>
       <c r="O109" s="6"/>
@@ -12229,35 +12223,35 @@
       </c>
       <c r="AB109" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.7400000000000011</v>
+        <v>6.89</v>
       </c>
       <c r="AC109" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.620000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="AD109" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.3400000000000007</v>
+        <v>7.4899999999999993</v>
       </c>
       <c r="AE109" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF109" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG109" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="110" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="110" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
@@ -12265,26 +12259,26 @@
         <v>1</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="6">
         <v>9</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="N110" s="22"/>
       <c r="O110" s="6"/>
@@ -12311,35 +12305,35 @@
       </c>
       <c r="AB110" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.2800000000000011</v>
+        <v>6.42</v>
       </c>
       <c r="AC110" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.160000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AD110" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.8800000000000008</v>
+        <v>7.02</v>
       </c>
       <c r="AE110" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF110" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG110" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="111" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
@@ -12347,13 +12341,13 @@
         <v>1</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="6"/>
@@ -12385,35 +12379,35 @@
       </c>
       <c r="AB111" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC111" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD111" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE111" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF111" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG111" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="112" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="7"/>
@@ -12421,13 +12415,13 @@
         <v>1</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="6"/>
@@ -12459,35 +12453,35 @@
       </c>
       <c r="AB112" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC112" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD112" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE112" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF112" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG112" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="113" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="113" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
@@ -12495,26 +12489,26 @@
         <v>1</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="6">
         <v>4</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="N113" s="22"/>
       <c r="O113" s="6"/>
@@ -12541,35 +12535,35 @@
       </c>
       <c r="AB113" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC113" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="AD113" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AE113" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF113" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG113" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="114" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="114" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
@@ -12577,13 +12571,13 @@
         <v>1</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="6">
@@ -12593,10 +12587,10 @@
         <v>31</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="N114" s="22"/>
       <c r="O114" s="6"/>
@@ -12623,35 +12617,35 @@
       </c>
       <c r="AB114" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC114" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD114" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE114" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF114" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG114" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="115" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
@@ -12659,39 +12653,39 @@
         <v>1</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I115" s="7"/>
       <c r="J115" s="6">
         <v>3</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="N115" s="22"/>
       <c r="O115" s="6">
         <v>10</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="Q115" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="R115" s="8" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="S115" s="7"/>
       <c r="T115" s="6"/>
@@ -12713,35 +12707,35 @@
       </c>
       <c r="AB115" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC115" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD115" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE115" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.98</v>
+        <v>7.1899999999999995</v>
       </c>
       <c r="AF115" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.86</v>
+        <v>7.0699999999999994</v>
       </c>
       <c r="AG115" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.58</v>
-      </c>
-    </row>
-    <row r="116" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>7.7899999999999991</v>
+      </c>
+    </row>
+    <row r="116" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="7"/>
@@ -12749,26 +12743,26 @@
         <v>1</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I116" s="7"/>
       <c r="J116" s="6">
         <v>3</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N116" s="22"/>
       <c r="O116" s="6"/>
@@ -12795,35 +12789,35 @@
       </c>
       <c r="AB116" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AC116" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD116" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AE116" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF116" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG116" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="117" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
@@ -12831,13 +12825,13 @@
         <v>1</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I117" s="7"/>
       <c r="J117" s="6"/>
@@ -12869,30 +12863,30 @@
       </c>
       <c r="AB117" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC117" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>2.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AD117" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AE117" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.38</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="AF117" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>2.2599999999999998</v>
+        <v>2.37</v>
       </c>
       <c r="AG117" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+        <v>3.0900000000000003</v>
+      </c>
+    </row>
+    <row r="118" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="19"/>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -12927,7 +12921,7 @@
       <c r="AF118" s="19"/>
       <c r="AG118" s="20"/>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="19"/>
       <c r="B119" s="19"/>
       <c r="C119" s="19"/>
@@ -12962,7 +12956,7 @@
       <c r="AF119" s="19"/>
       <c r="AG119" s="20"/>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="19"/>
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
@@ -12997,7 +12991,7 @@
       <c r="AF120" s="19"/>
       <c r="AG120" s="20"/>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="19"/>
       <c r="B121" s="19"/>
       <c r="C121" s="19"/>
@@ -13032,7 +13026,7 @@
       <c r="AF121" s="19"/>
       <c r="AG121" s="20"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="19"/>
       <c r="B122" s="19"/>
       <c r="C122" s="19"/>
@@ -13067,7 +13061,7 @@
       <c r="AF122" s="19"/>
       <c r="AG122" s="20"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="19"/>
       <c r="B123" s="19"/>
       <c r="C123" s="19"/>
@@ -13102,7 +13096,7 @@
       <c r="AF123" s="19"/>
       <c r="AG123" s="20"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="19"/>
       <c r="B124" s="19"/>
       <c r="C124" s="19"/>
@@ -13137,7 +13131,7 @@
       <c r="AF124" s="19"/>
       <c r="AG124" s="20"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="19"/>
       <c r="B125" s="19"/>
       <c r="C125" s="19"/>
@@ -13172,7 +13166,7 @@
       <c r="AF125" s="19"/>
       <c r="AG125" s="20"/>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="19"/>
       <c r="B126" s="19"/>
       <c r="C126" s="19"/>
@@ -13207,7 +13201,7 @@
       <c r="AF126" s="19"/>
       <c r="AG126" s="20"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="19"/>
       <c r="B127" s="19"/>
       <c r="C127" s="19"/>
@@ -13242,7 +13236,7 @@
       <c r="AF127" s="19"/>
       <c r="AG127" s="20"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="19"/>
       <c r="B128" s="19"/>
       <c r="C128" s="19"/>
@@ -13277,7 +13271,7 @@
       <c r="AF128" s="19"/>
       <c r="AG128" s="20"/>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="19"/>
       <c r="B129" s="19"/>
       <c r="C129" s="19"/>
@@ -13312,7 +13306,7 @@
       <c r="AF129" s="19"/>
       <c r="AG129" s="20"/>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="19"/>
       <c r="B130" s="19"/>
       <c r="C130" s="19"/>
@@ -13347,7 +13341,7 @@
       <c r="AF130" s="19"/>
       <c r="AG130" s="20"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="19"/>
       <c r="B131" s="19"/>
       <c r="C131" s="19"/>
@@ -13382,7 +13376,7 @@
       <c r="AF131" s="19"/>
       <c r="AG131" s="20"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="19"/>
       <c r="B132" s="19"/>
       <c r="C132" s="19"/>
@@ -13417,7 +13411,7 @@
       <c r="AF132" s="19"/>
       <c r="AG132" s="20"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -13452,7 +13446,7 @@
       <c r="AF133" s="19"/>
       <c r="AG133" s="20"/>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="19"/>
       <c r="B134" s="19"/>
       <c r="C134" s="19"/>
@@ -13487,7 +13481,7 @@
       <c r="AF134" s="19"/>
       <c r="AG134" s="20"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="19"/>
       <c r="B135" s="19"/>
       <c r="C135" s="19"/>
@@ -13522,7 +13516,7 @@
       <c r="AF135" s="19"/>
       <c r="AG135" s="20"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="19"/>
       <c r="B136" s="19"/>
       <c r="C136" s="19"/>
@@ -13557,7 +13551,7 @@
       <c r="AF136" s="19"/>
       <c r="AG136" s="20"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="19"/>
       <c r="B137" s="19"/>
       <c r="C137" s="19"/>
@@ -13592,7 +13586,7 @@
       <c r="AF137" s="19"/>
       <c r="AG137" s="20"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="19"/>
       <c r="B138" s="19"/>
       <c r="C138" s="19"/>
@@ -13627,7 +13621,7 @@
       <c r="AF138" s="19"/>
       <c r="AG138" s="20"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="19"/>
       <c r="B139" s="19"/>
       <c r="C139" s="19"/>
@@ -13662,7 +13656,7 @@
       <c r="AF139" s="19"/>
       <c r="AG139" s="20"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="19"/>
       <c r="B140" s="19"/>
       <c r="C140" s="19"/>
@@ -13697,7 +13691,7 @@
       <c r="AF140" s="19"/>
       <c r="AG140" s="20"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="19"/>
       <c r="B141" s="19"/>
       <c r="C141" s="19"/>
@@ -13732,7 +13726,7 @@
       <c r="AF141" s="19"/>
       <c r="AG141" s="20"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="19"/>
       <c r="B142" s="19"/>
       <c r="C142" s="19"/>
@@ -13767,7 +13761,7 @@
       <c r="AF142" s="19"/>
       <c r="AG142" s="20"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="19"/>
       <c r="B143" s="19"/>
       <c r="C143" s="19"/>
@@ -13802,7 +13796,7 @@
       <c r="AF143" s="19"/>
       <c r="AG143" s="20"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="19"/>
       <c r="B144" s="19"/>
       <c r="C144" s="19"/>
@@ -13837,7 +13831,7 @@
       <c r="AF144" s="19"/>
       <c r="AG144" s="20"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="19"/>
       <c r="B145" s="19"/>
       <c r="C145" s="19"/>
@@ -13872,7 +13866,7 @@
       <c r="AF145" s="19"/>
       <c r="AG145" s="20"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="19"/>
       <c r="B146" s="19"/>
       <c r="C146" s="19"/>
@@ -13907,7 +13901,7 @@
       <c r="AF146" s="19"/>
       <c r="AG146" s="20"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="19"/>
       <c r="B147" s="19"/>
       <c r="C147" s="19"/>
@@ -13942,7 +13936,7 @@
       <c r="AF147" s="19"/>
       <c r="AG147" s="20"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="19"/>
       <c r="B148" s="19"/>
       <c r="C148" s="19"/>
@@ -13977,7 +13971,7 @@
       <c r="AF148" s="19"/>
       <c r="AG148" s="20"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="19"/>
       <c r="B149" s="19"/>
       <c r="C149" s="19"/>
@@ -14012,7 +14006,7 @@
       <c r="AF149" s="19"/>
       <c r="AG149" s="20"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="19"/>
       <c r="B150" s="19"/>
       <c r="C150" s="19"/>
@@ -14047,7 +14041,7 @@
       <c r="AF150" s="19"/>
       <c r="AG150" s="20"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="19"/>
       <c r="B151" s="19"/>
       <c r="C151" s="19"/>
@@ -14082,7 +14076,7 @@
       <c r="AF151" s="19"/>
       <c r="AG151" s="20"/>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="19"/>
       <c r="B152" s="19"/>
       <c r="C152" s="19"/>
@@ -14117,7 +14111,7 @@
       <c r="AF152" s="19"/>
       <c r="AG152" s="20"/>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="19"/>
       <c r="B153" s="19"/>
       <c r="C153" s="19"/>
@@ -14152,7 +14146,7 @@
       <c r="AF153" s="19"/>
       <c r="AG153" s="20"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="19"/>
       <c r="B154" s="19"/>
       <c r="C154" s="19"/>
@@ -14187,7 +14181,7 @@
       <c r="AF154" s="19"/>
       <c r="AG154" s="20"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="19"/>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
@@ -14222,7 +14216,7 @@
       <c r="AF155" s="19"/>
       <c r="AG155" s="20"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="19"/>
       <c r="B156" s="19"/>
       <c r="C156" s="19"/>
@@ -14257,7 +14251,7 @@
       <c r="AF156" s="19"/>
       <c r="AG156" s="20"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="19"/>
       <c r="B157" s="19"/>
       <c r="C157" s="19"/>
@@ -14292,7 +14286,7 @@
       <c r="AF157" s="19"/>
       <c r="AG157" s="20"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="19"/>
       <c r="B158" s="19"/>
       <c r="C158" s="19"/>
@@ -14327,7 +14321,7 @@
       <c r="AF158" s="19"/>
       <c r="AG158" s="20"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="19"/>
       <c r="B159" s="19"/>
       <c r="C159" s="19"/>
@@ -14362,7 +14356,7 @@
       <c r="AF159" s="19"/>
       <c r="AG159" s="20"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="19"/>
       <c r="B160" s="19"/>
       <c r="C160" s="19"/>
@@ -14397,7 +14391,7 @@
       <c r="AF160" s="19"/>
       <c r="AG160" s="20"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="19"/>
       <c r="B161" s="19"/>
       <c r="C161" s="19"/>
@@ -14432,7 +14426,7 @@
       <c r="AF161" s="19"/>
       <c r="AG161" s="20"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="19"/>
       <c r="B162" s="19"/>
       <c r="C162" s="19"/>
@@ -14467,7 +14461,7 @@
       <c r="AF162" s="19"/>
       <c r="AG162" s="20"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="19"/>
       <c r="B163" s="19"/>
       <c r="C163" s="19"/>
@@ -14502,7 +14496,7 @@
       <c r="AF163" s="19"/>
       <c r="AG163" s="20"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="19"/>
       <c r="B164" s="19"/>
       <c r="C164" s="19"/>
@@ -14537,7 +14531,7 @@
       <c r="AF164" s="19"/>
       <c r="AG164" s="20"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="19"/>
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
@@ -14572,7 +14566,7 @@
       <c r="AF165" s="19"/>
       <c r="AG165" s="20"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="19"/>
       <c r="B166" s="19"/>
       <c r="C166" s="19"/>
@@ -14607,7 +14601,7 @@
       <c r="AF166" s="19"/>
       <c r="AG166" s="20"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="19"/>
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
@@ -14642,7 +14636,7 @@
       <c r="AF167" s="19"/>
       <c r="AG167" s="20"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="19"/>
       <c r="B168" s="19"/>
       <c r="C168" s="19"/>
@@ -14677,7 +14671,7 @@
       <c r="AF168" s="19"/>
       <c r="AG168" s="20"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="19"/>
       <c r="B169" s="19"/>
       <c r="C169" s="19"/>
@@ -14712,7 +14706,7 @@
       <c r="AF169" s="19"/>
       <c r="AG169" s="20"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="19"/>
       <c r="B170" s="19"/>
       <c r="C170" s="19"/>
@@ -14747,7 +14741,7 @@
       <c r="AF170" s="19"/>
       <c r="AG170" s="20"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="19"/>
       <c r="B171" s="19"/>
       <c r="C171" s="19"/>
@@ -14782,7 +14776,7 @@
       <c r="AF171" s="19"/>
       <c r="AG171" s="20"/>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="19"/>
       <c r="B172" s="19"/>
       <c r="C172" s="19"/>
@@ -14817,7 +14811,7 @@
       <c r="AF172" s="19"/>
       <c r="AG172" s="20"/>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="19"/>
       <c r="B173" s="19"/>
       <c r="C173" s="19"/>
@@ -14852,7 +14846,7 @@
       <c r="AF173" s="19"/>
       <c r="AG173" s="20"/>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="19"/>
       <c r="B174" s="19"/>
       <c r="C174" s="19"/>
@@ -14887,7 +14881,7 @@
       <c r="AF174" s="19"/>
       <c r="AG174" s="20"/>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="19"/>
       <c r="B175" s="19"/>
       <c r="C175" s="19"/>
@@ -14922,7 +14916,7 @@
       <c r="AF175" s="19"/>
       <c r="AG175" s="20"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="19"/>
       <c r="B176" s="19"/>
       <c r="C176" s="19"/>
@@ -14957,7 +14951,7 @@
       <c r="AF176" s="19"/>
       <c r="AG176" s="20"/>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="19"/>
       <c r="B177" s="19"/>
       <c r="C177" s="19"/>
@@ -14992,7 +14986,7 @@
       <c r="AF177" s="19"/>
       <c r="AG177" s="20"/>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="19"/>
       <c r="B178" s="19"/>
       <c r="C178" s="19"/>
@@ -15027,7 +15021,7 @@
       <c r="AF178" s="19"/>
       <c r="AG178" s="20"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="19"/>
       <c r="B179" s="19"/>
       <c r="C179" s="19"/>
@@ -15062,7 +15056,7 @@
       <c r="AF179" s="19"/>
       <c r="AG179" s="20"/>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="19"/>
       <c r="B180" s="19"/>
       <c r="C180" s="19"/>
@@ -15097,7 +15091,7 @@
       <c r="AF180" s="19"/>
       <c r="AG180" s="20"/>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="19"/>
       <c r="B181" s="19"/>
       <c r="C181" s="19"/>
@@ -15132,7 +15126,7 @@
       <c r="AF181" s="19"/>
       <c r="AG181" s="20"/>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="19"/>
       <c r="B182" s="19"/>
       <c r="C182" s="19"/>
@@ -15167,7 +15161,7 @@
       <c r="AF182" s="19"/>
       <c r="AG182" s="20"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="19"/>
       <c r="B183" s="19"/>
       <c r="C183" s="19"/>
@@ -15202,7 +15196,7 @@
       <c r="AF183" s="19"/>
       <c r="AG183" s="20"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="19"/>
       <c r="B184" s="19"/>
       <c r="C184" s="19"/>
@@ -15237,7 +15231,7 @@
       <c r="AF184" s="19"/>
       <c r="AG184" s="20"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="19"/>
       <c r="B185" s="19"/>
       <c r="C185" s="19"/>
@@ -15272,7 +15266,7 @@
       <c r="AF185" s="19"/>
       <c r="AG185" s="20"/>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="19"/>
       <c r="B186" s="19"/>
       <c r="C186" s="19"/>
@@ -15307,7 +15301,7 @@
       <c r="AF186" s="19"/>
       <c r="AG186" s="20"/>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="19"/>
       <c r="B187" s="19"/>
       <c r="C187" s="19"/>
@@ -15342,7 +15336,7 @@
       <c r="AF187" s="19"/>
       <c r="AG187" s="20"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="19"/>
       <c r="B188" s="19"/>
       <c r="C188" s="19"/>
@@ -15377,7 +15371,7 @@
       <c r="AF188" s="19"/>
       <c r="AG188" s="20"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="19"/>
       <c r="B189" s="19"/>
       <c r="C189" s="19"/>
@@ -15412,7 +15406,7 @@
       <c r="AF189" s="19"/>
       <c r="AG189" s="20"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="19"/>
       <c r="B190" s="19"/>
       <c r="C190" s="19"/>
@@ -15447,7 +15441,7 @@
       <c r="AF190" s="19"/>
       <c r="AG190" s="20"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="19"/>
       <c r="B191" s="19"/>
       <c r="C191" s="19"/>
@@ -15482,7 +15476,7 @@
       <c r="AF191" s="19"/>
       <c r="AG191" s="20"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="19"/>
       <c r="B192" s="19"/>
       <c r="C192" s="19"/>
@@ -15517,7 +15511,7 @@
       <c r="AF192" s="19"/>
       <c r="AG192" s="20"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="19"/>
       <c r="B193" s="19"/>
       <c r="C193" s="19"/>
@@ -15552,7 +15546,7 @@
       <c r="AF193" s="19"/>
       <c r="AG193" s="20"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="19"/>
       <c r="B194" s="19"/>
       <c r="C194" s="19"/>
@@ -15587,7 +15581,7 @@
       <c r="AF194" s="19"/>
       <c r="AG194" s="20"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="19"/>
       <c r="B195" s="19"/>
       <c r="C195" s="19"/>
@@ -15622,7 +15616,7 @@
       <c r="AF195" s="19"/>
       <c r="AG195" s="20"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="19"/>
       <c r="B196" s="19"/>
       <c r="C196" s="19"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntk\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A16E7FA-3275-429B-93F6-A05018BD16A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD22D64C-6B08-4EE9-A317-4C125E0306C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="560">
   <si>
     <t>Name</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>&lt;b&gt;&lt;i&gt;Reckless&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>Whenever you inflict a status effect, you may set that creature's composure to 1</t>
   </si>
   <si>
     <t>Beast</t>
@@ -755,9 +752,6 @@
     <t>&lt;b&gt;Coerce:&lt;/b&gt; 1 AP or WeirdT</t>
   </si>
   <si>
-    <t>Give an Ally 1 AP.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Command:&lt;/b&gt; 1 AP or WeirdT</t>
   </si>
   <si>
@@ -968,10 +962,6 @@
     </r>
   </si>
   <si>
-    <t>Effects cannot move you, only the move action will cause you to move.
-&lt;br&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
-  </si>
-  <si>
     <t>Unstable</t>
   </si>
   <si>
@@ -1003,32 +993,7 @@
     <t>Worm Nest</t>
   </si>
   <si>
-    <t>chargebig X 4</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Infect&lt;/b&gt;</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Your attacks have the Crit option
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>&lt;br&gt;&lt;b&gt;Infect:&lt;/b&gt; Spend one chargeT, target takes the chargeT and is infected.</t>
-    </r>
   </si>
   <si>
     <t>&lt;b&gt;&lt;i&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;</t>
@@ -1076,28 +1041,6 @@
         <charset val="1"/>
       </rPr>
       <t>&lt;i&gt;Through Fire&lt;/i&gt;&lt;/b&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Your attacks have the Crit option
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>&lt;br&gt;&lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
     </r>
   </si>
   <si>
@@ -1177,9 +1120,6 @@
     <t>&lt;b&gt;&lt;i&gt;Charger&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t>When you make an attack, you may move 2 tiles before attacking</t>
-  </si>
-  <si>
     <t>Balanced</t>
   </si>
   <si>
@@ -1240,9 +1180,6 @@
     <t>Disciplined</t>
   </si>
   <si>
-    <t>When you chill out, also gain up to 2 temporary composure.</t>
-  </si>
-  <si>
     <t>Dormant</t>
   </si>
   <si>
@@ -1256,9 +1193,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Burst:&lt;/b&gt; chargeT or weirdT</t>
-  </si>
-  <si>
-    <t>Replenish a jazzt or flesht</t>
   </si>
   <si>
     <t>Grandiose</t>
@@ -1333,9 +1267,6 @@
     <t>Ignore the effects of an ability with weirdt in its cost (even if no weirdT was spent).</t>
   </si>
   <si>
-    <t>&lt;b&gt;A Cup of Tea:&lt;/b&gt; 1 AP + 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;</t>
-  </si>
-  <si>
     <t>Gain the &lt;b&gt;Well rested&lt;/b&gt; status effect.</t>
   </si>
   <si>
@@ -2606,6 +2537,58 @@
   <si>
     <t>Your attacks have the Crit option:
 &lt;br&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
+  </si>
+  <si>
+    <t>Whenever you inflict a status effect, you may set that creature's composure to 1.</t>
+  </si>
+  <si>
+    <t>When you make an attack, you may move 2 tiles before attacking.</t>
+  </si>
+  <si>
+    <t>When you the the &lt;b&gt;chill out&lt;/b&gt; action, also gain up to 2 temporary composure.</t>
+  </si>
+  <si>
+    <t>Replenish a jazzt or flesht.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Cup of Tea:&lt;/b&gt; 1 AP + 1 &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Give an ally 1 AP.</t>
+  </si>
+  <si>
+    <t>You cannot be move or be made to move except with the move action.
+&lt;br&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Your attacks have the Crit option </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>&lt;b&gt;Infect:&lt;/b&gt; Spend one chargeT, target takes the chargeT and is infected.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Your attacks have the Crit option </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>&lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3354,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -3369,7 +3352,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>7</v>
@@ -3384,7 +3367,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>11</v>
@@ -3399,7 +3382,7 @@
         <v>14</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>15</v>
@@ -3476,7 +3459,7 @@
         <v>34</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>35</v>
+        <v>551</v>
       </c>
       <c r="N2" s="22"/>
       <c r="O2" s="6"/>
@@ -3488,13 +3471,13 @@
         <v>2.96</v>
       </c>
       <c r="U2" s="6">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="V2" s="6">
         <v>0.3</v>
       </c>
       <c r="W2" s="6">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="X2" s="6">
         <v>-0.6</v>
@@ -3505,7 +3488,7 @@
       </c>
       <c r="Z2" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3513,19 +3496,19 @@
       </c>
       <c r="AB2" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC2" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD2" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE2" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF2" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -3533,12 +3516,12 @@
       </c>
       <c r="AG2" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>30</v>
@@ -3552,10 +3535,10 @@
         <v>31</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="6">
@@ -3565,10 +3548,10 @@
         <v>31</v>
       </c>
       <c r="L3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="N3" s="22"/>
       <c r="O3" s="6">
@@ -3578,10 +3561,10 @@
         <v>31</v>
       </c>
       <c r="Q3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="S3" s="7"/>
       <c r="T3" s="6"/>
@@ -3595,7 +3578,7 @@
       </c>
       <c r="Z3" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3603,38 +3586,38 @@
       </c>
       <c r="AB3" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC3" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD3" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE3" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.25</v>
+        <v>6.32</v>
       </c>
       <c r="AF3" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="AG3" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="6">
@@ -3644,23 +3627,23 @@
         <v>31</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="6">
         <v>3</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="6"/>
@@ -3670,7 +3653,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="6"/>
       <c r="U4" s="11" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -3681,7 +3664,7 @@
       </c>
       <c r="Z4" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3689,19 +3672,19 @@
       </c>
       <c r="AB4" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC4" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD4" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE4" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF4" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -3709,31 +3692,31 @@
       </c>
       <c r="AG4" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="6">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="6">
@@ -3743,10 +3726,10 @@
         <v>31</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="6"/>
@@ -3756,7 +3739,7 @@
       <c r="S5" s="7"/>
       <c r="T5" s="6"/>
       <c r="U5" s="12" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -3767,7 +3750,7 @@
       </c>
       <c r="Z5" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3775,19 +3758,19 @@
       </c>
       <c r="AB5" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC5" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD5" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE5" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF5" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -3795,12 +3778,12 @@
       </c>
       <c r="AG5" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -3814,10 +3797,10 @@
         <v>31</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="6"/>
@@ -3832,7 +3815,7 @@
       <c r="S6" s="7"/>
       <c r="T6" s="6"/>
       <c r="U6" s="13" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -3843,7 +3826,7 @@
       </c>
       <c r="Z6" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3851,7 +3834,7 @@
       </c>
       <c r="AB6" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC6" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -3859,11 +3842,11 @@
       </c>
       <c r="AD6" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE6" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -3871,12 +3854,12 @@
       </c>
       <c r="AG6" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>30</v>
@@ -3890,23 +3873,23 @@
         <v>31</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
         <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="N7" s="22"/>
       <c r="O7" s="6"/>
@@ -3925,7 +3908,7 @@
       </c>
       <c r="Z7" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -3933,19 +3916,19 @@
       </c>
       <c r="AB7" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC7" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD7" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE7" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF7" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -3953,12 +3936,12 @@
       </c>
       <c r="AG7" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
@@ -3972,10 +3955,10 @@
         <v>31</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6">
@@ -3985,10 +3968,10 @@
         <v>31</v>
       </c>
       <c r="L8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="N8" s="22"/>
       <c r="O8" s="6">
@@ -3998,10 +3981,10 @@
         <v>31</v>
       </c>
       <c r="Q8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="6"/>
@@ -4015,7 +3998,7 @@
       </c>
       <c r="Z8" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4023,32 +4006,32 @@
       </c>
       <c r="AB8" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC8" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD8" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE8" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.25</v>
+        <v>6.32</v>
       </c>
       <c r="AF8" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="AG8" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>30</v>
@@ -4062,10 +4045,10 @@
         <v>31</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -4075,10 +4058,10 @@
         <v>31</v>
       </c>
       <c r="L9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="N9" s="22"/>
       <c r="O9" s="6"/>
@@ -4097,7 +4080,7 @@
       </c>
       <c r="Z9" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4105,19 +4088,19 @@
       </c>
       <c r="AB9" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC9" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD9" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE9" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4125,18 +4108,18 @@
       </c>
       <c r="AG9" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="6">
@@ -4146,10 +4129,10 @@
         <v>31</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
@@ -4159,10 +4142,10 @@
         <v>31</v>
       </c>
       <c r="L10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="N10" s="22"/>
       <c r="O10" s="6"/>
@@ -4181,7 +4164,7 @@
       </c>
       <c r="Z10" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4189,19 +4172,19 @@
       </c>
       <c r="AB10" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC10" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD10" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE10" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF10" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4209,18 +4192,18 @@
       </c>
       <c r="AG10" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="6">
@@ -4230,10 +4213,10 @@
         <v>31</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
@@ -4243,23 +4226,23 @@
         <v>31</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="N11" s="22"/>
       <c r="O11" s="6">
         <v>6</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="6"/>
@@ -4273,7 +4256,7 @@
       </c>
       <c r="Z11" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4281,32 +4264,32 @@
       </c>
       <c r="AB11" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC11" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD11" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE11" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.31</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AF11" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.1899999999999995</v>
+        <v>5.2499999999999991</v>
       </c>
       <c r="AG11" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.9099999999999993</v>
+        <v>5.9599999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
@@ -4320,10 +4303,10 @@
         <v>31</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="6">
@@ -4333,10 +4316,10 @@
         <v>31</v>
       </c>
       <c r="L12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="N12" s="22"/>
       <c r="O12" s="6"/>
@@ -4355,7 +4338,7 @@
       </c>
       <c r="Z12" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4363,19 +4346,19 @@
       </c>
       <c r="AB12" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC12" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD12" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE12" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF12" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4383,12 +4366,12 @@
       </c>
       <c r="AG12" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
@@ -4402,10 +4385,10 @@
         <v>31</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="6">
@@ -4415,10 +4398,10 @@
         <v>31</v>
       </c>
       <c r="L13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="N13" s="22"/>
       <c r="O13" s="6">
@@ -4428,10 +4411,10 @@
         <v>31</v>
       </c>
       <c r="Q13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="S13" s="7"/>
       <c r="T13" s="6"/>
@@ -4445,7 +4428,7 @@
       </c>
       <c r="Z13" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4453,64 +4436,64 @@
       </c>
       <c r="AB13" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC13" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD13" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.25</v>
+        <v>6.32</v>
       </c>
       <c r="AF13" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="AG13" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="6">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="6">
         <v>4</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="N14" s="22"/>
       <c r="O14" s="6">
@@ -4520,10 +4503,10 @@
         <v>31</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="S14" s="7"/>
       <c r="T14" s="6"/>
@@ -4537,7 +4520,7 @@
       </c>
       <c r="Z14" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4545,38 +4528,38 @@
       </c>
       <c r="AB14" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC14" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD14" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.7799999999999994</v>
+        <v>5.84</v>
       </c>
       <c r="AF14" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.6599999999999993</v>
+        <v>5.7299999999999995</v>
       </c>
       <c r="AG14" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.379999999999999</v>
+        <v>6.4399999999999995</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="6">
@@ -4586,10 +4569,10 @@
         <v>31</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="6">
@@ -4615,7 +4598,7 @@
       </c>
       <c r="Z15" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4623,19 +4606,19 @@
       </c>
       <c r="AB15" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC15" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD15" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF15" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4643,18 +4626,18 @@
       </c>
       <c r="AG15" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="6">
@@ -4664,10 +4647,10 @@
         <v>31</v>
       </c>
       <c r="G16" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="6">
@@ -4677,10 +4660,10 @@
         <v>31</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="N16" s="22"/>
       <c r="O16" s="6">
@@ -4690,10 +4673,10 @@
         <v>31</v>
       </c>
       <c r="Q16" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R16" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="S16" s="7"/>
       <c r="T16" s="6"/>
@@ -4707,7 +4690,7 @@
       </c>
       <c r="Z16" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4715,32 +4698,32 @@
       </c>
       <c r="AB16" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC16" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD16" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE16" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.72</v>
+        <v>6.8</v>
       </c>
       <c r="AF16" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.6</v>
+        <v>6.6899999999999995</v>
       </c>
       <c r="AG16" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.3199999999999994</v>
+        <v>7.3999999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>30</v>
@@ -4751,26 +4734,26 @@
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>114</v>
+        <v>556</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6">
         <v>3</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N17" s="22"/>
       <c r="O17" s="6">
@@ -4780,10 +4763,10 @@
         <v>31</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="6"/>
@@ -4797,7 +4780,7 @@
       </c>
       <c r="Z17" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA17" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4805,32 +4788,32 @@
       </c>
       <c r="AB17" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC17" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD17" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE17" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.31</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AF17" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.1899999999999995</v>
+        <v>5.2499999999999991</v>
       </c>
       <c r="AG17" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.9099999999999993</v>
+        <v>5.9599999999999991</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>30</v>
@@ -4844,23 +4827,23 @@
         <v>31</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="6">
         <v>8</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N18" s="22"/>
       <c r="O18" s="6"/>
@@ -4879,7 +4862,7 @@
       </c>
       <c r="Z18" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4887,19 +4870,19 @@
       </c>
       <c r="AB18" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.95</v>
+        <v>6.0200000000000005</v>
       </c>
       <c r="AC18" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.83</v>
+        <v>5.91</v>
       </c>
       <c r="AD18" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.55</v>
+        <v>6.62</v>
       </c>
       <c r="AE18" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF18" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4907,12 +4890,12 @@
       </c>
       <c r="AG18" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>30</v>
@@ -4926,10 +4909,10 @@
         <v>31</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="6">
@@ -4939,10 +4922,10 @@
         <v>31</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N19" s="22"/>
       <c r="O19" s="6"/>
@@ -4961,7 +4944,7 @@
       </c>
       <c r="Z19" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -4969,19 +4952,19 @@
       </c>
       <c r="AB19" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC19" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD19" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE19" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF19" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -4989,44 +4972,44 @@
       </c>
       <c r="AG19" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="6">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6">
         <v>11</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N20" s="22"/>
       <c r="O20" s="6"/>
@@ -5045,7 +5028,7 @@
       </c>
       <c r="Z20" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA20" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5053,19 +5036,19 @@
       </c>
       <c r="AB20" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>7.3599999999999994</v>
+        <v>7.4600000000000009</v>
       </c>
       <c r="AC20" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>7.2399999999999993</v>
+        <v>7.3500000000000005</v>
       </c>
       <c r="AD20" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.9599999999999991</v>
+        <v>8.06</v>
       </c>
       <c r="AE20" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF20" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5073,12 +5056,12 @@
       </c>
       <c r="AG20" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>30</v>
@@ -5092,10 +5075,10 @@
         <v>31</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6">
@@ -5105,10 +5088,10 @@
         <v>31</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N21" s="22"/>
       <c r="O21" s="6">
@@ -5118,10 +5101,10 @@
         <v>31</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S21" s="7"/>
       <c r="T21" s="6"/>
@@ -5135,7 +5118,7 @@
       </c>
       <c r="Z21" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5143,38 +5126,38 @@
       </c>
       <c r="AB21" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC21" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD21" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE21" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.31</v>
+        <v>5.3599999999999994</v>
       </c>
       <c r="AF21" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.1899999999999995</v>
+        <v>5.2499999999999991</v>
       </c>
       <c r="AG21" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.9099999999999993</v>
+        <v>5.9599999999999991</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="6">
@@ -5184,10 +5167,10 @@
         <v>31</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6">
@@ -5197,10 +5180,10 @@
         <v>31</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N22" s="22"/>
       <c r="O22" s="6">
@@ -5210,10 +5193,10 @@
         <v>31</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>148</v>
+        <v>557</v>
       </c>
       <c r="S22" s="7"/>
       <c r="T22" s="6"/>
@@ -5227,7 +5210,7 @@
       </c>
       <c r="Z22" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA22" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5235,32 +5218,32 @@
       </c>
       <c r="AB22" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC22" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD22" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE22" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.7799999999999994</v>
+        <v>5.84</v>
       </c>
       <c r="AF22" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.6599999999999993</v>
+        <v>5.7299999999999995</v>
       </c>
       <c r="AG22" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.379999999999999</v>
+        <v>6.4399999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>30</v>
@@ -5274,10 +5257,10 @@
         <v>31</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="6">
@@ -5287,10 +5270,10 @@
         <v>31</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N23" s="23"/>
       <c r="O23" s="6"/>
@@ -5319,7 +5302,7 @@
       </c>
       <c r="Z23" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA23" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5327,19 +5310,19 @@
       </c>
       <c r="AB23" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC23" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD23" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE23" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF23" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5347,12 +5330,12 @@
       </c>
       <c r="AG23" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>30</v>
@@ -5366,23 +5349,23 @@
         <v>31</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="6">
         <v>4</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N24" s="22"/>
       <c r="O24" s="8"/>
@@ -5401,7 +5384,7 @@
       </c>
       <c r="Z24" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5409,19 +5392,19 @@
       </c>
       <c r="AB24" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC24" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD24" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE24" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF24" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5429,31 +5412,31 @@
       </c>
       <c r="AG24" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>159</v>
+        <v>536</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="6">
         <v>1</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>161</v>
+        <v>558</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="6">
@@ -5463,23 +5446,23 @@
         <v>31</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N25" s="22"/>
       <c r="O25" s="6">
         <v>9</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="6"/>
@@ -5493,7 +5476,7 @@
       </c>
       <c r="Z25" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5501,32 +5484,32 @@
       </c>
       <c r="AB25" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC25" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD25" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE25" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.72</v>
+        <v>6.8</v>
       </c>
       <c r="AF25" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.6</v>
+        <v>6.6899999999999995</v>
       </c>
       <c r="AG25" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.3199999999999994</v>
+        <v>7.3999999999999995</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>30</v>
@@ -5540,10 +5523,10 @@
         <v>31</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="6">
@@ -5553,10 +5536,10 @@
         <v>31</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N26" s="22"/>
       <c r="O26" s="6">
@@ -5566,10 +5549,10 @@
         <v>31</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>172</v>
+        <v>559</v>
       </c>
       <c r="S26" s="7"/>
       <c r="T26" s="6"/>
@@ -5583,7 +5566,7 @@
       </c>
       <c r="Z26" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5591,32 +5574,32 @@
       </c>
       <c r="AB26" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC26" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD26" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE26" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.25</v>
+        <v>6.32</v>
       </c>
       <c r="AF26" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.13</v>
+        <v>6.21</v>
       </c>
       <c r="AG26" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>30</v>
@@ -5630,23 +5613,23 @@
         <v>31</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="6">
         <v>5</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="N27" s="22"/>
       <c r="O27" s="6"/>
@@ -5665,7 +5648,7 @@
       </c>
       <c r="Z27" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5673,19 +5656,19 @@
       </c>
       <c r="AB27" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC27" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD27" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE27" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF27" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5693,15 +5676,15 @@
       </c>
       <c r="AG27" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="7"/>
@@ -5709,13 +5692,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="6"/>
@@ -5739,7 +5722,7 @@
       </c>
       <c r="Z28" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5747,7 +5730,7 @@
       </c>
       <c r="AB28" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC28" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -5755,11 +5738,11 @@
       </c>
       <c r="AD28" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE28" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF28" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5767,15 +5750,15 @@
       </c>
       <c r="AG28" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
@@ -5786,10 +5769,10 @@
         <v>31</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="6">
@@ -5799,10 +5782,10 @@
         <v>31</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="N29" s="22"/>
       <c r="O29" s="6"/>
@@ -5821,7 +5804,7 @@
       </c>
       <c r="Z29" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA29" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5829,19 +5812,19 @@
       </c>
       <c r="AB29" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC29" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD29" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE29" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF29" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5849,15 +5832,15 @@
       </c>
       <c r="AG29" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="15"/>
@@ -5868,10 +5851,10 @@
         <v>31</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>189</v>
+        <v>552</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="6"/>
@@ -5895,7 +5878,7 @@
       </c>
       <c r="Z30" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5903,7 +5886,7 @@
       </c>
       <c r="AB30" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC30" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -5911,11 +5894,11 @@
       </c>
       <c r="AD30" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE30" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF30" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5923,15 +5906,15 @@
       </c>
       <c r="AG30" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="15"/>
@@ -5942,10 +5925,10 @@
         <v>31</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="6"/>
@@ -5969,7 +5952,7 @@
       </c>
       <c r="Z31" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -5977,7 +5960,7 @@
       </c>
       <c r="AB31" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC31" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -5985,11 +5968,11 @@
       </c>
       <c r="AD31" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE31" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF31" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -5997,15 +5980,15 @@
       </c>
       <c r="AG31" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="15"/>
@@ -6016,10 +5999,10 @@
         <v>31</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="6"/>
@@ -6043,7 +6026,7 @@
       </c>
       <c r="Z32" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6051,7 +6034,7 @@
       </c>
       <c r="AB32" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC32" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6059,11 +6042,11 @@
       </c>
       <c r="AD32" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE32" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF32" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6071,15 +6054,15 @@
       </c>
       <c r="AG32" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="33" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="15"/>
@@ -6090,10 +6073,10 @@
         <v>31</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="6"/>
@@ -6117,7 +6100,7 @@
       </c>
       <c r="Z33" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6125,7 +6108,7 @@
       </c>
       <c r="AB33" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC33" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6133,11 +6116,11 @@
       </c>
       <c r="AD33" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE33" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF33" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6145,15 +6128,15 @@
       </c>
       <c r="AG33" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="34" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7"/>
@@ -6161,13 +6144,13 @@
         <v>1</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="6"/>
@@ -6191,7 +6174,7 @@
       </c>
       <c r="Z34" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6199,7 +6182,7 @@
       </c>
       <c r="AB34" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC34" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6207,11 +6190,11 @@
       </c>
       <c r="AD34" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE34" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF34" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6219,15 +6202,15 @@
       </c>
       <c r="AG34" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="35" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
@@ -6238,10 +6221,10 @@
         <v>31</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="6"/>
@@ -6265,7 +6248,7 @@
       </c>
       <c r="Z35" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6273,7 +6256,7 @@
       </c>
       <c r="AB35" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC35" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6281,11 +6264,11 @@
       </c>
       <c r="AD35" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE35" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF35" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6293,15 +6276,15 @@
       </c>
       <c r="AG35" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="7"/>
@@ -6312,10 +6295,10 @@
         <v>31</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="6">
@@ -6325,10 +6308,10 @@
         <v>31</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="N36" s="22"/>
       <c r="O36" s="6"/>
@@ -6347,7 +6330,7 @@
       </c>
       <c r="Z36" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6355,19 +6338,19 @@
       </c>
       <c r="AB36" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC36" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD36" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE36" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF36" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6375,15 +6358,15 @@
       </c>
       <c r="AG36" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="37" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="7"/>
@@ -6394,10 +6377,10 @@
         <v>31</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>209</v>
+        <v>553</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6"/>
@@ -6421,7 +6404,7 @@
       </c>
       <c r="Z37" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6429,7 +6412,7 @@
       </c>
       <c r="AB37" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC37" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6437,11 +6420,11 @@
       </c>
       <c r="AD37" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE37" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF37" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6449,15 +6432,15 @@
       </c>
       <c r="AG37" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="38" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
@@ -6468,10 +6451,10 @@
         <v>31</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="6"/>
@@ -6495,7 +6478,7 @@
       </c>
       <c r="Z38" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6503,7 +6486,7 @@
       </c>
       <c r="AB38" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC38" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6511,11 +6494,11 @@
       </c>
       <c r="AD38" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE38" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF38" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6523,31 +6506,31 @@
       </c>
       <c r="AG38" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="39" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="6">
         <v>1</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>215</v>
+        <v>554</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="6"/>
@@ -6571,7 +6554,7 @@
       </c>
       <c r="Z39" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6579,7 +6562,7 @@
       </c>
       <c r="AB39" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC39" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6587,11 +6570,11 @@
       </c>
       <c r="AD39" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE39" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF39" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6599,15 +6582,15 @@
       </c>
       <c r="AG39" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="40" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
@@ -6615,26 +6598,26 @@
         <v>1</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>31</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="N40" s="22"/>
       <c r="O40" s="6"/>
@@ -6653,7 +6636,7 @@
       </c>
       <c r="Z40" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6661,19 +6644,19 @@
       </c>
       <c r="AB40" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.4799999999999995</v>
+        <v>5.7320000000000002</v>
       </c>
       <c r="AC40" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.3599999999999994</v>
+        <v>5.6219999999999999</v>
       </c>
       <c r="AD40" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.0799999999999992</v>
+        <v>6.3319999999999999</v>
       </c>
       <c r="AE40" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF40" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6681,15 +6664,15 @@
       </c>
       <c r="AG40" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="41" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="7"/>
@@ -6700,10 +6683,10 @@
         <v>31</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="6"/>
@@ -6727,7 +6710,7 @@
       </c>
       <c r="Z41" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6735,7 +6718,7 @@
       </c>
       <c r="AB41" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC41" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6743,11 +6726,11 @@
       </c>
       <c r="AD41" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE41" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF41" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6755,15 +6738,15 @@
       </c>
       <c r="AG41" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="42" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="7"/>
@@ -6774,10 +6757,10 @@
         <v>31</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="6"/>
@@ -6801,7 +6784,7 @@
       </c>
       <c r="Z42" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6809,7 +6792,7 @@
       </c>
       <c r="AB42" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC42" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -6817,11 +6800,11 @@
       </c>
       <c r="AD42" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE42" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF42" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -6829,15 +6812,15 @@
       </c>
       <c r="AG42" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="43" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="7"/>
@@ -6848,36 +6831,36 @@
         <v>31</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="6">
         <v>5</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N43" s="22"/>
       <c r="O43" s="6">
         <v>9</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>230</v>
+        <v>555</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="6"/>
@@ -6891,7 +6874,7 @@
       </c>
       <c r="Z43" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6899,35 +6882,35 @@
       </c>
       <c r="AB43" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC43" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD43" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE43" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.72</v>
+        <v>6.8</v>
       </c>
       <c r="AF43" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.6</v>
+        <v>6.6899999999999995</v>
       </c>
       <c r="AG43" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.3199999999999994</v>
+        <v>7.3999999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="7"/>
@@ -6935,13 +6918,13 @@
         <v>1</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6">
@@ -6951,10 +6934,10 @@
         <v>31</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="N44" s="22"/>
       <c r="O44" s="6"/>
@@ -6973,7 +6956,7 @@
       </c>
       <c r="Z44" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -6981,19 +6964,19 @@
       </c>
       <c r="AB44" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.4799999999999995</v>
+        <v>5.54</v>
       </c>
       <c r="AC44" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.3599999999999994</v>
+        <v>5.43</v>
       </c>
       <c r="AD44" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.0799999999999992</v>
+        <v>6.14</v>
       </c>
       <c r="AE44" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF44" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7001,31 +6984,31 @@
       </c>
       <c r="AG44" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="45" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="6">
         <v>1</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
@@ -7049,7 +7032,7 @@
       </c>
       <c r="Z45" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7057,7 +7040,7 @@
       </c>
       <c r="AB45" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC45" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7065,11 +7048,11 @@
       </c>
       <c r="AD45" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE45" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF45" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7077,15 +7060,15 @@
       </c>
       <c r="AG45" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="46" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
@@ -7096,23 +7079,23 @@
         <v>31</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>31</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="N46" s="22"/>
       <c r="O46" s="6"/>
@@ -7131,7 +7114,7 @@
       </c>
       <c r="Z46" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7139,19 +7122,19 @@
       </c>
       <c r="AB46" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC46" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD46" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE46" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF46" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7159,15 +7142,15 @@
       </c>
       <c r="AG46" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="47" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="7"/>
@@ -7178,10 +7161,10 @@
         <v>31</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="6"/>
@@ -7205,7 +7188,7 @@
       </c>
       <c r="Z47" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7213,7 +7196,7 @@
       </c>
       <c r="AB47" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC47" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7221,11 +7204,11 @@
       </c>
       <c r="AD47" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE47" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF47" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7233,15 +7216,15 @@
       </c>
       <c r="AG47" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="48" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
@@ -7252,23 +7235,23 @@
         <v>31</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="6">
         <v>6</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="N48" s="22"/>
       <c r="O48" s="6"/>
@@ -7287,7 +7270,7 @@
       </c>
       <c r="Z48" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA48" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7295,19 +7278,19 @@
       </c>
       <c r="AB48" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC48" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD48" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE48" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF48" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7315,15 +7298,15 @@
       </c>
       <c r="AG48" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="49" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
@@ -7331,13 +7314,13 @@
         <v>1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="6"/>
@@ -7361,7 +7344,7 @@
       </c>
       <c r="Z49" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA49" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7369,7 +7352,7 @@
       </c>
       <c r="AB49" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC49" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7377,11 +7360,11 @@
       </c>
       <c r="AD49" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE49" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF49" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7389,15 +7372,15 @@
       </c>
       <c r="AG49" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="50" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
@@ -7408,10 +7391,10 @@
         <v>31</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="6">
@@ -7421,10 +7404,10 @@
         <v>31</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="N50" s="22"/>
       <c r="O50" s="6"/>
@@ -7443,7 +7426,7 @@
       </c>
       <c r="Z50" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7451,19 +7434,19 @@
       </c>
       <c r="AB50" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC50" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD50" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE50" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF50" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7471,15 +7454,15 @@
       </c>
       <c r="AG50" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="51" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
@@ -7487,13 +7470,13 @@
         <v>1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="6"/>
@@ -7517,7 +7500,7 @@
       </c>
       <c r="Z51" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA51" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7525,7 +7508,7 @@
       </c>
       <c r="AB51" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC51" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7533,11 +7516,11 @@
       </c>
       <c r="AD51" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE51" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF51" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7545,15 +7528,15 @@
       </c>
       <c r="AG51" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="52" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
@@ -7561,13 +7544,13 @@
         <v>1</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
@@ -7591,7 +7574,7 @@
       </c>
       <c r="Z52" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA52" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7599,7 +7582,7 @@
       </c>
       <c r="AB52" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC52" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7607,11 +7590,11 @@
       </c>
       <c r="AD52" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE52" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF52" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7619,15 +7602,15 @@
       </c>
       <c r="AG52" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="53" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
@@ -7635,13 +7618,13 @@
         <v>1</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="6"/>
@@ -7665,7 +7648,7 @@
       </c>
       <c r="Z53" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7673,7 +7656,7 @@
       </c>
       <c r="AB53" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC53" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7681,11 +7664,11 @@
       </c>
       <c r="AD53" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE53" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF53" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7693,15 +7676,15 @@
       </c>
       <c r="AG53" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="54" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="7"/>
@@ -7709,13 +7692,13 @@
         <v>1</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="6">
@@ -7725,10 +7708,10 @@
         <v>31</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="N54" s="22"/>
       <c r="O54" s="6"/>
@@ -7747,7 +7730,7 @@
       </c>
       <c r="Z54" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7755,19 +7738,19 @@
       </c>
       <c r="AB54" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC54" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD54" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE54" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF54" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7775,15 +7758,15 @@
       </c>
       <c r="AG54" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="55" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="7"/>
@@ -7794,10 +7777,10 @@
         <v>31</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="6"/>
@@ -7821,7 +7804,7 @@
       </c>
       <c r="Z55" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7829,7 +7812,7 @@
       </c>
       <c r="AB55" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC55" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -7837,11 +7820,11 @@
       </c>
       <c r="AD55" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE55" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF55" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7849,15 +7832,15 @@
       </c>
       <c r="AG55" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="56" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="7"/>
@@ -7868,23 +7851,23 @@
         <v>31</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="6">
         <v>6</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="N56" s="22"/>
       <c r="O56" s="6"/>
@@ -7903,7 +7886,7 @@
       </c>
       <c r="Z56" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA56" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7911,19 +7894,19 @@
       </c>
       <c r="AB56" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC56" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD56" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE56" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF56" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -7931,15 +7914,15 @@
       </c>
       <c r="AG56" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="57" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="7"/>
@@ -7947,13 +7930,13 @@
         <v>1</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="6">
@@ -7963,10 +7946,10 @@
         <v>31</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="N57" s="22"/>
       <c r="O57" s="6"/>
@@ -7985,7 +7968,7 @@
       </c>
       <c r="Z57" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA57" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -7993,19 +7976,19 @@
       </c>
       <c r="AB57" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC57" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD57" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE57" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF57" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8013,15 +7996,15 @@
       </c>
       <c r="AG57" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="58" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="7"/>
@@ -8032,23 +8015,23 @@
         <v>31</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="6">
         <v>5</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="N58" s="22"/>
       <c r="O58" s="6"/>
@@ -8067,7 +8050,7 @@
       </c>
       <c r="Z58" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA58" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8075,19 +8058,19 @@
       </c>
       <c r="AB58" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC58" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD58" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE58" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF58" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8095,15 +8078,15 @@
       </c>
       <c r="AG58" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="59" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="7"/>
@@ -8114,10 +8097,10 @@
         <v>31</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="6"/>
@@ -8141,7 +8124,7 @@
       </c>
       <c r="Z59" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8149,7 +8132,7 @@
       </c>
       <c r="AB59" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC59" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8157,11 +8140,11 @@
       </c>
       <c r="AD59" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE59" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF59" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8169,15 +8152,15 @@
       </c>
       <c r="AG59" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="60" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="7"/>
@@ -8185,26 +8168,26 @@
         <v>1</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="K60" s="8" t="s">
         <v>31</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="N60" s="22"/>
       <c r="O60" s="6"/>
@@ -8223,7 +8206,7 @@
       </c>
       <c r="Z60" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA60" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8231,19 +8214,19 @@
       </c>
       <c r="AB60" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.6920000000000002</v>
       </c>
       <c r="AC60" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.5819999999999999</v>
       </c>
       <c r="AD60" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.2919999999999998</v>
       </c>
       <c r="AE60" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF60" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8251,15 +8234,15 @@
       </c>
       <c r="AG60" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="61" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="7"/>
@@ -8270,10 +8253,10 @@
         <v>31</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="6"/>
@@ -8297,7 +8280,7 @@
       </c>
       <c r="Z61" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA61" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8305,7 +8288,7 @@
       </c>
       <c r="AB61" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC61" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8313,11 +8296,11 @@
       </c>
       <c r="AD61" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE61" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF61" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8325,15 +8308,15 @@
       </c>
       <c r="AG61" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="62" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="7"/>
@@ -8341,13 +8324,13 @@
         <v>1</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="6"/>
@@ -8371,7 +8354,7 @@
       </c>
       <c r="Z62" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA62" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8379,7 +8362,7 @@
       </c>
       <c r="AB62" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC62" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8387,11 +8370,11 @@
       </c>
       <c r="AD62" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE62" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF62" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8399,15 +8382,15 @@
       </c>
       <c r="AG62" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="63" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="7"/>
@@ -8415,13 +8398,13 @@
         <v>1</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="6"/>
@@ -8445,7 +8428,7 @@
       </c>
       <c r="Z63" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA63" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8453,7 +8436,7 @@
       </c>
       <c r="AB63" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC63" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8461,11 +8444,11 @@
       </c>
       <c r="AD63" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE63" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF63" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8473,15 +8456,15 @@
       </c>
       <c r="AG63" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="7"/>
@@ -8489,13 +8472,13 @@
         <v>1</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="6">
@@ -8505,10 +8488,10 @@
         <v>31</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="N64" s="22"/>
       <c r="O64" s="6"/>
@@ -8527,7 +8510,7 @@
       </c>
       <c r="Z64" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA64" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8535,19 +8518,19 @@
       </c>
       <c r="AB64" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC64" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD64" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE64" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF64" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8555,15 +8538,15 @@
       </c>
       <c r="AG64" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="65" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="7"/>
@@ -8574,10 +8557,10 @@
         <v>31</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="6"/>
@@ -8601,7 +8584,7 @@
       </c>
       <c r="Z65" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA65" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8609,7 +8592,7 @@
       </c>
       <c r="AB65" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC65" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8617,11 +8600,11 @@
       </c>
       <c r="AD65" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE65" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF65" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8629,15 +8612,15 @@
       </c>
       <c r="AG65" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="66" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="7"/>
@@ -8645,13 +8628,13 @@
         <v>1</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="6">
@@ -8661,10 +8644,10 @@
         <v>31</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N66" s="22"/>
       <c r="O66" s="6"/>
@@ -8683,7 +8666,7 @@
       </c>
       <c r="Z66" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA66" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8691,19 +8674,19 @@
       </c>
       <c r="AB66" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.4799999999999995</v>
+        <v>5.54</v>
       </c>
       <c r="AC66" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.3599999999999994</v>
+        <v>5.43</v>
       </c>
       <c r="AD66" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.0799999999999992</v>
+        <v>6.14</v>
       </c>
       <c r="AE66" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF66" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8711,15 +8694,15 @@
       </c>
       <c r="AG66" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="67" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="7"/>
@@ -8727,13 +8710,13 @@
         <v>1</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="6"/>
@@ -8757,7 +8740,7 @@
       </c>
       <c r="Z67" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA67" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8765,7 +8748,7 @@
       </c>
       <c r="AB67" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC67" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8773,11 +8756,11 @@
       </c>
       <c r="AD67" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE67" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF67" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8785,15 +8768,15 @@
       </c>
       <c r="AG67" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="68" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="7"/>
@@ -8801,13 +8784,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="6">
@@ -8817,10 +8800,10 @@
         <v>31</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="N68" s="22"/>
       <c r="O68" s="6"/>
@@ -8839,7 +8822,7 @@
       </c>
       <c r="Z68" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA68" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8847,19 +8830,19 @@
       </c>
       <c r="AB68" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC68" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD68" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE68" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF68" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8867,15 +8850,15 @@
       </c>
       <c r="AG68" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="69" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="7"/>
@@ -8883,13 +8866,13 @@
         <v>1</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="6"/>
@@ -8913,7 +8896,7 @@
       </c>
       <c r="Z69" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA69" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -8921,7 +8904,7 @@
       </c>
       <c r="AB69" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC69" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -8929,11 +8912,11 @@
       </c>
       <c r="AD69" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE69" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF69" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -8941,15 +8924,15 @@
       </c>
       <c r="AG69" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="70" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="15"/>
@@ -8957,39 +8940,39 @@
         <v>1</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I70" s="15"/>
       <c r="J70" s="6">
         <v>5</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="N70" s="23"/>
       <c r="O70" s="6">
         <v>9.5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="S70" s="15"/>
       <c r="T70" s="6"/>
@@ -9003,7 +8986,7 @@
       </c>
       <c r="Z70" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA70" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9011,35 +8994,35 @@
       </c>
       <c r="AB70" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC70" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD70" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE70" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.9550000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="AF70" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.835</v>
+        <v>6.93</v>
       </c>
       <c r="AG70" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.5549999999999997</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="71" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="15"/>
@@ -9047,26 +9030,26 @@
         <v>1</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="6">
         <v>9</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="N71" s="23"/>
       <c r="O71" s="6">
@@ -9087,7 +9070,7 @@
       </c>
       <c r="Z71" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA71" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9095,35 +9078,35 @@
       </c>
       <c r="AB71" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AC71" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="AD71" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="AE71" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.84</v>
+        <v>4.88</v>
       </c>
       <c r="AF71" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.72</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="AG71" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.4399999999999995</v>
+        <v>5.4799999999999995</v>
       </c>
     </row>
     <row r="72" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="7"/>
@@ -9131,26 +9114,26 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="6">
         <v>6</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N72" s="22"/>
       <c r="O72" s="6"/>
@@ -9169,7 +9152,7 @@
       </c>
       <c r="Z72" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA72" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9177,19 +9160,19 @@
       </c>
       <c r="AB72" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC72" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD72" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE72" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF72" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9197,15 +9180,15 @@
       </c>
       <c r="AG72" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="73" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="15"/>
@@ -9213,26 +9196,26 @@
         <v>1</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="I73" s="15"/>
       <c r="J73" s="6">
         <v>5</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="N73" s="23"/>
       <c r="O73" s="6">
@@ -9253,7 +9236,7 @@
       </c>
       <c r="Z73" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA73" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9261,35 +9244,35 @@
       </c>
       <c r="AB73" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC73" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD73" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE73" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.84</v>
+        <v>4.88</v>
       </c>
       <c r="AF73" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.72</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="AG73" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.4399999999999995</v>
+        <v>5.4799999999999995</v>
       </c>
     </row>
     <row r="74" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="7"/>
@@ -9297,13 +9280,13 @@
         <v>1</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="6">
@@ -9313,10 +9296,10 @@
         <v>31</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="N74" s="22"/>
       <c r="O74" s="6"/>
@@ -9335,7 +9318,7 @@
       </c>
       <c r="Z74" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA74" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9343,19 +9326,19 @@
       </c>
       <c r="AB74" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC74" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD74" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE74" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF74" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9363,15 +9346,15 @@
       </c>
       <c r="AG74" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="75" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="7"/>
@@ -9379,13 +9362,13 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="6">
@@ -9395,10 +9378,10 @@
         <v>31</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="N75" s="22"/>
       <c r="O75" s="6"/>
@@ -9417,7 +9400,7 @@
       </c>
       <c r="Z75" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA75" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9425,19 +9408,19 @@
       </c>
       <c r="AB75" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC75" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD75" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE75" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF75" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9445,15 +9428,15 @@
       </c>
       <c r="AG75" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="76" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="7"/>
@@ -9461,26 +9444,26 @@
         <v>1</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="6">
         <v>9</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N76" s="22"/>
       <c r="O76" s="6"/>
@@ -9499,7 +9482,7 @@
       </c>
       <c r="Z76" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA76" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9507,19 +9490,19 @@
       </c>
       <c r="AB76" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AC76" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="AD76" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="AE76" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF76" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9527,15 +9510,15 @@
       </c>
       <c r="AG76" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="77" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="7"/>
@@ -9543,13 +9526,13 @@
         <v>1</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="6">
@@ -9559,10 +9542,10 @@
         <v>31</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="N77" s="22"/>
       <c r="O77" s="6"/>
@@ -9581,7 +9564,7 @@
       </c>
       <c r="Z77" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA77" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9589,19 +9572,19 @@
       </c>
       <c r="AB77" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC77" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD77" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE77" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF77" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9609,15 +9592,15 @@
       </c>
       <c r="AG77" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="78" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="7"/>
@@ -9625,13 +9608,13 @@
         <v>1</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="8">
@@ -9641,10 +9624,10 @@
         <v>31</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="N78" s="22"/>
       <c r="O78" s="6"/>
@@ -9663,7 +9646,7 @@
       </c>
       <c r="Z78" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA78" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9671,19 +9654,19 @@
       </c>
       <c r="AB78" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC78" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD78" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE78" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF78" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9691,15 +9674,15 @@
       </c>
       <c r="AG78" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="79" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C79" s="6"/>
       <c r="D79" s="7"/>
@@ -9707,26 +9690,26 @@
         <v>1</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="6">
         <v>3</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="N79" s="22"/>
       <c r="O79" s="6"/>
@@ -9745,7 +9728,7 @@
       </c>
       <c r="Z79" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA79" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9753,19 +9736,19 @@
       </c>
       <c r="AB79" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC79" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD79" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE79" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF79" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -9773,15 +9756,15 @@
       </c>
       <c r="AG79" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="80" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="7"/>
@@ -9789,39 +9772,39 @@
         <v>1</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="8">
         <v>3</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="N80" s="22"/>
       <c r="O80" s="6">
         <v>9.5</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="S80" s="7"/>
       <c r="T80" s="6"/>
@@ -9835,7 +9818,7 @@
       </c>
       <c r="Z80" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA80" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9843,35 +9826,35 @@
       </c>
       <c r="AB80" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC80" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD80" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE80" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.9550000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="AF80" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.835</v>
+        <v>6.93</v>
       </c>
       <c r="AG80" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.5549999999999997</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="81" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C81" s="6"/>
       <c r="D81" s="7"/>
@@ -9879,39 +9862,39 @@
         <v>1</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="6">
         <v>3</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="N81" s="22"/>
       <c r="O81" s="6">
         <v>9.5</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="6"/>
@@ -9925,7 +9908,7 @@
       </c>
       <c r="Z81" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA81" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -9933,35 +9916,35 @@
       </c>
       <c r="AB81" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC81" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD81" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE81" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.9550000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="AF81" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.835</v>
+        <v>6.93</v>
       </c>
       <c r="AG81" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.5549999999999997</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="82" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="7"/>
@@ -9969,13 +9952,13 @@
         <v>1</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="6"/>
@@ -9999,7 +9982,7 @@
       </c>
       <c r="Z82" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA82" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10007,7 +9990,7 @@
       </c>
       <c r="AB82" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC82" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -10015,11 +9998,11 @@
       </c>
       <c r="AD82" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE82" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF82" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10027,44 +10010,44 @@
       </c>
       <c r="AG82" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="83" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="6">
         <v>1</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="6">
         <v>4</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="N83" s="22"/>
       <c r="O83" s="6"/>
@@ -10083,7 +10066,7 @@
       </c>
       <c r="Z83" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA83" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10091,19 +10074,19 @@
       </c>
       <c r="AB83" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC83" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD83" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE83" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF83" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10111,15 +10094,15 @@
       </c>
       <c r="AG83" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="84" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="7"/>
@@ -10127,26 +10110,26 @@
         <v>1</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
         <v>9.5</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="N84" s="22"/>
       <c r="O84" s="6"/>
@@ -10165,7 +10148,7 @@
       </c>
       <c r="Z84" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA84" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10173,19 +10156,19 @@
       </c>
       <c r="AB84" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.6550000000000002</v>
+        <v>6.74</v>
       </c>
       <c r="AC84" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.5350000000000001</v>
+        <v>6.63</v>
       </c>
       <c r="AD84" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.2549999999999999</v>
+        <v>7.34</v>
       </c>
       <c r="AE84" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF84" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10193,15 +10176,15 @@
       </c>
       <c r="AG84" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="85" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="7"/>
@@ -10209,26 +10192,26 @@
         <v>1</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="6">
         <v>3</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="N85" s="22"/>
       <c r="O85" s="6"/>
@@ -10247,7 +10230,7 @@
       </c>
       <c r="Z85" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA85" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10255,19 +10238,19 @@
       </c>
       <c r="AB85" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC85" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD85" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE85" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF85" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10275,15 +10258,15 @@
       </c>
       <c r="AG85" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="86" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="7"/>
@@ -10291,13 +10274,13 @@
         <v>1</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="6"/>
@@ -10321,7 +10304,7 @@
       </c>
       <c r="Z86" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA86" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10329,7 +10312,7 @@
       </c>
       <c r="AB86" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC86" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -10337,11 +10320,11 @@
       </c>
       <c r="AD86" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE86" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF86" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10349,15 +10332,15 @@
       </c>
       <c r="AG86" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="87" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="7"/>
@@ -10365,26 +10348,26 @@
         <v>1</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="6">
         <v>8.5</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="M87" s="18" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="N87" s="22"/>
       <c r="O87" s="6"/>
@@ -10403,7 +10386,7 @@
       </c>
       <c r="Z87" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA87" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10411,19 +10394,19 @@
       </c>
       <c r="AB87" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.1849999999999996</v>
+        <v>6.26</v>
       </c>
       <c r="AC87" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.0649999999999995</v>
+        <v>6.1499999999999995</v>
       </c>
       <c r="AD87" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>6.7849999999999993</v>
+        <v>6.8599999999999994</v>
       </c>
       <c r="AE87" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF87" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10431,15 +10414,15 @@
       </c>
       <c r="AG87" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="88" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="7"/>
@@ -10447,26 +10430,26 @@
         <v>1</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="6">
         <v>3</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="N88" s="22"/>
       <c r="O88" s="6"/>
@@ -10485,7 +10468,7 @@
       </c>
       <c r="Z88" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA88" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10493,19 +10476,19 @@
       </c>
       <c r="AB88" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC88" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD88" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE88" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF88" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10513,15 +10496,15 @@
       </c>
       <c r="AG88" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="89" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="7"/>
@@ -10529,26 +10512,26 @@
         <v>1</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="6">
         <v>3</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="N89" s="22"/>
       <c r="O89" s="6"/>
@@ -10567,7 +10550,7 @@
       </c>
       <c r="Z89" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA89" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10575,19 +10558,19 @@
       </c>
       <c r="AB89" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC89" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD89" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE89" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF89" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10595,15 +10578,15 @@
       </c>
       <c r="AG89" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="90" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="7"/>
@@ -10611,26 +10594,26 @@
         <v>1</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="6">
         <v>3</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="N90" s="22"/>
       <c r="O90" s="6"/>
@@ -10649,7 +10632,7 @@
       </c>
       <c r="Z90" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA90" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10657,19 +10640,19 @@
       </c>
       <c r="AB90" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC90" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD90" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE90" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF90" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10677,44 +10660,44 @@
       </c>
       <c r="AG90" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="91" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="6">
         <v>1</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="6">
         <v>5</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="N91" s="22"/>
       <c r="O91" s="6"/>
@@ -10733,7 +10716,7 @@
       </c>
       <c r="Z91" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA91" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10741,19 +10724,19 @@
       </c>
       <c r="AB91" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC91" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD91" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE91" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF91" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10761,15 +10744,15 @@
       </c>
       <c r="AG91" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="92" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
@@ -10777,13 +10760,13 @@
         <v>1</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="6">
@@ -10793,10 +10776,10 @@
         <v>31</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N92" s="22"/>
       <c r="O92" s="6"/>
@@ -10815,7 +10798,7 @@
       </c>
       <c r="Z92" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA92" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10823,19 +10806,19 @@
       </c>
       <c r="AB92" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC92" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD92" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE92" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF92" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10843,15 +10826,15 @@
       </c>
       <c r="AG92" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="93" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="7"/>
@@ -10859,26 +10842,26 @@
         <v>1</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="N93" s="22"/>
       <c r="O93" s="6"/>
@@ -10897,7 +10880,7 @@
       </c>
       <c r="Z93" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA93" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10905,19 +10888,19 @@
       </c>
       <c r="AB93" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.58</v>
       </c>
       <c r="AC93" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>4.47</v>
       </c>
       <c r="AD93" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="AE93" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF93" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -10925,15 +10908,15 @@
       </c>
       <c r="AG93" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="94" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="7"/>
@@ -10941,26 +10924,26 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="6">
         <v>10</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="N94" s="22"/>
       <c r="O94" s="6"/>
@@ -10979,7 +10962,7 @@
       </c>
       <c r="Z94" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA94" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -10987,19 +10970,19 @@
       </c>
       <c r="AB94" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.89</v>
+        <v>6.98</v>
       </c>
       <c r="AC94" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="AD94" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.4899999999999993</v>
+        <v>7.58</v>
       </c>
       <c r="AE94" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF94" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11007,15 +10990,15 @@
       </c>
       <c r="AG94" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="95" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="7"/>
@@ -11023,13 +11006,13 @@
         <v>1</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="6">
@@ -11039,10 +11022,10 @@
         <v>31</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="N95" s="22"/>
       <c r="O95" s="6"/>
@@ -11061,7 +11044,7 @@
       </c>
       <c r="Z95" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA95" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11069,19 +11052,19 @@
       </c>
       <c r="AB95" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.01</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AC95" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.8899999999999997</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AD95" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.6099999999999994</v>
+        <v>5.6599999999999993</v>
       </c>
       <c r="AE95" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF95" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11089,15 +11072,15 @@
       </c>
       <c r="AG95" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="96" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="7"/>
@@ -11105,13 +11088,13 @@
         <v>1</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="6">
@@ -11121,23 +11104,23 @@
         <v>31</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="N96" s="22"/>
       <c r="O96" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="S96" s="7"/>
       <c r="T96" s="6"/>
@@ -11151,7 +11134,7 @@
       </c>
       <c r="Z96" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA96" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11159,35 +11142,35 @@
       </c>
       <c r="AB96" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC96" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD96" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE96" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>7.66</v>
+        <v>7.28</v>
       </c>
       <c r="AF96" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>7.54</v>
+        <v>7.17</v>
       </c>
       <c r="AG96" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>8.26</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="97" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="7"/>
@@ -11195,13 +11178,13 @@
         <v>1</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="6"/>
@@ -11225,7 +11208,7 @@
       </c>
       <c r="Z97" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11233,7 +11216,7 @@
       </c>
       <c r="AB97" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC97" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -11241,11 +11224,11 @@
       </c>
       <c r="AD97" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE97" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF97" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11253,15 +11236,15 @@
       </c>
       <c r="AG97" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="98" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="7"/>
@@ -11269,13 +11252,13 @@
         <v>1</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="6"/>
@@ -11299,7 +11282,7 @@
       </c>
       <c r="Z98" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA98" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11307,7 +11290,7 @@
       </c>
       <c r="AB98" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC98" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -11315,11 +11298,11 @@
       </c>
       <c r="AD98" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE98" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF98" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11327,15 +11310,15 @@
       </c>
       <c r="AG98" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="99" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C99" s="6"/>
       <c r="D99" s="7"/>
@@ -11343,39 +11326,39 @@
         <v>1</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="6">
         <v>3</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N99" s="22"/>
       <c r="O99" s="6">
         <v>10</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="S99" s="7"/>
       <c r="T99" s="6"/>
@@ -11389,7 +11372,7 @@
       </c>
       <c r="Z99" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA99" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11397,35 +11380,35 @@
       </c>
       <c r="AB99" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC99" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD99" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE99" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>7.1899999999999995</v>
+        <v>7.28</v>
       </c>
       <c r="AF99" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>7.0699999999999994</v>
+        <v>7.17</v>
       </c>
       <c r="AG99" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.7899999999999991</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="100" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="7"/>
@@ -11433,26 +11416,26 @@
         <v>1</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="6">
         <v>10</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="N100" s="22"/>
       <c r="O100" s="6"/>
@@ -11471,7 +11454,7 @@
       </c>
       <c r="Z100" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA100" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11479,19 +11462,19 @@
       </c>
       <c r="AB100" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.89</v>
+        <v>6.98</v>
       </c>
       <c r="AC100" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="AD100" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.4899999999999993</v>
+        <v>7.58</v>
       </c>
       <c r="AE100" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF100" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11499,15 +11482,15 @@
       </c>
       <c r="AG100" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="101" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C101" s="6"/>
       <c r="D101" s="7"/>
@@ -11515,13 +11498,13 @@
         <v>1</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="6"/>
@@ -11545,7 +11528,7 @@
       </c>
       <c r="Z101" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA101" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11553,7 +11536,7 @@
       </c>
       <c r="AB101" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC101" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -11561,11 +11544,11 @@
       </c>
       <c r="AD101" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE101" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF101" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11573,15 +11556,15 @@
       </c>
       <c r="AG101" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="102" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="7"/>
@@ -11589,13 +11572,13 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="6">
@@ -11605,10 +11588,10 @@
         <v>31</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="N102" s="22"/>
       <c r="O102" s="6"/>
@@ -11627,7 +11610,7 @@
       </c>
       <c r="Z102" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA102" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11635,19 +11618,19 @@
       </c>
       <c r="AB102" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="AC102" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AD102" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="AE102" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF102" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11655,31 +11638,31 @@
       </c>
       <c r="AG102" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="103" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="6">
         <v>1</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="6">
@@ -11689,10 +11672,10 @@
         <v>31</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="N103" s="22"/>
       <c r="O103" s="6"/>
@@ -11711,7 +11694,7 @@
       </c>
       <c r="Z103" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA103" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11719,19 +11702,19 @@
       </c>
       <c r="AB103" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AC103" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="AD103" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="AE103" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF103" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11739,44 +11722,44 @@
       </c>
       <c r="AG103" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="104" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="6">
         <v>1</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="6">
         <v>3</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="N104" s="22"/>
       <c r="O104" s="6"/>
@@ -11795,7 +11778,7 @@
       </c>
       <c r="Z104" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA104" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11803,19 +11786,19 @@
       </c>
       <c r="AB104" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC104" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD104" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE104" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF104" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11823,15 +11806,15 @@
       </c>
       <c r="AG104" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="105" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C105" s="6"/>
       <c r="D105" s="7"/>
@@ -11839,39 +11822,39 @@
         <v>1</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="6">
         <v>3</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="N105" s="22"/>
       <c r="O105" s="6">
         <v>10</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q105" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="S105" s="7"/>
       <c r="T105" s="6"/>
@@ -11885,7 +11868,7 @@
       </c>
       <c r="Z105" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA105" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11893,35 +11876,35 @@
       </c>
       <c r="AB105" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC105" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD105" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE105" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>7.1899999999999995</v>
+        <v>7.28</v>
       </c>
       <c r="AF105" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>7.0699999999999994</v>
+        <v>7.17</v>
       </c>
       <c r="AG105" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.7899999999999991</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="106" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="7"/>
@@ -11929,26 +11912,26 @@
         <v>1</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="6">
         <v>10</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="N106" s="22"/>
       <c r="O106" s="6"/>
@@ -11967,7 +11950,7 @@
       </c>
       <c r="Z106" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA106" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -11975,19 +11958,19 @@
       </c>
       <c r="AB106" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.89</v>
+        <v>6.98</v>
       </c>
       <c r="AC106" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="AD106" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.4899999999999993</v>
+        <v>7.58</v>
       </c>
       <c r="AE106" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF106" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -11995,15 +11978,15 @@
       </c>
       <c r="AG106" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="107" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C107" s="6"/>
       <c r="D107" s="15"/>
@@ -12011,26 +11994,26 @@
         <v>1</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="I107" s="15"/>
       <c r="J107" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="N107" s="23"/>
       <c r="O107" s="6">
@@ -12051,7 +12034,7 @@
       </c>
       <c r="Z107" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA107" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12059,35 +12042,35 @@
       </c>
       <c r="AB107" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.58</v>
       </c>
       <c r="AC107" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>4.47</v>
       </c>
       <c r="AD107" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="AE107" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>4.84</v>
+        <v>4.88</v>
       </c>
       <c r="AF107" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>4.72</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="AG107" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.4399999999999995</v>
+        <v>5.4799999999999995</v>
       </c>
     </row>
     <row r="108" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="7"/>
@@ -12095,26 +12078,26 @@
         <v>1</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="6">
         <v>9</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="N108" s="22"/>
       <c r="O108" s="6"/>
@@ -12133,7 +12116,7 @@
       </c>
       <c r="Z108" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA108" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12141,19 +12124,19 @@
       </c>
       <c r="AB108" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AC108" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="AD108" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="AE108" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF108" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12161,15 +12144,15 @@
       </c>
       <c r="AG108" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="109" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
@@ -12177,26 +12160,26 @@
         <v>1</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="6">
         <v>10</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="N109" s="22"/>
       <c r="O109" s="6"/>
@@ -12215,7 +12198,7 @@
       </c>
       <c r="Z109" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA109" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12223,19 +12206,19 @@
       </c>
       <c r="AB109" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.89</v>
+        <v>6.98</v>
       </c>
       <c r="AC109" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="AD109" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.4899999999999993</v>
+        <v>7.58</v>
       </c>
       <c r="AE109" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF109" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12243,15 +12226,15 @@
       </c>
       <c r="AG109" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="110" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
@@ -12259,26 +12242,26 @@
         <v>1</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="6">
         <v>9</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="N110" s="22"/>
       <c r="O110" s="6"/>
@@ -12297,7 +12280,7 @@
       </c>
       <c r="Z110" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA110" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12305,19 +12288,19 @@
       </c>
       <c r="AB110" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AC110" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="AD110" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="AE110" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF110" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12325,15 +12308,15 @@
       </c>
       <c r="AG110" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="111" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
@@ -12341,13 +12324,13 @@
         <v>1</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="6"/>
@@ -12371,7 +12354,7 @@
       </c>
       <c r="Z111" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA111" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12379,7 +12362,7 @@
       </c>
       <c r="AB111" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC111" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -12387,11 +12370,11 @@
       </c>
       <c r="AD111" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE111" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF111" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12399,15 +12382,15 @@
       </c>
       <c r="AG111" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="112" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="7"/>
@@ -12415,13 +12398,13 @@
         <v>1</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="6"/>
@@ -12445,7 +12428,7 @@
       </c>
       <c r="Z112" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA112" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12453,7 +12436,7 @@
       </c>
       <c r="AB112" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC112" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -12461,11 +12444,11 @@
       </c>
       <c r="AD112" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE112" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF112" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12473,15 +12456,15 @@
       </c>
       <c r="AG112" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="113" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
@@ -12489,26 +12472,26 @@
         <v>1</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="6">
         <v>4</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="N113" s="22"/>
       <c r="O113" s="6"/>
@@ -12527,7 +12510,7 @@
       </c>
       <c r="Z113" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA113" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12535,19 +12518,19 @@
       </c>
       <c r="AB113" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.07</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="AC113" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.95</v>
+        <v>3.9900000000000007</v>
       </c>
       <c r="AD113" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AE113" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF113" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12555,15 +12538,15 @@
       </c>
       <c r="AG113" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="114" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
@@ -12571,13 +12554,13 @@
         <v>1</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="6">
@@ -12587,10 +12570,10 @@
         <v>31</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="N114" s="22"/>
       <c r="O114" s="6"/>
@@ -12609,7 +12592,7 @@
       </c>
       <c r="Z114" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA114" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12617,19 +12600,19 @@
       </c>
       <c r="AB114" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC114" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD114" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE114" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF114" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12637,15 +12620,15 @@
       </c>
       <c r="AG114" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="115" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
@@ -12653,39 +12636,39 @@
         <v>1</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="I115" s="7"/>
       <c r="J115" s="6">
         <v>3</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="N115" s="22"/>
       <c r="O115" s="6">
         <v>10</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R115" s="8" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="S115" s="7"/>
       <c r="T115" s="6"/>
@@ -12699,7 +12682,7 @@
       </c>
       <c r="Z115" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA115" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12707,35 +12690,35 @@
       </c>
       <c r="AB115" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC115" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD115" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE115" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>7.1899999999999995</v>
+        <v>7.28</v>
       </c>
       <c r="AF115" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>7.0699999999999994</v>
+        <v>7.17</v>
       </c>
       <c r="AG115" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.7899999999999991</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="116" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="7"/>
@@ -12743,26 +12726,26 @@
         <v>1</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="I116" s="7"/>
       <c r="J116" s="6">
         <v>3</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="N116" s="22"/>
       <c r="O116" s="6"/>
@@ -12781,7 +12764,7 @@
       </c>
       <c r="Z116" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA116" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12789,19 +12772,19 @@
       </c>
       <c r="AB116" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>3.6</v>
+        <v>3.6199999999999997</v>
       </c>
       <c r="AC116" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AD116" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AE116" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF116" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12809,15 +12792,15 @@
       </c>
       <c r="AG116" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="117" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
@@ -12825,13 +12808,13 @@
         <v>1</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="I117" s="7"/>
       <c r="J117" s="6"/>
@@ -12855,7 +12838,7 @@
       </c>
       <c r="Z117" s="6">
         <f>Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>2.2399999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="AA117" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
@@ -12863,7 +12846,7 @@
       </c>
       <c r="AB117" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>2.19</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="AC117" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
@@ -12871,11 +12854,11 @@
       </c>
       <c r="AD117" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AE117" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>2.4900000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="AF117" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
@@ -12883,7 +12866,7 @@
       </c>
       <c r="AG117" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>3.0900000000000003</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="118" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntk\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC2C0EC-688D-4CD3-B61B-578A631B7889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021DC251-7457-4539-BD0E-176CE36AEA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="577">
   <si>
     <t>Name</t>
   </si>
@@ -2475,9 +2475,6 @@
 &lt;br&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
   </si>
   <si>
-    <t>Whenever you inflict a status effect, you may set that creature's composure to 1.</t>
-  </si>
-  <si>
     <t>When you make an attack, you may move 2 tiles before attacking.</t>
   </si>
   <si>
@@ -2545,9 +2542,81 @@
     <t>&lt;b&gt;Fire&lt;/b&gt; and &lt;b&gt;Burning&lt;/b&gt; give you temporary composure instead of dealing damage.</t>
   </si>
   <si>
+    <t>&lt;b&gt;Snigger:&lt;/b&gt; WeirdT or &lt;b&gt;Exhasusted&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Detonate: Exhaust&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Snap:&lt;/b&gt; 3 AP + &lt;b&gt;Exhaust&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Whenever a being leaves your attack range, you may spend jazzT to make an attack with any limb against them. If the attack would cost 3 or more AP, &lt;b&gt;Exhaust&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>You may clear a status effect (except &lt;b&gt;Exhausted&lt;/b&gt;) to refresh a token of your choice.</t>
+  </si>
+  <si>
+    <t>When you would take a status effect (except &lt;b&gt;Exhausted&lt;/b&gt;), ignore it instead.</t>
+  </si>
+  <si>
+    <t>Shovelling Talons</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Bloom:&lt;/b&gt;  WeirdT</t>
+  </si>
+  <si>
+    <t>Competely ignore damage from falling.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Smear:&lt;/b&gt; 2 AP + weirdTweirdT</t>
+  </si>
+  <si>
+    <t>Engraved Slab</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Read the Runes:&lt;/b weirdT</t>
+  </si>
+  <si>
+    <t>Target being has half speed until the start of you next turn. (Each hex costs 2 move points)</t>
+  </si>
+  <si>
+    <t>&lt;B&gt;Slam:&lt;/b&gt; 4 AP</t>
+  </si>
+  <si>
+    <t>Storm Conduit</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Channel Storm:&lt;/b&gt; 2AP + weirdT</t>
+  </si>
+  <si>
+    <t>Create a 1 hex storm cloud at target empty hex.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;i&gt;Growing Storm&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>At the start of your turn, each storm cloud grows by one hex in all direction</t>
+  </si>
+  <si>
+    <t>&lt;B&gt;&lt;i&gt;Electrified&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Whenever you spend weirdT, all beings underneath a storm cloud take 4 damage. This damage cannot be reduced.</t>
+  </si>
+  <si>
+    <t>Your second attack each turn costs 1 less AP.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;i&gt;Creative Duelist&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Whenever you inflict a status effect, you may set that creatures composure to 1.</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
-&lt;br&gt;-1 </t>
+      <t xml:space="preserve">Reduce damage taken by 1.
+&lt;br&gt;- 1 </t>
     </r>
     <r>
       <rPr>
@@ -2570,73 +2639,29 @@
     </r>
   </si>
   <si>
-    <t>&lt;b&gt;Snigger:&lt;/b&gt; WeirdT or &lt;b&gt;Exhasusted&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Detonate: Exhaust&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Snap:&lt;/b&gt; 3 AP + &lt;b&gt;Exhaust&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>Whenever a being leaves your attack range, you may spend jazzT to make an attack with any limb against them. If the attack would cost 3 or more AP, &lt;b&gt;Exhaust&lt;/b&gt;.</t>
-  </si>
-  <si>
-    <t>You may clear a status effect (except &lt;b&gt;Exhausted&lt;/b&gt;) to refresh a token of your choice.</t>
-  </si>
-  <si>
-    <t>When you would take a status effect (except &lt;b&gt;Exhausted&lt;/b&gt;), ignore it instead.</t>
-  </si>
-  <si>
-    <t>Shovelling Talons</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Bloom:&lt;/b&gt;  WeirdT</t>
-  </si>
-  <si>
-    <t>Competely ignore damage from falling.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Smear:&lt;/b&gt; 2 AP + weirdTweirdT</t>
-  </si>
-  <si>
-    <t>Engraved Slab</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Read the Runes:&lt;/b weirdT</t>
-  </si>
-  <si>
-    <t>Target being has half speed until the start of you next turn. (Each hex costs 2 move points)</t>
-  </si>
-  <si>
-    <t>&lt;B&gt;Slam:&lt;/b&gt; 4 AP</t>
-  </si>
-  <si>
-    <t>Storm Conduit</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Channel Storm:&lt;/b&gt; 2AP + weirdT</t>
-  </si>
-  <si>
-    <t>Create a 1 hex storm cloud at target empty hex.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Growing Storm&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>At the start of your turn, each storm cloud grows by one hex in all direction</t>
-  </si>
-  <si>
-    <t>&lt;B&gt;&lt;i&gt;Electrified&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
-    <t>Whenever you spend weirdT, all beings underneath a storm cloud take 4 damage. This damage cannot be reduced.</t>
-  </si>
-  <si>
-    <t>Your second attack each turn costs 1 less AP.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Creative Duelist&lt;/i&gt;&lt;/b&gt;</t>
+    <r>
+      <t xml:space="preserve">&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
+&lt;br&gt;- 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Movement Speed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3351,33 +3376,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG199"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="1.42578125" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="1.44140625" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="42.42578125" customWidth="1"/>
-    <col min="9" max="9" width="1.42578125" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
-    <col min="12" max="12" width="31.7109375" customWidth="1"/>
-    <col min="13" max="13" width="37.85546875" style="24" customWidth="1"/>
-    <col min="14" max="14" width="1.42578125" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" customWidth="1"/>
-    <col min="17" max="17" width="25.5703125" customWidth="1"/>
-    <col min="18" max="18" width="35.140625" customWidth="1"/>
-    <col min="19" max="19" width="1.42578125" customWidth="1"/>
+    <col min="8" max="8" width="42.44140625" customWidth="1"/>
+    <col min="9" max="9" width="1.44140625" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="12" max="12" width="31.6640625" customWidth="1"/>
+    <col min="13" max="13" width="37.88671875" style="24" customWidth="1"/>
+    <col min="14" max="14" width="1.44140625" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" customWidth="1"/>
+    <col min="17" max="17" width="25.5546875" customWidth="1"/>
+    <col min="18" max="18" width="35.109375" customWidth="1"/>
+    <col min="19" max="19" width="1.44140625" customWidth="1"/>
     <col min="20" max="20" width="10" customWidth="1"/>
     <col min="21" max="21" width="38" customWidth="1"/>
-    <col min="24" max="31" width="10.5703125" customWidth="1"/>
+    <col min="24" max="31" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3478,7 +3503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3510,7 +3535,7 @@
         <v>34</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="N2" s="21"/>
       <c r="O2" s="6"/>
@@ -3570,7 +3595,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -3606,7 +3631,7 @@
       </c>
       <c r="N3" s="21"/>
       <c r="O3" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>31</v>
@@ -3649,18 +3674,18 @@
       </c>
       <c r="AE3" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.04</v>
+        <v>5.6</v>
       </c>
       <c r="AF3" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.93</v>
+        <v>5.4899999999999993</v>
       </c>
       <c r="AG3" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>6.1999999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -3746,7 +3771,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
@@ -3832,7 +3857,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>53</v>
       </c>
@@ -3908,9 +3933,9 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>30</v>
@@ -3926,10 +3951,10 @@
         <v>314</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>547</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>548</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
@@ -3939,10 +3964,10 @@
         <v>31</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>549</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>550</v>
       </c>
       <c r="N7" s="21"/>
       <c r="O7" s="6"/>
@@ -3992,7 +4017,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
         <v>56</v>
       </c>
@@ -4074,7 +4099,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>61</v>
       </c>
@@ -4093,7 +4118,7 @@
         <v>62</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -4119,7 +4144,7 @@
         <v>65</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="6"/>
@@ -4164,7 +4189,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
@@ -4246,7 +4271,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>71</v>
       </c>
@@ -4267,7 +4292,7 @@
         <v>73</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>74</v>
+        <v>575</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
@@ -4330,7 +4355,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>77</v>
       </c>
@@ -4368,7 +4393,7 @@
       </c>
       <c r="N12" s="21"/>
       <c r="O12" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>44</v>
@@ -4411,18 +4436,18 @@
       </c>
       <c r="AE12" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.16</v>
+        <v>4.72</v>
       </c>
       <c r="AF12" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.05</v>
+        <v>4.6099999999999994</v>
       </c>
       <c r="AG12" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>5.3199999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>83</v>
       </c>
@@ -4445,7 +4470,7 @@
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>31</v>
@@ -4481,15 +4506,15 @@
       </c>
       <c r="AB13" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.8600000000000003</v>
+        <v>4.42</v>
       </c>
       <c r="AC13" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.75</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="AD13" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.46</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="AE13" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
@@ -4504,7 +4529,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>87</v>
       </c>
@@ -4594,7 +4619,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>94</v>
       </c>
@@ -4686,7 +4711,7 @@
         <v>6.1999999999999993</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>101</v>
       </c>
@@ -4764,7 +4789,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>103</v>
       </c>
@@ -4856,7 +4881,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>110</v>
       </c>
@@ -4875,7 +4900,7 @@
         <v>111</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="6">
@@ -4946,7 +4971,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
@@ -5028,7 +5053,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>121</v>
       </c>
@@ -5110,7 +5135,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="135" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>126</v>
       </c>
@@ -5194,7 +5219,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>131</v>
       </c>
@@ -5284,7 +5309,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>138</v>
       </c>
@@ -5331,7 +5356,7 @@
         <v>144</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="6"/>
@@ -5376,7 +5401,7 @@
         <v>6.1999999999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>145</v>
       </c>
@@ -5468,7 +5493,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>150</v>
       </c>
@@ -5550,7 +5575,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>154</v>
       </c>
@@ -5571,7 +5596,7 @@
         <v>155</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="6">
@@ -5642,7 +5667,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>160</v>
       </c>
@@ -5661,7 +5686,7 @@
         <v>161</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="6">
@@ -5687,7 +5712,7 @@
         <v>164</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="S27" s="7"/>
       <c r="T27" s="6"/>
@@ -5732,7 +5757,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>165</v>
       </c>
@@ -5814,7 +5839,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>170</v>
       </c>
@@ -5888,7 +5913,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>174</v>
       </c>
@@ -5907,7 +5932,7 @@
         <v>175</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="6">
@@ -5917,7 +5942,7 @@
         <v>31</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>176</v>
@@ -5970,7 +5995,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>177</v>
       </c>
@@ -5989,7 +6014,7 @@
         <v>178</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="6"/>
@@ -6044,7 +6069,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>179</v>
       </c>
@@ -6118,7 +6143,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>182</v>
       </c>
@@ -6192,7 +6217,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>184</v>
       </c>
@@ -6266,7 +6291,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>186</v>
       </c>
@@ -6340,7 +6365,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>190</v>
       </c>
@@ -6414,7 +6439,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>192</v>
       </c>
@@ -6437,7 +6462,7 @@
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K37" s="8" t="s">
         <v>31</v>
@@ -6473,15 +6498,15 @@
       </c>
       <c r="AB37" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.8600000000000003</v>
+        <v>4.42</v>
       </c>
       <c r="AC37" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.75</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="AD37" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.46</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="AE37" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6496,7 +6521,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>197</v>
       </c>
@@ -6515,7 +6540,7 @@
         <v>180</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="6"/>
@@ -6570,7 +6595,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>198</v>
       </c>
@@ -6644,7 +6669,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>200</v>
       </c>
@@ -6665,7 +6690,7 @@
         <v>202</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="6"/>
@@ -6720,7 +6745,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>203</v>
       </c>
@@ -6802,7 +6827,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>208</v>
       </c>
@@ -6876,7 +6901,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>210</v>
       </c>
@@ -6950,7 +6975,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>212</v>
       </c>
@@ -6973,7 +6998,7 @@
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>44</v>
@@ -6986,13 +7011,13 @@
       </c>
       <c r="N44" s="21"/>
       <c r="O44" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>44</v>
       </c>
       <c r="Q44" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>217</v>
@@ -7017,30 +7042,30 @@
       </c>
       <c r="AB44" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.42</v>
+        <v>3.98</v>
       </c>
       <c r="AC44" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.3099999999999996</v>
+        <v>3.87</v>
       </c>
       <c r="AD44" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.0199999999999996</v>
+        <v>4.58</v>
       </c>
       <c r="AE44" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.48</v>
+        <v>6.04</v>
       </c>
       <c r="AF44" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.37</v>
+        <v>5.93</v>
       </c>
       <c r="AG44" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>218</v>
       </c>
@@ -7122,7 +7147,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>223</v>
       </c>
@@ -7198,7 +7223,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>227</v>
       </c>
@@ -7221,7 +7246,7 @@
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K47" s="8" t="s">
         <v>31</v>
@@ -7257,15 +7282,15 @@
       </c>
       <c r="AB47" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.8600000000000003</v>
+        <v>4.42</v>
       </c>
       <c r="AC47" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.75</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="AD47" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.46</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="AE47" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7280,7 +7305,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>232</v>
       </c>
@@ -7354,7 +7379,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>234</v>
       </c>
@@ -7436,7 +7461,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>237</v>
       </c>
@@ -7510,7 +7535,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>240</v>
       </c>
@@ -7592,7 +7617,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>245</v>
       </c>
@@ -7666,7 +7691,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="90" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>248</v>
       </c>
@@ -7740,7 +7765,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>251</v>
       </c>
@@ -7814,7 +7839,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>254</v>
       </c>
@@ -7896,7 +7921,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>259</v>
       </c>
@@ -7970,7 +7995,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>260</v>
       </c>
@@ -8052,7 +8077,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>265</v>
       </c>
@@ -8134,7 +8159,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>270</v>
       </c>
@@ -8216,7 +8241,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>275</v>
       </c>
@@ -8290,7 +8315,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>277</v>
       </c>
@@ -8372,7 +8397,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>282</v>
       </c>
@@ -8446,7 +8471,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>284</v>
       </c>
@@ -8520,7 +8545,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>287</v>
       </c>
@@ -8539,7 +8564,7 @@
         <v>288</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="6"/>
@@ -8594,7 +8619,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>289</v>
       </c>
@@ -8676,7 +8701,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>294</v>
       </c>
@@ -8750,7 +8775,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>296</v>
       </c>
@@ -8766,14 +8791,14 @@
         <v>187</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H67" s="8" t="s">
         <v>297</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>31</v>
@@ -8809,15 +8834,15 @@
       </c>
       <c r="AB67" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>5.3</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="AC67" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>5.1899999999999995</v>
+        <v>4.75</v>
       </c>
       <c r="AD67" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.8999999999999995</v>
+        <v>5.46</v>
       </c>
       <c r="AE67" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8832,7 +8857,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>300</v>
       </c>
@@ -8906,7 +8931,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>303</v>
       </c>
@@ -8988,7 +9013,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>307</v>
       </c>
@@ -9062,7 +9087,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>310</v>
       </c>
@@ -9152,7 +9177,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>320</v>
       </c>
@@ -9236,7 +9261,7 @@
         <v>5.3199999999999994</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>324</v>
       </c>
@@ -9318,7 +9343,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>329</v>
       </c>
@@ -9402,7 +9427,7 @@
         <v>5.3199999999999994</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>334</v>
       </c>
@@ -9484,7 +9509,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>339</v>
       </c>
@@ -9566,7 +9591,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>344</v>
       </c>
@@ -9648,7 +9673,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>347</v>
       </c>
@@ -9730,7 +9755,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>352</v>
       </c>
@@ -9812,7 +9837,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>356</v>
       </c>
@@ -9894,7 +9919,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>361</v>
       </c>
@@ -9923,7 +9948,7 @@
         <v>44</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>364</v>
@@ -9984,7 +10009,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>366</v>
       </c>
@@ -10074,9 +10099,9 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B83" s="15" t="s">
         <v>311</v>
@@ -10090,10 +10115,10 @@
         <v>44</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="6">
@@ -10103,7 +10128,7 @@
         <v>314</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>379</v>
@@ -10156,7 +10181,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>371</v>
       </c>
@@ -10230,7 +10255,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>374</v>
       </c>
@@ -10261,7 +10286,7 @@
         <v>187</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>377</v>
@@ -10314,7 +10339,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>378</v>
       </c>
@@ -10396,7 +10421,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>381</v>
       </c>
@@ -10486,7 +10511,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>386</v>
       </c>
@@ -10560,7 +10585,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>389</v>
       </c>
@@ -10642,7 +10667,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>394</v>
       </c>
@@ -10724,7 +10749,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>398</v>
       </c>
@@ -10806,7 +10831,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>402</v>
       </c>
@@ -10835,10 +10860,10 @@
         <v>187</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="N92" s="21"/>
       <c r="O92" s="6"/>
@@ -10888,7 +10913,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>405</v>
       </c>
@@ -10972,7 +10997,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>411</v>
       </c>
@@ -11054,7 +11079,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>415</v>
       </c>
@@ -11077,7 +11102,7 @@
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>31</v>
@@ -11113,15 +11138,15 @@
       </c>
       <c r="AB95" s="6">
         <f>Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>4.42</v>
+        <v>3.98</v>
       </c>
       <c r="AC95" s="6">
         <f>Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>4.3099999999999996</v>
+        <v>3.87</v>
       </c>
       <c r="AD95" s="6">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>5.0199999999999996</v>
+        <v>4.58</v>
       </c>
       <c r="AE95" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11136,7 +11161,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>420</v>
       </c>
@@ -11218,7 +11243,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>423</v>
       </c>
@@ -11300,7 +11325,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>428</v>
       </c>
@@ -11336,7 +11361,7 @@
       </c>
       <c r="N98" s="21"/>
       <c r="O98" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>317</v>
@@ -11379,18 +11404,18 @@
       </c>
       <c r="AE98" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>6.92</v>
+        <v>7.36</v>
       </c>
       <c r="AF98" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>6.81</v>
+        <v>7.25</v>
       </c>
       <c r="AG98" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>7.52</v>
-      </c>
-    </row>
-    <row r="99" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>433</v>
       </c>
@@ -11464,7 +11489,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>436</v>
       </c>
@@ -11480,7 +11505,7 @@
         <v>314</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H100" s="8" t="s">
         <v>437</v>
@@ -11538,7 +11563,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>438</v>
       </c>
@@ -11628,7 +11653,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>444</v>
       </c>
@@ -11710,7 +11735,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>446</v>
       </c>
@@ -11784,7 +11809,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>449</v>
       </c>
@@ -11866,7 +11891,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>454</v>
       </c>
@@ -11950,7 +11975,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>459</v>
       </c>
@@ -12034,9 +12059,9 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>311</v>
@@ -12124,7 +12149,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>468</v>
       </c>
@@ -12206,7 +12231,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>472</v>
       </c>
@@ -12290,7 +12315,7 @@
         <v>5.3199999999999994</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>477</v>
       </c>
@@ -12372,7 +12397,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>481</v>
       </c>
@@ -12454,7 +12479,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>484</v>
       </c>
@@ -12536,7 +12561,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>488</v>
       </c>
@@ -12610,9 +12635,9 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B114" s="15" t="s">
         <v>311</v>
@@ -12626,10 +12651,10 @@
         <v>44</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="6">
@@ -12639,23 +12664,23 @@
         <v>31</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N114" s="21"/>
       <c r="O114" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Q114" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="S114" s="7"/>
       <c r="T114" s="6"/>
@@ -12689,18 +12714,18 @@
       </c>
       <c r="AE114" s="6">
         <f>Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>5.6</v>
+        <v>6.04</v>
       </c>
       <c r="AF114" s="6">
         <f>Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>5.4899999999999993</v>
+        <v>5.93</v>
       </c>
       <c r="AG114" s="8">
         <f>T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>6.1999999999999993</v>
-      </c>
-    </row>
-    <row r="115" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="115" spans="1:33" ht="72" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>491</v>
       </c>
@@ -12774,7 +12799,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>494</v>
       </c>
@@ -12856,7 +12881,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>499</v>
       </c>
@@ -12888,7 +12913,7 @@
         <v>501</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="N117" s="21"/>
       <c r="O117" s="6"/>
@@ -12938,7 +12963,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>502</v>
       </c>
@@ -13028,7 +13053,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>508</v>
       </c>
@@ -13110,7 +13135,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>512</v>
       </c>
@@ -13184,7 +13209,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="18"/>
       <c r="B121" s="18"/>
       <c r="C121" s="18"/>
@@ -13219,7 +13244,7 @@
       <c r="AF121" s="18"/>
       <c r="AG121" s="19"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="18"/>
       <c r="B122" s="18"/>
       <c r="C122" s="18"/>
@@ -13254,7 +13279,7 @@
       <c r="AF122" s="18"/>
       <c r="AG122" s="19"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="18"/>
       <c r="B123" s="18"/>
       <c r="C123" s="18"/>
@@ -13289,7 +13314,7 @@
       <c r="AF123" s="18"/>
       <c r="AG123" s="19"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="18"/>
       <c r="B124" s="18"/>
       <c r="C124" s="18"/>
@@ -13324,7 +13349,7 @@
       <c r="AF124" s="18"/>
       <c r="AG124" s="19"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="18"/>
       <c r="B125" s="18"/>
       <c r="C125" s="18"/>
@@ -13359,7 +13384,7 @@
       <c r="AF125" s="18"/>
       <c r="AG125" s="19"/>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="18"/>
       <c r="B126" s="18"/>
       <c r="C126" s="18"/>
@@ -13394,7 +13419,7 @@
       <c r="AF126" s="18"/>
       <c r="AG126" s="19"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="18"/>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
@@ -13429,7 +13454,7 @@
       <c r="AF127" s="18"/>
       <c r="AG127" s="19"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="18"/>
       <c r="B128" s="18"/>
       <c r="C128" s="18"/>
@@ -13464,7 +13489,7 @@
       <c r="AF128" s="18"/>
       <c r="AG128" s="19"/>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="18"/>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -13499,7 +13524,7 @@
       <c r="AF129" s="18"/>
       <c r="AG129" s="19"/>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="18"/>
       <c r="B130" s="18"/>
       <c r="C130" s="18"/>
@@ -13534,7 +13559,7 @@
       <c r="AF130" s="18"/>
       <c r="AG130" s="19"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="18"/>
       <c r="B131" s="18"/>
       <c r="C131" s="18"/>
@@ -13569,7 +13594,7 @@
       <c r="AF131" s="18"/>
       <c r="AG131" s="19"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="18"/>
       <c r="B132" s="18"/>
       <c r="C132" s="18"/>
@@ -13604,7 +13629,7 @@
       <c r="AF132" s="18"/>
       <c r="AG132" s="19"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="18"/>
       <c r="B133" s="18"/>
       <c r="C133" s="18"/>
@@ -13639,7 +13664,7 @@
       <c r="AF133" s="18"/>
       <c r="AG133" s="19"/>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="18"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
@@ -13674,7 +13699,7 @@
       <c r="AF134" s="18"/>
       <c r="AG134" s="19"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="18"/>
       <c r="B135" s="18"/>
       <c r="C135" s="18"/>
@@ -13709,7 +13734,7 @@
       <c r="AF135" s="18"/>
       <c r="AG135" s="19"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="18"/>
       <c r="B136" s="18"/>
       <c r="C136" s="18"/>
@@ -13744,7 +13769,7 @@
       <c r="AF136" s="18"/>
       <c r="AG136" s="19"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="18"/>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -13779,7 +13804,7 @@
       <c r="AF137" s="18"/>
       <c r="AG137" s="19"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="18"/>
       <c r="B138" s="18"/>
       <c r="C138" s="18"/>
@@ -13814,7 +13839,7 @@
       <c r="AF138" s="18"/>
       <c r="AG138" s="19"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="18"/>
       <c r="B139" s="18"/>
       <c r="C139" s="18"/>
@@ -13849,7 +13874,7 @@
       <c r="AF139" s="18"/>
       <c r="AG139" s="19"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="18"/>
       <c r="B140" s="18"/>
       <c r="C140" s="18"/>
@@ -13884,7 +13909,7 @@
       <c r="AF140" s="18"/>
       <c r="AG140" s="19"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="18"/>
       <c r="B141" s="18"/>
       <c r="C141" s="18"/>
@@ -13919,7 +13944,7 @@
       <c r="AF141" s="18"/>
       <c r="AG141" s="19"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="18"/>
       <c r="B142" s="18"/>
       <c r="C142" s="18"/>
@@ -13954,7 +13979,7 @@
       <c r="AF142" s="18"/>
       <c r="AG142" s="19"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="18"/>
       <c r="B143" s="18"/>
       <c r="C143" s="18"/>
@@ -13989,7 +14014,7 @@
       <c r="AF143" s="18"/>
       <c r="AG143" s="19"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="18"/>
       <c r="B144" s="18"/>
       <c r="C144" s="18"/>
@@ -14024,7 +14049,7 @@
       <c r="AF144" s="18"/>
       <c r="AG144" s="19"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="18"/>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
@@ -14059,7 +14084,7 @@
       <c r="AF145" s="18"/>
       <c r="AG145" s="19"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="18"/>
       <c r="B146" s="18"/>
       <c r="C146" s="18"/>
@@ -14094,7 +14119,7 @@
       <c r="AF146" s="18"/>
       <c r="AG146" s="19"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="18"/>
       <c r="B147" s="18"/>
       <c r="C147" s="18"/>
@@ -14129,7 +14154,7 @@
       <c r="AF147" s="18"/>
       <c r="AG147" s="19"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="18"/>
       <c r="B148" s="18"/>
       <c r="C148" s="18"/>
@@ -14164,7 +14189,7 @@
       <c r="AF148" s="18"/>
       <c r="AG148" s="19"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="18"/>
       <c r="B149" s="18"/>
       <c r="C149" s="18"/>
@@ -14199,7 +14224,7 @@
       <c r="AF149" s="18"/>
       <c r="AG149" s="19"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="18"/>
       <c r="B150" s="18"/>
       <c r="C150" s="18"/>
@@ -14234,7 +14259,7 @@
       <c r="AF150" s="18"/>
       <c r="AG150" s="19"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="18"/>
       <c r="B151" s="18"/>
       <c r="C151" s="18"/>
@@ -14269,7 +14294,7 @@
       <c r="AF151" s="18"/>
       <c r="AG151" s="19"/>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="18"/>
       <c r="B152" s="18"/>
       <c r="C152" s="18"/>
@@ -14304,7 +14329,7 @@
       <c r="AF152" s="18"/>
       <c r="AG152" s="19"/>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="18"/>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -14339,7 +14364,7 @@
       <c r="AF153" s="18"/>
       <c r="AG153" s="19"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="18"/>
       <c r="B154" s="18"/>
       <c r="C154" s="18"/>
@@ -14374,7 +14399,7 @@
       <c r="AF154" s="18"/>
       <c r="AG154" s="19"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="18"/>
       <c r="B155" s="18"/>
       <c r="C155" s="18"/>
@@ -14409,7 +14434,7 @@
       <c r="AF155" s="18"/>
       <c r="AG155" s="19"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="18"/>
       <c r="B156" s="18"/>
       <c r="C156" s="18"/>
@@ -14444,7 +14469,7 @@
       <c r="AF156" s="18"/>
       <c r="AG156" s="19"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="18"/>
       <c r="B157" s="18"/>
       <c r="C157" s="18"/>
@@ -14479,7 +14504,7 @@
       <c r="AF157" s="18"/>
       <c r="AG157" s="19"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="18"/>
       <c r="B158" s="18"/>
       <c r="C158" s="18"/>
@@ -14514,7 +14539,7 @@
       <c r="AF158" s="18"/>
       <c r="AG158" s="19"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="18"/>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
@@ -14549,7 +14574,7 @@
       <c r="AF159" s="18"/>
       <c r="AG159" s="19"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="18"/>
       <c r="B160" s="18"/>
       <c r="C160" s="18"/>
@@ -14584,7 +14609,7 @@
       <c r="AF160" s="18"/>
       <c r="AG160" s="19"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="18"/>
       <c r="B161" s="18"/>
       <c r="C161" s="18"/>
@@ -14619,7 +14644,7 @@
       <c r="AF161" s="18"/>
       <c r="AG161" s="19"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="18"/>
       <c r="B162" s="18"/>
       <c r="C162" s="18"/>
@@ -14654,7 +14679,7 @@
       <c r="AF162" s="18"/>
       <c r="AG162" s="19"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="18"/>
       <c r="B163" s="18"/>
       <c r="C163" s="18"/>
@@ -14689,7 +14714,7 @@
       <c r="AF163" s="18"/>
       <c r="AG163" s="19"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="18"/>
       <c r="B164" s="18"/>
       <c r="C164" s="18"/>
@@ -14724,7 +14749,7 @@
       <c r="AF164" s="18"/>
       <c r="AG164" s="19"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="18"/>
       <c r="B165" s="18"/>
       <c r="C165" s="18"/>
@@ -14759,7 +14784,7 @@
       <c r="AF165" s="18"/>
       <c r="AG165" s="19"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="18"/>
       <c r="B166" s="18"/>
       <c r="C166" s="18"/>
@@ -14794,7 +14819,7 @@
       <c r="AF166" s="18"/>
       <c r="AG166" s="19"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="18"/>
       <c r="B167" s="18"/>
       <c r="C167" s="18"/>
@@ -14829,7 +14854,7 @@
       <c r="AF167" s="18"/>
       <c r="AG167" s="19"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="18"/>
       <c r="B168" s="18"/>
       <c r="C168" s="18"/>
@@ -14864,7 +14889,7 @@
       <c r="AF168" s="18"/>
       <c r="AG168" s="19"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
@@ -14899,7 +14924,7 @@
       <c r="AF169" s="18"/>
       <c r="AG169" s="19"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="18"/>
       <c r="B170" s="18"/>
       <c r="C170" s="18"/>
@@ -14934,7 +14959,7 @@
       <c r="AF170" s="18"/>
       <c r="AG170" s="19"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="18"/>
       <c r="B171" s="18"/>
       <c r="C171" s="18"/>
@@ -14969,7 +14994,7 @@
       <c r="AF171" s="18"/>
       <c r="AG171" s="19"/>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="18"/>
       <c r="B172" s="18"/>
       <c r="C172" s="18"/>
@@ -15004,7 +15029,7 @@
       <c r="AF172" s="18"/>
       <c r="AG172" s="19"/>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="18"/>
       <c r="B173" s="18"/>
       <c r="C173" s="18"/>
@@ -15039,7 +15064,7 @@
       <c r="AF173" s="18"/>
       <c r="AG173" s="19"/>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="18"/>
       <c r="B174" s="18"/>
       <c r="C174" s="18"/>
@@ -15074,7 +15099,7 @@
       <c r="AF174" s="18"/>
       <c r="AG174" s="19"/>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="18"/>
       <c r="B175" s="18"/>
       <c r="C175" s="18"/>
@@ -15109,7 +15134,7 @@
       <c r="AF175" s="18"/>
       <c r="AG175" s="19"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="18"/>
       <c r="B176" s="18"/>
       <c r="C176" s="18"/>
@@ -15144,7 +15169,7 @@
       <c r="AF176" s="18"/>
       <c r="AG176" s="19"/>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="18"/>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -15179,7 +15204,7 @@
       <c r="AF177" s="18"/>
       <c r="AG177" s="19"/>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="18"/>
       <c r="B178" s="18"/>
       <c r="C178" s="18"/>
@@ -15214,7 +15239,7 @@
       <c r="AF178" s="18"/>
       <c r="AG178" s="19"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="18"/>
       <c r="B179" s="18"/>
       <c r="C179" s="18"/>
@@ -15249,7 +15274,7 @@
       <c r="AF179" s="18"/>
       <c r="AG179" s="19"/>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="18"/>
       <c r="B180" s="18"/>
       <c r="C180" s="18"/>
@@ -15284,7 +15309,7 @@
       <c r="AF180" s="18"/>
       <c r="AG180" s="19"/>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="18"/>
       <c r="B181" s="18"/>
       <c r="C181" s="18"/>
@@ -15319,7 +15344,7 @@
       <c r="AF181" s="18"/>
       <c r="AG181" s="19"/>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="18"/>
       <c r="B182" s="18"/>
       <c r="C182" s="18"/>
@@ -15354,7 +15379,7 @@
       <c r="AF182" s="18"/>
       <c r="AG182" s="19"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="18"/>
       <c r="B183" s="18"/>
       <c r="C183" s="18"/>
@@ -15389,7 +15414,7 @@
       <c r="AF183" s="18"/>
       <c r="AG183" s="19"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="18"/>
       <c r="B184" s="18"/>
       <c r="C184" s="18"/>
@@ -15424,7 +15449,7 @@
       <c r="AF184" s="18"/>
       <c r="AG184" s="19"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="18"/>
       <c r="B185" s="18"/>
       <c r="C185" s="18"/>
@@ -15459,7 +15484,7 @@
       <c r="AF185" s="18"/>
       <c r="AG185" s="19"/>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="18"/>
       <c r="B186" s="18"/>
       <c r="C186" s="18"/>
@@ -15494,7 +15519,7 @@
       <c r="AF186" s="18"/>
       <c r="AG186" s="19"/>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="18"/>
       <c r="B187" s="18"/>
       <c r="C187" s="18"/>
@@ -15529,7 +15554,7 @@
       <c r="AF187" s="18"/>
       <c r="AG187" s="19"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="18"/>
       <c r="B188" s="18"/>
       <c r="C188" s="18"/>
@@ -15564,7 +15589,7 @@
       <c r="AF188" s="18"/>
       <c r="AG188" s="19"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="18"/>
       <c r="B189" s="18"/>
       <c r="C189" s="18"/>
@@ -15599,7 +15624,7 @@
       <c r="AF189" s="18"/>
       <c r="AG189" s="19"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="18"/>
       <c r="B190" s="18"/>
       <c r="C190" s="18"/>
@@ -15634,7 +15659,7 @@
       <c r="AF190" s="18"/>
       <c r="AG190" s="19"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="18"/>
       <c r="B191" s="18"/>
       <c r="C191" s="18"/>
@@ -15669,7 +15694,7 @@
       <c r="AF191" s="18"/>
       <c r="AG191" s="19"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="18"/>
       <c r="B192" s="18"/>
       <c r="C192" s="18"/>
@@ -15704,7 +15729,7 @@
       <c r="AF192" s="18"/>
       <c r="AG192" s="19"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="18"/>
       <c r="B193" s="18"/>
       <c r="C193" s="18"/>
@@ -15739,7 +15764,7 @@
       <c r="AF193" s="18"/>
       <c r="AG193" s="19"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="18"/>
       <c r="B194" s="18"/>
       <c r="C194" s="18"/>
@@ -15774,7 +15799,7 @@
       <c r="AF194" s="18"/>
       <c r="AG194" s="19"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="18"/>
       <c r="B195" s="18"/>
       <c r="C195" s="18"/>
@@ -15809,7 +15834,7 @@
       <c r="AF195" s="18"/>
       <c r="AG195" s="19"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="18"/>
       <c r="B196" s="18"/>
       <c r="C196" s="18"/>
@@ -15844,7 +15869,7 @@
       <c r="AF196" s="18"/>
       <c r="AG196" s="19"/>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="18"/>
       <c r="B197" s="18"/>
       <c r="C197" s="18"/>
@@ -15879,7 +15904,7 @@
       <c r="AF197" s="18"/>
       <c r="AG197" s="19"/>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198" s="18"/>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
@@ -15914,7 +15939,7 @@
       <c r="AF198" s="18"/>
       <c r="AG198" s="19"/>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" s="18"/>
       <c r="B199" s="18"/>
       <c r="C199" s="18"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="574">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -135,12 +135,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Pain to Power&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whenever you take damage, refresh 1 WeirdT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Reckless&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <r>
@@ -151,8 +145,8 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Whenever you inflict a status effect, you may set that creatures composure to 1.
-</t>
+      <t xml:space="preserve">Whenever you take damage, 
+&lt;b</t>
     </r>
     <r>
       <rPr>
@@ -161,18 +155,31 @@
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">&lt;br&gt;This is a test 
-&lt;br /&gt;Did it work? 
-\13\How about now? 
-&lt;p&gt;This CAN’T be the only option that works </t>
+      <t xml:space="preserve">r /&gt;</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">refresh 1 WeirdT.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Reckless&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whenever you inflict a status effect, you may set that creatures composure to 1.</t>
   </si>
   <si>
     <t xml:space="preserve">Beast</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
-&lt;br&gt;+1 Movement Speed.</t>
+&lt;br /&gt;+1 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Relentless&lt;/i&gt;&lt;/b&gt;</t>
@@ -185,7 +192,7 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Howl: &lt;/b&gt;Gain &lt;b&gt;Monstrous&lt;/b&gt;.</t>
+&lt;br /&gt;&lt;b&gt;Howl: &lt;/b&gt;Gain &lt;b&gt;Monstrous&lt;/b&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">Carcinous</t>
@@ -207,7 +214,7 @@
   </si>
   <si>
     <t xml:space="preserve">You may only move sideways.
-&lt;br&gt;Swivel on a point you're standing on, then move as many tiles as you like in a straight line aligned with the hexes. </t>
+&lt;br /&gt;Swivel on a point you're standing on, then move as many tiles as you like in a straight line aligned with the hexes. </t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#e74c3c"&gt;&lt;b&gt;Flesh&lt;/b&gt;&lt;/span&gt;</t>
@@ -259,7 +266,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 3, Close&lt;/b&gt;
-&lt;br&gt;On a hit, you may move to any hex adjacent to the target.</t>
+&lt;br /&gt;On a hit, you may move to any hex adjacent to the target.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Massive Limbs&lt;/i&gt;&lt;/b&gt;</t>
@@ -275,16 +282,16 @@
   </si>
   <si>
     <t xml:space="preserve">At the start of your turn, gain 
-&lt;br&gt;tempct tempct. Temporary composure can stack from any source up to a cap of 5.</t>
+&lt;br /&gt;tempct tempct. Temporary composure can stack from any source up to 5.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Light Beam:&lt;/b&gt; 1 tempct</t>
   </si>
   <si>
     <t xml:space="preserve">Do one of the following:
-&lt;br&gt;&lt;b&gt;Scamper:&lt;/b&gt; Move 1 tile.
-&lt;br&gt;&lt;b&gt;Focus:&lt;/b&gt; Increase your attack roll by 1. Once per attack.
-&lt;br&gt;&lt;b&gt;Calm:&lt;/b&gt; Restore comptcompt.</t>
+&lt;br /&gt;&lt;b&gt;Scamper:&lt;/b&gt; Move 1 tile.
+&lt;br /&gt;&lt;b&gt;Focus:&lt;/b&gt; Increase your attack roll by 1. Once per attack.
+&lt;br /&gt;&lt;b&gt;Calm:&lt;/b&gt; Restore comptcompt.</t>
   </si>
   <si>
     <t xml:space="preserve">Hag</t>
@@ -294,7 +301,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
-&lt;br&gt;- 1 Movement Speed.</t>
+&lt;br /&gt;- 1 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Twisted&lt;/i&gt;&lt;/b&gt;</t>
@@ -331,14 +338,14 @@
   </si>
   <si>
     <t xml:space="preserve">Reduce damage taken by 1.
-&lt;br&gt;- 1 Movement Speed.</t>
+&lt;br /&gt;- 1 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Punk Rock&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Your melee attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Hurl: &lt;/b&gt;Throw the victim in a straight line tiles equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;. If they hit terrain or another being, both take 3 damage.</t>
+&lt;br /&gt;&lt;b&gt;Hurl: &lt;/b&gt;Throw the victim in a straight line tiles equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;. If they hit terrain or another being, both take 3 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Human</t>
@@ -369,7 +376,7 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option:
-&lt;br&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
+&lt;br /&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Regenerative&lt;/i&gt;&lt;/b&gt;</t>
@@ -421,15 +428,12 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option:
-&lt;br&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
+&lt;br /&gt;&lt;b&gt;Extract energy:&lt;/b&gt; Refresh 1 chargeT.</t>
   </si>
   <si>
     <t xml:space="preserve">Mechanical</t>
   </si>
   <si>
-    <t xml:space="preserve">chargebig X P</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Modal&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
@@ -554,7 +558,7 @@
   </si>
   <si>
     <t xml:space="preserve">Reduce damage taken by 1.
-&lt;br&gt;-2 Movement Speed.</t>
+&lt;br /&gt;-2 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Impervious Plates&lt;/i&gt;&lt;/b&gt;</t>
@@ -567,7 +571,7 @@
   </si>
   <si>
     <t xml:space="preserve">You cannot be move or be made to move except with the move action.
-&lt;br&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
+&lt;br /&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
   </si>
   <si>
     <t xml:space="preserve">Unstable</t>
@@ -592,19 +596,40 @@
   </si>
   <si>
     <t xml:space="preserve">Reduce damage taken by 1.
-&lt;br&gt;-1 Movement Speed.</t>
+&lt;br /&gt;-1 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Breathe Fire:&lt;/b&gt; 3 AP + weirdT</t>
   </si>
   <si>
     <t xml:space="preserve">Emit an inferno of fire, all other beings within 3 hexes take 7 damage.
-&lt;br&gt;You and all adjacent beings suffer the &lt;b&gt;Burning&lt;/b&gt; status.</t>
+&lt;br /&gt;You and all adjacent beings suffer the &lt;b&gt;Burning&lt;/b&gt; status.</t>
   </si>
   <si>
     <t xml:space="preserve">Worm Nest</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chargebigx Playe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">rs</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;b&gt;Infect&lt;/b&gt;</t>
   </si>
   <si>
@@ -702,8 +727,8 @@
   </si>
   <si>
     <t xml:space="preserve">At the start of your turn, if you have an equal number of unspent tokens in each stat, refresh two spent stat tokens.
-&lt;br&gt;
-&lt;br&gt;They must be different tokens.</t>
+&lt;br /&gt;
+&lt;br /&gt;They must be different tokens.</t>
   </si>
   <si>
     <t xml:space="preserve">Blood Mage</t>
@@ -734,7 +759,7 @@
   </si>
   <si>
     <t xml:space="preserve">At the start of your first turn, draw an impression and equip it over creative.
-&lt;br&gt;At the end of your each turn, you &lt;b&gt;may&lt;/b&gt; discard that impression to draw and equip a new impression over creative.</t>
+&lt;br /&gt;At the end of your each turn, you &lt;b&gt;may&lt;/b&gt; discard that impression to draw and equip a new impression over creative.</t>
   </si>
   <si>
     <t xml:space="preserve">Dancer</t>
@@ -743,7 +768,7 @@
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt; Flow State&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Your attacks have the Crit Option &lt;br&gt;&lt;b&gt;Pirouette:&lt;/b&gt; Move hexes up to your  &lt;span style="color:#27ae60"&gt;&lt;strong&gt;Jazz&lt;/strong&gt;&lt;/span&gt;.</t>
+    <t xml:space="preserve">Your attacks have the Crit Option &lt;br /&gt;&lt;b&gt;Pirouette:&lt;/b&gt; Move hexes up to your  &lt;span style="color:#27ae60"&gt;&lt;strong&gt;Jazz&lt;/strong&gt;&lt;/span&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;On the Move&lt;/b&gt;&lt;/i&gt;</t>
@@ -783,7 +808,7 @@
   </si>
   <si>
     <t xml:space="preserve">Create a large pillar Hex1b in target empty location.
-&lt;br&gt;&lt;br&gt;Pillars can be climbed by spending 3 AP or jazzT.</t>
+&lt;br /&gt;&lt;br /&gt;Pillars can be climbed by spending 3 AP or jazzT. Beings take 8 damage if they fall off.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;World Sculptor&lt;/i&gt;&lt;/b&gt;</t>
@@ -802,7 +827,7 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to 1 temporary composure.</t>
+&lt;br /&gt;&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to 1 temporary composure.</t>
   </si>
   <si>
     <t xml:space="preserve">I'm Normal</t>
@@ -860,7 +885,7 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Imbue:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
+&lt;br /&gt;&lt;b&gt;Imbue:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Treasure!&lt;/b&gt;&lt;/i&gt;</t>
@@ -930,8 +955,8 @@
   </si>
   <si>
     <t xml:space="preserve">Offer a deal to a player. If they accept they gain one temporary stat token.
-&lt;br&gt;If they then break the deal, they take 8 damage.
-&lt;br&gt;If they reject the deal, you gain the temporary stat token.</t>
+&lt;br /&gt;If they then break the deal, they take 8 damage.
+&lt;br /&gt;If they reject the deal, you gain the temporary stat token.</t>
   </si>
   <si>
     <t xml:space="preserve">Nimble</t>
@@ -967,7 +992,7 @@
     <t xml:space="preserve">Patient</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Inhale&lt;br&gt;&lt;/i&gt;&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Inhale&lt;br /&gt;&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">At the end of your turn, for each unspent action point add charget to this card, up to max of your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt;.</t>
@@ -1022,7 +1047,7 @@
   </si>
   <si>
     <t xml:space="preserve">Create a 3 hex area of darkness Hex1b
-&lt;br&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only Crit on a 12.</t>
+&lt;br /&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only Crit on a 12.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Creature of the Shadows&lt;/i&gt;&lt;/b&gt;</t>
@@ -1068,7 +1093,7 @@
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option
-&lt;br&gt;&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
+&lt;br /&gt;&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
   </si>
   <si>
     <t xml:space="preserve">Strong Heartbeat</t>
@@ -1141,7 +1166,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
-&lt;br&gt;This attack can only target your hated target.</t>
+&lt;br /&gt;This attack can only target your hated target.</t>
   </si>
   <si>
     <t xml:space="preserve">Crit</t>
@@ -1163,7 +1188,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Flurry:&lt;/b&gt; Your next attack costs 1 less AP.
-&lt;br&gt;&lt;b&gt;Strike:&lt;/b&gt; +1 Damage.</t>
+&lt;br /&gt;&lt;b&gt;Strike:&lt;/b&gt; +1 Damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Chalk Vein</t>
@@ -1233,7 +1258,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Dash:&lt;/b&gt; Take a move action.
-&lt;br&gt;&lt;b&gt;Mighty Shove:&lt;/b&gt; Push the target 2 hexes.</t>
+&lt;br /&gt;&lt;b&gt;Mighty Shove:&lt;/b&gt; Push the target 2 hexes.</t>
   </si>
   <si>
     <t xml:space="preserve">Crackling Geode</t>
@@ -1243,7 +1268,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 1, Reach&lt;/b&gt;
-&lt;br&gt;This damage cannot be reduced.</t>
+&lt;br /&gt;This damage cannot be reduced.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Sparks&lt;/i&gt;&lt;/b&gt;</t>
@@ -1265,7 +1290,7 @@
   </si>
   <si>
     <t xml:space="preserve">At the end of your turn, if you are adjacent to a crystal, choose one of the following status effects to gain:
-&lt;br&gt;&lt;b&gt;Monstrous, Well Rested, Imbued&lt;/b&gt;.</t>
+&lt;br /&gt;&lt;b&gt;Monstrous, Well Rested, Imbued&lt;/b&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">Dolem Piston</t>
@@ -1377,7 +1402,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 3, Close&lt;/b&gt;
-&lt;br&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
+&lt;br /&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
   </si>
   <si>
     <t xml:space="preserve">Hammer and Chisel</t>
@@ -1387,7 +1412,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 2, Close&lt;/b&gt;
-&lt;br&gt;On a hit, you may destroy this card to destroy any equipped Limb or Impression from the target.</t>
+&lt;br /&gt;On a hit, you may destroy this card to destroy any equipped Limb or Impression from the target.</t>
   </si>
   <si>
     <t xml:space="preserve">Horns</t>
@@ -1397,14 +1422,14 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = hexes moved, Close&lt;/b&gt;
-&lt;br&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br&gt; hornshexes</t>
+&lt;br /&gt;Charge any number of hexes in a straight line as part of making the attack.&lt;br /&gt; hornshexes</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt; Shove:&lt;/b&gt;  1 AP + fleshT</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 2, Close&lt;/b&gt;
-&lt;br&gt;On a hit, the target is pushed back hexes equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
+&lt;br /&gt;On a hit, the target is pushed back hexes equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">Humming Moonstone</t>
@@ -1429,7 +1454,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 7, Ranged&lt;/b&gt;
-&lt;br&gt;Throw this limb at your target as part of the attack, regardless of attack outcome, they now have Hungering Hand equipped .</t>
+&lt;br /&gt;Throw this limb at your target as part of the attack, regardless of attack outcome, they now have Hungering Hand equipped .</t>
   </si>
   <si>
     <t xml:space="preserve">Lanceflower Bloom</t>
@@ -1484,7 +1509,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 1, Close&lt;/b&gt;
-&lt;br&gt;This attack always hits, do not roll.</t>
+&lt;br /&gt;This attack always hits, do not roll.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Snack&lt;/i&gt;&lt;/b&gt;</t>
@@ -1539,7 +1564,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
-&lt;br&gt;Ignores damage reduction effects.</t>
+&lt;br /&gt;Ignores damage reduction effects.</t>
   </si>
   <si>
     <t xml:space="preserve">Oversized Claw</t>
@@ -1585,7 +1610,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
-&lt;br&gt;You take 1 damage when you use this attack, this damage cannot be reduced.</t>
+&lt;br /&gt;You take 1 damage when you use this attack, this damage cannot be reduced.</t>
   </si>
   <si>
     <t xml:space="preserve">Pulsing Heartstone</t>
@@ -1613,7 +1638,7 @@
   </si>
   <si>
     <t xml:space="preserve">Place a &lt;b&gt;crystal spire&lt;/b&gt; on an adjacent hex, it has a two hex radius aura, blocks line of sight, and is &lt;b&gt;destructible&lt;/b&gt;.
-&lt;br&gt;Whiskey_Xplo</t>
+&lt;br /&gt;Whiskey_Xplo</t>
   </si>
   <si>
     <t xml:space="preserve">Other beings that start their turn inside a &lt;b&gt;crystal spire&lt;/b&gt; aura or enter it take 3 damage.</t>
@@ -1640,9 +1665,6 @@
     <t xml:space="preserve">&lt;b&gt;Thump:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Damage =4, Close&lt;/b&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;b&gt;Dig:&lt;/b&gt; 1 AP or fleshT</t>
   </si>
   <si>
@@ -1656,7 +1678,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 0, Ranged&lt;/b&gt;
-&lt;br&gt;Pull the target to an adjacent hex on a hit</t>
+&lt;br /&gt;Pull the target to an adjacent hex on a hit</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Entangle:&lt;/b&gt; Inflict the &lt;b&gt;Entangled&lt;/b&gt; status effect.</t>
@@ -1669,7 +1691,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 2, Reach&lt;/b&gt;
-&lt;br&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
+&lt;br /&gt;Inflicts the &lt;b&gt;Entangled&lt;/b&gt; status effect on a hit.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Secretions&lt;/b&gt;&lt;/i&gt;   </t>
@@ -1688,7 +1710,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Dash:&lt;/b&gt; Take a move action for free.
-&lt;br&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage.</t>
+&lt;br /&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage.</t>
   </si>
   <si>
     <t xml:space="preserve">Stalagmite</t>
@@ -1698,7 +1720,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 4, Reach&lt;/b&gt;
-&lt;br&gt;This can only target non-adjacent beings.</t>
+&lt;br /&gt;This can only target non-adjacent beings.</t>
   </si>
   <si>
     <t xml:space="preserve">Steam Vent</t>
@@ -1708,7 +1730,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 2, Reach&lt;/b&gt;
-&lt;br&gt;On a hit, remove all &lt;b&gt;temporary composure&lt;/b&gt; from the target before dealing damage.</t>
+&lt;br /&gt;On a hit, remove all &lt;b&gt;temporary composure&lt;/b&gt; from the target before dealing damage.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack cannot be reduced.</t>
@@ -1751,8 +1773,8 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 5, Ranged&lt;/b&gt;
-&lt;br&gt;On a hit, inflict the &lt;b&gt;burning&lt;/b&gt; status effect.
-&lt;br&gt;On a miss, inflict the &lt;b&gt;burning&lt;/b&gt; status effect on you.</t>
+&lt;br /&gt;On a hit, inflict the &lt;b&gt;burning&lt;/b&gt; status effect.
+&lt;br /&gt;On a miss, inflict the &lt;b&gt;burning&lt;/b&gt; status effect on you.</t>
   </si>
   <si>
     <t xml:space="preserve">Torsion Ribs</t>
@@ -1768,7 +1790,7 @@
   </si>
   <si>
     <t xml:space="preserve">Automatically activates upon reaching 5 charget.
-&lt;br&gt;Deal 8 damage to all beings in a straight line from you. No attack roll required.</t>
+&lt;br /&gt;Deal 8 damage to all beings in a straight line from you. No attack roll required.</t>
   </si>
   <si>
     <t xml:space="preserve">Twitching Talons</t>
@@ -1820,7 +1842,7 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 5, Close&lt;/b&gt;
-&lt;br&gt;Inflict the &lt;b&gt;Exhausted&lt;/b&gt; status effect on a hit.</t>
+&lt;br /&gt;Inflict the &lt;b&gt;Exhausted&lt;/b&gt; status effect on a hit.</t>
   </si>
 </sst>
 </file>
@@ -2779,7 +2801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="68.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
@@ -3293,7 +3315,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
         <v>72</v>
       </c>
@@ -3316,7 +3338,7 @@
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>50</v>
@@ -3352,15 +3374,15 @@
       </c>
       <c r="AB8" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>44.2</v>
       </c>
       <c r="AC8" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="AD8" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="AE8" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -3994,9 +4016,7 @@
       <c r="B16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>122</v>
-      </c>
+      <c r="C16" s="9"/>
       <c r="D16" s="10"/>
       <c r="E16" s="9" t="n">
         <v>1</v>
@@ -4005,10 +4025,10 @@
         <v>35</v>
       </c>
       <c r="G16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="9" t="n">
@@ -4067,13 +4087,13 @@
     </row>
     <row r="17" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="9" t="n">
@@ -4083,10 +4103,10 @@
         <v>35</v>
       </c>
       <c r="G17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="9" t="n">
@@ -4096,10 +4116,10 @@
         <v>35</v>
       </c>
       <c r="L17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="9" t="n">
@@ -4109,10 +4129,10 @@
         <v>35</v>
       </c>
       <c r="Q17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R17" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>132</v>
       </c>
       <c r="S17" s="10"/>
       <c r="T17" s="9"/>
@@ -4159,7 +4179,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>34</v>
@@ -4173,10 +4193,10 @@
         <v>50</v>
       </c>
       <c r="G18" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="9" t="n">
@@ -4186,10 +4206,10 @@
         <v>50</v>
       </c>
       <c r="L18" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="9" t="n">
@@ -4199,10 +4219,10 @@
         <v>35</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="R18" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="S18" s="10"/>
       <c r="T18" s="9"/>
@@ -4249,7 +4269,7 @@
     </row>
     <row r="19" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>34</v>
@@ -4263,23 +4283,23 @@
         <v>35</v>
       </c>
       <c r="G19" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>50</v>
       </c>
       <c r="L19" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="9"/>
@@ -4306,15 +4326,15 @@
       </c>
       <c r="AB19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>57.4</v>
+        <v>53</v>
       </c>
       <c r="AC19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>56.3</v>
+        <v>51.9</v>
       </c>
       <c r="AD19" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>63.4</v>
+        <v>59</v>
       </c>
       <c r="AE19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -4331,7 +4351,7 @@
     </row>
     <row r="20" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>34</v>
@@ -4345,10 +4365,10 @@
         <v>35</v>
       </c>
       <c r="G20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>147</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="9" t="n">
@@ -4358,10 +4378,10 @@
         <v>35</v>
       </c>
       <c r="L20" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="9"/>
@@ -4413,7 +4433,7 @@
     </row>
     <row r="21" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>34</v>
@@ -4429,23 +4449,23 @@
         <v>50</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>50</v>
       </c>
       <c r="L21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="9"/>
@@ -4472,15 +4492,15 @@
       </c>
       <c r="AB21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>70.6</v>
+        <v>68.4</v>
       </c>
       <c r="AC21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>69.5</v>
+        <v>67.3</v>
       </c>
       <c r="AD21" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>76.6</v>
+        <v>74.4</v>
       </c>
       <c r="AE21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -4497,7 +4517,7 @@
     </row>
     <row r="22" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>34</v>
@@ -4511,10 +4531,10 @@
         <v>35</v>
       </c>
       <c r="G22" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>157</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="9" t="n">
@@ -4524,10 +4544,10 @@
         <v>35</v>
       </c>
       <c r="L22" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="9" t="n">
@@ -4537,10 +4557,10 @@
         <v>35</v>
       </c>
       <c r="Q22" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="R22" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="9"/>
@@ -4587,7 +4607,7 @@
     </row>
     <row r="23" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>34</v>
@@ -4603,10 +4623,10 @@
         <v>35</v>
       </c>
       <c r="G23" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="9" t="n">
@@ -4616,10 +4636,10 @@
         <v>35</v>
       </c>
       <c r="L23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="M23" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="9" t="n">
@@ -4629,10 +4649,10 @@
         <v>35</v>
       </c>
       <c r="Q23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="R23" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="S23" s="10"/>
       <c r="T23" s="9"/>
@@ -4679,7 +4699,7 @@
     </row>
     <row r="24" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>34</v>
@@ -4693,10 +4713,10 @@
         <v>35</v>
       </c>
       <c r="G24" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="I24" s="18"/>
       <c r="J24" s="9" t="n">
@@ -4706,10 +4726,10 @@
         <v>35</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="M24" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="N24" s="19"/>
       <c r="O24" s="9"/>
@@ -4771,7 +4791,7 @@
     </row>
     <row r="25" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>34</v>
@@ -4785,10 +4805,10 @@
         <v>35</v>
       </c>
       <c r="G25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="9" t="n">
@@ -4798,10 +4818,10 @@
         <v>50</v>
       </c>
       <c r="L25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="M25" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="11"/>
@@ -4851,15 +4871,15 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="9" t="n">
@@ -6021,7 +6041,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
         <v>236</v>
       </c>
@@ -6287,7 +6307,7 @@
       </c>
       <c r="N44" s="12"/>
       <c r="O44" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P44" s="9" t="s">
         <v>50</v>
@@ -6330,15 +6350,15 @@
       </c>
       <c r="AE44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="AF44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>59.3</v>
+        <v>54.9</v>
       </c>
       <c r="AG44" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>66.4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,7 +6698,7 @@
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>50</v>
@@ -6714,15 +6734,15 @@
       </c>
       <c r="AB49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>44.2</v>
       </c>
       <c r="AC49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="AD49" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="AE49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7138,7 +7158,7 @@
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>35</v>
@@ -7174,15 +7194,15 @@
       </c>
       <c r="AB55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD55" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7294,7 +7314,7 @@
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>50</v>
@@ -7330,15 +7350,15 @@
       </c>
       <c r="AB57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>44.2</v>
       </c>
       <c r="AC57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="AD57" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="AE57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7614,7 +7634,7 @@
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>35</v>
@@ -7650,15 +7670,15 @@
       </c>
       <c r="AB61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>57.4</v>
       </c>
       <c r="AC61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>56.3</v>
       </c>
       <c r="AD61" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>63.4</v>
       </c>
       <c r="AE61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8230,7 +8250,7 @@
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>35</v>
@@ -8266,15 +8286,15 @@
       </c>
       <c r="AB69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD69" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8972,7 +8992,7 @@
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78" s="9" t="s">
         <v>35</v>
@@ -9008,15 +9028,15 @@
       </c>
       <c r="AB78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD78" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9398,7 +9418,7 @@
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>67</v>
@@ -9434,15 +9454,15 @@
       </c>
       <c r="AB83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>44.2</v>
       </c>
       <c r="AC83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="AD83" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="AE83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11354,7 +11374,7 @@
         <v>516</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>517</v>
+        <v>380</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9" t="n">
@@ -11364,10 +11384,10 @@
         <v>50</v>
       </c>
       <c r="L107" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="M107" s="9" t="s">
         <v>518</v>
-      </c>
-      <c r="M107" s="9" t="s">
-        <v>519</v>
       </c>
       <c r="N107" s="12"/>
       <c r="O107" s="9" t="n">
@@ -11425,9 +11445,9 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B108" s="20" t="s">
         <v>351</v>
@@ -11441,10 +11461,10 @@
         <v>67</v>
       </c>
       <c r="G108" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="H108" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="H108" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="I108" s="10"/>
       <c r="J108" s="9" t="n">
@@ -11457,7 +11477,7 @@
         <v>357</v>
       </c>
       <c r="M108" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N108" s="12"/>
       <c r="O108" s="9"/>
@@ -11509,7 +11529,7 @@
     </row>
     <row r="109" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B109" s="20" t="s">
         <v>351</v>
@@ -11523,10 +11543,10 @@
         <v>67</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>525</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>526</v>
       </c>
       <c r="I109" s="18"/>
       <c r="J109" s="9" t="n">
@@ -11536,10 +11556,10 @@
         <v>35</v>
       </c>
       <c r="L109" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="M109" s="9" t="s">
         <v>527</v>
-      </c>
-      <c r="M109" s="9" t="s">
-        <v>528</v>
       </c>
       <c r="N109" s="19"/>
       <c r="O109" s="9" t="n">
@@ -11593,7 +11613,7 @@
     </row>
     <row r="110" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B110" s="20" t="s">
         <v>351</v>
@@ -11607,10 +11627,10 @@
         <v>67</v>
       </c>
       <c r="G110" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="H110" s="11" t="s">
         <v>530</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>531</v>
       </c>
       <c r="I110" s="10"/>
       <c r="J110" s="9" t="n">
@@ -11623,7 +11643,7 @@
         <v>357</v>
       </c>
       <c r="M110" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N110" s="12"/>
       <c r="O110" s="9"/>
@@ -11675,7 +11695,7 @@
     </row>
     <row r="111" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B111" s="20" t="s">
         <v>351</v>
@@ -11689,10 +11709,10 @@
         <v>67</v>
       </c>
       <c r="G111" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="H111" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="H111" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9" t="n">
@@ -11757,7 +11777,7 @@
     </row>
     <row r="112" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B112" s="20" t="s">
         <v>351</v>
@@ -11771,10 +11791,10 @@
         <v>67</v>
       </c>
       <c r="G112" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="H112" s="11" t="s">
         <v>537</v>
-      </c>
-      <c r="H112" s="11" t="s">
-        <v>538</v>
       </c>
       <c r="I112" s="10"/>
       <c r="J112" s="9" t="n">
@@ -11787,7 +11807,7 @@
         <v>357</v>
       </c>
       <c r="M112" s="11" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N112" s="12"/>
       <c r="O112" s="9"/>
@@ -11839,7 +11859,7 @@
     </row>
     <row r="113" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B113" s="20" t="s">
         <v>351</v>
@@ -11853,10 +11873,10 @@
         <v>67</v>
       </c>
       <c r="G113" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="H113" s="11" t="s">
         <v>541</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>542</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9"/>
@@ -11913,7 +11933,7 @@
     </row>
     <row r="114" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B114" s="20" t="s">
         <v>351</v>
@@ -11927,10 +11947,10 @@
         <v>50</v>
       </c>
       <c r="G114" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="H114" s="11" t="s">
         <v>544</v>
-      </c>
-      <c r="H114" s="11" t="s">
-        <v>545</v>
       </c>
       <c r="I114" s="10"/>
       <c r="J114" s="9" t="n">
@@ -11940,10 +11960,10 @@
         <v>35</v>
       </c>
       <c r="L114" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="M114" s="9" t="s">
         <v>546</v>
-      </c>
-      <c r="M114" s="9" t="s">
-        <v>547</v>
       </c>
       <c r="N114" s="12"/>
       <c r="O114" s="9" t="n">
@@ -11953,10 +11973,10 @@
         <v>35</v>
       </c>
       <c r="Q114" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="R114" s="9" t="s">
         <v>548</v>
-      </c>
-      <c r="R114" s="9" t="s">
-        <v>549</v>
       </c>
       <c r="S114" s="10"/>
       <c r="T114" s="9"/>
@@ -12003,7 +12023,7 @@
     </row>
     <row r="115" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B115" s="20" t="s">
         <v>351</v>
@@ -12017,10 +12037,10 @@
         <v>67</v>
       </c>
       <c r="G115" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="H115" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="H115" s="11" t="s">
-        <v>552</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9"/>
@@ -12077,7 +12097,7 @@
     </row>
     <row r="116" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B116" s="20" t="s">
         <v>351</v>
@@ -12091,10 +12111,10 @@
         <v>50</v>
       </c>
       <c r="G116" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="H116" s="11" t="s">
         <v>554</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>555</v>
       </c>
       <c r="I116" s="10"/>
       <c r="J116" s="9" t="n">
@@ -12104,10 +12124,10 @@
         <v>67</v>
       </c>
       <c r="L116" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="M116" s="11" t="s">
         <v>556</v>
-      </c>
-      <c r="M116" s="11" t="s">
-        <v>557</v>
       </c>
       <c r="N116" s="12"/>
       <c r="O116" s="9"/>
@@ -12159,7 +12179,7 @@
     </row>
     <row r="117" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B117" s="20" t="s">
         <v>351</v>
@@ -12173,7 +12193,7 @@
         <v>67</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H117" s="11" t="s">
         <v>380</v>
@@ -12186,10 +12206,10 @@
         <v>35</v>
       </c>
       <c r="L117" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="M117" s="11" t="s">
         <v>560</v>
-      </c>
-      <c r="M117" s="11" t="s">
-        <v>561</v>
       </c>
       <c r="N117" s="12"/>
       <c r="O117" s="9"/>
@@ -12241,7 +12261,7 @@
     </row>
     <row r="118" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B118" s="20" t="s">
         <v>351</v>
@@ -12255,10 +12275,10 @@
         <v>67</v>
       </c>
       <c r="G118" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="H118" s="11" t="s">
         <v>563</v>
-      </c>
-      <c r="H118" s="11" t="s">
-        <v>564</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="9" t="n">
@@ -12268,10 +12288,10 @@
         <v>218</v>
       </c>
       <c r="L118" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="M118" s="9" t="s">
         <v>565</v>
-      </c>
-      <c r="M118" s="9" t="s">
-        <v>566</v>
       </c>
       <c r="N118" s="12"/>
       <c r="O118" s="9" t="n">
@@ -12284,7 +12304,7 @@
         <v>357</v>
       </c>
       <c r="R118" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S118" s="10"/>
       <c r="T118" s="9"/>
@@ -12331,7 +12351,7 @@
     </row>
     <row r="119" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B119" s="20" t="s">
         <v>351</v>
@@ -12345,7 +12365,7 @@
         <v>67</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H119" s="11" t="s">
         <v>451</v>
@@ -12358,10 +12378,10 @@
         <v>50</v>
       </c>
       <c r="L119" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="M119" s="9" t="s">
         <v>570</v>
-      </c>
-      <c r="M119" s="9" t="s">
-        <v>571</v>
       </c>
       <c r="N119" s="12"/>
       <c r="O119" s="9"/>
@@ -12413,7 +12433,7 @@
     </row>
     <row r="120" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B120" s="20" t="s">
         <v>351</v>
@@ -12427,10 +12447,10 @@
         <v>67</v>
       </c>
       <c r="G120" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="H120" s="11" t="s">
         <v>573</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>574</v>
       </c>
       <c r="I120" s="10"/>
       <c r="J120" s="9"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="576">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -134,48 +134,31 @@
     <t xml:space="preserve">Passive</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Pain to Power&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Whenever you take damage, 
-&lt;b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">r /&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">refresh 1 WeirdT.</t>
-    </r>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Clear Mind&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the start of your turn, flip an impression face up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Thief of thought&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn one of your impressions face down to stun target being</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandon Soul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the end of your turn, if you have no face up impressions then refresh 2 stat tokens and gain monstrous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Reckless&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whenever you inflict a status effect, you may set that creatures composure to 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
@@ -201,20 +184,24 @@
     <t xml:space="preserve">Shape = Hex2wide</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Chiten&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduce damage taken by 2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Sidesteps:&lt;/b&gt; 1AP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You may only move sideways.
-&lt;br /&gt;Swivel on a point you're standing on, then move as many tiles as you like in a straight line aligned with the hexes. </t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Many Legs&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 Movement Speed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Sideways Scuttle&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Emergence, declare a front hex and a back hex for your character token. 
+&lt;br /&gt;You may attack using either hex.
+&lt;br /&gt;You move with your front hex. When you stop moving, place your back hex in any adjacent hex.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Cracked Shell&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduce all damage to your back hex by 3.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#e74c3c"&gt;&lt;b&gt;Flesh&lt;/b&gt;&lt;/span&gt;</t>
@@ -244,10 +231,16 @@
     <t xml:space="preserve">Fungal</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Spores&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whenever you are struck by a melee attack, after damage is resolved, deal 2 damage to all adjacent beings and refresh your composure.</t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Pulpy&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase you maximum composure by 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Toxic&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whenever you would deal damage, you may instead set that beings composure to 1</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#27ae60"&gt;&lt;b&gt;Jazz&lt;/b&gt;&lt;/span&gt;</t>
@@ -262,17 +255,22 @@
     <t xml:space="preserve">Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Squash:&lt;/b&gt;  2 AP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Damage = 3, Close&lt;/b&gt;
-&lt;br /&gt;On a hit, you may move to any hex adjacent to the target.</t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Behemoth&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can't be be forced to move against your will. When you move, declare one of your hex as your moving hex. Your other Hexes follow behind.  Moving through a 1 wide gap counts as moving 2 hexes.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Massive Limbs&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Attacks that cost more than 2 AP cost 1 less and have &lt;b&gt;Reach&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Heft&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After emergence, gain +1 Flesh.</t>
   </si>
   <si>
     <t xml:space="preserve">Glowing Kintsugi</t>
@@ -331,30 +329,10 @@
     <t xml:space="preserve">If you take a wound during combat, you &lt;b&gt;die.&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Hulking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Immense&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduce damage taken by 1.
-&lt;br /&gt;- 1 Movement Speed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Punk Rock&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your melee attacks have the Crit option
-&lt;br /&gt;&lt;b&gt;Hurl: &lt;/b&gt;Throw the victim in a straight line tiles equal to your &lt;span style="color:#e74c3c"&gt;&lt;strong&gt;Flesh&lt;/strong&gt;&lt;/span&gt;. If they hit terrain or another being, both take 3 damage.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Human</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Two Legs&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1 Movement Speed.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Two Arms&lt;/i&gt;&lt;/b&gt;</t>
@@ -440,7 +418,7 @@
     <t xml:space="preserve">At the start of your turn, put a counter on an empty mode, then use that effect.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mob of Deep Ones</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">hex1big   hex1big   hex1big</t>
@@ -567,9 +545,6 @@
     <t xml:space="preserve">Reduce damage from non-adjacent beings to 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Behemoth&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">You cannot be move or be made to move except with the move action.
 &lt;br /&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
   </si>
@@ -609,25 +584,7 @@
     <t xml:space="preserve">Worm Nest</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">chargebigx Playe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">rs</t>
-    </r>
+    <t xml:space="preserve">chargebigx Players</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Infect&lt;/b&gt;</t>
@@ -1852,7 +1809,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1881,12 +1838,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2456,8 +2407,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:AG199" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:AG199"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:AG198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:AG198"/>
   <tableColumns count="33">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Type"/>
@@ -2673,7 +2624,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG199"/>
+  <dimension ref="A1:AG1048576"/>
   <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -2824,22 +2775,30 @@
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="9"/>
+      <c r="Q2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="S2" s="10"/>
       <c r="T2" s="9" t="n">
         <v>29.6</v>
@@ -2870,32 +2829,32 @@
       </c>
       <c r="AB2" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>35.4</v>
       </c>
       <c r="AC2" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="AD2" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>41.4</v>
       </c>
       <c r="AE2" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>51.6</v>
       </c>
       <c r="AF2" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>50.5</v>
       </c>
       <c r="AG2" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>34</v>
@@ -2909,10 +2868,10 @@
         <v>35</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="9" t="n">
@@ -2922,10 +2881,10 @@
         <v>35</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N3" s="12"/>
       <c r="O3" s="9" t="n">
@@ -2935,10 +2894,10 @@
         <v>35</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S3" s="10"/>
       <c r="T3" s="9"/>
@@ -2983,15 +2942,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="68.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="n">
@@ -3001,33 +2960,41 @@
         <v>35</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="N4" s="12"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="9"/>
+      <c r="O4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>57</v>
+      </c>
       <c r="S4" s="10"/>
       <c r="T4" s="9"/>
       <c r="U4" s="14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
@@ -3058,52 +3025,52 @@
       </c>
       <c r="AE4" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>69.2</v>
       </c>
       <c r="AF4" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>68.1</v>
       </c>
       <c r="AG4" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="9"/>
@@ -3113,7 +3080,7 @@
       <c r="S5" s="10"/>
       <c r="T5" s="9"/>
       <c r="U5" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
@@ -3132,15 +3099,15 @@
       </c>
       <c r="AB5" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>53</v>
       </c>
       <c r="AC5" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>51.9</v>
       </c>
       <c r="AD5" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>59</v>
       </c>
       <c r="AE5" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -3157,7 +3124,7 @@
     </row>
     <row r="6" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>34</v>
@@ -3171,16 +3138,24 @@
         <v>35</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="9"/>
+      <c r="J6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="N6" s="12"/>
       <c r="O6" s="9"/>
       <c r="P6" s="11"/>
@@ -3189,7 +3164,7 @@
       <c r="S6" s="10"/>
       <c r="T6" s="9"/>
       <c r="U6" s="16" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -3208,15 +3183,15 @@
       </c>
       <c r="AB6" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>35.4</v>
       </c>
       <c r="AC6" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>34.3</v>
       </c>
       <c r="AD6" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>41.4</v>
       </c>
       <c r="AE6" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -3231,28 +3206,28 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>65</v>
+    <row r="7" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="9" t="n">
@@ -3262,16 +3237,24 @@
         <v>35</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N7" s="12"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="9"/>
+      <c r="O7" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="S7" s="10"/>
       <c r="T7" s="9"/>
       <c r="U7" s="16"/>
@@ -3304,20 +3287,20 @@
       </c>
       <c r="AE7" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>64.8</v>
       </c>
       <c r="AF7" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>63.7</v>
       </c>
       <c r="AG7" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>34</v>
@@ -3331,23 +3314,23 @@
         <v>35</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="9" t="n">
         <v>5</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="9"/>
@@ -3399,7 +3382,7 @@
     </row>
     <row r="9" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>34</v>
@@ -3413,10 +3396,10 @@
         <v>35</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="9" t="n">
@@ -3426,10 +3409,10 @@
         <v>35</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="9" t="n">
@@ -3439,10 +3422,10 @@
         <v>35</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="S9" s="10"/>
       <c r="T9" s="9"/>
@@ -3489,7 +3472,7 @@
     </row>
     <row r="10" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>34</v>
@@ -3503,10 +3486,10 @@
         <v>35</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="9" t="n">
@@ -3516,10 +3499,10 @@
         <v>35</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="9"/>
@@ -3569,15 +3552,15 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>66</v>
+      <c r="C11" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="9" t="n">
@@ -3587,29 +3570,37 @@
         <v>35</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="N11" s="12"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="9"/>
+      <c r="O11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>103</v>
+      </c>
       <c r="S11" s="10"/>
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
@@ -3630,39 +3621,37 @@
       </c>
       <c r="AB11" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>35.4</v>
       </c>
       <c r="AC11" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="AD11" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>41.4</v>
       </c>
       <c r="AE11" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>47.2</v>
       </c>
       <c r="AF11" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>46.1</v>
       </c>
       <c r="AG11" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="C12" s="9"/>
       <c r="D12" s="10"/>
       <c r="E12" s="9" t="n">
         <v>1</v>
@@ -3671,37 +3660,29 @@
         <v>35</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="N12" s="12"/>
-      <c r="O12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>100</v>
-      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="9"/>
       <c r="S12" s="10"/>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
@@ -3722,32 +3703,32 @@
       </c>
       <c r="AB12" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>44.2</v>
       </c>
       <c r="AC12" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="AD12" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>50.2</v>
       </c>
       <c r="AE12" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>47.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF12" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>46.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG12" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>34</v>
@@ -3761,29 +3742,37 @@
         <v>35</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N13" s="12"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="9"/>
+      <c r="O13" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="S13" s="10"/>
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
@@ -3804,75 +3793,77 @@
       </c>
       <c r="AB13" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC13" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD13" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE13" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>60.4</v>
       </c>
       <c r="AF13" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>59.3</v>
       </c>
       <c r="AG13" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>66.4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="D14" s="10"/>
       <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="S14" s="10"/>
       <c r="T14" s="9"/>
@@ -3906,66 +3897,50 @@
       </c>
       <c r="AE14" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="AF14" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>59.3</v>
+        <v>54.9</v>
       </c>
       <c r="AG14" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>66.4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>114</v>
-      </c>
+      <c r="C15" s="9"/>
       <c r="D15" s="10"/>
       <c r="E15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>118</v>
-      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="9"/>
       <c r="N15" s="12"/>
-      <c r="O15" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="9"/>
       <c r="S15" s="10"/>
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
@@ -3998,25 +3973,27 @@
       </c>
       <c r="AE15" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>56</v>
+        <v>25.2</v>
       </c>
       <c r="AF15" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>54.9</v>
+        <v>24.1</v>
       </c>
       <c r="AG15" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="D16" s="10"/>
       <c r="E16" s="9" t="n">
         <v>1</v>
@@ -4025,23 +4002,37 @@
         <v>35</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="N16" s="12"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="9"/>
+      <c r="O16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>134</v>
+      </c>
       <c r="S16" s="10"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
@@ -4062,77 +4053,75 @@
       </c>
       <c r="AB16" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>35.4</v>
       </c>
       <c r="AC16" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="AD16" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>41.4</v>
       </c>
       <c r="AE16" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>64.8</v>
       </c>
       <c r="AF16" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>63.7</v>
       </c>
       <c r="AG16" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>125</v>
-      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="10"/>
       <c r="E17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P17" s="11" t="s">
         <v>35</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="S17" s="10"/>
       <c r="T17" s="9"/>
@@ -4166,20 +4155,20 @@
       </c>
       <c r="AE17" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>64.8</v>
+        <v>51.6</v>
       </c>
       <c r="AF17" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>63.7</v>
+        <v>50.5</v>
       </c>
       <c r="AG17" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>34</v>
@@ -4190,40 +4179,32 @@
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="N18" s="12"/>
-      <c r="O18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>138</v>
-      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="9"/>
       <c r="S18" s="10"/>
       <c r="T18" s="9"/>
       <c r="U18" s="9"/>
@@ -4244,32 +4225,32 @@
       </c>
       <c r="AB18" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>53</v>
       </c>
       <c r="AC18" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>51.9</v>
       </c>
       <c r="AD18" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>59</v>
       </c>
       <c r="AE18" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>51.6</v>
+        <v>25.2</v>
       </c>
       <c r="AF18" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>50.5</v>
+        <v>24.1</v>
       </c>
       <c r="AG18" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>57.6</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>34</v>
@@ -4283,23 +4264,23 @@
         <v>35</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="9"/>
@@ -4326,15 +4307,15 @@
       </c>
       <c r="AB19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>53</v>
+        <v>44.2</v>
       </c>
       <c r="AC19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>51.9</v>
+        <v>43.1</v>
       </c>
       <c r="AD19" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>59</v>
+        <v>50.2</v>
       </c>
       <c r="AE19" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -4349,39 +4330,41 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>35</v>
+      <c r="F20" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>35</v>
+        <v>10.5</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="9"/>
@@ -4408,15 +4391,15 @@
       </c>
       <c r="AB20" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>68.4</v>
       </c>
       <c r="AC20" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>67.3</v>
       </c>
       <c r="AD20" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>74.4</v>
       </c>
       <c r="AE20" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -4431,47 +4414,53 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="C21" s="9"/>
       <c r="D21" s="10"/>
       <c r="E21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>50</v>
+      <c r="F21" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>50</v>
+        <v>3</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="N21" s="12"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="9"/>
+      <c r="O21" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>163</v>
+      </c>
       <c r="S21" s="10"/>
       <c r="T21" s="9"/>
       <c r="U21" s="9"/>
@@ -4492,37 +4481,39 @@
       </c>
       <c r="AB21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>68.4</v>
+        <v>35.4</v>
       </c>
       <c r="AC21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>67.3</v>
+        <v>34.3</v>
       </c>
       <c r="AD21" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>74.4</v>
+        <v>41.4</v>
       </c>
       <c r="AE21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>51.6</v>
       </c>
       <c r="AF21" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>50.5</v>
       </c>
       <c r="AG21" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D22" s="10"/>
       <c r="E22" s="9" t="n">
         <v>1</v>
@@ -4531,36 +4522,36 @@
         <v>35</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>35</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="9"/>
@@ -4582,53 +4573,51 @@
       </c>
       <c r="AB22" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>39.8</v>
       </c>
       <c r="AC22" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="AD22" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AE22" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>51.6</v>
+        <v>56</v>
       </c>
       <c r="AF22" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>50.5</v>
+        <v>54.9</v>
       </c>
       <c r="AG22" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>57.6</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="10"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="18"/>
       <c r="E23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="10"/>
+      <c r="G23" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23" s="18"/>
       <c r="J23" s="9" t="n">
         <v>4</v>
       </c>
@@ -4636,30 +4625,32 @@
         <v>35</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="S23" s="10"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
+        <v>174</v>
+      </c>
+      <c r="N23" s="19"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X23" s="9" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="Y23" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E1Y]]+X$2</f>
         <v>23.6</v>
@@ -4686,72 +4677,62 @@
       </c>
       <c r="AE23" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>56</v>
+        <v>25.2</v>
       </c>
       <c r="AF23" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>54.9</v>
+        <v>24.1</v>
       </c>
       <c r="AG23" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C24" s="9"/>
-      <c r="D24" s="18"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="18"/>
+      <c r="G24" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="10"/>
       <c r="J24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K24" s="11" t="s">
-        <v>35</v>
+      <c r="K24" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+        <v>178</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U24" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="X24" s="9" t="n">
-        <v>-0.6</v>
-      </c>
+      <c r="S24" s="10"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
       <c r="Y24" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E1Y]]+X$2</f>
         <v>23.6</v>
@@ -4789,45 +4770,55 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>181</v>
+      </c>
       <c r="D25" s="10"/>
       <c r="E25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>35</v>
+      <c r="F25" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>50</v>
+        <v>5</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>177</v>
+        <v>184</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="N25" s="12"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
+      <c r="O25" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="R25" s="9" t="s">
+        <v>187</v>
+      </c>
       <c r="S25" s="10"/>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
@@ -4848,51 +4839,49 @@
       </c>
       <c r="AB25" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>44.2</v>
       </c>
       <c r="AC25" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>43.1</v>
       </c>
       <c r="AD25" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>50.2</v>
       </c>
       <c r="AE25" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>64.8</v>
       </c>
       <c r="AF25" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>63.7</v>
       </c>
       <c r="AG25" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>179</v>
-      </c>
+      <c r="C26" s="9"/>
       <c r="D26" s="10"/>
       <c r="E26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>50</v>
+      <c r="F26" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="9" t="n">
@@ -4902,23 +4891,23 @@
         <v>35</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="R26" s="9" t="s">
-        <v>185</v>
+        <v>193</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="S26" s="10"/>
       <c r="T26" s="9"/>
@@ -4952,20 +4941,20 @@
       </c>
       <c r="AE26" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>64.8</v>
+        <v>60.4</v>
       </c>
       <c r="AF26" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>63.7</v>
+        <v>59.3</v>
       </c>
       <c r="AG26" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66.4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>34</v>
@@ -4979,37 +4968,29 @@
         <v>35</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="K27" s="11" t="s">
-        <v>35</v>
+      <c r="K27" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="N27" s="12"/>
-      <c r="O27" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="P27" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q27" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="R27" s="13" t="s">
-        <v>192</v>
-      </c>
+      <c r="O27" s="9"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="9"/>
       <c r="S27" s="10"/>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
@@ -5042,55 +5023,47 @@
       </c>
       <c r="AE27" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>60.4</v>
+        <v>25.2</v>
       </c>
       <c r="AF27" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>59.3</v>
+        <v>24.1</v>
       </c>
       <c r="AG27" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>66.4</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>200</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>201</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>35</v>
+      <c r="F28" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I28" s="10"/>
-      <c r="J28" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>197</v>
-      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
       <c r="N28" s="12"/>
       <c r="O28" s="9"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="10"/>
       <c r="T28" s="9"/>
@@ -5112,15 +5085,15 @@
       </c>
       <c r="AB28" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC28" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD28" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE28" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -5135,32 +5108,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C29" s="9"/>
+        <v>201</v>
+      </c>
+      <c r="C29" s="11"/>
       <c r="D29" s="10"/>
       <c r="E29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>50</v>
+      <c r="F29" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I29" s="10"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
+      <c r="J29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>208</v>
+      </c>
       <c r="N29" s="12"/>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
@@ -5186,15 +5167,15 @@
       </c>
       <c r="AB29" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC29" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD29" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE29" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -5211,44 +5192,36 @@
     </row>
     <row r="30" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="10"/>
+        <v>201</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="18"/>
       <c r="E30" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="N30" s="12"/>
+      <c r="G30" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I30" s="18"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="19"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
-      <c r="S30" s="10"/>
+      <c r="S30" s="18"/>
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
       <c r="V30" s="9"/>
@@ -5268,15 +5241,15 @@
       </c>
       <c r="AB30" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC30" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD30" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE30" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -5291,12 +5264,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="18"/>
@@ -5307,10 +5280,10 @@
         <v>35</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="9"/>
@@ -5365,12 +5338,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="18"/>
@@ -5381,10 +5354,10 @@
         <v>35</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I32" s="18"/>
       <c r="J32" s="9"/>
@@ -5441,10 +5414,10 @@
     </row>
     <row r="33" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="18"/>
@@ -5455,10 +5428,10 @@
         <v>35</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I33" s="18"/>
       <c r="J33" s="9"/>
@@ -5515,36 +5488,36 @@
     </row>
     <row r="34" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C34" s="9"/>
-      <c r="D34" s="18"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="I34" s="18"/>
+        <v>220</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I34" s="10"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="19"/>
+      <c r="N34" s="12"/>
       <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
       <c r="R34" s="9"/>
-      <c r="S34" s="18"/>
+      <c r="S34" s="10"/>
       <c r="T34" s="9"/>
       <c r="U34" s="9"/>
       <c r="V34" s="9"/>
@@ -5587,12 +5560,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="10"/>
@@ -5600,13 +5573,13 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="9"/>
@@ -5661,12 +5634,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -5677,16 +5650,24 @@
         <v>35</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I36" s="10"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="N36" s="12"/>
       <c r="O36" s="9"/>
       <c r="P36" s="11"/>
@@ -5712,15 +5693,15 @@
       </c>
       <c r="AB36" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC36" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD36" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE36" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -5735,12 +5716,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
@@ -5751,24 +5732,16 @@
         <v>35</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I37" s="10"/>
-      <c r="J37" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>227</v>
-      </c>
+      <c r="J37" s="9"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="9"/>
       <c r="N37" s="12"/>
       <c r="O37" s="9"/>
       <c r="P37" s="11"/>
@@ -5794,15 +5767,15 @@
       </c>
       <c r="AB37" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC37" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD37" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE37" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -5819,10 +5792,10 @@
     </row>
     <row r="38" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
@@ -5833,10 +5806,10 @@
         <v>35</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="9"/>
@@ -5893,24 +5866,26 @@
     </row>
     <row r="39" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C39" s="9"/>
+        <v>201</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="D39" s="10"/>
       <c r="E39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>35</v>
+      <c r="F39" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9"/>
@@ -5965,34 +5940,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>233</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="C40" s="9"/>
       <c r="D40" s="10"/>
       <c r="E40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I40" s="10"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="9"/>
+      <c r="J40" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="N40" s="12"/>
       <c r="O40" s="9"/>
       <c r="P40" s="11"/>
@@ -6018,15 +5999,15 @@
       </c>
       <c r="AB40" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>54.76</v>
       </c>
       <c r="AC40" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>53.66</v>
       </c>
       <c r="AD40" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>60.76</v>
       </c>
       <c r="AE40" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6041,40 +6022,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
       <c r="E41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>50</v>
+      <c r="F41" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="I41" s="10"/>
-      <c r="J41" s="9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>240</v>
-      </c>
+      <c r="J41" s="9"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="9"/>
       <c r="N41" s="12"/>
       <c r="O41" s="9"/>
       <c r="P41" s="11"/>
@@ -6100,15 +6073,15 @@
       </c>
       <c r="AB41" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>54.76</v>
+        <v>22.2</v>
       </c>
       <c r="AC41" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>53.66</v>
+        <v>21.1</v>
       </c>
       <c r="AD41" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>60.76</v>
+        <v>28.2</v>
       </c>
       <c r="AE41" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6123,12 +6096,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
@@ -6139,10 +6112,10 @@
         <v>35</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="9"/>
@@ -6197,12 +6170,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -6213,21 +6186,37 @@
         <v>35</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I43" s="10"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>251</v>
+      </c>
       <c r="N43" s="12"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="9"/>
+      <c r="O43" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q43" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="R43" s="9" t="s">
+        <v>253</v>
+      </c>
       <c r="S43" s="10"/>
       <c r="T43" s="9"/>
       <c r="U43" s="9"/>
@@ -6248,76 +6237,68 @@
       </c>
       <c r="AB43" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC43" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD43" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE43" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>56</v>
       </c>
       <c r="AF43" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>54.9</v>
       </c>
       <c r="AG43" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="10"/>
       <c r="E44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>35</v>
+      <c r="F44" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>249</v>
+        <v>257</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>258</v>
       </c>
       <c r="N44" s="12"/>
-      <c r="O44" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P44" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q44" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="R44" s="9" t="s">
-        <v>251</v>
-      </c>
+      <c r="O44" s="9"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="9"/>
       <c r="S44" s="10"/>
       <c r="T44" s="9"/>
       <c r="U44" s="9"/>
@@ -6338,63 +6319,57 @@
       </c>
       <c r="AB44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>53</v>
       </c>
       <c r="AC44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>51.9</v>
       </c>
       <c r="AD44" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>59</v>
       </c>
       <c r="AE44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>56</v>
+        <v>25.2</v>
       </c>
       <c r="AF44" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>54.9</v>
+        <v>24.1</v>
       </c>
       <c r="AG44" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C45" s="9"/>
+        <v>201</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>260</v>
+      </c>
       <c r="D45" s="10"/>
       <c r="E45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>50</v>
+      <c r="F45" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="I45" s="10"/>
-      <c r="J45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>256</v>
-      </c>
+      <c r="J45" s="9"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="9"/>
       <c r="N45" s="12"/>
       <c r="O45" s="9"/>
       <c r="P45" s="11"/>
@@ -6420,15 +6395,15 @@
       </c>
       <c r="AB45" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>53</v>
+        <v>22.2</v>
       </c>
       <c r="AC45" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>51.9</v>
+        <v>21.1</v>
       </c>
       <c r="AD45" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>59</v>
+        <v>28.2</v>
       </c>
       <c r="AE45" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6443,34 +6418,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>258</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="C46" s="9"/>
       <c r="D46" s="10"/>
       <c r="E46" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I46" s="10"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="9"/>
+      <c r="J46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="N46" s="12"/>
       <c r="O46" s="9"/>
       <c r="P46" s="11"/>
@@ -6496,15 +6477,15 @@
       </c>
       <c r="AB46" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC46" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD46" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE46" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6519,12 +6500,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="10"/>
@@ -6535,24 +6516,16 @@
         <v>35</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I47" s="10"/>
-      <c r="J47" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>265</v>
-      </c>
+      <c r="J47" s="9"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="9"/>
       <c r="N47" s="12"/>
       <c r="O47" s="9"/>
       <c r="P47" s="11"/>
@@ -6578,15 +6551,15 @@
       </c>
       <c r="AB47" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC47" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD47" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE47" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6603,10 +6576,10 @@
     </row>
     <row r="48" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="10"/>
@@ -6617,16 +6590,24 @@
         <v>35</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I48" s="10"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="9"/>
+      <c r="J48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>274</v>
+      </c>
       <c r="N48" s="12"/>
       <c r="O48" s="9"/>
       <c r="P48" s="11"/>
@@ -6652,15 +6633,15 @@
       </c>
       <c r="AB48" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC48" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD48" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE48" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6675,40 +6656,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="10"/>
       <c r="E49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="11" t="s">
-        <v>35</v>
+      <c r="F49" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="I49" s="10"/>
-      <c r="J49" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L49" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="M49" s="9" t="s">
-        <v>272</v>
-      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="9"/>
       <c r="N49" s="12"/>
       <c r="O49" s="9"/>
       <c r="P49" s="11"/>
@@ -6734,15 +6707,15 @@
       </c>
       <c r="AB49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD49" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE49" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6757,32 +6730,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="10"/>
       <c r="E50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>50</v>
+      <c r="F50" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I50" s="10"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="9"/>
+      <c r="J50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>282</v>
+      </c>
       <c r="N50" s="12"/>
       <c r="O50" s="9"/>
       <c r="P50" s="11"/>
@@ -6808,15 +6789,15 @@
       </c>
       <c r="AB50" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC50" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD50" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE50" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6831,40 +6812,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="10"/>
       <c r="E51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>35</v>
+      <c r="F51" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="I51" s="10"/>
-      <c r="J51" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>280</v>
-      </c>
+      <c r="J51" s="9"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="9"/>
       <c r="N51" s="12"/>
       <c r="O51" s="9"/>
       <c r="P51" s="11"/>
@@ -6890,15 +6863,15 @@
       </c>
       <c r="AB51" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC51" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD51" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE51" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -6913,12 +6886,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="10"/>
@@ -6926,13 +6899,13 @@
         <v>1</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="9"/>
@@ -6987,12 +6960,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="10"/>
@@ -7000,13 +6973,13 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9"/>
@@ -7061,12 +7034,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="10"/>
@@ -7074,19 +7047,27 @@
         <v>1</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I54" s="10"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="9"/>
+      <c r="J54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>296</v>
+      </c>
       <c r="N54" s="12"/>
       <c r="O54" s="9"/>
       <c r="P54" s="11"/>
@@ -7112,15 +7093,15 @@
       </c>
       <c r="AB54" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC54" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD54" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE54" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7137,38 +7118,30 @@
     </row>
     <row r="55" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="10"/>
       <c r="E55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>50</v>
+      <c r="F55" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>291</v>
+        <v>213</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I55" s="10"/>
-      <c r="J55" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J55" s="9"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="9"/>
       <c r="N55" s="12"/>
       <c r="O55" s="9"/>
       <c r="P55" s="11"/>
@@ -7194,15 +7167,15 @@
       </c>
       <c r="AB55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD55" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE55" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7217,12 +7190,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="10"/>
@@ -7233,16 +7206,24 @@
         <v>35</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>211</v>
+        <v>300</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I56" s="10"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="9"/>
+      <c r="J56" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="N56" s="12"/>
       <c r="O56" s="9"/>
       <c r="P56" s="11"/>
@@ -7268,15 +7249,15 @@
       </c>
       <c r="AB56" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC56" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD56" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE56" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7291,39 +7272,39 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="10"/>
       <c r="E57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>35</v>
+      <c r="F57" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>50</v>
+        <v>4</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="N57" s="12"/>
       <c r="O57" s="9"/>
@@ -7350,15 +7331,15 @@
       </c>
       <c r="AB57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD57" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE57" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7375,37 +7356,37 @@
     </row>
     <row r="58" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="10"/>
       <c r="E58" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>50</v>
+      <c r="F58" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="N58" s="12"/>
       <c r="O58" s="9"/>
@@ -7432,15 +7413,15 @@
       </c>
       <c r="AB58" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>44.2</v>
       </c>
       <c r="AC58" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>43.1</v>
       </c>
       <c r="AD58" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>50.2</v>
       </c>
       <c r="AE58" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7457,10 +7438,10 @@
     </row>
     <row r="59" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="10"/>
@@ -7471,24 +7452,16 @@
         <v>35</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>308</v>
+        <v>213</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="I59" s="10"/>
-      <c r="J59" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>311</v>
-      </c>
+      <c r="J59" s="9"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="9"/>
       <c r="N59" s="12"/>
       <c r="O59" s="9"/>
       <c r="P59" s="11"/>
@@ -7514,15 +7487,15 @@
       </c>
       <c r="AB59" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC59" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD59" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE59" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7537,32 +7510,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="10"/>
       <c r="E60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="I60" s="10"/>
+      <c r="J60" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I60" s="10"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="9"/>
+      <c r="L60" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>320</v>
+      </c>
       <c r="N60" s="12"/>
       <c r="O60" s="9"/>
       <c r="P60" s="11"/>
@@ -7588,15 +7569,15 @@
       </c>
       <c r="AB60" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>57.4</v>
       </c>
       <c r="AC60" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>56.3</v>
       </c>
       <c r="AD60" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>63.4</v>
       </c>
       <c r="AE60" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7611,40 +7592,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="10"/>
       <c r="E61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>50</v>
+      <c r="F61" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I61" s="10"/>
-      <c r="J61" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>318</v>
-      </c>
+      <c r="J61" s="9"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="9"/>
       <c r="N61" s="12"/>
       <c r="O61" s="9"/>
       <c r="P61" s="11"/>
@@ -7670,15 +7643,15 @@
       </c>
       <c r="AB61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>57.4</v>
+        <v>22.2</v>
       </c>
       <c r="AC61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>56.3</v>
+        <v>21.1</v>
       </c>
       <c r="AD61" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>63.4</v>
+        <v>28.2</v>
       </c>
       <c r="AE61" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7693,12 +7666,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
@@ -7706,13 +7679,13 @@
         <v>1</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="9"/>
@@ -7769,10 +7742,10 @@
     </row>
     <row r="63" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
@@ -7780,13 +7753,13 @@
         <v>1</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9"/>
@@ -7841,32 +7814,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="10"/>
       <c r="E64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="11" t="s">
-        <v>218</v>
+      <c r="F64" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I64" s="10"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>333</v>
+      </c>
       <c r="N64" s="12"/>
       <c r="O64" s="9"/>
       <c r="P64" s="11"/>
@@ -7892,15 +7873,15 @@
       </c>
       <c r="AB64" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC64" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD64" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE64" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7915,40 +7896,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="10"/>
       <c r="E65" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>50</v>
+      <c r="F65" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>328</v>
+        <v>213</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I65" s="10"/>
-      <c r="J65" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K65" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L65" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>331</v>
-      </c>
+      <c r="J65" s="9"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="9"/>
       <c r="N65" s="12"/>
       <c r="O65" s="9"/>
       <c r="P65" s="11"/>
@@ -7974,15 +7947,15 @@
       </c>
       <c r="AB65" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC65" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD65" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE65" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -7997,36 +7970,44 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="10"/>
       <c r="E66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I66" s="10"/>
+      <c r="J66" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G66" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="9"/>
+      <c r="L66" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>340</v>
+      </c>
       <c r="N66" s="12"/>
       <c r="O66" s="9"/>
-      <c r="P66" s="11"/>
-      <c r="Q66" s="11"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
       <c r="R66" s="9"/>
       <c r="S66" s="10"/>
       <c r="T66" s="9"/>
@@ -8048,15 +8029,15 @@
       </c>
       <c r="AB66" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>48.6</v>
       </c>
       <c r="AC66" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>47.5</v>
       </c>
       <c r="AD66" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>54.6</v>
       </c>
       <c r="AE66" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8071,44 +8052,36 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="10"/>
       <c r="E67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>218</v>
+      <c r="F67" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="I67" s="10"/>
-      <c r="J67" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>338</v>
-      </c>
+      <c r="J67" s="9"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="9"/>
       <c r="N67" s="12"/>
       <c r="O67" s="9"/>
-      <c r="P67" s="9"/>
-      <c r="Q67" s="9"/>
+      <c r="P67" s="11"/>
+      <c r="Q67" s="11"/>
       <c r="R67" s="9"/>
       <c r="S67" s="10"/>
       <c r="T67" s="9"/>
@@ -8130,15 +8103,15 @@
       </c>
       <c r="AB67" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>22.2</v>
       </c>
       <c r="AC67" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>21.1</v>
       </c>
       <c r="AD67" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>28.2</v>
       </c>
       <c r="AE67" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8155,10 +8128,10 @@
     </row>
     <row r="68" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="10"/>
@@ -8166,19 +8139,27 @@
         <v>1</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I68" s="10"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>348</v>
+      </c>
       <c r="N68" s="12"/>
       <c r="O68" s="9"/>
       <c r="P68" s="11"/>
@@ -8204,15 +8185,15 @@
       </c>
       <c r="AB68" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC68" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD68" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE68" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8227,40 +8208,32 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="10"/>
       <c r="E69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="11" t="s">
-        <v>218</v>
+      <c r="F69" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I69" s="10"/>
-      <c r="J69" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K69" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L69" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>346</v>
-      </c>
+      <c r="J69" s="9"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="9"/>
       <c r="N69" s="12"/>
       <c r="O69" s="9"/>
       <c r="P69" s="11"/>
@@ -8286,15 +8259,15 @@
       </c>
       <c r="AB69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD69" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE69" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8309,38 +8282,54 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>199</v>
+        <v>352</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>353</v>
       </c>
       <c r="C70" s="9"/>
-      <c r="D70" s="10"/>
+      <c r="D70" s="18"/>
       <c r="E70" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="H70" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="I70" s="10"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="9"/>
-      <c r="N70" s="12"/>
-      <c r="O70" s="9"/>
-      <c r="P70" s="11"/>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="9"/>
-      <c r="S70" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I70" s="18"/>
+      <c r="J70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="N70" s="19"/>
+      <c r="O70" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P70" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q70" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R70" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="S70" s="18"/>
       <c r="T70" s="9"/>
       <c r="U70" s="9"/>
       <c r="V70" s="9"/>
@@ -8360,35 +8349,35 @@
       </c>
       <c r="AB70" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC70" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD70" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE70" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>67</v>
       </c>
       <c r="AF70" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>65.9</v>
       </c>
       <c r="AG70" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="18"/>
@@ -8396,40 +8385,34 @@
         <v>1</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="I71" s="18"/>
       <c r="J71" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>67</v>
+        <v>358</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="N71" s="19"/>
       <c r="O71" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q71" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R71" s="9" t="s">
-        <v>358</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
       <c r="S71" s="18"/>
       <c r="T71" s="9"/>
       <c r="U71" s="9"/>
@@ -8450,71 +8433,69 @@
       </c>
       <c r="AB71" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>61.8</v>
       </c>
       <c r="AC71" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>60.7</v>
       </c>
       <c r="AD71" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>67.8</v>
       </c>
       <c r="AE71" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>67</v>
+        <v>47.2</v>
       </c>
       <c r="AF71" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>65.9</v>
+        <v>46.1</v>
       </c>
       <c r="AG71" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C72" s="9"/>
-      <c r="D72" s="18"/>
+      <c r="D72" s="10"/>
       <c r="E72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="I72" s="18"/>
+      <c r="F72" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I72" s="10"/>
       <c r="J72" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>356</v>
+        <v>38</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="N72" s="19"/>
-      <c r="O72" s="9" t="n">
-        <v>5</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N72" s="12"/>
+      <c r="O72" s="9"/>
       <c r="P72" s="9"/>
       <c r="Q72" s="9"/>
       <c r="R72" s="9"/>
-      <c r="S72" s="18"/>
+      <c r="S72" s="10"/>
       <c r="T72" s="9"/>
       <c r="U72" s="9"/>
       <c r="V72" s="9"/>
@@ -8534,69 +8515,71 @@
       </c>
       <c r="AB72" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>48.6</v>
       </c>
       <c r="AC72" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>47.5</v>
       </c>
       <c r="AD72" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>54.6</v>
       </c>
       <c r="AE72" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>47.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF72" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>46.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG72" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C73" s="9"/>
-      <c r="D73" s="10"/>
+      <c r="D73" s="18"/>
       <c r="E73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="H73" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I73" s="10"/>
+      <c r="F73" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="I73" s="18"/>
       <c r="J73" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="N73" s="12"/>
-      <c r="O73" s="9"/>
+        <v>374</v>
+      </c>
+      <c r="N73" s="19"/>
+      <c r="O73" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P73" s="9"/>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
-      <c r="S73" s="10"/>
+      <c r="S73" s="18"/>
       <c r="T73" s="9"/>
       <c r="U73" s="9"/>
       <c r="V73" s="9"/>
@@ -8616,71 +8599,69 @@
       </c>
       <c r="AB73" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>44.2</v>
       </c>
       <c r="AC73" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>43.1</v>
       </c>
       <c r="AD73" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="AE73" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>47.2</v>
       </c>
       <c r="AF73" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>46.1</v>
       </c>
       <c r="AG73" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C74" s="9"/>
-      <c r="D74" s="18"/>
+      <c r="D74" s="10"/>
       <c r="E74" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="I74" s="18"/>
+      <c r="F74" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="I74" s="10"/>
       <c r="J74" s="9" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="N74" s="19"/>
-      <c r="O74" s="9" t="n">
-        <v>5</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N74" s="12"/>
+      <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="9"/>
       <c r="R74" s="9"/>
-      <c r="S74" s="18"/>
+      <c r="S74" s="10"/>
       <c r="T74" s="9"/>
       <c r="U74" s="9"/>
       <c r="V74" s="9"/>
@@ -8712,23 +8693,23 @@
       </c>
       <c r="AE74" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>47.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF74" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>46.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG74" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="10"/>
@@ -8736,26 +8717,26 @@
         <v>1</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K75" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K75" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L75" s="9" t="s">
-        <v>376</v>
+      <c r="L75" s="11" t="s">
+        <v>383</v>
       </c>
       <c r="M75" s="9" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="N75" s="12"/>
       <c r="O75" s="9"/>
@@ -8782,15 +8763,15 @@
       </c>
       <c r="AB75" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>35.4</v>
       </c>
       <c r="AC75" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="AD75" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>41.4</v>
       </c>
       <c r="AE75" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8807,10 +8788,10 @@
     </row>
     <row r="76" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="10"/>
@@ -8818,26 +8799,26 @@
         <v>1</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K76" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L76" s="11" t="s">
-        <v>381</v>
+        <v>9</v>
+      </c>
+      <c r="K76" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>359</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="N76" s="12"/>
       <c r="O76" s="9"/>
@@ -8864,15 +8845,15 @@
       </c>
       <c r="AB76" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>61.8</v>
       </c>
       <c r="AC76" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>60.7</v>
       </c>
       <c r="AD76" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>67.8</v>
       </c>
       <c r="AE76" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8889,10 +8870,10 @@
     </row>
     <row r="77" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="10"/>
@@ -8900,26 +8881,26 @@
         <v>1</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>356</v>
+        <v>35</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="N77" s="12"/>
       <c r="O77" s="9"/>
@@ -8946,15 +8927,15 @@
       </c>
       <c r="AB77" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>39.8</v>
       </c>
       <c r="AC77" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>38.7</v>
       </c>
       <c r="AD77" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>45.8</v>
       </c>
       <c r="AE77" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -8969,12 +8950,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="10"/>
@@ -8982,26 +8963,26 @@
         <v>1</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="I78" s="10"/>
-      <c r="J78" s="9" t="n">
-        <v>4</v>
+      <c r="J78" s="11" t="n">
+        <v>5</v>
       </c>
       <c r="K78" s="9" t="s">
         <v>35</v>
       </c>
       <c r="L78" s="9" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="M78" s="9" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="N78" s="12"/>
       <c r="O78" s="9"/>
@@ -9028,15 +9009,15 @@
       </c>
       <c r="AB78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>44.2</v>
       </c>
       <c r="AC78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>43.1</v>
       </c>
       <c r="AD78" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>50.2</v>
       </c>
       <c r="AE78" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9051,12 +9032,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="10"/>
@@ -9064,26 +9045,26 @@
         <v>1</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="I79" s="10"/>
-      <c r="J79" s="11" t="n">
-        <v>5</v>
+      <c r="J79" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="N79" s="12"/>
       <c r="O79" s="9"/>
@@ -9110,15 +9091,15 @@
       </c>
       <c r="AB79" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>35.4</v>
       </c>
       <c r="AC79" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="AD79" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>41.4</v>
       </c>
       <c r="AE79" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9135,10 +9116,10 @@
     </row>
     <row r="80" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="10"/>
@@ -9146,32 +9127,40 @@
         <v>1</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="I80" s="10"/>
-      <c r="J80" s="9" t="n">
+      <c r="J80" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K80" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M80" s="9" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N80" s="12"/>
-      <c r="O80" s="9"/>
-      <c r="P80" s="9"/>
-      <c r="Q80" s="9"/>
-      <c r="R80" s="9"/>
+      <c r="O80" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P80" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q80" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R80" s="9" t="s">
+        <v>408</v>
+      </c>
       <c r="S80" s="10"/>
       <c r="T80" s="9"/>
       <c r="U80" s="9"/>
@@ -9204,23 +9193,23 @@
       </c>
       <c r="AE80" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>67</v>
       </c>
       <c r="AF80" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>65.9</v>
       </c>
       <c r="AG80" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="10"/>
@@ -9228,39 +9217,39 @@
         <v>1</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="I81" s="10"/>
-      <c r="J81" s="11" t="n">
+      <c r="J81" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N81" s="12"/>
       <c r="O81" s="9" t="n">
         <v>9.5</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="R81" s="9" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="S81" s="10"/>
       <c r="T81" s="9"/>
@@ -9307,10 +9296,10 @@
     </row>
     <row r="82" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="10"/>
@@ -9318,40 +9307,32 @@
         <v>1</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K82" s="9" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L82" s="9" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N82" s="12"/>
-      <c r="O82" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P82" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q82" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R82" s="9" t="s">
-        <v>411</v>
-      </c>
+      <c r="O82" s="9"/>
+      <c r="P82" s="9"/>
+      <c r="Q82" s="9"/>
+      <c r="R82" s="9"/>
       <c r="S82" s="10"/>
       <c r="T82" s="9"/>
       <c r="U82" s="9"/>
@@ -9372,35 +9353,35 @@
       </c>
       <c r="AB82" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>44.2</v>
       </c>
       <c r="AC82" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="AD82" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>50.2</v>
       </c>
       <c r="AE82" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>67</v>
+        <v>25.2</v>
       </c>
       <c r="AF82" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>65.9</v>
+        <v>24.1</v>
       </c>
       <c r="AG82" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>73</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="10"/>
@@ -9408,27 +9389,19 @@
         <v>1</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="I83" s="10"/>
-      <c r="J83" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K83" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>416</v>
-      </c>
+      <c r="J83" s="9"/>
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
       <c r="N83" s="12"/>
       <c r="O83" s="9"/>
       <c r="P83" s="9"/>
@@ -9454,15 +9427,15 @@
       </c>
       <c r="AB83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD83" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE83" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9477,32 +9450,42 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C84" s="9"/>
+        <v>353</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>260</v>
+      </c>
       <c r="D84" s="10"/>
       <c r="E84" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I84" s="10"/>
-      <c r="J84" s="9"/>
-      <c r="K84" s="9"/>
-      <c r="L84" s="9"/>
-      <c r="M84" s="9"/>
+      <c r="J84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="M84" s="9" t="s">
+        <v>426</v>
+      </c>
       <c r="N84" s="12"/>
       <c r="O84" s="9"/>
       <c r="P84" s="9"/>
@@ -9528,15 +9511,15 @@
       </c>
       <c r="AB84" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC84" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD84" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE84" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9551,41 +9534,39 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>258</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C85" s="9"/>
       <c r="D85" s="10"/>
       <c r="E85" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I85" s="10"/>
-      <c r="J85" s="9" t="n">
-        <v>4</v>
+      <c r="J85" s="11" t="n">
+        <v>9.5</v>
       </c>
       <c r="K85" s="9" t="s">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>423</v>
+        <v>359</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N85" s="12"/>
       <c r="O85" s="9"/>
@@ -9612,15 +9593,15 @@
       </c>
       <c r="AB85" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>64</v>
       </c>
       <c r="AC85" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>62.9</v>
       </c>
       <c r="AD85" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>70</v>
       </c>
       <c r="AE85" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9635,12 +9616,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="10"/>
@@ -9648,32 +9629,40 @@
         <v>1</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="I86" s="10"/>
-      <c r="J86" s="11" t="n">
+      <c r="J86" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L86" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="M86" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="N86" s="12"/>
+      <c r="O86" s="11" t="n">
         <v>9.5</v>
       </c>
-      <c r="K86" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="L86" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="M86" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="N86" s="12"/>
-      <c r="O86" s="9"/>
-      <c r="P86" s="9"/>
-      <c r="Q86" s="9"/>
-      <c r="R86" s="9"/>
+      <c r="P86" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q86" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R86" s="9" t="s">
+        <v>429</v>
+      </c>
       <c r="S86" s="10"/>
       <c r="T86" s="9"/>
       <c r="U86" s="9"/>
@@ -9694,76 +9683,60 @@
       </c>
       <c r="AB86" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>64</v>
+        <v>35.4</v>
       </c>
       <c r="AC86" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>62.9</v>
+        <v>34.3</v>
       </c>
       <c r="AD86" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>70</v>
+        <v>41.4</v>
       </c>
       <c r="AE86" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>67</v>
       </c>
       <c r="AF86" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>65.9</v>
       </c>
       <c r="AG86" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C87" s="9"/>
+        <v>435</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C87" s="11"/>
       <c r="D87" s="10"/>
       <c r="E87" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="I87" s="10"/>
-      <c r="J87" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>432</v>
-      </c>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="11"/>
       <c r="N87" s="12"/>
-      <c r="O87" s="11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q87" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R87" s="9" t="s">
-        <v>427</v>
-      </c>
+      <c r="O87" s="9"/>
+      <c r="P87" s="9"/>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="11"/>
       <c r="S87" s="10"/>
       <c r="T87" s="9"/>
       <c r="U87" s="9"/>
@@ -9784,60 +9757,68 @@
       </c>
       <c r="AB87" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>22.2</v>
       </c>
       <c r="AC87" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>21.1</v>
       </c>
       <c r="AD87" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>28.2</v>
       </c>
       <c r="AE87" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>67</v>
+        <v>25.2</v>
       </c>
       <c r="AF87" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>65.9</v>
+        <v>24.1</v>
       </c>
       <c r="AG87" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B88" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="C88" s="11"/>
+        <v>438</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C88" s="9"/>
       <c r="D88" s="10"/>
       <c r="E88" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="I88" s="10"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
-      <c r="M88" s="11"/>
+      <c r="J88" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K88" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L88" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="M88" s="22" t="s">
+        <v>442</v>
+      </c>
       <c r="N88" s="12"/>
       <c r="O88" s="9"/>
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
-      <c r="R88" s="11"/>
+      <c r="R88" s="9"/>
       <c r="S88" s="10"/>
       <c r="T88" s="9"/>
       <c r="U88" s="9"/>
@@ -9858,15 +9839,15 @@
       </c>
       <c r="AB88" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>59.6</v>
       </c>
       <c r="AC88" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>58.5</v>
       </c>
       <c r="AD88" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>65.6</v>
       </c>
       <c r="AE88" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9881,45 +9862,45 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C89" s="9"/>
+        <v>353</v>
+      </c>
+      <c r="C89" s="11"/>
       <c r="D89" s="10"/>
       <c r="E89" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="K89" s="9" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="M89" s="22" t="s">
-        <v>440</v>
+        <v>445</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="N89" s="12"/>
       <c r="O89" s="9"/>
       <c r="P89" s="9"/>
       <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
+      <c r="R89" s="11"/>
       <c r="S89" s="10"/>
       <c r="T89" s="9"/>
       <c r="U89" s="9"/>
@@ -9940,15 +9921,15 @@
       </c>
       <c r="AB89" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>59.6</v>
+        <v>35.4</v>
       </c>
       <c r="AC89" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>58.5</v>
+        <v>34.3</v>
       </c>
       <c r="AD89" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>65.6</v>
+        <v>41.4</v>
       </c>
       <c r="AE89" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -9963,45 +9944,45 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C90" s="11"/>
+        <v>353</v>
+      </c>
+      <c r="C90" s="9"/>
       <c r="D90" s="10"/>
       <c r="E90" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>430</v>
+        <v>382</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K90" s="9" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="M90" s="9" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="N90" s="12"/>
       <c r="O90" s="9"/>
       <c r="P90" s="9"/>
       <c r="Q90" s="9"/>
-      <c r="R90" s="11"/>
+      <c r="R90" s="9"/>
       <c r="S90" s="10"/>
       <c r="T90" s="9"/>
       <c r="U90" s="9"/>
@@ -10045,12 +10026,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="10"/>
@@ -10058,26 +10039,26 @@
         <v>1</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>380</v>
+        <v>453</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>67</v>
+        <v>220</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="M91" s="9" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="N91" s="12"/>
       <c r="O91" s="9"/>
@@ -10127,39 +10108,41 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C92" s="9"/>
+        <v>353</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>457</v>
+      </c>
       <c r="D92" s="10"/>
       <c r="E92" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K92" s="9" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="L92" s="9" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M92" s="9" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N92" s="12"/>
       <c r="O92" s="9"/>
@@ -10186,15 +10169,15 @@
       </c>
       <c r="AB92" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>44.2</v>
       </c>
       <c r="AC92" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="AD92" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>50.2</v>
       </c>
       <c r="AE92" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -10209,47 +10192,45 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>455</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C93" s="11"/>
       <c r="D93" s="10"/>
       <c r="E93" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>457</v>
+        <v>382</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K93" s="9" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>459</v>
+        <v>464</v>
+      </c>
+      <c r="M93" s="11" t="s">
+        <v>465</v>
       </c>
       <c r="N93" s="12"/>
       <c r="O93" s="9"/>
       <c r="P93" s="9"/>
       <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
+      <c r="R93" s="11"/>
       <c r="S93" s="10"/>
       <c r="T93" s="9"/>
       <c r="U93" s="9"/>
@@ -10270,15 +10251,15 @@
       </c>
       <c r="AB93" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>35.4</v>
       </c>
       <c r="AC93" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="AD93" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>41.4</v>
       </c>
       <c r="AE93" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -10295,43 +10276,43 @@
     </row>
     <row r="94" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C94" s="11"/>
+        <v>353</v>
+      </c>
+      <c r="C94" s="9"/>
       <c r="D94" s="10"/>
       <c r="E94" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K94" s="9" t="s">
         <v>35</v>
       </c>
       <c r="L94" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="M94" s="11" t="s">
-        <v>463</v>
+        <v>469</v>
+      </c>
+      <c r="M94" s="9" t="s">
+        <v>470</v>
       </c>
       <c r="N94" s="12"/>
       <c r="O94" s="9"/>
       <c r="P94" s="9"/>
       <c r="Q94" s="9"/>
-      <c r="R94" s="11"/>
+      <c r="R94" s="9"/>
       <c r="S94" s="10"/>
       <c r="T94" s="9"/>
       <c r="U94" s="9"/>
@@ -10352,15 +10333,15 @@
       </c>
       <c r="AB94" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>39.8</v>
       </c>
       <c r="AC94" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="AD94" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AE94" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -10375,12 +10356,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="10"/>
@@ -10388,26 +10369,26 @@
         <v>1</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K95" s="9" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="L95" s="9" t="s">
-        <v>467</v>
+        <v>359</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N95" s="12"/>
       <c r="O95" s="9"/>
@@ -10434,15 +10415,15 @@
       </c>
       <c r="AB95" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>66.2</v>
       </c>
       <c r="AC95" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>65.1</v>
       </c>
       <c r="AD95" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>72.2</v>
       </c>
       <c r="AE95" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -10457,12 +10438,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="10"/>
@@ -10470,26 +10451,26 @@
         <v>1</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>67</v>
+        <v>220</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>356</v>
+        <v>35</v>
       </c>
       <c r="L96" s="9" t="s">
-        <v>357</v>
+        <v>477</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="N96" s="12"/>
       <c r="O96" s="9"/>
@@ -10516,15 +10497,15 @@
       </c>
       <c r="AB96" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>66.2</v>
+        <v>48.6</v>
       </c>
       <c r="AC96" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>65.1</v>
+        <v>47.5</v>
       </c>
       <c r="AD96" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>72.2</v>
+        <v>54.6</v>
       </c>
       <c r="AE96" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -10539,12 +10520,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="10"/>
@@ -10552,32 +10533,40 @@
         <v>1</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>474</v>
+        <v>363</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>35</v>
       </c>
       <c r="L97" s="9" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="N97" s="12"/>
-      <c r="O97" s="9"/>
-      <c r="P97" s="9"/>
-      <c r="Q97" s="9"/>
-      <c r="R97" s="9"/>
+      <c r="O97" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P97" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q97" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R97" s="9" t="s">
+        <v>483</v>
+      </c>
       <c r="S97" s="10"/>
       <c r="T97" s="9"/>
       <c r="U97" s="9"/>
@@ -10598,35 +10587,35 @@
       </c>
       <c r="AB97" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>48.6</v>
+        <v>35.4</v>
       </c>
       <c r="AC97" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>47.5</v>
+        <v>34.3</v>
       </c>
       <c r="AD97" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>54.6</v>
+        <v>41.4</v>
       </c>
       <c r="AE97" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>73.6</v>
       </c>
       <c r="AF97" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>72.5</v>
       </c>
       <c r="AG97" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>79.6</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="10"/>
@@ -10634,40 +10623,24 @@
         <v>1</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>361</v>
+        <v>486</v>
       </c>
       <c r="I98" s="10"/>
-      <c r="J98" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K98" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L98" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="M98" s="9" t="s">
-        <v>480</v>
-      </c>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
       <c r="N98" s="12"/>
-      <c r="O98" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="P98" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q98" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R98" s="9" t="s">
-        <v>481</v>
-      </c>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
       <c r="S98" s="10"/>
       <c r="T98" s="9"/>
       <c r="U98" s="9"/>
@@ -10688,60 +10661,60 @@
       </c>
       <c r="AB98" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>22.2</v>
       </c>
       <c r="AC98" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>21.1</v>
       </c>
       <c r="AD98" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>28.2</v>
       </c>
       <c r="AE98" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>73.6</v>
+        <v>25.2</v>
       </c>
       <c r="AF98" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>72.5</v>
+        <v>24.1</v>
       </c>
       <c r="AG98" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>79.6</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="B99" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C99" s="9"/>
+        <v>487</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C99" s="11"/>
       <c r="D99" s="10"/>
       <c r="E99" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
       <c r="L99" s="9"/>
-      <c r="M99" s="9"/>
+      <c r="M99" s="11"/>
       <c r="N99" s="12"/>
       <c r="O99" s="9"/>
       <c r="P99" s="9"/>
       <c r="Q99" s="9"/>
-      <c r="R99" s="9"/>
+      <c r="R99" s="11"/>
       <c r="S99" s="10"/>
       <c r="T99" s="9"/>
       <c r="U99" s="9"/>
@@ -10785,37 +10758,53 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="B100" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="C100" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C100" s="9"/>
       <c r="D100" s="10"/>
       <c r="E100" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>487</v>
+        <v>418</v>
       </c>
       <c r="I100" s="10"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
-      <c r="M100" s="11"/>
+      <c r="J100" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L100" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="M100" s="9" t="s">
+        <v>493</v>
+      </c>
       <c r="N100" s="12"/>
-      <c r="O100" s="9"/>
-      <c r="P100" s="9"/>
-      <c r="Q100" s="9"/>
-      <c r="R100" s="11"/>
+      <c r="O100" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P100" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q100" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="R100" s="9" t="s">
+        <v>495</v>
+      </c>
       <c r="S100" s="10"/>
       <c r="T100" s="9"/>
       <c r="U100" s="9"/>
@@ -10836,35 +10825,35 @@
       </c>
       <c r="AB100" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>35.4</v>
       </c>
       <c r="AC100" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>34.3</v>
       </c>
       <c r="AD100" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>41.4</v>
       </c>
       <c r="AE100" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>69.2</v>
       </c>
       <c r="AF100" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>68.1</v>
       </c>
       <c r="AG100" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="10"/>
@@ -10872,40 +10861,32 @@
         <v>1</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>416</v>
+        <v>497</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K101" s="9" t="s">
-        <v>50</v>
+        <v>358</v>
       </c>
       <c r="L101" s="9" t="s">
-        <v>490</v>
+        <v>359</v>
       </c>
       <c r="M101" s="9" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="N101" s="12"/>
-      <c r="O101" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q101" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="R101" s="9" t="s">
-        <v>493</v>
-      </c>
+      <c r="O101" s="9"/>
+      <c r="P101" s="9"/>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
       <c r="S101" s="10"/>
       <c r="T101" s="9"/>
       <c r="U101" s="9"/>
@@ -10926,35 +10907,35 @@
       </c>
       <c r="AB101" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>66.2</v>
       </c>
       <c r="AC101" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>65.1</v>
       </c>
       <c r="AD101" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>72.2</v>
       </c>
       <c r="AE101" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>69.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF101" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>68.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG101" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>75.2</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="10"/>
@@ -10962,27 +10943,19 @@
         <v>1</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="I102" s="10"/>
-      <c r="J102" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K102" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="L102" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="M102" s="9" t="s">
-        <v>496</v>
-      </c>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="9"/>
+      <c r="M102" s="9"/>
       <c r="N102" s="12"/>
       <c r="O102" s="9"/>
       <c r="P102" s="9"/>
@@ -11008,15 +10981,15 @@
       </c>
       <c r="AB102" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>66.2</v>
+        <v>22.2</v>
       </c>
       <c r="AC102" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>65.1</v>
+        <v>21.1</v>
       </c>
       <c r="AD102" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>72.2</v>
+        <v>28.2</v>
       </c>
       <c r="AE102" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11033,10 +11006,10 @@
     </row>
     <row r="103" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="10"/>
@@ -11044,19 +11017,27 @@
         <v>1</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="I103" s="10"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
-      <c r="M103" s="9"/>
+      <c r="J103" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="M103" s="9" t="s">
+        <v>506</v>
+      </c>
       <c r="N103" s="12"/>
       <c r="O103" s="9"/>
       <c r="P103" s="9"/>
@@ -11082,15 +11063,15 @@
       </c>
       <c r="AB103" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC103" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD103" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE103" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11105,45 +11086,47 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="B104" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C104" s="9"/>
+        <v>507</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>508</v>
+      </c>
       <c r="D104" s="10"/>
       <c r="E104" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K104" s="9" t="s">
         <v>35</v>
       </c>
       <c r="L104" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="M104" s="9" t="s">
-        <v>504</v>
+        <v>213</v>
+      </c>
+      <c r="M104" s="11" t="s">
+        <v>511</v>
       </c>
       <c r="N104" s="12"/>
       <c r="O104" s="9"/>
       <c r="P104" s="9"/>
       <c r="Q104" s="9"/>
-      <c r="R104" s="9"/>
+      <c r="R104" s="11"/>
       <c r="S104" s="10"/>
       <c r="T104" s="9"/>
       <c r="U104" s="9"/>
@@ -11164,15 +11147,15 @@
       </c>
       <c r="AB104" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>61.8</v>
       </c>
       <c r="AC104" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>60.7</v>
       </c>
       <c r="AD104" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>67.8</v>
       </c>
       <c r="AE104" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11187,47 +11170,47 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="B105" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>506</v>
+        <v>512</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>508</v>
       </c>
       <c r="D105" s="10"/>
       <c r="E105" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K105" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="M105" s="11" t="s">
-        <v>509</v>
+        <v>515</v>
+      </c>
+      <c r="M105" s="9" t="s">
+        <v>516</v>
       </c>
       <c r="N105" s="12"/>
       <c r="O105" s="9"/>
       <c r="P105" s="9"/>
       <c r="Q105" s="9"/>
-      <c r="R105" s="11"/>
+      <c r="R105" s="9"/>
       <c r="S105" s="10"/>
       <c r="T105" s="9"/>
       <c r="U105" s="9"/>
@@ -11248,15 +11231,15 @@
       </c>
       <c r="AB105" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>35.4</v>
       </c>
       <c r="AC105" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>34.3</v>
       </c>
       <c r="AD105" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>41.4</v>
       </c>
       <c r="AE105" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11271,47 +11254,53 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>506</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C106" s="9"/>
       <c r="D106" s="10"/>
       <c r="E106" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>512</v>
+        <v>382</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K106" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="M106" s="9" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="N106" s="12"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
-      <c r="Q106" s="9"/>
-      <c r="R106" s="9"/>
+      <c r="O106" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P106" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q106" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R106" s="9" t="s">
+        <v>429</v>
+      </c>
       <c r="S106" s="10"/>
       <c r="T106" s="9"/>
       <c r="U106" s="9"/>
@@ -11344,23 +11333,23 @@
       </c>
       <c r="AE106" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>69.2</v>
       </c>
       <c r="AF106" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>68.1</v>
       </c>
       <c r="AG106" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="10"/>
@@ -11368,40 +11357,32 @@
         <v>1</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>380</v>
+        <v>523</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K107" s="9" t="s">
-        <v>50</v>
+        <v>358</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>517</v>
+        <v>359</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="N107" s="12"/>
-      <c r="O107" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q107" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R107" s="9" t="s">
-        <v>427</v>
-      </c>
+      <c r="O107" s="9"/>
+      <c r="P107" s="9"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
       <c r="S107" s="10"/>
       <c r="T107" s="9"/>
       <c r="U107" s="9"/>
@@ -11422,71 +11403,73 @@
       </c>
       <c r="AB107" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>66.2</v>
       </c>
       <c r="AC107" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>65.1</v>
       </c>
       <c r="AD107" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>72.2</v>
       </c>
       <c r="AE107" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>69.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF107" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>68.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG107" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>75.2</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C108" s="9"/>
-      <c r="D108" s="10"/>
+      <c r="D108" s="18"/>
       <c r="E108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G108" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="H108" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="I108" s="10"/>
+      <c r="F108" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="I108" s="18"/>
       <c r="J108" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K108" s="9" t="s">
-        <v>356</v>
+        <v>35</v>
       </c>
       <c r="L108" s="9" t="s">
-        <v>357</v>
+        <v>528</v>
       </c>
       <c r="M108" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="N108" s="12"/>
-      <c r="O108" s="9"/>
+        <v>529</v>
+      </c>
+      <c r="N108" s="19"/>
+      <c r="O108" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="P108" s="9"/>
       <c r="Q108" s="9"/>
       <c r="R108" s="9"/>
-      <c r="S108" s="10"/>
-      <c r="T108" s="9"/>
-      <c r="U108" s="9"/>
+      <c r="S108" s="18"/>
+      <c r="T108" s="11"/>
+      <c r="U108" s="11"/>
       <c r="V108" s="9"/>
       <c r="W108" s="9"/>
       <c r="X108" s="9"/>
@@ -11504,73 +11487,71 @@
       </c>
       <c r="AB108" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>66.2</v>
+        <v>44.2</v>
       </c>
       <c r="AC108" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>65.1</v>
+        <v>43.1</v>
       </c>
       <c r="AD108" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>72.2</v>
+        <v>50.2</v>
       </c>
       <c r="AE108" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>47.2</v>
       </c>
       <c r="AF108" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>46.1</v>
       </c>
       <c r="AG108" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C109" s="9"/>
-      <c r="D109" s="18"/>
+        <v>353</v>
+      </c>
+      <c r="C109" s="11"/>
+      <c r="D109" s="10"/>
       <c r="E109" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="I109" s="18"/>
+      <c r="F109" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="I109" s="10"/>
       <c r="J109" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K109" s="9" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="L109" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="M109" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="N109" s="19"/>
-      <c r="O109" s="9" t="n">
-        <v>5</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="M109" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="N109" s="12"/>
+      <c r="O109" s="9"/>
       <c r="P109" s="9"/>
       <c r="Q109" s="9"/>
-      <c r="R109" s="9"/>
-      <c r="S109" s="18"/>
-      <c r="T109" s="11"/>
-      <c r="U109" s="11"/>
+      <c r="R109" s="11"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
       <c r="V109" s="9"/>
       <c r="W109" s="9"/>
       <c r="X109" s="9"/>
@@ -11588,35 +11569,35 @@
       </c>
       <c r="AB109" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>44.2</v>
+        <v>61.8</v>
       </c>
       <c r="AC109" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>43.1</v>
+        <v>60.7</v>
       </c>
       <c r="AD109" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>50.2</v>
+        <v>67.8</v>
       </c>
       <c r="AE109" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>47.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF109" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>46.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG109" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>53.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="10"/>
@@ -11624,26 +11605,26 @@
         <v>1</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="I110" s="10"/>
       <c r="J110" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K110" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L110" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M110" s="11" t="s">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="N110" s="12"/>
       <c r="O110" s="9"/>
@@ -11670,15 +11651,15 @@
       </c>
       <c r="AB110" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>66.2</v>
       </c>
       <c r="AC110" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>65.1</v>
       </c>
       <c r="AD110" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>72.2</v>
       </c>
       <c r="AE110" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11693,12 +11674,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="10"/>
@@ -11706,26 +11687,26 @@
         <v>1</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K111" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L111" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M111" s="11" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="N111" s="12"/>
       <c r="O111" s="9"/>
@@ -11752,15 +11733,15 @@
       </c>
       <c r="AB111" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>66.2</v>
+        <v>61.8</v>
       </c>
       <c r="AC111" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>65.1</v>
+        <v>60.7</v>
       </c>
       <c r="AD111" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>72.2</v>
+        <v>67.8</v>
       </c>
       <c r="AE111" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11775,12 +11756,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C112" s="11"/>
       <c r="D112" s="10"/>
@@ -11788,27 +11769,19 @@
         <v>1</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="I112" s="10"/>
-      <c r="J112" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K112" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="L112" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="M112" s="11" t="s">
-        <v>538</v>
-      </c>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="11"/>
       <c r="N112" s="12"/>
       <c r="O112" s="9"/>
       <c r="P112" s="9"/>
@@ -11834,15 +11807,15 @@
       </c>
       <c r="AB112" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>61.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC112" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>60.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD112" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>67.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE112" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -11857,37 +11830,53 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C113" s="11"/>
+        <v>353</v>
+      </c>
+      <c r="C113" s="9"/>
       <c r="D113" s="10"/>
       <c r="E113" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="I113" s="10"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="9"/>
-      <c r="L113" s="9"/>
-      <c r="M113" s="11"/>
+      <c r="J113" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L113" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="M113" s="9" t="s">
+        <v>548</v>
+      </c>
       <c r="N113" s="12"/>
-      <c r="O113" s="9"/>
-      <c r="P113" s="9"/>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="11"/>
+      <c r="O113" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P113" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q113" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="R113" s="9" t="s">
+        <v>550</v>
+      </c>
       <c r="S113" s="10"/>
       <c r="T113" s="9"/>
       <c r="U113" s="9"/>
@@ -11908,76 +11897,60 @@
       </c>
       <c r="AB113" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC113" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD113" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE113" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>60.4</v>
       </c>
       <c r="AF113" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>59.3</v>
       </c>
       <c r="AG113" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66.4</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B114" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C114" s="9"/>
+        <v>353</v>
+      </c>
+      <c r="C114" s="11"/>
       <c r="D114" s="10"/>
       <c r="E114" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I114" s="10"/>
-      <c r="J114" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K114" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L114" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="M114" s="9" t="s">
-        <v>546</v>
-      </c>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="11"/>
       <c r="N114" s="12"/>
-      <c r="O114" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="P114" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q114" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="R114" s="9" t="s">
-        <v>548</v>
-      </c>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="11"/>
       <c r="S114" s="10"/>
       <c r="T114" s="9"/>
       <c r="U114" s="9"/>
@@ -11998,35 +11971,35 @@
       </c>
       <c r="AB114" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>22.2</v>
       </c>
       <c r="AC114" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>21.1</v>
       </c>
       <c r="AD114" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>28.2</v>
       </c>
       <c r="AE114" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>60.4</v>
+        <v>25.2</v>
       </c>
       <c r="AF114" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>59.3</v>
+        <v>24.1</v>
       </c>
       <c r="AG114" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>66.4</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="10"/>
@@ -12034,19 +12007,27 @@
         <v>1</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="I115" s="10"/>
-      <c r="J115" s="9"/>
-      <c r="K115" s="9"/>
-      <c r="L115" s="9"/>
-      <c r="M115" s="11"/>
+      <c r="J115" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L115" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="M115" s="11" t="s">
+        <v>558</v>
+      </c>
       <c r="N115" s="12"/>
       <c r="O115" s="9"/>
       <c r="P115" s="9"/>
@@ -12072,15 +12053,15 @@
       </c>
       <c r="AB115" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
+        <v>39.8</v>
       </c>
       <c r="AC115" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
+        <v>38.7</v>
       </c>
       <c r="AD115" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
+        <v>45.8</v>
       </c>
       <c r="AE115" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -12095,12 +12076,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="10"/>
@@ -12108,26 +12089,26 @@
         <v>1</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>554</v>
+        <v>382</v>
       </c>
       <c r="I116" s="10"/>
       <c r="J116" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K116" s="9" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="L116" s="9" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="M116" s="11" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="N116" s="12"/>
       <c r="O116" s="9"/>
@@ -12154,15 +12135,15 @@
       </c>
       <c r="AB116" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>39.8</v>
+        <v>35.4</v>
       </c>
       <c r="AC116" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="AD116" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>45.8</v>
+        <v>41.4</v>
       </c>
       <c r="AE116" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -12177,12 +12158,12 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="10"/>
@@ -12190,32 +12171,40 @@
         <v>1</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>380</v>
+        <v>565</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="M117" s="11" t="s">
-        <v>560</v>
+        <v>566</v>
+      </c>
+      <c r="M117" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="N117" s="12"/>
-      <c r="O117" s="9"/>
-      <c r="P117" s="9"/>
-      <c r="Q117" s="9"/>
-      <c r="R117" s="11"/>
+      <c r="O117" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P117" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q117" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="R117" s="11" t="s">
+        <v>568</v>
+      </c>
       <c r="S117" s="10"/>
       <c r="T117" s="9"/>
       <c r="U117" s="9"/>
@@ -12248,23 +12237,23 @@
       </c>
       <c r="AE117" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
+        <v>69.2</v>
       </c>
       <c r="AF117" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
+        <v>68.1</v>
       </c>
       <c r="AG117" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="10"/>
@@ -12272,40 +12261,32 @@
         <v>1</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>563</v>
+        <v>453</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K118" s="9" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="L118" s="9" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="M118" s="9" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="N118" s="12"/>
-      <c r="O118" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P118" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q118" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="R118" s="11" t="s">
-        <v>566</v>
-      </c>
+      <c r="O118" s="9"/>
+      <c r="P118" s="9"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="11"/>
       <c r="S118" s="10"/>
       <c r="T118" s="9"/>
       <c r="U118" s="9"/>
@@ -12338,23 +12319,23 @@
       </c>
       <c r="AE118" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>69.2</v>
+        <v>25.2</v>
       </c>
       <c r="AF118" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>68.1</v>
+        <v>24.1</v>
       </c>
       <c r="AG118" s="11" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>75.2</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C119" s="11"/>
       <c r="D119" s="10"/>
@@ -12362,27 +12343,19 @@
         <v>1</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>451</v>
+        <v>575</v>
       </c>
       <c r="I119" s="10"/>
-      <c r="J119" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K119" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L119" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="M119" s="9" t="s">
-        <v>570</v>
-      </c>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9"/>
+      <c r="L119" s="9"/>
+      <c r="M119" s="11"/>
       <c r="N119" s="12"/>
       <c r="O119" s="9"/>
       <c r="P119" s="9"/>
@@ -12408,15 +12381,15 @@
       </c>
       <c r="AB119" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>35.4</v>
+        <v>22.2</v>
       </c>
       <c r="AC119" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>34.3</v>
+        <v>21.1</v>
       </c>
       <c r="AD119" s="9" t="n">
         <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>41.4</v>
+        <v>28.2</v>
       </c>
       <c r="AE119" s="9" t="n">
         <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
@@ -12431,79 +12404,40 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="B120" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="C120" s="11"/>
-      <c r="D120" s="10"/>
-      <c r="E120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G120" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="H120" s="11" t="s">
-        <v>573</v>
-      </c>
-      <c r="I120" s="10"/>
-      <c r="J120" s="9"/>
-      <c r="K120" s="9"/>
-      <c r="L120" s="9"/>
-      <c r="M120" s="11"/>
-      <c r="N120" s="12"/>
-      <c r="O120" s="9"/>
-      <c r="P120" s="9"/>
-      <c r="Q120" s="9"/>
-      <c r="R120" s="11"/>
-      <c r="S120" s="10"/>
-      <c r="T120" s="9"/>
-      <c r="U120" s="9"/>
-      <c r="V120" s="9"/>
-      <c r="W120" s="9"/>
-      <c r="X120" s="9"/>
-      <c r="Y120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E1Y]]+X$2</f>
-        <v>23.6</v>
-      </c>
-      <c r="Z120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E1TY]]+W$2</f>
-        <v>22.5</v>
-      </c>
-      <c r="AA120" s="9" t="n">
-        <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 1 Y]]-1)</f>
-        <v>29.6</v>
-      </c>
-      <c r="AB120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E2Y]]+X$2</f>
-        <v>22.2</v>
-      </c>
-      <c r="AC120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E2TY]]+W$2</f>
-        <v>21.1</v>
-      </c>
-      <c r="AD120" s="9" t="n">
-        <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 2 Y]]-1)+V$2</f>
-        <v>28.2</v>
-      </c>
-      <c r="AE120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E3Y]]+X$2</f>
-        <v>25.2</v>
-      </c>
-      <c r="AF120" s="9" t="n">
-        <f aca="false">Table3[[#This Row],[E3TY]]+W$2</f>
-        <v>24.1</v>
-      </c>
-      <c r="AG120" s="11" t="n">
-        <f aca="false">T$2+U$2*(Table3[[#This Row],[Effect 3 Y]]-1)+2*V$2</f>
-        <v>31.2</v>
-      </c>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="23"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+      <c r="D120" s="23"/>
+      <c r="E120" s="23"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="23"/>
+      <c r="I120" s="23"/>
+      <c r="J120" s="23"/>
+      <c r="K120" s="24"/>
+      <c r="L120" s="24"/>
+      <c r="M120" s="25"/>
+      <c r="N120" s="23"/>
+      <c r="O120" s="23"/>
+      <c r="P120" s="24"/>
+      <c r="Q120" s="24"/>
+      <c r="R120" s="23"/>
+      <c r="S120" s="23"/>
+      <c r="T120" s="23"/>
+      <c r="U120" s="23"/>
+      <c r="V120" s="23"/>
+      <c r="W120" s="23"/>
+      <c r="X120" s="23"/>
+      <c r="Y120" s="23"/>
+      <c r="Z120" s="23"/>
+      <c r="AA120" s="23"/>
+      <c r="AB120" s="23"/>
+      <c r="AC120" s="23"/>
+      <c r="AD120" s="23"/>
+      <c r="AE120" s="23"/>
+      <c r="AF120" s="23"/>
+      <c r="AG120" s="24"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="23"/>
@@ -15235,43 +15169,9 @@
       <c r="AF198" s="23"/>
       <c r="AG198" s="24"/>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="23"/>
-      <c r="B199" s="23"/>
-      <c r="C199" s="23"/>
-      <c r="D199" s="23"/>
-      <c r="E199" s="23"/>
-      <c r="F199" s="24"/>
-      <c r="G199" s="24"/>
-      <c r="H199" s="23"/>
-      <c r="I199" s="23"/>
-      <c r="J199" s="23"/>
-      <c r="K199" s="24"/>
-      <c r="L199" s="24"/>
-      <c r="M199" s="25"/>
-      <c r="N199" s="23"/>
-      <c r="O199" s="23"/>
-      <c r="P199" s="24"/>
-      <c r="Q199" s="24"/>
-      <c r="R199" s="23"/>
-      <c r="S199" s="23"/>
-      <c r="T199" s="23"/>
-      <c r="U199" s="23"/>
-      <c r="V199" s="23"/>
-      <c r="W199" s="23"/>
-      <c r="X199" s="23"/>
-      <c r="Y199" s="23"/>
-      <c r="Z199" s="23"/>
-      <c r="AA199" s="23"/>
-      <c r="AB199" s="23"/>
-      <c r="AC199" s="23"/>
-      <c r="AD199" s="23"/>
-      <c r="AE199" s="23"/>
-      <c r="AF199" s="23"/>
-      <c r="AG199" s="24"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="B2:B96">
+  <conditionalFormatting sqref="B2:B95">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Accessory" dxfId="12">
       <formula>NOT(ISERROR(SEARCH("Accessory",B2)))</formula>
     </cfRule>
@@ -15288,38 +15188,38 @@
       <formula>NOT(ISERROR(SEARCH("Spell",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121:B199">
+  <conditionalFormatting sqref="B120:B198">
     <cfRule type="containsText" priority="7" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Accessory" dxfId="17">
-      <formula>NOT(ISERROR(SEARCH("Accessory",B121)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Accessory",B120)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="8" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Armour" dxfId="18">
-      <formula>NOT(ISERROR(SEARCH("Armour",B121)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Armour",B120)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="9" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Equipment" dxfId="19">
-      <formula>NOT(ISERROR(SEARCH("Equipment",B121)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Equipment",B120)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="10" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Impression" dxfId="20">
-      <formula>NOT(ISERROR(SEARCH("Impression",B121)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Impression",B120)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="11" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Spell" dxfId="21">
-      <formula>NOT(ISERROR(SEARCH("Spell",B121)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Spell",B120)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
+  <conditionalFormatting sqref="C17">
     <cfRule type="containsText" priority="12" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Accessory" dxfId="22">
-      <formula>NOT(ISERROR(SEARCH("Accessory",C18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Accessory",C17)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="13" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Armour" dxfId="23">
-      <formula>NOT(ISERROR(SEARCH("Armour",C18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Armour",C17)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="14" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Equipment" dxfId="24">
-      <formula>NOT(ISERROR(SEARCH("Equipment",C18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Equipment",C17)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="15" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Impression" dxfId="25">
-      <formula>NOT(ISERROR(SEARCH("Impression",C18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Impression",C17)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="16" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Spell" dxfId="26">
-      <formula>NOT(ISERROR(SEARCH("Spell",C18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Spell",C17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 J1:M1 O1:R1 T1:AG1">

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="591">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -258,7 +258,7 @@
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Behemoth&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">You can't be be forced to move against your will. When you move, declare one of your hex as your moving hex. Your other Hexes follow behind.  Moving through a 1 wide gap counts as moving 2 hexes.</t>
+    <t xml:space="preserve">You can't be be forced to move against your will.</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Massive Limbs&lt;/i&gt;&lt;/b&gt;</t>
@@ -267,10 +267,10 @@
     <t xml:space="preserve">Attacks that cost more than 2 AP cost 1 less and have &lt;b&gt;Reach&lt;/b&gt;.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Heft&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After emergence, gain +1 Flesh.</t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Hefty&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After emergence, gain +1 Heft.</t>
   </si>
   <si>
     <t xml:space="preserve">Glowing Kintsugi</t>
@@ -418,7 +418,7 @@
     <t xml:space="preserve">At the start of your turn, put a counter on an empty mode, then use that effect.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">Mob of the Deep Ones</t>
   </si>
   <si>
     <t xml:space="preserve">hex1big   hex1big   hex1big</t>
@@ -545,10 +545,6 @@
     <t xml:space="preserve">Reduce damage from non-adjacent beings to 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">You cannot be move or be made to move except with the move action.
-&lt;br /&gt;Moving into a 1 hex wide space counts as moving 2 hexes.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unstable</t>
   </si>
   <si>
@@ -662,7 +658,7 @@
     <t xml:space="preserve">Your second attack each turn costs 1 less AP.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Creative Duelist&lt;/i&gt;&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Creative Duellist&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">You may use Crit options available to any of your limbs on all attacks.</t>
@@ -1062,7 +1058,7 @@
     <t xml:space="preserve">Treacherous</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Snigger:&lt;/b&gt; WeirdT or &lt;b&gt;Exhasusted&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;Snigger:&lt;/b&gt; WeirdT or &lt;b&gt;Exhausted&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">When you see a being take damage from a source other than you, you may increase that damage by 2. This does not stack.</t>
@@ -1319,7 +1315,7 @@
     <t xml:space="preserve">&lt;b&gt;Burst Block:&lt;/b&gt; Destroy this card</t>
   </si>
   <si>
-    <t xml:space="preserve">Completely block an incoming attack and deal 5 damage to all adjacent beings.</t>
+    <t xml:space="preserve">After taking damage, deal 6 damage to all adjacent beings.</t>
   </si>
   <si>
     <t xml:space="preserve">Explosive Polyps</t>
@@ -1426,7 +1422,7 @@
     <t xml:space="preserve">&lt;b&gt;Bloom:&lt;/b&gt;  WeirdT</t>
   </si>
   <si>
-    <t xml:space="preserve">Competely ignore damage from falling.</t>
+    <t xml:space="preserve">Completely ignore damage from falling.</t>
   </si>
   <si>
     <t xml:space="preserve">Lithium Geode</t>
@@ -1530,7 +1526,7 @@
     <t xml:space="preserve">&lt;b&gt;Snap:&lt;/b&gt; 3 AP + &lt;b&gt;Exhaust&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Damage = 6, Reach&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;Damage = 7, Reach&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Painted Slab</t>
@@ -1697,9 +1693,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Smash:&lt;/b&gt; 3 AP + comptcompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Damage = 7, Reach&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Storm Conduit</t>
@@ -1800,6 +1793,86 @@
   <si>
     <t xml:space="preserve">&lt;b&gt;Damage = 5, Close&lt;/b&gt;
 &lt;br /&gt;Inflict the &lt;b&gt;Exhausted&lt;/b&gt; status effect on a hit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects from terrain or abilities cannot reduce your speed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">While you have the &lt;b&gt;Well Rested&lt;/b&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">status effect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, gain an additional +1 speed.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Anhedonia:&lt;/b&gt; 2 AP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage = 2, Close&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrain interactions cost 1 AP less.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swarm of Eyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Squint:&lt;/b&gt; 2 AP or (weirdT + 1 AP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage = 2, Ranged&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack can’t be reduced.
+&lt;br /&gt;&lt;b&gt;Insight:&lt;/b&gt; Regain a spent WeirdT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spore Coat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whenever you take damage, deal 1 damage to all adjacent beings. This damage can’t be reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Sbonge:&lt;/b&gt; fleshTfleshT, &lt;b&gt;Exhausted&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore your composure.</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1882,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1838,6 +1911,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2942,7 +3021,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="68.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>50</v>
       </c>
@@ -3122,7 +3201,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>66</v>
       </c>
@@ -3206,7 +3285,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>72</v>
       </c>
@@ -4504,7 +4583,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
         <v>164</v>
       </c>
@@ -4522,10 +4601,10 @@
         <v>35</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="9" t="n">
@@ -4535,10 +4614,10 @@
         <v>35</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="9" t="n">
@@ -4548,10 +4627,10 @@
         <v>35</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="9"/>
@@ -4598,7 +4677,7 @@
     </row>
     <row r="23" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>34</v>
@@ -4612,10 +4691,10 @@
         <v>35</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="I23" s="18"/>
       <c r="J23" s="9" t="n">
@@ -4625,10 +4704,10 @@
         <v>35</v>
       </c>
       <c r="L23" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="M23" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="N23" s="19"/>
       <c r="O23" s="9"/>
@@ -4690,7 +4769,7 @@
     </row>
     <row r="24" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>34</v>
@@ -4704,10 +4783,10 @@
         <v>35</v>
       </c>
       <c r="G24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="9" t="n">
@@ -4717,10 +4796,10 @@
         <v>38</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="11"/>
@@ -4772,13 +4851,13 @@
     </row>
     <row r="25" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="9" t="n">
@@ -4788,10 +4867,10 @@
         <v>38</v>
       </c>
       <c r="G25" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="9" t="n">
@@ -4801,10 +4880,10 @@
         <v>35</v>
       </c>
       <c r="L25" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="9" t="n">
@@ -4814,10 +4893,10 @@
         <v>38</v>
       </c>
       <c r="Q25" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="R25" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="9"/>
@@ -4864,7 +4943,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>34</v>
@@ -4878,10 +4957,10 @@
         <v>35</v>
       </c>
       <c r="G26" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>190</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="9" t="n">
@@ -4891,10 +4970,10 @@
         <v>35</v>
       </c>
       <c r="L26" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="M26" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="9" t="n">
@@ -4904,10 +4983,10 @@
         <v>35</v>
       </c>
       <c r="Q26" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="R26" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>194</v>
       </c>
       <c r="S26" s="10"/>
       <c r="T26" s="9"/>
@@ -4954,7 +5033,7 @@
     </row>
     <row r="27" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>34</v>
@@ -4968,10 +5047,10 @@
         <v>35</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>196</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>197</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="9" t="n">
@@ -4981,10 +5060,10 @@
         <v>38</v>
       </c>
       <c r="L27" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="9"/>
@@ -5036,10 +5115,10 @@
     </row>
     <row r="28" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="10"/>
@@ -5050,10 +5129,10 @@
         <v>38</v>
       </c>
       <c r="G28" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H28" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>203</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="9"/>
@@ -5110,10 +5189,10 @@
     </row>
     <row r="29" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="10"/>
@@ -5124,10 +5203,10 @@
         <v>35</v>
       </c>
       <c r="G29" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>205</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="9" t="n">
@@ -5137,10 +5216,10 @@
         <v>35</v>
       </c>
       <c r="L29" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="N29" s="12"/>
       <c r="O29" s="9"/>
@@ -5192,10 +5271,10 @@
     </row>
     <row r="30" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="18"/>
@@ -5206,10 +5285,10 @@
         <v>35</v>
       </c>
       <c r="G30" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I30" s="18"/>
       <c r="J30" s="9"/>
@@ -5266,10 +5345,10 @@
     </row>
     <row r="31" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="18"/>
@@ -5280,10 +5359,10 @@
         <v>35</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="9"/>
@@ -5340,10 +5419,10 @@
     </row>
     <row r="32" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="18"/>
@@ -5354,10 +5433,10 @@
         <v>35</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I32" s="18"/>
       <c r="J32" s="9"/>
@@ -5414,10 +5493,10 @@
     </row>
     <row r="33" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="18"/>
@@ -5428,10 +5507,10 @@
         <v>35</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I33" s="18"/>
       <c r="J33" s="9"/>
@@ -5488,10 +5567,10 @@
     </row>
     <row r="34" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="10"/>
@@ -5499,13 +5578,13 @@
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="H34" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>222</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="9"/>
@@ -5562,10 +5641,10 @@
     </row>
     <row r="35" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="10"/>
@@ -5576,10 +5655,10 @@
         <v>35</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="9"/>
@@ -5636,10 +5715,10 @@
     </row>
     <row r="36" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -5650,10 +5729,10 @@
         <v>35</v>
       </c>
       <c r="G36" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="H36" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>227</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="9" t="n">
@@ -5663,10 +5742,10 @@
         <v>35</v>
       </c>
       <c r="L36" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="N36" s="12"/>
       <c r="O36" s="9"/>
@@ -5718,10 +5797,10 @@
     </row>
     <row r="37" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
@@ -5732,10 +5811,10 @@
         <v>35</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="9"/>
@@ -5792,10 +5871,10 @@
     </row>
     <row r="38" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
@@ -5806,10 +5885,10 @@
         <v>35</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="9"/>
@@ -5866,13 +5945,13 @@
     </row>
     <row r="39" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="9" t="n">
@@ -5882,10 +5961,10 @@
         <v>38</v>
       </c>
       <c r="G39" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="H39" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="9"/>
@@ -5942,10 +6021,10 @@
     </row>
     <row r="40" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
@@ -5956,10 +6035,10 @@
         <v>38</v>
       </c>
       <c r="G40" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H40" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>240</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="9" t="n">
@@ -5969,10 +6048,10 @@
         <v>35</v>
       </c>
       <c r="L40" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="M40" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="M40" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="N40" s="12"/>
       <c r="O40" s="9"/>
@@ -6024,10 +6103,10 @@
     </row>
     <row r="41" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
@@ -6038,10 +6117,10 @@
         <v>35</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9"/>
@@ -6098,10 +6177,10 @@
     </row>
     <row r="42" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
@@ -6112,10 +6191,10 @@
         <v>35</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="9"/>
@@ -6172,10 +6251,10 @@
     </row>
     <row r="43" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -6186,10 +6265,10 @@
         <v>35</v>
       </c>
       <c r="G43" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9" t="n">
@@ -6199,10 +6278,10 @@
         <v>38</v>
       </c>
       <c r="L43" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="M43" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="N43" s="12"/>
       <c r="O43" s="9" t="n">
@@ -6212,10 +6291,10 @@
         <v>38</v>
       </c>
       <c r="Q43" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="R43" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="R43" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="S43" s="10"/>
       <c r="T43" s="9"/>
@@ -6262,10 +6341,10 @@
     </row>
     <row r="44" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="10"/>
@@ -6276,10 +6355,10 @@
         <v>38</v>
       </c>
       <c r="G44" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="H44" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="9" t="n">
@@ -6289,10 +6368,10 @@
         <v>35</v>
       </c>
       <c r="L44" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="N44" s="12"/>
       <c r="O44" s="9"/>
@@ -6344,26 +6423,26 @@
     </row>
     <row r="45" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>259</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G45" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="H45" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9"/>
@@ -6420,10 +6499,10 @@
     </row>
     <row r="46" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="10"/>
@@ -6434,10 +6513,10 @@
         <v>35</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>265</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="9" t="n">
@@ -6447,10 +6526,10 @@
         <v>35</v>
       </c>
       <c r="L46" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="M46" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="M46" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="N46" s="12"/>
       <c r="O46" s="9"/>
@@ -6502,10 +6581,10 @@
     </row>
     <row r="47" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="10"/>
@@ -6516,10 +6595,10 @@
         <v>35</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9"/>
@@ -6576,10 +6655,10 @@
     </row>
     <row r="48" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="10"/>
@@ -6590,10 +6669,10 @@
         <v>35</v>
       </c>
       <c r="G48" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>272</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="9" t="n">
@@ -6603,10 +6682,10 @@
         <v>38</v>
       </c>
       <c r="L48" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="M48" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="M48" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="N48" s="12"/>
       <c r="O48" s="9"/>
@@ -6658,10 +6737,10 @@
     </row>
     <row r="49" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="10"/>
@@ -6672,10 +6751,10 @@
         <v>38</v>
       </c>
       <c r="G49" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9"/>
@@ -6732,10 +6811,10 @@
     </row>
     <row r="50" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="10"/>
@@ -6746,10 +6825,10 @@
         <v>35</v>
       </c>
       <c r="G50" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="H50" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="9" t="n">
@@ -6759,10 +6838,10 @@
         <v>35</v>
       </c>
       <c r="L50" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>282</v>
       </c>
       <c r="N50" s="12"/>
       <c r="O50" s="9"/>
@@ -6814,10 +6893,10 @@
     </row>
     <row r="51" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="10"/>
@@ -6828,10 +6907,10 @@
         <v>38</v>
       </c>
       <c r="G51" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="H51" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9"/>
@@ -6888,10 +6967,10 @@
     </row>
     <row r="52" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="10"/>
@@ -6902,10 +6981,10 @@
         <v>38</v>
       </c>
       <c r="G52" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="H52" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="9"/>
@@ -6962,10 +7041,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="10"/>
@@ -6976,10 +7055,10 @@
         <v>38</v>
       </c>
       <c r="G53" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>291</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9"/>
@@ -7036,10 +7115,10 @@
     </row>
     <row r="54" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="10"/>
@@ -7050,10 +7129,10 @@
         <v>38</v>
       </c>
       <c r="G54" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="H54" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>294</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="9" t="n">
@@ -7063,10 +7142,10 @@
         <v>35</v>
       </c>
       <c r="L54" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="M54" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="M54" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="N54" s="12"/>
       <c r="O54" s="9"/>
@@ -7118,10 +7197,10 @@
     </row>
     <row r="55" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="10"/>
@@ -7132,10 +7211,10 @@
         <v>35</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9"/>
@@ -7192,10 +7271,10 @@
     </row>
     <row r="56" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="10"/>
@@ -7206,10 +7285,10 @@
         <v>35</v>
       </c>
       <c r="G56" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>300</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="9" t="n">
@@ -7219,10 +7298,10 @@
         <v>38</v>
       </c>
       <c r="L56" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="M56" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>303</v>
       </c>
       <c r="N56" s="12"/>
       <c r="O56" s="9"/>
@@ -7274,10 +7353,10 @@
     </row>
     <row r="57" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="10"/>
@@ -7288,10 +7367,10 @@
         <v>38</v>
       </c>
       <c r="G57" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>305</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>306</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9" t="n">
@@ -7301,10 +7380,10 @@
         <v>35</v>
       </c>
       <c r="L57" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="M57" s="9" t="s">
         <v>307</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>308</v>
       </c>
       <c r="N57" s="12"/>
       <c r="O57" s="9"/>
@@ -7356,10 +7435,10 @@
     </row>
     <row r="58" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="10"/>
@@ -7370,23 +7449,23 @@
         <v>35</v>
       </c>
       <c r="G58" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>311</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="9" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L58" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="M58" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="M58" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="N58" s="12"/>
       <c r="O58" s="9"/>
@@ -7438,10 +7517,10 @@
     </row>
     <row r="59" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="10"/>
@@ -7452,10 +7531,10 @@
         <v>35</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9"/>
@@ -7512,10 +7591,10 @@
     </row>
     <row r="60" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="10"/>
@@ -7526,10 +7605,10 @@
         <v>38</v>
       </c>
       <c r="G60" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>317</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>318</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="9" t="n">
@@ -7539,10 +7618,10 @@
         <v>35</v>
       </c>
       <c r="L60" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="M60" s="9" t="s">
         <v>319</v>
-      </c>
-      <c r="M60" s="9" t="s">
-        <v>320</v>
       </c>
       <c r="N60" s="12"/>
       <c r="O60" s="9"/>
@@ -7594,10 +7673,10 @@
     </row>
     <row r="61" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="10"/>
@@ -7608,10 +7687,10 @@
         <v>35</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9"/>
@@ -7668,10 +7747,10 @@
     </row>
     <row r="62" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
@@ -7679,13 +7758,13 @@
         <v>1</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G62" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="H62" s="11" t="s">
         <v>324</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>325</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="9"/>
@@ -7742,10 +7821,10 @@
     </row>
     <row r="63" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
@@ -7753,13 +7832,13 @@
         <v>1</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G63" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H63" s="11" t="s">
         <v>327</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>328</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9"/>
@@ -7816,10 +7895,10 @@
     </row>
     <row r="64" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="10"/>
@@ -7830,10 +7909,10 @@
         <v>38</v>
       </c>
       <c r="G64" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="H64" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>331</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="9" t="n">
@@ -7843,10 +7922,10 @@
         <v>35</v>
       </c>
       <c r="L64" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="M64" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="M64" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="N64" s="12"/>
       <c r="O64" s="9"/>
@@ -7898,10 +7977,10 @@
     </row>
     <row r="65" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="10"/>
@@ -7912,10 +7991,10 @@
         <v>35</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="9"/>
@@ -7972,10 +8051,10 @@
     </row>
     <row r="66" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="10"/>
@@ -7983,13 +8062,13 @@
         <v>1</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G66" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="H66" s="11" t="s">
         <v>337</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>338</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="9" t="n">
@@ -7999,10 +8078,10 @@
         <v>35</v>
       </c>
       <c r="L66" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="M66" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="M66" s="9" t="s">
-        <v>340</v>
       </c>
       <c r="N66" s="12"/>
       <c r="O66" s="9"/>
@@ -8054,10 +8133,10 @@
     </row>
     <row r="67" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="10"/>
@@ -8065,13 +8144,13 @@
         <v>1</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G67" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="H67" s="11" t="s">
         <v>342</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>343</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9"/>
@@ -8128,10 +8207,10 @@
     </row>
     <row r="68" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="10"/>
@@ -8139,13 +8218,13 @@
         <v>1</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G68" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="H68" s="11" t="s">
         <v>345</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="9" t="n">
@@ -8155,10 +8234,10 @@
         <v>35</v>
       </c>
       <c r="L68" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="M68" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>348</v>
       </c>
       <c r="N68" s="12"/>
       <c r="O68" s="9"/>
@@ -8210,10 +8289,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="10"/>
@@ -8224,10 +8303,10 @@
         <v>38</v>
       </c>
       <c r="G69" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="H69" s="11" t="s">
         <v>350</v>
-      </c>
-      <c r="H69" s="11" t="s">
-        <v>351</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9"/>
@@ -8284,10 +8363,10 @@
     </row>
     <row r="70" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B70" s="20" t="s">
         <v>352</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>353</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="18"/>
@@ -8298,10 +8377,10 @@
         <v>38</v>
       </c>
       <c r="G70" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="H70" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="I70" s="18"/>
       <c r="J70" s="9" t="n">
@@ -8311,23 +8390,23 @@
         <v>74</v>
       </c>
       <c r="L70" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="M70" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="M70" s="9" t="s">
-        <v>357</v>
       </c>
       <c r="N70" s="19"/>
       <c r="O70" s="9" t="n">
         <v>9.5</v>
       </c>
       <c r="P70" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q70" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q70" s="9" t="s">
+      <c r="R70" s="9" t="s">
         <v>359</v>
-      </c>
-      <c r="R70" s="9" t="s">
-        <v>360</v>
       </c>
       <c r="S70" s="18"/>
       <c r="T70" s="9"/>
@@ -8374,10 +8453,10 @@
     </row>
     <row r="71" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="18"/>
@@ -8388,23 +8467,23 @@
         <v>74</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>363</v>
       </c>
       <c r="I71" s="18"/>
       <c r="J71" s="9" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L71" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L71" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M71" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N71" s="19"/>
       <c r="O71" s="9" t="n">
@@ -8458,10 +8537,10 @@
     </row>
     <row r="72" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="10"/>
@@ -8472,10 +8551,10 @@
         <v>38</v>
       </c>
       <c r="G72" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="H72" s="11" t="s">
         <v>366</v>
-      </c>
-      <c r="H72" s="11" t="s">
-        <v>367</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="9" t="n">
@@ -8485,10 +8564,10 @@
         <v>38</v>
       </c>
       <c r="L72" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="M72" s="9" t="s">
         <v>368</v>
-      </c>
-      <c r="M72" s="9" t="s">
-        <v>369</v>
       </c>
       <c r="N72" s="12"/>
       <c r="O72" s="9"/>
@@ -8540,10 +8619,10 @@
     </row>
     <row r="73" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="18"/>
@@ -8554,10 +8633,10 @@
         <v>38</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>372</v>
       </c>
       <c r="I73" s="18"/>
       <c r="J73" s="9" t="n">
@@ -8567,10 +8646,10 @@
         <v>38</v>
       </c>
       <c r="L73" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="M73" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>374</v>
       </c>
       <c r="N73" s="19"/>
       <c r="O73" s="9" t="n">
@@ -8624,10 +8703,10 @@
     </row>
     <row r="74" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="10"/>
@@ -8638,10 +8717,10 @@
         <v>38</v>
       </c>
       <c r="G74" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="H74" s="11" t="s">
         <v>376</v>
-      </c>
-      <c r="H74" s="11" t="s">
-        <v>377</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="9" t="n">
@@ -8651,10 +8730,10 @@
         <v>35</v>
       </c>
       <c r="L74" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="M74" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="M74" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="N74" s="12"/>
       <c r="O74" s="9"/>
@@ -8706,10 +8785,10 @@
     </row>
     <row r="75" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="10"/>
@@ -8720,10 +8799,10 @@
         <v>74</v>
       </c>
       <c r="G75" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="H75" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="H75" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9" t="n">
@@ -8733,10 +8812,10 @@
         <v>35</v>
       </c>
       <c r="L75" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="M75" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>384</v>
       </c>
       <c r="N75" s="12"/>
       <c r="O75" s="9"/>
@@ -8788,10 +8867,10 @@
     </row>
     <row r="76" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="10"/>
@@ -8802,23 +8881,23 @@
         <v>74</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="9" t="n">
         <v>9</v>
       </c>
       <c r="K76" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L76" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L76" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M76" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N76" s="12"/>
       <c r="O76" s="9"/>
@@ -8870,10 +8949,10 @@
     </row>
     <row r="77" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="10"/>
@@ -8884,10 +8963,10 @@
         <v>74</v>
       </c>
       <c r="G77" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="H77" s="11" t="s">
         <v>389</v>
-      </c>
-      <c r="H77" s="11" t="s">
-        <v>390</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9" t="n">
@@ -8897,10 +8976,10 @@
         <v>35</v>
       </c>
       <c r="L77" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="M77" s="9" t="s">
         <v>391</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>392</v>
       </c>
       <c r="N77" s="12"/>
       <c r="O77" s="9"/>
@@ -8952,10 +9031,10 @@
     </row>
     <row r="78" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="10"/>
@@ -8966,10 +9045,10 @@
         <v>38</v>
       </c>
       <c r="G78" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="H78" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="H78" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="11" t="n">
@@ -8979,10 +9058,10 @@
         <v>35</v>
       </c>
       <c r="L78" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="M78" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="M78" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="N78" s="12"/>
       <c r="O78" s="9"/>
@@ -9034,10 +9113,10 @@
     </row>
     <row r="79" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="10"/>
@@ -9048,10 +9127,10 @@
         <v>74</v>
       </c>
       <c r="G79" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="H79" s="11" t="s">
         <v>399</v>
-      </c>
-      <c r="H79" s="11" t="s">
-        <v>400</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9" t="n">
@@ -9061,10 +9140,10 @@
         <v>38</v>
       </c>
       <c r="L79" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="M79" s="9" t="s">
         <v>401</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>402</v>
       </c>
       <c r="N79" s="12"/>
       <c r="O79" s="9"/>
@@ -9116,10 +9195,10 @@
     </row>
     <row r="80" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="10"/>
@@ -9130,10 +9209,10 @@
         <v>74</v>
       </c>
       <c r="G80" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="H80" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="H80" s="11" t="s">
-        <v>405</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="11" t="n">
@@ -9143,23 +9222,23 @@
         <v>38</v>
       </c>
       <c r="L80" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="M80" s="9" t="s">
         <v>406</v>
-      </c>
-      <c r="M80" s="9" t="s">
-        <v>407</v>
       </c>
       <c r="N80" s="12"/>
       <c r="O80" s="9" t="n">
         <v>9.5</v>
       </c>
       <c r="P80" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q80" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q80" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R80" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="S80" s="10"/>
       <c r="T80" s="9"/>
@@ -9206,10 +9285,10 @@
     </row>
     <row r="81" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="10"/>
@@ -9220,10 +9299,10 @@
         <v>74</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9" t="n">
@@ -9233,23 +9312,23 @@
         <v>38</v>
       </c>
       <c r="L81" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="M81" s="9" t="s">
         <v>411</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>412</v>
       </c>
       <c r="N81" s="12"/>
       <c r="O81" s="9" t="n">
         <v>9.5</v>
       </c>
       <c r="P81" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q81" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q81" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R81" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S81" s="10"/>
       <c r="T81" s="9"/>
@@ -9296,10 +9375,10 @@
     </row>
     <row r="82" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="10"/>
@@ -9310,10 +9389,10 @@
         <v>38</v>
       </c>
       <c r="G82" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="H82" s="11" t="s">
         <v>415</v>
-      </c>
-      <c r="H82" s="11" t="s">
-        <v>416</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="9" t="n">
@@ -9323,10 +9402,10 @@
         <v>74</v>
       </c>
       <c r="L82" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="M82" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="M82" s="9" t="s">
-        <v>418</v>
       </c>
       <c r="N82" s="12"/>
       <c r="O82" s="9"/>
@@ -9378,10 +9457,10 @@
     </row>
     <row r="83" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="10"/>
@@ -9389,13 +9468,13 @@
         <v>1</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G83" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="H83" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="H83" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9"/>
@@ -9452,13 +9531,13 @@
     </row>
     <row r="84" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D84" s="10"/>
       <c r="E84" s="9" t="n">
@@ -9468,23 +9547,23 @@
         <v>38</v>
       </c>
       <c r="G84" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="H84" s="11" t="s">
         <v>423</v>
-      </c>
-      <c r="H84" s="11" t="s">
-        <v>424</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="9" t="n">
         <v>4</v>
       </c>
       <c r="K84" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L84" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="M84" s="9" t="s">
         <v>425</v>
-      </c>
-      <c r="M84" s="9" t="s">
-        <v>426</v>
       </c>
       <c r="N84" s="12"/>
       <c r="O84" s="9"/>
@@ -9536,10 +9615,10 @@
     </row>
     <row r="85" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="10"/>
@@ -9550,23 +9629,23 @@
         <v>74</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="11" t="n">
         <v>9.5</v>
       </c>
       <c r="K85" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L85" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L85" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M85" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N85" s="12"/>
       <c r="O85" s="9"/>
@@ -9618,10 +9697,10 @@
     </row>
     <row r="86" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="10"/>
@@ -9632,10 +9711,10 @@
         <v>74</v>
       </c>
       <c r="G86" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="H86" s="11" t="s">
         <v>431</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>432</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="9" t="n">
@@ -9645,23 +9724,23 @@
         <v>74</v>
       </c>
       <c r="L86" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="M86" s="9" t="s">
         <v>433</v>
-      </c>
-      <c r="M86" s="9" t="s">
-        <v>434</v>
       </c>
       <c r="N86" s="12"/>
       <c r="O86" s="11" t="n">
         <v>9.5</v>
       </c>
       <c r="P86" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q86" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q86" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R86" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S86" s="10"/>
       <c r="T86" s="9"/>
@@ -9708,10 +9787,10 @@
     </row>
     <row r="87" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="10"/>
@@ -9722,10 +9801,10 @@
         <v>74</v>
       </c>
       <c r="G87" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="H87" s="11" t="s">
         <v>436</v>
-      </c>
-      <c r="H87" s="11" t="s">
-        <v>437</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9"/>
@@ -9782,10 +9861,10 @@
     </row>
     <row r="88" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="10"/>
@@ -9796,10 +9875,10 @@
         <v>74</v>
       </c>
       <c r="G88" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="H88" s="11" t="s">
         <v>439</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>440</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="9" t="n">
@@ -9809,10 +9888,10 @@
         <v>74</v>
       </c>
       <c r="L88" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="M88" s="22" t="s">
         <v>441</v>
-      </c>
-      <c r="M88" s="22" t="s">
-        <v>442</v>
       </c>
       <c r="N88" s="12"/>
       <c r="O88" s="9"/>
@@ -9864,10 +9943,10 @@
     </row>
     <row r="89" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="10"/>
@@ -9878,10 +9957,10 @@
         <v>74</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9" t="n">
@@ -9891,10 +9970,10 @@
         <v>38</v>
       </c>
       <c r="L89" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="M89" s="9" t="s">
         <v>445</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>446</v>
       </c>
       <c r="N89" s="12"/>
       <c r="O89" s="9"/>
@@ -9946,10 +10025,10 @@
     </row>
     <row r="90" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="10"/>
@@ -9960,10 +10039,10 @@
         <v>74</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="9" t="n">
@@ -9973,10 +10052,10 @@
         <v>74</v>
       </c>
       <c r="L90" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="M90" s="9" t="s">
         <v>449</v>
-      </c>
-      <c r="M90" s="9" t="s">
-        <v>450</v>
       </c>
       <c r="N90" s="12"/>
       <c r="O90" s="9"/>
@@ -10028,10 +10107,10 @@
     </row>
     <row r="91" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="10"/>
@@ -10042,23 +10121,23 @@
         <v>74</v>
       </c>
       <c r="G91" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="H91" s="11" t="s">
         <v>452</v>
-      </c>
-      <c r="H91" s="11" t="s">
-        <v>453</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L91" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="M91" s="9" t="s">
         <v>454</v>
-      </c>
-      <c r="M91" s="9" t="s">
-        <v>455</v>
       </c>
       <c r="N91" s="12"/>
       <c r="O91" s="9"/>
@@ -10110,13 +10189,13 @@
     </row>
     <row r="92" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B92" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="B92" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>457</v>
       </c>
       <c r="D92" s="10"/>
       <c r="E92" s="9" t="n">
@@ -10126,10 +10205,10 @@
         <v>38</v>
       </c>
       <c r="G92" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H92" s="11" t="s">
         <v>458</v>
-      </c>
-      <c r="H92" s="11" t="s">
-        <v>459</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="9" t="n">
@@ -10139,10 +10218,10 @@
         <v>38</v>
       </c>
       <c r="L92" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="M92" s="9" t="s">
         <v>460</v>
-      </c>
-      <c r="M92" s="9" t="s">
-        <v>461</v>
       </c>
       <c r="N92" s="12"/>
       <c r="O92" s="9"/>
@@ -10194,10 +10273,10 @@
     </row>
     <row r="93" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="10"/>
@@ -10208,10 +10287,10 @@
         <v>74</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9" t="n">
@@ -10221,10 +10300,10 @@
         <v>35</v>
       </c>
       <c r="L93" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="M93" s="11" t="s">
         <v>464</v>
-      </c>
-      <c r="M93" s="11" t="s">
-        <v>465</v>
       </c>
       <c r="N93" s="12"/>
       <c r="O93" s="9"/>
@@ -10276,10 +10355,10 @@
     </row>
     <row r="94" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="10"/>
@@ -10290,10 +10369,10 @@
         <v>74</v>
       </c>
       <c r="G94" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="H94" s="11" t="s">
         <v>467</v>
-      </c>
-      <c r="H94" s="11" t="s">
-        <v>468</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="9" t="n">
@@ -10303,10 +10382,10 @@
         <v>35</v>
       </c>
       <c r="L94" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="M94" s="9" t="s">
         <v>469</v>
-      </c>
-      <c r="M94" s="9" t="s">
-        <v>470</v>
       </c>
       <c r="N94" s="12"/>
       <c r="O94" s="9"/>
@@ -10358,10 +10437,10 @@
     </row>
     <row r="95" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="10"/>
@@ -10372,23 +10451,23 @@
         <v>74</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9" t="n">
         <v>10</v>
       </c>
       <c r="K95" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L95" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L95" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M95" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N95" s="12"/>
       <c r="O95" s="9"/>
@@ -10440,10 +10519,10 @@
     </row>
     <row r="96" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="10"/>
@@ -10451,13 +10530,13 @@
         <v>1</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G96" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="H96" s="11" t="s">
         <v>475</v>
-      </c>
-      <c r="H96" s="11" t="s">
-        <v>476</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="9" t="n">
@@ -10467,10 +10546,10 @@
         <v>35</v>
       </c>
       <c r="L96" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="M96" s="9" t="s">
         <v>477</v>
-      </c>
-      <c r="M96" s="9" t="s">
-        <v>478</v>
       </c>
       <c r="N96" s="12"/>
       <c r="O96" s="9"/>
@@ -10522,10 +10601,10 @@
     </row>
     <row r="97" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="10"/>
@@ -10536,10 +10615,10 @@
         <v>74</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9" t="n">
@@ -10549,23 +10628,23 @@
         <v>35</v>
       </c>
       <c r="L97" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="M97" s="9" t="s">
         <v>481</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>482</v>
       </c>
       <c r="N97" s="12"/>
       <c r="O97" s="9" t="n">
         <v>11</v>
       </c>
       <c r="P97" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q97" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q97" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R97" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S97" s="10"/>
       <c r="T97" s="9"/>
@@ -10612,10 +10691,10 @@
     </row>
     <row r="98" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="10"/>
@@ -10626,10 +10705,10 @@
         <v>74</v>
       </c>
       <c r="G98" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="H98" s="11" t="s">
         <v>485</v>
-      </c>
-      <c r="H98" s="11" t="s">
-        <v>486</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="9"/>
@@ -10686,10 +10765,10 @@
     </row>
     <row r="99" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="10"/>
@@ -10700,10 +10779,10 @@
         <v>74</v>
       </c>
       <c r="G99" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="H99" s="11" t="s">
         <v>488</v>
-      </c>
-      <c r="H99" s="11" t="s">
-        <v>489</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9"/>
@@ -10760,10 +10839,10 @@
     </row>
     <row r="100" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="10"/>
@@ -10774,10 +10853,10 @@
         <v>74</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="9" t="n">
@@ -10787,10 +10866,10 @@
         <v>38</v>
       </c>
       <c r="L100" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="M100" s="9" t="s">
         <v>492</v>
-      </c>
-      <c r="M100" s="9" t="s">
-        <v>493</v>
       </c>
       <c r="N100" s="12"/>
       <c r="O100" s="9" t="n">
@@ -10800,10 +10879,10 @@
         <v>38</v>
       </c>
       <c r="Q100" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="R100" s="9" t="s">
         <v>494</v>
-      </c>
-      <c r="R100" s="9" t="s">
-        <v>495</v>
       </c>
       <c r="S100" s="10"/>
       <c r="T100" s="9"/>
@@ -10850,10 +10929,10 @@
     </row>
     <row r="101" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="10"/>
@@ -10864,23 +10943,23 @@
         <v>74</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9" t="n">
         <v>10</v>
       </c>
       <c r="K101" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L101" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L101" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M101" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N101" s="12"/>
       <c r="O101" s="9"/>
@@ -10932,10 +11011,10 @@
     </row>
     <row r="102" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="10"/>
@@ -10946,10 +11025,10 @@
         <v>74</v>
       </c>
       <c r="G102" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="H102" s="11" t="s">
         <v>500</v>
-      </c>
-      <c r="H102" s="11" t="s">
-        <v>501</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="9"/>
@@ -11006,10 +11085,10 @@
     </row>
     <row r="103" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="10"/>
@@ -11020,10 +11099,10 @@
         <v>38</v>
       </c>
       <c r="G103" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="H103" s="11" t="s">
         <v>503</v>
-      </c>
-      <c r="H103" s="11" t="s">
-        <v>504</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9" t="n">
@@ -11033,10 +11112,10 @@
         <v>35</v>
       </c>
       <c r="L103" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="M103" s="9" t="s">
         <v>505</v>
-      </c>
-      <c r="M103" s="9" t="s">
-        <v>506</v>
       </c>
       <c r="N103" s="12"/>
       <c r="O103" s="9"/>
@@ -11088,13 +11167,13 @@
     </row>
     <row r="104" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C104" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="B104" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>508</v>
       </c>
       <c r="D104" s="10"/>
       <c r="E104" s="9" t="n">
@@ -11104,10 +11183,10 @@
         <v>38</v>
       </c>
       <c r="G104" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="H104" s="11" t="s">
         <v>509</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>510</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="9" t="n">
@@ -11117,10 +11196,10 @@
         <v>35</v>
       </c>
       <c r="L104" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N104" s="12"/>
       <c r="O104" s="9"/>
@@ -11172,13 +11251,13 @@
     </row>
     <row r="105" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D105" s="10"/>
       <c r="E105" s="9" t="n">
@@ -11188,10 +11267,10 @@
         <v>74</v>
       </c>
       <c r="G105" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="H105" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="H105" s="11" t="s">
-        <v>514</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9" t="n">
@@ -11201,10 +11280,10 @@
         <v>38</v>
       </c>
       <c r="L105" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="M105" s="9" t="s">
         <v>515</v>
-      </c>
-      <c r="M105" s="9" t="s">
-        <v>516</v>
       </c>
       <c r="N105" s="12"/>
       <c r="O105" s="9"/>
@@ -11256,10 +11335,10 @@
     </row>
     <row r="106" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="10"/>
@@ -11270,10 +11349,10 @@
         <v>74</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="9" t="n">
@@ -11283,23 +11362,23 @@
         <v>38</v>
       </c>
       <c r="L106" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="M106" s="9" t="s">
         <v>519</v>
-      </c>
-      <c r="M106" s="9" t="s">
-        <v>520</v>
       </c>
       <c r="N106" s="12"/>
       <c r="O106" s="9" t="n">
         <v>10</v>
       </c>
       <c r="P106" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q106" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q106" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R106" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S106" s="10"/>
       <c r="T106" s="9"/>
@@ -11346,10 +11425,10 @@
     </row>
     <row r="107" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="10"/>
@@ -11360,23 +11439,23 @@
         <v>74</v>
       </c>
       <c r="G107" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="H107" s="11" t="s">
         <v>522</v>
-      </c>
-      <c r="H107" s="11" t="s">
-        <v>523</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L107" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L107" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M107" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="N107" s="12"/>
       <c r="O107" s="9"/>
@@ -11428,10 +11507,10 @@
     </row>
     <row r="108" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="18"/>
@@ -11442,10 +11521,10 @@
         <v>74</v>
       </c>
       <c r="G108" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="H108" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>527</v>
       </c>
       <c r="I108" s="18"/>
       <c r="J108" s="9" t="n">
@@ -11455,10 +11534,10 @@
         <v>35</v>
       </c>
       <c r="L108" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="M108" s="9" t="s">
         <v>528</v>
-      </c>
-      <c r="M108" s="9" t="s">
-        <v>529</v>
       </c>
       <c r="N108" s="19"/>
       <c r="O108" s="9" t="n">
@@ -11512,10 +11591,10 @@
     </row>
     <row r="109" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C109" s="11"/>
       <c r="D109" s="10"/>
@@ -11526,23 +11605,23 @@
         <v>74</v>
       </c>
       <c r="G109" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="H109" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H109" s="11" t="s">
-        <v>532</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="9" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L109" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L109" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M109" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N109" s="12"/>
       <c r="O109" s="9"/>
@@ -11594,10 +11673,10 @@
     </row>
     <row r="110" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="10"/>
@@ -11608,23 +11687,23 @@
         <v>74</v>
       </c>
       <c r="G110" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="H110" s="11" t="s">
         <v>535</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>536</v>
       </c>
       <c r="I110" s="10"/>
       <c r="J110" s="9" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L110" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L110" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M110" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N110" s="12"/>
       <c r="O110" s="9"/>
@@ -11676,10 +11755,10 @@
     </row>
     <row r="111" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="10"/>
@@ -11690,23 +11769,23 @@
         <v>74</v>
       </c>
       <c r="G111" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="H111" s="11" t="s">
         <v>538</v>
-      </c>
-      <c r="H111" s="11" t="s">
-        <v>539</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L111" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="L111" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="M111" s="11" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N111" s="12"/>
       <c r="O111" s="9"/>
@@ -11758,10 +11837,10 @@
     </row>
     <row r="112" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C112" s="11"/>
       <c r="D112" s="10"/>
@@ -11772,10 +11851,10 @@
         <v>74</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>543</v>
+        <v>488</v>
       </c>
       <c r="I112" s="10"/>
       <c r="J112" s="9"/>
@@ -11832,10 +11911,10 @@
     </row>
     <row r="113" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="10"/>
@@ -11846,10 +11925,10 @@
         <v>38</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9" t="n">
@@ -11859,10 +11938,10 @@
         <v>35</v>
       </c>
       <c r="L113" s="9" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M113" s="9" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N113" s="12"/>
       <c r="O113" s="9" t="n">
@@ -11872,10 +11951,10 @@
         <v>35</v>
       </c>
       <c r="Q113" s="9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="R113" s="9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="S113" s="10"/>
       <c r="T113" s="9"/>
@@ -11922,10 +12001,10 @@
     </row>
     <row r="114" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B114" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="10"/>
@@ -11936,10 +12015,10 @@
         <v>74</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I114" s="10"/>
       <c r="J114" s="9"/>
@@ -11996,10 +12075,10 @@
     </row>
     <row r="115" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="10"/>
@@ -12010,10 +12089,10 @@
         <v>38</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9" t="n">
@@ -12023,10 +12102,10 @@
         <v>74</v>
       </c>
       <c r="L115" s="9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="M115" s="11" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="N115" s="12"/>
       <c r="O115" s="9"/>
@@ -12078,10 +12157,10 @@
     </row>
     <row r="116" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="10"/>
@@ -12092,10 +12171,10 @@
         <v>74</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I116" s="10"/>
       <c r="J116" s="9" t="n">
@@ -12105,10 +12184,10 @@
         <v>35</v>
       </c>
       <c r="L116" s="9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M116" s="11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N116" s="12"/>
       <c r="O116" s="9"/>
@@ -12160,10 +12239,10 @@
     </row>
     <row r="117" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="10"/>
@@ -12174,36 +12253,36 @@
         <v>74</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9" t="n">
         <v>3</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M117" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="N117" s="12"/>
       <c r="O117" s="9" t="n">
         <v>10</v>
       </c>
       <c r="P117" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q117" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q117" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="R117" s="11" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="S117" s="10"/>
       <c r="T117" s="9"/>
@@ -12250,10 +12329,10 @@
     </row>
     <row r="118" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="10"/>
@@ -12264,10 +12343,10 @@
         <v>74</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="9" t="n">
@@ -12277,10 +12356,10 @@
         <v>38</v>
       </c>
       <c r="L118" s="9" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M118" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N118" s="12"/>
       <c r="O118" s="9"/>
@@ -12332,10 +12411,10 @@
     </row>
     <row r="119" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C119" s="11"/>
       <c r="D119" s="10"/>
@@ -12346,10 +12425,10 @@
         <v>74</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9"/>
@@ -12404,145 +12483,225 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="23"/>
-      <c r="B120" s="23"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="23"/>
-      <c r="E120" s="23"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="23"/>
-      <c r="I120" s="23"/>
-      <c r="J120" s="23"/>
-      <c r="K120" s="24"/>
-      <c r="L120" s="24"/>
-      <c r="M120" s="25"/>
-      <c r="N120" s="23"/>
-      <c r="O120" s="23"/>
-      <c r="P120" s="24"/>
-      <c r="Q120" s="24"/>
-      <c r="R120" s="23"/>
-      <c r="S120" s="23"/>
-      <c r="T120" s="23"/>
-      <c r="U120" s="23"/>
-      <c r="V120" s="23"/>
-      <c r="W120" s="23"/>
-      <c r="X120" s="23"/>
-      <c r="Y120" s="23"/>
-      <c r="Z120" s="23"/>
-      <c r="AA120" s="23"/>
-      <c r="AB120" s="23"/>
-      <c r="AC120" s="23"/>
-      <c r="AD120" s="23"/>
-      <c r="AE120" s="23"/>
-      <c r="AF120" s="23"/>
-      <c r="AG120" s="24"/>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="23"/>
-      <c r="B121" s="23"/>
-      <c r="C121" s="23"/>
-      <c r="D121" s="23"/>
-      <c r="E121" s="23"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="23"/>
-      <c r="I121" s="23"/>
-      <c r="J121" s="23"/>
-      <c r="K121" s="24"/>
-      <c r="L121" s="24"/>
-      <c r="M121" s="25"/>
-      <c r="N121" s="23"/>
-      <c r="O121" s="23"/>
-      <c r="P121" s="24"/>
-      <c r="Q121" s="24"/>
-      <c r="R121" s="23"/>
-      <c r="S121" s="23"/>
-      <c r="T121" s="23"/>
-      <c r="U121" s="23"/>
-      <c r="V121" s="23"/>
-      <c r="W121" s="23"/>
-      <c r="X121" s="23"/>
-      <c r="Y121" s="23"/>
-      <c r="Z121" s="23"/>
-      <c r="AA121" s="23"/>
-      <c r="AB121" s="23"/>
-      <c r="AC121" s="23"/>
-      <c r="AD121" s="23"/>
-      <c r="AE121" s="23"/>
-      <c r="AF121" s="23"/>
-      <c r="AG121" s="24"/>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="23"/>
-      <c r="B122" s="23"/>
-      <c r="C122" s="23"/>
-      <c r="D122" s="23"/>
-      <c r="E122" s="23"/>
-      <c r="F122" s="24"/>
-      <c r="G122" s="24"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-      <c r="J122" s="23"/>
-      <c r="K122" s="24"/>
-      <c r="L122" s="24"/>
-      <c r="M122" s="25"/>
-      <c r="N122" s="23"/>
-      <c r="O122" s="23"/>
-      <c r="P122" s="24"/>
-      <c r="Q122" s="24"/>
-      <c r="R122" s="23"/>
-      <c r="S122" s="23"/>
-      <c r="T122" s="23"/>
-      <c r="U122" s="23"/>
-      <c r="V122" s="23"/>
-      <c r="W122" s="23"/>
-      <c r="X122" s="23"/>
-      <c r="Y122" s="23"/>
-      <c r="Z122" s="23"/>
-      <c r="AA122" s="23"/>
-      <c r="AB122" s="23"/>
-      <c r="AC122" s="23"/>
-      <c r="AD122" s="23"/>
-      <c r="AE122" s="23"/>
-      <c r="AF122" s="23"/>
-      <c r="AG122" s="24"/>
-    </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="23"/>
-      <c r="B123" s="23"/>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-      <c r="E123" s="23"/>
-      <c r="F123" s="24"/>
-      <c r="G123" s="24"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="24"/>
-      <c r="L123" s="24"/>
-      <c r="M123" s="25"/>
-      <c r="N123" s="23"/>
-      <c r="O123" s="23"/>
-      <c r="P123" s="24"/>
-      <c r="Q123" s="24"/>
-      <c r="R123" s="23"/>
-      <c r="S123" s="23"/>
-      <c r="T123" s="23"/>
-      <c r="U123" s="23"/>
-      <c r="V123" s="23"/>
-      <c r="W123" s="23"/>
-      <c r="X123" s="23"/>
-      <c r="Y123" s="23"/>
-      <c r="Z123" s="23"/>
-      <c r="AA123" s="23"/>
-      <c r="AB123" s="23"/>
-      <c r="AC123" s="23"/>
-      <c r="AD123" s="23"/>
-      <c r="AE123" s="23"/>
-      <c r="AF123" s="23"/>
-      <c r="AG123" s="24"/>
+    <row r="120" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C120" s="11"/>
+      <c r="D120" s="10"/>
+      <c r="E120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="I120" s="10"/>
+      <c r="J120" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L120" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="M120" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="N120" s="12"/>
+      <c r="O120" s="9"/>
+      <c r="P120" s="9"/>
+      <c r="Q120" s="9"/>
+      <c r="R120" s="11"/>
+      <c r="S120" s="10"/>
+      <c r="T120" s="9"/>
+      <c r="U120" s="9"/>
+      <c r="V120" s="9"/>
+      <c r="W120" s="9"/>
+      <c r="X120" s="9"/>
+      <c r="Y120" s="9"/>
+      <c r="Z120" s="9"/>
+      <c r="AA120" s="9"/>
+      <c r="AB120" s="9"/>
+      <c r="AC120" s="9"/>
+      <c r="AD120" s="9"/>
+      <c r="AE120" s="9"/>
+      <c r="AF120" s="9"/>
+      <c r="AG120" s="11"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C121" s="11"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G121" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="I121" s="10"/>
+      <c r="J121" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K121" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="N121" s="12"/>
+      <c r="O121" s="9"/>
+      <c r="P121" s="9"/>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="11"/>
+      <c r="S121" s="10"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="9"/>
+      <c r="W121" s="9"/>
+      <c r="X121" s="9"/>
+      <c r="Y121" s="9"/>
+      <c r="Z121" s="9"/>
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+      <c r="AD121" s="9"/>
+      <c r="AE121" s="9"/>
+      <c r="AF121" s="9"/>
+      <c r="AG121" s="11"/>
+    </row>
+    <row r="122" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C122" s="11"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G122" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="I122" s="10"/>
+      <c r="J122" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K122" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="M122" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="N122" s="12"/>
+      <c r="O122" s="9"/>
+      <c r="P122" s="9"/>
+      <c r="Q122" s="9"/>
+      <c r="R122" s="11"/>
+      <c r="S122" s="10"/>
+      <c r="T122" s="9"/>
+      <c r="U122" s="9"/>
+      <c r="V122" s="9"/>
+      <c r="W122" s="9"/>
+      <c r="X122" s="9"/>
+      <c r="Y122" s="9"/>
+      <c r="Z122" s="9"/>
+      <c r="AA122" s="9"/>
+      <c r="AB122" s="9"/>
+      <c r="AC122" s="9"/>
+      <c r="AD122" s="9"/>
+      <c r="AE122" s="9"/>
+      <c r="AF122" s="9"/>
+      <c r="AG122" s="11"/>
+    </row>
+    <row r="123" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C123" s="11"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G123" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="I123" s="10"/>
+      <c r="J123" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="M123" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="N123" s="12"/>
+      <c r="O123" s="9"/>
+      <c r="P123" s="9"/>
+      <c r="Q123" s="9"/>
+      <c r="R123" s="11"/>
+      <c r="S123" s="10"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
+      <c r="V123" s="9"/>
+      <c r="W123" s="9"/>
+      <c r="X123" s="9"/>
+      <c r="Y123" s="9"/>
+      <c r="Z123" s="9"/>
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="9"/>
+      <c r="AD123" s="9"/>
+      <c r="AE123" s="9"/>
+      <c r="AF123" s="9"/>
+      <c r="AG123" s="11"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="23"/>
@@ -15188,21 +15347,21 @@
       <formula>NOT(ISERROR(SEARCH("Spell",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120:B198">
+  <conditionalFormatting sqref="B124:B198">
     <cfRule type="containsText" priority="7" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Accessory" dxfId="17">
-      <formula>NOT(ISERROR(SEARCH("Accessory",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Accessory",B124)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="8" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Armour" dxfId="18">
-      <formula>NOT(ISERROR(SEARCH("Armour",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Armour",B124)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="9" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Equipment" dxfId="19">
-      <formula>NOT(ISERROR(SEARCH("Equipment",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Equipment",B124)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="10" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Impression" dxfId="20">
-      <formula>NOT(ISERROR(SEARCH("Impression",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Impression",B124)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="11" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="Spell" dxfId="21">
-      <formula>NOT(ISERROR(SEARCH("Spell",B120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Spell",B124)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -1653,35 +1653,7 @@
     <t xml:space="preserve">&lt;b&gt;Pop: Exhaust&lt;/b&gt;</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Burst one target puffball or all </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">puffballs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">on the map. Adjacent beings take 5 damage and terrain is destroyed, including walls.</t>
-    </r>
+    <t xml:space="preserve">Burst one target puffball or all puffballs on the map. Adjacent beings take 5 damage and terrain is destroyed, including walls.</t>
   </si>
   <si>
     <t xml:space="preserve">Pulsing Heartstone</t>
@@ -1693,25 +1665,7 @@
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Living Rhythm&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">At the end of your turn, if there is at least one crystal on the map,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> you gain up to 3 temporary composure at the end of your turn.</t>
-    </r>
+    <t xml:space="preserve">At the end of your turn, if there is at least one crystal on the map, you gain up to 3 temporary composure at the end of your turn.</t>
   </si>
   <si>
     <t xml:space="preserve">Quartz Seed</t>
@@ -1912,7 +1866,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1941,12 +1895,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2066,7 +2014,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2079,7 +2027,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2156,10 +2104,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2744,8 +2688,7 @@
   <dimension ref="A1:AH200"/>
   <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="1.44"/>
@@ -2874,7 +2817,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -3331,7 +3274,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -3425,7 +3368,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
         <v>81</v>
       </c>
@@ -3680,7 +3623,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -4207,6 +4150,9 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="B17" s="8" t="s">
         <v>135</v>
       </c>
@@ -4551,7 +4497,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -5168,7 +5114,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -6479,7 +6425,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -6714,7 +6660,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -7177,7 +7123,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -7418,7 +7364,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -8010,7 +7956,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -8251,7 +8197,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -8328,7 +8274,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -8386,7 +8332,7 @@
       <c r="AH69" s="12"/>
     </row>
     <row r="70" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+      <c r="A70" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -8537,7 +8483,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -8714,7 +8660,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -9211,7 +9157,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -9470,7 +9416,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -9717,7 +9663,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -9775,7 +9721,7 @@
       <c r="AH86" s="12"/>
     </row>
     <row r="87" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -9868,6 +9814,9 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="B88" s="8" t="s">
         <v>439</v>
       </c>
@@ -10124,7 +10073,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="n">
+      <c r="A91" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -10255,7 +10204,7 @@
       <c r="AG92" s="10"/>
       <c r="AH92" s="12"/>
     </row>
-    <row r="93" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="8" t="s">
         <v>461</v>
       </c>
@@ -10914,7 +10863,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="n">
+      <c r="A101" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -11237,7 +11186,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="n">
+      <c r="A105" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -11412,7 +11361,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="n">
+      <c r="A107" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B107" s="8" t="s">
@@ -11488,7 +11437,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="8" t="s">
         <v>525</v>
       </c>
@@ -11605,7 +11554,7 @@
       <c r="M109" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="N109" s="23" t="s">
+      <c r="N109" s="14" t="s">
         <v>533</v>
       </c>
       <c r="O109" s="13"/>
@@ -11657,7 +11606,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="n">
+      <c r="A110" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -11915,8 +11864,8 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="n">
+    <row r="113" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B113" s="8" t="s">
@@ -11993,7 +11942,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="n">
+      <c r="A114" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -12078,7 +12027,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="n">
+      <c r="A115" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B115" s="8" t="s">
@@ -12847,7 +12796,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="n">
+      <c r="A125" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B125" s="8" t="s">
@@ -12924,2629 +12873,2629 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="24"/>
-      <c r="C126" s="24"/>
-      <c r="D126" s="24"/>
-      <c r="E126" s="24"/>
-      <c r="F126" s="24"/>
-      <c r="G126" s="25"/>
-      <c r="H126" s="25"/>
-      <c r="I126" s="24"/>
-      <c r="J126" s="24"/>
-      <c r="K126" s="24"/>
-      <c r="L126" s="25"/>
-      <c r="M126" s="25"/>
-      <c r="N126" s="26"/>
-      <c r="O126" s="24"/>
-      <c r="P126" s="24"/>
-      <c r="Q126" s="25"/>
-      <c r="R126" s="25"/>
-      <c r="S126" s="24"/>
-      <c r="T126" s="24"/>
-      <c r="U126" s="24"/>
-      <c r="V126" s="24"/>
-      <c r="W126" s="24"/>
-      <c r="X126" s="24"/>
-      <c r="Y126" s="24"/>
-      <c r="Z126" s="24"/>
-      <c r="AA126" s="24"/>
-      <c r="AB126" s="24"/>
-      <c r="AC126" s="24"/>
-      <c r="AD126" s="24"/>
-      <c r="AE126" s="24"/>
-      <c r="AF126" s="24"/>
-      <c r="AG126" s="24"/>
-      <c r="AH126" s="25"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="23"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
+      <c r="G126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="23"/>
+      <c r="J126" s="23"/>
+      <c r="K126" s="23"/>
+      <c r="L126" s="24"/>
+      <c r="M126" s="24"/>
+      <c r="N126" s="25"/>
+      <c r="O126" s="23"/>
+      <c r="P126" s="23"/>
+      <c r="Q126" s="24"/>
+      <c r="R126" s="24"/>
+      <c r="S126" s="23"/>
+      <c r="T126" s="23"/>
+      <c r="U126" s="23"/>
+      <c r="V126" s="23"/>
+      <c r="W126" s="23"/>
+      <c r="X126" s="23"/>
+      <c r="Y126" s="23"/>
+      <c r="Z126" s="23"/>
+      <c r="AA126" s="23"/>
+      <c r="AB126" s="23"/>
+      <c r="AC126" s="23"/>
+      <c r="AD126" s="23"/>
+      <c r="AE126" s="23"/>
+      <c r="AF126" s="23"/>
+      <c r="AG126" s="23"/>
+      <c r="AH126" s="24"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
-      <c r="D127" s="24"/>
-      <c r="E127" s="24"/>
-      <c r="F127" s="24"/>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="24"/>
-      <c r="K127" s="24"/>
-      <c r="L127" s="25"/>
-      <c r="M127" s="25"/>
-      <c r="N127" s="26"/>
-      <c r="O127" s="24"/>
-      <c r="P127" s="24"/>
-      <c r="Q127" s="25"/>
-      <c r="R127" s="25"/>
-      <c r="S127" s="24"/>
-      <c r="T127" s="24"/>
-      <c r="U127" s="24"/>
-      <c r="V127" s="24"/>
-      <c r="W127" s="24"/>
-      <c r="X127" s="24"/>
-      <c r="Y127" s="24"/>
-      <c r="Z127" s="24"/>
-      <c r="AA127" s="24"/>
-      <c r="AB127" s="24"/>
-      <c r="AC127" s="24"/>
-      <c r="AD127" s="24"/>
-      <c r="AE127" s="24"/>
-      <c r="AF127" s="24"/>
-      <c r="AG127" s="24"/>
-      <c r="AH127" s="25"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="23"/>
+      <c r="K127" s="23"/>
+      <c r="L127" s="24"/>
+      <c r="M127" s="24"/>
+      <c r="N127" s="25"/>
+      <c r="O127" s="23"/>
+      <c r="P127" s="23"/>
+      <c r="Q127" s="24"/>
+      <c r="R127" s="24"/>
+      <c r="S127" s="23"/>
+      <c r="T127" s="23"/>
+      <c r="U127" s="23"/>
+      <c r="V127" s="23"/>
+      <c r="W127" s="23"/>
+      <c r="X127" s="23"/>
+      <c r="Y127" s="23"/>
+      <c r="Z127" s="23"/>
+      <c r="AA127" s="23"/>
+      <c r="AB127" s="23"/>
+      <c r="AC127" s="23"/>
+      <c r="AD127" s="23"/>
+      <c r="AE127" s="23"/>
+      <c r="AF127" s="23"/>
+      <c r="AG127" s="23"/>
+      <c r="AH127" s="24"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="24"/>
-      <c r="C128" s="24"/>
-      <c r="D128" s="24"/>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="24"/>
-      <c r="K128" s="24"/>
-      <c r="L128" s="25"/>
-      <c r="M128" s="25"/>
-      <c r="N128" s="26"/>
-      <c r="O128" s="24"/>
-      <c r="P128" s="24"/>
-      <c r="Q128" s="25"/>
-      <c r="R128" s="25"/>
-      <c r="S128" s="24"/>
-      <c r="T128" s="24"/>
-      <c r="U128" s="24"/>
-      <c r="V128" s="24"/>
-      <c r="W128" s="24"/>
-      <c r="X128" s="24"/>
-      <c r="Y128" s="24"/>
-      <c r="Z128" s="24"/>
-      <c r="AA128" s="24"/>
-      <c r="AB128" s="24"/>
-      <c r="AC128" s="24"/>
-      <c r="AD128" s="24"/>
-      <c r="AE128" s="24"/>
-      <c r="AF128" s="24"/>
-      <c r="AG128" s="24"/>
-      <c r="AH128" s="25"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="23"/>
+      <c r="K128" s="23"/>
+      <c r="L128" s="24"/>
+      <c r="M128" s="24"/>
+      <c r="N128" s="25"/>
+      <c r="O128" s="23"/>
+      <c r="P128" s="23"/>
+      <c r="Q128" s="24"/>
+      <c r="R128" s="24"/>
+      <c r="S128" s="23"/>
+      <c r="T128" s="23"/>
+      <c r="U128" s="23"/>
+      <c r="V128" s="23"/>
+      <c r="W128" s="23"/>
+      <c r="X128" s="23"/>
+      <c r="Y128" s="23"/>
+      <c r="Z128" s="23"/>
+      <c r="AA128" s="23"/>
+      <c r="AB128" s="23"/>
+      <c r="AC128" s="23"/>
+      <c r="AD128" s="23"/>
+      <c r="AE128" s="23"/>
+      <c r="AF128" s="23"/>
+      <c r="AG128" s="23"/>
+      <c r="AH128" s="24"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="24"/>
-      <c r="C129" s="24"/>
-      <c r="D129" s="24"/>
-      <c r="E129" s="24"/>
-      <c r="F129" s="24"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="25"/>
-      <c r="I129" s="24"/>
-      <c r="J129" s="24"/>
-      <c r="K129" s="24"/>
-      <c r="L129" s="25"/>
-      <c r="M129" s="25"/>
-      <c r="N129" s="26"/>
-      <c r="O129" s="24"/>
-      <c r="P129" s="24"/>
-      <c r="Q129" s="25"/>
-      <c r="R129" s="25"/>
-      <c r="S129" s="24"/>
-      <c r="T129" s="24"/>
-      <c r="U129" s="24"/>
-      <c r="V129" s="24"/>
-      <c r="W129" s="24"/>
-      <c r="X129" s="24"/>
-      <c r="Y129" s="24"/>
-      <c r="Z129" s="24"/>
-      <c r="AA129" s="24"/>
-      <c r="AB129" s="24"/>
-      <c r="AC129" s="24"/>
-      <c r="AD129" s="24"/>
-      <c r="AE129" s="24"/>
-      <c r="AF129" s="24"/>
-      <c r="AG129" s="24"/>
-      <c r="AH129" s="25"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
+      <c r="F129" s="23"/>
+      <c r="G129" s="24"/>
+      <c r="H129" s="24"/>
+      <c r="I129" s="23"/>
+      <c r="J129" s="23"/>
+      <c r="K129" s="23"/>
+      <c r="L129" s="24"/>
+      <c r="M129" s="24"/>
+      <c r="N129" s="25"/>
+      <c r="O129" s="23"/>
+      <c r="P129" s="23"/>
+      <c r="Q129" s="24"/>
+      <c r="R129" s="24"/>
+      <c r="S129" s="23"/>
+      <c r="T129" s="23"/>
+      <c r="U129" s="23"/>
+      <c r="V129" s="23"/>
+      <c r="W129" s="23"/>
+      <c r="X129" s="23"/>
+      <c r="Y129" s="23"/>
+      <c r="Z129" s="23"/>
+      <c r="AA129" s="23"/>
+      <c r="AB129" s="23"/>
+      <c r="AC129" s="23"/>
+      <c r="AD129" s="23"/>
+      <c r="AE129" s="23"/>
+      <c r="AF129" s="23"/>
+      <c r="AG129" s="23"/>
+      <c r="AH129" s="24"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="24"/>
-      <c r="C130" s="24"/>
-      <c r="D130" s="24"/>
-      <c r="E130" s="24"/>
-      <c r="F130" s="24"/>
-      <c r="G130" s="25"/>
-      <c r="H130" s="25"/>
-      <c r="I130" s="24"/>
-      <c r="J130" s="24"/>
-      <c r="K130" s="24"/>
-      <c r="L130" s="25"/>
-      <c r="M130" s="25"/>
-      <c r="N130" s="26"/>
-      <c r="O130" s="24"/>
-      <c r="P130" s="24"/>
-      <c r="Q130" s="25"/>
-      <c r="R130" s="25"/>
-      <c r="S130" s="24"/>
-      <c r="T130" s="24"/>
-      <c r="U130" s="24"/>
-      <c r="V130" s="24"/>
-      <c r="W130" s="24"/>
-      <c r="X130" s="24"/>
-      <c r="Y130" s="24"/>
-      <c r="Z130" s="24"/>
-      <c r="AA130" s="24"/>
-      <c r="AB130" s="24"/>
-      <c r="AC130" s="24"/>
-      <c r="AD130" s="24"/>
-      <c r="AE130" s="24"/>
-      <c r="AF130" s="24"/>
-      <c r="AG130" s="24"/>
-      <c r="AH130" s="25"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23"/>
+      <c r="D130" s="23"/>
+      <c r="E130" s="23"/>
+      <c r="F130" s="23"/>
+      <c r="G130" s="24"/>
+      <c r="H130" s="24"/>
+      <c r="I130" s="23"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="23"/>
+      <c r="L130" s="24"/>
+      <c r="M130" s="24"/>
+      <c r="N130" s="25"/>
+      <c r="O130" s="23"/>
+      <c r="P130" s="23"/>
+      <c r="Q130" s="24"/>
+      <c r="R130" s="24"/>
+      <c r="S130" s="23"/>
+      <c r="T130" s="23"/>
+      <c r="U130" s="23"/>
+      <c r="V130" s="23"/>
+      <c r="W130" s="23"/>
+      <c r="X130" s="23"/>
+      <c r="Y130" s="23"/>
+      <c r="Z130" s="23"/>
+      <c r="AA130" s="23"/>
+      <c r="AB130" s="23"/>
+      <c r="AC130" s="23"/>
+      <c r="AD130" s="23"/>
+      <c r="AE130" s="23"/>
+      <c r="AF130" s="23"/>
+      <c r="AG130" s="23"/>
+      <c r="AH130" s="24"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="24"/>
-      <c r="C131" s="24"/>
-      <c r="D131" s="24"/>
-      <c r="E131" s="24"/>
-      <c r="F131" s="24"/>
-      <c r="G131" s="25"/>
-      <c r="H131" s="25"/>
-      <c r="I131" s="24"/>
-      <c r="J131" s="24"/>
-      <c r="K131" s="24"/>
-      <c r="L131" s="25"/>
-      <c r="M131" s="25"/>
-      <c r="N131" s="26"/>
-      <c r="O131" s="24"/>
-      <c r="P131" s="24"/>
-      <c r="Q131" s="25"/>
-      <c r="R131" s="25"/>
-      <c r="S131" s="24"/>
-      <c r="T131" s="24"/>
-      <c r="U131" s="24"/>
-      <c r="V131" s="24"/>
-      <c r="W131" s="24"/>
-      <c r="X131" s="24"/>
-      <c r="Y131" s="24"/>
-      <c r="Z131" s="24"/>
-      <c r="AA131" s="24"/>
-      <c r="AB131" s="24"/>
-      <c r="AC131" s="24"/>
-      <c r="AD131" s="24"/>
-      <c r="AE131" s="24"/>
-      <c r="AF131" s="24"/>
-      <c r="AG131" s="24"/>
-      <c r="AH131" s="25"/>
+      <c r="B131" s="23"/>
+      <c r="C131" s="23"/>
+      <c r="D131" s="23"/>
+      <c r="E131" s="23"/>
+      <c r="F131" s="23"/>
+      <c r="G131" s="24"/>
+      <c r="H131" s="24"/>
+      <c r="I131" s="23"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="23"/>
+      <c r="L131" s="24"/>
+      <c r="M131" s="24"/>
+      <c r="N131" s="25"/>
+      <c r="O131" s="23"/>
+      <c r="P131" s="23"/>
+      <c r="Q131" s="24"/>
+      <c r="R131" s="24"/>
+      <c r="S131" s="23"/>
+      <c r="T131" s="23"/>
+      <c r="U131" s="23"/>
+      <c r="V131" s="23"/>
+      <c r="W131" s="23"/>
+      <c r="X131" s="23"/>
+      <c r="Y131" s="23"/>
+      <c r="Z131" s="23"/>
+      <c r="AA131" s="23"/>
+      <c r="AB131" s="23"/>
+      <c r="AC131" s="23"/>
+      <c r="AD131" s="23"/>
+      <c r="AE131" s="23"/>
+      <c r="AF131" s="23"/>
+      <c r="AG131" s="23"/>
+      <c r="AH131" s="24"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
-      <c r="I132" s="24"/>
-      <c r="J132" s="24"/>
-      <c r="K132" s="24"/>
-      <c r="L132" s="25"/>
-      <c r="M132" s="25"/>
-      <c r="N132" s="26"/>
-      <c r="O132" s="24"/>
-      <c r="P132" s="24"/>
-      <c r="Q132" s="25"/>
-      <c r="R132" s="25"/>
-      <c r="S132" s="24"/>
-      <c r="T132" s="24"/>
-      <c r="U132" s="24"/>
-      <c r="V132" s="24"/>
-      <c r="W132" s="24"/>
-      <c r="X132" s="24"/>
-      <c r="Y132" s="24"/>
-      <c r="Z132" s="24"/>
-      <c r="AA132" s="24"/>
-      <c r="AB132" s="24"/>
-      <c r="AC132" s="24"/>
-      <c r="AD132" s="24"/>
-      <c r="AE132" s="24"/>
-      <c r="AF132" s="24"/>
-      <c r="AG132" s="24"/>
-      <c r="AH132" s="25"/>
+      <c r="B132" s="23"/>
+      <c r="C132" s="23"/>
+      <c r="D132" s="23"/>
+      <c r="E132" s="23"/>
+      <c r="F132" s="23"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="23"/>
+      <c r="J132" s="23"/>
+      <c r="K132" s="23"/>
+      <c r="L132" s="24"/>
+      <c r="M132" s="24"/>
+      <c r="N132" s="25"/>
+      <c r="O132" s="23"/>
+      <c r="P132" s="23"/>
+      <c r="Q132" s="24"/>
+      <c r="R132" s="24"/>
+      <c r="S132" s="23"/>
+      <c r="T132" s="23"/>
+      <c r="U132" s="23"/>
+      <c r="V132" s="23"/>
+      <c r="W132" s="23"/>
+      <c r="X132" s="23"/>
+      <c r="Y132" s="23"/>
+      <c r="Z132" s="23"/>
+      <c r="AA132" s="23"/>
+      <c r="AB132" s="23"/>
+      <c r="AC132" s="23"/>
+      <c r="AD132" s="23"/>
+      <c r="AE132" s="23"/>
+      <c r="AF132" s="23"/>
+      <c r="AG132" s="23"/>
+      <c r="AH132" s="24"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="24"/>
-      <c r="C133" s="24"/>
-      <c r="D133" s="24"/>
-      <c r="E133" s="24"/>
-      <c r="F133" s="24"/>
-      <c r="G133" s="25"/>
-      <c r="H133" s="25"/>
-      <c r="I133" s="24"/>
-      <c r="J133" s="24"/>
-      <c r="K133" s="24"/>
-      <c r="L133" s="25"/>
-      <c r="M133" s="25"/>
-      <c r="N133" s="26"/>
-      <c r="O133" s="24"/>
-      <c r="P133" s="24"/>
-      <c r="Q133" s="25"/>
-      <c r="R133" s="25"/>
-      <c r="S133" s="24"/>
-      <c r="T133" s="24"/>
-      <c r="U133" s="24"/>
-      <c r="V133" s="24"/>
-      <c r="W133" s="24"/>
-      <c r="X133" s="24"/>
-      <c r="Y133" s="24"/>
-      <c r="Z133" s="24"/>
-      <c r="AA133" s="24"/>
-      <c r="AB133" s="24"/>
-      <c r="AC133" s="24"/>
-      <c r="AD133" s="24"/>
-      <c r="AE133" s="24"/>
-      <c r="AF133" s="24"/>
-      <c r="AG133" s="24"/>
-      <c r="AH133" s="25"/>
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="24"/>
+      <c r="H133" s="24"/>
+      <c r="I133" s="23"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="23"/>
+      <c r="L133" s="24"/>
+      <c r="M133" s="24"/>
+      <c r="N133" s="25"/>
+      <c r="O133" s="23"/>
+      <c r="P133" s="23"/>
+      <c r="Q133" s="24"/>
+      <c r="R133" s="24"/>
+      <c r="S133" s="23"/>
+      <c r="T133" s="23"/>
+      <c r="U133" s="23"/>
+      <c r="V133" s="23"/>
+      <c r="W133" s="23"/>
+      <c r="X133" s="23"/>
+      <c r="Y133" s="23"/>
+      <c r="Z133" s="23"/>
+      <c r="AA133" s="23"/>
+      <c r="AB133" s="23"/>
+      <c r="AC133" s="23"/>
+      <c r="AD133" s="23"/>
+      <c r="AE133" s="23"/>
+      <c r="AF133" s="23"/>
+      <c r="AG133" s="23"/>
+      <c r="AH133" s="24"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="24"/>
-      <c r="C134" s="24"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="25"/>
-      <c r="H134" s="25"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="24"/>
-      <c r="K134" s="24"/>
-      <c r="L134" s="25"/>
-      <c r="M134" s="25"/>
-      <c r="N134" s="26"/>
-      <c r="O134" s="24"/>
-      <c r="P134" s="24"/>
-      <c r="Q134" s="25"/>
-      <c r="R134" s="25"/>
-      <c r="S134" s="24"/>
-      <c r="T134" s="24"/>
-      <c r="U134" s="24"/>
-      <c r="V134" s="24"/>
-      <c r="W134" s="24"/>
-      <c r="X134" s="24"/>
-      <c r="Y134" s="24"/>
-      <c r="Z134" s="24"/>
-      <c r="AA134" s="24"/>
-      <c r="AB134" s="24"/>
-      <c r="AC134" s="24"/>
-      <c r="AD134" s="24"/>
-      <c r="AE134" s="24"/>
-      <c r="AF134" s="24"/>
-      <c r="AG134" s="24"/>
-      <c r="AH134" s="25"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="23"/>
+      <c r="E134" s="23"/>
+      <c r="F134" s="23"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="23"/>
+      <c r="J134" s="23"/>
+      <c r="K134" s="23"/>
+      <c r="L134" s="24"/>
+      <c r="M134" s="24"/>
+      <c r="N134" s="25"/>
+      <c r="O134" s="23"/>
+      <c r="P134" s="23"/>
+      <c r="Q134" s="24"/>
+      <c r="R134" s="24"/>
+      <c r="S134" s="23"/>
+      <c r="T134" s="23"/>
+      <c r="U134" s="23"/>
+      <c r="V134" s="23"/>
+      <c r="W134" s="23"/>
+      <c r="X134" s="23"/>
+      <c r="Y134" s="23"/>
+      <c r="Z134" s="23"/>
+      <c r="AA134" s="23"/>
+      <c r="AB134" s="23"/>
+      <c r="AC134" s="23"/>
+      <c r="AD134" s="23"/>
+      <c r="AE134" s="23"/>
+      <c r="AF134" s="23"/>
+      <c r="AG134" s="23"/>
+      <c r="AH134" s="24"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="24"/>
-      <c r="C135" s="24"/>
-      <c r="D135" s="24"/>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="24"/>
-      <c r="K135" s="24"/>
-      <c r="L135" s="25"/>
-      <c r="M135" s="25"/>
-      <c r="N135" s="26"/>
-      <c r="O135" s="24"/>
-      <c r="P135" s="24"/>
-      <c r="Q135" s="25"/>
-      <c r="R135" s="25"/>
-      <c r="S135" s="24"/>
-      <c r="T135" s="24"/>
-      <c r="U135" s="24"/>
-      <c r="V135" s="24"/>
-      <c r="W135" s="24"/>
-      <c r="X135" s="24"/>
-      <c r="Y135" s="24"/>
-      <c r="Z135" s="24"/>
-      <c r="AA135" s="24"/>
-      <c r="AB135" s="24"/>
-      <c r="AC135" s="24"/>
-      <c r="AD135" s="24"/>
-      <c r="AE135" s="24"/>
-      <c r="AF135" s="24"/>
-      <c r="AG135" s="24"/>
-      <c r="AH135" s="25"/>
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="23"/>
+      <c r="F135" s="23"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="23"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="23"/>
+      <c r="L135" s="24"/>
+      <c r="M135" s="24"/>
+      <c r="N135" s="25"/>
+      <c r="O135" s="23"/>
+      <c r="P135" s="23"/>
+      <c r="Q135" s="24"/>
+      <c r="R135" s="24"/>
+      <c r="S135" s="23"/>
+      <c r="T135" s="23"/>
+      <c r="U135" s="23"/>
+      <c r="V135" s="23"/>
+      <c r="W135" s="23"/>
+      <c r="X135" s="23"/>
+      <c r="Y135" s="23"/>
+      <c r="Z135" s="23"/>
+      <c r="AA135" s="23"/>
+      <c r="AB135" s="23"/>
+      <c r="AC135" s="23"/>
+      <c r="AD135" s="23"/>
+      <c r="AE135" s="23"/>
+      <c r="AF135" s="23"/>
+      <c r="AG135" s="23"/>
+      <c r="AH135" s="24"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="24"/>
-      <c r="C136" s="24"/>
-      <c r="D136" s="24"/>
-      <c r="E136" s="24"/>
-      <c r="F136" s="24"/>
-      <c r="G136" s="25"/>
-      <c r="H136" s="25"/>
-      <c r="I136" s="24"/>
-      <c r="J136" s="24"/>
-      <c r="K136" s="24"/>
-      <c r="L136" s="25"/>
-      <c r="M136" s="25"/>
-      <c r="N136" s="26"/>
-      <c r="O136" s="24"/>
-      <c r="P136" s="24"/>
-      <c r="Q136" s="25"/>
-      <c r="R136" s="25"/>
-      <c r="S136" s="24"/>
-      <c r="T136" s="24"/>
-      <c r="U136" s="24"/>
-      <c r="V136" s="24"/>
-      <c r="W136" s="24"/>
-      <c r="X136" s="24"/>
-      <c r="Y136" s="24"/>
-      <c r="Z136" s="24"/>
-      <c r="AA136" s="24"/>
-      <c r="AB136" s="24"/>
-      <c r="AC136" s="24"/>
-      <c r="AD136" s="24"/>
-      <c r="AE136" s="24"/>
-      <c r="AF136" s="24"/>
-      <c r="AG136" s="24"/>
-      <c r="AH136" s="25"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="24"/>
+      <c r="H136" s="24"/>
+      <c r="I136" s="23"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="23"/>
+      <c r="L136" s="24"/>
+      <c r="M136" s="24"/>
+      <c r="N136" s="25"/>
+      <c r="O136" s="23"/>
+      <c r="P136" s="23"/>
+      <c r="Q136" s="24"/>
+      <c r="R136" s="24"/>
+      <c r="S136" s="23"/>
+      <c r="T136" s="23"/>
+      <c r="U136" s="23"/>
+      <c r="V136" s="23"/>
+      <c r="W136" s="23"/>
+      <c r="X136" s="23"/>
+      <c r="Y136" s="23"/>
+      <c r="Z136" s="23"/>
+      <c r="AA136" s="23"/>
+      <c r="AB136" s="23"/>
+      <c r="AC136" s="23"/>
+      <c r="AD136" s="23"/>
+      <c r="AE136" s="23"/>
+      <c r="AF136" s="23"/>
+      <c r="AG136" s="23"/>
+      <c r="AH136" s="24"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="24"/>
-      <c r="C137" s="24"/>
-      <c r="D137" s="24"/>
-      <c r="E137" s="24"/>
-      <c r="F137" s="24"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
-      <c r="I137" s="24"/>
-      <c r="J137" s="24"/>
-      <c r="K137" s="24"/>
-      <c r="L137" s="25"/>
-      <c r="M137" s="25"/>
-      <c r="N137" s="26"/>
-      <c r="O137" s="24"/>
-      <c r="P137" s="24"/>
-      <c r="Q137" s="25"/>
-      <c r="R137" s="25"/>
-      <c r="S137" s="24"/>
-      <c r="T137" s="24"/>
-      <c r="U137" s="24"/>
-      <c r="V137" s="24"/>
-      <c r="W137" s="24"/>
-      <c r="X137" s="24"/>
-      <c r="Y137" s="24"/>
-      <c r="Z137" s="24"/>
-      <c r="AA137" s="24"/>
-      <c r="AB137" s="24"/>
-      <c r="AC137" s="24"/>
-      <c r="AD137" s="24"/>
-      <c r="AE137" s="24"/>
-      <c r="AF137" s="24"/>
-      <c r="AG137" s="24"/>
-      <c r="AH137" s="25"/>
+      <c r="B137" s="23"/>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="24"/>
+      <c r="H137" s="24"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="23"/>
+      <c r="L137" s="24"/>
+      <c r="M137" s="24"/>
+      <c r="N137" s="25"/>
+      <c r="O137" s="23"/>
+      <c r="P137" s="23"/>
+      <c r="Q137" s="24"/>
+      <c r="R137" s="24"/>
+      <c r="S137" s="23"/>
+      <c r="T137" s="23"/>
+      <c r="U137" s="23"/>
+      <c r="V137" s="23"/>
+      <c r="W137" s="23"/>
+      <c r="X137" s="23"/>
+      <c r="Y137" s="23"/>
+      <c r="Z137" s="23"/>
+      <c r="AA137" s="23"/>
+      <c r="AB137" s="23"/>
+      <c r="AC137" s="23"/>
+      <c r="AD137" s="23"/>
+      <c r="AE137" s="23"/>
+      <c r="AF137" s="23"/>
+      <c r="AG137" s="23"/>
+      <c r="AH137" s="24"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="24"/>
-      <c r="C138" s="24"/>
-      <c r="D138" s="24"/>
-      <c r="E138" s="24"/>
-      <c r="F138" s="24"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
-      <c r="I138" s="24"/>
-      <c r="J138" s="24"/>
-      <c r="K138" s="24"/>
-      <c r="L138" s="25"/>
-      <c r="M138" s="25"/>
-      <c r="N138" s="26"/>
-      <c r="O138" s="24"/>
-      <c r="P138" s="24"/>
-      <c r="Q138" s="25"/>
-      <c r="R138" s="25"/>
-      <c r="S138" s="24"/>
-      <c r="T138" s="24"/>
-      <c r="U138" s="24"/>
-      <c r="V138" s="24"/>
-      <c r="W138" s="24"/>
-      <c r="X138" s="24"/>
-      <c r="Y138" s="24"/>
-      <c r="Z138" s="24"/>
-      <c r="AA138" s="24"/>
-      <c r="AB138" s="24"/>
-      <c r="AC138" s="24"/>
-      <c r="AD138" s="24"/>
-      <c r="AE138" s="24"/>
-      <c r="AF138" s="24"/>
-      <c r="AG138" s="24"/>
-      <c r="AH138" s="25"/>
+      <c r="B138" s="23"/>
+      <c r="C138" s="23"/>
+      <c r="D138" s="23"/>
+      <c r="E138" s="23"/>
+      <c r="F138" s="23"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="23"/>
+      <c r="K138" s="23"/>
+      <c r="L138" s="24"/>
+      <c r="M138" s="24"/>
+      <c r="N138" s="25"/>
+      <c r="O138" s="23"/>
+      <c r="P138" s="23"/>
+      <c r="Q138" s="24"/>
+      <c r="R138" s="24"/>
+      <c r="S138" s="23"/>
+      <c r="T138" s="23"/>
+      <c r="U138" s="23"/>
+      <c r="V138" s="23"/>
+      <c r="W138" s="23"/>
+      <c r="X138" s="23"/>
+      <c r="Y138" s="23"/>
+      <c r="Z138" s="23"/>
+      <c r="AA138" s="23"/>
+      <c r="AB138" s="23"/>
+      <c r="AC138" s="23"/>
+      <c r="AD138" s="23"/>
+      <c r="AE138" s="23"/>
+      <c r="AF138" s="23"/>
+      <c r="AG138" s="23"/>
+      <c r="AH138" s="24"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="24"/>
-      <c r="C139" s="24"/>
-      <c r="D139" s="24"/>
-      <c r="E139" s="24"/>
-      <c r="F139" s="24"/>
-      <c r="G139" s="25"/>
-      <c r="H139" s="25"/>
-      <c r="I139" s="24"/>
-      <c r="J139" s="24"/>
-      <c r="K139" s="24"/>
-      <c r="L139" s="25"/>
-      <c r="M139" s="25"/>
-      <c r="N139" s="26"/>
-      <c r="O139" s="24"/>
-      <c r="P139" s="24"/>
-      <c r="Q139" s="25"/>
-      <c r="R139" s="25"/>
-      <c r="S139" s="24"/>
-      <c r="T139" s="24"/>
-      <c r="U139" s="24"/>
-      <c r="V139" s="24"/>
-      <c r="W139" s="24"/>
-      <c r="X139" s="24"/>
-      <c r="Y139" s="24"/>
-      <c r="Z139" s="24"/>
-      <c r="AA139" s="24"/>
-      <c r="AB139" s="24"/>
-      <c r="AC139" s="24"/>
-      <c r="AD139" s="24"/>
-      <c r="AE139" s="24"/>
-      <c r="AF139" s="24"/>
-      <c r="AG139" s="24"/>
-      <c r="AH139" s="25"/>
+      <c r="B139" s="23"/>
+      <c r="C139" s="23"/>
+      <c r="D139" s="23"/>
+      <c r="E139" s="23"/>
+      <c r="F139" s="23"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="24"/>
+      <c r="I139" s="23"/>
+      <c r="J139" s="23"/>
+      <c r="K139" s="23"/>
+      <c r="L139" s="24"/>
+      <c r="M139" s="24"/>
+      <c r="N139" s="25"/>
+      <c r="O139" s="23"/>
+      <c r="P139" s="23"/>
+      <c r="Q139" s="24"/>
+      <c r="R139" s="24"/>
+      <c r="S139" s="23"/>
+      <c r="T139" s="23"/>
+      <c r="U139" s="23"/>
+      <c r="V139" s="23"/>
+      <c r="W139" s="23"/>
+      <c r="X139" s="23"/>
+      <c r="Y139" s="23"/>
+      <c r="Z139" s="23"/>
+      <c r="AA139" s="23"/>
+      <c r="AB139" s="23"/>
+      <c r="AC139" s="23"/>
+      <c r="AD139" s="23"/>
+      <c r="AE139" s="23"/>
+      <c r="AF139" s="23"/>
+      <c r="AG139" s="23"/>
+      <c r="AH139" s="24"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="24"/>
-      <c r="C140" s="24"/>
-      <c r="D140" s="24"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="24"/>
-      <c r="G140" s="25"/>
-      <c r="H140" s="25"/>
-      <c r="I140" s="24"/>
-      <c r="J140" s="24"/>
-      <c r="K140" s="24"/>
-      <c r="L140" s="25"/>
-      <c r="M140" s="25"/>
-      <c r="N140" s="26"/>
-      <c r="O140" s="24"/>
-      <c r="P140" s="24"/>
-      <c r="Q140" s="25"/>
-      <c r="R140" s="25"/>
-      <c r="S140" s="24"/>
-      <c r="T140" s="24"/>
-      <c r="U140" s="24"/>
-      <c r="V140" s="24"/>
-      <c r="W140" s="24"/>
-      <c r="X140" s="24"/>
-      <c r="Y140" s="24"/>
-      <c r="Z140" s="24"/>
-      <c r="AA140" s="24"/>
-      <c r="AB140" s="24"/>
-      <c r="AC140" s="24"/>
-      <c r="AD140" s="24"/>
-      <c r="AE140" s="24"/>
-      <c r="AF140" s="24"/>
-      <c r="AG140" s="24"/>
-      <c r="AH140" s="25"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="23"/>
+      <c r="D140" s="23"/>
+      <c r="E140" s="23"/>
+      <c r="F140" s="23"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
+      <c r="I140" s="23"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="23"/>
+      <c r="L140" s="24"/>
+      <c r="M140" s="24"/>
+      <c r="N140" s="25"/>
+      <c r="O140" s="23"/>
+      <c r="P140" s="23"/>
+      <c r="Q140" s="24"/>
+      <c r="R140" s="24"/>
+      <c r="S140" s="23"/>
+      <c r="T140" s="23"/>
+      <c r="U140" s="23"/>
+      <c r="V140" s="23"/>
+      <c r="W140" s="23"/>
+      <c r="X140" s="23"/>
+      <c r="Y140" s="23"/>
+      <c r="Z140" s="23"/>
+      <c r="AA140" s="23"/>
+      <c r="AB140" s="23"/>
+      <c r="AC140" s="23"/>
+      <c r="AD140" s="23"/>
+      <c r="AE140" s="23"/>
+      <c r="AF140" s="23"/>
+      <c r="AG140" s="23"/>
+      <c r="AH140" s="24"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="24"/>
-      <c r="C141" s="24"/>
-      <c r="D141" s="24"/>
-      <c r="E141" s="24"/>
-      <c r="F141" s="24"/>
-      <c r="G141" s="25"/>
-      <c r="H141" s="25"/>
-      <c r="I141" s="24"/>
-      <c r="J141" s="24"/>
-      <c r="K141" s="24"/>
-      <c r="L141" s="25"/>
-      <c r="M141" s="25"/>
-      <c r="N141" s="26"/>
-      <c r="O141" s="24"/>
-      <c r="P141" s="24"/>
-      <c r="Q141" s="25"/>
-      <c r="R141" s="25"/>
-      <c r="S141" s="24"/>
-      <c r="T141" s="24"/>
-      <c r="U141" s="24"/>
-      <c r="V141" s="24"/>
-      <c r="W141" s="24"/>
-      <c r="X141" s="24"/>
-      <c r="Y141" s="24"/>
-      <c r="Z141" s="24"/>
-      <c r="AA141" s="24"/>
-      <c r="AB141" s="24"/>
-      <c r="AC141" s="24"/>
-      <c r="AD141" s="24"/>
-      <c r="AE141" s="24"/>
-      <c r="AF141" s="24"/>
-      <c r="AG141" s="24"/>
-      <c r="AH141" s="25"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="23"/>
+      <c r="D141" s="23"/>
+      <c r="E141" s="23"/>
+      <c r="F141" s="23"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
+      <c r="I141" s="23"/>
+      <c r="J141" s="23"/>
+      <c r="K141" s="23"/>
+      <c r="L141" s="24"/>
+      <c r="M141" s="24"/>
+      <c r="N141" s="25"/>
+      <c r="O141" s="23"/>
+      <c r="P141" s="23"/>
+      <c r="Q141" s="24"/>
+      <c r="R141" s="24"/>
+      <c r="S141" s="23"/>
+      <c r="T141" s="23"/>
+      <c r="U141" s="23"/>
+      <c r="V141" s="23"/>
+      <c r="W141" s="23"/>
+      <c r="X141" s="23"/>
+      <c r="Y141" s="23"/>
+      <c r="Z141" s="23"/>
+      <c r="AA141" s="23"/>
+      <c r="AB141" s="23"/>
+      <c r="AC141" s="23"/>
+      <c r="AD141" s="23"/>
+      <c r="AE141" s="23"/>
+      <c r="AF141" s="23"/>
+      <c r="AG141" s="23"/>
+      <c r="AH141" s="24"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="24"/>
-      <c r="C142" s="24"/>
-      <c r="D142" s="24"/>
-      <c r="E142" s="24"/>
-      <c r="F142" s="24"/>
-      <c r="G142" s="25"/>
-      <c r="H142" s="25"/>
-      <c r="I142" s="24"/>
-      <c r="J142" s="24"/>
-      <c r="K142" s="24"/>
-      <c r="L142" s="25"/>
-      <c r="M142" s="25"/>
-      <c r="N142" s="26"/>
-      <c r="O142" s="24"/>
-      <c r="P142" s="24"/>
-      <c r="Q142" s="25"/>
-      <c r="R142" s="25"/>
-      <c r="S142" s="24"/>
-      <c r="T142" s="24"/>
-      <c r="U142" s="24"/>
-      <c r="V142" s="24"/>
-      <c r="W142" s="24"/>
-      <c r="X142" s="24"/>
-      <c r="Y142" s="24"/>
-      <c r="Z142" s="24"/>
-      <c r="AA142" s="24"/>
-      <c r="AB142" s="24"/>
-      <c r="AC142" s="24"/>
-      <c r="AD142" s="24"/>
-      <c r="AE142" s="24"/>
-      <c r="AF142" s="24"/>
-      <c r="AG142" s="24"/>
-      <c r="AH142" s="25"/>
+      <c r="B142" s="23"/>
+      <c r="C142" s="23"/>
+      <c r="D142" s="23"/>
+      <c r="E142" s="23"/>
+      <c r="F142" s="23"/>
+      <c r="G142" s="24"/>
+      <c r="H142" s="24"/>
+      <c r="I142" s="23"/>
+      <c r="J142" s="23"/>
+      <c r="K142" s="23"/>
+      <c r="L142" s="24"/>
+      <c r="M142" s="24"/>
+      <c r="N142" s="25"/>
+      <c r="O142" s="23"/>
+      <c r="P142" s="23"/>
+      <c r="Q142" s="24"/>
+      <c r="R142" s="24"/>
+      <c r="S142" s="23"/>
+      <c r="T142" s="23"/>
+      <c r="U142" s="23"/>
+      <c r="V142" s="23"/>
+      <c r="W142" s="23"/>
+      <c r="X142" s="23"/>
+      <c r="Y142" s="23"/>
+      <c r="Z142" s="23"/>
+      <c r="AA142" s="23"/>
+      <c r="AB142" s="23"/>
+      <c r="AC142" s="23"/>
+      <c r="AD142" s="23"/>
+      <c r="AE142" s="23"/>
+      <c r="AF142" s="23"/>
+      <c r="AG142" s="23"/>
+      <c r="AH142" s="24"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="24"/>
-      <c r="C143" s="24"/>
-      <c r="D143" s="24"/>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="24"/>
-      <c r="K143" s="24"/>
-      <c r="L143" s="25"/>
-      <c r="M143" s="25"/>
-      <c r="N143" s="26"/>
-      <c r="O143" s="24"/>
-      <c r="P143" s="24"/>
-      <c r="Q143" s="25"/>
-      <c r="R143" s="25"/>
-      <c r="S143" s="24"/>
-      <c r="T143" s="24"/>
-      <c r="U143" s="24"/>
-      <c r="V143" s="24"/>
-      <c r="W143" s="24"/>
-      <c r="X143" s="24"/>
-      <c r="Y143" s="24"/>
-      <c r="Z143" s="24"/>
-      <c r="AA143" s="24"/>
-      <c r="AB143" s="24"/>
-      <c r="AC143" s="24"/>
-      <c r="AD143" s="24"/>
-      <c r="AE143" s="24"/>
-      <c r="AF143" s="24"/>
-      <c r="AG143" s="24"/>
-      <c r="AH143" s="25"/>
+      <c r="B143" s="23"/>
+      <c r="C143" s="23"/>
+      <c r="D143" s="23"/>
+      <c r="E143" s="23"/>
+      <c r="F143" s="23"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="23"/>
+      <c r="J143" s="23"/>
+      <c r="K143" s="23"/>
+      <c r="L143" s="24"/>
+      <c r="M143" s="24"/>
+      <c r="N143" s="25"/>
+      <c r="O143" s="23"/>
+      <c r="P143" s="23"/>
+      <c r="Q143" s="24"/>
+      <c r="R143" s="24"/>
+      <c r="S143" s="23"/>
+      <c r="T143" s="23"/>
+      <c r="U143" s="23"/>
+      <c r="V143" s="23"/>
+      <c r="W143" s="23"/>
+      <c r="X143" s="23"/>
+      <c r="Y143" s="23"/>
+      <c r="Z143" s="23"/>
+      <c r="AA143" s="23"/>
+      <c r="AB143" s="23"/>
+      <c r="AC143" s="23"/>
+      <c r="AD143" s="23"/>
+      <c r="AE143" s="23"/>
+      <c r="AF143" s="23"/>
+      <c r="AG143" s="23"/>
+      <c r="AH143" s="24"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="24"/>
-      <c r="C144" s="24"/>
-      <c r="D144" s="24"/>
-      <c r="E144" s="24"/>
-      <c r="F144" s="24"/>
-      <c r="G144" s="25"/>
-      <c r="H144" s="25"/>
-      <c r="I144" s="24"/>
-      <c r="J144" s="24"/>
-      <c r="K144" s="24"/>
-      <c r="L144" s="25"/>
-      <c r="M144" s="25"/>
-      <c r="N144" s="26"/>
-      <c r="O144" s="24"/>
-      <c r="P144" s="24"/>
-      <c r="Q144" s="25"/>
-      <c r="R144" s="25"/>
-      <c r="S144" s="24"/>
-      <c r="T144" s="24"/>
-      <c r="U144" s="24"/>
-      <c r="V144" s="24"/>
-      <c r="W144" s="24"/>
-      <c r="X144" s="24"/>
-      <c r="Y144" s="24"/>
-      <c r="Z144" s="24"/>
-      <c r="AA144" s="24"/>
-      <c r="AB144" s="24"/>
-      <c r="AC144" s="24"/>
-      <c r="AD144" s="24"/>
-      <c r="AE144" s="24"/>
-      <c r="AF144" s="24"/>
-      <c r="AG144" s="24"/>
-      <c r="AH144" s="25"/>
+      <c r="B144" s="23"/>
+      <c r="C144" s="23"/>
+      <c r="D144" s="23"/>
+      <c r="E144" s="23"/>
+      <c r="F144" s="23"/>
+      <c r="G144" s="24"/>
+      <c r="H144" s="24"/>
+      <c r="I144" s="23"/>
+      <c r="J144" s="23"/>
+      <c r="K144" s="23"/>
+      <c r="L144" s="24"/>
+      <c r="M144" s="24"/>
+      <c r="N144" s="25"/>
+      <c r="O144" s="23"/>
+      <c r="P144" s="23"/>
+      <c r="Q144" s="24"/>
+      <c r="R144" s="24"/>
+      <c r="S144" s="23"/>
+      <c r="T144" s="23"/>
+      <c r="U144" s="23"/>
+      <c r="V144" s="23"/>
+      <c r="W144" s="23"/>
+      <c r="X144" s="23"/>
+      <c r="Y144" s="23"/>
+      <c r="Z144" s="23"/>
+      <c r="AA144" s="23"/>
+      <c r="AB144" s="23"/>
+      <c r="AC144" s="23"/>
+      <c r="AD144" s="23"/>
+      <c r="AE144" s="23"/>
+      <c r="AF144" s="23"/>
+      <c r="AG144" s="23"/>
+      <c r="AH144" s="24"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="24"/>
-      <c r="C145" s="24"/>
-      <c r="D145" s="24"/>
-      <c r="E145" s="24"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="25"/>
-      <c r="H145" s="25"/>
-      <c r="I145" s="24"/>
-      <c r="J145" s="24"/>
-      <c r="K145" s="24"/>
-      <c r="L145" s="25"/>
-      <c r="M145" s="25"/>
-      <c r="N145" s="26"/>
-      <c r="O145" s="24"/>
-      <c r="P145" s="24"/>
-      <c r="Q145" s="25"/>
-      <c r="R145" s="25"/>
-      <c r="S145" s="24"/>
-      <c r="T145" s="24"/>
-      <c r="U145" s="24"/>
-      <c r="V145" s="24"/>
-      <c r="W145" s="24"/>
-      <c r="X145" s="24"/>
-      <c r="Y145" s="24"/>
-      <c r="Z145" s="24"/>
-      <c r="AA145" s="24"/>
-      <c r="AB145" s="24"/>
-      <c r="AC145" s="24"/>
-      <c r="AD145" s="24"/>
-      <c r="AE145" s="24"/>
-      <c r="AF145" s="24"/>
-      <c r="AG145" s="24"/>
-      <c r="AH145" s="25"/>
+      <c r="B145" s="23"/>
+      <c r="C145" s="23"/>
+      <c r="D145" s="23"/>
+      <c r="E145" s="23"/>
+      <c r="F145" s="23"/>
+      <c r="G145" s="24"/>
+      <c r="H145" s="24"/>
+      <c r="I145" s="23"/>
+      <c r="J145" s="23"/>
+      <c r="K145" s="23"/>
+      <c r="L145" s="24"/>
+      <c r="M145" s="24"/>
+      <c r="N145" s="25"/>
+      <c r="O145" s="23"/>
+      <c r="P145" s="23"/>
+      <c r="Q145" s="24"/>
+      <c r="R145" s="24"/>
+      <c r="S145" s="23"/>
+      <c r="T145" s="23"/>
+      <c r="U145" s="23"/>
+      <c r="V145" s="23"/>
+      <c r="W145" s="23"/>
+      <c r="X145" s="23"/>
+      <c r="Y145" s="23"/>
+      <c r="Z145" s="23"/>
+      <c r="AA145" s="23"/>
+      <c r="AB145" s="23"/>
+      <c r="AC145" s="23"/>
+      <c r="AD145" s="23"/>
+      <c r="AE145" s="23"/>
+      <c r="AF145" s="23"/>
+      <c r="AG145" s="23"/>
+      <c r="AH145" s="24"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="24"/>
-      <c r="C146" s="24"/>
-      <c r="D146" s="24"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="25"/>
-      <c r="H146" s="25"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="24"/>
-      <c r="K146" s="24"/>
-      <c r="L146" s="25"/>
-      <c r="M146" s="25"/>
-      <c r="N146" s="26"/>
-      <c r="O146" s="24"/>
-      <c r="P146" s="24"/>
-      <c r="Q146" s="25"/>
-      <c r="R146" s="25"/>
-      <c r="S146" s="24"/>
-      <c r="T146" s="24"/>
-      <c r="U146" s="24"/>
-      <c r="V146" s="24"/>
-      <c r="W146" s="24"/>
-      <c r="X146" s="24"/>
-      <c r="Y146" s="24"/>
-      <c r="Z146" s="24"/>
-      <c r="AA146" s="24"/>
-      <c r="AB146" s="24"/>
-      <c r="AC146" s="24"/>
-      <c r="AD146" s="24"/>
-      <c r="AE146" s="24"/>
-      <c r="AF146" s="24"/>
-      <c r="AG146" s="24"/>
-      <c r="AH146" s="25"/>
+      <c r="B146" s="23"/>
+      <c r="C146" s="23"/>
+      <c r="D146" s="23"/>
+      <c r="E146" s="23"/>
+      <c r="F146" s="23"/>
+      <c r="G146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="23"/>
+      <c r="J146" s="23"/>
+      <c r="K146" s="23"/>
+      <c r="L146" s="24"/>
+      <c r="M146" s="24"/>
+      <c r="N146" s="25"/>
+      <c r="O146" s="23"/>
+      <c r="P146" s="23"/>
+      <c r="Q146" s="24"/>
+      <c r="R146" s="24"/>
+      <c r="S146" s="23"/>
+      <c r="T146" s="23"/>
+      <c r="U146" s="23"/>
+      <c r="V146" s="23"/>
+      <c r="W146" s="23"/>
+      <c r="X146" s="23"/>
+      <c r="Y146" s="23"/>
+      <c r="Z146" s="23"/>
+      <c r="AA146" s="23"/>
+      <c r="AB146" s="23"/>
+      <c r="AC146" s="23"/>
+      <c r="AD146" s="23"/>
+      <c r="AE146" s="23"/>
+      <c r="AF146" s="23"/>
+      <c r="AG146" s="23"/>
+      <c r="AH146" s="24"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="24"/>
-      <c r="C147" s="24"/>
-      <c r="D147" s="24"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="25"/>
-      <c r="H147" s="25"/>
-      <c r="I147" s="24"/>
-      <c r="J147" s="24"/>
-      <c r="K147" s="24"/>
-      <c r="L147" s="25"/>
-      <c r="M147" s="25"/>
-      <c r="N147" s="26"/>
-      <c r="O147" s="24"/>
-      <c r="P147" s="24"/>
-      <c r="Q147" s="25"/>
-      <c r="R147" s="25"/>
-      <c r="S147" s="24"/>
-      <c r="T147" s="24"/>
-      <c r="U147" s="24"/>
-      <c r="V147" s="24"/>
-      <c r="W147" s="24"/>
-      <c r="X147" s="24"/>
-      <c r="Y147" s="24"/>
-      <c r="Z147" s="24"/>
-      <c r="AA147" s="24"/>
-      <c r="AB147" s="24"/>
-      <c r="AC147" s="24"/>
-      <c r="AD147" s="24"/>
-      <c r="AE147" s="24"/>
-      <c r="AF147" s="24"/>
-      <c r="AG147" s="24"/>
-      <c r="AH147" s="25"/>
+      <c r="B147" s="23"/>
+      <c r="C147" s="23"/>
+      <c r="D147" s="23"/>
+      <c r="E147" s="23"/>
+      <c r="F147" s="23"/>
+      <c r="G147" s="24"/>
+      <c r="H147" s="24"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="23"/>
+      <c r="K147" s="23"/>
+      <c r="L147" s="24"/>
+      <c r="M147" s="24"/>
+      <c r="N147" s="25"/>
+      <c r="O147" s="23"/>
+      <c r="P147" s="23"/>
+      <c r="Q147" s="24"/>
+      <c r="R147" s="24"/>
+      <c r="S147" s="23"/>
+      <c r="T147" s="23"/>
+      <c r="U147" s="23"/>
+      <c r="V147" s="23"/>
+      <c r="W147" s="23"/>
+      <c r="X147" s="23"/>
+      <c r="Y147" s="23"/>
+      <c r="Z147" s="23"/>
+      <c r="AA147" s="23"/>
+      <c r="AB147" s="23"/>
+      <c r="AC147" s="23"/>
+      <c r="AD147" s="23"/>
+      <c r="AE147" s="23"/>
+      <c r="AF147" s="23"/>
+      <c r="AG147" s="23"/>
+      <c r="AH147" s="24"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="24"/>
-      <c r="C148" s="24"/>
-      <c r="D148" s="24"/>
-      <c r="E148" s="24"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
-      <c r="I148" s="24"/>
-      <c r="J148" s="24"/>
-      <c r="K148" s="24"/>
-      <c r="L148" s="25"/>
-      <c r="M148" s="25"/>
-      <c r="N148" s="26"/>
-      <c r="O148" s="24"/>
-      <c r="P148" s="24"/>
-      <c r="Q148" s="25"/>
-      <c r="R148" s="25"/>
-      <c r="S148" s="24"/>
-      <c r="T148" s="24"/>
-      <c r="U148" s="24"/>
-      <c r="V148" s="24"/>
-      <c r="W148" s="24"/>
-      <c r="X148" s="24"/>
-      <c r="Y148" s="24"/>
-      <c r="Z148" s="24"/>
-      <c r="AA148" s="24"/>
-      <c r="AB148" s="24"/>
-      <c r="AC148" s="24"/>
-      <c r="AD148" s="24"/>
-      <c r="AE148" s="24"/>
-      <c r="AF148" s="24"/>
-      <c r="AG148" s="24"/>
-      <c r="AH148" s="25"/>
+      <c r="B148" s="23"/>
+      <c r="C148" s="23"/>
+      <c r="D148" s="23"/>
+      <c r="E148" s="23"/>
+      <c r="F148" s="23"/>
+      <c r="G148" s="24"/>
+      <c r="H148" s="24"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23"/>
+      <c r="L148" s="24"/>
+      <c r="M148" s="24"/>
+      <c r="N148" s="25"/>
+      <c r="O148" s="23"/>
+      <c r="P148" s="23"/>
+      <c r="Q148" s="24"/>
+      <c r="R148" s="24"/>
+      <c r="S148" s="23"/>
+      <c r="T148" s="23"/>
+      <c r="U148" s="23"/>
+      <c r="V148" s="23"/>
+      <c r="W148" s="23"/>
+      <c r="X148" s="23"/>
+      <c r="Y148" s="23"/>
+      <c r="Z148" s="23"/>
+      <c r="AA148" s="23"/>
+      <c r="AB148" s="23"/>
+      <c r="AC148" s="23"/>
+      <c r="AD148" s="23"/>
+      <c r="AE148" s="23"/>
+      <c r="AF148" s="23"/>
+      <c r="AG148" s="23"/>
+      <c r="AH148" s="24"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="25"/>
-      <c r="M149" s="25"/>
-      <c r="N149" s="26"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="25"/>
-      <c r="R149" s="25"/>
-      <c r="S149" s="24"/>
-      <c r="T149" s="24"/>
-      <c r="U149" s="24"/>
-      <c r="V149" s="24"/>
-      <c r="W149" s="24"/>
-      <c r="X149" s="24"/>
-      <c r="Y149" s="24"/>
-      <c r="Z149" s="24"/>
-      <c r="AA149" s="24"/>
-      <c r="AB149" s="24"/>
-      <c r="AC149" s="24"/>
-      <c r="AD149" s="24"/>
-      <c r="AE149" s="24"/>
-      <c r="AF149" s="24"/>
-      <c r="AG149" s="24"/>
-      <c r="AH149" s="25"/>
+      <c r="B149" s="23"/>
+      <c r="C149" s="23"/>
+      <c r="D149" s="23"/>
+      <c r="E149" s="23"/>
+      <c r="F149" s="23"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="23"/>
+      <c r="J149" s="23"/>
+      <c r="K149" s="23"/>
+      <c r="L149" s="24"/>
+      <c r="M149" s="24"/>
+      <c r="N149" s="25"/>
+      <c r="O149" s="23"/>
+      <c r="P149" s="23"/>
+      <c r="Q149" s="24"/>
+      <c r="R149" s="24"/>
+      <c r="S149" s="23"/>
+      <c r="T149" s="23"/>
+      <c r="U149" s="23"/>
+      <c r="V149" s="23"/>
+      <c r="W149" s="23"/>
+      <c r="X149" s="23"/>
+      <c r="Y149" s="23"/>
+      <c r="Z149" s="23"/>
+      <c r="AA149" s="23"/>
+      <c r="AB149" s="23"/>
+      <c r="AC149" s="23"/>
+      <c r="AD149" s="23"/>
+      <c r="AE149" s="23"/>
+      <c r="AF149" s="23"/>
+      <c r="AG149" s="23"/>
+      <c r="AH149" s="24"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="24"/>
-      <c r="C150" s="24"/>
-      <c r="D150" s="24"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="25"/>
-      <c r="H150" s="25"/>
-      <c r="I150" s="24"/>
-      <c r="J150" s="24"/>
-      <c r="K150" s="24"/>
-      <c r="L150" s="25"/>
-      <c r="M150" s="25"/>
-      <c r="N150" s="26"/>
-      <c r="O150" s="24"/>
-      <c r="P150" s="24"/>
-      <c r="Q150" s="25"/>
-      <c r="R150" s="25"/>
-      <c r="S150" s="24"/>
-      <c r="T150" s="24"/>
-      <c r="U150" s="24"/>
-      <c r="V150" s="24"/>
-      <c r="W150" s="24"/>
-      <c r="X150" s="24"/>
-      <c r="Y150" s="24"/>
-      <c r="Z150" s="24"/>
-      <c r="AA150" s="24"/>
-      <c r="AB150" s="24"/>
-      <c r="AC150" s="24"/>
-      <c r="AD150" s="24"/>
-      <c r="AE150" s="24"/>
-      <c r="AF150" s="24"/>
-      <c r="AG150" s="24"/>
-      <c r="AH150" s="25"/>
+      <c r="B150" s="23"/>
+      <c r="C150" s="23"/>
+      <c r="D150" s="23"/>
+      <c r="E150" s="23"/>
+      <c r="F150" s="23"/>
+      <c r="G150" s="24"/>
+      <c r="H150" s="24"/>
+      <c r="I150" s="23"/>
+      <c r="J150" s="23"/>
+      <c r="K150" s="23"/>
+      <c r="L150" s="24"/>
+      <c r="M150" s="24"/>
+      <c r="N150" s="25"/>
+      <c r="O150" s="23"/>
+      <c r="P150" s="23"/>
+      <c r="Q150" s="24"/>
+      <c r="R150" s="24"/>
+      <c r="S150" s="23"/>
+      <c r="T150" s="23"/>
+      <c r="U150" s="23"/>
+      <c r="V150" s="23"/>
+      <c r="W150" s="23"/>
+      <c r="X150" s="23"/>
+      <c r="Y150" s="23"/>
+      <c r="Z150" s="23"/>
+      <c r="AA150" s="23"/>
+      <c r="AB150" s="23"/>
+      <c r="AC150" s="23"/>
+      <c r="AD150" s="23"/>
+      <c r="AE150" s="23"/>
+      <c r="AF150" s="23"/>
+      <c r="AG150" s="23"/>
+      <c r="AH150" s="24"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="24"/>
-      <c r="C151" s="24"/>
-      <c r="D151" s="24"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="25"/>
-      <c r="H151" s="25"/>
-      <c r="I151" s="24"/>
-      <c r="J151" s="24"/>
-      <c r="K151" s="24"/>
-      <c r="L151" s="25"/>
-      <c r="M151" s="25"/>
-      <c r="N151" s="26"/>
-      <c r="O151" s="24"/>
-      <c r="P151" s="24"/>
-      <c r="Q151" s="25"/>
-      <c r="R151" s="25"/>
-      <c r="S151" s="24"/>
-      <c r="T151" s="24"/>
-      <c r="U151" s="24"/>
-      <c r="V151" s="24"/>
-      <c r="W151" s="24"/>
-      <c r="X151" s="24"/>
-      <c r="Y151" s="24"/>
-      <c r="Z151" s="24"/>
-      <c r="AA151" s="24"/>
-      <c r="AB151" s="24"/>
-      <c r="AC151" s="24"/>
-      <c r="AD151" s="24"/>
-      <c r="AE151" s="24"/>
-      <c r="AF151" s="24"/>
-      <c r="AG151" s="24"/>
-      <c r="AH151" s="25"/>
+      <c r="B151" s="23"/>
+      <c r="C151" s="23"/>
+      <c r="D151" s="23"/>
+      <c r="E151" s="23"/>
+      <c r="F151" s="23"/>
+      <c r="G151" s="24"/>
+      <c r="H151" s="24"/>
+      <c r="I151" s="23"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="23"/>
+      <c r="L151" s="24"/>
+      <c r="M151" s="24"/>
+      <c r="N151" s="25"/>
+      <c r="O151" s="23"/>
+      <c r="P151" s="23"/>
+      <c r="Q151" s="24"/>
+      <c r="R151" s="24"/>
+      <c r="S151" s="23"/>
+      <c r="T151" s="23"/>
+      <c r="U151" s="23"/>
+      <c r="V151" s="23"/>
+      <c r="W151" s="23"/>
+      <c r="X151" s="23"/>
+      <c r="Y151" s="23"/>
+      <c r="Z151" s="23"/>
+      <c r="AA151" s="23"/>
+      <c r="AB151" s="23"/>
+      <c r="AC151" s="23"/>
+      <c r="AD151" s="23"/>
+      <c r="AE151" s="23"/>
+      <c r="AF151" s="23"/>
+      <c r="AG151" s="23"/>
+      <c r="AH151" s="24"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="24"/>
-      <c r="C152" s="24"/>
-      <c r="D152" s="24"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="25"/>
-      <c r="H152" s="25"/>
-      <c r="I152" s="24"/>
-      <c r="J152" s="24"/>
-      <c r="K152" s="24"/>
-      <c r="L152" s="25"/>
-      <c r="M152" s="25"/>
-      <c r="N152" s="26"/>
-      <c r="O152" s="24"/>
-      <c r="P152" s="24"/>
-      <c r="Q152" s="25"/>
-      <c r="R152" s="25"/>
-      <c r="S152" s="24"/>
-      <c r="T152" s="24"/>
-      <c r="U152" s="24"/>
-      <c r="V152" s="24"/>
-      <c r="W152" s="24"/>
-      <c r="X152" s="24"/>
-      <c r="Y152" s="24"/>
-      <c r="Z152" s="24"/>
-      <c r="AA152" s="24"/>
-      <c r="AB152" s="24"/>
-      <c r="AC152" s="24"/>
-      <c r="AD152" s="24"/>
-      <c r="AE152" s="24"/>
-      <c r="AF152" s="24"/>
-      <c r="AG152" s="24"/>
-      <c r="AH152" s="25"/>
+      <c r="B152" s="23"/>
+      <c r="C152" s="23"/>
+      <c r="D152" s="23"/>
+      <c r="E152" s="23"/>
+      <c r="F152" s="23"/>
+      <c r="G152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="23"/>
+      <c r="K152" s="23"/>
+      <c r="L152" s="24"/>
+      <c r="M152" s="24"/>
+      <c r="N152" s="25"/>
+      <c r="O152" s="23"/>
+      <c r="P152" s="23"/>
+      <c r="Q152" s="24"/>
+      <c r="R152" s="24"/>
+      <c r="S152" s="23"/>
+      <c r="T152" s="23"/>
+      <c r="U152" s="23"/>
+      <c r="V152" s="23"/>
+      <c r="W152" s="23"/>
+      <c r="X152" s="23"/>
+      <c r="Y152" s="23"/>
+      <c r="Z152" s="23"/>
+      <c r="AA152" s="23"/>
+      <c r="AB152" s="23"/>
+      <c r="AC152" s="23"/>
+      <c r="AD152" s="23"/>
+      <c r="AE152" s="23"/>
+      <c r="AF152" s="23"/>
+      <c r="AG152" s="23"/>
+      <c r="AH152" s="24"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="24"/>
-      <c r="C153" s="24"/>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="25"/>
-      <c r="H153" s="25"/>
-      <c r="I153" s="24"/>
-      <c r="J153" s="24"/>
-      <c r="K153" s="24"/>
-      <c r="L153" s="25"/>
-      <c r="M153" s="25"/>
-      <c r="N153" s="26"/>
-      <c r="O153" s="24"/>
-      <c r="P153" s="24"/>
-      <c r="Q153" s="25"/>
-      <c r="R153" s="25"/>
-      <c r="S153" s="24"/>
-      <c r="T153" s="24"/>
-      <c r="U153" s="24"/>
-      <c r="V153" s="24"/>
-      <c r="W153" s="24"/>
-      <c r="X153" s="24"/>
-      <c r="Y153" s="24"/>
-      <c r="Z153" s="24"/>
-      <c r="AA153" s="24"/>
-      <c r="AB153" s="24"/>
-      <c r="AC153" s="24"/>
-      <c r="AD153" s="24"/>
-      <c r="AE153" s="24"/>
-      <c r="AF153" s="24"/>
-      <c r="AG153" s="24"/>
-      <c r="AH153" s="25"/>
+      <c r="B153" s="23"/>
+      <c r="C153" s="23"/>
+      <c r="D153" s="23"/>
+      <c r="E153" s="23"/>
+      <c r="F153" s="23"/>
+      <c r="G153" s="24"/>
+      <c r="H153" s="24"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="23"/>
+      <c r="K153" s="23"/>
+      <c r="L153" s="24"/>
+      <c r="M153" s="24"/>
+      <c r="N153" s="25"/>
+      <c r="O153" s="23"/>
+      <c r="P153" s="23"/>
+      <c r="Q153" s="24"/>
+      <c r="R153" s="24"/>
+      <c r="S153" s="23"/>
+      <c r="T153" s="23"/>
+      <c r="U153" s="23"/>
+      <c r="V153" s="23"/>
+      <c r="W153" s="23"/>
+      <c r="X153" s="23"/>
+      <c r="Y153" s="23"/>
+      <c r="Z153" s="23"/>
+      <c r="AA153" s="23"/>
+      <c r="AB153" s="23"/>
+      <c r="AC153" s="23"/>
+      <c r="AD153" s="23"/>
+      <c r="AE153" s="23"/>
+      <c r="AF153" s="23"/>
+      <c r="AG153" s="23"/>
+      <c r="AH153" s="24"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="24"/>
-      <c r="C154" s="24"/>
-      <c r="D154" s="24"/>
-      <c r="E154" s="24"/>
-      <c r="F154" s="24"/>
-      <c r="G154" s="25"/>
-      <c r="H154" s="25"/>
-      <c r="I154" s="24"/>
-      <c r="J154" s="24"/>
-      <c r="K154" s="24"/>
-      <c r="L154" s="25"/>
-      <c r="M154" s="25"/>
-      <c r="N154" s="26"/>
-      <c r="O154" s="24"/>
-      <c r="P154" s="24"/>
-      <c r="Q154" s="25"/>
-      <c r="R154" s="25"/>
-      <c r="S154" s="24"/>
-      <c r="T154" s="24"/>
-      <c r="U154" s="24"/>
-      <c r="V154" s="24"/>
-      <c r="W154" s="24"/>
-      <c r="X154" s="24"/>
-      <c r="Y154" s="24"/>
-      <c r="Z154" s="24"/>
-      <c r="AA154" s="24"/>
-      <c r="AB154" s="24"/>
-      <c r="AC154" s="24"/>
-      <c r="AD154" s="24"/>
-      <c r="AE154" s="24"/>
-      <c r="AF154" s="24"/>
-      <c r="AG154" s="24"/>
-      <c r="AH154" s="25"/>
+      <c r="B154" s="23"/>
+      <c r="C154" s="23"/>
+      <c r="D154" s="23"/>
+      <c r="E154" s="23"/>
+      <c r="F154" s="23"/>
+      <c r="G154" s="24"/>
+      <c r="H154" s="24"/>
+      <c r="I154" s="23"/>
+      <c r="J154" s="23"/>
+      <c r="K154" s="23"/>
+      <c r="L154" s="24"/>
+      <c r="M154" s="24"/>
+      <c r="N154" s="25"/>
+      <c r="O154" s="23"/>
+      <c r="P154" s="23"/>
+      <c r="Q154" s="24"/>
+      <c r="R154" s="24"/>
+      <c r="S154" s="23"/>
+      <c r="T154" s="23"/>
+      <c r="U154" s="23"/>
+      <c r="V154" s="23"/>
+      <c r="W154" s="23"/>
+      <c r="X154" s="23"/>
+      <c r="Y154" s="23"/>
+      <c r="Z154" s="23"/>
+      <c r="AA154" s="23"/>
+      <c r="AB154" s="23"/>
+      <c r="AC154" s="23"/>
+      <c r="AD154" s="23"/>
+      <c r="AE154" s="23"/>
+      <c r="AF154" s="23"/>
+      <c r="AG154" s="23"/>
+      <c r="AH154" s="24"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="24"/>
-      <c r="C155" s="24"/>
-      <c r="D155" s="24"/>
-      <c r="E155" s="24"/>
-      <c r="F155" s="24"/>
-      <c r="G155" s="25"/>
-      <c r="H155" s="25"/>
-      <c r="I155" s="24"/>
-      <c r="J155" s="24"/>
-      <c r="K155" s="24"/>
-      <c r="L155" s="25"/>
-      <c r="M155" s="25"/>
-      <c r="N155" s="26"/>
-      <c r="O155" s="24"/>
-      <c r="P155" s="24"/>
-      <c r="Q155" s="25"/>
-      <c r="R155" s="25"/>
-      <c r="S155" s="24"/>
-      <c r="T155" s="24"/>
-      <c r="U155" s="24"/>
-      <c r="V155" s="24"/>
-      <c r="W155" s="24"/>
-      <c r="X155" s="24"/>
-      <c r="Y155" s="24"/>
-      <c r="Z155" s="24"/>
-      <c r="AA155" s="24"/>
-      <c r="AB155" s="24"/>
-      <c r="AC155" s="24"/>
-      <c r="AD155" s="24"/>
-      <c r="AE155" s="24"/>
-      <c r="AF155" s="24"/>
-      <c r="AG155" s="24"/>
-      <c r="AH155" s="25"/>
+      <c r="B155" s="23"/>
+      <c r="C155" s="23"/>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
+      <c r="F155" s="23"/>
+      <c r="G155" s="24"/>
+      <c r="H155" s="24"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="23"/>
+      <c r="K155" s="23"/>
+      <c r="L155" s="24"/>
+      <c r="M155" s="24"/>
+      <c r="N155" s="25"/>
+      <c r="O155" s="23"/>
+      <c r="P155" s="23"/>
+      <c r="Q155" s="24"/>
+      <c r="R155" s="24"/>
+      <c r="S155" s="23"/>
+      <c r="T155" s="23"/>
+      <c r="U155" s="23"/>
+      <c r="V155" s="23"/>
+      <c r="W155" s="23"/>
+      <c r="X155" s="23"/>
+      <c r="Y155" s="23"/>
+      <c r="Z155" s="23"/>
+      <c r="AA155" s="23"/>
+      <c r="AB155" s="23"/>
+      <c r="AC155" s="23"/>
+      <c r="AD155" s="23"/>
+      <c r="AE155" s="23"/>
+      <c r="AF155" s="23"/>
+      <c r="AG155" s="23"/>
+      <c r="AH155" s="24"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="24"/>
-      <c r="C156" s="24"/>
-      <c r="D156" s="24"/>
-      <c r="E156" s="24"/>
-      <c r="F156" s="24"/>
-      <c r="G156" s="25"/>
-      <c r="H156" s="25"/>
-      <c r="I156" s="24"/>
-      <c r="J156" s="24"/>
-      <c r="K156" s="24"/>
-      <c r="L156" s="25"/>
-      <c r="M156" s="25"/>
-      <c r="N156" s="26"/>
-      <c r="O156" s="24"/>
-      <c r="P156" s="24"/>
-      <c r="Q156" s="25"/>
-      <c r="R156" s="25"/>
-      <c r="S156" s="24"/>
-      <c r="T156" s="24"/>
-      <c r="U156" s="24"/>
-      <c r="V156" s="24"/>
-      <c r="W156" s="24"/>
-      <c r="X156" s="24"/>
-      <c r="Y156" s="24"/>
-      <c r="Z156" s="24"/>
-      <c r="AA156" s="24"/>
-      <c r="AB156" s="24"/>
-      <c r="AC156" s="24"/>
-      <c r="AD156" s="24"/>
-      <c r="AE156" s="24"/>
-      <c r="AF156" s="24"/>
-      <c r="AG156" s="24"/>
-      <c r="AH156" s="25"/>
+      <c r="B156" s="23"/>
+      <c r="C156" s="23"/>
+      <c r="D156" s="23"/>
+      <c r="E156" s="23"/>
+      <c r="F156" s="23"/>
+      <c r="G156" s="24"/>
+      <c r="H156" s="24"/>
+      <c r="I156" s="23"/>
+      <c r="J156" s="23"/>
+      <c r="K156" s="23"/>
+      <c r="L156" s="24"/>
+      <c r="M156" s="24"/>
+      <c r="N156" s="25"/>
+      <c r="O156" s="23"/>
+      <c r="P156" s="23"/>
+      <c r="Q156" s="24"/>
+      <c r="R156" s="24"/>
+      <c r="S156" s="23"/>
+      <c r="T156" s="23"/>
+      <c r="U156" s="23"/>
+      <c r="V156" s="23"/>
+      <c r="W156" s="23"/>
+      <c r="X156" s="23"/>
+      <c r="Y156" s="23"/>
+      <c r="Z156" s="23"/>
+      <c r="AA156" s="23"/>
+      <c r="AB156" s="23"/>
+      <c r="AC156" s="23"/>
+      <c r="AD156" s="23"/>
+      <c r="AE156" s="23"/>
+      <c r="AF156" s="23"/>
+      <c r="AG156" s="23"/>
+      <c r="AH156" s="24"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="24"/>
-      <c r="C157" s="24"/>
-      <c r="D157" s="24"/>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="24"/>
-      <c r="K157" s="24"/>
-      <c r="L157" s="25"/>
-      <c r="M157" s="25"/>
-      <c r="N157" s="26"/>
-      <c r="O157" s="24"/>
-      <c r="P157" s="24"/>
-      <c r="Q157" s="25"/>
-      <c r="R157" s="25"/>
-      <c r="S157" s="24"/>
-      <c r="T157" s="24"/>
-      <c r="U157" s="24"/>
-      <c r="V157" s="24"/>
-      <c r="W157" s="24"/>
-      <c r="X157" s="24"/>
-      <c r="Y157" s="24"/>
-      <c r="Z157" s="24"/>
-      <c r="AA157" s="24"/>
-      <c r="AB157" s="24"/>
-      <c r="AC157" s="24"/>
-      <c r="AD157" s="24"/>
-      <c r="AE157" s="24"/>
-      <c r="AF157" s="24"/>
-      <c r="AG157" s="24"/>
-      <c r="AH157" s="25"/>
+      <c r="B157" s="23"/>
+      <c r="C157" s="23"/>
+      <c r="D157" s="23"/>
+      <c r="E157" s="23"/>
+      <c r="F157" s="23"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="23"/>
+      <c r="J157" s="23"/>
+      <c r="K157" s="23"/>
+      <c r="L157" s="24"/>
+      <c r="M157" s="24"/>
+      <c r="N157" s="25"/>
+      <c r="O157" s="23"/>
+      <c r="P157" s="23"/>
+      <c r="Q157" s="24"/>
+      <c r="R157" s="24"/>
+      <c r="S157" s="23"/>
+      <c r="T157" s="23"/>
+      <c r="U157" s="23"/>
+      <c r="V157" s="23"/>
+      <c r="W157" s="23"/>
+      <c r="X157" s="23"/>
+      <c r="Y157" s="23"/>
+      <c r="Z157" s="23"/>
+      <c r="AA157" s="23"/>
+      <c r="AB157" s="23"/>
+      <c r="AC157" s="23"/>
+      <c r="AD157" s="23"/>
+      <c r="AE157" s="23"/>
+      <c r="AF157" s="23"/>
+      <c r="AG157" s="23"/>
+      <c r="AH157" s="24"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="24"/>
-      <c r="C158" s="24"/>
-      <c r="D158" s="24"/>
-      <c r="E158" s="24"/>
-      <c r="F158" s="24"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
-      <c r="I158" s="24"/>
-      <c r="J158" s="24"/>
-      <c r="K158" s="24"/>
-      <c r="L158" s="25"/>
-      <c r="M158" s="25"/>
-      <c r="N158" s="26"/>
-      <c r="O158" s="24"/>
-      <c r="P158" s="24"/>
-      <c r="Q158" s="25"/>
-      <c r="R158" s="25"/>
-      <c r="S158" s="24"/>
-      <c r="T158" s="24"/>
-      <c r="U158" s="24"/>
-      <c r="V158" s="24"/>
-      <c r="W158" s="24"/>
-      <c r="X158" s="24"/>
-      <c r="Y158" s="24"/>
-      <c r="Z158" s="24"/>
-      <c r="AA158" s="24"/>
-      <c r="AB158" s="24"/>
-      <c r="AC158" s="24"/>
-      <c r="AD158" s="24"/>
-      <c r="AE158" s="24"/>
-      <c r="AF158" s="24"/>
-      <c r="AG158" s="24"/>
-      <c r="AH158" s="25"/>
+      <c r="B158" s="23"/>
+      <c r="C158" s="23"/>
+      <c r="D158" s="23"/>
+      <c r="E158" s="23"/>
+      <c r="F158" s="23"/>
+      <c r="G158" s="24"/>
+      <c r="H158" s="24"/>
+      <c r="I158" s="23"/>
+      <c r="J158" s="23"/>
+      <c r="K158" s="23"/>
+      <c r="L158" s="24"/>
+      <c r="M158" s="24"/>
+      <c r="N158" s="25"/>
+      <c r="O158" s="23"/>
+      <c r="P158" s="23"/>
+      <c r="Q158" s="24"/>
+      <c r="R158" s="24"/>
+      <c r="S158" s="23"/>
+      <c r="T158" s="23"/>
+      <c r="U158" s="23"/>
+      <c r="V158" s="23"/>
+      <c r="W158" s="23"/>
+      <c r="X158" s="23"/>
+      <c r="Y158" s="23"/>
+      <c r="Z158" s="23"/>
+      <c r="AA158" s="23"/>
+      <c r="AB158" s="23"/>
+      <c r="AC158" s="23"/>
+      <c r="AD158" s="23"/>
+      <c r="AE158" s="23"/>
+      <c r="AF158" s="23"/>
+      <c r="AG158" s="23"/>
+      <c r="AH158" s="24"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="24"/>
-      <c r="C159" s="24"/>
-      <c r="D159" s="24"/>
-      <c r="E159" s="24"/>
-      <c r="F159" s="24"/>
-      <c r="G159" s="25"/>
-      <c r="H159" s="25"/>
-      <c r="I159" s="24"/>
-      <c r="J159" s="24"/>
-      <c r="K159" s="24"/>
-      <c r="L159" s="25"/>
-      <c r="M159" s="25"/>
-      <c r="N159" s="26"/>
-      <c r="O159" s="24"/>
-      <c r="P159" s="24"/>
-      <c r="Q159" s="25"/>
-      <c r="R159" s="25"/>
-      <c r="S159" s="24"/>
-      <c r="T159" s="24"/>
-      <c r="U159" s="24"/>
-      <c r="V159" s="24"/>
-      <c r="W159" s="24"/>
-      <c r="X159" s="24"/>
-      <c r="Y159" s="24"/>
-      <c r="Z159" s="24"/>
-      <c r="AA159" s="24"/>
-      <c r="AB159" s="24"/>
-      <c r="AC159" s="24"/>
-      <c r="AD159" s="24"/>
-      <c r="AE159" s="24"/>
-      <c r="AF159" s="24"/>
-      <c r="AG159" s="24"/>
-      <c r="AH159" s="25"/>
+      <c r="B159" s="23"/>
+      <c r="C159" s="23"/>
+      <c r="D159" s="23"/>
+      <c r="E159" s="23"/>
+      <c r="F159" s="23"/>
+      <c r="G159" s="24"/>
+      <c r="H159" s="24"/>
+      <c r="I159" s="23"/>
+      <c r="J159" s="23"/>
+      <c r="K159" s="23"/>
+      <c r="L159" s="24"/>
+      <c r="M159" s="24"/>
+      <c r="N159" s="25"/>
+      <c r="O159" s="23"/>
+      <c r="P159" s="23"/>
+      <c r="Q159" s="24"/>
+      <c r="R159" s="24"/>
+      <c r="S159" s="23"/>
+      <c r="T159" s="23"/>
+      <c r="U159" s="23"/>
+      <c r="V159" s="23"/>
+      <c r="W159" s="23"/>
+      <c r="X159" s="23"/>
+      <c r="Y159" s="23"/>
+      <c r="Z159" s="23"/>
+      <c r="AA159" s="23"/>
+      <c r="AB159" s="23"/>
+      <c r="AC159" s="23"/>
+      <c r="AD159" s="23"/>
+      <c r="AE159" s="23"/>
+      <c r="AF159" s="23"/>
+      <c r="AG159" s="23"/>
+      <c r="AH159" s="24"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="24"/>
-      <c r="C160" s="24"/>
-      <c r="D160" s="24"/>
-      <c r="E160" s="24"/>
-      <c r="F160" s="24"/>
-      <c r="G160" s="25"/>
-      <c r="H160" s="25"/>
-      <c r="I160" s="24"/>
-      <c r="J160" s="24"/>
-      <c r="K160" s="24"/>
-      <c r="L160" s="25"/>
-      <c r="M160" s="25"/>
-      <c r="N160" s="26"/>
-      <c r="O160" s="24"/>
-      <c r="P160" s="24"/>
-      <c r="Q160" s="25"/>
-      <c r="R160" s="25"/>
-      <c r="S160" s="24"/>
-      <c r="T160" s="24"/>
-      <c r="U160" s="24"/>
-      <c r="V160" s="24"/>
-      <c r="W160" s="24"/>
-      <c r="X160" s="24"/>
-      <c r="Y160" s="24"/>
-      <c r="Z160" s="24"/>
-      <c r="AA160" s="24"/>
-      <c r="AB160" s="24"/>
-      <c r="AC160" s="24"/>
-      <c r="AD160" s="24"/>
-      <c r="AE160" s="24"/>
-      <c r="AF160" s="24"/>
-      <c r="AG160" s="24"/>
-      <c r="AH160" s="25"/>
+      <c r="B160" s="23"/>
+      <c r="C160" s="23"/>
+      <c r="D160" s="23"/>
+      <c r="E160" s="23"/>
+      <c r="F160" s="23"/>
+      <c r="G160" s="24"/>
+      <c r="H160" s="24"/>
+      <c r="I160" s="23"/>
+      <c r="J160" s="23"/>
+      <c r="K160" s="23"/>
+      <c r="L160" s="24"/>
+      <c r="M160" s="24"/>
+      <c r="N160" s="25"/>
+      <c r="O160" s="23"/>
+      <c r="P160" s="23"/>
+      <c r="Q160" s="24"/>
+      <c r="R160" s="24"/>
+      <c r="S160" s="23"/>
+      <c r="T160" s="23"/>
+      <c r="U160" s="23"/>
+      <c r="V160" s="23"/>
+      <c r="W160" s="23"/>
+      <c r="X160" s="23"/>
+      <c r="Y160" s="23"/>
+      <c r="Z160" s="23"/>
+      <c r="AA160" s="23"/>
+      <c r="AB160" s="23"/>
+      <c r="AC160" s="23"/>
+      <c r="AD160" s="23"/>
+      <c r="AE160" s="23"/>
+      <c r="AF160" s="23"/>
+      <c r="AG160" s="23"/>
+      <c r="AH160" s="24"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="24"/>
-      <c r="C161" s="24"/>
-      <c r="D161" s="24"/>
-      <c r="E161" s="24"/>
-      <c r="F161" s="24"/>
-      <c r="G161" s="25"/>
-      <c r="H161" s="25"/>
-      <c r="I161" s="24"/>
-      <c r="J161" s="24"/>
-      <c r="K161" s="24"/>
-      <c r="L161" s="25"/>
-      <c r="M161" s="25"/>
-      <c r="N161" s="26"/>
-      <c r="O161" s="24"/>
-      <c r="P161" s="24"/>
-      <c r="Q161" s="25"/>
-      <c r="R161" s="25"/>
-      <c r="S161" s="24"/>
-      <c r="T161" s="24"/>
-      <c r="U161" s="24"/>
-      <c r="V161" s="24"/>
-      <c r="W161" s="24"/>
-      <c r="X161" s="24"/>
-      <c r="Y161" s="24"/>
-      <c r="Z161" s="24"/>
-      <c r="AA161" s="24"/>
-      <c r="AB161" s="24"/>
-      <c r="AC161" s="24"/>
-      <c r="AD161" s="24"/>
-      <c r="AE161" s="24"/>
-      <c r="AF161" s="24"/>
-      <c r="AG161" s="24"/>
-      <c r="AH161" s="25"/>
+      <c r="B161" s="23"/>
+      <c r="C161" s="23"/>
+      <c r="D161" s="23"/>
+      <c r="E161" s="23"/>
+      <c r="F161" s="23"/>
+      <c r="G161" s="24"/>
+      <c r="H161" s="24"/>
+      <c r="I161" s="23"/>
+      <c r="J161" s="23"/>
+      <c r="K161" s="23"/>
+      <c r="L161" s="24"/>
+      <c r="M161" s="24"/>
+      <c r="N161" s="25"/>
+      <c r="O161" s="23"/>
+      <c r="P161" s="23"/>
+      <c r="Q161" s="24"/>
+      <c r="R161" s="24"/>
+      <c r="S161" s="23"/>
+      <c r="T161" s="23"/>
+      <c r="U161" s="23"/>
+      <c r="V161" s="23"/>
+      <c r="W161" s="23"/>
+      <c r="X161" s="23"/>
+      <c r="Y161" s="23"/>
+      <c r="Z161" s="23"/>
+      <c r="AA161" s="23"/>
+      <c r="AB161" s="23"/>
+      <c r="AC161" s="23"/>
+      <c r="AD161" s="23"/>
+      <c r="AE161" s="23"/>
+      <c r="AF161" s="23"/>
+      <c r="AG161" s="23"/>
+      <c r="AH161" s="24"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="24"/>
-      <c r="C162" s="24"/>
-      <c r="D162" s="24"/>
-      <c r="E162" s="24"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="25"/>
-      <c r="I162" s="24"/>
-      <c r="J162" s="24"/>
-      <c r="K162" s="24"/>
-      <c r="L162" s="25"/>
-      <c r="M162" s="25"/>
-      <c r="N162" s="26"/>
-      <c r="O162" s="24"/>
-      <c r="P162" s="24"/>
-      <c r="Q162" s="25"/>
-      <c r="R162" s="25"/>
-      <c r="S162" s="24"/>
-      <c r="T162" s="24"/>
-      <c r="U162" s="24"/>
-      <c r="V162" s="24"/>
-      <c r="W162" s="24"/>
-      <c r="X162" s="24"/>
-      <c r="Y162" s="24"/>
-      <c r="Z162" s="24"/>
-      <c r="AA162" s="24"/>
-      <c r="AB162" s="24"/>
-      <c r="AC162" s="24"/>
-      <c r="AD162" s="24"/>
-      <c r="AE162" s="24"/>
-      <c r="AF162" s="24"/>
-      <c r="AG162" s="24"/>
-      <c r="AH162" s="25"/>
+      <c r="B162" s="23"/>
+      <c r="C162" s="23"/>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
+      <c r="F162" s="23"/>
+      <c r="G162" s="24"/>
+      <c r="H162" s="24"/>
+      <c r="I162" s="23"/>
+      <c r="J162" s="23"/>
+      <c r="K162" s="23"/>
+      <c r="L162" s="24"/>
+      <c r="M162" s="24"/>
+      <c r="N162" s="25"/>
+      <c r="O162" s="23"/>
+      <c r="P162" s="23"/>
+      <c r="Q162" s="24"/>
+      <c r="R162" s="24"/>
+      <c r="S162" s="23"/>
+      <c r="T162" s="23"/>
+      <c r="U162" s="23"/>
+      <c r="V162" s="23"/>
+      <c r="W162" s="23"/>
+      <c r="X162" s="23"/>
+      <c r="Y162" s="23"/>
+      <c r="Z162" s="23"/>
+      <c r="AA162" s="23"/>
+      <c r="AB162" s="23"/>
+      <c r="AC162" s="23"/>
+      <c r="AD162" s="23"/>
+      <c r="AE162" s="23"/>
+      <c r="AF162" s="23"/>
+      <c r="AG162" s="23"/>
+      <c r="AH162" s="24"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="24"/>
-      <c r="C163" s="24"/>
-      <c r="D163" s="24"/>
-      <c r="E163" s="24"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="25"/>
-      <c r="I163" s="24"/>
-      <c r="J163" s="24"/>
-      <c r="K163" s="24"/>
-      <c r="L163" s="25"/>
-      <c r="M163" s="25"/>
-      <c r="N163" s="26"/>
-      <c r="O163" s="24"/>
-      <c r="P163" s="24"/>
-      <c r="Q163" s="25"/>
-      <c r="R163" s="25"/>
-      <c r="S163" s="24"/>
-      <c r="T163" s="24"/>
-      <c r="U163" s="24"/>
-      <c r="V163" s="24"/>
-      <c r="W163" s="24"/>
-      <c r="X163" s="24"/>
-      <c r="Y163" s="24"/>
-      <c r="Z163" s="24"/>
-      <c r="AA163" s="24"/>
-      <c r="AB163" s="24"/>
-      <c r="AC163" s="24"/>
-      <c r="AD163" s="24"/>
-      <c r="AE163" s="24"/>
-      <c r="AF163" s="24"/>
-      <c r="AG163" s="24"/>
-      <c r="AH163" s="25"/>
+      <c r="B163" s="23"/>
+      <c r="C163" s="23"/>
+      <c r="D163" s="23"/>
+      <c r="E163" s="23"/>
+      <c r="F163" s="23"/>
+      <c r="G163" s="24"/>
+      <c r="H163" s="24"/>
+      <c r="I163" s="23"/>
+      <c r="J163" s="23"/>
+      <c r="K163" s="23"/>
+      <c r="L163" s="24"/>
+      <c r="M163" s="24"/>
+      <c r="N163" s="25"/>
+      <c r="O163" s="23"/>
+      <c r="P163" s="23"/>
+      <c r="Q163" s="24"/>
+      <c r="R163" s="24"/>
+      <c r="S163" s="23"/>
+      <c r="T163" s="23"/>
+      <c r="U163" s="23"/>
+      <c r="V163" s="23"/>
+      <c r="W163" s="23"/>
+      <c r="X163" s="23"/>
+      <c r="Y163" s="23"/>
+      <c r="Z163" s="23"/>
+      <c r="AA163" s="23"/>
+      <c r="AB163" s="23"/>
+      <c r="AC163" s="23"/>
+      <c r="AD163" s="23"/>
+      <c r="AE163" s="23"/>
+      <c r="AF163" s="23"/>
+      <c r="AG163" s="23"/>
+      <c r="AH163" s="24"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="24"/>
-      <c r="C164" s="24"/>
-      <c r="D164" s="24"/>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="24"/>
-      <c r="K164" s="24"/>
-      <c r="L164" s="25"/>
-      <c r="M164" s="25"/>
-      <c r="N164" s="26"/>
-      <c r="O164" s="24"/>
-      <c r="P164" s="24"/>
-      <c r="Q164" s="25"/>
-      <c r="R164" s="25"/>
-      <c r="S164" s="24"/>
-      <c r="T164" s="24"/>
-      <c r="U164" s="24"/>
-      <c r="V164" s="24"/>
-      <c r="W164" s="24"/>
-      <c r="X164" s="24"/>
-      <c r="Y164" s="24"/>
-      <c r="Z164" s="24"/>
-      <c r="AA164" s="24"/>
-      <c r="AB164" s="24"/>
-      <c r="AC164" s="24"/>
-      <c r="AD164" s="24"/>
-      <c r="AE164" s="24"/>
-      <c r="AF164" s="24"/>
-      <c r="AG164" s="24"/>
-      <c r="AH164" s="25"/>
+      <c r="B164" s="23"/>
+      <c r="C164" s="23"/>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
+      <c r="F164" s="23"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="23"/>
+      <c r="J164" s="23"/>
+      <c r="K164" s="23"/>
+      <c r="L164" s="24"/>
+      <c r="M164" s="24"/>
+      <c r="N164" s="25"/>
+      <c r="O164" s="23"/>
+      <c r="P164" s="23"/>
+      <c r="Q164" s="24"/>
+      <c r="R164" s="24"/>
+      <c r="S164" s="23"/>
+      <c r="T164" s="23"/>
+      <c r="U164" s="23"/>
+      <c r="V164" s="23"/>
+      <c r="W164" s="23"/>
+      <c r="X164" s="23"/>
+      <c r="Y164" s="23"/>
+      <c r="Z164" s="23"/>
+      <c r="AA164" s="23"/>
+      <c r="AB164" s="23"/>
+      <c r="AC164" s="23"/>
+      <c r="AD164" s="23"/>
+      <c r="AE164" s="23"/>
+      <c r="AF164" s="23"/>
+      <c r="AG164" s="23"/>
+      <c r="AH164" s="24"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="24"/>
-      <c r="C165" s="24"/>
-      <c r="D165" s="24"/>
-      <c r="E165" s="24"/>
-      <c r="F165" s="24"/>
-      <c r="G165" s="25"/>
-      <c r="H165" s="25"/>
-      <c r="I165" s="24"/>
-      <c r="J165" s="24"/>
-      <c r="K165" s="24"/>
-      <c r="L165" s="25"/>
-      <c r="M165" s="25"/>
-      <c r="N165" s="26"/>
-      <c r="O165" s="24"/>
-      <c r="P165" s="24"/>
-      <c r="Q165" s="25"/>
-      <c r="R165" s="25"/>
-      <c r="S165" s="24"/>
-      <c r="T165" s="24"/>
-      <c r="U165" s="24"/>
-      <c r="V165" s="24"/>
-      <c r="W165" s="24"/>
-      <c r="X165" s="24"/>
-      <c r="Y165" s="24"/>
-      <c r="Z165" s="24"/>
-      <c r="AA165" s="24"/>
-      <c r="AB165" s="24"/>
-      <c r="AC165" s="24"/>
-      <c r="AD165" s="24"/>
-      <c r="AE165" s="24"/>
-      <c r="AF165" s="24"/>
-      <c r="AG165" s="24"/>
-      <c r="AH165" s="25"/>
+      <c r="B165" s="23"/>
+      <c r="C165" s="23"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
+      <c r="F165" s="23"/>
+      <c r="G165" s="24"/>
+      <c r="H165" s="24"/>
+      <c r="I165" s="23"/>
+      <c r="J165" s="23"/>
+      <c r="K165" s="23"/>
+      <c r="L165" s="24"/>
+      <c r="M165" s="24"/>
+      <c r="N165" s="25"/>
+      <c r="O165" s="23"/>
+      <c r="P165" s="23"/>
+      <c r="Q165" s="24"/>
+      <c r="R165" s="24"/>
+      <c r="S165" s="23"/>
+      <c r="T165" s="23"/>
+      <c r="U165" s="23"/>
+      <c r="V165" s="23"/>
+      <c r="W165" s="23"/>
+      <c r="X165" s="23"/>
+      <c r="Y165" s="23"/>
+      <c r="Z165" s="23"/>
+      <c r="AA165" s="23"/>
+      <c r="AB165" s="23"/>
+      <c r="AC165" s="23"/>
+      <c r="AD165" s="23"/>
+      <c r="AE165" s="23"/>
+      <c r="AF165" s="23"/>
+      <c r="AG165" s="23"/>
+      <c r="AH165" s="24"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="24"/>
-      <c r="C166" s="24"/>
-      <c r="D166" s="24"/>
-      <c r="E166" s="24"/>
-      <c r="F166" s="24"/>
-      <c r="G166" s="25"/>
-      <c r="H166" s="25"/>
-      <c r="I166" s="24"/>
-      <c r="J166" s="24"/>
-      <c r="K166" s="24"/>
-      <c r="L166" s="25"/>
-      <c r="M166" s="25"/>
-      <c r="N166" s="26"/>
-      <c r="O166" s="24"/>
-      <c r="P166" s="24"/>
-      <c r="Q166" s="25"/>
-      <c r="R166" s="25"/>
-      <c r="S166" s="24"/>
-      <c r="T166" s="24"/>
-      <c r="U166" s="24"/>
-      <c r="V166" s="24"/>
-      <c r="W166" s="24"/>
-      <c r="X166" s="24"/>
-      <c r="Y166" s="24"/>
-      <c r="Z166" s="24"/>
-      <c r="AA166" s="24"/>
-      <c r="AB166" s="24"/>
-      <c r="AC166" s="24"/>
-      <c r="AD166" s="24"/>
-      <c r="AE166" s="24"/>
-      <c r="AF166" s="24"/>
-      <c r="AG166" s="24"/>
-      <c r="AH166" s="25"/>
+      <c r="B166" s="23"/>
+      <c r="C166" s="23"/>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
+      <c r="F166" s="23"/>
+      <c r="G166" s="24"/>
+      <c r="H166" s="24"/>
+      <c r="I166" s="23"/>
+      <c r="J166" s="23"/>
+      <c r="K166" s="23"/>
+      <c r="L166" s="24"/>
+      <c r="M166" s="24"/>
+      <c r="N166" s="25"/>
+      <c r="O166" s="23"/>
+      <c r="P166" s="23"/>
+      <c r="Q166" s="24"/>
+      <c r="R166" s="24"/>
+      <c r="S166" s="23"/>
+      <c r="T166" s="23"/>
+      <c r="U166" s="23"/>
+      <c r="V166" s="23"/>
+      <c r="W166" s="23"/>
+      <c r="X166" s="23"/>
+      <c r="Y166" s="23"/>
+      <c r="Z166" s="23"/>
+      <c r="AA166" s="23"/>
+      <c r="AB166" s="23"/>
+      <c r="AC166" s="23"/>
+      <c r="AD166" s="23"/>
+      <c r="AE166" s="23"/>
+      <c r="AF166" s="23"/>
+      <c r="AG166" s="23"/>
+      <c r="AH166" s="24"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
-      <c r="I167" s="24"/>
-      <c r="J167" s="24"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="25"/>
-      <c r="M167" s="25"/>
-      <c r="N167" s="26"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="25"/>
-      <c r="R167" s="25"/>
-      <c r="S167" s="24"/>
-      <c r="T167" s="24"/>
-      <c r="U167" s="24"/>
-      <c r="V167" s="24"/>
-      <c r="W167" s="24"/>
-      <c r="X167" s="24"/>
-      <c r="Y167" s="24"/>
-      <c r="Z167" s="24"/>
-      <c r="AA167" s="24"/>
-      <c r="AB167" s="24"/>
-      <c r="AC167" s="24"/>
-      <c r="AD167" s="24"/>
-      <c r="AE167" s="24"/>
-      <c r="AF167" s="24"/>
-      <c r="AG167" s="24"/>
-      <c r="AH167" s="25"/>
+      <c r="B167" s="23"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="23"/>
+      <c r="E167" s="23"/>
+      <c r="F167" s="23"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
+      <c r="I167" s="23"/>
+      <c r="J167" s="23"/>
+      <c r="K167" s="23"/>
+      <c r="L167" s="24"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="25"/>
+      <c r="O167" s="23"/>
+      <c r="P167" s="23"/>
+      <c r="Q167" s="24"/>
+      <c r="R167" s="24"/>
+      <c r="S167" s="23"/>
+      <c r="T167" s="23"/>
+      <c r="U167" s="23"/>
+      <c r="V167" s="23"/>
+      <c r="W167" s="23"/>
+      <c r="X167" s="23"/>
+      <c r="Y167" s="23"/>
+      <c r="Z167" s="23"/>
+      <c r="AA167" s="23"/>
+      <c r="AB167" s="23"/>
+      <c r="AC167" s="23"/>
+      <c r="AD167" s="23"/>
+      <c r="AE167" s="23"/>
+      <c r="AF167" s="23"/>
+      <c r="AG167" s="23"/>
+      <c r="AH167" s="24"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="24"/>
-      <c r="C168" s="24"/>
-      <c r="D168" s="24"/>
-      <c r="E168" s="24"/>
-      <c r="F168" s="24"/>
-      <c r="G168" s="25"/>
-      <c r="H168" s="25"/>
-      <c r="I168" s="24"/>
-      <c r="J168" s="24"/>
-      <c r="K168" s="24"/>
-      <c r="L168" s="25"/>
-      <c r="M168" s="25"/>
-      <c r="N168" s="26"/>
-      <c r="O168" s="24"/>
-      <c r="P168" s="24"/>
-      <c r="Q168" s="25"/>
-      <c r="R168" s="25"/>
-      <c r="S168" s="24"/>
-      <c r="T168" s="24"/>
-      <c r="U168" s="24"/>
-      <c r="V168" s="24"/>
-      <c r="W168" s="24"/>
-      <c r="X168" s="24"/>
-      <c r="Y168" s="24"/>
-      <c r="Z168" s="24"/>
-      <c r="AA168" s="24"/>
-      <c r="AB168" s="24"/>
-      <c r="AC168" s="24"/>
-      <c r="AD168" s="24"/>
-      <c r="AE168" s="24"/>
-      <c r="AF168" s="24"/>
-      <c r="AG168" s="24"/>
-      <c r="AH168" s="25"/>
+      <c r="B168" s="23"/>
+      <c r="C168" s="23"/>
+      <c r="D168" s="23"/>
+      <c r="E168" s="23"/>
+      <c r="F168" s="23"/>
+      <c r="G168" s="24"/>
+      <c r="H168" s="24"/>
+      <c r="I168" s="23"/>
+      <c r="J168" s="23"/>
+      <c r="K168" s="23"/>
+      <c r="L168" s="24"/>
+      <c r="M168" s="24"/>
+      <c r="N168" s="25"/>
+      <c r="O168" s="23"/>
+      <c r="P168" s="23"/>
+      <c r="Q168" s="24"/>
+      <c r="R168" s="24"/>
+      <c r="S168" s="23"/>
+      <c r="T168" s="23"/>
+      <c r="U168" s="23"/>
+      <c r="V168" s="23"/>
+      <c r="W168" s="23"/>
+      <c r="X168" s="23"/>
+      <c r="Y168" s="23"/>
+      <c r="Z168" s="23"/>
+      <c r="AA168" s="23"/>
+      <c r="AB168" s="23"/>
+      <c r="AC168" s="23"/>
+      <c r="AD168" s="23"/>
+      <c r="AE168" s="23"/>
+      <c r="AF168" s="23"/>
+      <c r="AG168" s="23"/>
+      <c r="AH168" s="24"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="24"/>
-      <c r="C169" s="24"/>
-      <c r="D169" s="24"/>
-      <c r="E169" s="24"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="25"/>
-      <c r="H169" s="25"/>
-      <c r="I169" s="24"/>
-      <c r="J169" s="24"/>
-      <c r="K169" s="24"/>
-      <c r="L169" s="25"/>
-      <c r="M169" s="25"/>
-      <c r="N169" s="26"/>
-      <c r="O169" s="24"/>
-      <c r="P169" s="24"/>
-      <c r="Q169" s="25"/>
-      <c r="R169" s="25"/>
-      <c r="S169" s="24"/>
-      <c r="T169" s="24"/>
-      <c r="U169" s="24"/>
-      <c r="V169" s="24"/>
-      <c r="W169" s="24"/>
-      <c r="X169" s="24"/>
-      <c r="Y169" s="24"/>
-      <c r="Z169" s="24"/>
-      <c r="AA169" s="24"/>
-      <c r="AB169" s="24"/>
-      <c r="AC169" s="24"/>
-      <c r="AD169" s="24"/>
-      <c r="AE169" s="24"/>
-      <c r="AF169" s="24"/>
-      <c r="AG169" s="24"/>
-      <c r="AH169" s="25"/>
+      <c r="B169" s="23"/>
+      <c r="C169" s="23"/>
+      <c r="D169" s="23"/>
+      <c r="E169" s="23"/>
+      <c r="F169" s="23"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="24"/>
+      <c r="I169" s="23"/>
+      <c r="J169" s="23"/>
+      <c r="K169" s="23"/>
+      <c r="L169" s="24"/>
+      <c r="M169" s="24"/>
+      <c r="N169" s="25"/>
+      <c r="O169" s="23"/>
+      <c r="P169" s="23"/>
+      <c r="Q169" s="24"/>
+      <c r="R169" s="24"/>
+      <c r="S169" s="23"/>
+      <c r="T169" s="23"/>
+      <c r="U169" s="23"/>
+      <c r="V169" s="23"/>
+      <c r="W169" s="23"/>
+      <c r="X169" s="23"/>
+      <c r="Y169" s="23"/>
+      <c r="Z169" s="23"/>
+      <c r="AA169" s="23"/>
+      <c r="AB169" s="23"/>
+      <c r="AC169" s="23"/>
+      <c r="AD169" s="23"/>
+      <c r="AE169" s="23"/>
+      <c r="AF169" s="23"/>
+      <c r="AG169" s="23"/>
+      <c r="AH169" s="24"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="24"/>
-      <c r="C170" s="24"/>
-      <c r="D170" s="24"/>
-      <c r="E170" s="24"/>
-      <c r="F170" s="24"/>
-      <c r="G170" s="25"/>
-      <c r="H170" s="25"/>
-      <c r="I170" s="24"/>
-      <c r="J170" s="24"/>
-      <c r="K170" s="24"/>
-      <c r="L170" s="25"/>
-      <c r="M170" s="25"/>
-      <c r="N170" s="26"/>
-      <c r="O170" s="24"/>
-      <c r="P170" s="24"/>
-      <c r="Q170" s="25"/>
-      <c r="R170" s="25"/>
-      <c r="S170" s="24"/>
-      <c r="T170" s="24"/>
-      <c r="U170" s="24"/>
-      <c r="V170" s="24"/>
-      <c r="W170" s="24"/>
-      <c r="X170" s="24"/>
-      <c r="Y170" s="24"/>
-      <c r="Z170" s="24"/>
-      <c r="AA170" s="24"/>
-      <c r="AB170" s="24"/>
-      <c r="AC170" s="24"/>
-      <c r="AD170" s="24"/>
-      <c r="AE170" s="24"/>
-      <c r="AF170" s="24"/>
-      <c r="AG170" s="24"/>
-      <c r="AH170" s="25"/>
+      <c r="B170" s="23"/>
+      <c r="C170" s="23"/>
+      <c r="D170" s="23"/>
+      <c r="E170" s="23"/>
+      <c r="F170" s="23"/>
+      <c r="G170" s="24"/>
+      <c r="H170" s="24"/>
+      <c r="I170" s="23"/>
+      <c r="J170" s="23"/>
+      <c r="K170" s="23"/>
+      <c r="L170" s="24"/>
+      <c r="M170" s="24"/>
+      <c r="N170" s="25"/>
+      <c r="O170" s="23"/>
+      <c r="P170" s="23"/>
+      <c r="Q170" s="24"/>
+      <c r="R170" s="24"/>
+      <c r="S170" s="23"/>
+      <c r="T170" s="23"/>
+      <c r="U170" s="23"/>
+      <c r="V170" s="23"/>
+      <c r="W170" s="23"/>
+      <c r="X170" s="23"/>
+      <c r="Y170" s="23"/>
+      <c r="Z170" s="23"/>
+      <c r="AA170" s="23"/>
+      <c r="AB170" s="23"/>
+      <c r="AC170" s="23"/>
+      <c r="AD170" s="23"/>
+      <c r="AE170" s="23"/>
+      <c r="AF170" s="23"/>
+      <c r="AG170" s="23"/>
+      <c r="AH170" s="24"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="24"/>
-      <c r="C171" s="24"/>
-      <c r="D171" s="24"/>
-      <c r="E171" s="24"/>
-      <c r="F171" s="24"/>
-      <c r="G171" s="25"/>
-      <c r="H171" s="25"/>
-      <c r="I171" s="24"/>
-      <c r="J171" s="24"/>
-      <c r="K171" s="24"/>
-      <c r="L171" s="25"/>
-      <c r="M171" s="25"/>
-      <c r="N171" s="26"/>
-      <c r="O171" s="24"/>
-      <c r="P171" s="24"/>
-      <c r="Q171" s="25"/>
-      <c r="R171" s="25"/>
-      <c r="S171" s="24"/>
-      <c r="T171" s="24"/>
-      <c r="U171" s="24"/>
-      <c r="V171" s="24"/>
-      <c r="W171" s="24"/>
-      <c r="X171" s="24"/>
-      <c r="Y171" s="24"/>
-      <c r="Z171" s="24"/>
-      <c r="AA171" s="24"/>
-      <c r="AB171" s="24"/>
-      <c r="AC171" s="24"/>
-      <c r="AD171" s="24"/>
-      <c r="AE171" s="24"/>
-      <c r="AF171" s="24"/>
-      <c r="AG171" s="24"/>
-      <c r="AH171" s="25"/>
+      <c r="B171" s="23"/>
+      <c r="C171" s="23"/>
+      <c r="D171" s="23"/>
+      <c r="E171" s="23"/>
+      <c r="F171" s="23"/>
+      <c r="G171" s="24"/>
+      <c r="H171" s="24"/>
+      <c r="I171" s="23"/>
+      <c r="J171" s="23"/>
+      <c r="K171" s="23"/>
+      <c r="L171" s="24"/>
+      <c r="M171" s="24"/>
+      <c r="N171" s="25"/>
+      <c r="O171" s="23"/>
+      <c r="P171" s="23"/>
+      <c r="Q171" s="24"/>
+      <c r="R171" s="24"/>
+      <c r="S171" s="23"/>
+      <c r="T171" s="23"/>
+      <c r="U171" s="23"/>
+      <c r="V171" s="23"/>
+      <c r="W171" s="23"/>
+      <c r="X171" s="23"/>
+      <c r="Y171" s="23"/>
+      <c r="Z171" s="23"/>
+      <c r="AA171" s="23"/>
+      <c r="AB171" s="23"/>
+      <c r="AC171" s="23"/>
+      <c r="AD171" s="23"/>
+      <c r="AE171" s="23"/>
+      <c r="AF171" s="23"/>
+      <c r="AG171" s="23"/>
+      <c r="AH171" s="24"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="24"/>
-      <c r="C172" s="24"/>
-      <c r="D172" s="24"/>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="24"/>
-      <c r="K172" s="24"/>
-      <c r="L172" s="25"/>
-      <c r="M172" s="25"/>
-      <c r="N172" s="26"/>
-      <c r="O172" s="24"/>
-      <c r="P172" s="24"/>
-      <c r="Q172" s="25"/>
-      <c r="R172" s="25"/>
-      <c r="S172" s="24"/>
-      <c r="T172" s="24"/>
-      <c r="U172" s="24"/>
-      <c r="V172" s="24"/>
-      <c r="W172" s="24"/>
-      <c r="X172" s="24"/>
-      <c r="Y172" s="24"/>
-      <c r="Z172" s="24"/>
-      <c r="AA172" s="24"/>
-      <c r="AB172" s="24"/>
-      <c r="AC172" s="24"/>
-      <c r="AD172" s="24"/>
-      <c r="AE172" s="24"/>
-      <c r="AF172" s="24"/>
-      <c r="AG172" s="24"/>
-      <c r="AH172" s="25"/>
+      <c r="B172" s="23"/>
+      <c r="C172" s="23"/>
+      <c r="D172" s="23"/>
+      <c r="E172" s="23"/>
+      <c r="F172" s="23"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="23"/>
+      <c r="J172" s="23"/>
+      <c r="K172" s="23"/>
+      <c r="L172" s="24"/>
+      <c r="M172" s="24"/>
+      <c r="N172" s="25"/>
+      <c r="O172" s="23"/>
+      <c r="P172" s="23"/>
+      <c r="Q172" s="24"/>
+      <c r="R172" s="24"/>
+      <c r="S172" s="23"/>
+      <c r="T172" s="23"/>
+      <c r="U172" s="23"/>
+      <c r="V172" s="23"/>
+      <c r="W172" s="23"/>
+      <c r="X172" s="23"/>
+      <c r="Y172" s="23"/>
+      <c r="Z172" s="23"/>
+      <c r="AA172" s="23"/>
+      <c r="AB172" s="23"/>
+      <c r="AC172" s="23"/>
+      <c r="AD172" s="23"/>
+      <c r="AE172" s="23"/>
+      <c r="AF172" s="23"/>
+      <c r="AG172" s="23"/>
+      <c r="AH172" s="24"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="24"/>
-      <c r="C173" s="24"/>
-      <c r="D173" s="24"/>
-      <c r="E173" s="24"/>
-      <c r="F173" s="24"/>
-      <c r="G173" s="25"/>
-      <c r="H173" s="25"/>
-      <c r="I173" s="24"/>
-      <c r="J173" s="24"/>
-      <c r="K173" s="24"/>
-      <c r="L173" s="25"/>
-      <c r="M173" s="25"/>
-      <c r="N173" s="26"/>
-      <c r="O173" s="24"/>
-      <c r="P173" s="24"/>
-      <c r="Q173" s="25"/>
-      <c r="R173" s="25"/>
-      <c r="S173" s="24"/>
-      <c r="T173" s="24"/>
-      <c r="U173" s="24"/>
-      <c r="V173" s="24"/>
-      <c r="W173" s="24"/>
-      <c r="X173" s="24"/>
-      <c r="Y173" s="24"/>
-      <c r="Z173" s="24"/>
-      <c r="AA173" s="24"/>
-      <c r="AB173" s="24"/>
-      <c r="AC173" s="24"/>
-      <c r="AD173" s="24"/>
-      <c r="AE173" s="24"/>
-      <c r="AF173" s="24"/>
-      <c r="AG173" s="24"/>
-      <c r="AH173" s="25"/>
+      <c r="B173" s="23"/>
+      <c r="C173" s="23"/>
+      <c r="D173" s="23"/>
+      <c r="E173" s="23"/>
+      <c r="F173" s="23"/>
+      <c r="G173" s="24"/>
+      <c r="H173" s="24"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="23"/>
+      <c r="K173" s="23"/>
+      <c r="L173" s="24"/>
+      <c r="M173" s="24"/>
+      <c r="N173" s="25"/>
+      <c r="O173" s="23"/>
+      <c r="P173" s="23"/>
+      <c r="Q173" s="24"/>
+      <c r="R173" s="24"/>
+      <c r="S173" s="23"/>
+      <c r="T173" s="23"/>
+      <c r="U173" s="23"/>
+      <c r="V173" s="23"/>
+      <c r="W173" s="23"/>
+      <c r="X173" s="23"/>
+      <c r="Y173" s="23"/>
+      <c r="Z173" s="23"/>
+      <c r="AA173" s="23"/>
+      <c r="AB173" s="23"/>
+      <c r="AC173" s="23"/>
+      <c r="AD173" s="23"/>
+      <c r="AE173" s="23"/>
+      <c r="AF173" s="23"/>
+      <c r="AG173" s="23"/>
+      <c r="AH173" s="24"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="24"/>
-      <c r="C174" s="24"/>
-      <c r="D174" s="24"/>
-      <c r="E174" s="24"/>
-      <c r="F174" s="24"/>
-      <c r="G174" s="25"/>
-      <c r="H174" s="25"/>
-      <c r="I174" s="24"/>
-      <c r="J174" s="24"/>
-      <c r="K174" s="24"/>
-      <c r="L174" s="25"/>
-      <c r="M174" s="25"/>
-      <c r="N174" s="26"/>
-      <c r="O174" s="24"/>
-      <c r="P174" s="24"/>
-      <c r="Q174" s="25"/>
-      <c r="R174" s="25"/>
-      <c r="S174" s="24"/>
-      <c r="T174" s="24"/>
-      <c r="U174" s="24"/>
-      <c r="V174" s="24"/>
-      <c r="W174" s="24"/>
-      <c r="X174" s="24"/>
-      <c r="Y174" s="24"/>
-      <c r="Z174" s="24"/>
-      <c r="AA174" s="24"/>
-      <c r="AB174" s="24"/>
-      <c r="AC174" s="24"/>
-      <c r="AD174" s="24"/>
-      <c r="AE174" s="24"/>
-      <c r="AF174" s="24"/>
-      <c r="AG174" s="24"/>
-      <c r="AH174" s="25"/>
+      <c r="B174" s="23"/>
+      <c r="C174" s="23"/>
+      <c r="D174" s="23"/>
+      <c r="E174" s="23"/>
+      <c r="F174" s="23"/>
+      <c r="G174" s="24"/>
+      <c r="H174" s="24"/>
+      <c r="I174" s="23"/>
+      <c r="J174" s="23"/>
+      <c r="K174" s="23"/>
+      <c r="L174" s="24"/>
+      <c r="M174" s="24"/>
+      <c r="N174" s="25"/>
+      <c r="O174" s="23"/>
+      <c r="P174" s="23"/>
+      <c r="Q174" s="24"/>
+      <c r="R174" s="24"/>
+      <c r="S174" s="23"/>
+      <c r="T174" s="23"/>
+      <c r="U174" s="23"/>
+      <c r="V174" s="23"/>
+      <c r="W174" s="23"/>
+      <c r="X174" s="23"/>
+      <c r="Y174" s="23"/>
+      <c r="Z174" s="23"/>
+      <c r="AA174" s="23"/>
+      <c r="AB174" s="23"/>
+      <c r="AC174" s="23"/>
+      <c r="AD174" s="23"/>
+      <c r="AE174" s="23"/>
+      <c r="AF174" s="23"/>
+      <c r="AG174" s="23"/>
+      <c r="AH174" s="24"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="24"/>
-      <c r="C175" s="24"/>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="25"/>
-      <c r="H175" s="25"/>
-      <c r="I175" s="24"/>
-      <c r="J175" s="24"/>
-      <c r="K175" s="24"/>
-      <c r="L175" s="25"/>
-      <c r="M175" s="25"/>
-      <c r="N175" s="26"/>
-      <c r="O175" s="24"/>
-      <c r="P175" s="24"/>
-      <c r="Q175" s="25"/>
-      <c r="R175" s="25"/>
-      <c r="S175" s="24"/>
-      <c r="T175" s="24"/>
-      <c r="U175" s="24"/>
-      <c r="V175" s="24"/>
-      <c r="W175" s="24"/>
-      <c r="X175" s="24"/>
-      <c r="Y175" s="24"/>
-      <c r="Z175" s="24"/>
-      <c r="AA175" s="24"/>
-      <c r="AB175" s="24"/>
-      <c r="AC175" s="24"/>
-      <c r="AD175" s="24"/>
-      <c r="AE175" s="24"/>
-      <c r="AF175" s="24"/>
-      <c r="AG175" s="24"/>
-      <c r="AH175" s="25"/>
+      <c r="B175" s="23"/>
+      <c r="C175" s="23"/>
+      <c r="D175" s="23"/>
+      <c r="E175" s="23"/>
+      <c r="F175" s="23"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="23"/>
+      <c r="J175" s="23"/>
+      <c r="K175" s="23"/>
+      <c r="L175" s="24"/>
+      <c r="M175" s="24"/>
+      <c r="N175" s="25"/>
+      <c r="O175" s="23"/>
+      <c r="P175" s="23"/>
+      <c r="Q175" s="24"/>
+      <c r="R175" s="24"/>
+      <c r="S175" s="23"/>
+      <c r="T175" s="23"/>
+      <c r="U175" s="23"/>
+      <c r="V175" s="23"/>
+      <c r="W175" s="23"/>
+      <c r="X175" s="23"/>
+      <c r="Y175" s="23"/>
+      <c r="Z175" s="23"/>
+      <c r="AA175" s="23"/>
+      <c r="AB175" s="23"/>
+      <c r="AC175" s="23"/>
+      <c r="AD175" s="23"/>
+      <c r="AE175" s="23"/>
+      <c r="AF175" s="23"/>
+      <c r="AG175" s="23"/>
+      <c r="AH175" s="24"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="24"/>
-      <c r="C176" s="24"/>
-      <c r="D176" s="24"/>
-      <c r="E176" s="24"/>
-      <c r="F176" s="24"/>
-      <c r="G176" s="25"/>
-      <c r="H176" s="25"/>
-      <c r="I176" s="24"/>
-      <c r="J176" s="24"/>
-      <c r="K176" s="24"/>
-      <c r="L176" s="25"/>
-      <c r="M176" s="25"/>
-      <c r="N176" s="26"/>
-      <c r="O176" s="24"/>
-      <c r="P176" s="24"/>
-      <c r="Q176" s="25"/>
-      <c r="R176" s="25"/>
-      <c r="S176" s="24"/>
-      <c r="T176" s="24"/>
-      <c r="U176" s="24"/>
-      <c r="V176" s="24"/>
-      <c r="W176" s="24"/>
-      <c r="X176" s="24"/>
-      <c r="Y176" s="24"/>
-      <c r="Z176" s="24"/>
-      <c r="AA176" s="24"/>
-      <c r="AB176" s="24"/>
-      <c r="AC176" s="24"/>
-      <c r="AD176" s="24"/>
-      <c r="AE176" s="24"/>
-      <c r="AF176" s="24"/>
-      <c r="AG176" s="24"/>
-      <c r="AH176" s="25"/>
+      <c r="B176" s="23"/>
+      <c r="C176" s="23"/>
+      <c r="D176" s="23"/>
+      <c r="E176" s="23"/>
+      <c r="F176" s="23"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="24"/>
+      <c r="I176" s="23"/>
+      <c r="J176" s="23"/>
+      <c r="K176" s="23"/>
+      <c r="L176" s="24"/>
+      <c r="M176" s="24"/>
+      <c r="N176" s="25"/>
+      <c r="O176" s="23"/>
+      <c r="P176" s="23"/>
+      <c r="Q176" s="24"/>
+      <c r="R176" s="24"/>
+      <c r="S176" s="23"/>
+      <c r="T176" s="23"/>
+      <c r="U176" s="23"/>
+      <c r="V176" s="23"/>
+      <c r="W176" s="23"/>
+      <c r="X176" s="23"/>
+      <c r="Y176" s="23"/>
+      <c r="Z176" s="23"/>
+      <c r="AA176" s="23"/>
+      <c r="AB176" s="23"/>
+      <c r="AC176" s="23"/>
+      <c r="AD176" s="23"/>
+      <c r="AE176" s="23"/>
+      <c r="AF176" s="23"/>
+      <c r="AG176" s="23"/>
+      <c r="AH176" s="24"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="24"/>
-      <c r="C177" s="24"/>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="24"/>
-      <c r="K177" s="24"/>
-      <c r="L177" s="25"/>
-      <c r="M177" s="25"/>
-      <c r="N177" s="26"/>
-      <c r="O177" s="24"/>
-      <c r="P177" s="24"/>
-      <c r="Q177" s="25"/>
-      <c r="R177" s="25"/>
-      <c r="S177" s="24"/>
-      <c r="T177" s="24"/>
-      <c r="U177" s="24"/>
-      <c r="V177" s="24"/>
-      <c r="W177" s="24"/>
-      <c r="X177" s="24"/>
-      <c r="Y177" s="24"/>
-      <c r="Z177" s="24"/>
-      <c r="AA177" s="24"/>
-      <c r="AB177" s="24"/>
-      <c r="AC177" s="24"/>
-      <c r="AD177" s="24"/>
-      <c r="AE177" s="24"/>
-      <c r="AF177" s="24"/>
-      <c r="AG177" s="24"/>
-      <c r="AH177" s="25"/>
+      <c r="B177" s="23"/>
+      <c r="C177" s="23"/>
+      <c r="D177" s="23"/>
+      <c r="E177" s="23"/>
+      <c r="F177" s="23"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="23"/>
+      <c r="J177" s="23"/>
+      <c r="K177" s="23"/>
+      <c r="L177" s="24"/>
+      <c r="M177" s="24"/>
+      <c r="N177" s="25"/>
+      <c r="O177" s="23"/>
+      <c r="P177" s="23"/>
+      <c r="Q177" s="24"/>
+      <c r="R177" s="24"/>
+      <c r="S177" s="23"/>
+      <c r="T177" s="23"/>
+      <c r="U177" s="23"/>
+      <c r="V177" s="23"/>
+      <c r="W177" s="23"/>
+      <c r="X177" s="23"/>
+      <c r="Y177" s="23"/>
+      <c r="Z177" s="23"/>
+      <c r="AA177" s="23"/>
+      <c r="AB177" s="23"/>
+      <c r="AC177" s="23"/>
+      <c r="AD177" s="23"/>
+      <c r="AE177" s="23"/>
+      <c r="AF177" s="23"/>
+      <c r="AG177" s="23"/>
+      <c r="AH177" s="24"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="24"/>
-      <c r="C178" s="24"/>
-      <c r="D178" s="24"/>
-      <c r="E178" s="24"/>
-      <c r="F178" s="24"/>
-      <c r="G178" s="25"/>
-      <c r="H178" s="25"/>
-      <c r="I178" s="24"/>
-      <c r="J178" s="24"/>
-      <c r="K178" s="24"/>
-      <c r="L178" s="25"/>
-      <c r="M178" s="25"/>
-      <c r="N178" s="26"/>
-      <c r="O178" s="24"/>
-      <c r="P178" s="24"/>
-      <c r="Q178" s="25"/>
-      <c r="R178" s="25"/>
-      <c r="S178" s="24"/>
-      <c r="T178" s="24"/>
-      <c r="U178" s="24"/>
-      <c r="V178" s="24"/>
-      <c r="W178" s="24"/>
-      <c r="X178" s="24"/>
-      <c r="Y178" s="24"/>
-      <c r="Z178" s="24"/>
-      <c r="AA178" s="24"/>
-      <c r="AB178" s="24"/>
-      <c r="AC178" s="24"/>
-      <c r="AD178" s="24"/>
-      <c r="AE178" s="24"/>
-      <c r="AF178" s="24"/>
-      <c r="AG178" s="24"/>
-      <c r="AH178" s="25"/>
+      <c r="B178" s="23"/>
+      <c r="C178" s="23"/>
+      <c r="D178" s="23"/>
+      <c r="E178" s="23"/>
+      <c r="F178" s="23"/>
+      <c r="G178" s="24"/>
+      <c r="H178" s="24"/>
+      <c r="I178" s="23"/>
+      <c r="J178" s="23"/>
+      <c r="K178" s="23"/>
+      <c r="L178" s="24"/>
+      <c r="M178" s="24"/>
+      <c r="N178" s="25"/>
+      <c r="O178" s="23"/>
+      <c r="P178" s="23"/>
+      <c r="Q178" s="24"/>
+      <c r="R178" s="24"/>
+      <c r="S178" s="23"/>
+      <c r="T178" s="23"/>
+      <c r="U178" s="23"/>
+      <c r="V178" s="23"/>
+      <c r="W178" s="23"/>
+      <c r="X178" s="23"/>
+      <c r="Y178" s="23"/>
+      <c r="Z178" s="23"/>
+      <c r="AA178" s="23"/>
+      <c r="AB178" s="23"/>
+      <c r="AC178" s="23"/>
+      <c r="AD178" s="23"/>
+      <c r="AE178" s="23"/>
+      <c r="AF178" s="23"/>
+      <c r="AG178" s="23"/>
+      <c r="AH178" s="24"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="24"/>
-      <c r="C179" s="24"/>
-      <c r="D179" s="24"/>
-      <c r="E179" s="24"/>
-      <c r="F179" s="24"/>
-      <c r="G179" s="25"/>
-      <c r="H179" s="25"/>
-      <c r="I179" s="24"/>
-      <c r="J179" s="24"/>
-      <c r="K179" s="24"/>
-      <c r="L179" s="25"/>
-      <c r="M179" s="25"/>
-      <c r="N179" s="26"/>
-      <c r="O179" s="24"/>
-      <c r="P179" s="24"/>
-      <c r="Q179" s="25"/>
-      <c r="R179" s="25"/>
-      <c r="S179" s="24"/>
-      <c r="T179" s="24"/>
-      <c r="U179" s="24"/>
-      <c r="V179" s="24"/>
-      <c r="W179" s="24"/>
-      <c r="X179" s="24"/>
-      <c r="Y179" s="24"/>
-      <c r="Z179" s="24"/>
-      <c r="AA179" s="24"/>
-      <c r="AB179" s="24"/>
-      <c r="AC179" s="24"/>
-      <c r="AD179" s="24"/>
-      <c r="AE179" s="24"/>
-      <c r="AF179" s="24"/>
-      <c r="AG179" s="24"/>
-      <c r="AH179" s="25"/>
+      <c r="B179" s="23"/>
+      <c r="C179" s="23"/>
+      <c r="D179" s="23"/>
+      <c r="E179" s="23"/>
+      <c r="F179" s="23"/>
+      <c r="G179" s="24"/>
+      <c r="H179" s="24"/>
+      <c r="I179" s="23"/>
+      <c r="J179" s="23"/>
+      <c r="K179" s="23"/>
+      <c r="L179" s="24"/>
+      <c r="M179" s="24"/>
+      <c r="N179" s="25"/>
+      <c r="O179" s="23"/>
+      <c r="P179" s="23"/>
+      <c r="Q179" s="24"/>
+      <c r="R179" s="24"/>
+      <c r="S179" s="23"/>
+      <c r="T179" s="23"/>
+      <c r="U179" s="23"/>
+      <c r="V179" s="23"/>
+      <c r="W179" s="23"/>
+      <c r="X179" s="23"/>
+      <c r="Y179" s="23"/>
+      <c r="Z179" s="23"/>
+      <c r="AA179" s="23"/>
+      <c r="AB179" s="23"/>
+      <c r="AC179" s="23"/>
+      <c r="AD179" s="23"/>
+      <c r="AE179" s="23"/>
+      <c r="AF179" s="23"/>
+      <c r="AG179" s="23"/>
+      <c r="AH179" s="24"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="24"/>
-      <c r="C180" s="24"/>
-      <c r="D180" s="24"/>
-      <c r="E180" s="24"/>
-      <c r="F180" s="24"/>
-      <c r="G180" s="25"/>
-      <c r="H180" s="25"/>
-      <c r="I180" s="24"/>
-      <c r="J180" s="24"/>
-      <c r="K180" s="24"/>
-      <c r="L180" s="25"/>
-      <c r="M180" s="25"/>
-      <c r="N180" s="26"/>
-      <c r="O180" s="24"/>
-      <c r="P180" s="24"/>
-      <c r="Q180" s="25"/>
-      <c r="R180" s="25"/>
-      <c r="S180" s="24"/>
-      <c r="T180" s="24"/>
-      <c r="U180" s="24"/>
-      <c r="V180" s="24"/>
-      <c r="W180" s="24"/>
-      <c r="X180" s="24"/>
-      <c r="Y180" s="24"/>
-      <c r="Z180" s="24"/>
-      <c r="AA180" s="24"/>
-      <c r="AB180" s="24"/>
-      <c r="AC180" s="24"/>
-      <c r="AD180" s="24"/>
-      <c r="AE180" s="24"/>
-      <c r="AF180" s="24"/>
-      <c r="AG180" s="24"/>
-      <c r="AH180" s="25"/>
+      <c r="B180" s="23"/>
+      <c r="C180" s="23"/>
+      <c r="D180" s="23"/>
+      <c r="E180" s="23"/>
+      <c r="F180" s="23"/>
+      <c r="G180" s="24"/>
+      <c r="H180" s="24"/>
+      <c r="I180" s="23"/>
+      <c r="J180" s="23"/>
+      <c r="K180" s="23"/>
+      <c r="L180" s="24"/>
+      <c r="M180" s="24"/>
+      <c r="N180" s="25"/>
+      <c r="O180" s="23"/>
+      <c r="P180" s="23"/>
+      <c r="Q180" s="24"/>
+      <c r="R180" s="24"/>
+      <c r="S180" s="23"/>
+      <c r="T180" s="23"/>
+      <c r="U180" s="23"/>
+      <c r="V180" s="23"/>
+      <c r="W180" s="23"/>
+      <c r="X180" s="23"/>
+      <c r="Y180" s="23"/>
+      <c r="Z180" s="23"/>
+      <c r="AA180" s="23"/>
+      <c r="AB180" s="23"/>
+      <c r="AC180" s="23"/>
+      <c r="AD180" s="23"/>
+      <c r="AE180" s="23"/>
+      <c r="AF180" s="23"/>
+      <c r="AG180" s="23"/>
+      <c r="AH180" s="24"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="24"/>
-      <c r="C181" s="24"/>
-      <c r="D181" s="24"/>
-      <c r="E181" s="24"/>
-      <c r="F181" s="24"/>
-      <c r="G181" s="25"/>
-      <c r="H181" s="25"/>
-      <c r="I181" s="24"/>
-      <c r="J181" s="24"/>
-      <c r="K181" s="24"/>
-      <c r="L181" s="25"/>
-      <c r="M181" s="25"/>
-      <c r="N181" s="26"/>
-      <c r="O181" s="24"/>
-      <c r="P181" s="24"/>
-      <c r="Q181" s="25"/>
-      <c r="R181" s="25"/>
-      <c r="S181" s="24"/>
-      <c r="T181" s="24"/>
-      <c r="U181" s="24"/>
-      <c r="V181" s="24"/>
-      <c r="W181" s="24"/>
-      <c r="X181" s="24"/>
-      <c r="Y181" s="24"/>
-      <c r="Z181" s="24"/>
-      <c r="AA181" s="24"/>
-      <c r="AB181" s="24"/>
-      <c r="AC181" s="24"/>
-      <c r="AD181" s="24"/>
-      <c r="AE181" s="24"/>
-      <c r="AF181" s="24"/>
-      <c r="AG181" s="24"/>
-      <c r="AH181" s="25"/>
+      <c r="B181" s="23"/>
+      <c r="C181" s="23"/>
+      <c r="D181" s="23"/>
+      <c r="E181" s="23"/>
+      <c r="F181" s="23"/>
+      <c r="G181" s="24"/>
+      <c r="H181" s="24"/>
+      <c r="I181" s="23"/>
+      <c r="J181" s="23"/>
+      <c r="K181" s="23"/>
+      <c r="L181" s="24"/>
+      <c r="M181" s="24"/>
+      <c r="N181" s="25"/>
+      <c r="O181" s="23"/>
+      <c r="P181" s="23"/>
+      <c r="Q181" s="24"/>
+      <c r="R181" s="24"/>
+      <c r="S181" s="23"/>
+      <c r="T181" s="23"/>
+      <c r="U181" s="23"/>
+      <c r="V181" s="23"/>
+      <c r="W181" s="23"/>
+      <c r="X181" s="23"/>
+      <c r="Y181" s="23"/>
+      <c r="Z181" s="23"/>
+      <c r="AA181" s="23"/>
+      <c r="AB181" s="23"/>
+      <c r="AC181" s="23"/>
+      <c r="AD181" s="23"/>
+      <c r="AE181" s="23"/>
+      <c r="AF181" s="23"/>
+      <c r="AG181" s="23"/>
+      <c r="AH181" s="24"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="24"/>
-      <c r="C182" s="24"/>
-      <c r="D182" s="24"/>
-      <c r="E182" s="24"/>
-      <c r="F182" s="24"/>
-      <c r="G182" s="25"/>
-      <c r="H182" s="25"/>
-      <c r="I182" s="24"/>
-      <c r="J182" s="24"/>
-      <c r="K182" s="24"/>
-      <c r="L182" s="25"/>
-      <c r="M182" s="25"/>
-      <c r="N182" s="26"/>
-      <c r="O182" s="24"/>
-      <c r="P182" s="24"/>
-      <c r="Q182" s="25"/>
-      <c r="R182" s="25"/>
-      <c r="S182" s="24"/>
-      <c r="T182" s="24"/>
-      <c r="U182" s="24"/>
-      <c r="V182" s="24"/>
-      <c r="W182" s="24"/>
-      <c r="X182" s="24"/>
-      <c r="Y182" s="24"/>
-      <c r="Z182" s="24"/>
-      <c r="AA182" s="24"/>
-      <c r="AB182" s="24"/>
-      <c r="AC182" s="24"/>
-      <c r="AD182" s="24"/>
-      <c r="AE182" s="24"/>
-      <c r="AF182" s="24"/>
-      <c r="AG182" s="24"/>
-      <c r="AH182" s="25"/>
+      <c r="B182" s="23"/>
+      <c r="C182" s="23"/>
+      <c r="D182" s="23"/>
+      <c r="E182" s="23"/>
+      <c r="F182" s="23"/>
+      <c r="G182" s="24"/>
+      <c r="H182" s="24"/>
+      <c r="I182" s="23"/>
+      <c r="J182" s="23"/>
+      <c r="K182" s="23"/>
+      <c r="L182" s="24"/>
+      <c r="M182" s="24"/>
+      <c r="N182" s="25"/>
+      <c r="O182" s="23"/>
+      <c r="P182" s="23"/>
+      <c r="Q182" s="24"/>
+      <c r="R182" s="24"/>
+      <c r="S182" s="23"/>
+      <c r="T182" s="23"/>
+      <c r="U182" s="23"/>
+      <c r="V182" s="23"/>
+      <c r="W182" s="23"/>
+      <c r="X182" s="23"/>
+      <c r="Y182" s="23"/>
+      <c r="Z182" s="23"/>
+      <c r="AA182" s="23"/>
+      <c r="AB182" s="23"/>
+      <c r="AC182" s="23"/>
+      <c r="AD182" s="23"/>
+      <c r="AE182" s="23"/>
+      <c r="AF182" s="23"/>
+      <c r="AG182" s="23"/>
+      <c r="AH182" s="24"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="24"/>
-      <c r="C183" s="24"/>
-      <c r="D183" s="24"/>
-      <c r="E183" s="24"/>
-      <c r="F183" s="24"/>
-      <c r="G183" s="25"/>
-      <c r="H183" s="25"/>
-      <c r="I183" s="24"/>
-      <c r="J183" s="24"/>
-      <c r="K183" s="24"/>
-      <c r="L183" s="25"/>
-      <c r="M183" s="25"/>
-      <c r="N183" s="26"/>
-      <c r="O183" s="24"/>
-      <c r="P183" s="24"/>
-      <c r="Q183" s="25"/>
-      <c r="R183" s="25"/>
-      <c r="S183" s="24"/>
-      <c r="T183" s="24"/>
-      <c r="U183" s="24"/>
-      <c r="V183" s="24"/>
-      <c r="W183" s="24"/>
-      <c r="X183" s="24"/>
-      <c r="Y183" s="24"/>
-      <c r="Z183" s="24"/>
-      <c r="AA183" s="24"/>
-      <c r="AB183" s="24"/>
-      <c r="AC183" s="24"/>
-      <c r="AD183" s="24"/>
-      <c r="AE183" s="24"/>
-      <c r="AF183" s="24"/>
-      <c r="AG183" s="24"/>
-      <c r="AH183" s="25"/>
+      <c r="B183" s="23"/>
+      <c r="C183" s="23"/>
+      <c r="D183" s="23"/>
+      <c r="E183" s="23"/>
+      <c r="F183" s="23"/>
+      <c r="G183" s="24"/>
+      <c r="H183" s="24"/>
+      <c r="I183" s="23"/>
+      <c r="J183" s="23"/>
+      <c r="K183" s="23"/>
+      <c r="L183" s="24"/>
+      <c r="M183" s="24"/>
+      <c r="N183" s="25"/>
+      <c r="O183" s="23"/>
+      <c r="P183" s="23"/>
+      <c r="Q183" s="24"/>
+      <c r="R183" s="24"/>
+      <c r="S183" s="23"/>
+      <c r="T183" s="23"/>
+      <c r="U183" s="23"/>
+      <c r="V183" s="23"/>
+      <c r="W183" s="23"/>
+      <c r="X183" s="23"/>
+      <c r="Y183" s="23"/>
+      <c r="Z183" s="23"/>
+      <c r="AA183" s="23"/>
+      <c r="AB183" s="23"/>
+      <c r="AC183" s="23"/>
+      <c r="AD183" s="23"/>
+      <c r="AE183" s="23"/>
+      <c r="AF183" s="23"/>
+      <c r="AG183" s="23"/>
+      <c r="AH183" s="24"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="25"/>
-      <c r="H184" s="25"/>
-      <c r="I184" s="24"/>
-      <c r="J184" s="24"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="25"/>
-      <c r="M184" s="25"/>
-      <c r="N184" s="26"/>
-      <c r="O184" s="24"/>
-      <c r="P184" s="24"/>
-      <c r="Q184" s="25"/>
-      <c r="R184" s="25"/>
-      <c r="S184" s="24"/>
-      <c r="T184" s="24"/>
-      <c r="U184" s="24"/>
-      <c r="V184" s="24"/>
-      <c r="W184" s="24"/>
-      <c r="X184" s="24"/>
-      <c r="Y184" s="24"/>
-      <c r="Z184" s="24"/>
-      <c r="AA184" s="24"/>
-      <c r="AB184" s="24"/>
-      <c r="AC184" s="24"/>
-      <c r="AD184" s="24"/>
-      <c r="AE184" s="24"/>
-      <c r="AF184" s="24"/>
-      <c r="AG184" s="24"/>
-      <c r="AH184" s="25"/>
+      <c r="B184" s="23"/>
+      <c r="C184" s="23"/>
+      <c r="D184" s="23"/>
+      <c r="E184" s="23"/>
+      <c r="F184" s="23"/>
+      <c r="G184" s="24"/>
+      <c r="H184" s="24"/>
+      <c r="I184" s="23"/>
+      <c r="J184" s="23"/>
+      <c r="K184" s="23"/>
+      <c r="L184" s="24"/>
+      <c r="M184" s="24"/>
+      <c r="N184" s="25"/>
+      <c r="O184" s="23"/>
+      <c r="P184" s="23"/>
+      <c r="Q184" s="24"/>
+      <c r="R184" s="24"/>
+      <c r="S184" s="23"/>
+      <c r="T184" s="23"/>
+      <c r="U184" s="23"/>
+      <c r="V184" s="23"/>
+      <c r="W184" s="23"/>
+      <c r="X184" s="23"/>
+      <c r="Y184" s="23"/>
+      <c r="Z184" s="23"/>
+      <c r="AA184" s="23"/>
+      <c r="AB184" s="23"/>
+      <c r="AC184" s="23"/>
+      <c r="AD184" s="23"/>
+      <c r="AE184" s="23"/>
+      <c r="AF184" s="23"/>
+      <c r="AG184" s="23"/>
+      <c r="AH184" s="24"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="24"/>
-      <c r="C185" s="24"/>
-      <c r="D185" s="24"/>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="24"/>
-      <c r="K185" s="24"/>
-      <c r="L185" s="25"/>
-      <c r="M185" s="25"/>
-      <c r="N185" s="26"/>
-      <c r="O185" s="24"/>
-      <c r="P185" s="24"/>
-      <c r="Q185" s="25"/>
-      <c r="R185" s="25"/>
-      <c r="S185" s="24"/>
-      <c r="T185" s="24"/>
-      <c r="U185" s="24"/>
-      <c r="V185" s="24"/>
-      <c r="W185" s="24"/>
-      <c r="X185" s="24"/>
-      <c r="Y185" s="24"/>
-      <c r="Z185" s="24"/>
-      <c r="AA185" s="24"/>
-      <c r="AB185" s="24"/>
-      <c r="AC185" s="24"/>
-      <c r="AD185" s="24"/>
-      <c r="AE185" s="24"/>
-      <c r="AF185" s="24"/>
-      <c r="AG185" s="24"/>
-      <c r="AH185" s="25"/>
+      <c r="B185" s="23"/>
+      <c r="C185" s="23"/>
+      <c r="D185" s="23"/>
+      <c r="E185" s="23"/>
+      <c r="F185" s="23"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="23"/>
+      <c r="J185" s="23"/>
+      <c r="K185" s="23"/>
+      <c r="L185" s="24"/>
+      <c r="M185" s="24"/>
+      <c r="N185" s="25"/>
+      <c r="O185" s="23"/>
+      <c r="P185" s="23"/>
+      <c r="Q185" s="24"/>
+      <c r="R185" s="24"/>
+      <c r="S185" s="23"/>
+      <c r="T185" s="23"/>
+      <c r="U185" s="23"/>
+      <c r="V185" s="23"/>
+      <c r="W185" s="23"/>
+      <c r="X185" s="23"/>
+      <c r="Y185" s="23"/>
+      <c r="Z185" s="23"/>
+      <c r="AA185" s="23"/>
+      <c r="AB185" s="23"/>
+      <c r="AC185" s="23"/>
+      <c r="AD185" s="23"/>
+      <c r="AE185" s="23"/>
+      <c r="AF185" s="23"/>
+      <c r="AG185" s="23"/>
+      <c r="AH185" s="24"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="24"/>
-      <c r="C186" s="24"/>
-      <c r="D186" s="24"/>
-      <c r="E186" s="24"/>
-      <c r="F186" s="24"/>
-      <c r="G186" s="25"/>
-      <c r="H186" s="25"/>
-      <c r="I186" s="24"/>
-      <c r="J186" s="24"/>
-      <c r="K186" s="24"/>
-      <c r="L186" s="25"/>
-      <c r="M186" s="25"/>
-      <c r="N186" s="26"/>
-      <c r="O186" s="24"/>
-      <c r="P186" s="24"/>
-      <c r="Q186" s="25"/>
-      <c r="R186" s="25"/>
-      <c r="S186" s="24"/>
-      <c r="T186" s="24"/>
-      <c r="U186" s="24"/>
-      <c r="V186" s="24"/>
-      <c r="W186" s="24"/>
-      <c r="X186" s="24"/>
-      <c r="Y186" s="24"/>
-      <c r="Z186" s="24"/>
-      <c r="AA186" s="24"/>
-      <c r="AB186" s="24"/>
-      <c r="AC186" s="24"/>
-      <c r="AD186" s="24"/>
-      <c r="AE186" s="24"/>
-      <c r="AF186" s="24"/>
-      <c r="AG186" s="24"/>
-      <c r="AH186" s="25"/>
+      <c r="B186" s="23"/>
+      <c r="C186" s="23"/>
+      <c r="D186" s="23"/>
+      <c r="E186" s="23"/>
+      <c r="F186" s="23"/>
+      <c r="G186" s="24"/>
+      <c r="H186" s="24"/>
+      <c r="I186" s="23"/>
+      <c r="J186" s="23"/>
+      <c r="K186" s="23"/>
+      <c r="L186" s="24"/>
+      <c r="M186" s="24"/>
+      <c r="N186" s="25"/>
+      <c r="O186" s="23"/>
+      <c r="P186" s="23"/>
+      <c r="Q186" s="24"/>
+      <c r="R186" s="24"/>
+      <c r="S186" s="23"/>
+      <c r="T186" s="23"/>
+      <c r="U186" s="23"/>
+      <c r="V186" s="23"/>
+      <c r="W186" s="23"/>
+      <c r="X186" s="23"/>
+      <c r="Y186" s="23"/>
+      <c r="Z186" s="23"/>
+      <c r="AA186" s="23"/>
+      <c r="AB186" s="23"/>
+      <c r="AC186" s="23"/>
+      <c r="AD186" s="23"/>
+      <c r="AE186" s="23"/>
+      <c r="AF186" s="23"/>
+      <c r="AG186" s="23"/>
+      <c r="AH186" s="24"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="24"/>
-      <c r="C187" s="24"/>
-      <c r="D187" s="24"/>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="24"/>
-      <c r="J187" s="24"/>
-      <c r="K187" s="24"/>
-      <c r="L187" s="25"/>
-      <c r="M187" s="25"/>
-      <c r="N187" s="26"/>
-      <c r="O187" s="24"/>
-      <c r="P187" s="24"/>
-      <c r="Q187" s="25"/>
-      <c r="R187" s="25"/>
-      <c r="S187" s="24"/>
-      <c r="T187" s="24"/>
-      <c r="U187" s="24"/>
-      <c r="V187" s="24"/>
-      <c r="W187" s="24"/>
-      <c r="X187" s="24"/>
-      <c r="Y187" s="24"/>
-      <c r="Z187" s="24"/>
-      <c r="AA187" s="24"/>
-      <c r="AB187" s="24"/>
-      <c r="AC187" s="24"/>
-      <c r="AD187" s="24"/>
-      <c r="AE187" s="24"/>
-      <c r="AF187" s="24"/>
-      <c r="AG187" s="24"/>
-      <c r="AH187" s="25"/>
+      <c r="B187" s="23"/>
+      <c r="C187" s="23"/>
+      <c r="D187" s="23"/>
+      <c r="E187" s="23"/>
+      <c r="F187" s="23"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="23"/>
+      <c r="J187" s="23"/>
+      <c r="K187" s="23"/>
+      <c r="L187" s="24"/>
+      <c r="M187" s="24"/>
+      <c r="N187" s="25"/>
+      <c r="O187" s="23"/>
+      <c r="P187" s="23"/>
+      <c r="Q187" s="24"/>
+      <c r="R187" s="24"/>
+      <c r="S187" s="23"/>
+      <c r="T187" s="23"/>
+      <c r="U187" s="23"/>
+      <c r="V187" s="23"/>
+      <c r="W187" s="23"/>
+      <c r="X187" s="23"/>
+      <c r="Y187" s="23"/>
+      <c r="Z187" s="23"/>
+      <c r="AA187" s="23"/>
+      <c r="AB187" s="23"/>
+      <c r="AC187" s="23"/>
+      <c r="AD187" s="23"/>
+      <c r="AE187" s="23"/>
+      <c r="AF187" s="23"/>
+      <c r="AG187" s="23"/>
+      <c r="AH187" s="24"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="24"/>
-      <c r="C188" s="24"/>
-      <c r="D188" s="24"/>
-      <c r="E188" s="24"/>
-      <c r="F188" s="24"/>
-      <c r="G188" s="25"/>
-      <c r="H188" s="25"/>
-      <c r="I188" s="24"/>
-      <c r="J188" s="24"/>
-      <c r="K188" s="24"/>
-      <c r="L188" s="25"/>
-      <c r="M188" s="25"/>
-      <c r="N188" s="26"/>
-      <c r="O188" s="24"/>
-      <c r="P188" s="24"/>
-      <c r="Q188" s="25"/>
-      <c r="R188" s="25"/>
-      <c r="S188" s="24"/>
-      <c r="T188" s="24"/>
-      <c r="U188" s="24"/>
-      <c r="V188" s="24"/>
-      <c r="W188" s="24"/>
-      <c r="X188" s="24"/>
-      <c r="Y188" s="24"/>
-      <c r="Z188" s="24"/>
-      <c r="AA188" s="24"/>
-      <c r="AB188" s="24"/>
-      <c r="AC188" s="24"/>
-      <c r="AD188" s="24"/>
-      <c r="AE188" s="24"/>
-      <c r="AF188" s="24"/>
-      <c r="AG188" s="24"/>
-      <c r="AH188" s="25"/>
+      <c r="B188" s="23"/>
+      <c r="C188" s="23"/>
+      <c r="D188" s="23"/>
+      <c r="E188" s="23"/>
+      <c r="F188" s="23"/>
+      <c r="G188" s="24"/>
+      <c r="H188" s="24"/>
+      <c r="I188" s="23"/>
+      <c r="J188" s="23"/>
+      <c r="K188" s="23"/>
+      <c r="L188" s="24"/>
+      <c r="M188" s="24"/>
+      <c r="N188" s="25"/>
+      <c r="O188" s="23"/>
+      <c r="P188" s="23"/>
+      <c r="Q188" s="24"/>
+      <c r="R188" s="24"/>
+      <c r="S188" s="23"/>
+      <c r="T188" s="23"/>
+      <c r="U188" s="23"/>
+      <c r="V188" s="23"/>
+      <c r="W188" s="23"/>
+      <c r="X188" s="23"/>
+      <c r="Y188" s="23"/>
+      <c r="Z188" s="23"/>
+      <c r="AA188" s="23"/>
+      <c r="AB188" s="23"/>
+      <c r="AC188" s="23"/>
+      <c r="AD188" s="23"/>
+      <c r="AE188" s="23"/>
+      <c r="AF188" s="23"/>
+      <c r="AG188" s="23"/>
+      <c r="AH188" s="24"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="24"/>
-      <c r="C189" s="24"/>
-      <c r="D189" s="24"/>
-      <c r="E189" s="24"/>
-      <c r="F189" s="24"/>
-      <c r="G189" s="25"/>
-      <c r="H189" s="25"/>
-      <c r="I189" s="24"/>
-      <c r="J189" s="24"/>
-      <c r="K189" s="24"/>
-      <c r="L189" s="25"/>
-      <c r="M189" s="25"/>
-      <c r="N189" s="26"/>
-      <c r="O189" s="24"/>
-      <c r="P189" s="24"/>
-      <c r="Q189" s="25"/>
-      <c r="R189" s="25"/>
-      <c r="S189" s="24"/>
-      <c r="T189" s="24"/>
-      <c r="U189" s="24"/>
-      <c r="V189" s="24"/>
-      <c r="W189" s="24"/>
-      <c r="X189" s="24"/>
-      <c r="Y189" s="24"/>
-      <c r="Z189" s="24"/>
-      <c r="AA189" s="24"/>
-      <c r="AB189" s="24"/>
-      <c r="AC189" s="24"/>
-      <c r="AD189" s="24"/>
-      <c r="AE189" s="24"/>
-      <c r="AF189" s="24"/>
-      <c r="AG189" s="24"/>
-      <c r="AH189" s="25"/>
+      <c r="B189" s="23"/>
+      <c r="C189" s="23"/>
+      <c r="D189" s="23"/>
+      <c r="E189" s="23"/>
+      <c r="F189" s="23"/>
+      <c r="G189" s="24"/>
+      <c r="H189" s="24"/>
+      <c r="I189" s="23"/>
+      <c r="J189" s="23"/>
+      <c r="K189" s="23"/>
+      <c r="L189" s="24"/>
+      <c r="M189" s="24"/>
+      <c r="N189" s="25"/>
+      <c r="O189" s="23"/>
+      <c r="P189" s="23"/>
+      <c r="Q189" s="24"/>
+      <c r="R189" s="24"/>
+      <c r="S189" s="23"/>
+      <c r="T189" s="23"/>
+      <c r="U189" s="23"/>
+      <c r="V189" s="23"/>
+      <c r="W189" s="23"/>
+      <c r="X189" s="23"/>
+      <c r="Y189" s="23"/>
+      <c r="Z189" s="23"/>
+      <c r="AA189" s="23"/>
+      <c r="AB189" s="23"/>
+      <c r="AC189" s="23"/>
+      <c r="AD189" s="23"/>
+      <c r="AE189" s="23"/>
+      <c r="AF189" s="23"/>
+      <c r="AG189" s="23"/>
+      <c r="AH189" s="24"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="24"/>
-      <c r="C190" s="24"/>
-      <c r="D190" s="24"/>
-      <c r="E190" s="24"/>
-      <c r="F190" s="24"/>
-      <c r="G190" s="25"/>
-      <c r="H190" s="25"/>
-      <c r="I190" s="24"/>
-      <c r="J190" s="24"/>
-      <c r="K190" s="24"/>
-      <c r="L190" s="25"/>
-      <c r="M190" s="25"/>
-      <c r="N190" s="26"/>
-      <c r="O190" s="24"/>
-      <c r="P190" s="24"/>
-      <c r="Q190" s="25"/>
-      <c r="R190" s="25"/>
-      <c r="S190" s="24"/>
-      <c r="T190" s="24"/>
-      <c r="U190" s="24"/>
-      <c r="V190" s="24"/>
-      <c r="W190" s="24"/>
-      <c r="X190" s="24"/>
-      <c r="Y190" s="24"/>
-      <c r="Z190" s="24"/>
-      <c r="AA190" s="24"/>
-      <c r="AB190" s="24"/>
-      <c r="AC190" s="24"/>
-      <c r="AD190" s="24"/>
-      <c r="AE190" s="24"/>
-      <c r="AF190" s="24"/>
-      <c r="AG190" s="24"/>
-      <c r="AH190" s="25"/>
+      <c r="B190" s="23"/>
+      <c r="C190" s="23"/>
+      <c r="D190" s="23"/>
+      <c r="E190" s="23"/>
+      <c r="F190" s="23"/>
+      <c r="G190" s="24"/>
+      <c r="H190" s="24"/>
+      <c r="I190" s="23"/>
+      <c r="J190" s="23"/>
+      <c r="K190" s="23"/>
+      <c r="L190" s="24"/>
+      <c r="M190" s="24"/>
+      <c r="N190" s="25"/>
+      <c r="O190" s="23"/>
+      <c r="P190" s="23"/>
+      <c r="Q190" s="24"/>
+      <c r="R190" s="24"/>
+      <c r="S190" s="23"/>
+      <c r="T190" s="23"/>
+      <c r="U190" s="23"/>
+      <c r="V190" s="23"/>
+      <c r="W190" s="23"/>
+      <c r="X190" s="23"/>
+      <c r="Y190" s="23"/>
+      <c r="Z190" s="23"/>
+      <c r="AA190" s="23"/>
+      <c r="AB190" s="23"/>
+      <c r="AC190" s="23"/>
+      <c r="AD190" s="23"/>
+      <c r="AE190" s="23"/>
+      <c r="AF190" s="23"/>
+      <c r="AG190" s="23"/>
+      <c r="AH190" s="24"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="24"/>
-      <c r="C191" s="24"/>
-      <c r="D191" s="24"/>
-      <c r="E191" s="24"/>
-      <c r="F191" s="24"/>
-      <c r="G191" s="25"/>
-      <c r="H191" s="25"/>
-      <c r="I191" s="24"/>
-      <c r="J191" s="24"/>
-      <c r="K191" s="24"/>
-      <c r="L191" s="25"/>
-      <c r="M191" s="25"/>
-      <c r="N191" s="26"/>
-      <c r="O191" s="24"/>
-      <c r="P191" s="24"/>
-      <c r="Q191" s="25"/>
-      <c r="R191" s="25"/>
-      <c r="S191" s="24"/>
-      <c r="T191" s="24"/>
-      <c r="U191" s="24"/>
-      <c r="V191" s="24"/>
-      <c r="W191" s="24"/>
-      <c r="X191" s="24"/>
-      <c r="Y191" s="24"/>
-      <c r="Z191" s="24"/>
-      <c r="AA191" s="24"/>
-      <c r="AB191" s="24"/>
-      <c r="AC191" s="24"/>
-      <c r="AD191" s="24"/>
-      <c r="AE191" s="24"/>
-      <c r="AF191" s="24"/>
-      <c r="AG191" s="24"/>
-      <c r="AH191" s="25"/>
+      <c r="B191" s="23"/>
+      <c r="C191" s="23"/>
+      <c r="D191" s="23"/>
+      <c r="E191" s="23"/>
+      <c r="F191" s="23"/>
+      <c r="G191" s="24"/>
+      <c r="H191" s="24"/>
+      <c r="I191" s="23"/>
+      <c r="J191" s="23"/>
+      <c r="K191" s="23"/>
+      <c r="L191" s="24"/>
+      <c r="M191" s="24"/>
+      <c r="N191" s="25"/>
+      <c r="O191" s="23"/>
+      <c r="P191" s="23"/>
+      <c r="Q191" s="24"/>
+      <c r="R191" s="24"/>
+      <c r="S191" s="23"/>
+      <c r="T191" s="23"/>
+      <c r="U191" s="23"/>
+      <c r="V191" s="23"/>
+      <c r="W191" s="23"/>
+      <c r="X191" s="23"/>
+      <c r="Y191" s="23"/>
+      <c r="Z191" s="23"/>
+      <c r="AA191" s="23"/>
+      <c r="AB191" s="23"/>
+      <c r="AC191" s="23"/>
+      <c r="AD191" s="23"/>
+      <c r="AE191" s="23"/>
+      <c r="AF191" s="23"/>
+      <c r="AG191" s="23"/>
+      <c r="AH191" s="24"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="24"/>
-      <c r="C192" s="24"/>
-      <c r="D192" s="24"/>
-      <c r="E192" s="24"/>
-      <c r="F192" s="24"/>
-      <c r="G192" s="25"/>
-      <c r="H192" s="25"/>
-      <c r="I192" s="24"/>
-      <c r="J192" s="24"/>
-      <c r="K192" s="24"/>
-      <c r="L192" s="25"/>
-      <c r="M192" s="25"/>
-      <c r="N192" s="26"/>
-      <c r="O192" s="24"/>
-      <c r="P192" s="24"/>
-      <c r="Q192" s="25"/>
-      <c r="R192" s="25"/>
-      <c r="S192" s="24"/>
-      <c r="T192" s="24"/>
-      <c r="U192" s="24"/>
-      <c r="V192" s="24"/>
-      <c r="W192" s="24"/>
-      <c r="X192" s="24"/>
-      <c r="Y192" s="24"/>
-      <c r="Z192" s="24"/>
-      <c r="AA192" s="24"/>
-      <c r="AB192" s="24"/>
-      <c r="AC192" s="24"/>
-      <c r="AD192" s="24"/>
-      <c r="AE192" s="24"/>
-      <c r="AF192" s="24"/>
-      <c r="AG192" s="24"/>
-      <c r="AH192" s="25"/>
+      <c r="B192" s="23"/>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23"/>
+      <c r="E192" s="23"/>
+      <c r="F192" s="23"/>
+      <c r="G192" s="24"/>
+      <c r="H192" s="24"/>
+      <c r="I192" s="23"/>
+      <c r="J192" s="23"/>
+      <c r="K192" s="23"/>
+      <c r="L192" s="24"/>
+      <c r="M192" s="24"/>
+      <c r="N192" s="25"/>
+      <c r="O192" s="23"/>
+      <c r="P192" s="23"/>
+      <c r="Q192" s="24"/>
+      <c r="R192" s="24"/>
+      <c r="S192" s="23"/>
+      <c r="T192" s="23"/>
+      <c r="U192" s="23"/>
+      <c r="V192" s="23"/>
+      <c r="W192" s="23"/>
+      <c r="X192" s="23"/>
+      <c r="Y192" s="23"/>
+      <c r="Z192" s="23"/>
+      <c r="AA192" s="23"/>
+      <c r="AB192" s="23"/>
+      <c r="AC192" s="23"/>
+      <c r="AD192" s="23"/>
+      <c r="AE192" s="23"/>
+      <c r="AF192" s="23"/>
+      <c r="AG192" s="23"/>
+      <c r="AH192" s="24"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="24"/>
-      <c r="C193" s="24"/>
-      <c r="D193" s="24"/>
-      <c r="E193" s="24"/>
-      <c r="F193" s="24"/>
-      <c r="G193" s="25"/>
-      <c r="H193" s="25"/>
-      <c r="I193" s="24"/>
-      <c r="J193" s="24"/>
-      <c r="K193" s="24"/>
-      <c r="L193" s="25"/>
-      <c r="M193" s="25"/>
-      <c r="N193" s="26"/>
-      <c r="O193" s="24"/>
-      <c r="P193" s="24"/>
-      <c r="Q193" s="25"/>
-      <c r="R193" s="25"/>
-      <c r="S193" s="24"/>
-      <c r="T193" s="24"/>
-      <c r="U193" s="24"/>
-      <c r="V193" s="24"/>
-      <c r="W193" s="24"/>
-      <c r="X193" s="24"/>
-      <c r="Y193" s="24"/>
-      <c r="Z193" s="24"/>
-      <c r="AA193" s="24"/>
-      <c r="AB193" s="24"/>
-      <c r="AC193" s="24"/>
-      <c r="AD193" s="24"/>
-      <c r="AE193" s="24"/>
-      <c r="AF193" s="24"/>
-      <c r="AG193" s="24"/>
-      <c r="AH193" s="25"/>
+      <c r="B193" s="23"/>
+      <c r="C193" s="23"/>
+      <c r="D193" s="23"/>
+      <c r="E193" s="23"/>
+      <c r="F193" s="23"/>
+      <c r="G193" s="24"/>
+      <c r="H193" s="24"/>
+      <c r="I193" s="23"/>
+      <c r="J193" s="23"/>
+      <c r="K193" s="23"/>
+      <c r="L193" s="24"/>
+      <c r="M193" s="24"/>
+      <c r="N193" s="25"/>
+      <c r="O193" s="23"/>
+      <c r="P193" s="23"/>
+      <c r="Q193" s="24"/>
+      <c r="R193" s="24"/>
+      <c r="S193" s="23"/>
+      <c r="T193" s="23"/>
+      <c r="U193" s="23"/>
+      <c r="V193" s="23"/>
+      <c r="W193" s="23"/>
+      <c r="X193" s="23"/>
+      <c r="Y193" s="23"/>
+      <c r="Z193" s="23"/>
+      <c r="AA193" s="23"/>
+      <c r="AB193" s="23"/>
+      <c r="AC193" s="23"/>
+      <c r="AD193" s="23"/>
+      <c r="AE193" s="23"/>
+      <c r="AF193" s="23"/>
+      <c r="AG193" s="23"/>
+      <c r="AH193" s="24"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B194" s="24"/>
-      <c r="C194" s="24"/>
-      <c r="D194" s="24"/>
-      <c r="E194" s="24"/>
-      <c r="F194" s="24"/>
-      <c r="G194" s="25"/>
-      <c r="H194" s="25"/>
-      <c r="I194" s="24"/>
-      <c r="J194" s="24"/>
-      <c r="K194" s="24"/>
-      <c r="L194" s="25"/>
-      <c r="M194" s="25"/>
-      <c r="N194" s="26"/>
-      <c r="O194" s="24"/>
-      <c r="P194" s="24"/>
-      <c r="Q194" s="25"/>
-      <c r="R194" s="25"/>
-      <c r="S194" s="24"/>
-      <c r="T194" s="24"/>
-      <c r="U194" s="24"/>
-      <c r="V194" s="24"/>
-      <c r="W194" s="24"/>
-      <c r="X194" s="24"/>
-      <c r="Y194" s="24"/>
-      <c r="Z194" s="24"/>
-      <c r="AA194" s="24"/>
-      <c r="AB194" s="24"/>
-      <c r="AC194" s="24"/>
-      <c r="AD194" s="24"/>
-      <c r="AE194" s="24"/>
-      <c r="AF194" s="24"/>
-      <c r="AG194" s="24"/>
-      <c r="AH194" s="25"/>
+      <c r="B194" s="23"/>
+      <c r="C194" s="23"/>
+      <c r="D194" s="23"/>
+      <c r="E194" s="23"/>
+      <c r="F194" s="23"/>
+      <c r="G194" s="24"/>
+      <c r="H194" s="24"/>
+      <c r="I194" s="23"/>
+      <c r="J194" s="23"/>
+      <c r="K194" s="23"/>
+      <c r="L194" s="24"/>
+      <c r="M194" s="24"/>
+      <c r="N194" s="25"/>
+      <c r="O194" s="23"/>
+      <c r="P194" s="23"/>
+      <c r="Q194" s="24"/>
+      <c r="R194" s="24"/>
+      <c r="S194" s="23"/>
+      <c r="T194" s="23"/>
+      <c r="U194" s="23"/>
+      <c r="V194" s="23"/>
+      <c r="W194" s="23"/>
+      <c r="X194" s="23"/>
+      <c r="Y194" s="23"/>
+      <c r="Z194" s="23"/>
+      <c r="AA194" s="23"/>
+      <c r="AB194" s="23"/>
+      <c r="AC194" s="23"/>
+      <c r="AD194" s="23"/>
+      <c r="AE194" s="23"/>
+      <c r="AF194" s="23"/>
+      <c r="AG194" s="23"/>
+      <c r="AH194" s="24"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="24"/>
-      <c r="C195" s="24"/>
-      <c r="D195" s="24"/>
-      <c r="E195" s="24"/>
-      <c r="F195" s="24"/>
-      <c r="G195" s="25"/>
-      <c r="H195" s="25"/>
-      <c r="I195" s="24"/>
-      <c r="J195" s="24"/>
-      <c r="K195" s="24"/>
-      <c r="L195" s="25"/>
-      <c r="M195" s="25"/>
-      <c r="N195" s="26"/>
-      <c r="O195" s="24"/>
-      <c r="P195" s="24"/>
-      <c r="Q195" s="25"/>
-      <c r="R195" s="25"/>
-      <c r="S195" s="24"/>
-      <c r="T195" s="24"/>
-      <c r="U195" s="24"/>
-      <c r="V195" s="24"/>
-      <c r="W195" s="24"/>
-      <c r="X195" s="24"/>
-      <c r="Y195" s="24"/>
-      <c r="Z195" s="24"/>
-      <c r="AA195" s="24"/>
-      <c r="AB195" s="24"/>
-      <c r="AC195" s="24"/>
-      <c r="AD195" s="24"/>
-      <c r="AE195" s="24"/>
-      <c r="AF195" s="24"/>
-      <c r="AG195" s="24"/>
-      <c r="AH195" s="25"/>
+      <c r="B195" s="23"/>
+      <c r="C195" s="23"/>
+      <c r="D195" s="23"/>
+      <c r="E195" s="23"/>
+      <c r="F195" s="23"/>
+      <c r="G195" s="24"/>
+      <c r="H195" s="24"/>
+      <c r="I195" s="23"/>
+      <c r="J195" s="23"/>
+      <c r="K195" s="23"/>
+      <c r="L195" s="24"/>
+      <c r="M195" s="24"/>
+      <c r="N195" s="25"/>
+      <c r="O195" s="23"/>
+      <c r="P195" s="23"/>
+      <c r="Q195" s="24"/>
+      <c r="R195" s="24"/>
+      <c r="S195" s="23"/>
+      <c r="T195" s="23"/>
+      <c r="U195" s="23"/>
+      <c r="V195" s="23"/>
+      <c r="W195" s="23"/>
+      <c r="X195" s="23"/>
+      <c r="Y195" s="23"/>
+      <c r="Z195" s="23"/>
+      <c r="AA195" s="23"/>
+      <c r="AB195" s="23"/>
+      <c r="AC195" s="23"/>
+      <c r="AD195" s="23"/>
+      <c r="AE195" s="23"/>
+      <c r="AF195" s="23"/>
+      <c r="AG195" s="23"/>
+      <c r="AH195" s="24"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="24"/>
-      <c r="C196" s="24"/>
-      <c r="D196" s="24"/>
-      <c r="E196" s="24"/>
-      <c r="F196" s="24"/>
-      <c r="G196" s="25"/>
-      <c r="H196" s="25"/>
-      <c r="I196" s="24"/>
-      <c r="J196" s="24"/>
-      <c r="K196" s="24"/>
-      <c r="L196" s="25"/>
-      <c r="M196" s="25"/>
-      <c r="N196" s="26"/>
-      <c r="O196" s="24"/>
-      <c r="P196" s="24"/>
-      <c r="Q196" s="25"/>
-      <c r="R196" s="25"/>
-      <c r="S196" s="24"/>
-      <c r="T196" s="24"/>
-      <c r="U196" s="24"/>
-      <c r="V196" s="24"/>
-      <c r="W196" s="24"/>
-      <c r="X196" s="24"/>
-      <c r="Y196" s="24"/>
-      <c r="Z196" s="24"/>
-      <c r="AA196" s="24"/>
-      <c r="AB196" s="24"/>
-      <c r="AC196" s="24"/>
-      <c r="AD196" s="24"/>
-      <c r="AE196" s="24"/>
-      <c r="AF196" s="24"/>
-      <c r="AG196" s="24"/>
-      <c r="AH196" s="25"/>
+      <c r="B196" s="23"/>
+      <c r="C196" s="23"/>
+      <c r="D196" s="23"/>
+      <c r="E196" s="23"/>
+      <c r="F196" s="23"/>
+      <c r="G196" s="24"/>
+      <c r="H196" s="24"/>
+      <c r="I196" s="23"/>
+      <c r="J196" s="23"/>
+      <c r="K196" s="23"/>
+      <c r="L196" s="24"/>
+      <c r="M196" s="24"/>
+      <c r="N196" s="25"/>
+      <c r="O196" s="23"/>
+      <c r="P196" s="23"/>
+      <c r="Q196" s="24"/>
+      <c r="R196" s="24"/>
+      <c r="S196" s="23"/>
+      <c r="T196" s="23"/>
+      <c r="U196" s="23"/>
+      <c r="V196" s="23"/>
+      <c r="W196" s="23"/>
+      <c r="X196" s="23"/>
+      <c r="Y196" s="23"/>
+      <c r="Z196" s="23"/>
+      <c r="AA196" s="23"/>
+      <c r="AB196" s="23"/>
+      <c r="AC196" s="23"/>
+      <c r="AD196" s="23"/>
+      <c r="AE196" s="23"/>
+      <c r="AF196" s="23"/>
+      <c r="AG196" s="23"/>
+      <c r="AH196" s="24"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="24"/>
-      <c r="C197" s="24"/>
-      <c r="D197" s="24"/>
-      <c r="E197" s="24"/>
-      <c r="F197" s="24"/>
-      <c r="G197" s="25"/>
-      <c r="H197" s="25"/>
-      <c r="I197" s="24"/>
-      <c r="J197" s="24"/>
-      <c r="K197" s="24"/>
-      <c r="L197" s="25"/>
-      <c r="M197" s="25"/>
-      <c r="N197" s="26"/>
-      <c r="O197" s="24"/>
-      <c r="P197" s="24"/>
-      <c r="Q197" s="25"/>
-      <c r="R197" s="25"/>
-      <c r="S197" s="24"/>
-      <c r="T197" s="24"/>
-      <c r="U197" s="24"/>
-      <c r="V197" s="24"/>
-      <c r="W197" s="24"/>
-      <c r="X197" s="24"/>
-      <c r="Y197" s="24"/>
-      <c r="Z197" s="24"/>
-      <c r="AA197" s="24"/>
-      <c r="AB197" s="24"/>
-      <c r="AC197" s="24"/>
-      <c r="AD197" s="24"/>
-      <c r="AE197" s="24"/>
-      <c r="AF197" s="24"/>
-      <c r="AG197" s="24"/>
-      <c r="AH197" s="25"/>
+      <c r="B197" s="23"/>
+      <c r="C197" s="23"/>
+      <c r="D197" s="23"/>
+      <c r="E197" s="23"/>
+      <c r="F197" s="23"/>
+      <c r="G197" s="24"/>
+      <c r="H197" s="24"/>
+      <c r="I197" s="23"/>
+      <c r="J197" s="23"/>
+      <c r="K197" s="23"/>
+      <c r="L197" s="24"/>
+      <c r="M197" s="24"/>
+      <c r="N197" s="25"/>
+      <c r="O197" s="23"/>
+      <c r="P197" s="23"/>
+      <c r="Q197" s="24"/>
+      <c r="R197" s="24"/>
+      <c r="S197" s="23"/>
+      <c r="T197" s="23"/>
+      <c r="U197" s="23"/>
+      <c r="V197" s="23"/>
+      <c r="W197" s="23"/>
+      <c r="X197" s="23"/>
+      <c r="Y197" s="23"/>
+      <c r="Z197" s="23"/>
+      <c r="AA197" s="23"/>
+      <c r="AB197" s="23"/>
+      <c r="AC197" s="23"/>
+      <c r="AD197" s="23"/>
+      <c r="AE197" s="23"/>
+      <c r="AF197" s="23"/>
+      <c r="AG197" s="23"/>
+      <c r="AH197" s="24"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B198" s="24"/>
-      <c r="C198" s="24"/>
-      <c r="D198" s="24"/>
-      <c r="E198" s="24"/>
-      <c r="F198" s="24"/>
-      <c r="G198" s="25"/>
-      <c r="H198" s="25"/>
-      <c r="I198" s="24"/>
-      <c r="J198" s="24"/>
-      <c r="K198" s="24"/>
-      <c r="L198" s="25"/>
-      <c r="M198" s="25"/>
-      <c r="N198" s="26"/>
-      <c r="O198" s="24"/>
-      <c r="P198" s="24"/>
-      <c r="Q198" s="25"/>
-      <c r="R198" s="25"/>
-      <c r="S198" s="24"/>
-      <c r="T198" s="24"/>
-      <c r="U198" s="24"/>
-      <c r="V198" s="24"/>
-      <c r="W198" s="24"/>
-      <c r="X198" s="24"/>
-      <c r="Y198" s="24"/>
-      <c r="Z198" s="24"/>
-      <c r="AA198" s="24"/>
-      <c r="AB198" s="24"/>
-      <c r="AC198" s="24"/>
-      <c r="AD198" s="24"/>
-      <c r="AE198" s="24"/>
-      <c r="AF198" s="24"/>
-      <c r="AG198" s="24"/>
-      <c r="AH198" s="25"/>
+      <c r="B198" s="23"/>
+      <c r="C198" s="23"/>
+      <c r="D198" s="23"/>
+      <c r="E198" s="23"/>
+      <c r="F198" s="23"/>
+      <c r="G198" s="24"/>
+      <c r="H198" s="24"/>
+      <c r="I198" s="23"/>
+      <c r="J198" s="23"/>
+      <c r="K198" s="23"/>
+      <c r="L198" s="24"/>
+      <c r="M198" s="24"/>
+      <c r="N198" s="25"/>
+      <c r="O198" s="23"/>
+      <c r="P198" s="23"/>
+      <c r="Q198" s="24"/>
+      <c r="R198" s="24"/>
+      <c r="S198" s="23"/>
+      <c r="T198" s="23"/>
+      <c r="U198" s="23"/>
+      <c r="V198" s="23"/>
+      <c r="W198" s="23"/>
+      <c r="X198" s="23"/>
+      <c r="Y198" s="23"/>
+      <c r="Z198" s="23"/>
+      <c r="AA198" s="23"/>
+      <c r="AB198" s="23"/>
+      <c r="AC198" s="23"/>
+      <c r="AD198" s="23"/>
+      <c r="AE198" s="23"/>
+      <c r="AF198" s="23"/>
+      <c r="AG198" s="23"/>
+      <c r="AH198" s="24"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B199" s="24"/>
-      <c r="C199" s="24"/>
-      <c r="D199" s="24"/>
-      <c r="E199" s="24"/>
-      <c r="F199" s="24"/>
-      <c r="G199" s="25"/>
-      <c r="H199" s="25"/>
-      <c r="I199" s="24"/>
-      <c r="J199" s="24"/>
-      <c r="K199" s="24"/>
-      <c r="L199" s="25"/>
-      <c r="M199" s="25"/>
-      <c r="N199" s="26"/>
-      <c r="O199" s="24"/>
-      <c r="P199" s="24"/>
-      <c r="Q199" s="25"/>
-      <c r="R199" s="25"/>
-      <c r="S199" s="24"/>
-      <c r="T199" s="24"/>
-      <c r="U199" s="24"/>
-      <c r="V199" s="24"/>
-      <c r="W199" s="24"/>
-      <c r="X199" s="24"/>
-      <c r="Y199" s="24"/>
-      <c r="Z199" s="24"/>
-      <c r="AA199" s="24"/>
-      <c r="AB199" s="24"/>
-      <c r="AC199" s="24"/>
-      <c r="AD199" s="24"/>
-      <c r="AE199" s="24"/>
-      <c r="AF199" s="24"/>
-      <c r="AG199" s="24"/>
-      <c r="AH199" s="25"/>
+      <c r="B199" s="23"/>
+      <c r="C199" s="23"/>
+      <c r="D199" s="23"/>
+      <c r="E199" s="23"/>
+      <c r="F199" s="23"/>
+      <c r="G199" s="24"/>
+      <c r="H199" s="24"/>
+      <c r="I199" s="23"/>
+      <c r="J199" s="23"/>
+      <c r="K199" s="23"/>
+      <c r="L199" s="24"/>
+      <c r="M199" s="24"/>
+      <c r="N199" s="25"/>
+      <c r="O199" s="23"/>
+      <c r="P199" s="23"/>
+      <c r="Q199" s="24"/>
+      <c r="R199" s="24"/>
+      <c r="S199" s="23"/>
+      <c r="T199" s="23"/>
+      <c r="U199" s="23"/>
+      <c r="V199" s="23"/>
+      <c r="W199" s="23"/>
+      <c r="X199" s="23"/>
+      <c r="Y199" s="23"/>
+      <c r="Z199" s="23"/>
+      <c r="AA199" s="23"/>
+      <c r="AB199" s="23"/>
+      <c r="AC199" s="23"/>
+      <c r="AD199" s="23"/>
+      <c r="AE199" s="23"/>
+      <c r="AF199" s="23"/>
+      <c r="AG199" s="23"/>
+      <c r="AH199" s="24"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B200" s="24"/>
-      <c r="C200" s="24"/>
-      <c r="D200" s="24"/>
-      <c r="E200" s="24"/>
-      <c r="F200" s="24"/>
-      <c r="G200" s="25"/>
-      <c r="H200" s="25"/>
-      <c r="I200" s="24"/>
-      <c r="J200" s="24"/>
-      <c r="K200" s="24"/>
-      <c r="L200" s="25"/>
-      <c r="M200" s="25"/>
-      <c r="N200" s="26"/>
-      <c r="O200" s="24"/>
-      <c r="P200" s="24"/>
-      <c r="Q200" s="25"/>
-      <c r="R200" s="25"/>
-      <c r="S200" s="24"/>
-      <c r="T200" s="24"/>
-      <c r="U200" s="24"/>
-      <c r="V200" s="24"/>
-      <c r="W200" s="24"/>
-      <c r="X200" s="24"/>
-      <c r="Y200" s="24"/>
-      <c r="Z200" s="24"/>
-      <c r="AA200" s="24"/>
-      <c r="AB200" s="24"/>
-      <c r="AC200" s="24"/>
-      <c r="AD200" s="24"/>
-      <c r="AE200" s="24"/>
-      <c r="AF200" s="24"/>
-      <c r="AG200" s="24"/>
-      <c r="AH200" s="25"/>
+      <c r="B200" s="23"/>
+      <c r="C200" s="23"/>
+      <c r="D200" s="23"/>
+      <c r="E200" s="23"/>
+      <c r="F200" s="23"/>
+      <c r="G200" s="24"/>
+      <c r="H200" s="24"/>
+      <c r="I200" s="23"/>
+      <c r="J200" s="23"/>
+      <c r="K200" s="23"/>
+      <c r="L200" s="24"/>
+      <c r="M200" s="24"/>
+      <c r="N200" s="25"/>
+      <c r="O200" s="23"/>
+      <c r="P200" s="23"/>
+      <c r="Q200" s="24"/>
+      <c r="R200" s="24"/>
+      <c r="S200" s="23"/>
+      <c r="T200" s="23"/>
+      <c r="U200" s="23"/>
+      <c r="V200" s="23"/>
+      <c r="W200" s="23"/>
+      <c r="X200" s="23"/>
+      <c r="Y200" s="23"/>
+      <c r="Z200" s="23"/>
+      <c r="AA200" s="23"/>
+      <c r="AB200" s="23"/>
+      <c r="AC200" s="23"/>
+      <c r="AD200" s="23"/>
+      <c r="AE200" s="23"/>
+      <c r="AF200" s="23"/>
+      <c r="AG200" s="23"/>
+      <c r="AH200" s="24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AH141"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -587,22 +587,22 @@
     <t xml:space="preserve">chargebigx Players</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the start of your turn, gain 1 temporary composure for each infected being including you.</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;b&gt;Infect&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Your attacks have the Crit option &lt;b&gt;Infect:&lt;/b&gt; Spend one chargeT, target takes the chargeT and is infected.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the start of your turn, gain 1 temporary composure for each infected being including you.</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;b&gt;Feast&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Remove an infected token from a being, and use one of your abilities spending their tokens.</t>
+    <t xml:space="preserve">Remove an infected token from a being, and force them to use an ability on one of their cards without AP costs.</t>
   </si>
   <si>
     <t xml:space="preserve">Wreathed in Flame</t>
@@ -1074,7 +1074,7 @@
     <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Minion&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">The boss does not consider you a target unless you are the last alive.</t>
+    <t xml:space="preserve">The boss does not consider you a target unless you are the last alive or you have dealt damage to it.</t>
   </si>
   <si>
     <t xml:space="preserve">Trickster</t>
@@ -4849,7 +4849,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="33.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="s">
         <v>180</v>
       </c>
@@ -4864,12 +4864,12 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="10" t="s">
         <v>183</v>
       </c>
       <c r="J25" s="11"/>
@@ -4882,7 +4882,7 @@
       <c r="M25" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="N25" s="12" t="s">
         <v>185</v>
       </c>
       <c r="O25" s="13"/>
@@ -4890,7 +4890,7 @@
         <v>9</v>
       </c>
       <c r="Q25" s="10" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="R25" s="12" t="s">
         <v>186</v>
@@ -5031,7 +5031,7 @@
         <v>66.4</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="46.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
         <v>195</v>
       </c>
@@ -5068,7 +5068,7 @@
       <c r="O27" s="13"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
+      <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="11"/>
       <c r="U27" s="10"/>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B672240D-CB5C-4879-96B5-81A770181858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE86A141-4EF2-4A0A-9ECD-3D047A2A2298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$1:$AH$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$1:$AH$139</definedName>
     <definedName name="Break">#REF!</definedName>
     <definedName name="start">#REF!</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="598">
   <si>
     <t>Change state</t>
   </si>
@@ -1364,18 +1364,12 @@
     <t>&lt;b&gt;&lt;i&gt;Snack&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
-    <t>Whenever you inflict a wound with Mandibles, refresh a spent token of the same type as the wound</t>
-  </si>
-  <si>
     <t>Mantid Scythe</t>
   </si>
   <si>
     <t>&lt;b&gt;Nasty Stab:&lt;/b&gt; 3 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;Armour Piercing:&lt;/b&gt; Ignore damage reduction effects.</t>
-  </si>
-  <si>
     <t>Monolith of Pain</t>
   </si>
   <si>
@@ -1424,10 +1418,6 @@
     <t>&lt;b&gt;Corrosive Spit:&lt;/b&gt; 2 AP + weirdT</t>
   </si>
   <si>
-    <t>&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
-&lt;br /&gt;Ignores damage reduction effects.</t>
-  </si>
-  <si>
     <t>Oversized Claw</t>
   </si>
   <si>
@@ -1468,10 +1458,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Volley:&lt;/b&gt; 2 AP</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
-&lt;br /&gt;You take 1 damage when you use this attack, this damage cannot be reduced.</t>
   </si>
   <si>
     <t>Puffballs</t>
@@ -1555,10 +1541,6 @@
     <t>&lt;b&gt;Ping!:&lt;/b&gt; 1 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;Dash:&lt;/b&gt; Take a move action for free.
-&lt;br /&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage.</t>
-  </si>
-  <si>
     <t>Spore Coat</t>
   </si>
   <si>
@@ -1591,9 +1573,6 @@
 &lt;br /&gt;On a hit, remove all &lt;b&gt;temporary composure&lt;/b&gt; from the target before dealing damage.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack cannot be reduced.</t>
-  </si>
-  <si>
     <t>Stone-Swivel Hinge</t>
   </si>
   <si>
@@ -1607,13 +1586,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Squint:&lt;/b&gt; 2 AP or (weirdT + 1 AP)</t>
-  </si>
-  <si>
-    <t>Damage = 2, Ranged&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Armour Piercing:&lt;/b&gt; Damage from this attack can’t be reduced.
-&lt;br /&gt;&lt;b&gt;Insight:&lt;/b&gt; Regain a spent WeirdT.</t>
   </si>
   <si>
     <t>Thermal Funnel</t>
@@ -1633,9 +1605,6 @@
     <t>&lt;b&gt;Winch:&lt;/b&gt; 1 AP</t>
   </si>
   <si>
-    <t>Add chargeT to this card. Activate only once each turn.</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Release:&lt;/b&gt; 5 x chargeT</t>
   </si>
   <si>
@@ -1677,9 +1646,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Summon Saplings:&lt;/b&gt; weirdtweirdT</t>
-  </si>
-  <si>
-    <t>Fill 3 target connected empty hexes with a willow tree which blocks movement and vision. Each hex can be individually destroyed by dealing damage.</t>
   </si>
   <si>
     <t>Withered Hand</t>
@@ -1858,6 +1824,66 @@
   </si>
   <si>
     <t>&lt;b&gt;Slap:&lt;/b&gt; 2 AP or 1 AP + jazztjazzt</t>
+  </si>
+  <si>
+    <t>Whenever you inflict a wound with Mandibles, refresh a spent token of the same type as the wound.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;True Strike:&lt;/b&gt; Attack deals &lt;b&gt;true damage&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Damage = 4 true damage, Ranged&lt;/b&gt;
+</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Damage = 4, Ranged&lt;/b&gt;
+&lt;br /&gt;You take &lt;b&gt;true damage&lt;/b&gt; when you use this attack, this damage cannot be reduced.</t>
+  </si>
+  <si>
+    <t>Pustule</t>
+  </si>
+  <si>
+    <t>ChargeBig</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Burst:&lt;/b&gt; Destroy this card</t>
+  </si>
+  <si>
+    <t>Deal 6 damage to all beings within 2 hexes, activate only after taking damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Dash:&lt;/b&gt; Take a move action for free.
+&lt;br /&gt;&lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage. Use this only once per attack</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Strike:&lt;/b&gt; +1 damage.&lt;br/&gt;&lt;b&gt;Impale: &lt;/b&gt;Move to a hex adjacent to the target and deal + 2 damage. Use this only once per attack</t>
+  </si>
+  <si>
+    <t>Damage = 2 &lt;b&gt;true damage&lt;/b&gt;, Ranged&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Add chargeT to this card. Activate up to twice each turn.</t>
+  </si>
+  <si>
+    <t>Weird Stone</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Embed:&lt;/b&gt; weirdtweirdt or charget</t>
+  </si>
+  <si>
+    <t>Place a 1 hex crystal on an adjacent hex. Is blocks line of sight and is &lt;b&gt;destructible&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;i&gt;Disruption&lt;/b&gt;&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>While the crystal is in play, any being that spends weirdT takes 2 damage.</t>
+  </si>
+  <si>
+    <t>Fill 3 target connected empty hexes with a willow tree which blocks movement and vision. Each hex is &lt;b&gt;destructible&lt;/b&gt;.</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH197"/>
+  <dimension ref="A1:AH198"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -2604,7 +2630,7 @@
         <v>40</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="8">
@@ -2617,7 +2643,7 @@
         <v>41</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="8">
@@ -2704,7 +2730,7 @@
         <v>45</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="8">
@@ -2717,7 +2743,7 @@
         <v>46</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="T3" s="9"/>
       <c r="U3" s="8"/>
@@ -2796,7 +2822,7 @@
         <v>51</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="O4" s="11"/>
       <c r="P4" s="8">
@@ -2961,7 +2987,7 @@
         <v>63</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8">
@@ -2974,7 +3000,7 @@
         <v>64</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="8"/>
@@ -3150,7 +3176,7 @@
         <v>39</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>77</v>
@@ -3554,7 +3580,7 @@
     </row>
     <row r="13" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>35</v>
@@ -3568,10 +3594,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="8">
@@ -3581,10 +3607,10 @@
         <v>39</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="8"/>
@@ -3835,7 +3861,7 @@
         <v>117</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8">
@@ -3845,10 +3871,10 @@
         <v>36</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="8"/>
@@ -4202,7 +4228,7 @@
         <v>39</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>144</v>
@@ -4711,7 +4737,7 @@
         <v>172</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8">
@@ -4901,7 +4927,7 @@
         <v>39</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>187</v>
@@ -5491,7 +5517,7 @@
         <v>199</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="8"/>
@@ -5565,7 +5591,7 @@
         <v>210</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="8">
@@ -5647,10 +5673,10 @@
         <v>134</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="8"/>
@@ -5724,7 +5750,7 @@
         <v>199</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="8"/>
@@ -6104,7 +6130,7 @@
         <v>199</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="8"/>
@@ -6516,7 +6542,7 @@
         <v>39</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="N49" s="8" t="s">
         <v>249</v>
@@ -6662,7 +6688,7 @@
         <v>254</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="J51" s="9"/>
       <c r="K51" s="8"/>
@@ -7376,7 +7402,7 @@
         <v>288</v>
       </c>
       <c r="N60" s="8" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="O60" s="11"/>
       <c r="P60" s="8"/>
@@ -7938,39 +7964,39 @@
       <c r="X67" s="8"/>
       <c r="Y67" s="8"/>
       <c r="Z67" s="8">
-        <f t="shared" ref="Z67:Z122" si="18">AB67+Y$2</f>
+        <f t="shared" ref="Z67:Z123" si="18">AB67+Y$2</f>
         <v>20</v>
       </c>
       <c r="AA67" s="8">
-        <f t="shared" ref="AA67:AA122" si="19">Z67+X$2</f>
+        <f t="shared" ref="AA67:AA123" si="19">Z67+X$2</f>
         <v>18.899999999999999</v>
       </c>
       <c r="AB67" s="8">
-        <f t="shared" ref="AB67:AB122" si="20">U$2+V$2*(F67-1)</f>
+        <f t="shared" ref="AB67:AB123" si="20">U$2+V$2*(F67-1)</f>
         <v>26</v>
       </c>
       <c r="AC67" s="8">
-        <f t="shared" ref="AC67:AC122" si="21">AE67+Y$2</f>
+        <f t="shared" ref="AC67:AC123" si="21">AE67+Y$2</f>
         <v>45</v>
       </c>
       <c r="AD67" s="8">
-        <f t="shared" ref="AD67:AD122" si="22">AC67+X$2</f>
+        <f t="shared" ref="AD67:AD123" si="22">AC67+X$2</f>
         <v>43.9</v>
       </c>
       <c r="AE67" s="8">
-        <f t="shared" ref="AE67:AE122" si="23">U$2+V$2*(K67-1)+W$2</f>
+        <f t="shared" ref="AE67:AE123" si="23">U$2+V$2*(K67-1)+W$2</f>
         <v>51</v>
       </c>
       <c r="AF67" s="8">
-        <f t="shared" ref="AF67:AF122" si="24">AH67+Y$2</f>
+        <f t="shared" ref="AF67:AF123" si="24">AH67+Y$2</f>
         <v>21.6</v>
       </c>
       <c r="AG67" s="8">
-        <f t="shared" ref="AG67:AG122" si="25">AF67+X$2</f>
+        <f t="shared" ref="AG67:AG123" si="25">AF67+X$2</f>
         <v>20.5</v>
       </c>
       <c r="AH67" s="10">
-        <f t="shared" ref="AH67:AH122" si="26">U$2+V$2*(P67-1)+2*W$2</f>
+        <f t="shared" ref="AH67:AH123" si="26">U$2+V$2*(P67-1)+2*W$2</f>
         <v>27.6</v>
       </c>
     </row>
@@ -8337,7 +8363,7 @@
         <v>338</v>
       </c>
       <c r="N72" s="8" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="O72" s="11"/>
       <c r="P72" s="8"/>
@@ -8490,7 +8516,7 @@
         <v>345</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="J74" s="9"/>
       <c r="K74" s="8">
@@ -8503,7 +8529,7 @@
         <v>346</v>
       </c>
       <c r="N74" s="8" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="O74" s="11"/>
       <c r="P74" s="8"/>
@@ -8736,7 +8762,7 @@
         <v>356</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="J77" s="9"/>
       <c r="K77" s="8">
@@ -8749,7 +8775,7 @@
         <v>357</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="O77" s="11"/>
       <c r="P77" s="8"/>
@@ -8902,7 +8928,7 @@
         <v>325</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>364</v>
@@ -9080,7 +9106,7 @@
         <v>374</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="J81" s="9"/>
       <c r="K81" s="8">
@@ -9090,10 +9116,10 @@
         <v>36</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="O81" s="11"/>
       <c r="P81" s="8">
@@ -9170,7 +9196,7 @@
         <v>378</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="J82" s="9"/>
       <c r="K82" s="8">
@@ -9255,7 +9281,7 @@
         <v>382</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="J83" s="9"/>
       <c r="K83" s="8">
@@ -9265,7 +9291,7 @@
         <v>36</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="N83" s="8" t="s">
         <v>383</v>
@@ -9339,7 +9365,7 @@
         <v>39</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>385</v>
@@ -9355,7 +9381,7 @@
         <v>386</v>
       </c>
       <c r="N84" s="8" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="O84" s="11"/>
       <c r="P84" s="8">
@@ -9418,13 +9444,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>322</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E85" s="9"/>
       <c r="F85" s="8">
@@ -9437,7 +9463,7 @@
         <v>390</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="J85" s="9"/>
       <c r="K85" s="8">
@@ -9447,7 +9473,7 @@
         <v>39</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="N85" s="8" t="s">
         <v>391</v>
@@ -9460,10 +9486,10 @@
         <v>36</v>
       </c>
       <c r="R85" s="8" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="S85" s="8" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="T85" s="9"/>
       <c r="U85" s="8"/>
@@ -9702,7 +9728,7 @@
         <v>401</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="J88" s="9"/>
       <c r="K88" s="8"/>
@@ -9773,10 +9799,10 @@
         <v>325</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="J89" s="9"/>
       <c r="K89" s="8">
@@ -9802,7 +9828,7 @@
         <v>329</v>
       </c>
       <c r="S89" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="T89" s="9"/>
       <c r="U89" s="8"/>
@@ -9866,7 +9892,7 @@
         <v>406</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="8">
@@ -10127,7 +10153,7 @@
         <v>422</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="O93" s="11"/>
       <c r="P93" s="8"/>
@@ -10291,7 +10317,7 @@
         <v>430</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>431</v>
+        <v>579</v>
       </c>
       <c r="O95" s="11"/>
       <c r="P95" s="8"/>
@@ -10343,7 +10369,7 @@
     </row>
     <row r="96" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B96" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>322</v>
@@ -10357,7 +10383,7 @@
         <v>325</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I96" s="10" t="s">
         <v>397</v>
@@ -10373,7 +10399,7 @@
         <v>329</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>434</v>
+        <v>580</v>
       </c>
       <c r="O96" s="11"/>
       <c r="P96" s="8"/>
@@ -10425,7 +10451,7 @@
     </row>
     <row r="97" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B97" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>322</v>
@@ -10439,10 +10465,10 @@
         <v>134</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J97" s="9"/>
       <c r="K97" s="8">
@@ -10452,10 +10478,10 @@
         <v>36</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O97" s="11"/>
       <c r="P97" s="8"/>
@@ -10510,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>322</v>
@@ -10524,7 +10550,7 @@
         <v>325</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I98" s="10" t="s">
         <v>397</v>
@@ -10537,10 +10563,10 @@
         <v>39</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N98" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O98" s="11"/>
       <c r="P98" s="8"/>
@@ -10592,7 +10618,7 @@
     </row>
     <row r="99" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>322</v>
@@ -10606,7 +10632,7 @@
         <v>325</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>333</v>
@@ -10619,10 +10645,10 @@
         <v>36</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O99" s="11"/>
       <c r="P99" s="8">
@@ -10635,7 +10661,7 @@
         <v>329</v>
       </c>
       <c r="S99" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="T99" s="9"/>
       <c r="U99" s="8"/>
@@ -10682,7 +10708,7 @@
     </row>
     <row r="100" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B100" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C100" s="17" t="s">
         <v>322</v>
@@ -10696,10 +10722,10 @@
         <v>325</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>451</v>
+        <v>581</v>
       </c>
       <c r="J100" s="9"/>
       <c r="K100" s="8"/>
@@ -10756,7 +10782,7 @@
     </row>
     <row r="101" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>322</v>
@@ -10770,10 +10796,10 @@
         <v>325</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J101" s="9"/>
       <c r="K101" s="8"/>
@@ -10833,7 +10859,7 @@
         <v>1</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C102" s="17" t="s">
         <v>322</v>
@@ -10847,7 +10873,7 @@
         <v>325</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I102" s="10" t="s">
         <v>380</v>
@@ -10860,10 +10886,10 @@
         <v>39</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="O102" s="11"/>
       <c r="P102" s="8">
@@ -10873,10 +10899,10 @@
         <v>39</v>
       </c>
       <c r="R102" s="8" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="S102" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="T102" s="9"/>
       <c r="U102" s="8"/>
@@ -10923,7 +10949,7 @@
     </row>
     <row r="103" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C103" s="17" t="s">
         <v>322</v>
@@ -10937,10 +10963,10 @@
         <v>325</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J103" s="9"/>
       <c r="K103" s="8">
@@ -10953,7 +10979,7 @@
         <v>329</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="O103" s="11"/>
       <c r="P103" s="8"/>
@@ -11003,12 +11029,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="104" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:34" ht="60" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C104" s="17" t="s">
         <v>322</v>
@@ -11022,10 +11048,10 @@
         <v>325</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>466</v>
+        <v>582</v>
       </c>
       <c r="J104" s="9"/>
       <c r="K104" s="8"/>
@@ -11082,7 +11108,7 @@
     </row>
     <row r="105" spans="1:34" ht="60" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C105" s="17" t="s">
         <v>322</v>
@@ -11098,10 +11124,10 @@
         <v>39</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="J105" s="9"/>
       <c r="K105" s="8">
@@ -11111,10 +11137,10 @@
         <v>134</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N105" s="8" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="O105" s="11"/>
       <c r="P105" s="8"/>
@@ -11164,42 +11190,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="106" spans="1:34" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B106" s="6" t="s">
-        <v>472</v>
+        <v>583</v>
       </c>
       <c r="C106" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="D106" s="10" t="s">
-        <v>109</v>
+      <c r="D106" s="8" t="s">
+        <v>584</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="8">
         <v>1</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>359</v>
+        <v>585</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>473</v>
+        <v>586</v>
       </c>
       <c r="J106" s="9"/>
-      <c r="K106" s="8">
-        <v>5</v>
-      </c>
-      <c r="L106" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M106" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="N106" s="8" t="s">
-        <v>475</v>
-      </c>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="8"/>
       <c r="O106" s="11"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="8"/>
@@ -11212,86 +11230,83 @@
       <c r="X106" s="8"/>
       <c r="Y106" s="8"/>
       <c r="Z106" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="Z106" si="27">AB106+Y$2</f>
         <v>20</v>
       </c>
       <c r="AA106" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="AA106" si="28">Z106+X$2</f>
         <v>18.899999999999999</v>
       </c>
       <c r="AB106" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="AB106" si="29">U$2+V$2*(F106-1)</f>
         <v>26</v>
       </c>
       <c r="AC106" s="8">
-        <f t="shared" si="21"/>
-        <v>40.6</v>
+        <f t="shared" ref="AC106" si="30">AE106+Y$2</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="AD106" s="8">
-        <f t="shared" si="22"/>
-        <v>39.5</v>
+        <f t="shared" ref="AD106" si="31">AC106+X$2</f>
+        <v>17.5</v>
       </c>
       <c r="AE106" s="8">
-        <f t="shared" si="23"/>
-        <v>46.6</v>
+        <f t="shared" ref="AE106" si="32">U$2+V$2*(K106-1)+W$2</f>
+        <v>24.6</v>
       </c>
       <c r="AF106" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="AF106" si="33">AH106+Y$2</f>
         <v>21.6</v>
       </c>
       <c r="AG106" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="AG106" si="34">AF106+X$2</f>
         <v>20.5</v>
       </c>
       <c r="AH106" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="AH106" si="35">U$2+V$2*(P106-1)+2*W$2</f>
         <v>27.6</v>
       </c>
     </row>
     <row r="107" spans="1:34" ht="60" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>1</v>
-      </c>
       <c r="B107" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="C107" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="C107" s="17" t="s">
         <v>322</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>389</v>
+        <v>109</v>
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="8">
         <v>1</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>39</v>
+        <v>587</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>477</v>
+        <v>359</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="J107" s="9"/>
       <c r="K107" s="8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>36</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="N107" s="10" t="s">
-        <v>479</v>
+        <v>470</v>
+      </c>
+      <c r="N107" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="O107" s="11"/>
       <c r="P107" s="8"/>
       <c r="Q107" s="8"/>
       <c r="R107" s="8"/>
-      <c r="S107" s="10"/>
+      <c r="S107" s="8"/>
       <c r="T107" s="9"/>
       <c r="U107" s="8"/>
       <c r="V107" s="8"/>
@@ -11312,15 +11327,15 @@
       </c>
       <c r="AC107" s="8">
         <f t="shared" si="21"/>
-        <v>58.2</v>
+        <v>40.6</v>
       </c>
       <c r="AD107" s="8">
         <f t="shared" si="22"/>
-        <v>57.1</v>
+        <v>39.5</v>
       </c>
       <c r="AE107" s="8">
         <f t="shared" si="23"/>
-        <v>64.2</v>
+        <v>46.6</v>
       </c>
       <c r="AF107" s="8">
         <f t="shared" si="24"/>
@@ -11335,53 +11350,50 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="108" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:34" ht="60" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1</v>
+      </c>
       <c r="B108" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="C108" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="C108" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="D108" s="8"/>
+      <c r="D108" s="10" t="s">
+        <v>389</v>
+      </c>
       <c r="E108" s="9"/>
       <c r="F108" s="8">
         <v>1</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>325</v>
+        <v>39</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>349</v>
+        <v>474</v>
       </c>
       <c r="J108" s="9"/>
       <c r="K108" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="N108" s="8" t="s">
-        <v>483</v>
+        <v>199</v>
+      </c>
+      <c r="N108" s="10" t="s">
+        <v>475</v>
       </c>
       <c r="O108" s="11"/>
-      <c r="P108" s="8">
-        <v>10</v>
-      </c>
-      <c r="Q108" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="R108" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S108" s="8" t="s">
-        <v>394</v>
-      </c>
+      <c r="P108" s="8"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="8"/>
+      <c r="S108" s="10"/>
       <c r="T108" s="9"/>
       <c r="U108" s="8"/>
       <c r="V108" s="8"/>
@@ -11402,32 +11414,32 @@
       </c>
       <c r="AC108" s="8">
         <f t="shared" si="21"/>
-        <v>31.799999999999997</v>
+        <v>58.2</v>
       </c>
       <c r="AD108" s="8">
         <f t="shared" si="22"/>
-        <v>30.699999999999996</v>
+        <v>57.1</v>
       </c>
       <c r="AE108" s="8">
         <f t="shared" si="23"/>
-        <v>37.799999999999997</v>
+        <v>64.2</v>
       </c>
       <c r="AF108" s="8">
         <f t="shared" si="24"/>
-        <v>65.599999999999994</v>
+        <v>21.6</v>
       </c>
       <c r="AG108" s="8">
         <f t="shared" si="25"/>
-        <v>64.5</v>
+        <v>20.5</v>
       </c>
       <c r="AH108" s="10">
         <f t="shared" si="26"/>
-        <v>71.599999999999994</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="109" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C109" s="17" t="s">
         <v>322</v>
@@ -11441,29 +11453,37 @@
         <v>325</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>486</v>
+        <v>349</v>
       </c>
       <c r="J109" s="9"/>
       <c r="K109" s="8">
+        <v>3</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="N109" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="O109" s="11"/>
+      <c r="P109" s="8">
         <v>10</v>
       </c>
-      <c r="L109" s="8" t="s">
+      <c r="Q109" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="M109" s="8" t="s">
+      <c r="R109" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="N109" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="O109" s="11"/>
-      <c r="P109" s="8"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
-      <c r="S109" s="8"/>
+      <c r="S109" s="8" t="s">
+        <v>394</v>
+      </c>
       <c r="T109" s="9"/>
       <c r="U109" s="8"/>
       <c r="V109" s="8"/>
@@ -11484,66 +11504,71 @@
       </c>
       <c r="AC109" s="8">
         <f t="shared" si="21"/>
-        <v>62.599999999999994</v>
+        <v>31.799999999999997</v>
       </c>
       <c r="AD109" s="8">
         <f t="shared" si="22"/>
-        <v>61.499999999999993</v>
+        <v>30.699999999999996</v>
       </c>
       <c r="AE109" s="8">
         <f t="shared" si="23"/>
-        <v>68.599999999999994</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AF109" s="8">
         <f t="shared" si="24"/>
-        <v>21.6</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="AG109" s="8">
         <f t="shared" si="25"/>
-        <v>20.5</v>
+        <v>64.5</v>
       </c>
       <c r="AH109" s="10">
         <f t="shared" si="26"/>
-        <v>27.6</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="110" spans="1:34" ht="45" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>1</v>
-      </c>
       <c r="B110" s="6" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>322</v>
       </c>
       <c r="D110" s="8"/>
-      <c r="E110" s="15"/>
+      <c r="E110" s="9"/>
       <c r="F110" s="8">
         <v>1</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="H110" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="J110" s="15"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
-      <c r="N110" s="8"/>
-      <c r="O110" s="16"/>
+      <c r="H110" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="J110" s="9"/>
+      <c r="K110" s="8">
+        <v>10</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="M110" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="N110" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="O110" s="11"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8"/>
       <c r="R110" s="8"/>
       <c r="S110" s="8"/>
-      <c r="T110" s="15"/>
-      <c r="U110" s="10"/>
-      <c r="V110" s="10"/>
+      <c r="T110" s="9"/>
+      <c r="U110" s="8"/>
+      <c r="V110" s="8"/>
       <c r="W110" s="8"/>
       <c r="X110" s="8"/>
       <c r="Y110" s="8"/>
@@ -11561,15 +11586,15 @@
       </c>
       <c r="AC110" s="8">
         <f t="shared" si="21"/>
-        <v>18.600000000000001</v>
+        <v>62.599999999999994</v>
       </c>
       <c r="AD110" s="8">
         <f t="shared" si="22"/>
-        <v>17.5</v>
+        <v>61.499999999999993</v>
       </c>
       <c r="AE110" s="8">
         <f t="shared" si="23"/>
-        <v>24.6</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="AF110" s="8">
         <f t="shared" si="24"/>
@@ -11589,46 +11614,38 @@
         <v>1</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C111" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="D111" s="10"/>
-      <c r="E111" s="9"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="15"/>
       <c r="F111" s="8">
         <v>1</v>
       </c>
-      <c r="G111" s="10" t="s">
+      <c r="G111" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="H111" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="I111" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J111" s="9"/>
-      <c r="K111" s="8">
-        <v>9</v>
-      </c>
-      <c r="L111" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="M111" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="N111" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="O111" s="11"/>
+      <c r="H111" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="J111" s="15"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
+      <c r="N111" s="8"/>
+      <c r="O111" s="16"/>
       <c r="P111" s="8"/>
       <c r="Q111" s="8"/>
       <c r="R111" s="8"/>
-      <c r="S111" s="10"/>
-      <c r="T111" s="9"/>
-      <c r="U111" s="8"/>
-      <c r="V111" s="8"/>
+      <c r="S111" s="8"/>
+      <c r="T111" s="15"/>
+      <c r="U111" s="10"/>
+      <c r="V111" s="10"/>
       <c r="W111" s="8"/>
       <c r="X111" s="8"/>
       <c r="Y111" s="8"/>
@@ -11646,15 +11663,15 @@
       </c>
       <c r="AC111" s="8">
         <f t="shared" si="21"/>
-        <v>58.2</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="AD111" s="8">
         <f t="shared" si="22"/>
-        <v>57.1</v>
+        <v>17.5</v>
       </c>
       <c r="AE111" s="8">
         <f t="shared" si="23"/>
-        <v>64.2</v>
+        <v>24.6</v>
       </c>
       <c r="AF111" s="8">
         <f t="shared" si="24"/>
@@ -11669,12 +11686,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="112" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:34" ht="60" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C112" s="17" t="s">
         <v>322</v>
@@ -11685,26 +11702,26 @@
         <v>1</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>36</v>
+        <v>488</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>495</v>
+        <v>369</v>
       </c>
       <c r="J112" s="9"/>
       <c r="K112" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>496</v>
+        <v>329</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>497</v>
+        <v>588</v>
       </c>
       <c r="O112" s="11"/>
       <c r="P112" s="8"/>
@@ -11731,15 +11748,15 @@
       </c>
       <c r="AC112" s="8">
         <f t="shared" si="21"/>
-        <v>36.200000000000003</v>
+        <v>58.2</v>
       </c>
       <c r="AD112" s="8">
         <f t="shared" si="22"/>
-        <v>35.1</v>
+        <v>57.1</v>
       </c>
       <c r="AE112" s="8">
         <f t="shared" si="23"/>
-        <v>42.2</v>
+        <v>64.2</v>
       </c>
       <c r="AF112" s="8">
         <f t="shared" si="24"/>
@@ -11755,8 +11772,11 @@
       </c>
     </row>
     <row r="113" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1</v>
+      </c>
       <c r="B113" s="6" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>322</v>
@@ -11767,26 +11787,26 @@
         <v>1</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>325</v>
+        <v>36</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>499</v>
+        <v>36</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="J113" s="9"/>
       <c r="K113" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>329</v>
+        <v>491</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="O113" s="11"/>
       <c r="P113" s="8"/>
@@ -11813,15 +11833,15 @@
       </c>
       <c r="AC113" s="8">
         <f t="shared" si="21"/>
-        <v>62.599999999999994</v>
+        <v>40.6</v>
       </c>
       <c r="AD113" s="8">
         <f t="shared" si="22"/>
-        <v>61.499999999999993</v>
+        <v>39.5</v>
       </c>
       <c r="AE113" s="8">
         <f t="shared" si="23"/>
-        <v>68.599999999999994</v>
+        <v>46.6</v>
       </c>
       <c r="AF113" s="8">
         <f t="shared" si="24"/>
@@ -11838,7 +11858,7 @@
     </row>
     <row r="114" spans="1:34" ht="60" x14ac:dyDescent="0.25">
       <c r="B114" s="6" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>322</v>
@@ -11852,14 +11872,14 @@
         <v>325</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="J114" s="9"/>
       <c r="K114" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>328</v>
@@ -11868,7 +11888,7 @@
         <v>329</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>504</v>
+        <v>589</v>
       </c>
       <c r="O114" s="11"/>
       <c r="P114" s="8"/>
@@ -11895,15 +11915,15 @@
       </c>
       <c r="AC114" s="8">
         <f t="shared" si="21"/>
-        <v>58.2</v>
+        <v>62.599999999999994</v>
       </c>
       <c r="AD114" s="8">
         <f t="shared" si="22"/>
-        <v>57.1</v>
+        <v>61.499999999999993</v>
       </c>
       <c r="AE114" s="8">
         <f t="shared" si="23"/>
-        <v>64.2</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="AF114" s="8">
         <f t="shared" si="24"/>
@@ -11918,9 +11938,9 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="115" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:34" ht="60" x14ac:dyDescent="0.25">
       <c r="B115" s="6" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>322</v>
@@ -11934,10 +11954,10 @@
         <v>325</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="J115" s="9"/>
       <c r="K115" s="8">
@@ -11950,7 +11970,7 @@
         <v>329</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="O115" s="11"/>
       <c r="P115" s="8"/>
@@ -12000,9 +12020,9 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="116" spans="1:34" ht="60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B116" s="6" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C116" s="17" t="s">
         <v>322</v>
@@ -12016,10 +12036,10 @@
         <v>325</v>
       </c>
       <c r="H116" s="10" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>510</v>
+        <v>451</v>
       </c>
       <c r="J116" s="9"/>
       <c r="K116" s="8">
@@ -12032,7 +12052,7 @@
         <v>329</v>
       </c>
       <c r="N116" s="10" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="O116" s="11"/>
       <c r="P116" s="8"/>
@@ -12082,9 +12102,9 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="117" spans="1:34" ht="75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="B117" s="6" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C117" s="17" t="s">
         <v>322</v>
@@ -12098,10 +12118,10 @@
         <v>325</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="J117" s="9"/>
       <c r="K117" s="8"/>
@@ -12158,7 +12178,7 @@
     </row>
     <row r="118" spans="1:34" ht="75" x14ac:dyDescent="0.25">
       <c r="B118" s="6" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="C118" s="17" t="s">
         <v>322</v>
@@ -12169,27 +12189,19 @@
         <v>1</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>39</v>
+        <v>325</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="J118" s="9"/>
-      <c r="K118" s="8">
-        <v>4</v>
-      </c>
-      <c r="L118" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="M118" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="N118" s="10" t="s">
-        <v>519</v>
-      </c>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="N118" s="10"/>
       <c r="O118" s="11"/>
       <c r="P118" s="8"/>
       <c r="Q118" s="8"/>
@@ -12215,15 +12227,15 @@
       </c>
       <c r="AC118" s="8">
         <f t="shared" si="21"/>
-        <v>36.200000000000003</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="AD118" s="8">
         <f t="shared" si="22"/>
-        <v>35.1</v>
+        <v>17.5</v>
       </c>
       <c r="AE118" s="8">
         <f t="shared" si="23"/>
-        <v>42.2</v>
+        <v>24.6</v>
       </c>
       <c r="AF118" s="8">
         <f t="shared" si="24"/>
@@ -12240,7 +12252,7 @@
     </row>
     <row r="119" spans="1:34" ht="75" x14ac:dyDescent="0.25">
       <c r="B119" s="6" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C119" s="17" t="s">
         <v>322</v>
@@ -12251,26 +12263,26 @@
         <v>1</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>325</v>
+        <v>39</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>349</v>
+        <v>591</v>
       </c>
       <c r="J119" s="9"/>
       <c r="K119" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="M119" s="8" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="O119" s="11"/>
       <c r="P119" s="8"/>
@@ -12297,15 +12309,15 @@
       </c>
       <c r="AC119" s="8">
         <f t="shared" si="21"/>
-        <v>31.799999999999997</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AD119" s="8">
         <f t="shared" si="22"/>
-        <v>30.699999999999996</v>
+        <v>35.1</v>
       </c>
       <c r="AE119" s="8">
         <f t="shared" si="23"/>
-        <v>37.799999999999997</v>
+        <v>42.2</v>
       </c>
       <c r="AF119" s="8">
         <f t="shared" si="24"/>
@@ -12320,9 +12332,9 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="120" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:34" ht="75" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C120" s="17" t="s">
         <v>322</v>
@@ -12336,37 +12348,29 @@
         <v>325</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="8">
         <v>3</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="M120" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="N120" s="8" t="s">
-        <v>527</v>
+        <v>513</v>
+      </c>
+      <c r="N120" s="10" t="s">
+        <v>514</v>
       </c>
       <c r="O120" s="11"/>
-      <c r="P120" s="8">
-        <v>10</v>
-      </c>
-      <c r="Q120" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="R120" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S120" s="10" t="s">
-        <v>528</v>
-      </c>
+      <c r="P120" s="8"/>
+      <c r="Q120" s="8"/>
+      <c r="R120" s="8"/>
+      <c r="S120" s="10"/>
       <c r="T120" s="9"/>
       <c r="U120" s="8"/>
       <c r="V120" s="8"/>
@@ -12399,20 +12403,20 @@
       </c>
       <c r="AF120" s="8">
         <f t="shared" si="24"/>
-        <v>65.599999999999994</v>
+        <v>21.6</v>
       </c>
       <c r="AG120" s="8">
         <f t="shared" si="25"/>
-        <v>64.5</v>
+        <v>20.5</v>
       </c>
       <c r="AH120" s="10">
         <f t="shared" si="26"/>
-        <v>71.599999999999994</v>
-      </c>
-    </row>
-    <row r="121" spans="1:34" ht="60" x14ac:dyDescent="0.25">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="B121" s="6" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="C121" s="17" t="s">
         <v>322</v>
@@ -12426,29 +12430,37 @@
         <v>325</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="J121" s="9"/>
       <c r="K121" s="8">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="M121" s="8" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="N121" s="8" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="O121" s="11"/>
-      <c r="P121" s="8"/>
-      <c r="Q121" s="8"/>
-      <c r="R121" s="8"/>
-      <c r="S121" s="10"/>
+      <c r="P121" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q121" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="R121" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="S121" s="10" t="s">
+        <v>519</v>
+      </c>
       <c r="T121" s="9"/>
       <c r="U121" s="8"/>
       <c r="V121" s="8"/>
@@ -12481,23 +12493,20 @@
       </c>
       <c r="AF121" s="8">
         <f t="shared" si="24"/>
-        <v>21.6</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="AG121" s="8">
         <f t="shared" si="25"/>
-        <v>20.5</v>
+        <v>64.5</v>
       </c>
       <c r="AH121" s="10">
         <f t="shared" si="26"/>
-        <v>27.6</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="122" spans="1:34" ht="45" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>1</v>
-      </c>
       <c r="B122" s="6" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C122" s="17" t="s">
         <v>322</v>
@@ -12511,16 +12520,24 @@
         <v>325</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>535</v>
+        <v>415</v>
       </c>
       <c r="J122" s="9"/>
-      <c r="K122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="8"/>
-      <c r="N122" s="10"/>
+      <c r="K122" s="8">
+        <v>3</v>
+      </c>
+      <c r="L122" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M122" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="N122" s="8" t="s">
+        <v>597</v>
+      </c>
       <c r="O122" s="11"/>
       <c r="P122" s="8"/>
       <c r="Q122" s="8"/>
@@ -12546,15 +12563,15 @@
       </c>
       <c r="AC122" s="8">
         <f t="shared" si="21"/>
-        <v>18.600000000000001</v>
+        <v>31.799999999999997</v>
       </c>
       <c r="AD122" s="8">
         <f t="shared" si="22"/>
-        <v>17.5</v>
+        <v>30.699999999999996</v>
       </c>
       <c r="AE122" s="8">
         <f t="shared" si="23"/>
-        <v>24.6</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AF122" s="8">
         <f t="shared" si="24"/>
@@ -12569,75 +12586,166 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="B123" s="20"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="21"/>
-      <c r="H123" s="21"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="20"/>
-      <c r="K123" s="20"/>
-      <c r="L123" s="21"/>
-      <c r="M123" s="21"/>
-      <c r="N123" s="22"/>
-      <c r="O123" s="20"/>
-      <c r="P123" s="20"/>
-      <c r="Q123" s="21"/>
-      <c r="R123" s="21"/>
-      <c r="S123" s="20"/>
-      <c r="T123" s="20"/>
-      <c r="U123" s="20"/>
-      <c r="V123" s="20"/>
-      <c r="W123" s="20"/>
-      <c r="X123" s="20"/>
-      <c r="Y123" s="20"/>
-      <c r="Z123" s="20"/>
-      <c r="AA123" s="20"/>
-      <c r="AB123" s="20"/>
-      <c r="AC123" s="20"/>
-      <c r="AD123" s="20"/>
-      <c r="AE123" s="20"/>
-      <c r="AF123" s="20"/>
-      <c r="AG123" s="20"/>
-      <c r="AH123" s="21"/>
-    </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="20"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="21"/>
-      <c r="H124" s="21"/>
-      <c r="I124" s="20"/>
-      <c r="J124" s="20"/>
-      <c r="K124" s="20"/>
-      <c r="L124" s="21"/>
-      <c r="M124" s="21"/>
-      <c r="N124" s="22"/>
-      <c r="O124" s="20"/>
-      <c r="P124" s="20"/>
-      <c r="Q124" s="21"/>
-      <c r="R124" s="21"/>
-      <c r="S124" s="20"/>
-      <c r="T124" s="20"/>
-      <c r="U124" s="20"/>
-      <c r="V124" s="20"/>
-      <c r="W124" s="20"/>
-      <c r="X124" s="20"/>
-      <c r="Y124" s="20"/>
-      <c r="Z124" s="20"/>
-      <c r="AA124" s="20"/>
-      <c r="AB124" s="20"/>
-      <c r="AC124" s="20"/>
-      <c r="AD124" s="20"/>
-      <c r="AE124" s="20"/>
-      <c r="AF124" s="20"/>
-      <c r="AG124" s="20"/>
-      <c r="AH124" s="21"/>
+    <row r="123" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="D123" s="10"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="8">
+        <v>1</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="I123" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J123" s="9"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="10"/>
+      <c r="O123" s="11"/>
+      <c r="P123" s="8"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="8"/>
+      <c r="S123" s="10"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="8"/>
+      <c r="V123" s="8"/>
+      <c r="W123" s="8"/>
+      <c r="X123" s="8"/>
+      <c r="Y123" s="8"/>
+      <c r="Z123" s="8">
+        <f t="shared" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="AA123" s="8">
+        <f t="shared" si="19"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AB123" s="8">
+        <f t="shared" si="20"/>
+        <v>26</v>
+      </c>
+      <c r="AC123" s="8">
+        <f t="shared" si="21"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AD123" s="8">
+        <f t="shared" si="22"/>
+        <v>17.5</v>
+      </c>
+      <c r="AE123" s="8">
+        <f t="shared" si="23"/>
+        <v>24.6</v>
+      </c>
+      <c r="AF123" s="8">
+        <f t="shared" si="24"/>
+        <v>21.6</v>
+      </c>
+      <c r="AG123" s="8">
+        <f t="shared" si="25"/>
+        <v>20.5</v>
+      </c>
+      <c r="AH123" s="10">
+        <f t="shared" si="26"/>
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+      <c r="B124" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E124" s="9"/>
+      <c r="F124" s="8">
+        <v>1</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="I124" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="J124" s="9"/>
+      <c r="K124" s="8">
+        <v>5</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M124" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="N124" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="O124" s="11"/>
+      <c r="P124" s="8"/>
+      <c r="Q124" s="8"/>
+      <c r="R124" s="8"/>
+      <c r="S124" s="10"/>
+      <c r="T124" s="9"/>
+      <c r="U124" s="8"/>
+      <c r="V124" s="8"/>
+      <c r="W124" s="8"/>
+      <c r="X124" s="8"/>
+      <c r="Y124" s="8"/>
+      <c r="Z124" s="8">
+        <f t="shared" ref="Z124" si="36">AB124+Y$2</f>
+        <v>20</v>
+      </c>
+      <c r="AA124" s="8">
+        <f t="shared" ref="AA124" si="37">Z124+X$2</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AB124" s="8">
+        <f t="shared" ref="AB124" si="38">U$2+V$2*(F124-1)</f>
+        <v>26</v>
+      </c>
+      <c r="AC124" s="8">
+        <f t="shared" ref="AC124" si="39">AE124+Y$2</f>
+        <v>40.6</v>
+      </c>
+      <c r="AD124" s="8">
+        <f t="shared" ref="AD124" si="40">AC124+X$2</f>
+        <v>39.5</v>
+      </c>
+      <c r="AE124" s="8">
+        <f t="shared" ref="AE124" si="41">U$2+V$2*(K124-1)+W$2</f>
+        <v>46.6</v>
+      </c>
+      <c r="AF124" s="8">
+        <f t="shared" ref="AF124" si="42">AH124+Y$2</f>
+        <v>21.6</v>
+      </c>
+      <c r="AG124" s="8">
+        <f t="shared" ref="AG124" si="43">AF124+X$2</f>
+        <v>20.5</v>
+      </c>
+      <c r="AH124" s="10">
+        <f t="shared" ref="AH124" si="44">U$2+V$2*(P124-1)+2*W$2</f>
+        <v>27.6</v>
+      </c>
     </row>
     <row r="125" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B125" s="20"/>
@@ -15194,10 +15302,45 @@
       <c r="AG197" s="20"/>
       <c r="AH197" s="21"/>
     </row>
+    <row r="198" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B198" s="20"/>
+      <c r="C198" s="20"/>
+      <c r="D198" s="20"/>
+      <c r="E198" s="20"/>
+      <c r="F198" s="20"/>
+      <c r="G198" s="21"/>
+      <c r="H198" s="21"/>
+      <c r="I198" s="20"/>
+      <c r="J198" s="20"/>
+      <c r="K198" s="20"/>
+      <c r="L198" s="21"/>
+      <c r="M198" s="21"/>
+      <c r="N198" s="22"/>
+      <c r="O198" s="20"/>
+      <c r="P198" s="20"/>
+      <c r="Q198" s="21"/>
+      <c r="R198" s="21"/>
+      <c r="S198" s="20"/>
+      <c r="T198" s="20"/>
+      <c r="U198" s="20"/>
+      <c r="V198" s="20"/>
+      <c r="W198" s="20"/>
+      <c r="X198" s="20"/>
+      <c r="Y198" s="20"/>
+      <c r="Z198" s="20"/>
+      <c r="AA198" s="20"/>
+      <c r="AB198" s="20"/>
+      <c r="AC198" s="20"/>
+      <c r="AD198" s="20"/>
+      <c r="AE198" s="20"/>
+      <c r="AF198" s="20"/>
+      <c r="AG198" s="20"/>
+      <c r="AH198" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH138" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH138">
-      <sortCondition ref="C1:C138"/>
+  <autoFilter ref="A1:AH139" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH139">
+      <sortCondition ref="C1:C139"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B1:AH1 C2:C94">
@@ -15217,21 +15360,21 @@
       <formula>NOT(ISERROR(SEARCH("Spell",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C123:C197">
+  <conditionalFormatting sqref="C125:C198">
     <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Accessory">
-      <formula>NOT(ISERROR(SEARCH("Accessory",C123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Accessory",C125)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Armour">
-      <formula>NOT(ISERROR(SEARCH("Armour",C123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Armour",C125)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Equipment">
-      <formula>NOT(ISERROR(SEARCH("Equipment",C123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Equipment",C125)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Impression">
-      <formula>NOT(ISERROR(SEARCH("Impression",C123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Impression",C125)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="Spell">
-      <formula>NOT(ISERROR(SEARCH("Spell",C123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Spell",C125)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kagen\OneDrive\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381C4C9F-CB23-41AE-A0D0-36151F81A6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC32A-1366-4275-9155-350ABBB028DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -2167,7 +2167,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Pūnoa" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2427,33 +2427,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI201"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="1.42578125" customWidth="1"/>
-    <col min="7" max="7" width="4.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="6" max="6" width="1.44140625" customWidth="1"/>
+    <col min="7" max="7" width="4.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" customWidth="1"/>
     <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="42.42578125" customWidth="1"/>
-    <col min="11" max="11" width="1.42578125" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" customWidth="1"/>
-    <col min="14" max="14" width="31.7109375" customWidth="1"/>
-    <col min="15" max="15" width="37.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="1.42578125" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" customWidth="1"/>
-    <col min="19" max="19" width="25.5703125" customWidth="1"/>
-    <col min="20" max="20" width="35.140625" customWidth="1"/>
-    <col min="21" max="21" width="1.42578125" customWidth="1"/>
+    <col min="10" max="10" width="42.44140625" customWidth="1"/>
+    <col min="11" max="11" width="1.44140625" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" customWidth="1"/>
+    <col min="14" max="14" width="31.6640625" customWidth="1"/>
+    <col min="15" max="15" width="37.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="1.44140625" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" customWidth="1"/>
+    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="19" max="19" width="25.5546875" customWidth="1"/>
+    <col min="20" max="20" width="35.109375" customWidth="1"/>
+    <col min="21" max="21" width="1.44140625" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="26" max="33" width="10.5703125" customWidth="1"/>
+    <col min="26" max="33" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="120" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="135" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="90" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="90" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -7149,7 +7149,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1</v>
       </c>
@@ -7397,7 +7397,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1</v>
       </c>
@@ -7829,7 +7829,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1</v>
       </c>
@@ -8669,7 +8669,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1</v>
       </c>
@@ -10559,7 +10559,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1</v>
       </c>
@@ -10823,7 +10823,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1</v>
       </c>
@@ -11053,11 +11053,11 @@
       <c r="Y98" s="8"/>
       <c r="Z98" s="8"/>
       <c r="AA98" s="8">
-        <f t="shared" ref="AA98:AA129" si="27">AC98+Z$2</f>
+        <f t="shared" ref="AA98:AA127" si="27">AC98+Z$2</f>
         <v>20</v>
       </c>
       <c r="AB98" s="8">
-        <f t="shared" ref="AB98:AB129" si="28">AA98+Y$2</f>
+        <f t="shared" ref="AB98:AB127" si="28">AA98+Y$2</f>
         <v>18.899999999999999</v>
       </c>
       <c r="AC98" s="8">
@@ -11069,7 +11069,7 @@
         <v>36.200000000000003</v>
       </c>
       <c r="AE98" s="8">
-        <f t="shared" ref="AE98:AE129" si="31">AD98+Y$2</f>
+        <f t="shared" ref="AE98:AE127" si="31">AD98+Y$2</f>
         <v>35.1</v>
       </c>
       <c r="AF98" s="8">
@@ -11081,7 +11081,7 @@
         <v>21.6</v>
       </c>
       <c r="AH98" s="8">
-        <f t="shared" ref="AH98:AH129" si="34">AG98+Y$2</f>
+        <f t="shared" ref="AH98:AH127" si="34">AG98+Y$2</f>
         <v>20.5</v>
       </c>
       <c r="AI98" s="10">
@@ -11089,7 +11089,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1</v>
       </c>
@@ -11963,7 +11963,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>1</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>1</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>1</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>1</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1</v>
       </c>
@@ -12577,7 +12577,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1</v>
       </c>
@@ -12665,7 +12665,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1</v>
       </c>
@@ -12753,7 +12753,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>1</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="72" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>1</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>1</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>1</v>
       </c>
@@ -13273,7 +13273,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>1</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>1</v>
       </c>
@@ -13459,7 +13459,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>1</v>
       </c>
@@ -13547,7 +13547,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>1</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>1</v>
       </c>
@@ -13715,40 +13715,40 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="129" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O129"/>
     </row>
-    <row r="130" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O130"/>
     </row>
-    <row r="131" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O131"/>
     </row>
-    <row r="132" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O132"/>
     </row>
-    <row r="133" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O133"/>
     </row>
-    <row r="134" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O134"/>
     </row>
-    <row r="135" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O135"/>
     </row>
-    <row r="136" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O136"/>
     </row>
-    <row r="137" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O137"/>
     </row>
-    <row r="138" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O138"/>
     </row>
-    <row r="139" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O139"/>
     </row>
-    <row r="140" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
       <c r="D140" s="22"/>
@@ -13784,7 +13784,7 @@
       <c r="AH140" s="22"/>
       <c r="AI140" s="23"/>
     </row>
-    <row r="141" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
       <c r="D141" s="22"/>
@@ -13820,7 +13820,7 @@
       <c r="AH141" s="22"/>
       <c r="AI141" s="23"/>
     </row>
-    <row r="142" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
       <c r="D142" s="22"/>
@@ -13856,7 +13856,7 @@
       <c r="AH142" s="22"/>
       <c r="AI142" s="23"/>
     </row>
-    <row r="143" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
       <c r="D143" s="22"/>
@@ -13892,7 +13892,7 @@
       <c r="AH143" s="22"/>
       <c r="AI143" s="23"/>
     </row>
-    <row r="144" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
       <c r="D144" s="22"/>
@@ -13928,7 +13928,7 @@
       <c r="AH144" s="22"/>
       <c r="AI144" s="23"/>
     </row>
-    <row r="145" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
       <c r="D145" s="22"/>
@@ -13964,7 +13964,7 @@
       <c r="AH145" s="22"/>
       <c r="AI145" s="23"/>
     </row>
-    <row r="146" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
       <c r="D146" s="22"/>
@@ -14000,7 +14000,7 @@
       <c r="AH146" s="22"/>
       <c r="AI146" s="23"/>
     </row>
-    <row r="147" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
       <c r="D147" s="22"/>
@@ -14036,7 +14036,7 @@
       <c r="AH147" s="22"/>
       <c r="AI147" s="23"/>
     </row>
-    <row r="148" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
       <c r="D148" s="22"/>
@@ -14072,7 +14072,7 @@
       <c r="AH148" s="22"/>
       <c r="AI148" s="23"/>
     </row>
-    <row r="149" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
       <c r="D149" s="22"/>
@@ -14108,7 +14108,7 @@
       <c r="AH149" s="22"/>
       <c r="AI149" s="23"/>
     </row>
-    <row r="150" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
       <c r="D150" s="22"/>
@@ -14144,7 +14144,7 @@
       <c r="AH150" s="22"/>
       <c r="AI150" s="23"/>
     </row>
-    <row r="151" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
       <c r="D151" s="22"/>
@@ -14180,7 +14180,7 @@
       <c r="AH151" s="22"/>
       <c r="AI151" s="23"/>
     </row>
-    <row r="152" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
       <c r="D152" s="22"/>
@@ -14216,7 +14216,7 @@
       <c r="AH152" s="22"/>
       <c r="AI152" s="23"/>
     </row>
-    <row r="153" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
       <c r="D153" s="22"/>
@@ -14252,7 +14252,7 @@
       <c r="AH153" s="22"/>
       <c r="AI153" s="23"/>
     </row>
-    <row r="154" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
       <c r="D154" s="22"/>
@@ -14288,7 +14288,7 @@
       <c r="AH154" s="22"/>
       <c r="AI154" s="23"/>
     </row>
-    <row r="155" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
       <c r="D155" s="22"/>
@@ -14324,7 +14324,7 @@
       <c r="AH155" s="22"/>
       <c r="AI155" s="23"/>
     </row>
-    <row r="156" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
       <c r="D156" s="22"/>
@@ -14360,7 +14360,7 @@
       <c r="AH156" s="22"/>
       <c r="AI156" s="23"/>
     </row>
-    <row r="157" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B157" s="22"/>
       <c r="C157" s="22"/>
       <c r="D157" s="22"/>
@@ -14396,7 +14396,7 @@
       <c r="AH157" s="22"/>
       <c r="AI157" s="23"/>
     </row>
-    <row r="158" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B158" s="22"/>
       <c r="C158" s="22"/>
       <c r="D158" s="22"/>
@@ -14432,7 +14432,7 @@
       <c r="AH158" s="22"/>
       <c r="AI158" s="23"/>
     </row>
-    <row r="159" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B159" s="22"/>
       <c r="C159" s="22"/>
       <c r="D159" s="22"/>
@@ -14468,7 +14468,7 @@
       <c r="AH159" s="22"/>
       <c r="AI159" s="23"/>
     </row>
-    <row r="160" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
       <c r="D160" s="22"/>
@@ -14504,7 +14504,7 @@
       <c r="AH160" s="22"/>
       <c r="AI160" s="23"/>
     </row>
-    <row r="161" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
       <c r="D161" s="22"/>
@@ -14540,7 +14540,7 @@
       <c r="AH161" s="22"/>
       <c r="AI161" s="23"/>
     </row>
-    <row r="162" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B162" s="22"/>
       <c r="C162" s="22"/>
       <c r="D162" s="22"/>
@@ -14576,7 +14576,7 @@
       <c r="AH162" s="22"/>
       <c r="AI162" s="23"/>
     </row>
-    <row r="163" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B163" s="22"/>
       <c r="C163" s="22"/>
       <c r="D163" s="22"/>
@@ -14612,7 +14612,7 @@
       <c r="AH163" s="22"/>
       <c r="AI163" s="23"/>
     </row>
-    <row r="164" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
       <c r="D164" s="22"/>
@@ -14648,7 +14648,7 @@
       <c r="AH164" s="22"/>
       <c r="AI164" s="23"/>
     </row>
-    <row r="165" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B165" s="22"/>
       <c r="C165" s="22"/>
       <c r="D165" s="22"/>
@@ -14684,7 +14684,7 @@
       <c r="AH165" s="22"/>
       <c r="AI165" s="23"/>
     </row>
-    <row r="166" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B166" s="22"/>
       <c r="C166" s="22"/>
       <c r="D166" s="22"/>
@@ -14720,7 +14720,7 @@
       <c r="AH166" s="22"/>
       <c r="AI166" s="23"/>
     </row>
-    <row r="167" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B167" s="22"/>
       <c r="C167" s="22"/>
       <c r="D167" s="22"/>
@@ -14756,7 +14756,7 @@
       <c r="AH167" s="22"/>
       <c r="AI167" s="23"/>
     </row>
-    <row r="168" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
       <c r="D168" s="22"/>
@@ -14792,7 +14792,7 @@
       <c r="AH168" s="22"/>
       <c r="AI168" s="23"/>
     </row>
-    <row r="169" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
       <c r="D169" s="22"/>
@@ -14828,7 +14828,7 @@
       <c r="AH169" s="22"/>
       <c r="AI169" s="23"/>
     </row>
-    <row r="170" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B170" s="22"/>
       <c r="C170" s="22"/>
       <c r="D170" s="22"/>
@@ -14864,7 +14864,7 @@
       <c r="AH170" s="22"/>
       <c r="AI170" s="23"/>
     </row>
-    <row r="171" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B171" s="22"/>
       <c r="C171" s="22"/>
       <c r="D171" s="22"/>
@@ -14900,7 +14900,7 @@
       <c r="AH171" s="22"/>
       <c r="AI171" s="23"/>
     </row>
-    <row r="172" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B172" s="22"/>
       <c r="C172" s="22"/>
       <c r="D172" s="22"/>
@@ -14936,7 +14936,7 @@
       <c r="AH172" s="22"/>
       <c r="AI172" s="23"/>
     </row>
-    <row r="173" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B173" s="22"/>
       <c r="C173" s="22"/>
       <c r="D173" s="22"/>
@@ -14972,7 +14972,7 @@
       <c r="AH173" s="22"/>
       <c r="AI173" s="23"/>
     </row>
-    <row r="174" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B174" s="22"/>
       <c r="C174" s="22"/>
       <c r="D174" s="22"/>
@@ -15008,7 +15008,7 @@
       <c r="AH174" s="22"/>
       <c r="AI174" s="23"/>
     </row>
-    <row r="175" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B175" s="22"/>
       <c r="C175" s="22"/>
       <c r="D175" s="22"/>
@@ -15044,7 +15044,7 @@
       <c r="AH175" s="22"/>
       <c r="AI175" s="23"/>
     </row>
-    <row r="176" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B176" s="22"/>
       <c r="C176" s="22"/>
       <c r="D176" s="22"/>
@@ -15080,7 +15080,7 @@
       <c r="AH176" s="22"/>
       <c r="AI176" s="23"/>
     </row>
-    <row r="177" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
       <c r="D177" s="22"/>
@@ -15116,7 +15116,7 @@
       <c r="AH177" s="22"/>
       <c r="AI177" s="23"/>
     </row>
-    <row r="178" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B178" s="22"/>
       <c r="C178" s="22"/>
       <c r="D178" s="22"/>
@@ -15152,7 +15152,7 @@
       <c r="AH178" s="22"/>
       <c r="AI178" s="23"/>
     </row>
-    <row r="179" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
       <c r="D179" s="22"/>
@@ -15188,7 +15188,7 @@
       <c r="AH179" s="22"/>
       <c r="AI179" s="23"/>
     </row>
-    <row r="180" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
       <c r="D180" s="22"/>
@@ -15224,7 +15224,7 @@
       <c r="AH180" s="22"/>
       <c r="AI180" s="23"/>
     </row>
-    <row r="181" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>
       <c r="D181" s="22"/>
@@ -15260,7 +15260,7 @@
       <c r="AH181" s="22"/>
       <c r="AI181" s="23"/>
     </row>
-    <row r="182" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B182" s="22"/>
       <c r="C182" s="22"/>
       <c r="D182" s="22"/>
@@ -15296,7 +15296,7 @@
       <c r="AH182" s="22"/>
       <c r="AI182" s="23"/>
     </row>
-    <row r="183" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B183" s="22"/>
       <c r="C183" s="22"/>
       <c r="D183" s="22"/>
@@ -15332,7 +15332,7 @@
       <c r="AH183" s="22"/>
       <c r="AI183" s="23"/>
     </row>
-    <row r="184" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B184" s="22"/>
       <c r="C184" s="22"/>
       <c r="D184" s="22"/>
@@ -15368,7 +15368,7 @@
       <c r="AH184" s="22"/>
       <c r="AI184" s="23"/>
     </row>
-    <row r="185" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
       <c r="D185" s="22"/>
@@ -15404,7 +15404,7 @@
       <c r="AH185" s="22"/>
       <c r="AI185" s="23"/>
     </row>
-    <row r="186" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B186" s="22"/>
       <c r="C186" s="22"/>
       <c r="D186" s="22"/>
@@ -15440,7 +15440,7 @@
       <c r="AH186" s="22"/>
       <c r="AI186" s="23"/>
     </row>
-    <row r="187" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B187" s="22"/>
       <c r="C187" s="22"/>
       <c r="D187" s="22"/>
@@ -15476,7 +15476,7 @@
       <c r="AH187" s="22"/>
       <c r="AI187" s="23"/>
     </row>
-    <row r="188" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B188" s="22"/>
       <c r="C188" s="22"/>
       <c r="D188" s="22"/>
@@ -15512,7 +15512,7 @@
       <c r="AH188" s="22"/>
       <c r="AI188" s="23"/>
     </row>
-    <row r="189" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B189" s="22"/>
       <c r="C189" s="22"/>
       <c r="D189" s="22"/>
@@ -15548,7 +15548,7 @@
       <c r="AH189" s="22"/>
       <c r="AI189" s="23"/>
     </row>
-    <row r="190" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B190" s="22"/>
       <c r="C190" s="22"/>
       <c r="D190" s="22"/>
@@ -15584,7 +15584,7 @@
       <c r="AH190" s="22"/>
       <c r="AI190" s="23"/>
     </row>
-    <row r="191" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B191" s="22"/>
       <c r="C191" s="22"/>
       <c r="D191" s="22"/>
@@ -15620,7 +15620,7 @@
       <c r="AH191" s="22"/>
       <c r="AI191" s="23"/>
     </row>
-    <row r="192" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B192" s="22"/>
       <c r="C192" s="22"/>
       <c r="D192" s="22"/>
@@ -15656,7 +15656,7 @@
       <c r="AH192" s="22"/>
       <c r="AI192" s="23"/>
     </row>
-    <row r="193" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
       <c r="D193" s="22"/>
@@ -15692,7 +15692,7 @@
       <c r="AH193" s="22"/>
       <c r="AI193" s="23"/>
     </row>
-    <row r="194" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B194" s="22"/>
       <c r="C194" s="22"/>
       <c r="D194" s="22"/>
@@ -15728,7 +15728,7 @@
       <c r="AH194" s="22"/>
       <c r="AI194" s="23"/>
     </row>
-    <row r="195" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B195" s="22"/>
       <c r="C195" s="22"/>
       <c r="D195" s="22"/>
@@ -15764,7 +15764,7 @@
       <c r="AH195" s="22"/>
       <c r="AI195" s="23"/>
     </row>
-    <row r="196" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B196" s="22"/>
       <c r="C196" s="22"/>
       <c r="D196" s="22"/>
@@ -15800,7 +15800,7 @@
       <c r="AH196" s="22"/>
       <c r="AI196" s="23"/>
     </row>
-    <row r="197" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B197" s="22"/>
       <c r="C197" s="22"/>
       <c r="D197" s="22"/>
@@ -15836,7 +15836,7 @@
       <c r="AH197" s="22"/>
       <c r="AI197" s="23"/>
     </row>
-    <row r="198" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B198" s="22"/>
       <c r="C198" s="22"/>
       <c r="D198" s="22"/>
@@ -15872,13 +15872,13 @@
       <c r="AH198" s="22"/>
       <c r="AI198" s="23"/>
     </row>
-    <row r="199" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C199" s="22"/>
     </row>
-    <row r="200" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C200" s="22"/>
     </row>
-    <row r="201" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C201" s="22"/>
     </row>
   </sheetData>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kagen\OneDrive\Documents\GitHub\Sculpt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC32A-1366-4275-9155-350ABBB028DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CF2448-889F-46BC-B364-C42537A02ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="616">
   <si>
     <t>Change state</t>
   </si>
@@ -160,24 +160,15 @@
     <t>Passive</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Clear Mind&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the start of your turn, flip an impression face up</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Thief of thought&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Turn one of your impressions face down to inflict the &lt;b&gt;Stunned&lt;/b&gt; status on a target.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Abandon Soul&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>If you have no impressions face up at the end of your turn, refresh a stat token and gain &lt;b&gt;Monstrous&lt;b&gt;.</t>
   </si>
   <si>
@@ -185,22 +176,13 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Reckless&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>&lt;b&gt;Increase damage taken by 1.&lt;/b&gt;
 &lt;br /&gt;+1 Movement Speed.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Relentless&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>If you are &lt;b&gt;Monstrous&lt;/b&gt;, gain 1 extra AP at the start of your turn.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Victorious&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Your attacks have the Crit option:
@@ -213,13 +195,7 @@
     <t>Shape = Hex2wide</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Many Legs&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>+1 Movement Speed.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Sideways Scuttle&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Declare a permanent front hex and back hex for your character token. 
@@ -227,9 +203,6 @@
 &lt;br /&gt;You move with your front hex. When you stop moving, place your back hex in any adjacent hex.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Cracked Shell&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Reduce all damage to your back hex by 3.</t>
   </si>
   <si>
@@ -248,9 +221,6 @@
     <t>Make a 2 tile wall Hex2wide of Crystal. It can not be climbed and is &lt;b&gt;destructible.&lt;/b&gt; Then gain up to two tempct.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Budding Growth&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the start of combat, add an extra charge to all your limbs with charges</t>
   </si>
   <si>
@@ -260,15 +230,9 @@
     <t>Fungal</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Pulpy&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Increase your maximum composure by 1.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Toxic&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you would deal damage, you may instead set that beings composure to 1.</t>
   </si>
   <si>
@@ -281,28 +245,16 @@
     <t>Shape = Hex1b</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Behemoth&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You can't be be forced to move against your will.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Massive Limbs&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Attacks that cost more than 2 AP cost 1 less and have &lt;b&gt;Reach&lt;/b&gt;.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Hefty&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>After emergence, gain +1 Heft.</t>
   </si>
   <si>
     <t>Glowing Kintsugi</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Warm Glow&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>At the start of your turn, gain 
@@ -321,9 +273,6 @@
     <t>Hag</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Symptom Sower: 2 AP + weirdt&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Inflict any status other than &lt;b&gt;cursed&lt;/b&gt; effect on target being.</t>
   </si>
   <si>
@@ -333,36 +282,21 @@
     <t>Suffer a wound to a stat of your choice and inflict the &lt;b&gt;cursed&lt;/b&gt; status on an adjacent target.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Rake Essence&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Your attacks against cursed targets have the crit option &lt;b&gt;Siphon:&lt;/b&gt;&lt;br/&gt;Restore a weirdt, choose only once per attack.</t>
   </si>
   <si>
     <t>Hollow</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Odd structure&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Your composure is equal to &lt;b&gt;twice&lt;/b&gt; your &lt;span style="color:#3366cc"&gt;&lt;strong&gt;Weird&lt;/strong&gt;&lt;/span&gt;.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Fragile&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>If you take a wound during combat, you &lt;b&gt;die.&lt;/b&gt;</t>
   </si>
   <si>
     <t>Human</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Two Legs&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Two Arms&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Terrain interactions cost 1 less AP.</t>
   </si>
   <si>
@@ -373,27 +307,18 @@
   </si>
   <si>
     <t>Hungry Clay</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Consuming&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Your attacks have the Crit option:
 &lt;br /&gt;&lt;b&gt;Absorb:&lt;/b&gt; Heal a wound of the same stat you wounded.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Regenerative&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>When you take a wound, replenish a spent token of the same stat.</t>
   </si>
   <si>
     <t>Insectile</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Exoskeleton&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you take a move action, gain a charget.&lt;/br&gt;Maximum of 4 charges.</t>
   </si>
   <si>
@@ -406,21 +331,12 @@
     <t>Lanky</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Long Limbed&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You have +1 range on all melee attacks and terrain interactions.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Sweeper&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Your melee attacks target all possible targets in range, roll once for the attack.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Butter Cutter&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>When you hit two or more creatures with a single attack, replenish a multtok.</t>
   </si>
   <si>
@@ -440,9 +356,6 @@
   </si>
   <si>
     <t>Teleport to any hex inside a starting zone.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Recharge&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Your attacks have the Crit option:
@@ -452,15 +365,9 @@
     <t>Mechanical</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Modal&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>At the start of your turn, put a counter on an empty mode, then gain up to tempcttempct and use that effect.</t>
   </si>
   <si>
-    <t>&lt;i&gt;&lt;b&gt;Modes&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Flight Mode: Gain +2 move speed and ignore terrain effects this turn.&lt;/br&gt;Destruction Mode: All attacks deal 2 extra damage this turn.&lt;/br&gt;Charge Mode: Refresh a multtok or charget.&lt;/br&gt;Overdrive: Remove all counters from this and gain up to two tempct for each removed.</t>
   </si>
   <si>
@@ -470,30 +377,18 @@
     <t>hex1big   hex1big   hex1big</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Very Fast&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>+2 Movement Speed.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Multitudinous&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You have 3 bodies, each 1 hex1a in size. You may distribute movement between them when moving. All bodies attack when you make a melee attack.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Shared Mind&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Damage taken by any of your bodies is taken in full. </t>
   </si>
   <si>
     <t>Ooze</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Easy as Walking&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Climbing does not cost you jazzT.</t>
   </si>
   <si>
@@ -503,9 +398,6 @@
     <t>When you next take the move action, you leave a trail of goo in all hexes moved out of. Moving through this goo takes 2 hexes of movement per hex.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Moving is Optional&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the end of your turn, if you did not move, gain up to 4 tempct.</t>
   </si>
   <si>
@@ -527,18 +419,12 @@
     <t>Target creature moves one tile under your control.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Consume&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you land a killing blow (including death by command), restore all wounds to one stat of your choice.</t>
   </si>
   <si>
     <t>Phantom</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Ghostly&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend a weirdT, for your next move that turn you may pass through solid objects freely and ignore terrain penalties. You may not stop inside terrain.</t>
   </si>
   <si>
@@ -551,15 +437,9 @@
     <t>Serpentine</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Just a Tail&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>While you have at most 1 limb equipped, you refresh 1 WeirdT at the start of each of your turns.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Fast&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Your move speed is increased by 1.</t>
   </si>
   <si>
@@ -579,40 +459,25 @@
   </si>
   <si>
     <t>Stone Plated</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Stone Flesh&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Reduce damage taken by 1.
 &lt;br /&gt;-2 Movement Speed.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Impervious Plates&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Reduce damage from non-adjacent beings to 0.</t>
   </si>
   <si>
     <t>Unstable</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Radioactive&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdt, adjacent beings take 2 damage.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;&lt;i&gt;Decay&lt;/b&gt;&lt;/i&gt; </t>
-  </si>
-  <si>
     <t>At the end of each of your turns, take 2 damage and refresh 1 weirdT.</t>
   </si>
   <si>
     <t>Volcanic</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Furnace&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Reduce damage taken by 1.
@@ -632,9 +497,6 @@
     <t>chargebigx 5</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Writhe and Revel&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the start of your turn, gain 1 temporary composure for each infected being, including you.</t>
   </si>
   <si>
@@ -653,30 +515,18 @@
     <t>Wreathed in Flame</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Enflamed&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Fire&lt;/b&gt; and &lt;b&gt;Burning&lt;/b&gt; give you temporary composure instead of dealing damage.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Flame Geysers&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the start of each turn, gain the &lt;b&gt;Burning&lt;/b&gt; status effect.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Through Fire&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Your attacks have the Crit option &lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
   </si>
   <si>
     <t>Writhing Mass</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Generative&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>At the start of your turn, if you have less than 4 limbs equipped, draw and equip a limb.</t>
   </si>
   <si>
@@ -701,25 +551,16 @@
     <t>Ambidextrous</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Creative Duellist&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You may use Crit options available to any of your limbs on all attacks.</t>
   </si>
   <si>
     <t>Assertive</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Charger&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>When you make an attack, you may move 2 tiles before attacking.</t>
   </si>
   <si>
     <t>Balanced</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Passive&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>At the start of your turn, if you have an equal number of unspent tokens in each stat, refresh multtokmulttok.
@@ -758,13 +599,7 @@
     <t>Dancer</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt; Flow State&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Your attacks have the Crit Option &lt;br /&gt;&lt;b&gt;Dash:&lt;/b&gt; Take a move action.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;On the Move&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>Whenever you gain temporary composure, you may move that many hexes.</t>
@@ -813,9 +648,6 @@
 &lt;br /&gt;&lt;br /&gt;Pillars can be climbed by spending 3 AP or jazzT. Beings take 8 damage if they fall off.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;World Sculptor&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdt, create a small pillar Hex1a in target empty hex.</t>
   </si>
   <si>
@@ -835,9 +667,6 @@
     <t>I'm Normal</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Normality&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Replace your  &lt;span style="color:#3366cc"&gt;&lt;strong&gt;Weird&lt;/strong&gt;&lt;/span&gt; with &lt;span style="color:#d964d4"&gt;&lt;strong&gt;Normal&lt;/strong&gt;&lt;/span&gt;. You cannot spend weirdt any more.</t>
   </si>
   <si>
@@ -856,15 +685,9 @@
     <t>Kind</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Sharing&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Whenever you gain a status effect, you may also grant it to a willing target.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Giving&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend a weirdt, restore 2 of another targets compure</t>
   </si>
   <si>
@@ -881,18 +704,12 @@
   </si>
   <si>
     <t>Loot Goblin</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Magic Touch&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Your attacks have the Crit option
 &lt;br /&gt;&lt;b&gt;Imbue:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Treasure!&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>During map creation, search the boons deck for any card. You may place this on the map in addition to your allotted terrain cards.</t>
   </si>
   <si>
@@ -903,9 +720,6 @@
   </si>
   <si>
     <t>Malevolent</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Twisted Kindness&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>Whenever you would give another creature temporary composure, you may deal that much damage instead.</t>
@@ -964,9 +778,6 @@
     <t>Mark a target, your attacks against marked target deal +1 damage.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Vulgarity&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend a weirdt, all marked targets lose 1 composure, down to a minimum of 1.</t>
   </si>
   <si>
@@ -979,9 +790,6 @@
     <t>Patient</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Inhale&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the end of your turn, for each unspent action point add charget to this card, up to max of your &lt;span style="color: #1563da;"&gt;Weird&lt;/span&gt;.</t>
   </si>
   <si>
@@ -1000,16 +808,10 @@
     <t>You and up to 1 adjacent being restore 1 wound.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Aura of Earth&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdt, target being gains up to 2 temporary composure.</t>
   </si>
   <si>
     <t>Relentless</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Relish in battle&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>Whenever you Critically hit, restore 2 composure or gain up to 2 temporary composure.</t>
@@ -1037,9 +839,6 @@
 &lt;br /&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only Crit on a 12.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Creature of the Shadows&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You are unnaffected by darkness</t>
   </si>
   <si>
@@ -1074,9 +873,6 @@
   </si>
   <si>
     <t>Your next melee attack this turn has range equal to your &lt;span style="color:#27ae60"&gt;&lt;b&gt;Jazz&lt;/b&gt;&lt;/span&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Pressure Points&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>Your attacks have the Crit option
@@ -1098,9 +894,6 @@
     <t>Wreath target limb in shards, placing a counter on it. The next time this limb hits with an attack, that attack deals +2 damage and remove a counter.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Enchanting&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend Weirdt, wreath one of your own limbs.</t>
   </si>
   <si>
@@ -1111,9 +904,6 @@
   </si>
   <si>
     <t>When you see a being take damage from a source other than you, you may increase that damage by 2. This does not stack.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Minion&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>The boss does not consider you a target unless you are the last alive or you have dealt damage to it.</t>
@@ -1214,9 +1004,6 @@
     <t>A target gains up to 4 tempct and the &lt;b&gt;Entangled&lt;/b&gt; status.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Spreading Clay&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdt, gain up to tempcttempct.</t>
   </si>
   <si>
@@ -1227,9 +1014,6 @@
   </si>
   <si>
     <t>Damage = 4, Close</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Autonomous Limb&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>At the end of your turn, this limb uses &lt;b&gt;Flail&lt;/b&gt; for free, it will target you if there are no other targets available.</t>
@@ -1255,9 +1039,6 @@
 </t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Sparks&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdt, deal 1 &lt;b&gt;true damage&lt;/b&gt; to any target. This damage cannot be reduced.</t>
   </si>
   <si>
@@ -1268,9 +1049,6 @@
   </si>
   <si>
     <t>Place a 1 hex crystal on an adjacent hex. The crystal breaks if it takes damage.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Radiance&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>At the end of your turn, if there is at least one crystal on the map, choose one of the following status effects to gain:
@@ -1331,9 +1109,6 @@
     <t>Damage = 2, Reach</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Flame Devourer&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Has the &lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage crit option against targets that are already &lt;b&gt;Burning&lt;/b&gt;.</t>
   </si>
   <si>
@@ -1365,24 +1140,15 @@
     <t>Remove all temporary composure from a target.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Surprising thwack: jazzTjazzTjazzT</t>
-  </si>
-  <si>
     <t>Damage = 4, Close.</t>
   </si>
   <si>
     <t>Feet</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Sure Footed&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>You have + 1 speed and effects from terrain or abilities cannot reduce your speed.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Fleet&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>While you have the &lt;b&gt;Well Rested&lt;/b&gt; status effect, gain an additional +1 speed.</t>
   </si>
   <si>
@@ -1398,15 +1164,9 @@
     <t>Create a 1 hex cloud at target empty hex.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Growing Cloud&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>At the start of your turn, each cloud grows by one hex in all directions.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Toxic&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend weirdT, all beings inside a cloud take 4 damage. This damage cannot be reduced.</t>
   </si>
   <si>
@@ -1426,9 +1186,6 @@
   </si>
   <si>
     <t>Recharge this item.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Ungrown&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>This limb starts with no charges.</t>
@@ -1554,9 +1311,6 @@
     <t>&lt;b&gt;Headbutt:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Release&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>When you hit with this limb, you may spend flesht as though it were weirdt until the end of your turn.</t>
   </si>
   <si>
@@ -1570,9 +1324,6 @@
 &lt;br /&gt;This attack always hits, do not roll.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Snack&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you inflict a wound with Mandibles, refresh a spent token of the same type as the wound.</t>
   </si>
   <si>
@@ -1594,9 +1345,6 @@
     <t>Whenever an adjacent creature takes a wound, you may activate this and inflict the &lt;b&gt;Stunned&lt;/b&gt; status effect on them.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Fuelled by Pain&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever you suffer a wound, gain the &lt;b&gt;Well Rested&lt;/b&gt; status effect.</t>
   </si>
   <si>
@@ -1616,9 +1364,6 @@
   </si>
   <si>
     <t>&lt;b&gt;Nip:&lt;/b&gt; 2 AP</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Precise&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>Wounds inflicted by this limb's attacks always target the stat of your choice.</t>
@@ -1699,9 +1444,6 @@
   </si>
   <si>
     <t>Place a 1 hex sized heartstone on an adjacent hex. It is &lt;b&gt;destructible&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Living Rhythm&lt;/i&gt;&lt;/b&gt;</t>
   </si>
   <si>
     <t>At the end of your turn, if there is at least one crystal on the map, you gain up to 3 temporary composure at the end of your turn.</t>
@@ -1857,9 +1599,6 @@
 &lt;br /&gt;Deal 8 damage to all beings in a straight line from you. No attack roll required.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Flex&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Whenever you spend a weirdt, add a charget to this card.</t>
   </si>
   <si>
@@ -1869,9 +1608,6 @@
     <t>&lt;b&gt;Scour:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Snatch&lt;/i&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>Whenever a being leaves your attack range, you may spend jazzT to make an attack with any limb against them. If the attack would cost 3 or more AP, &lt;b&gt;Exhaust&lt;/b&gt;.</t>
   </si>
   <si>
@@ -1900,9 +1636,6 @@
   </si>
   <si>
     <t>Place a 1 hex crystal on an adjacent hex. Is blocks line of sight and is &lt;b&gt;destructible&lt;/b&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Disruption&lt;/b&gt;&lt;/i&gt;</t>
   </si>
   <si>
     <t>While the crystal is in play, any being that spends weirdT takes 2 damage.</t>
@@ -1933,16 +1666,277 @@
     <t>Ravenous</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Unsated&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Start combat with all tokens spent instead of available. If you equip this impression during combat, immediately spend all available tokens.</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;i&gt;Consuming&lt;/b&gt;&lt;/i&gt;</t>
-  </si>
-  <si>
     <t>Whenever you inflict a wound, restore a multtok</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Clear Mind&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Reckless&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Many Legs&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Pulpy&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Behemoth&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Warm Glow&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Symptom Sower: 2 AP + weirdt&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Odd structure&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Two Legs&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Consuming&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exoskeleton&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Long Limbed&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Modal&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Very Fast&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Easy as Walking&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Ghostly&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Just a Tail&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Radioactive&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Furnace&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Writhe and Revel&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Enflamed&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Generative&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Creative Duellist&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Charger&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Passive&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt; Flow State&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Normality&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sharing&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Magic Touch&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Twisted Kindness&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Inhale&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Relish in battle&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sure Footed&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Unsated&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Thief of thought&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Relentless&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sideways Scuttle&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Budding Growth&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Toxic&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Massive Limbs&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Fragile&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Two Arms&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Regenerative&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sweeper&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Modes&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Multitudinous&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Fast&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Stone Flesh&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Decay&lt;/b&gt; </t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Flame Geysers&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;On the Move&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;World Sculptor&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Giving&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Treasure!&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Vulgarity&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Aura of Earth&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Creature of the Shadows&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Pressure Points&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Enchanting&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Minion&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Spreading Clay&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Autonomous Limb&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Sparks&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Radiance&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Flame Devourer&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Surprising thwack: jazzTjazzTjazzT</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Fleet&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Growing Cloud&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Release&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Snack&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Fuelled by Pain&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Precise&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Living Rhythm&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Snatch&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Disruption&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Abandon Soul&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Victorious&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Cracked Shell&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Hefty&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Rake Essence&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Butter Cutter&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Recharge&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Shared Mind&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Moving is Optional&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Consume&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Impervious Plates&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Through Fire&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Ungrown&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Flex&lt;/b&gt;</t>
   </si>
 </sst>
 </file>
@@ -2167,7 +2161,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Pūnoa" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2427,33 +2421,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI201"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="1.44140625" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="1.42578125" customWidth="1"/>
+    <col min="7" max="7" width="4.28515625" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" customWidth="1"/>
     <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="42.44140625" customWidth="1"/>
-    <col min="11" max="11" width="1.44140625" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" customWidth="1"/>
-    <col min="13" max="13" width="14.88671875" customWidth="1"/>
-    <col min="14" max="14" width="31.6640625" customWidth="1"/>
-    <col min="15" max="15" width="37.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="1.44140625" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
-    <col min="19" max="19" width="25.5546875" customWidth="1"/>
-    <col min="20" max="20" width="35.109375" customWidth="1"/>
-    <col min="21" max="21" width="1.44140625" customWidth="1"/>
+    <col min="10" max="10" width="42.42578125" customWidth="1"/>
+    <col min="11" max="11" width="1.42578125" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="14" width="31.7109375" customWidth="1"/>
+    <col min="15" max="15" width="37.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="1.42578125" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" customWidth="1"/>
+    <col min="19" max="19" width="25.5703125" customWidth="1"/>
+    <col min="20" max="20" width="35.140625" customWidth="1"/>
+    <col min="21" max="21" width="1.42578125" customWidth="1"/>
     <col min="22" max="22" width="10" customWidth="1"/>
     <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="26" max="33" width="10.5546875" customWidth="1"/>
+    <col min="26" max="33" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2582,23 +2576,23 @@
         <v>38</v>
       </c>
       <c r="I2" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="8">
         <v>4</v>
       </c>
       <c r="M2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="8">
@@ -2608,10 +2602,10 @@
         <v>38</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>44</v>
+        <v>602</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U2" s="9"/>
       <c r="V2" s="8">
@@ -2666,15 +2660,15 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>37</v>
@@ -2688,10 +2682,10 @@
         <v>38</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>48</v>
+        <v>528</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="8">
@@ -2701,10 +2695,10 @@
         <v>38</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>50</v>
+        <v>562</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="8">
@@ -2714,10 +2708,10 @@
         <v>38</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>52</v>
+        <v>603</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="U3" s="9"/>
       <c r="V3" s="8"/>
@@ -2762,12 +2756,12 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" ht="90" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>36</v>
@@ -2776,7 +2770,7 @@
         <v>37</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="8">
@@ -2786,10 +2780,10 @@
         <v>38</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>56</v>
+        <v>529</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="8">
@@ -2799,10 +2793,10 @@
         <v>38</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>58</v>
+        <v>563</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="8">
@@ -2812,15 +2806,15 @@
         <v>38</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>60</v>
+        <v>604</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="U4" s="9"/>
       <c r="V4" s="8"/>
       <c r="W4" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
@@ -2862,34 +2856,34 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="8">
@@ -2899,10 +2893,10 @@
         <v>38</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>67</v>
+        <v>564</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="8"/>
@@ -2912,7 +2906,7 @@
       <c r="U5" s="9"/>
       <c r="V5" s="8"/>
       <c r="W5" s="13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
@@ -2954,15 +2948,15 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>37</v>
@@ -2976,10 +2970,10 @@
         <v>38</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>71</v>
+        <v>530</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="8">
@@ -2989,10 +2983,10 @@
         <v>38</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>73</v>
+        <v>565</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="8"/>
@@ -3002,7 +2996,7 @@
       <c r="U6" s="9"/>
       <c r="V6" s="8"/>
       <c r="W6" s="14" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -3044,21 +3038,21 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="8">
@@ -3068,10 +3062,10 @@
         <v>38</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="8">
@@ -3081,10 +3075,10 @@
         <v>38</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>80</v>
+        <v>566</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="8">
@@ -3094,10 +3088,10 @@
         <v>38</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="U7" s="9"/>
       <c r="V7" s="8"/>
@@ -3142,15 +3136,15 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" ht="90" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>37</v>
@@ -3164,23 +3158,23 @@
         <v>38</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>85</v>
+        <v>532</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="8">
         <v>5</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="8"/>
@@ -3230,12 +3224,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>36</v>
@@ -3249,26 +3243,26 @@
         <v>1</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>90</v>
+        <v>533</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="8">
         <v>4</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="8">
@@ -3278,10 +3272,10 @@
         <v>38</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>94</v>
+        <v>606</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="U9" s="9"/>
       <c r="V9" s="8"/>
@@ -3326,12 +3320,12 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>36</v>
@@ -3348,10 +3342,10 @@
         <v>38</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>97</v>
+        <v>534</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="8">
@@ -3361,10 +3355,10 @@
         <v>38</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>99</v>
+        <v>567</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="8"/>
@@ -3414,21 +3408,21 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="8">
@@ -3438,10 +3432,10 @@
         <v>38</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>102</v>
+        <v>535</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="8">
@@ -3451,23 +3445,23 @@
         <v>38</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>103</v>
+        <v>568</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="8">
         <v>5</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="U11" s="9"/>
       <c r="V11" s="8"/>
@@ -3512,15 +3506,15 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>37</v>
@@ -3534,10 +3528,10 @@
         <v>38</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>108</v>
+        <v>536</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="8">
@@ -3547,10 +3541,10 @@
         <v>38</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>110</v>
+        <v>569</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="8"/>
@@ -3600,15 +3594,15 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>37</v>
@@ -3622,23 +3616,23 @@
         <v>38</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>113</v>
+        <v>537</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="8">
         <v>5</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="8"/>
@@ -3688,15 +3682,15 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>37</v>
@@ -3710,10 +3704,10 @@
         <v>38</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>118</v>
+        <v>538</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="8">
@@ -3723,10 +3717,10 @@
         <v>38</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="8">
@@ -3736,10 +3730,10 @@
         <v>38</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>122</v>
+        <v>607</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="U14" s="9"/>
       <c r="V14" s="8"/>
@@ -3784,47 +3778,47 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="8">
         <v>1</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="8">
         <v>4</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="8">
@@ -3834,10 +3828,10 @@
         <v>38</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>130</v>
+        <v>608</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="U15" s="9"/>
       <c r="V15" s="8"/>
@@ -3882,12 +3876,12 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="120" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>36</v>
@@ -3904,10 +3898,10 @@
         <v>38</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>133</v>
+        <v>539</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="8">
@@ -3917,10 +3911,10 @@
         <v>38</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>135</v>
+        <v>571</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="8"/>
@@ -3970,12 +3964,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>36</v>
@@ -3984,7 +3978,7 @@
         <v>37</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="8">
@@ -3994,10 +3988,10 @@
         <v>38</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>139</v>
+        <v>540</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="8">
@@ -4007,10 +4001,10 @@
         <v>38</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>141</v>
+        <v>572</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="8">
@@ -4020,10 +4014,10 @@
         <v>38</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>143</v>
+        <v>609</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="U17" s="9"/>
       <c r="V17" s="8"/>
@@ -4068,15 +4062,15 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>37</v>
@@ -4090,23 +4084,23 @@
         <v>38</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>146</v>
+        <v>541</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="8">
         <v>3</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="8">
@@ -4116,10 +4110,10 @@
         <v>38</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>150</v>
+        <v>610</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="8"/>
@@ -4164,15 +4158,15 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>37</v>
@@ -4183,26 +4177,26 @@
         <v>1</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="8">
         <v>3</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="8">
@@ -4212,10 +4206,10 @@
         <v>38</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>158</v>
+        <v>611</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="U19" s="9"/>
       <c r="V19" s="8"/>
@@ -4260,12 +4254,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>36</v>
@@ -4282,23 +4276,23 @@
         <v>38</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>161</v>
+        <v>542</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="8">
         <v>7</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="8"/>
@@ -4348,15 +4342,15 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>37</v>
@@ -4370,10 +4364,10 @@
         <v>38</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>166</v>
+        <v>543</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="8">
@@ -4383,10 +4377,10 @@
         <v>38</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>168</v>
+        <v>573</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="P21" s="11"/>
       <c r="Q21" s="8"/>
@@ -4436,12 +4430,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="135" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>36</v>
@@ -4450,33 +4444,33 @@
         <v>37</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="8">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="8">
         <v>10.5</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="P22" s="11"/>
       <c r="Q22" s="8"/>
@@ -4536,12 +4530,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>36</v>
@@ -4550,7 +4544,7 @@
         <v>37</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="8">
@@ -4560,10 +4554,10 @@
         <v>38</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="8">
@@ -4573,10 +4567,10 @@
         <v>38</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>176</v>
+        <v>574</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="8">
@@ -4586,10 +4580,10 @@
         <v>38</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>178</v>
+        <v>612</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="U23" s="9"/>
       <c r="V23" s="8"/>
@@ -4634,15 +4628,15 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>37</v>
@@ -4656,10 +4650,10 @@
         <v>38</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>181</v>
+        <v>544</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="8">
@@ -4669,10 +4663,10 @@
         <v>38</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>183</v>
+        <v>575</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="8"/>
@@ -4722,12 +4716,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -4744,23 +4738,23 @@
         <v>38</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>186</v>
+        <v>545</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="8">
         <v>4</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="10"/>
@@ -4810,12 +4804,12 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>36</v>
@@ -4824,7 +4818,7 @@
         <v>37</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="8">
@@ -4834,10 +4828,10 @@
         <v>38</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>192</v>
+        <v>546</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="8">
@@ -4847,23 +4841,23 @@
         <v>38</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="O26" s="10" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="8">
         <v>9</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="S26" s="10" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="8"/>
@@ -4908,15 +4902,15 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>37</v>
@@ -4930,10 +4924,10 @@
         <v>38</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>199</v>
+        <v>547</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="8">
@@ -4943,10 +4937,10 @@
         <v>38</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>201</v>
+        <v>576</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="P27" s="11"/>
       <c r="Q27" s="8">
@@ -4956,10 +4950,10 @@
         <v>38</v>
       </c>
       <c r="S27" s="10" t="s">
-        <v>203</v>
+        <v>613</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="U27" s="9"/>
       <c r="V27" s="8"/>
@@ -5004,12 +4998,12 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>36</v>
@@ -5026,23 +5020,23 @@
         <v>38</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>206</v>
+        <v>548</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="8">
         <v>5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="P28" s="11"/>
       <c r="Q28" s="8"/>
@@ -5092,18 +5086,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
@@ -5111,13 +5105,13 @@
         <v>1</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="8"/>
@@ -5172,18 +5166,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="9"/>
@@ -5194,10 +5188,10 @@
         <v>38</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>215</v>
+        <v>549</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="8"/>
@@ -5249,18 +5243,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="16"/>
@@ -5271,10 +5265,10 @@
         <v>38</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>218</v>
+        <v>550</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="8"/>
@@ -5329,18 +5323,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="16"/>
@@ -5351,10 +5345,10 @@
         <v>38</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="8"/>
@@ -5409,18 +5403,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="16"/>
@@ -5431,10 +5425,10 @@
         <v>38</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="K33" s="16"/>
       <c r="L33" s="8"/>
@@ -5489,18 +5483,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="16"/>
@@ -5511,10 +5505,10 @@
         <v>38</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="K34" s="16"/>
       <c r="L34" s="8"/>
@@ -5569,18 +5563,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="9"/>
@@ -5588,13 +5582,13 @@
         <v>1</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="8"/>
@@ -5649,18 +5643,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="9"/>
@@ -5671,10 +5665,10 @@
         <v>38</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="8"/>
@@ -5729,18 +5723,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="9"/>
@@ -5751,10 +5745,10 @@
         <v>38</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>233</v>
+        <v>552</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="8">
@@ -5764,10 +5758,10 @@
         <v>38</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>235</v>
+        <v>577</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="8"/>
@@ -5817,18 +5811,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
@@ -5836,13 +5830,13 @@
         <v>1</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="8"/>
@@ -5897,18 +5891,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
@@ -5919,10 +5913,10 @@
         <v>38</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="8"/>
@@ -5977,18 +5971,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="9"/>
@@ -5999,10 +5993,10 @@
         <v>38</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>243</v>
+        <v>188</v>
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="8"/>
@@ -6057,34 +6051,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>244</v>
+        <v>189</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="8">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="8"/>
@@ -6139,18 +6133,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="9"/>
@@ -6158,13 +6152,13 @@
         <v>1</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="8">
@@ -6174,10 +6168,10 @@
         <v>38</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>251</v>
+        <v>578</v>
       </c>
       <c r="O42" s="8" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="8"/>
@@ -6227,18 +6221,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
@@ -6249,10 +6243,10 @@
         <v>38</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="8"/>
@@ -6307,18 +6301,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="9"/>
@@ -6329,10 +6323,10 @@
         <v>38</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="8"/>
@@ -6387,18 +6381,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" ht="90" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="9"/>
@@ -6409,36 +6403,36 @@
         <v>38</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>258</v>
+        <v>553</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="8">
         <v>4</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="8">
         <v>8</v>
       </c>
       <c r="R45" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="T45" s="8" t="s">
-        <v>263</v>
+        <v>206</v>
       </c>
       <c r="U45" s="9"/>
       <c r="V45" s="8"/>
@@ -6483,18 +6477,18 @@
         <v>62.800000000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="9"/>
@@ -6505,10 +6499,10 @@
         <v>38</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>265</v>
+        <v>554</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="8">
@@ -6518,10 +6512,10 @@
         <v>38</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>267</v>
+        <v>579</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="8"/>
@@ -6571,34 +6565,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D47" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>211</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="8">
         <v>1</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>271</v>
+        <v>212</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="8"/>
@@ -6653,18 +6647,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="9"/>
@@ -6675,10 +6669,10 @@
         <v>38</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>274</v>
+        <v>555</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="8">
@@ -6688,10 +6682,10 @@
         <v>38</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>276</v>
+        <v>580</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="P48" s="11"/>
       <c r="Q48" s="8"/>
@@ -6741,18 +6735,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="9"/>
@@ -6763,10 +6757,10 @@
         <v>38</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="8"/>
@@ -6821,18 +6815,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="9"/>
@@ -6843,23 +6837,23 @@
         <v>38</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>281</v>
+        <v>556</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="8">
         <v>6</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="P50" s="11"/>
       <c r="Q50" s="8"/>
@@ -6909,18 +6903,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
@@ -6928,13 +6922,13 @@
         <v>1</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="8"/>
@@ -6989,18 +6983,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="9"/>
@@ -7008,13 +7002,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="8"/>
@@ -7069,18 +7063,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" ht="90" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>291</v>
+        <v>229</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="9"/>
@@ -7088,13 +7082,13 @@
         <v>1</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>292</v>
+        <v>230</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="8"/>
@@ -7149,18 +7143,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>294</v>
+        <v>232</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="9"/>
@@ -7168,13 +7162,13 @@
         <v>1</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>295</v>
+        <v>233</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="8"/>
@@ -7229,18 +7223,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="9"/>
@@ -7248,13 +7242,13 @@
         <v>1</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>298</v>
+        <v>236</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>299</v>
+        <v>237</v>
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="8">
@@ -7264,10 +7258,10 @@
         <v>38</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>300</v>
+        <v>581</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="P55" s="11"/>
       <c r="Q55" s="8"/>
@@ -7317,18 +7311,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="9"/>
@@ -7339,10 +7333,10 @@
         <v>38</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="8"/>
@@ -7397,18 +7391,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="9"/>
@@ -7419,23 +7413,23 @@
         <v>38</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>305</v>
+        <v>557</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="8">
         <v>5</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>307</v>
+        <v>243</v>
       </c>
       <c r="O57" s="8" t="s">
-        <v>308</v>
+        <v>244</v>
       </c>
       <c r="P57" s="11"/>
       <c r="Q57" s="8"/>
@@ -7485,18 +7479,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>309</v>
+        <v>245</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="9"/>
@@ -7504,13 +7498,13 @@
         <v>1</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>311</v>
+        <v>247</v>
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="8">
@@ -7520,10 +7514,10 @@
         <v>38</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>312</v>
+        <v>582</v>
       </c>
       <c r="O58" s="8" t="s">
-        <v>313</v>
+        <v>248</v>
       </c>
       <c r="P58" s="11"/>
       <c r="Q58" s="8"/>
@@ -7573,18 +7567,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="9"/>
@@ -7595,23 +7589,23 @@
         <v>38</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>315</v>
+        <v>558</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="8">
         <v>5</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>318</v>
+        <v>252</v>
       </c>
       <c r="P59" s="11"/>
       <c r="Q59" s="8"/>
@@ -7661,18 +7655,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>319</v>
+        <v>253</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="9"/>
@@ -7683,10 +7677,10 @@
         <v>38</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="8"/>
@@ -7741,18 +7735,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="9"/>
@@ -7760,13 +7754,13 @@
         <v>1</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="8">
@@ -7776,10 +7770,10 @@
         <v>38</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>324</v>
+        <v>583</v>
       </c>
       <c r="O61" s="8" t="s">
-        <v>325</v>
+        <v>258</v>
       </c>
       <c r="P61" s="11"/>
       <c r="Q61" s="8"/>
@@ -7829,18 +7823,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="9"/>
@@ -7851,10 +7845,10 @@
         <v>38</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>327</v>
+        <v>260</v>
       </c>
       <c r="K62" s="9"/>
       <c r="L62" s="8"/>
@@ -7909,18 +7903,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>328</v>
+        <v>261</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="9"/>
@@ -7928,13 +7922,13 @@
         <v>1</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>329</v>
+        <v>262</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>330</v>
+        <v>263</v>
       </c>
       <c r="K63" s="9"/>
       <c r="L63" s="8"/>
@@ -7989,18 +7983,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="9"/>
@@ -8008,13 +8002,13 @@
         <v>1</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>332</v>
+        <v>265</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="K64" s="9"/>
       <c r="L64" s="8"/>
@@ -8069,18 +8063,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>334</v>
+        <v>267</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="9"/>
@@ -8088,13 +8082,13 @@
         <v>1</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>335</v>
+        <v>268</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>336</v>
+        <v>269</v>
       </c>
       <c r="K65" s="9"/>
       <c r="L65" s="8">
@@ -8104,10 +8098,10 @@
         <v>38</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>337</v>
+        <v>584</v>
       </c>
       <c r="O65" s="8" t="s">
-        <v>338</v>
+        <v>270</v>
       </c>
       <c r="P65" s="11"/>
       <c r="Q65" s="8"/>
@@ -8157,18 +8151,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>339</v>
+        <v>271</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="9"/>
@@ -8179,10 +8173,10 @@
         <v>38</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="K66" s="9"/>
       <c r="L66" s="8"/>
@@ -8237,18 +8231,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="9"/>
@@ -8256,13 +8250,13 @@
         <v>1</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>342</v>
+        <v>274</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="K67" s="9"/>
       <c r="L67" s="8">
@@ -8272,10 +8266,10 @@
         <v>38</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>344</v>
+        <v>585</v>
       </c>
       <c r="O67" s="8" t="s">
-        <v>345</v>
+        <v>276</v>
       </c>
       <c r="P67" s="11"/>
       <c r="Q67" s="8"/>
@@ -8325,18 +8319,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="9"/>
@@ -8344,13 +8338,13 @@
         <v>1</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="K68" s="9"/>
       <c r="L68" s="8">
@@ -8360,10 +8354,10 @@
         <v>38</v>
       </c>
       <c r="N68" s="8" t="s">
-        <v>349</v>
+        <v>586</v>
       </c>
       <c r="O68" s="8" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="P68" s="11"/>
       <c r="Q68" s="8"/>
@@ -8413,18 +8407,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="9"/>
@@ -8432,13 +8426,13 @@
         <v>1</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>352</v>
+        <v>282</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>353</v>
+        <v>283</v>
       </c>
       <c r="K69" s="9"/>
       <c r="L69" s="8"/>
@@ -8493,18 +8487,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="9"/>
@@ -8512,13 +8506,13 @@
         <v>1</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>356</v>
+        <v>286</v>
       </c>
       <c r="K70" s="9"/>
       <c r="L70" s="8"/>
@@ -8573,18 +8567,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="16"/>
@@ -8592,39 +8586,39 @@
         <v>1</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="K71" s="16"/>
       <c r="L71" s="8">
         <v>5</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="O71" s="8" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="P71" s="17"/>
       <c r="Q71" s="8">
         <v>9.5</v>
       </c>
       <c r="R71" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S71" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T71" s="8" t="s">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="U71" s="16"/>
       <c r="V71" s="8"/>
@@ -8669,18 +8663,18 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="16"/>
@@ -8688,26 +8682,26 @@
         <v>1</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="K72" s="16"/>
       <c r="L72" s="8">
         <v>10</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N72" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="P72" s="17"/>
       <c r="Q72" s="8">
@@ -8759,18 +8753,18 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>371</v>
+        <v>301</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="9"/>
@@ -8778,26 +8772,26 @@
         <v>1</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="K73" s="9"/>
       <c r="L73" s="8">
         <v>6</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="O73" s="8" t="s">
-        <v>375</v>
+        <v>305</v>
       </c>
       <c r="P73" s="11"/>
       <c r="Q73" s="8"/>
@@ -8847,18 +8841,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="16"/>
@@ -8866,13 +8860,13 @@
         <v>1</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="K74" s="16"/>
       <c r="L74" s="8"/>
@@ -8929,18 +8923,18 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="9"/>
@@ -8948,13 +8942,13 @@
         <v>1</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>381</v>
+        <v>311</v>
       </c>
       <c r="K75" s="9"/>
       <c r="L75" s="8">
@@ -8964,10 +8958,10 @@
         <v>38</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>382</v>
+        <v>587</v>
       </c>
       <c r="O75" s="8" t="s">
-        <v>383</v>
+        <v>312</v>
       </c>
       <c r="P75" s="11"/>
       <c r="Q75" s="8"/>
@@ -9017,18 +9011,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="9"/>
@@ -9036,13 +9030,13 @@
         <v>1</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K76" s="9"/>
       <c r="L76" s="8">
@@ -9052,10 +9046,10 @@
         <v>38</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>387</v>
+        <v>588</v>
       </c>
       <c r="O76" s="8" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="P76" s="11"/>
       <c r="Q76" s="8"/>
@@ -9105,18 +9099,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="9"/>
@@ -9124,26 +9118,26 @@
         <v>1</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K77" s="9"/>
       <c r="L77" s="8">
         <v>10</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O77" s="8" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="P77" s="11"/>
       <c r="Q77" s="8"/>
@@ -9193,18 +9187,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="9"/>
@@ -9212,13 +9206,13 @@
         <v>1</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="K78" s="9"/>
       <c r="L78" s="8">
@@ -9228,10 +9222,10 @@
         <v>38</v>
       </c>
       <c r="N78" s="8" t="s">
-        <v>395</v>
+        <v>589</v>
       </c>
       <c r="O78" s="8" t="s">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="P78" s="11"/>
       <c r="Q78" s="8"/>
@@ -9281,34 +9275,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>397</v>
+        <v>324</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="F79" s="9"/>
       <c r="G79" s="8">
         <v>1</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>398</v>
+        <v>325</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="K79" s="9"/>
       <c r="L79" s="10">
@@ -9318,10 +9312,10 @@
         <v>38</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="O79" s="8" t="s">
-        <v>401</v>
+        <v>327</v>
       </c>
       <c r="P79" s="11"/>
       <c r="Q79" s="8"/>
@@ -9371,18 +9365,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="9"/>
@@ -9390,26 +9384,26 @@
         <v>1</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>404</v>
+        <v>330</v>
       </c>
       <c r="K80" s="9"/>
       <c r="L80" s="8">
         <v>3</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N80" s="8" t="s">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>406</v>
+        <v>332</v>
       </c>
       <c r="P80" s="11"/>
       <c r="Q80" s="8"/>
@@ -9459,18 +9453,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="9"/>
@@ -9478,39 +9472,39 @@
         <v>1</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>408</v>
+        <v>334</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="K81" s="9"/>
       <c r="L81" s="10">
         <v>3</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>410</v>
+        <v>336</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>411</v>
+        <v>337</v>
       </c>
       <c r="P81" s="11"/>
       <c r="Q81" s="8">
         <v>10</v>
       </c>
       <c r="R81" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T81" s="8" t="s">
-        <v>412</v>
+        <v>338</v>
       </c>
       <c r="U81" s="9"/>
       <c r="V81" s="8"/>
@@ -9555,18 +9549,18 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>413</v>
+        <v>339</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="9"/>
@@ -9574,13 +9568,13 @@
         <v>1</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>415</v>
+        <v>341</v>
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="8"/>
@@ -9592,13 +9586,13 @@
         <v>9.5</v>
       </c>
       <c r="R82" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T82" s="10" t="s">
-        <v>416</v>
+        <v>342</v>
       </c>
       <c r="U82" s="9"/>
       <c r="V82" s="8"/>
@@ -9643,18 +9637,18 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="9"/>
@@ -9662,13 +9656,13 @@
         <v>1</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>418</v>
+        <v>344</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>419</v>
+        <v>345</v>
       </c>
       <c r="K83" s="9"/>
       <c r="L83" s="8">
@@ -9678,23 +9672,23 @@
         <v>38</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>420</v>
+        <v>591</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>421</v>
+        <v>346</v>
       </c>
       <c r="P83" s="11"/>
       <c r="Q83" s="8">
         <v>9</v>
       </c>
       <c r="R83" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S83" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T83" s="8" t="s">
-        <v>422</v>
+        <v>347</v>
       </c>
       <c r="U83" s="9"/>
       <c r="V83" s="8"/>
@@ -9739,18 +9733,18 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>423</v>
+        <v>348</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="9"/>
@@ -9758,26 +9752,26 @@
         <v>1</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>424</v>
+        <v>349</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="K84" s="9"/>
       <c r="L84" s="8">
         <v>4</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N84" s="8" t="s">
-        <v>426</v>
+        <v>351</v>
       </c>
       <c r="O84" s="8" t="s">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="P84" s="11"/>
       <c r="Q84" s="8"/>
@@ -9827,18 +9821,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>428</v>
+        <v>353</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="9"/>
@@ -9846,26 +9840,26 @@
         <v>1</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>429</v>
+        <v>354</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>430</v>
+        <v>355</v>
       </c>
       <c r="K85" s="9"/>
       <c r="L85" s="8">
         <v>4</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>431</v>
+        <v>592</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>432</v>
+        <v>356</v>
       </c>
       <c r="P85" s="11"/>
       <c r="Q85" s="8"/>
@@ -9915,18 +9909,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>433</v>
+        <v>357</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="9"/>
@@ -9937,10 +9931,10 @@
         <v>38</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>435</v>
+        <v>358</v>
       </c>
       <c r="K86" s="9"/>
       <c r="L86" s="8">
@@ -9950,10 +9944,10 @@
         <v>38</v>
       </c>
       <c r="N86" s="8" t="s">
-        <v>436</v>
+        <v>593</v>
       </c>
       <c r="O86" s="8" t="s">
-        <v>437</v>
+        <v>359</v>
       </c>
       <c r="P86" s="11"/>
       <c r="Q86" s="8"/>
@@ -10003,34 +9997,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>438</v>
+        <v>360</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>439</v>
+        <v>361</v>
       </c>
       <c r="F87" s="9"/>
       <c r="G87" s="8">
         <v>1</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>440</v>
+        <v>362</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>441</v>
+        <v>363</v>
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="8">
@@ -10040,10 +10034,10 @@
         <v>38</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>442</v>
+        <v>594</v>
       </c>
       <c r="O87" s="8" t="s">
-        <v>443</v>
+        <v>364</v>
       </c>
       <c r="P87" s="11"/>
       <c r="Q87" s="8">
@@ -10053,10 +10047,10 @@
         <v>38</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>444</v>
+        <v>565</v>
       </c>
       <c r="T87" s="8" t="s">
-        <v>445</v>
+        <v>365</v>
       </c>
       <c r="U87" s="9"/>
       <c r="V87" s="8"/>
@@ -10101,47 +10095,47 @@
         <v>58.400000000000006</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>446</v>
+        <v>366</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>447</v>
+        <v>367</v>
       </c>
       <c r="F88" s="9"/>
       <c r="G88" s="8">
         <v>1</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>448</v>
+        <v>368</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>449</v>
+        <v>369</v>
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="8">
         <v>3</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N88" s="8" t="s">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="O88" s="8" t="s">
-        <v>451</v>
+        <v>371</v>
       </c>
       <c r="P88" s="11"/>
       <c r="Q88" s="8">
@@ -10151,10 +10145,10 @@
         <v>38</v>
       </c>
       <c r="S88" s="8" t="s">
-        <v>452</v>
+        <v>614</v>
       </c>
       <c r="T88" s="8" t="s">
-        <v>453</v>
+        <v>372</v>
       </c>
       <c r="U88" s="9"/>
       <c r="V88" s="8"/>
@@ -10199,18 +10193,18 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>454</v>
+        <v>373</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E89" s="8"/>
       <c r="F89" s="9"/>
@@ -10218,26 +10212,26 @@
         <v>1</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>455</v>
+        <v>374</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="10">
         <v>9.5</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O89" s="8" t="s">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="P89" s="11"/>
       <c r="Q89" s="8"/>
@@ -10287,18 +10281,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="9"/>
@@ -10306,39 +10300,39 @@
         <v>1</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>458</v>
+        <v>377</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>459</v>
+        <v>378</v>
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="8">
         <v>3</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N90" s="8" t="s">
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="O90" s="8" t="s">
-        <v>461</v>
+        <v>380</v>
       </c>
       <c r="P90" s="11"/>
       <c r="Q90" s="10">
         <v>10</v>
       </c>
       <c r="R90" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S90" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="U90" s="9"/>
       <c r="V90" s="8"/>
@@ -10383,18 +10377,18 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>462</v>
+        <v>381</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="9"/>
@@ -10402,13 +10396,13 @@
         <v>1</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>463</v>
+        <v>382</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="8"/>
@@ -10463,18 +10457,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>465</v>
+        <v>384</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="9"/>
@@ -10482,13 +10476,13 @@
         <v>1</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>466</v>
+        <v>385</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="8">
@@ -10498,23 +10492,23 @@
         <v>38</v>
       </c>
       <c r="N92" s="8" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="P92" s="11"/>
       <c r="Q92" s="8">
         <v>11</v>
       </c>
       <c r="R92" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S92" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T92" s="10" t="s">
-        <v>469</v>
+        <v>388</v>
       </c>
       <c r="U92" s="9"/>
       <c r="V92" s="8"/>
@@ -10559,18 +10553,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>470</v>
+        <v>389</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="9"/>
@@ -10578,26 +10572,26 @@
         <v>1</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>472</v>
+        <v>391</v>
       </c>
       <c r="K93" s="9"/>
       <c r="L93" s="8">
         <v>9.5</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>473</v>
+        <v>392</v>
       </c>
       <c r="O93" s="21" t="s">
-        <v>474</v>
+        <v>393</v>
       </c>
       <c r="P93" s="11"/>
       <c r="Q93" s="8"/>
@@ -10647,18 +10641,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>475</v>
+        <v>394</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="9"/>
@@ -10666,26 +10660,26 @@
         <v>1</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>476</v>
+        <v>395</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K94" s="9"/>
       <c r="L94" s="8">
         <v>3</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N94" s="8" t="s">
-        <v>477</v>
+        <v>396</v>
       </c>
       <c r="O94" s="8" t="s">
-        <v>478</v>
+        <v>397</v>
       </c>
       <c r="P94" s="11"/>
       <c r="Q94" s="8"/>
@@ -10735,18 +10729,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>479</v>
+        <v>398</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="9"/>
@@ -10754,26 +10748,26 @@
         <v>1</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>481</v>
+        <v>400</v>
       </c>
       <c r="K95" s="9"/>
       <c r="L95" s="8">
         <v>3</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>482</v>
+        <v>401</v>
       </c>
       <c r="O95" s="8" t="s">
-        <v>483</v>
+        <v>402</v>
       </c>
       <c r="P95" s="11"/>
       <c r="Q95" s="8"/>
@@ -10823,47 +10817,47 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>485</v>
+        <v>404</v>
       </c>
       <c r="F96" s="9"/>
       <c r="G96" s="8">
         <v>1</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>486</v>
+        <v>405</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="8">
         <v>5</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="O96" s="8" t="s">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="P96" s="11"/>
       <c r="Q96" s="8"/>
@@ -10913,18 +10907,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>490</v>
+        <v>409</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="9"/>
@@ -10932,13 +10926,13 @@
         <v>1</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K97" s="9"/>
       <c r="L97" s="8">
@@ -10948,10 +10942,10 @@
         <v>38</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>492</v>
+        <v>595</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>493</v>
+        <v>411</v>
       </c>
       <c r="P97" s="11"/>
       <c r="Q97" s="8"/>
@@ -11001,18 +10995,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>494</v>
+        <v>412</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="9"/>
@@ -11020,13 +11014,13 @@
         <v>1</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>495</v>
+        <v>413</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>496</v>
+        <v>414</v>
       </c>
       <c r="K98" s="9"/>
       <c r="L98" s="8">
@@ -11036,10 +11030,10 @@
         <v>38</v>
       </c>
       <c r="N98" s="8" t="s">
-        <v>497</v>
+        <v>596</v>
       </c>
       <c r="O98" s="8" t="s">
-        <v>498</v>
+        <v>415</v>
       </c>
       <c r="P98" s="11"/>
       <c r="Q98" s="8"/>
@@ -11089,18 +11083,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>499</v>
+        <v>416</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="9"/>
@@ -11108,26 +11102,26 @@
         <v>1</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>500</v>
+        <v>417</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>459</v>
+        <v>378</v>
       </c>
       <c r="K99" s="9"/>
       <c r="L99" s="8">
         <v>10</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O99" s="8" t="s">
-        <v>501</v>
+        <v>418</v>
       </c>
       <c r="P99" s="11"/>
       <c r="Q99" s="8"/>
@@ -11177,18 +11171,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>502</v>
+        <v>419</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="9"/>
@@ -11196,13 +11190,13 @@
         <v>1</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>503</v>
+        <v>420</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>504</v>
+        <v>421</v>
       </c>
       <c r="K100" s="9"/>
       <c r="L100" s="8">
@@ -11212,10 +11206,10 @@
         <v>38</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>505</v>
+        <v>597</v>
       </c>
       <c r="O100" s="8" t="s">
-        <v>506</v>
+        <v>422</v>
       </c>
       <c r="P100" s="11"/>
       <c r="Q100" s="8"/>
@@ -11265,18 +11259,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>507</v>
+        <v>423</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="9"/>
@@ -11284,26 +11278,26 @@
         <v>1</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>508</v>
+        <v>424</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>459</v>
+        <v>378</v>
       </c>
       <c r="K101" s="9"/>
       <c r="L101" s="8">
         <v>3</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>509</v>
+        <v>425</v>
       </c>
       <c r="O101" s="8" t="s">
-        <v>510</v>
+        <v>426</v>
       </c>
       <c r="P101" s="11"/>
       <c r="Q101" s="8"/>
@@ -11353,18 +11347,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>511</v>
+        <v>427</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="9"/>
@@ -11372,13 +11366,13 @@
         <v>1</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="K102" s="9"/>
       <c r="L102" s="8">
@@ -11388,23 +11382,23 @@
         <v>38</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>513</v>
+        <v>598</v>
       </c>
       <c r="O102" s="8" t="s">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="P102" s="11"/>
       <c r="Q102" s="8">
         <v>11</v>
       </c>
       <c r="R102" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S102" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T102" s="8" t="s">
-        <v>469</v>
+        <v>388</v>
       </c>
       <c r="U102" s="9"/>
       <c r="V102" s="8"/>
@@ -11449,18 +11443,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>515</v>
+        <v>430</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E103" s="8"/>
       <c r="F103" s="9"/>
@@ -11468,13 +11462,13 @@
         <v>1</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>516</v>
+        <v>431</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="K103" s="9"/>
       <c r="L103" s="8"/>
@@ -11529,18 +11523,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>518</v>
+        <v>433</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="9"/>
@@ -11548,13 +11542,13 @@
         <v>1</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>519</v>
+        <v>434</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="K104" s="9"/>
       <c r="L104" s="8"/>
@@ -11609,18 +11603,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>521</v>
+        <v>436</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E105" s="8"/>
       <c r="F105" s="9"/>
@@ -11628,39 +11622,39 @@
         <v>1</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="8">
         <v>3</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N105" s="8" t="s">
-        <v>523</v>
+        <v>438</v>
       </c>
       <c r="O105" s="8" t="s">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="P105" s="11"/>
       <c r="Q105" s="8">
         <v>9</v>
       </c>
       <c r="R105" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S105" s="8" t="s">
-        <v>525</v>
+        <v>440</v>
       </c>
       <c r="T105" s="8" t="s">
-        <v>526</v>
+        <v>441</v>
       </c>
       <c r="U105" s="9"/>
       <c r="V105" s="8"/>
@@ -11705,18 +11699,18 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>527</v>
+        <v>442</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E106" s="8"/>
       <c r="F106" s="9"/>
@@ -11724,26 +11718,26 @@
         <v>1</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>528</v>
+        <v>443</v>
       </c>
       <c r="K106" s="9"/>
       <c r="L106" s="8">
         <v>11</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N106" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O106" s="8" t="s">
-        <v>529</v>
+        <v>444</v>
       </c>
       <c r="P106" s="11"/>
       <c r="Q106" s="8"/>
@@ -11793,18 +11787,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>530</v>
+        <v>445</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="9"/>
@@ -11812,13 +11806,13 @@
         <v>1</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>531</v>
+        <v>446</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>532</v>
+        <v>447</v>
       </c>
       <c r="K107" s="9"/>
       <c r="L107" s="8"/>
@@ -11873,47 +11867,47 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>533</v>
+        <v>448</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="F108" s="9"/>
       <c r="G108" s="8">
         <v>1</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>534</v>
+        <v>449</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>535</v>
+        <v>450</v>
       </c>
       <c r="K108" s="9"/>
       <c r="L108" s="8">
         <v>5</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="N108" s="8" t="s">
-        <v>536</v>
+        <v>451</v>
       </c>
       <c r="O108" s="8" t="s">
-        <v>537</v>
+        <v>452</v>
       </c>
       <c r="P108" s="11"/>
       <c r="Q108" s="8"/>
@@ -11963,34 +11957,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="F109" s="9"/>
       <c r="G109" s="8">
         <v>1</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>398</v>
+        <v>325</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="K109" s="9"/>
       <c r="L109" s="8">
@@ -12000,10 +11994,10 @@
         <v>38</v>
       </c>
       <c r="N109" s="8" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="O109" s="8" t="s">
-        <v>541</v>
+        <v>455</v>
       </c>
       <c r="P109" s="11"/>
       <c r="Q109" s="8"/>
@@ -12053,34 +12047,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>542</v>
+        <v>456</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>543</v>
+        <v>457</v>
       </c>
       <c r="F110" s="9"/>
       <c r="G110" s="8">
         <v>1</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>544</v>
+        <v>458</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>545</v>
+        <v>459</v>
       </c>
       <c r="K110" s="9"/>
       <c r="L110" s="8"/>
@@ -12135,34 +12129,34 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>546</v>
+        <v>460</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D111" s="20" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>439</v>
+        <v>361</v>
       </c>
       <c r="F111" s="9"/>
       <c r="G111" s="8">
         <v>1</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>547</v>
+        <v>461</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>548</v>
+        <v>462</v>
       </c>
       <c r="K111" s="9"/>
       <c r="L111" s="8">
@@ -12172,10 +12166,10 @@
         <v>38</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>549</v>
+        <v>463</v>
       </c>
       <c r="P111" s="11"/>
       <c r="Q111" s="8"/>
@@ -12225,18 +12219,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>550</v>
+        <v>464</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E112" s="8"/>
       <c r="F112" s="9"/>
@@ -12244,39 +12238,39 @@
         <v>1</v>
       </c>
       <c r="H112" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>551</v>
+        <v>465</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K112" s="9"/>
       <c r="L112" s="8">
         <v>3</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>552</v>
+        <v>466</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>553</v>
+        <v>467</v>
       </c>
       <c r="P112" s="11"/>
       <c r="Q112" s="8">
         <v>10</v>
       </c>
       <c r="R112" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S112" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T112" s="8" t="s">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="U112" s="9"/>
       <c r="V112" s="8"/>
@@ -12321,18 +12315,18 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E113" s="8"/>
       <c r="F113" s="9"/>
@@ -12340,26 +12334,26 @@
         <v>1</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>556</v>
+        <v>470</v>
       </c>
       <c r="K113" s="9"/>
       <c r="L113" s="8">
         <v>11</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="P113" s="11"/>
       <c r="Q113" s="8"/>
@@ -12409,18 +12403,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>558</v>
+        <v>472</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E114" s="8"/>
       <c r="F114" s="16"/>
@@ -12428,13 +12422,13 @@
         <v>1</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>559</v>
+        <v>473</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>560</v>
+        <v>474</v>
       </c>
       <c r="K114" s="16"/>
       <c r="L114" s="8"/>
@@ -12489,18 +12483,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E115" s="10"/>
       <c r="F115" s="9"/>
@@ -12508,26 +12502,26 @@
         <v>1</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="K115" s="9"/>
       <c r="L115" s="8">
         <v>10</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N115" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>563</v>
+        <v>477</v>
       </c>
       <c r="P115" s="11"/>
       <c r="Q115" s="8"/>
@@ -12577,18 +12571,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="9"/>
@@ -12602,20 +12596,20 @@
         <v>38</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>565</v>
+        <v>479</v>
       </c>
       <c r="K116" s="9"/>
       <c r="L116" s="8">
         <v>4</v>
       </c>
       <c r="M116" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="N116" s="8" t="s">
-        <v>566</v>
+        <v>480</v>
       </c>
       <c r="O116" s="10" t="s">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="P116" s="11"/>
       <c r="Q116" s="8"/>
@@ -12665,18 +12659,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>568</v>
+        <v>482</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E117" s="10"/>
       <c r="F117" s="9"/>
@@ -12684,26 +12678,26 @@
         <v>1</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>569</v>
+        <v>483</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="K117" s="9"/>
       <c r="L117" s="8">
         <v>9</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>571</v>
+        <v>485</v>
       </c>
       <c r="P117" s="11"/>
       <c r="Q117" s="8"/>
@@ -12753,18 +12747,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>572</v>
+        <v>486</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E118" s="10"/>
       <c r="F118" s="9"/>
@@ -12772,26 +12766,26 @@
         <v>1</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>573</v>
+        <v>487</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>574</v>
+        <v>488</v>
       </c>
       <c r="K118" s="9"/>
       <c r="L118" s="8">
         <v>11</v>
       </c>
       <c r="M118" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N118" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O118" s="10" t="s">
-        <v>501</v>
+        <v>418</v>
       </c>
       <c r="P118" s="11"/>
       <c r="Q118" s="8"/>
@@ -12841,18 +12835,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>575</v>
+        <v>489</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E119" s="10"/>
       <c r="F119" s="9"/>
@@ -12860,26 +12854,26 @@
         <v>1</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>576</v>
+        <v>490</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="K119" s="9"/>
       <c r="L119" s="8">
         <v>11</v>
       </c>
       <c r="M119" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N119" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>577</v>
+        <v>491</v>
       </c>
       <c r="P119" s="11"/>
       <c r="Q119" s="8"/>
@@ -12929,18 +12923,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>578</v>
+        <v>492</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E120" s="10"/>
       <c r="F120" s="9"/>
@@ -12948,13 +12942,13 @@
         <v>1</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>579</v>
+        <v>493</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>580</v>
+        <v>494</v>
       </c>
       <c r="K120" s="9"/>
       <c r="L120" s="8"/>
@@ -13009,18 +13003,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>581</v>
+        <v>495</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E121" s="10"/>
       <c r="F121" s="9"/>
@@ -13028,13 +13022,13 @@
         <v>1</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>582</v>
+        <v>496</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>583</v>
+        <v>497</v>
       </c>
       <c r="K121" s="9"/>
       <c r="L121" s="8"/>
@@ -13089,18 +13083,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>584</v>
+        <v>498</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E122" s="10"/>
       <c r="F122" s="9"/>
@@ -13108,26 +13102,26 @@
         <v>1</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>585</v>
+        <v>499</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>586</v>
+        <v>500</v>
       </c>
       <c r="K122" s="9"/>
       <c r="L122" s="8">
         <v>4</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="N122" s="8" t="s">
-        <v>587</v>
+        <v>501</v>
       </c>
       <c r="O122" s="10" t="s">
-        <v>588</v>
+        <v>502</v>
       </c>
       <c r="P122" s="11"/>
       <c r="Q122" s="8">
@@ -13137,10 +13131,10 @@
         <v>38</v>
       </c>
       <c r="S122" s="8" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="T122" s="8" t="s">
-        <v>590</v>
+        <v>503</v>
       </c>
       <c r="U122" s="9"/>
       <c r="V122" s="8"/>
@@ -13185,18 +13179,18 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>591</v>
+        <v>504</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E123" s="10"/>
       <c r="F123" s="9"/>
@@ -13204,13 +13198,13 @@
         <v>1</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>592</v>
+        <v>505</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="K123" s="9"/>
       <c r="L123" s="8">
@@ -13220,10 +13214,10 @@
         <v>38</v>
       </c>
       <c r="N123" s="8" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>594</v>
+        <v>506</v>
       </c>
       <c r="P123" s="11"/>
       <c r="Q123" s="8"/>
@@ -13273,18 +13267,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>1</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>595</v>
+        <v>507</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E124" s="10"/>
       <c r="F124" s="9"/>
@@ -13292,39 +13286,39 @@
         <v>1</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>596</v>
+        <v>508</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>597</v>
+        <v>509</v>
       </c>
       <c r="K124" s="9"/>
       <c r="L124" s="8">
         <v>3</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="N124" s="8" t="s">
-        <v>598</v>
+        <v>510</v>
       </c>
       <c r="O124" s="8" t="s">
-        <v>599</v>
+        <v>511</v>
       </c>
       <c r="P124" s="11"/>
       <c r="Q124">
         <v>10</v>
       </c>
       <c r="R124" s="8" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="S124" s="8" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="T124" s="10" t="s">
-        <v>600</v>
+        <v>512</v>
       </c>
       <c r="U124" s="9"/>
       <c r="V124" s="8"/>
@@ -13369,34 +13363,34 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>1</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>601</v>
+        <v>513</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>543</v>
+        <v>457</v>
       </c>
       <c r="F125" s="9"/>
       <c r="G125" s="8">
         <v>1</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>602</v>
+        <v>514</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>603</v>
+        <v>515</v>
       </c>
       <c r="K125" s="9"/>
       <c r="L125" s="8">
@@ -13406,10 +13400,10 @@
         <v>38</v>
       </c>
       <c r="N125" s="8" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>605</v>
+        <v>516</v>
       </c>
       <c r="P125" s="11"/>
       <c r="Q125" s="8"/>
@@ -13459,18 +13453,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>1</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>606</v>
+        <v>517</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E126" s="10"/>
       <c r="F126" s="9"/>
@@ -13478,26 +13472,26 @@
         <v>1</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>607</v>
+        <v>518</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>481</v>
+        <v>400</v>
       </c>
       <c r="K126" s="9"/>
       <c r="L126" s="8">
         <v>3</v>
       </c>
       <c r="M126" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>608</v>
+        <v>519</v>
       </c>
       <c r="O126" s="8" t="s">
-        <v>609</v>
+        <v>520</v>
       </c>
       <c r="P126" s="11"/>
       <c r="Q126" s="8"/>
@@ -13547,18 +13541,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>1</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>610</v>
+        <v>521</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E127" s="10"/>
       <c r="F127" s="9"/>
@@ -13566,13 +13560,13 @@
         <v>1</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>611</v>
+        <v>522</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>612</v>
+        <v>523</v>
       </c>
       <c r="K127" s="9"/>
       <c r="L127" s="8"/>
@@ -13627,18 +13621,18 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>1</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>613</v>
+        <v>524</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D128" s="19" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="E128" s="10"/>
       <c r="F128" s="9"/>
@@ -13649,10 +13643,10 @@
         <v>38</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>614</v>
+        <v>560</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>615</v>
+        <v>525</v>
       </c>
       <c r="K128" s="9"/>
       <c r="L128" s="8">
@@ -13662,10 +13656,10 @@
         <v>38</v>
       </c>
       <c r="N128" s="8" t="s">
-        <v>616</v>
+        <v>536</v>
       </c>
       <c r="O128" s="10" t="s">
-        <v>617</v>
+        <v>526</v>
       </c>
       <c r="P128" s="11"/>
       <c r="Q128" s="8"/>
@@ -13715,40 +13709,40 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="129" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O129"/>
     </row>
-    <row r="130" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O130"/>
     </row>
-    <row r="131" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O131"/>
     </row>
-    <row r="132" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O132"/>
     </row>
-    <row r="133" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O133"/>
     </row>
-    <row r="134" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O134"/>
     </row>
-    <row r="135" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O135"/>
     </row>
-    <row r="136" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O136"/>
     </row>
-    <row r="137" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O137"/>
     </row>
-    <row r="138" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O138"/>
     </row>
-    <row r="139" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:35" x14ac:dyDescent="0.25">
       <c r="O139"/>
     </row>
-    <row r="140" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
       <c r="D140" s="22"/>
@@ -13784,7 +13778,7 @@
       <c r="AH140" s="22"/>
       <c r="AI140" s="23"/>
     </row>
-    <row r="141" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
       <c r="D141" s="22"/>
@@ -13820,7 +13814,7 @@
       <c r="AH141" s="22"/>
       <c r="AI141" s="23"/>
     </row>
-    <row r="142" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
       <c r="D142" s="22"/>
@@ -13856,7 +13850,7 @@
       <c r="AH142" s="22"/>
       <c r="AI142" s="23"/>
     </row>
-    <row r="143" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
       <c r="D143" s="22"/>
@@ -13892,7 +13886,7 @@
       <c r="AH143" s="22"/>
       <c r="AI143" s="23"/>
     </row>
-    <row r="144" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
       <c r="D144" s="22"/>
@@ -13928,7 +13922,7 @@
       <c r="AH144" s="22"/>
       <c r="AI144" s="23"/>
     </row>
-    <row r="145" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
       <c r="D145" s="22"/>
@@ -13964,7 +13958,7 @@
       <c r="AH145" s="22"/>
       <c r="AI145" s="23"/>
     </row>
-    <row r="146" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
       <c r="D146" s="22"/>
@@ -14000,7 +13994,7 @@
       <c r="AH146" s="22"/>
       <c r="AI146" s="23"/>
     </row>
-    <row r="147" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
       <c r="D147" s="22"/>
@@ -14036,7 +14030,7 @@
       <c r="AH147" s="22"/>
       <c r="AI147" s="23"/>
     </row>
-    <row r="148" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
       <c r="D148" s="22"/>
@@ -14072,7 +14066,7 @@
       <c r="AH148" s="22"/>
       <c r="AI148" s="23"/>
     </row>
-    <row r="149" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
       <c r="D149" s="22"/>
@@ -14108,7 +14102,7 @@
       <c r="AH149" s="22"/>
       <c r="AI149" s="23"/>
     </row>
-    <row r="150" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
       <c r="D150" s="22"/>
@@ -14144,7 +14138,7 @@
       <c r="AH150" s="22"/>
       <c r="AI150" s="23"/>
     </row>
-    <row r="151" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
       <c r="D151" s="22"/>
@@ -14180,7 +14174,7 @@
       <c r="AH151" s="22"/>
       <c r="AI151" s="23"/>
     </row>
-    <row r="152" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
       <c r="D152" s="22"/>
@@ -14216,7 +14210,7 @@
       <c r="AH152" s="22"/>
       <c r="AI152" s="23"/>
     </row>
-    <row r="153" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
       <c r="D153" s="22"/>
@@ -14252,7 +14246,7 @@
       <c r="AH153" s="22"/>
       <c r="AI153" s="23"/>
     </row>
-    <row r="154" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
       <c r="D154" s="22"/>
@@ -14288,7 +14282,7 @@
       <c r="AH154" s="22"/>
       <c r="AI154" s="23"/>
     </row>
-    <row r="155" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
       <c r="D155" s="22"/>
@@ -14324,7 +14318,7 @@
       <c r="AH155" s="22"/>
       <c r="AI155" s="23"/>
     </row>
-    <row r="156" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
       <c r="D156" s="22"/>
@@ -14360,7 +14354,7 @@
       <c r="AH156" s="22"/>
       <c r="AI156" s="23"/>
     </row>
-    <row r="157" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B157" s="22"/>
       <c r="C157" s="22"/>
       <c r="D157" s="22"/>
@@ -14396,7 +14390,7 @@
       <c r="AH157" s="22"/>
       <c r="AI157" s="23"/>
     </row>
-    <row r="158" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B158" s="22"/>
       <c r="C158" s="22"/>
       <c r="D158" s="22"/>
@@ -14432,7 +14426,7 @@
       <c r="AH158" s="22"/>
       <c r="AI158" s="23"/>
     </row>
-    <row r="159" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B159" s="22"/>
       <c r="C159" s="22"/>
       <c r="D159" s="22"/>
@@ -14468,7 +14462,7 @@
       <c r="AH159" s="22"/>
       <c r="AI159" s="23"/>
     </row>
-    <row r="160" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
       <c r="D160" s="22"/>
@@ -14504,7 +14498,7 @@
       <c r="AH160" s="22"/>
       <c r="AI160" s="23"/>
     </row>
-    <row r="161" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
       <c r="D161" s="22"/>
@@ -14540,7 +14534,7 @@
       <c r="AH161" s="22"/>
       <c r="AI161" s="23"/>
     </row>
-    <row r="162" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B162" s="22"/>
       <c r="C162" s="22"/>
       <c r="D162" s="22"/>
@@ -14576,7 +14570,7 @@
       <c r="AH162" s="22"/>
       <c r="AI162" s="23"/>
     </row>
-    <row r="163" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B163" s="22"/>
       <c r="C163" s="22"/>
       <c r="D163" s="22"/>
@@ -14612,7 +14606,7 @@
       <c r="AH163" s="22"/>
       <c r="AI163" s="23"/>
     </row>
-    <row r="164" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
       <c r="D164" s="22"/>
@@ -14648,7 +14642,7 @@
       <c r="AH164" s="22"/>
       <c r="AI164" s="23"/>
     </row>
-    <row r="165" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B165" s="22"/>
       <c r="C165" s="22"/>
       <c r="D165" s="22"/>
@@ -14684,7 +14678,7 @@
       <c r="AH165" s="22"/>
       <c r="AI165" s="23"/>
     </row>
-    <row r="166" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B166" s="22"/>
       <c r="C166" s="22"/>
       <c r="D166" s="22"/>
@@ -14720,7 +14714,7 @@
       <c r="AH166" s="22"/>
       <c r="AI166" s="23"/>
     </row>
-    <row r="167" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B167" s="22"/>
       <c r="C167" s="22"/>
       <c r="D167" s="22"/>
@@ -14756,7 +14750,7 @@
       <c r="AH167" s="22"/>
       <c r="AI167" s="23"/>
     </row>
-    <row r="168" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
       <c r="D168" s="22"/>
@@ -14792,7 +14786,7 @@
       <c r="AH168" s="22"/>
       <c r="AI168" s="23"/>
     </row>
-    <row r="169" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
       <c r="D169" s="22"/>
@@ -14828,7 +14822,7 @@
       <c r="AH169" s="22"/>
       <c r="AI169" s="23"/>
     </row>
-    <row r="170" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B170" s="22"/>
       <c r="C170" s="22"/>
       <c r="D170" s="22"/>
@@ -14864,7 +14858,7 @@
       <c r="AH170" s="22"/>
       <c r="AI170" s="23"/>
     </row>
-    <row r="171" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B171" s="22"/>
       <c r="C171" s="22"/>
       <c r="D171" s="22"/>
@@ -14900,7 +14894,7 @@
       <c r="AH171" s="22"/>
       <c r="AI171" s="23"/>
     </row>
-    <row r="172" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B172" s="22"/>
       <c r="C172" s="22"/>
       <c r="D172" s="22"/>
@@ -14936,7 +14930,7 @@
       <c r="AH172" s="22"/>
       <c r="AI172" s="23"/>
     </row>
-    <row r="173" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B173" s="22"/>
       <c r="C173" s="22"/>
       <c r="D173" s="22"/>
@@ -14972,7 +14966,7 @@
       <c r="AH173" s="22"/>
       <c r="AI173" s="23"/>
     </row>
-    <row r="174" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B174" s="22"/>
       <c r="C174" s="22"/>
       <c r="D174" s="22"/>
@@ -15008,7 +15002,7 @@
       <c r="AH174" s="22"/>
       <c r="AI174" s="23"/>
     </row>
-    <row r="175" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B175" s="22"/>
       <c r="C175" s="22"/>
       <c r="D175" s="22"/>
@@ -15044,7 +15038,7 @@
       <c r="AH175" s="22"/>
       <c r="AI175" s="23"/>
     </row>
-    <row r="176" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B176" s="22"/>
       <c r="C176" s="22"/>
       <c r="D176" s="22"/>
@@ -15080,7 +15074,7 @@
       <c r="AH176" s="22"/>
       <c r="AI176" s="23"/>
     </row>
-    <row r="177" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
       <c r="D177" s="22"/>
@@ -15116,7 +15110,7 @@
       <c r="AH177" s="22"/>
       <c r="AI177" s="23"/>
     </row>
-    <row r="178" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B178" s="22"/>
       <c r="C178" s="22"/>
       <c r="D178" s="22"/>
@@ -15152,7 +15146,7 @@
       <c r="AH178" s="22"/>
       <c r="AI178" s="23"/>
     </row>
-    <row r="179" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
       <c r="D179" s="22"/>
@@ -15188,7 +15182,7 @@
       <c r="AH179" s="22"/>
       <c r="AI179" s="23"/>
     </row>
-    <row r="180" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
       <c r="D180" s="22"/>
@@ -15224,7 +15218,7 @@
       <c r="AH180" s="22"/>
       <c r="AI180" s="23"/>
     </row>
-    <row r="181" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>
       <c r="D181" s="22"/>
@@ -15260,7 +15254,7 @@
       <c r="AH181" s="22"/>
       <c r="AI181" s="23"/>
     </row>
-    <row r="182" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B182" s="22"/>
       <c r="C182" s="22"/>
       <c r="D182" s="22"/>
@@ -15296,7 +15290,7 @@
       <c r="AH182" s="22"/>
       <c r="AI182" s="23"/>
     </row>
-    <row r="183" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B183" s="22"/>
       <c r="C183" s="22"/>
       <c r="D183" s="22"/>
@@ -15332,7 +15326,7 @@
       <c r="AH183" s="22"/>
       <c r="AI183" s="23"/>
     </row>
-    <row r="184" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B184" s="22"/>
       <c r="C184" s="22"/>
       <c r="D184" s="22"/>
@@ -15368,7 +15362,7 @@
       <c r="AH184" s="22"/>
       <c r="AI184" s="23"/>
     </row>
-    <row r="185" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
       <c r="D185" s="22"/>
@@ -15404,7 +15398,7 @@
       <c r="AH185" s="22"/>
       <c r="AI185" s="23"/>
     </row>
-    <row r="186" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B186" s="22"/>
       <c r="C186" s="22"/>
       <c r="D186" s="22"/>
@@ -15440,7 +15434,7 @@
       <c r="AH186" s="22"/>
       <c r="AI186" s="23"/>
     </row>
-    <row r="187" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B187" s="22"/>
       <c r="C187" s="22"/>
       <c r="D187" s="22"/>
@@ -15476,7 +15470,7 @@
       <c r="AH187" s="22"/>
       <c r="AI187" s="23"/>
     </row>
-    <row r="188" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B188" s="22"/>
       <c r="C188" s="22"/>
       <c r="D188" s="22"/>
@@ -15512,7 +15506,7 @@
       <c r="AH188" s="22"/>
       <c r="AI188" s="23"/>
     </row>
-    <row r="189" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B189" s="22"/>
       <c r="C189" s="22"/>
       <c r="D189" s="22"/>
@@ -15548,7 +15542,7 @@
       <c r="AH189" s="22"/>
       <c r="AI189" s="23"/>
     </row>
-    <row r="190" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B190" s="22"/>
       <c r="C190" s="22"/>
       <c r="D190" s="22"/>
@@ -15584,7 +15578,7 @@
       <c r="AH190" s="22"/>
       <c r="AI190" s="23"/>
     </row>
-    <row r="191" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B191" s="22"/>
       <c r="C191" s="22"/>
       <c r="D191" s="22"/>
@@ -15620,7 +15614,7 @@
       <c r="AH191" s="22"/>
       <c r="AI191" s="23"/>
     </row>
-    <row r="192" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B192" s="22"/>
       <c r="C192" s="22"/>
       <c r="D192" s="22"/>
@@ -15656,7 +15650,7 @@
       <c r="AH192" s="22"/>
       <c r="AI192" s="23"/>
     </row>
-    <row r="193" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
       <c r="D193" s="22"/>
@@ -15692,7 +15686,7 @@
       <c r="AH193" s="22"/>
       <c r="AI193" s="23"/>
     </row>
-    <row r="194" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B194" s="22"/>
       <c r="C194" s="22"/>
       <c r="D194" s="22"/>
@@ -15728,7 +15722,7 @@
       <c r="AH194" s="22"/>
       <c r="AI194" s="23"/>
     </row>
-    <row r="195" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B195" s="22"/>
       <c r="C195" s="22"/>
       <c r="D195" s="22"/>
@@ -15764,7 +15758,7 @@
       <c r="AH195" s="22"/>
       <c r="AI195" s="23"/>
     </row>
-    <row r="196" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B196" s="22"/>
       <c r="C196" s="22"/>
       <c r="D196" s="22"/>
@@ -15800,7 +15794,7 @@
       <c r="AH196" s="22"/>
       <c r="AI196" s="23"/>
     </row>
-    <row r="197" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B197" s="22"/>
       <c r="C197" s="22"/>
       <c r="D197" s="22"/>
@@ -15836,7 +15830,7 @@
       <c r="AH197" s="22"/>
       <c r="AI197" s="23"/>
     </row>
-    <row r="198" spans="2:35" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B198" s="22"/>
       <c r="C198" s="22"/>
       <c r="D198" s="22"/>
@@ -15872,13 +15866,13 @@
       <c r="AH198" s="22"/>
       <c r="AI198" s="23"/>
     </row>
-    <row r="199" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C199" s="22"/>
     </row>
-    <row r="200" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C200" s="22"/>
     </row>
-    <row r="201" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C201" s="22"/>
     </row>
   </sheetData>

--- a/Master1.0.xlsx
+++ b/Master1.0.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="NaN" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet3!$A$1:$AJ$140</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="617">
   <si>
     <t xml:space="preserve">Change state</t>
   </si>
@@ -190,10 +191,11 @@
     <t xml:space="preserve">Crit</t>
   </si>
   <si>
-    <t xml:space="preserve">Critical Options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Howl: &lt;/b&gt;Gain &lt;b&gt;Monstrous&lt;/b&gt;.</t>
+    <t xml:space="preserve">General Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Howl: &lt;/b&gt;Gain &lt;b&gt;Monstrous&lt;/b&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">Carcinous</t>
@@ -211,7 +213,7 @@
     <t xml:space="preserve">&lt;b&gt;Sideways Scuttle&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Declare a permanent front hex and back hex for your character token. 
+    <t xml:space="preserve">Mark a front hex and back hex for your character token. 
 &lt;br /&gt;You may attack using either hex.
 &lt;br /&gt;You move with your front hex. When you stop moving, place your back hex in any adjacent hex.</t>
   </si>
@@ -311,19 +313,20 @@
     <t xml:space="preserve">Hag</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Symptom Sower: 2 AP + weirdt&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;Symptom Sower:&lt;/b&gt; 2 AP + weirdt</t>
   </si>
   <si>
     <t xml:space="preserve">Inflict any status other than &lt;b&gt;cursed&lt;/b&gt; effect on target being.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Putrefy:&lt;/b&gt; 1AP&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suffer a wound to a stat of your choice and inflict the &lt;b&gt;cursed&lt;/b&gt; status on an adjacent target.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Rake Essence:&lt;/b&gt;If your target is cursed, restore a weirdt. Choose only once per attack.</t>
+    <t xml:space="preserve">&lt;b&gt;Putrefy:&lt;/b&gt; 1AP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suffer a wound to a stat of your choice and inflict the &lt;b&gt;Cursed&lt;/b&gt; status on an adjacent target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of your attacks have the critical option
+&lt;br /&gt;&lt;b&gt;Rake Essence:&lt;/b&gt; If your target is &lt;b&gt;Cursed&lt;/b&gt;, restore a weirdt. Choose only once per attack.</t>
   </si>
   <si>
     <t xml:space="preserve">Hollow</t>
@@ -384,7 +387,7 @@
     <t xml:space="preserve">Whenever you take a move action, gain a charget.&lt;/br&gt;Maximum of 4 charges.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Leap: &lt;/b&gt;4 x charget</t>
+    <t xml:space="preserve">&lt;b&gt;Leap:&lt;/b&gt; 4 x charget</t>
   </si>
   <si>
     <t xml:space="preserve">Leap to target hex and gain &lt;b&gt;Monstrous.&lt;/b&gt;&lt;/br&gt;Your next melee attack this turn hits all targets in range.</t>
@@ -656,7 +659,8 @@
     <t xml:space="preserve">At the start of each turn, gain the &lt;b&gt;Burning&lt;/b&gt; status effect.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Purification:&lt;/b&gt; Remove one of your status effects and inflict it.</t>
   </si>
   <si>
     <t xml:space="preserve">Writhing Mass</t>
@@ -752,7 +756,8 @@
     <t xml:space="preserve">Whenever you gain temporary composure, you may move that many hexes.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Dash:&lt;/b&gt; Take a move action.</t>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Dash:&lt;/b&gt; Take a move action.</t>
   </si>
   <si>
     <t xml:space="preserve">Determined</t>
@@ -813,7 +818,8 @@
     <t xml:space="preserve">Heroic</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to tempcttempct</t>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Rally:&lt;/b&gt; You and one ally gain up to tempcttempct</t>
   </si>
   <si>
     <t xml:space="preserve">I'm Normal</t>
@@ -873,7 +879,8 @@
     <t xml:space="preserve">During map creation, search the boons deck for any card. You may place this on the map in addition to your allotted terrain cards.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Magic Touch:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Magic Touch:&lt;/b&gt; Gain the &lt;b&gt;Imbued&lt;/b&gt; status effect.</t>
   </si>
   <si>
     <t xml:space="preserve">Lucky</t>
@@ -891,7 +898,7 @@
     <t xml:space="preserve">Whenever you would give another creature temporary composure, you may deal that much damage instead.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Bullying&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;Oppression&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Whenever you inflict a status effect, you may reduce that beings composure by 2 (down to a minimum of 1).</t>
@@ -1029,10 +1036,10 @@
 &lt;br /&gt;This blocks line of sight. Melee attacks against beings inside darkness will only hit on a 7 or higher and miss otherwise, they only Crit on a 12.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Creature of the Shadows&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You are unnaffected by darkness</t>
+    <t xml:space="preserve">&lt;b&gt;Slinking&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are unaffected by darkness</t>
   </si>
   <si>
     <t xml:space="preserve">Spiteful</t>
@@ -1068,13 +1075,14 @@
     <t xml:space="preserve">Your next melee attack this turn has range equal to your &lt;span style="color:#27ae60"&gt;&lt;b&gt;Jazz&lt;/b&gt;&lt;/span&gt;.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
+    <t xml:space="preserve">Attacks gain the critical option
+&lt;br /&gt;&lt;b&gt;Puppeteer:&lt;/b&gt; Move the target 2 hexes in any direction.</t>
   </si>
   <si>
     <t xml:space="preserve">Strong Heartbeat</t>
   </si>
   <si>
-    <t xml:space="preserve">Whenever you would heal or refresh a token, heal or refresh one more. </t>
+    <t xml:space="preserve">Whenever you would heal or refresh a stat token, heal or refresh one more. </t>
   </si>
   <si>
     <t xml:space="preserve">Tinkerer</t>
@@ -1147,7 +1155,7 @@
 &lt;br /&gt;This attack can only target your hated target.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;center&gt;Critical Options&lt;/center&gt;</t>
+    <t xml:space="preserve">Limb Criticals</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Omen:&lt;/b&gt; inflict the &lt;b&gt;Cursed&lt;/b&gt; status effect.</t>
@@ -1304,12 +1312,15 @@
     <t xml:space="preserve">Dragonfly Wings</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Fly:&lt;/b&gt;2AP or WeirdT</t>
+    <t xml:space="preserve">&lt;b&gt;Fly:&lt;/b&gt; 2AP or WeirdT</t>
   </si>
   <si>
     <t xml:space="preserve">Make a move action with +1 speed, ignore terrain during this move (within reason).</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapon Critical</t>
+  </si>
+  <si>
     <t xml:space="preserve">Elastic Heart-Spike</t>
   </si>
   <si>
@@ -1331,14 +1342,8 @@
     <t xml:space="preserve">Damage = 2, Reach</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Flame Devourer&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Has the &lt;b&gt;Brutal Strike:&lt;/b&gt; +2 damage crit option against targets that are already &lt;b&gt;Burning&lt;/b&gt;.</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;b&gt;Burn:&lt;/b&gt; Inflict the &lt;b&gt;Burning&lt;/b&gt; status effect.
-&lt;b&gt;Incinerate:&lt;/b&gt; Deal +2 damage if the target is burning.</t>
+&lt;b&gt;Incinerate:&lt;/b&gt; Deal +2 damage if the target is burning. Use only once per attack</t>
   </si>
   <si>
     <t xml:space="preserve">Engraved Slab</t>
@@ -1356,7 +1361,7 @@
     <t xml:space="preserve">Damage = 8, Close</t>
   </si>
   <si>
-    <t xml:space="preserve">Eyes on stalks</t>
+    <t xml:space="preserve">Eyes on Stalks</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Glare: &lt;/b&gt;1AP + weirdT</t>
@@ -1425,7 +1430,7 @@
     <t xml:space="preserve">Recharge this item.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Ungrown&lt;/b&gt;</t>
+    <t xml:space="preserve">&lt;b&gt;Bare&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">This limb starts with no charges.</t>
@@ -1484,7 +1489,7 @@
     <t xml:space="preserve">Horns</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Charge!:&lt;/b&gt; 2 AP</t>
+    <t xml:space="preserve">&lt;b&gt;Charge:&lt;/b&gt; 2 AP</t>
   </si>
   <si>
     <t xml:space="preserve">Damage = hexes moved, Close
@@ -2098,7 +2103,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2153,6 +2158,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2696,9 +2705,6 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B2" s="8" t="s">
         <v>36</v>
       </c>
@@ -2805,10 +2811,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
         <v>47</v>
       </c>
@@ -2851,7 +2854,7 @@
       </c>
       <c r="Q3" s="13"/>
       <c r="R3" s="10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>53</v>
@@ -2859,7 +2862,7 @@
       <c r="T3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="14" t="s">
         <v>55</v>
       </c>
       <c r="V3" s="11"/>
@@ -2894,21 +2897,18 @@
       </c>
       <c r="AH3" s="10" t="n">
         <f aca="false">AJ3+AA$2</f>
-        <v>63.4</v>
+        <v>65.6</v>
       </c>
       <c r="AI3" s="10" t="n">
         <f aca="false">AH3+Z$2</f>
-        <v>62.3</v>
+        <v>64.5</v>
       </c>
       <c r="AJ3" s="12" t="n">
         <f aca="false">W$2+X$2*(R3-1)+2*Y$2</f>
-        <v>69.4</v>
+        <v>71.6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B4" s="8" t="s">
         <v>56</v>
       </c>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S4" s="12" t="s">
         <v>39</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="10"/>
-      <c r="X4" s="14" t="s">
+      <c r="X4" s="15" t="s">
         <v>64</v>
       </c>
       <c r="Y4" s="10"/>
@@ -2998,21 +2998,18 @@
       </c>
       <c r="AH4" s="10" t="n">
         <f aca="false">AJ4+AA$2</f>
-        <v>70</v>
+        <v>65.6</v>
       </c>
       <c r="AI4" s="10" t="n">
         <f aca="false">AH4+Z$2</f>
-        <v>68.9</v>
+        <v>64.5</v>
       </c>
       <c r="AJ4" s="12" t="n">
         <f aca="false">W$2+X$2*(R4-1)+2*Y$2</f>
-        <v>76</v>
+        <v>71.6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>65</v>
       </c>
@@ -3062,7 +3059,7 @@
       <c r="U5" s="10"/>
       <c r="V5" s="11"/>
       <c r="W5" s="10"/>
-      <c r="X5" s="15" t="s">
+      <c r="X5" s="16" t="s">
         <v>71</v>
       </c>
       <c r="Y5" s="10"/>
@@ -3106,9 +3103,6 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B6" s="8" t="s">
         <v>72</v>
       </c>
@@ -3156,7 +3150,7 @@
       <c r="U6" s="10"/>
       <c r="V6" s="11"/>
       <c r="W6" s="10"/>
-      <c r="X6" s="16" t="s">
+      <c r="X6" s="17" t="s">
         <v>77</v>
       </c>
       <c r="Y6" s="10"/>
@@ -3200,9 +3194,6 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B7" s="8" t="s">
         <v>78</v>
       </c>
@@ -3260,7 +3251,7 @@
       </c>
       <c r="V7" s="11"/>
       <c r="W7" s="10"/>
-      <c r="X7" s="16"/>
+      <c r="X7" s="17"/>
       <c r="Y7" s="10"/>
       <c r="Z7" s="10"/>
       <c r="AA7" s="10"/>
@@ -3302,9 +3293,6 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B8" s="8" t="s">
         <v>86</v>
       </c>
@@ -3393,10 +3381,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
         <v>91</v>
       </c>
@@ -3447,7 +3432,7 @@
       <c r="T9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="U9" s="10" t="s">
+      <c r="U9" s="14" t="s">
         <v>96</v>
       </c>
       <c r="V9" s="11"/>
@@ -3494,9 +3479,6 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B10" s="8" t="s">
         <v>97</v>
       </c>
@@ -3586,9 +3568,6 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B11" s="8" t="s">
         <v>102</v>
       </c>
@@ -3688,9 +3667,6 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B12" s="8" t="s">
         <v>108</v>
       </c>
@@ -3780,9 +3756,6 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B13" s="8" t="s">
         <v>113</v>
       </c>
@@ -3872,9 +3845,6 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B14" s="8" t="s">
         <v>118</v>
       </c>
@@ -3972,9 +3942,6 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B15" s="8" t="s">
         <v>125</v>
       </c>
@@ -4074,9 +4041,6 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="109.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B16" s="8" t="s">
         <v>133</v>
       </c>
@@ -4111,7 +4075,7 @@
       <c r="N16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="17" t="s">
+      <c r="O16" s="18" t="s">
         <v>136</v>
       </c>
       <c r="P16" s="12" t="s">
@@ -4166,9 +4130,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B17" s="8" t="s">
         <v>138</v>
       </c>
@@ -4268,9 +4229,6 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B18" s="8" t="s">
         <v>146</v>
       </c>
@@ -4368,9 +4326,6 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B19" s="8" t="s">
         <v>153</v>
       </c>
@@ -4468,9 +4423,6 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B20" s="8" t="s">
         <v>161</v>
       </c>
@@ -4560,9 +4512,6 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B21" s="8" t="s">
         <v>166</v>
       </c>
@@ -4652,9 +4601,6 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B22" s="8" t="s">
         <v>171</v>
       </c>
@@ -4756,9 +4702,6 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B23" s="8" t="s">
         <v>176</v>
       </c>
@@ -4858,9 +4801,6 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B24" s="8" t="s">
         <v>181</v>
       </c>
@@ -4875,7 +4815,7 @@
         <v>FormB</v>
       </c>
       <c r="F24" s="10"/>
-      <c r="G24" s="18"/>
+      <c r="G24" s="19"/>
       <c r="H24" s="10" t="n">
         <v>1</v>
       </c>
@@ -4888,7 +4828,7 @@
       <c r="K24" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="L24" s="18"/>
+      <c r="L24" s="19"/>
       <c r="M24" s="10" t="n">
         <v>4</v>
       </c>
@@ -4901,12 +4841,12 @@
       <c r="P24" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="Q24" s="19"/>
+      <c r="Q24" s="20"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="19"/>
       <c r="W24" s="10"/>
       <c r="X24" s="10"/>
       <c r="Y24" s="10"/>
@@ -4950,9 +4890,6 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B25" s="8" t="s">
         <v>186</v>
       </c>
@@ -5042,9 +4979,6 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B26" s="8" t="s">
         <v>191</v>
       </c>
@@ -5144,9 +5078,6 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B27" s="8" t="s">
         <v>199</v>
       </c>
@@ -5192,12 +5123,12 @@
         <v>9.5</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="T27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="U27" s="10" t="s">
+      <c r="U27" s="14" t="s">
         <v>204</v>
       </c>
       <c r="V27" s="11"/>
@@ -5243,10 +5174,7 @@
         <v>69.4</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="28" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="8" t="s">
         <v>205</v>
       </c>
@@ -5335,17 +5263,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="29" customFormat="false" ht="55.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E29" s="9" t="str">
@@ -5419,24 +5344,21 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="30" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="8" t="s">
         <v>214</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E30" s="9" t="str">
         <f aca="false">D30&amp;C30</f>
         <v>ImpressionB</v>
       </c>
-      <c r="F30" s="12"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="11"/>
       <c r="H30" s="10" t="n">
         <v>1</v>
@@ -5444,14 +5366,17 @@
       <c r="I30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="12" t="s">
         <v>216</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
@@ -5500,17 +5425,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="31" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
         <v>217</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E31" s="9" t="str">
@@ -5518,7 +5440,7 @@
         <v>ImpressionB</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="18"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="10" t="n">
         <v>1</v>
       </c>
@@ -5531,17 +5453,17 @@
       <c r="K31" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="L31" s="18"/>
+      <c r="L31" s="19"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
-      <c r="Q31" s="19"/>
+      <c r="Q31" s="20"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
-      <c r="V31" s="18"/>
+      <c r="V31" s="19"/>
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
       <c r="Y31" s="10"/>
@@ -5584,17 +5506,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="32" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="8" t="s">
         <v>220</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E32" s="9" t="str">
@@ -5602,7 +5521,7 @@
         <v>ImpressionA</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="18"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
@@ -5615,17 +5534,17 @@
       <c r="K32" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="L32" s="18"/>
+      <c r="L32" s="19"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
-      <c r="Q32" s="19"/>
+      <c r="Q32" s="20"/>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
-      <c r="V32" s="18"/>
+      <c r="V32" s="19"/>
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="10"/>
@@ -5668,17 +5587,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="33" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="8" t="s">
         <v>223</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E33" s="9" t="str">
@@ -5686,7 +5602,7 @@
         <v>ImpressionA</v>
       </c>
       <c r="F33" s="10"/>
-      <c r="G33" s="18"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="10" t="n">
         <v>1</v>
       </c>
@@ -5699,17 +5615,17 @@
       <c r="K33" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="L33" s="18"/>
+      <c r="L33" s="19"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
-      <c r="Q33" s="19"/>
+      <c r="Q33" s="20"/>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
-      <c r="V33" s="18"/>
+      <c r="V33" s="19"/>
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
       <c r="Y33" s="10"/>
@@ -5752,17 +5668,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="34" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
         <v>225</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E34" s="9" t="str">
@@ -5770,7 +5683,7 @@
         <v>ImpressionB</v>
       </c>
       <c r="F34" s="10"/>
-      <c r="G34" s="18"/>
+      <c r="G34" s="19"/>
       <c r="H34" s="10" t="n">
         <v>1</v>
       </c>
@@ -5783,17 +5696,17 @@
       <c r="K34" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="L34" s="18"/>
+      <c r="L34" s="19"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
-      <c r="Q34" s="19"/>
+      <c r="Q34" s="20"/>
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
-      <c r="V34" s="18"/>
+      <c r="V34" s="19"/>
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
       <c r="Y34" s="10"/>
@@ -5836,17 +5749,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="35" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="8" t="s">
         <v>227</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E35" s="9" t="str">
@@ -5920,17 +5830,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="36" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="8" t="s">
         <v>230</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E36" s="9" t="str">
@@ -6004,17 +5911,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="37" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E37" s="9" t="str">
@@ -6096,17 +6000,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="38" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="8" t="s">
         <v>236</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E38" s="9" t="str">
@@ -6180,17 +6081,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="39" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
         <v>239</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E39" s="9" t="str">
@@ -6264,17 +6162,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="40" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E40" s="9" t="str">
@@ -6348,17 +6243,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="41" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="8" t="s">
         <v>243</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E41" s="9" t="str">
@@ -6434,17 +6326,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="42" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="8" t="s">
         <v>247</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E42" s="9" t="str">
@@ -6526,17 +6415,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="43" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E43" s="9" t="str">
@@ -6610,17 +6496,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="44" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="8" t="s">
         <v>254</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E44" s="9" t="str">
@@ -6630,7 +6513,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="11"/>
       <c r="H44" s="10" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>53</v>
@@ -6659,15 +6542,15 @@
       <c r="AA44" s="10"/>
       <c r="AB44" s="10" t="n">
         <f aca="false">AD44+AA$2</f>
-        <v>20</v>
+        <v>57.4</v>
       </c>
       <c r="AC44" s="10" t="n">
         <f aca="false">AB44+Z$2</f>
-        <v>18.9</v>
+        <v>56.3</v>
       </c>
       <c r="AD44" s="10" t="n">
         <f aca="false">W$2+X$2*(H44-1)</f>
-        <v>26</v>
+        <v>63.4</v>
       </c>
       <c r="AE44" s="10" t="n">
         <f aca="false">AG44+AA$2</f>
@@ -6694,17 +6577,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="45" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="8" t="s">
         <v>256</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E45" s="9" t="str">
@@ -6794,17 +6674,14 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="46" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="8" t="s">
         <v>263</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E46" s="9" t="str">
@@ -6886,17 +6763,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="47" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="s">
         <v>268</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E47" s="9" t="str">
@@ -6972,17 +6846,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="48" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="8" t="s">
         <v>272</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E48" s="9" t="str">
@@ -7064,17 +6935,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="49" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="8" t="s">
         <v>276</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E49" s="9" t="str">
@@ -7148,17 +7016,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="50" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="8" t="s">
         <v>278</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E50" s="9" t="str">
@@ -7184,7 +7049,7 @@
         <v>6</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>281</v>
@@ -7240,17 +7105,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="51" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="8" t="s">
         <v>283</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E51" s="9" t="str">
@@ -7324,17 +7186,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="52" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="8" t="s">
         <v>286</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E52" s="9" t="str">
@@ -7408,17 +7267,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="53" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="8" t="s">
         <v>289</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E53" s="9" t="str">
@@ -7492,17 +7348,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="54" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="8" t="s">
         <v>292</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E54" s="9" t="str">
@@ -7576,17 +7429,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="55" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E55" s="9" t="str">
@@ -7668,17 +7518,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="56" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="8" t="s">
         <v>300</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E56" s="9" t="str">
@@ -7752,17 +7599,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="57" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="8" t="s">
         <v>302</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E57" s="9" t="str">
@@ -7844,17 +7688,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="58" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="8" t="s">
         <v>307</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E58" s="9" t="str">
@@ -7936,17 +7777,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="59" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="22" t="s">
         <v>211</v>
       </c>
       <c r="E59" s="9" t="str">
@@ -8028,17 +7866,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="60" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="8" t="s">
         <v>316</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E60" s="9" t="str">
@@ -8120,17 +7955,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="61" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="8" t="s">
         <v>321</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E61" s="9" t="str">
@@ -8204,17 +8036,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="62" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="8" t="s">
         <v>323</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E62" s="9" t="str">
@@ -8296,17 +8125,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="63" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="8" t="s">
         <v>328</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E63" s="9" t="str">
@@ -8380,17 +8206,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="64" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="8" t="s">
         <v>330</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E64" s="9" t="str">
@@ -8464,17 +8287,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="65" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="8" t="s">
         <v>333</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E65" s="9" t="str">
@@ -8548,17 +8368,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="66" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="8" t="s">
         <v>336</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D66" s="20" t="s">
+      <c r="D66" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E66" s="9" t="str">
@@ -8589,7 +8406,7 @@
       <c r="O66" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="P66" s="10" t="s">
+      <c r="P66" s="14" t="s">
         <v>339</v>
       </c>
       <c r="Q66" s="13"/>
@@ -8640,17 +8457,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="67" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="8" t="s">
         <v>340</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D67" s="20" t="s">
+      <c r="D67" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E67" s="9" t="str">
@@ -8724,17 +8538,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="68" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="8" t="s">
         <v>342</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D68" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E68" s="9" t="str">
@@ -8816,17 +8627,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="69" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="8" t="s">
         <v>347</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D69" s="20" t="s">
+      <c r="D69" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E69" s="9" t="str">
@@ -8908,17 +8716,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="70" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="8" t="s">
         <v>352</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D70" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E70" s="9" t="str">
@@ -8992,17 +8797,14 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>1</v>
-      </c>
+    <row r="71" customFormat="false" ht="56.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="8" t="s">
         <v>355</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D71" s="20" t="s">
+      <c r="D71" s="21" t="s">
         <v>211</v>
       </c>
       <c r="E71" s="9" t="str">
@@ -9077,16 +8879,13 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B72" s="8" t="s">
         <v>358</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E72" s="9" t="str">
@@ -9094,7 +8893,7 @@
         <v>LimbA</v>
       </c>
       <c r="F72" s="10"/>
-      <c r="G72" s="18"/>
+      <c r="G72" s="19"/>
       <c r="H72" s="10" t="n">
         <v>1</v>
       </c>
@@ -9107,7 +8906,7 @@
       <c r="K72" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="L72" s="18"/>
+      <c r="L72" s="19"/>
       <c r="M72" s="10" t="n">
         <v>5</v>
       </c>
@@ -9120,7 +8919,7 @@
       <c r="P72" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="Q72" s="19"/>
+      <c r="Q72" s="20"/>
       <c r="R72" s="10" t="n">
         <v>9.5</v>
       </c>
@@ -9133,7 +8932,7 @@
       <c r="U72" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="V72" s="18"/>
+      <c r="V72" s="19"/>
       <c r="W72" s="10"/>
       <c r="X72" s="10"/>
       <c r="Y72" s="10"/>
@@ -9177,16 +8976,13 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B73" s="8" t="s">
         <v>367</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E73" s="9" t="str">
@@ -9194,7 +8990,7 @@
         <v>LimbB</v>
       </c>
       <c r="F73" s="10"/>
-      <c r="G73" s="18"/>
+      <c r="G73" s="19"/>
       <c r="H73" s="10" t="n">
         <v>1</v>
       </c>
@@ -9207,7 +9003,7 @@
       <c r="K73" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="L73" s="18"/>
+      <c r="L73" s="19"/>
       <c r="M73" s="10" t="n">
         <v>10</v>
       </c>
@@ -9220,12 +9016,12 @@
       <c r="P73" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="Q73" s="19"/>
+      <c r="Q73" s="20"/>
       <c r="R73" s="10"/>
       <c r="S73" s="10"/>
       <c r="T73" s="10"/>
       <c r="U73" s="10"/>
-      <c r="V73" s="18"/>
+      <c r="V73" s="19"/>
       <c r="W73" s="10"/>
       <c r="X73" s="10"/>
       <c r="Y73" s="10"/>
@@ -9269,16 +9065,13 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B74" s="8" t="s">
         <v>371</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="D74" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E74" s="9" t="str">
@@ -9361,16 +9154,13 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B75" s="8" t="s">
         <v>376</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E75" s="9" t="str">
@@ -9378,7 +9168,7 @@
         <v>LimbB</v>
       </c>
       <c r="F75" s="10"/>
-      <c r="G75" s="18"/>
+      <c r="G75" s="19"/>
       <c r="H75" s="10" t="n">
         <v>1</v>
       </c>
@@ -9391,9 +9181,9 @@
       <c r="K75" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="L75" s="18"/>
+      <c r="L75" s="19"/>
       <c r="M75" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75" s="10" t="s">
         <v>42</v>
@@ -9404,12 +9194,12 @@
       <c r="P75" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="Q75" s="19"/>
+      <c r="Q75" s="20"/>
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
       <c r="T75" s="10"/>
       <c r="U75" s="10"/>
-      <c r="V75" s="18"/>
+      <c r="V75" s="19"/>
       <c r="W75" s="10"/>
       <c r="X75" s="10"/>
       <c r="Y75" s="10"/>
@@ -9429,15 +9219,15 @@
       </c>
       <c r="AE75" s="10" t="n">
         <f aca="false">AG75+AA$2</f>
-        <v>36.2</v>
+        <v>40.6</v>
       </c>
       <c r="AF75" s="10" t="n">
         <f aca="false">AE75+Z$2</f>
-        <v>35.1</v>
+        <v>39.5</v>
       </c>
       <c r="AG75" s="10" t="n">
         <f aca="false">W$2+X$2*(M75-1)+Y$2</f>
-        <v>42.2</v>
+        <v>46.6</v>
       </c>
       <c r="AH75" s="10" t="n">
         <f aca="false">AJ75+AA$2</f>
@@ -9453,16 +9243,13 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B76" s="8" t="s">
         <v>381</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E76" s="9" t="str">
@@ -9545,16 +9332,13 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B77" s="8" t="s">
         <v>386</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E77" s="9" t="str">
@@ -9637,16 +9421,13 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B78" s="8" t="s">
         <v>390</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E78" s="9" t="str">
@@ -9729,16 +9510,13 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B79" s="8" t="s">
         <v>394</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E79" s="9" t="str">
@@ -9821,16 +9599,13 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B80" s="8" t="s">
         <v>399</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E80" s="9" t="str">
@@ -9915,16 +9690,13 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B81" s="8" t="s">
         <v>404</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D81" s="21" t="s">
+      <c r="D81" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E81" s="9" t="str">
@@ -10007,16 +9779,13 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B82" s="8" t="s">
         <v>409</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E82" s="9" t="str">
@@ -10107,16 +9876,13 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B83" s="8" t="s">
         <v>415</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E83" s="9" t="str">
@@ -10139,7 +9905,7 @@
       </c>
       <c r="L83" s="11"/>
       <c r="M83" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N83" s="10" t="s">
         <v>42</v>
@@ -10158,7 +9924,7 @@
         <v>53</v>
       </c>
       <c r="T83" s="10" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="U83" s="10" t="s">
         <v>414</v>
@@ -10183,15 +9949,15 @@
       </c>
       <c r="AE83" s="10" t="n">
         <f aca="false">AG83+AA$2</f>
-        <v>31.8</v>
+        <v>40.6</v>
       </c>
       <c r="AF83" s="10" t="n">
         <f aca="false">AE83+Z$2</f>
-        <v>30.7</v>
+        <v>39.5</v>
       </c>
       <c r="AG83" s="10" t="n">
         <f aca="false">W$2+X$2*(M83-1)+Y$2</f>
-        <v>37.8</v>
+        <v>46.6</v>
       </c>
       <c r="AH83" s="10" t="n">
         <f aca="false">AJ83+AA$2</f>
@@ -10207,16 +9973,13 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B84" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E84" s="9" t="str">
@@ -10232,10 +9995,10 @@
         <v>362</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L84" s="11"/>
       <c r="M84" s="10"/>
@@ -10253,7 +10016,7 @@
         <v>365</v>
       </c>
       <c r="U84" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="V84" s="11"/>
       <c r="W84" s="10"/>
@@ -10299,16 +10062,13 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B85" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D85" s="21" t="s">
+      <c r="D85" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E85" s="9" t="str">
@@ -10324,27 +10084,19 @@
         <v>362</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L85" s="11"/>
-      <c r="M85" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N85" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>426</v>
-      </c>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
       <c r="Q85" s="13"/>
       <c r="R85" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S85" s="10" t="s">
         <v>53</v>
@@ -10353,7 +10105,7 @@
         <v>365</v>
       </c>
       <c r="U85" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="V85" s="11"/>
       <c r="W85" s="10"/>
@@ -10375,40 +10127,37 @@
       </c>
       <c r="AE85" s="10" t="n">
         <f aca="false">AG85+AA$2</f>
-        <v>31.8</v>
+        <v>18.6</v>
       </c>
       <c r="AF85" s="10" t="n">
         <f aca="false">AE85+Z$2</f>
-        <v>30.7</v>
+        <v>17.5</v>
       </c>
       <c r="AG85" s="10" t="n">
         <f aca="false">W$2+X$2*(M85-1)+Y$2</f>
-        <v>37.8</v>
+        <v>24.6</v>
       </c>
       <c r="AH85" s="10" t="n">
         <f aca="false">AJ85+AA$2</f>
-        <v>61.2</v>
+        <v>56.8</v>
       </c>
       <c r="AI85" s="10" t="n">
         <f aca="false">AH85+Z$2</f>
-        <v>60.1</v>
+        <v>55.7</v>
       </c>
       <c r="AJ85" s="12" t="n">
         <f aca="false">W$2+X$2*(R85-1)+2*Y$2</f>
-        <v>67.2</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B86" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D86" s="21" t="s">
+      <c r="D86" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E86" s="9" t="str">
@@ -10424,10 +10173,10 @@
         <v>42</v>
       </c>
       <c r="J86" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="K86" s="12" t="s">
         <v>429</v>
-      </c>
-      <c r="K86" s="12" t="s">
-        <v>430</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" s="10" t="n">
@@ -10437,10 +10186,10 @@
         <v>362</v>
       </c>
       <c r="O86" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="P86" s="10" t="s">
         <v>431</v>
-      </c>
-      <c r="P86" s="10" t="s">
-        <v>432</v>
       </c>
       <c r="Q86" s="13"/>
       <c r="R86" s="10"/>
@@ -10491,16 +10240,13 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B87" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E87" s="9" t="str">
@@ -10516,10 +10262,10 @@
         <v>42</v>
       </c>
       <c r="J87" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="K87" s="12" t="s">
         <v>434</v>
-      </c>
-      <c r="K87" s="12" t="s">
-        <v>435</v>
       </c>
       <c r="L87" s="11"/>
       <c r="M87" s="10" t="n">
@@ -10529,10 +10275,10 @@
         <v>362</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="P87" s="12" t="s">
         <v>436</v>
-      </c>
-      <c r="P87" s="12" t="s">
-        <v>437</v>
       </c>
       <c r="Q87" s="13"/>
       <c r="R87" s="10"/>
@@ -10583,16 +10329,13 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B88" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E88" s="9" t="str">
@@ -10608,10 +10351,10 @@
         <v>39</v>
       </c>
       <c r="J88" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="K88" s="12" t="s">
         <v>439</v>
-      </c>
-      <c r="K88" s="12" t="s">
-        <v>440</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" s="10" t="n">
@@ -10621,10 +10364,10 @@
         <v>39</v>
       </c>
       <c r="O88" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="P88" s="10" t="s">
         <v>441</v>
-      </c>
-      <c r="P88" s="10" t="s">
-        <v>442</v>
       </c>
       <c r="Q88" s="13"/>
       <c r="R88" s="10"/>
@@ -10675,16 +10418,13 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B89" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E89" s="9" t="str">
@@ -10692,7 +10432,7 @@
         <v>LimbA</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="10" t="n">
@@ -10702,10 +10442,10 @@
         <v>42</v>
       </c>
       <c r="J89" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="K89" s="12" t="s">
         <v>445</v>
-      </c>
-      <c r="K89" s="12" t="s">
-        <v>446</v>
       </c>
       <c r="L89" s="11"/>
       <c r="M89" s="10" t="n">
@@ -10715,10 +10455,10 @@
         <v>39</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>447</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>448</v>
       </c>
       <c r="Q89" s="13"/>
       <c r="R89" s="10" t="n">
@@ -10731,7 +10471,7 @@
         <v>75</v>
       </c>
       <c r="U89" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="V89" s="11"/>
       <c r="W89" s="10"/>
@@ -10777,16 +10517,13 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B90" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E90" s="9" t="str">
@@ -10794,7 +10531,7 @@
         <v>LimbB</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="10" t="n">
@@ -10804,10 +10541,10 @@
         <v>362</v>
       </c>
       <c r="J90" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="K90" s="12" t="s">
         <v>452</v>
-      </c>
-      <c r="K90" s="12" t="s">
-        <v>453</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="10" t="n">
@@ -10817,10 +10554,10 @@
         <v>42</v>
       </c>
       <c r="O90" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="P90" s="10" t="s">
         <v>454</v>
-      </c>
-      <c r="P90" s="10" t="s">
-        <v>455</v>
       </c>
       <c r="Q90" s="13"/>
       <c r="R90" s="10" t="n">
@@ -10830,10 +10567,10 @@
         <v>39</v>
       </c>
       <c r="T90" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="U90" s="10" t="s">
         <v>456</v>
-      </c>
-      <c r="U90" s="10" t="s">
-        <v>457</v>
       </c>
       <c r="V90" s="11"/>
       <c r="W90" s="10"/>
@@ -10879,16 +10616,13 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B91" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E91" s="9" t="str">
@@ -10904,10 +10638,10 @@
         <v>362</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L91" s="11"/>
       <c r="M91" s="12" t="n">
@@ -10920,7 +10654,7 @@
         <v>365</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q91" s="13"/>
       <c r="R91" s="10"/>
@@ -10971,16 +10705,13 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B92" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E92" s="9" t="str">
@@ -10996,10 +10727,10 @@
         <v>362</v>
       </c>
       <c r="J92" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="K92" s="12" t="s">
         <v>462</v>
-      </c>
-      <c r="K92" s="12" t="s">
-        <v>463</v>
       </c>
       <c r="L92" s="11"/>
       <c r="M92" s="10" t="n">
@@ -11009,10 +10740,10 @@
         <v>362</v>
       </c>
       <c r="O92" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="P92" s="10" t="s">
         <v>464</v>
-      </c>
-      <c r="P92" s="10" t="s">
-        <v>465</v>
       </c>
       <c r="Q92" s="13"/>
       <c r="R92" s="12" t="n">
@@ -11025,7 +10756,7 @@
         <v>365</v>
       </c>
       <c r="U92" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="V92" s="11"/>
       <c r="W92" s="10"/>
@@ -11071,16 +10802,13 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B93" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" s="23" t="s">
         <v>359</v>
       </c>
       <c r="E93" s="9" t="str">
@@ -11096,10 +10824,10 @@
         <v>362</v>
       </c>
       <c r="J93" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="K93" s="12" t="s">
         <v>467</v>
-      </c>
-      <c r="K93" s="12" t="s">
-        <v>468</v>
       </c>
       <c r="L93" s="11"/>
       <c r="M93" s="10"/>
@@ -11155,16 +10883,13 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B94" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E94" s="9" t="str">
@@ -11180,7 +10905,7 @@
         <v>362</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K94" s="12" t="s">
         <v>369</v>
@@ -11193,10 +10918,10 @@
         <v>39</v>
       </c>
       <c r="O94" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="P94" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="P94" s="10" t="s">
-        <v>472</v>
       </c>
       <c r="Q94" s="13"/>
       <c r="R94" s="10" t="n">
@@ -11209,7 +10934,7 @@
         <v>365</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V94" s="11"/>
       <c r="W94" s="10"/>
@@ -11255,16 +10980,13 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B95" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E95" s="9" t="str">
@@ -11280,10 +11002,10 @@
         <v>362</v>
       </c>
       <c r="J95" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="K95" s="12" t="s">
         <v>475</v>
-      </c>
-      <c r="K95" s="12" t="s">
-        <v>476</v>
       </c>
       <c r="L95" s="11"/>
       <c r="M95" s="10" t="n">
@@ -11293,10 +11015,10 @@
         <v>362</v>
       </c>
       <c r="O95" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="P95" s="24" t="s">
         <v>477</v>
-      </c>
-      <c r="P95" s="23" t="s">
-        <v>478</v>
       </c>
       <c r="Q95" s="13"/>
       <c r="R95" s="10"/>
@@ -11347,16 +11069,13 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B96" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E96" s="9" t="str">
@@ -11372,7 +11091,7 @@
         <v>362</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K96" s="12" t="s">
         <v>392</v>
@@ -11385,10 +11104,10 @@
         <v>362</v>
       </c>
       <c r="O96" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="P96" s="10" t="s">
         <v>481</v>
-      </c>
-      <c r="P96" s="10" t="s">
-        <v>482</v>
       </c>
       <c r="Q96" s="13"/>
       <c r="R96" s="10"/>
@@ -11439,16 +11158,13 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B97" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E97" s="9" t="str">
@@ -11464,10 +11180,10 @@
         <v>362</v>
       </c>
       <c r="J97" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="K97" s="12" t="s">
         <v>484</v>
-      </c>
-      <c r="K97" s="12" t="s">
-        <v>485</v>
       </c>
       <c r="L97" s="11"/>
       <c r="M97" s="10" t="n">
@@ -11477,10 +11193,10 @@
         <v>154</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>486</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>487</v>
       </c>
       <c r="Q97" s="13"/>
       <c r="R97" s="10"/>
@@ -11531,16 +11247,13 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B98" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D98" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E98" s="9" t="str">
@@ -11548,7 +11261,7 @@
         <v>LimbA</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="10" t="n">
@@ -11558,10 +11271,10 @@
         <v>42</v>
       </c>
       <c r="J98" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="K98" s="12" t="s">
         <v>490</v>
-      </c>
-      <c r="K98" s="12" t="s">
-        <v>491</v>
       </c>
       <c r="L98" s="11"/>
       <c r="M98" s="10" t="n">
@@ -11571,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="O98" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="P98" s="10" t="s">
         <v>492</v>
-      </c>
-      <c r="P98" s="10" t="s">
-        <v>493</v>
       </c>
       <c r="Q98" s="13"/>
       <c r="R98" s="10"/>
@@ -11625,16 +11338,13 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B99" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="21" t="s">
+      <c r="D99" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E99" s="9" t="str">
@@ -11650,7 +11360,7 @@
         <v>362</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K99" s="12" t="s">
         <v>392</v>
@@ -11663,10 +11373,10 @@
         <v>39</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="P99" s="12" t="s">
         <v>496</v>
-      </c>
-      <c r="P99" s="12" t="s">
-        <v>497</v>
       </c>
       <c r="Q99" s="13"/>
       <c r="R99" s="10"/>
@@ -11717,16 +11427,13 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B100" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D100" s="21" t="s">
+      <c r="D100" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E100" s="9" t="str">
@@ -11742,10 +11449,10 @@
         <v>362</v>
       </c>
       <c r="J100" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="K100" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="K100" s="12" t="s">
-        <v>500</v>
       </c>
       <c r="L100" s="11"/>
       <c r="M100" s="10" t="n">
@@ -11755,10 +11462,10 @@
         <v>39</v>
       </c>
       <c r="O100" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="P100" s="10" t="s">
         <v>501</v>
-      </c>
-      <c r="P100" s="10" t="s">
-        <v>502</v>
       </c>
       <c r="Q100" s="13"/>
       <c r="R100" s="10"/>
@@ -11809,16 +11516,13 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B101" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D101" s="21" t="s">
+      <c r="D101" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E101" s="9" t="str">
@@ -11834,14 +11538,14 @@
         <v>362</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K101" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L101" s="11"/>
       <c r="M101" s="10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N101" s="10" t="s">
         <v>53</v>
@@ -11850,7 +11554,7 @@
         <v>365</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q101" s="13"/>
       <c r="R101" s="10"/>
@@ -11877,15 +11581,15 @@
       </c>
       <c r="AE101" s="10" t="n">
         <f aca="false">AG101+AA$2</f>
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="AF101" s="10" t="n">
         <f aca="false">AE101+Z$2</f>
-        <v>61.5</v>
+        <v>63.7</v>
       </c>
       <c r="AG101" s="10" t="n">
         <f aca="false">W$2+X$2*(M101-1)+Y$2</f>
-        <v>68.6</v>
+        <v>70.8</v>
       </c>
       <c r="AH101" s="10" t="n">
         <f aca="false">AJ101+AA$2</f>
@@ -11901,16 +11605,13 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B102" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D102" s="21" t="s">
+      <c r="D102" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E102" s="9" t="str">
@@ -11926,10 +11627,10 @@
         <v>154</v>
       </c>
       <c r="J102" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="K102" s="12" t="s">
         <v>507</v>
-      </c>
-      <c r="K102" s="12" t="s">
-        <v>508</v>
       </c>
       <c r="L102" s="11"/>
       <c r="M102" s="10" t="n">
@@ -11939,10 +11640,10 @@
         <v>39</v>
       </c>
       <c r="O102" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="P102" s="10" t="s">
         <v>509</v>
-      </c>
-      <c r="P102" s="10" t="s">
-        <v>510</v>
       </c>
       <c r="Q102" s="13"/>
       <c r="R102" s="10"/>
@@ -11993,16 +11694,13 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B103" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E103" s="9" t="str">
@@ -12018,10 +11716,10 @@
         <v>362</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L103" s="11"/>
       <c r="M103" s="10" t="n">
@@ -12031,10 +11729,10 @@
         <v>42</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>513</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>514</v>
       </c>
       <c r="Q103" s="13"/>
       <c r="R103" s="10"/>
@@ -12085,16 +11783,13 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B104" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="D104" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E104" s="9" t="str">
@@ -12110,7 +11805,7 @@
         <v>362</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K104" s="12" t="s">
         <v>369</v>
@@ -12123,10 +11818,10 @@
         <v>39</v>
       </c>
       <c r="O104" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="P104" s="10" t="s">
         <v>517</v>
-      </c>
-      <c r="P104" s="10" t="s">
-        <v>518</v>
       </c>
       <c r="Q104" s="13"/>
       <c r="R104" s="10" t="n">
@@ -12139,7 +11834,7 @@
         <v>365</v>
       </c>
       <c r="U104" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V104" s="11"/>
       <c r="W104" s="10"/>
@@ -12185,16 +11880,13 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B105" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E105" s="9" t="str">
@@ -12210,10 +11902,10 @@
         <v>362</v>
       </c>
       <c r="J105" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="K105" s="12" t="s">
         <v>520</v>
-      </c>
-      <c r="K105" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="L105" s="11"/>
       <c r="M105" s="10"/>
@@ -12269,16 +11961,13 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B106" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D106" s="23" t="s">
         <v>359</v>
       </c>
       <c r="E106" s="9" t="str">
@@ -12294,10 +11983,10 @@
         <v>362</v>
       </c>
       <c r="J106" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="K106" s="12" t="s">
         <v>523</v>
-      </c>
-      <c r="K106" s="12" t="s">
-        <v>524</v>
       </c>
       <c r="L106" s="11"/>
       <c r="M106" s="10"/>
@@ -12353,16 +12042,13 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B107" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E107" s="9" t="str">
@@ -12378,10 +12064,10 @@
         <v>362</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L107" s="11"/>
       <c r="M107" s="10" t="n">
@@ -12391,10 +12077,10 @@
         <v>42</v>
       </c>
       <c r="O107" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="P107" s="10" t="s">
         <v>527</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>528</v>
       </c>
       <c r="Q107" s="13"/>
       <c r="R107" s="10" t="n">
@@ -12404,10 +12090,10 @@
         <v>42</v>
       </c>
       <c r="T107" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="U107" s="10" t="s">
         <v>529</v>
-      </c>
-      <c r="U107" s="10" t="s">
-        <v>530</v>
       </c>
       <c r="V107" s="11"/>
       <c r="W107" s="10"/>
@@ -12453,16 +12139,13 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B108" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D108" s="21" t="s">
+      <c r="D108" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E108" s="9" t="str">
@@ -12478,10 +12161,10 @@
         <v>362</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" s="10" t="n">
@@ -12494,7 +12177,7 @@
         <v>365</v>
       </c>
       <c r="P108" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="Q108" s="13"/>
       <c r="R108" s="10"/>
@@ -12545,16 +12228,13 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B109" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D109" s="21" t="s">
+      <c r="D109" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E109" s="9" t="str">
@@ -12570,10 +12250,10 @@
         <v>362</v>
       </c>
       <c r="J109" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="K109" s="12" t="s">
         <v>535</v>
-      </c>
-      <c r="K109" s="12" t="s">
-        <v>536</v>
       </c>
       <c r="L109" s="11"/>
       <c r="M109" s="10"/>
@@ -12629,16 +12309,13 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B110" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D110" s="21" t="s">
+      <c r="D110" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E110" s="9" t="str">
@@ -12656,10 +12333,10 @@
         <v>42</v>
       </c>
       <c r="J110" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="K110" s="12" t="s">
         <v>538</v>
-      </c>
-      <c r="K110" s="12" t="s">
-        <v>539</v>
       </c>
       <c r="L110" s="11"/>
       <c r="M110" s="10" t="n">
@@ -12669,10 +12346,10 @@
         <v>154</v>
       </c>
       <c r="O110" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="P110" s="10" t="s">
         <v>540</v>
-      </c>
-      <c r="P110" s="10" t="s">
-        <v>541</v>
       </c>
       <c r="Q110" s="13"/>
       <c r="R110" s="10"/>
@@ -12723,16 +12400,13 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B111" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D111" s="21" t="s">
+      <c r="D111" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E111" s="9" t="str">
@@ -12753,20 +12427,20 @@
         <v>400</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L111" s="11"/>
       <c r="M111" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N111" s="10" t="s">
         <v>39</v>
       </c>
       <c r="O111" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>544</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>545</v>
       </c>
       <c r="Q111" s="13"/>
       <c r="R111" s="10"/>
@@ -12793,15 +12467,15 @@
       </c>
       <c r="AE111" s="10" t="n">
         <f aca="false">AG111+AA$2</f>
-        <v>45</v>
+        <v>40.6</v>
       </c>
       <c r="AF111" s="10" t="n">
         <f aca="false">AE111+Z$2</f>
-        <v>43.9</v>
+        <v>39.5</v>
       </c>
       <c r="AG111" s="10" t="n">
         <f aca="false">W$2+X$2*(M111-1)+Y$2</f>
-        <v>51</v>
+        <v>46.6</v>
       </c>
       <c r="AH111" s="10" t="n">
         <f aca="false">AJ111+AA$2</f>
@@ -12817,16 +12491,13 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B112" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D112" s="21" t="s">
+      <c r="D112" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E112" s="9" t="str">
@@ -12834,7 +12505,7 @@
         <v>LimbB</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G112" s="11"/>
       <c r="H112" s="10" t="n">
@@ -12844,10 +12515,10 @@
         <v>154</v>
       </c>
       <c r="J112" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="K112" s="12" t="s">
         <v>548</v>
-      </c>
-      <c r="K112" s="12" t="s">
-        <v>549</v>
       </c>
       <c r="L112" s="11"/>
       <c r="M112" s="10"/>
@@ -12903,16 +12574,13 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B113" s="8" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D113" s="23" t="s">
         <v>359</v>
       </c>
       <c r="E113" s="9" t="str">
@@ -12920,7 +12588,7 @@
         <v>LimbA</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G113" s="11"/>
       <c r="H113" s="10" t="n">
@@ -12930,10 +12598,10 @@
         <v>42</v>
       </c>
       <c r="J113" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="K113" s="12" t="s">
         <v>551</v>
-      </c>
-      <c r="K113" s="12" t="s">
-        <v>552</v>
       </c>
       <c r="L113" s="11"/>
       <c r="M113" s="10" t="n">
@@ -12946,7 +12614,7 @@
         <v>221</v>
       </c>
       <c r="P113" s="12" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q113" s="13"/>
       <c r="R113" s="10"/>
@@ -12997,16 +12665,13 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B114" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D114" s="21" t="s">
+      <c r="D114" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E114" s="9" t="str">
@@ -13022,7 +12687,7 @@
         <v>362</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K114" s="12" t="s">
         <v>392</v>
@@ -13035,10 +12700,10 @@
         <v>42</v>
       </c>
       <c r="O114" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="P114" s="10" t="s">
         <v>556</v>
-      </c>
-      <c r="P114" s="10" t="s">
-        <v>557</v>
       </c>
       <c r="Q114" s="13"/>
       <c r="R114" s="10" t="n">
@@ -13051,7 +12716,7 @@
         <v>365</v>
       </c>
       <c r="U114" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="V114" s="11"/>
       <c r="W114" s="10"/>
@@ -13097,16 +12762,13 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B115" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D115" s="21" t="s">
+      <c r="D115" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E115" s="9" t="str">
@@ -13122,10 +12784,10 @@
         <v>362</v>
       </c>
       <c r="J115" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="K115" s="12" t="s">
         <v>559</v>
-      </c>
-      <c r="K115" s="12" t="s">
-        <v>560</v>
       </c>
       <c r="L115" s="11"/>
       <c r="M115" s="10" t="n">
@@ -13138,7 +12800,7 @@
         <v>365</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q115" s="13"/>
       <c r="R115" s="10"/>
@@ -13189,16 +12851,13 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B116" s="8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D116" s="21" t="s">
+      <c r="D116" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E116" s="9" t="str">
@@ -13206,7 +12865,7 @@
         <v>LimbB</v>
       </c>
       <c r="F116" s="10"/>
-      <c r="G116" s="18"/>
+      <c r="G116" s="19"/>
       <c r="H116" s="10" t="n">
         <v>1</v>
       </c>
@@ -13214,22 +12873,22 @@
         <v>362</v>
       </c>
       <c r="J116" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="K116" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="K116" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="L116" s="18"/>
+      <c r="L116" s="19"/>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
-      <c r="Q116" s="19"/>
+      <c r="Q116" s="20"/>
       <c r="R116" s="10"/>
       <c r="S116" s="10"/>
       <c r="T116" s="10"/>
       <c r="U116" s="10"/>
-      <c r="V116" s="18"/>
+      <c r="V116" s="19"/>
       <c r="W116" s="12"/>
       <c r="X116" s="12"/>
       <c r="Y116" s="10"/>
@@ -13273,16 +12932,13 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B117" s="8" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D117" s="21" t="s">
+      <c r="D117" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E117" s="9" t="str">
@@ -13298,7 +12954,7 @@
         <v>362</v>
       </c>
       <c r="J117" s="12" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K117" s="12" t="s">
         <v>411</v>
@@ -13314,7 +12970,7 @@
         <v>365</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="Q117" s="13"/>
       <c r="R117" s="10"/>
@@ -13365,16 +13021,13 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B118" s="8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D118" s="21" t="s">
+      <c r="D118" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E118" s="9" t="str">
@@ -13390,10 +13043,10 @@
         <v>39</v>
       </c>
       <c r="J118" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="K118" s="12" t="s">
         <v>569</v>
-      </c>
-      <c r="K118" s="12" t="s">
-        <v>570</v>
       </c>
       <c r="L118" s="11"/>
       <c r="M118" s="10" t="n">
@@ -13403,10 +13056,10 @@
         <v>154</v>
       </c>
       <c r="O118" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="P118" s="12" t="s">
         <v>571</v>
-      </c>
-      <c r="P118" s="12" t="s">
-        <v>572</v>
       </c>
       <c r="Q118" s="13"/>
       <c r="R118" s="10"/>
@@ -13457,16 +13110,13 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B119" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D119" s="21" t="s">
+      <c r="D119" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E119" s="9" t="str">
@@ -13482,10 +13132,10 @@
         <v>362</v>
       </c>
       <c r="J119" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="K119" s="12" t="s">
         <v>574</v>
-      </c>
-      <c r="K119" s="12" t="s">
-        <v>575</v>
       </c>
       <c r="L119" s="11"/>
       <c r="M119" s="10" t="n">
@@ -13498,7 +13148,7 @@
         <v>365</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Q119" s="13"/>
       <c r="R119" s="10"/>
@@ -13549,16 +13199,13 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B120" s="8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D120" s="21" t="s">
+      <c r="D120" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E120" s="9" t="str">
@@ -13574,10 +13221,10 @@
         <v>362</v>
       </c>
       <c r="J120" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="K120" s="12" t="s">
         <v>578</v>
-      </c>
-      <c r="K120" s="12" t="s">
-        <v>579</v>
       </c>
       <c r="L120" s="11"/>
       <c r="M120" s="10" t="n">
@@ -13590,7 +13237,7 @@
         <v>365</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q120" s="13"/>
       <c r="R120" s="10"/>
@@ -13641,16 +13288,13 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B121" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D121" s="21" t="s">
+      <c r="D121" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E121" s="9" t="str">
@@ -13666,10 +13310,10 @@
         <v>362</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K121" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L121" s="11"/>
       <c r="M121" s="10" t="n">
@@ -13682,7 +13326,7 @@
         <v>365</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q121" s="13"/>
       <c r="R121" s="10"/>
@@ -13733,16 +13377,13 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B122" s="8" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D122" s="21" t="s">
+      <c r="D122" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E122" s="9" t="str">
@@ -13758,10 +13399,10 @@
         <v>362</v>
       </c>
       <c r="J122" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="K122" s="12" t="s">
         <v>584</v>
-      </c>
-      <c r="K122" s="12" t="s">
-        <v>585</v>
       </c>
       <c r="L122" s="11"/>
       <c r="M122" s="10"/>
@@ -13817,16 +13458,13 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B123" s="8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D123" s="21" t="s">
+      <c r="D123" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E123" s="9" t="str">
@@ -13842,10 +13480,10 @@
         <v>362</v>
       </c>
       <c r="J123" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="K123" s="12" t="s">
         <v>587</v>
-      </c>
-      <c r="K123" s="12" t="s">
-        <v>588</v>
       </c>
       <c r="L123" s="11"/>
       <c r="M123" s="10"/>
@@ -13901,16 +13539,13 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B124" s="8" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D124" s="21" t="s">
+      <c r="D124" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E124" s="9" t="str">
@@ -13926,10 +13561,10 @@
         <v>42</v>
       </c>
       <c r="J124" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="K124" s="12" t="s">
         <v>590</v>
-      </c>
-      <c r="K124" s="12" t="s">
-        <v>591</v>
       </c>
       <c r="L124" s="11"/>
       <c r="M124" s="10" t="n">
@@ -13939,10 +13574,10 @@
         <v>362</v>
       </c>
       <c r="O124" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="P124" s="12" t="s">
         <v>592</v>
-      </c>
-      <c r="P124" s="12" t="s">
-        <v>593</v>
       </c>
       <c r="Q124" s="13"/>
       <c r="R124" s="10" t="n">
@@ -13952,10 +13587,10 @@
         <v>39</v>
       </c>
       <c r="T124" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="U124" s="10" t="s">
         <v>594</v>
-      </c>
-      <c r="U124" s="10" t="s">
-        <v>595</v>
       </c>
       <c r="V124" s="11"/>
       <c r="W124" s="10"/>
@@ -14001,16 +13636,13 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B125" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D125" s="21" t="s">
+      <c r="D125" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E125" s="9" t="str">
@@ -14026,7 +13658,7 @@
         <v>362</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K125" s="12" t="s">
         <v>392</v>
@@ -14039,10 +13671,10 @@
         <v>39</v>
       </c>
       <c r="O125" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="P125" s="12" t="s">
         <v>598</v>
-      </c>
-      <c r="P125" s="12" t="s">
-        <v>599</v>
       </c>
       <c r="Q125" s="13"/>
       <c r="R125" s="10"/>
@@ -14093,16 +13725,13 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B126" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D126" s="21" t="s">
+      <c r="D126" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E126" s="9" t="str">
@@ -14118,10 +13747,10 @@
         <v>362</v>
       </c>
       <c r="J126" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="K126" s="12" t="s">
         <v>601</v>
-      </c>
-      <c r="K126" s="12" t="s">
-        <v>602</v>
       </c>
       <c r="L126" s="11"/>
       <c r="M126" s="10" t="n">
@@ -14131,10 +13760,10 @@
         <v>154</v>
       </c>
       <c r="O126" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="P126" s="10" t="s">
         <v>603</v>
-      </c>
-      <c r="P126" s="10" t="s">
-        <v>604</v>
       </c>
       <c r="Q126" s="13"/>
       <c r="R126" s="1" t="n">
@@ -14147,7 +13776,7 @@
         <v>365</v>
       </c>
       <c r="U126" s="12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="V126" s="11"/>
       <c r="W126" s="10"/>
@@ -14193,16 +13822,13 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B127" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="21" t="s">
+      <c r="D127" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E127" s="9" t="str">
@@ -14210,7 +13836,7 @@
         <v>LimbA</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G127" s="11"/>
       <c r="H127" s="10" t="n">
@@ -14220,10 +13846,10 @@
         <v>42</v>
       </c>
       <c r="J127" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="K127" s="12" t="s">
         <v>607</v>
-      </c>
-      <c r="K127" s="12" t="s">
-        <v>608</v>
       </c>
       <c r="L127" s="11"/>
       <c r="M127" s="10" t="n">
@@ -14233,10 +13859,10 @@
         <v>39</v>
       </c>
       <c r="O127" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="P127" s="12" t="s">
         <v>609</v>
-      </c>
-      <c r="P127" s="12" t="s">
-        <v>610</v>
       </c>
       <c r="Q127" s="13"/>
       <c r="R127" s="10"/>
@@ -14287,16 +13913,13 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B128" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D128" s="21" t="s">
+      <c r="D128" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E128" s="9" t="str">
@@ -14312,10 +13935,10 @@
         <v>362</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K128" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L128" s="11"/>
       <c r="M128" s="10" t="n">
@@ -14325,10 +13948,10 @@
         <v>42</v>
       </c>
       <c r="O128" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="P128" s="10" t="s">
         <v>613</v>
-      </c>
-      <c r="P128" s="10" t="s">
-        <v>614</v>
       </c>
       <c r="Q128" s="13"/>
       <c r="R128" s="10"/>
@@ -14379,16 +14002,13 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="B129" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D129" s="21" t="s">
+      <c r="D129" s="22" t="s">
         <v>359</v>
       </c>
       <c r="E129" s="9" t="str">
@@ -14404,10 +14024,10 @@
         <v>362</v>
       </c>
       <c r="J129" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="K129" s="12" t="s">
         <v>616</v>
-      </c>
-      <c r="K129" s="12" t="s">
-        <v>617</v>
       </c>
       <c r="L129" s="11"/>
       <c r="M129" s="10"/>
@@ -14474,2196 +14094,2196 @@
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="24"/>
-      <c r="C141" s="24"/>
-      <c r="D141" s="24"/>
-      <c r="E141" s="24"/>
-      <c r="F141" s="24"/>
-      <c r="G141" s="24"/>
-      <c r="H141" s="24"/>
-      <c r="I141" s="25"/>
-      <c r="J141" s="25"/>
-      <c r="K141" s="24"/>
-      <c r="L141" s="24"/>
-      <c r="M141" s="24"/>
-      <c r="N141" s="25"/>
-      <c r="O141" s="25"/>
-      <c r="P141" s="26"/>
-      <c r="Q141" s="24"/>
-      <c r="R141" s="24"/>
-      <c r="S141" s="25"/>
-      <c r="T141" s="25"/>
-      <c r="U141" s="24"/>
-      <c r="V141" s="24"/>
-      <c r="W141" s="24"/>
-      <c r="X141" s="24"/>
-      <c r="Y141" s="24"/>
-      <c r="Z141" s="24"/>
-      <c r="AA141" s="24"/>
-      <c r="AB141" s="24"/>
-      <c r="AC141" s="24"/>
-      <c r="AD141" s="24"/>
-      <c r="AE141" s="24"/>
-      <c r="AF141" s="24"/>
-      <c r="AG141" s="24"/>
-      <c r="AH141" s="24"/>
-      <c r="AI141" s="24"/>
-      <c r="AJ141" s="25"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="25"/>
+      <c r="D141" s="25"/>
+      <c r="E141" s="25"/>
+      <c r="F141" s="25"/>
+      <c r="G141" s="25"/>
+      <c r="H141" s="25"/>
+      <c r="I141" s="26"/>
+      <c r="J141" s="26"/>
+      <c r="K141" s="25"/>
+      <c r="L141" s="25"/>
+      <c r="M141" s="25"/>
+      <c r="N141" s="26"/>
+      <c r="O141" s="26"/>
+      <c r="P141" s="27"/>
+      <c r="Q141" s="25"/>
+      <c r="R141" s="25"/>
+      <c r="S141" s="26"/>
+      <c r="T141" s="26"/>
+      <c r="U141" s="25"/>
+      <c r="V141" s="25"/>
+      <c r="W141" s="25"/>
+      <c r="X141" s="25"/>
+      <c r="Y141" s="25"/>
+      <c r="Z141" s="25"/>
+      <c r="AA141" s="25"/>
+      <c r="AB141" s="25"/>
+      <c r="AC141" s="25"/>
+      <c r="AD141" s="25"/>
+      <c r="AE141" s="25"/>
+      <c r="AF141" s="25"/>
+      <c r="AG141" s="25"/>
+      <c r="AH141" s="25"/>
+      <c r="AI141" s="25"/>
+      <c r="AJ141" s="26"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="24"/>
-      <c r="C142" s="24"/>
-      <c r="D142" s="24"/>
-      <c r="E142" s="24"/>
-      <c r="F142" s="24"/>
-      <c r="G142" s="24"/>
-      <c r="H142" s="24"/>
-      <c r="I142" s="25"/>
-      <c r="J142" s="25"/>
-      <c r="K142" s="24"/>
-      <c r="L142" s="24"/>
-      <c r="M142" s="24"/>
-      <c r="N142" s="25"/>
-      <c r="O142" s="25"/>
-      <c r="P142" s="26"/>
-      <c r="Q142" s="24"/>
-      <c r="R142" s="24"/>
-      <c r="S142" s="25"/>
-      <c r="T142" s="25"/>
-      <c r="U142" s="24"/>
-      <c r="V142" s="24"/>
-      <c r="W142" s="24"/>
-      <c r="X142" s="24"/>
-      <c r="Y142" s="24"/>
-      <c r="Z142" s="24"/>
-      <c r="AA142" s="24"/>
-      <c r="AB142" s="24"/>
-      <c r="AC142" s="24"/>
-      <c r="AD142" s="24"/>
-      <c r="AE142" s="24"/>
-      <c r="AF142" s="24"/>
-      <c r="AG142" s="24"/>
-      <c r="AH142" s="24"/>
-      <c r="AI142" s="24"/>
-      <c r="AJ142" s="25"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="25"/>
+      <c r="D142" s="25"/>
+      <c r="E142" s="25"/>
+      <c r="F142" s="25"/>
+      <c r="G142" s="25"/>
+      <c r="H142" s="25"/>
+      <c r="I142" s="26"/>
+      <c r="J142" s="26"/>
+      <c r="K142" s="25"/>
+      <c r="L142" s="25"/>
+      <c r="M142" s="25"/>
+      <c r="N142" s="26"/>
+      <c r="O142" s="26"/>
+      <c r="P142" s="27"/>
+      <c r="Q142" s="25"/>
+      <c r="R142" s="25"/>
+      <c r="S142" s="26"/>
+      <c r="T142" s="26"/>
+      <c r="U142" s="25"/>
+      <c r="V142" s="25"/>
+      <c r="W142" s="25"/>
+      <c r="X142" s="25"/>
+      <c r="Y142" s="25"/>
+      <c r="Z142" s="25"/>
+      <c r="AA142" s="25"/>
+      <c r="AB142" s="25"/>
+      <c r="AC142" s="25"/>
+      <c r="AD142" s="25"/>
+      <c r="AE142" s="25"/>
+      <c r="AF142" s="25"/>
+      <c r="AG142" s="25"/>
+      <c r="AH142" s="25"/>
+      <c r="AI142" s="25"/>
+      <c r="AJ142" s="26"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="24"/>
-      <c r="C143" s="24"/>
-      <c r="D143" s="24"/>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="25"/>
-      <c r="K143" s="24"/>
-      <c r="L143" s="24"/>
-      <c r="M143" s="24"/>
-      <c r="N143" s="25"/>
-      <c r="O143" s="25"/>
-      <c r="P143" s="26"/>
-      <c r="Q143" s="24"/>
-      <c r="R143" s="24"/>
-      <c r="S143" s="25"/>
-      <c r="T143" s="25"/>
-      <c r="U143" s="24"/>
-      <c r="V143" s="24"/>
-      <c r="W143" s="24"/>
-      <c r="X143" s="24"/>
-      <c r="Y143" s="24"/>
-      <c r="Z143" s="24"/>
-      <c r="AA143" s="24"/>
-      <c r="AB143" s="24"/>
-      <c r="AC143" s="24"/>
-      <c r="AD143" s="24"/>
-      <c r="AE143" s="24"/>
-      <c r="AF143" s="24"/>
-      <c r="AG143" s="24"/>
-      <c r="AH143" s="24"/>
-      <c r="AI143" s="24"/>
-      <c r="AJ143" s="25"/>
+      <c r="B143" s="25"/>
+      <c r="C143" s="25"/>
+      <c r="D143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="26"/>
+      <c r="J143" s="26"/>
+      <c r="K143" s="25"/>
+      <c r="L143" s="25"/>
+      <c r="M143" s="25"/>
+      <c r="N143" s="26"/>
+      <c r="O143" s="26"/>
+      <c r="P143" s="27"/>
+      <c r="Q143" s="25"/>
+      <c r="R143" s="25"/>
+      <c r="S143" s="26"/>
+      <c r="T143" s="26"/>
+      <c r="U143" s="25"/>
+      <c r="V143" s="25"/>
+      <c r="W143" s="25"/>
+      <c r="X143" s="25"/>
+      <c r="Y143" s="25"/>
+      <c r="Z143" s="25"/>
+      <c r="AA143" s="25"/>
+      <c r="AB143" s="25"/>
+      <c r="AC143" s="25"/>
+      <c r="AD143" s="25"/>
+      <c r="AE143" s="25"/>
+      <c r="AF143" s="25"/>
+      <c r="AG143" s="25"/>
+      <c r="AH143" s="25"/>
+      <c r="AI143" s="25"/>
+      <c r="AJ143" s="26"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="24"/>
-      <c r="C144" s="24"/>
-      <c r="D144" s="24"/>
-      <c r="E144" s="24"/>
-      <c r="F144" s="24"/>
-      <c r="G144" s="24"/>
-      <c r="H144" s="24"/>
-      <c r="I144" s="25"/>
-      <c r="J144" s="25"/>
-      <c r="K144" s="24"/>
-      <c r="L144" s="24"/>
-      <c r="M144" s="24"/>
-      <c r="N144" s="25"/>
-      <c r="O144" s="25"/>
-      <c r="P144" s="26"/>
-      <c r="Q144" s="24"/>
-      <c r="R144" s="24"/>
-      <c r="S144" s="25"/>
-      <c r="T144" s="25"/>
-      <c r="U144" s="24"/>
-      <c r="V144" s="24"/>
-      <c r="W144" s="24"/>
-      <c r="X144" s="24"/>
-      <c r="Y144" s="24"/>
-      <c r="Z144" s="24"/>
-      <c r="AA144" s="24"/>
-      <c r="AB144" s="24"/>
-      <c r="AC144" s="24"/>
-      <c r="AD144" s="24"/>
-      <c r="AE144" s="24"/>
-      <c r="AF144" s="24"/>
-      <c r="AG144" s="24"/>
-      <c r="AH144" s="24"/>
-      <c r="AI144" s="24"/>
-      <c r="AJ144" s="25"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="25"/>
+      <c r="D144" s="25"/>
+      <c r="E144" s="25"/>
+      <c r="F144" s="25"/>
+      <c r="G144" s="25"/>
+      <c r="H144" s="25"/>
+      <c r="I144" s="26"/>
+      <c r="J144" s="26"/>
+      <c r="K144" s="25"/>
+      <c r="L144" s="25"/>
+      <c r="M144" s="25"/>
+      <c r="N144" s="26"/>
+      <c r="O144" s="26"/>
+      <c r="P144" s="27"/>
+      <c r="Q144" s="25"/>
+      <c r="R144" s="25"/>
+      <c r="S144" s="26"/>
+      <c r="T144" s="26"/>
+      <c r="U144" s="25"/>
+      <c r="V144" s="25"/>
+      <c r="W144" s="25"/>
+      <c r="X144" s="25"/>
+      <c r="Y144" s="25"/>
+      <c r="Z144" s="25"/>
+      <c r="AA144" s="25"/>
+      <c r="AB144" s="25"/>
+      <c r="AC144" s="25"/>
+      <c r="AD144" s="25"/>
+      <c r="AE144" s="25"/>
+      <c r="AF144" s="25"/>
+      <c r="AG144" s="25"/>
+      <c r="AH144" s="25"/>
+      <c r="AI144" s="25"/>
+      <c r="AJ144" s="26"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="24"/>
-      <c r="C145" s="24"/>
-      <c r="D145" s="24"/>
-      <c r="E145" s="24"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="24"/>
-      <c r="H145" s="24"/>
-      <c r="I145" s="25"/>
-      <c r="J145" s="25"/>
-      <c r="K145" s="24"/>
-      <c r="L145" s="24"/>
-      <c r="M145" s="24"/>
-      <c r="N145" s="25"/>
-      <c r="O145" s="25"/>
-      <c r="P145" s="26"/>
-      <c r="Q145" s="24"/>
-      <c r="R145" s="24"/>
-      <c r="S145" s="25"/>
-      <c r="T145" s="25"/>
-      <c r="U145" s="24"/>
-      <c r="V145" s="24"/>
-      <c r="W145" s="24"/>
-      <c r="X145" s="24"/>
-      <c r="Y145" s="24"/>
-      <c r="Z145" s="24"/>
-      <c r="AA145" s="24"/>
-      <c r="AB145" s="24"/>
-      <c r="AC145" s="24"/>
-      <c r="AD145" s="24"/>
-      <c r="AE145" s="24"/>
-      <c r="AF145" s="24"/>
-      <c r="AG145" s="24"/>
-      <c r="AH145" s="24"/>
-      <c r="AI145" s="24"/>
-      <c r="AJ145" s="25"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="25"/>
+      <c r="D145" s="25"/>
+      <c r="E145" s="25"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="25"/>
+      <c r="H145" s="25"/>
+      <c r="I145" s="26"/>
+      <c r="J145" s="26"/>
+      <c r="K145" s="25"/>
+      <c r="L145" s="25"/>
+      <c r="M145" s="25"/>
+      <c r="N145" s="26"/>
+      <c r="O145" s="26"/>
+      <c r="P145" s="27"/>
+      <c r="Q145" s="25"/>
+      <c r="R145" s="25"/>
+      <c r="S145" s="26"/>
+      <c r="T145" s="26"/>
+      <c r="U145" s="25"/>
+      <c r="V145" s="25"/>
+      <c r="W145" s="25"/>
+      <c r="X145" s="25"/>
+      <c r="Y145" s="25"/>
+      <c r="Z145" s="25"/>
+      <c r="AA145" s="25"/>
+      <c r="AB145" s="25"/>
+      <c r="AC145" s="25"/>
+      <c r="AD145" s="25"/>
+      <c r="AE145" s="25"/>
+      <c r="AF145" s="25"/>
+      <c r="AG145" s="25"/>
+      <c r="AH145" s="25"/>
+      <c r="AI145" s="25"/>
+      <c r="AJ145" s="26"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="24"/>
-      <c r="C146" s="24"/>
-      <c r="D146" s="24"/>
-      <c r="E146" s="24"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="24"/>
-      <c r="H146" s="24"/>
-      <c r="I146" s="25"/>
-      <c r="J146" s="25"/>
-      <c r="K146" s="24"/>
-      <c r="L146" s="24"/>
-      <c r="M146" s="24"/>
-      <c r="N146" s="25"/>
-      <c r="O146" s="25"/>
-      <c r="P146" s="26"/>
-      <c r="Q146" s="24"/>
-      <c r="R146" s="24"/>
-      <c r="S146" s="25"/>
-      <c r="T146" s="25"/>
-      <c r="U146" s="24"/>
-      <c r="V146" s="24"/>
-      <c r="W146" s="24"/>
-      <c r="X146" s="24"/>
-      <c r="Y146" s="24"/>
-      <c r="Z146" s="24"/>
-      <c r="AA146" s="24"/>
-      <c r="AB146" s="24"/>
-      <c r="AC146" s="24"/>
-      <c r="AD146" s="24"/>
-      <c r="AE146" s="24"/>
-      <c r="AF146" s="24"/>
-      <c r="AG146" s="24"/>
-      <c r="AH146" s="24"/>
-      <c r="AI146" s="24"/>
-      <c r="AJ146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+      <c r="D146" s="25"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="25"/>
+      <c r="G146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="26"/>
+      <c r="J146" s="26"/>
+      <c r="K146" s="25"/>
+      <c r="L146" s="25"/>
+      <c r="M146" s="25"/>
+      <c r="N146" s="26"/>
+      <c r="O146" s="26"/>
+      <c r="P146" s="27"/>
+      <c r="Q146" s="25"/>
+      <c r="R146" s="25"/>
+      <c r="S146" s="26"/>
+      <c r="T146" s="26"/>
+      <c r="U146" s="25"/>
+      <c r="V146" s="25"/>
+      <c r="W146" s="25"/>
+      <c r="X146" s="25"/>
+      <c r="Y146" s="25"/>
+      <c r="Z146" s="25"/>
+      <c r="AA146" s="25"/>
+      <c r="AB146" s="25"/>
+      <c r="AC146" s="25"/>
+      <c r="AD146" s="25"/>
+      <c r="AE146" s="25"/>
+      <c r="AF146" s="25"/>
+      <c r="AG146" s="25"/>
+      <c r="AH146" s="25"/>
+      <c r="AI146" s="25"/>
+      <c r="AJ146" s="26"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="24"/>
-      <c r="C147" s="24"/>
-      <c r="D147" s="24"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="24"/>
-      <c r="H147" s="24"/>
-      <c r="I147" s="25"/>
-      <c r="J147" s="25"/>
-      <c r="K147" s="24"/>
-      <c r="L147" s="24"/>
-      <c r="M147" s="24"/>
-      <c r="N147" s="25"/>
-      <c r="O147" s="25"/>
-      <c r="P147" s="26"/>
-      <c r="Q147" s="24"/>
-      <c r="R147" s="24"/>
-      <c r="S147" s="25"/>
-      <c r="T147" s="25"/>
-      <c r="U147" s="24"/>
-      <c r="V147" s="24"/>
-      <c r="W147" s="24"/>
-      <c r="X147" s="24"/>
-      <c r="Y147" s="24"/>
-      <c r="Z147" s="24"/>
-      <c r="AA147" s="24"/>
-      <c r="AB147" s="24"/>
-      <c r="AC147" s="24"/>
-      <c r="AD147" s="24"/>
-      <c r="AE147" s="24"/>
-      <c r="AF147" s="24"/>
-      <c r="AG147" s="24"/>
-      <c r="AH147" s="24"/>
-      <c r="AI147" s="24"/>
-      <c r="AJ147" s="25"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="25"/>
+      <c r="D147" s="25"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="25"/>
+      <c r="G147" s="25"/>
+      <c r="H147" s="25"/>
+      <c r="I147" s="26"/>
+      <c r="J147" s="26"/>
+      <c r="K147" s="25"/>
+      <c r="L147" s="25"/>
+      <c r="M147" s="25"/>
+      <c r="N147" s="26"/>
+      <c r="O147" s="26"/>
+      <c r="P147" s="27"/>
+      <c r="Q147" s="25"/>
+      <c r="R147" s="25"/>
+      <c r="S147" s="26"/>
+      <c r="T147" s="26"/>
+      <c r="U147" s="25"/>
+      <c r="V147" s="25"/>
+      <c r="W147" s="25"/>
+      <c r="X147" s="25"/>
+      <c r="Y147" s="25"/>
+      <c r="Z147" s="25"/>
+      <c r="AA147" s="25"/>
+      <c r="AB147" s="25"/>
+      <c r="AC147" s="25"/>
+      <c r="AD147" s="25"/>
+      <c r="AE147" s="25"/>
+      <c r="AF147" s="25"/>
+      <c r="AG147" s="25"/>
+      <c r="AH147" s="25"/>
+      <c r="AI147" s="25"/>
+      <c r="AJ147" s="26"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="24"/>
-      <c r="C148" s="24"/>
-      <c r="D148" s="24"/>
-      <c r="E148" s="24"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="24"/>
-      <c r="H148" s="24"/>
-      <c r="I148" s="25"/>
-      <c r="J148" s="25"/>
-      <c r="K148" s="24"/>
-      <c r="L148" s="24"/>
-      <c r="M148" s="24"/>
-      <c r="N148" s="25"/>
-      <c r="O148" s="25"/>
-      <c r="P148" s="26"/>
-      <c r="Q148" s="24"/>
-      <c r="R148" s="24"/>
-      <c r="S148" s="25"/>
-      <c r="T148" s="25"/>
-      <c r="U148" s="24"/>
-      <c r="V148" s="24"/>
-      <c r="W148" s="24"/>
-      <c r="X148" s="24"/>
-      <c r="Y148" s="24"/>
-      <c r="Z148" s="24"/>
-      <c r="AA148" s="24"/>
-      <c r="AB148" s="24"/>
-      <c r="AC148" s="24"/>
-      <c r="AD148" s="24"/>
-      <c r="AE148" s="24"/>
-      <c r="AF148" s="24"/>
-      <c r="AG148" s="24"/>
-      <c r="AH148" s="24"/>
-      <c r="AI148" s="24"/>
-      <c r="AJ148" s="25"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="25"/>
+      <c r="D148" s="25"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="25"/>
+      <c r="G148" s="25"/>
+      <c r="H148" s="25"/>
+      <c r="I148" s="26"/>
+      <c r="J148" s="26"/>
+      <c r="K148" s="25"/>
+      <c r="L148" s="25"/>
+      <c r="M148" s="25"/>
+      <c r="N148" s="26"/>
+      <c r="O148" s="26"/>
+      <c r="P148" s="27"/>
+      <c r="Q148" s="25"/>
+      <c r="R148" s="25"/>
+      <c r="S148" s="26"/>
+      <c r="T148" s="26"/>
+      <c r="U148" s="25"/>
+      <c r="V148" s="25"/>
+      <c r="W148" s="25"/>
+      <c r="X148" s="25"/>
+      <c r="Y148" s="25"/>
+      <c r="Z148" s="25"/>
+      <c r="AA148" s="25"/>
+      <c r="AB148" s="25"/>
+      <c r="AC148" s="25"/>
+      <c r="AD148" s="25"/>
+      <c r="AE148" s="25"/>
+      <c r="AF148" s="25"/>
+      <c r="AG148" s="25"/>
+      <c r="AH148" s="25"/>
+      <c r="AI148" s="25"/>
+      <c r="AJ148" s="26"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="25"/>
-      <c r="J149" s="25"/>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="25"/>
-      <c r="O149" s="25"/>
-      <c r="P149" s="26"/>
-      <c r="Q149" s="24"/>
-      <c r="R149" s="24"/>
-      <c r="S149" s="25"/>
-      <c r="T149" s="25"/>
-      <c r="U149" s="24"/>
-      <c r="V149" s="24"/>
-      <c r="W149" s="24"/>
-      <c r="X149" s="24"/>
-      <c r="Y149" s="24"/>
-      <c r="Z149" s="24"/>
-      <c r="AA149" s="24"/>
-      <c r="AB149" s="24"/>
-      <c r="AC149" s="24"/>
-      <c r="AD149" s="24"/>
-      <c r="AE149" s="24"/>
-      <c r="AF149" s="24"/>
-      <c r="AG149" s="24"/>
-      <c r="AH149" s="24"/>
-      <c r="AI149" s="24"/>
-      <c r="AJ149" s="25"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="25"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
+      <c r="K149" s="25"/>
+      <c r="L149" s="25"/>
+      <c r="M149" s="25"/>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="27"/>
+      <c r="Q149" s="25"/>
+      <c r="R149" s="25"/>
+      <c r="S149" s="26"/>
+      <c r="T149" s="26"/>
+      <c r="U149" s="25"/>
+      <c r="V149" s="25"/>
+      <c r="W149" s="25"/>
+      <c r="X149" s="25"/>
+      <c r="Y149" s="25"/>
+      <c r="Z149" s="25"/>
+      <c r="AA149" s="25"/>
+      <c r="AB149" s="25"/>
+      <c r="AC149" s="25"/>
+      <c r="AD149" s="25"/>
+      <c r="AE149" s="25"/>
+      <c r="AF149" s="25"/>
+      <c r="AG149" s="25"/>
+      <c r="AH149" s="25"/>
+      <c r="AI149" s="25"/>
+      <c r="AJ149" s="26"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="24"/>
-      <c r="C150" s="24"/>
-      <c r="D150" s="24"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="24"/>
-      <c r="H150" s="24"/>
-      <c r="I150" s="25"/>
-      <c r="J150" s="25"/>
-      <c r="K150" s="24"/>
-      <c r="L150" s="24"/>
-      <c r="M150" s="24"/>
-      <c r="N150" s="25"/>
-      <c r="O150" s="25"/>
-      <c r="P150" s="26"/>
-      <c r="Q150" s="24"/>
-      <c r="R150" s="24"/>
-      <c r="S150" s="25"/>
-      <c r="T150" s="25"/>
-      <c r="U150" s="24"/>
-      <c r="V150" s="24"/>
-      <c r="W150" s="24"/>
-      <c r="X150" s="24"/>
-      <c r="Y150" s="24"/>
-      <c r="Z150" s="24"/>
-      <c r="AA150" s="24"/>
-      <c r="AB150" s="24"/>
-      <c r="AC150" s="24"/>
-      <c r="AD150" s="24"/>
-      <c r="AE150" s="24"/>
-      <c r="AF150" s="24"/>
-      <c r="AG150" s="24"/>
-      <c r="AH150" s="24"/>
-      <c r="AI150" s="24"/>
-      <c r="AJ150" s="25"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="25"/>
+      <c r="H150" s="25"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="26"/>
+      <c r="K150" s="25"/>
+      <c r="L150" s="25"/>
+      <c r="M150" s="25"/>
+      <c r="N150" s="26"/>
+      <c r="O150" s="26"/>
+      <c r="P150" s="27"/>
+      <c r="Q150" s="25"/>
+      <c r="R150" s="25"/>
+      <c r="S150" s="26"/>
+      <c r="T150" s="26"/>
+      <c r="U150" s="25"/>
+      <c r="V150" s="25"/>
+      <c r="W150" s="25"/>
+      <c r="X150" s="25"/>
+      <c r="Y150" s="25"/>
+      <c r="Z150" s="25"/>
+      <c r="AA150" s="25"/>
+      <c r="AB150" s="25"/>
+      <c r="AC150" s="25"/>
+      <c r="AD150" s="25"/>
+      <c r="AE150" s="25"/>
+      <c r="AF150" s="25"/>
+      <c r="AG150" s="25"/>
+      <c r="AH150" s="25"/>
+      <c r="AI150" s="25"/>
+      <c r="AJ150" s="26"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="24"/>
-      <c r="C151" s="24"/>
-      <c r="D151" s="24"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="24"/>
-      <c r="H151" s="24"/>
-      <c r="I151" s="25"/>
-      <c r="J151" s="25"/>
-      <c r="K151" s="24"/>
-      <c r="L151" s="24"/>
-      <c r="M151" s="24"/>
-      <c r="N151" s="25"/>
-      <c r="O151" s="25"/>
-      <c r="P151" s="26"/>
-      <c r="Q151" s="24"/>
-      <c r="R151" s="24"/>
-      <c r="S151" s="25"/>
-      <c r="T151" s="25"/>
-      <c r="U151" s="24"/>
-      <c r="V151" s="24"/>
-      <c r="W151" s="24"/>
-      <c r="X151" s="24"/>
-      <c r="Y151" s="24"/>
-      <c r="Z151" s="24"/>
-      <c r="AA151" s="24"/>
-      <c r="AB151" s="24"/>
-      <c r="AC151" s="24"/>
-      <c r="AD151" s="24"/>
-      <c r="AE151" s="24"/>
-      <c r="AF151" s="24"/>
-      <c r="AG151" s="24"/>
-      <c r="AH151" s="24"/>
-      <c r="AI151" s="24"/>
-      <c r="AJ151" s="25"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="25"/>
+      <c r="D151" s="25"/>
+      <c r="E151" s="25"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="26"/>
+      <c r="J151" s="26"/>
+      <c r="K151" s="25"/>
+      <c r="L151" s="25"/>
+      <c r="M151" s="25"/>
+      <c r="N151" s="26"/>
+      <c r="O151" s="26"/>
+      <c r="P151" s="27"/>
+      <c r="Q151" s="25"/>
+      <c r="R151" s="25"/>
+      <c r="S151" s="26"/>
+      <c r="T151" s="26"/>
+      <c r="U151" s="25"/>
+      <c r="V151" s="25"/>
+      <c r="W151" s="25"/>
+      <c r="X151" s="25"/>
+      <c r="Y151" s="25"/>
+      <c r="Z151" s="25"/>
+      <c r="AA151" s="25"/>
+      <c r="AB151" s="25"/>
+      <c r="AC151" s="25"/>
+      <c r="AD151" s="25"/>
+      <c r="AE151" s="25"/>
+      <c r="AF151" s="25"/>
+      <c r="AG151" s="25"/>
+      <c r="AH151" s="25"/>
+      <c r="AI151" s="25"/>
+      <c r="AJ151" s="26"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="24"/>
-      <c r="C152" s="24"/>
-      <c r="D152" s="24"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="24"/>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
-      <c r="J152" s="25"/>
-      <c r="K152" s="24"/>
-      <c r="L152" s="24"/>
-      <c r="M152" s="24"/>
-      <c r="N152" s="25"/>
-      <c r="O152" s="25"/>
-      <c r="P152" s="26"/>
-      <c r="Q152" s="24"/>
-      <c r="R152" s="24"/>
-      <c r="S152" s="25"/>
-      <c r="T152" s="25"/>
-      <c r="U152" s="24"/>
-      <c r="V152" s="24"/>
-      <c r="W152" s="24"/>
-      <c r="X152" s="24"/>
-      <c r="Y152" s="24"/>
-      <c r="Z152" s="24"/>
-      <c r="AA152" s="24"/>
-      <c r="AB152" s="24"/>
-      <c r="AC152" s="24"/>
-      <c r="AD152" s="24"/>
-      <c r="AE152" s="24"/>
-      <c r="AF152" s="24"/>
-      <c r="AG152" s="24"/>
-      <c r="AH152" s="24"/>
-      <c r="AI152" s="24"/>
-      <c r="AJ152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+      <c r="D152" s="25"/>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="26"/>
+      <c r="J152" s="26"/>
+      <c r="K152" s="25"/>
+      <c r="L152" s="25"/>
+      <c r="M152" s="25"/>
+      <c r="N152" s="26"/>
+      <c r="O152" s="26"/>
+      <c r="P152" s="27"/>
+      <c r="Q152" s="25"/>
+      <c r="R152" s="25"/>
+      <c r="S152" s="26"/>
+      <c r="T152" s="26"/>
+      <c r="U152" s="25"/>
+      <c r="V152" s="25"/>
+      <c r="W152" s="25"/>
+      <c r="X152" s="25"/>
+      <c r="Y152" s="25"/>
+      <c r="Z152" s="25"/>
+      <c r="AA152" s="25"/>
+      <c r="AB152" s="25"/>
+      <c r="AC152" s="25"/>
+      <c r="AD152" s="25"/>
+      <c r="AE152" s="25"/>
+      <c r="AF152" s="25"/>
+      <c r="AG152" s="25"/>
+      <c r="AH152" s="25"/>
+      <c r="AI152" s="25"/>
+      <c r="AJ152" s="26"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="24"/>
-      <c r="C153" s="24"/>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="24"/>
-      <c r="H153" s="24"/>
-      <c r="I153" s="25"/>
-      <c r="J153" s="25"/>
-      <c r="K153" s="24"/>
-      <c r="L153" s="24"/>
-      <c r="M153" s="24"/>
-      <c r="N153" s="25"/>
-      <c r="O153" s="25"/>
-      <c r="P153" s="26"/>
-      <c r="Q153" s="24"/>
-      <c r="R153" s="24"/>
-      <c r="S153" s="25"/>
-      <c r="T153" s="25"/>
-      <c r="U153" s="24"/>
-      <c r="V153" s="24"/>
-      <c r="W153" s="24"/>
-      <c r="X153" s="24"/>
-      <c r="Y153" s="24"/>
-      <c r="Z153" s="24"/>
-      <c r="AA153" s="24"/>
-      <c r="AB153" s="24"/>
-      <c r="AC153" s="24"/>
-      <c r="AD153" s="24"/>
-      <c r="AE153" s="24"/>
-      <c r="AF153" s="24"/>
-      <c r="AG153" s="24"/>
-      <c r="AH153" s="24"/>
-      <c r="AI153" s="24"/>
-      <c r="AJ153" s="25"/>
+      <c r="B153" s="25"/>
+      <c r="C153" s="25"/>
+      <c r="D153" s="25"/>
+      <c r="E153" s="25"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="25"/>
+      <c r="H153" s="25"/>
+      <c r="I153" s="26"/>
+      <c r="J153" s="26"/>
+      <c r="K153" s="25"/>
+      <c r="L153" s="25"/>
+      <c r="M153" s="25"/>
+      <c r="N153" s="26"/>
+      <c r="O153" s="26"/>
+      <c r="P153" s="27"/>
+      <c r="Q153" s="25"/>
+      <c r="R153" s="25"/>
+      <c r="S153" s="26"/>
+      <c r="T153" s="26"/>
+      <c r="U153" s="25"/>
+      <c r="V153" s="25"/>
+      <c r="W153" s="25"/>
+      <c r="X153" s="25"/>
+      <c r="Y153" s="25"/>
+      <c r="Z153" s="25"/>
+      <c r="AA153" s="25"/>
+      <c r="AB153" s="25"/>
+      <c r="AC153" s="25"/>
+      <c r="AD153" s="25"/>
+      <c r="AE153" s="25"/>
+      <c r="AF153" s="25"/>
+      <c r="AG153" s="25"/>
+      <c r="AH153" s="25"/>
+      <c r="AI153" s="25"/>
+      <c r="AJ153" s="26"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="24"/>
-      <c r="C154" s="24"/>
-      <c r="D154" s="24"/>
-      <c r="E154" s="24"/>
-      <c r="F154" s="24"/>
-      <c r="G154" s="24"/>
-      <c r="H154" s="24"/>
-      <c r="I154" s="25"/>
-      <c r="J154" s="25"/>
-      <c r="K154" s="24"/>
-      <c r="L154" s="24"/>
-      <c r="M154" s="24"/>
-      <c r="N154" s="25"/>
-      <c r="O154" s="25"/>
-      <c r="P154" s="26"/>
-      <c r="Q154" s="24"/>
-      <c r="R154" s="24"/>
-      <c r="S154" s="25"/>
-      <c r="T154" s="25"/>
-      <c r="U154" s="24"/>
-      <c r="V154" s="24"/>
-      <c r="W154" s="24"/>
-      <c r="X154" s="24"/>
-      <c r="Y154" s="24"/>
-      <c r="Z154" s="24"/>
-      <c r="AA154" s="24"/>
-      <c r="AB154" s="24"/>
-      <c r="AC154" s="24"/>
-      <c r="AD154" s="24"/>
-      <c r="AE154" s="24"/>
-      <c r="AF154" s="24"/>
-      <c r="AG154" s="24"/>
-      <c r="AH154" s="24"/>
-      <c r="AI154" s="24"/>
-      <c r="AJ154" s="25"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="25"/>
+      <c r="D154" s="25"/>
+      <c r="E154" s="25"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
+      <c r="H154" s="25"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="26"/>
+      <c r="K154" s="25"/>
+      <c r="L154" s="25"/>
+      <c r="M154" s="25"/>
+      <c r="N154" s="26"/>
+      <c r="O154" s="26"/>
+      <c r="P154" s="27"/>
+      <c r="Q154" s="25"/>
+      <c r="R154" s="25"/>
+      <c r="S154" s="26"/>
+      <c r="T154" s="26"/>
+      <c r="U154" s="25"/>
+      <c r="V154" s="25"/>
+      <c r="W154" s="25"/>
+      <c r="X154" s="25"/>
+      <c r="Y154" s="25"/>
+      <c r="Z154" s="25"/>
+      <c r="AA154" s="25"/>
+      <c r="AB154" s="25"/>
+      <c r="AC154" s="25"/>
+      <c r="AD154" s="25"/>
+      <c r="AE154" s="25"/>
+      <c r="AF154" s="25"/>
+      <c r="AG154" s="25"/>
+      <c r="AH154" s="25"/>
+      <c r="AI154" s="25"/>
+      <c r="AJ154" s="26"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="24"/>
-      <c r="C155" s="24"/>
-      <c r="D155" s="24"/>
-      <c r="E155" s="24"/>
-      <c r="F155" s="24"/>
-      <c r="G155" s="24"/>
-      <c r="H155" s="24"/>
-      <c r="I155" s="25"/>
-      <c r="J155" s="25"/>
-      <c r="K155" s="24"/>
-      <c r="L155" s="24"/>
-      <c r="M155" s="24"/>
-      <c r="N155" s="25"/>
-      <c r="O155" s="25"/>
-      <c r="P155" s="26"/>
-      <c r="Q155" s="24"/>
-      <c r="R155" s="24"/>
-      <c r="S155" s="25"/>
-      <c r="T155" s="25"/>
-      <c r="U155" s="24"/>
-      <c r="V155" s="24"/>
-      <c r="W155" s="24"/>
-      <c r="X155" s="24"/>
-      <c r="Y155" s="24"/>
-      <c r="Z155" s="24"/>
-      <c r="AA155" s="24"/>
-      <c r="AB155" s="24"/>
-      <c r="AC155" s="24"/>
-      <c r="AD155" s="24"/>
-      <c r="AE155" s="24"/>
-      <c r="AF155" s="24"/>
-      <c r="AG155" s="24"/>
-      <c r="AH155" s="24"/>
-      <c r="AI155" s="24"/>
-      <c r="AJ155" s="25"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="25"/>
+      <c r="D155" s="25"/>
+      <c r="E155" s="25"/>
+      <c r="F155" s="25"/>
+      <c r="G155" s="25"/>
+      <c r="H155" s="25"/>
+      <c r="I155" s="26"/>
+      <c r="J155" s="26"/>
+      <c r="K155" s="25"/>
+      <c r="L155" s="25"/>
+      <c r="M155" s="25"/>
+      <c r="N155" s="26"/>
+      <c r="O155" s="26"/>
+      <c r="P155" s="27"/>
+      <c r="Q155" s="25"/>
+      <c r="R155" s="25"/>
+      <c r="S155" s="26"/>
+      <c r="T155" s="26"/>
+      <c r="U155" s="25"/>
+      <c r="V155" s="25"/>
+      <c r="W155" s="25"/>
+      <c r="X155" s="25"/>
+      <c r="Y155" s="25"/>
+      <c r="Z155" s="25"/>
+      <c r="AA155" s="25"/>
+      <c r="AB155" s="25"/>
+      <c r="AC155" s="25"/>
+      <c r="AD155" s="25"/>
+      <c r="AE155" s="25"/>
+      <c r="AF155" s="25"/>
+      <c r="AG155" s="25"/>
+      <c r="AH155" s="25"/>
+      <c r="AI155" s="25"/>
+      <c r="AJ155" s="26"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="24"/>
-      <c r="C156" s="24"/>
-      <c r="D156" s="24"/>
-      <c r="E156" s="24"/>
-      <c r="F156" s="24"/>
-      <c r="G156" s="24"/>
-      <c r="H156" s="24"/>
-      <c r="I156" s="25"/>
-      <c r="J156" s="25"/>
-      <c r="K156" s="24"/>
-      <c r="L156" s="24"/>
-      <c r="M156" s="24"/>
-      <c r="N156" s="25"/>
-      <c r="O156" s="25"/>
-      <c r="P156" s="26"/>
-      <c r="Q156" s="24"/>
-      <c r="R156" s="24"/>
-      <c r="S156" s="25"/>
-      <c r="T156" s="25"/>
-      <c r="U156" s="24"/>
-      <c r="V156" s="24"/>
-      <c r="W156" s="24"/>
-      <c r="X156" s="24"/>
-      <c r="Y156" s="24"/>
-      <c r="Z156" s="24"/>
-      <c r="AA156" s="24"/>
-      <c r="AB156" s="24"/>
-      <c r="AC156" s="24"/>
-      <c r="AD156" s="24"/>
-      <c r="AE156" s="24"/>
-      <c r="AF156" s="24"/>
-      <c r="AG156" s="24"/>
-      <c r="AH156" s="24"/>
-      <c r="AI156" s="24"/>
-      <c r="AJ156" s="25"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="25"/>
+      <c r="D156" s="25"/>
+      <c r="E156" s="25"/>
+      <c r="F156" s="25"/>
+      <c r="G156" s="25"/>
+      <c r="H156" s="25"/>
+      <c r="I156" s="26"/>
+      <c r="J156" s="26"/>
+      <c r="K156" s="25"/>
+      <c r="L156" s="25"/>
+      <c r="M156" s="25"/>
+      <c r="N156" s="26"/>
+      <c r="O156" s="26"/>
+      <c r="P156" s="27"/>
+      <c r="Q156" s="25"/>
+      <c r="R156" s="25"/>
+      <c r="S156" s="26"/>
+      <c r="T156" s="26"/>
+      <c r="U156" s="25"/>
+      <c r="V156" s="25"/>
+      <c r="W156" s="25"/>
+      <c r="X156" s="25"/>
+      <c r="Y156" s="25"/>
+      <c r="Z156" s="25"/>
+      <c r="AA156" s="25"/>
+      <c r="AB156" s="25"/>
+      <c r="AC156" s="25"/>
+      <c r="AD156" s="25"/>
+      <c r="AE156" s="25"/>
+      <c r="AF156" s="25"/>
+      <c r="AG156" s="25"/>
+      <c r="AH156" s="25"/>
+      <c r="AI156" s="25"/>
+      <c r="AJ156" s="26"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="24"/>
-      <c r="C157" s="24"/>
-      <c r="D157" s="24"/>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="25"/>
-      <c r="K157" s="24"/>
-      <c r="L157" s="24"/>
-      <c r="M157" s="24"/>
-      <c r="N157" s="25"/>
-      <c r="O157" s="25"/>
-      <c r="P157" s="26"/>
-      <c r="Q157" s="24"/>
-      <c r="R157" s="24"/>
-      <c r="S157" s="25"/>
-      <c r="T157" s="25"/>
-      <c r="U157" s="24"/>
-      <c r="V157" s="24"/>
-      <c r="W157" s="24"/>
-      <c r="X157" s="24"/>
-      <c r="Y157" s="24"/>
-      <c r="Z157" s="24"/>
-      <c r="AA157" s="24"/>
-      <c r="AB157" s="24"/>
-      <c r="AC157" s="24"/>
-      <c r="AD157" s="24"/>
-      <c r="AE157" s="24"/>
-      <c r="AF157" s="24"/>
-      <c r="AG157" s="24"/>
-      <c r="AH157" s="24"/>
-      <c r="AI157" s="24"/>
-      <c r="AJ157" s="25"/>
+      <c r="B157" s="25"/>
+      <c r="C157" s="25"/>
+      <c r="D157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="26"/>
+      <c r="J157" s="26"/>
+      <c r="K157" s="25"/>
+      <c r="L157" s="25"/>
+      <c r="M157" s="25"/>
+      <c r="N157" s="26"/>
+      <c r="O157" s="26"/>
+      <c r="P157" s="27"/>
+      <c r="Q157" s="25"/>
+      <c r="R157" s="25"/>
+      <c r="S157" s="26"/>
+      <c r="T157" s="26"/>
+      <c r="U157" s="25"/>
+      <c r="V157" s="25"/>
+      <c r="W157" s="25"/>
+      <c r="X157" s="25"/>
+      <c r="Y157" s="25"/>
+      <c r="Z157" s="25"/>
+      <c r="AA157" s="25"/>
+      <c r="AB157" s="25"/>
+      <c r="AC157" s="25"/>
+      <c r="AD157" s="25"/>
+      <c r="AE157" s="25"/>
+      <c r="AF157" s="25"/>
+      <c r="AG157" s="25"/>
+      <c r="AH157" s="25"/>
+      <c r="AI157" s="25"/>
+      <c r="AJ157" s="26"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="24"/>
-      <c r="C158" s="24"/>
-      <c r="D158" s="24"/>
-      <c r="E158" s="24"/>
-      <c r="F158" s="24"/>
-      <c r="G158" s="24"/>
-      <c r="H158" s="24"/>
-      <c r="I158" s="25"/>
-      <c r="J158" s="25"/>
-      <c r="K158" s="24"/>
-      <c r="L158" s="24"/>
-      <c r="M158" s="24"/>
-      <c r="N158" s="25"/>
-      <c r="O158" s="25"/>
-      <c r="P158" s="26"/>
-      <c r="Q158" s="24"/>
-      <c r="R158" s="24"/>
-      <c r="S158" s="25"/>
-      <c r="T158" s="25"/>
-      <c r="U158" s="24"/>
-      <c r="V158" s="24"/>
-      <c r="W158" s="24"/>
-      <c r="X158" s="24"/>
-      <c r="Y158" s="24"/>
-      <c r="Z158" s="24"/>
-      <c r="AA158" s="24"/>
-      <c r="AB158" s="24"/>
-      <c r="AC158" s="24"/>
-      <c r="AD158" s="24"/>
-      <c r="AE158" s="24"/>
-      <c r="AF158" s="24"/>
-      <c r="AG158" s="24"/>
-      <c r="AH158" s="24"/>
-      <c r="AI158" s="24"/>
-      <c r="AJ158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+      <c r="D158" s="25"/>
+      <c r="E158" s="25"/>
+      <c r="F158" s="25"/>
+      <c r="G158" s="25"/>
+      <c r="H158" s="25"/>
+      <c r="I158" s="26"/>
+      <c r="J158" s="26"/>
+      <c r="K158" s="25"/>
+      <c r="L158" s="25"/>
+      <c r="M158" s="25"/>
+      <c r="N158" s="26"/>
+      <c r="O158" s="26"/>
+      <c r="P158" s="27"/>
+      <c r="Q158" s="25"/>
+      <c r="R158" s="25"/>
+      <c r="S158" s="26"/>
+      <c r="T158" s="26"/>
+      <c r="U158" s="25"/>
+      <c r="V158" s="25"/>
+      <c r="W158" s="25"/>
+      <c r="X158" s="25"/>
+      <c r="Y158" s="25"/>
+      <c r="Z158" s="25"/>
+      <c r="AA158" s="25"/>
+      <c r="AB158" s="25"/>
+      <c r="AC158" s="25"/>
+      <c r="AD158" s="25"/>
+      <c r="AE158" s="25"/>
+      <c r="AF158" s="25"/>
+      <c r="AG158" s="25"/>
+      <c r="AH158" s="25"/>
+      <c r="AI158" s="25"/>
+      <c r="AJ158" s="26"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="24"/>
-      <c r="C159" s="24"/>
-      <c r="D159" s="24"/>
-      <c r="E159" s="24"/>
-      <c r="F159" s="24"/>
-      <c r="G159" s="24"/>
-      <c r="H159" s="24"/>
-      <c r="I159" s="25"/>
-      <c r="J159" s="25"/>
-      <c r="K159" s="24"/>
-      <c r="L159" s="24"/>
-      <c r="M159" s="24"/>
-      <c r="N159" s="25"/>
-      <c r="O159" s="25"/>
-      <c r="P159" s="26"/>
-      <c r="Q159" s="24"/>
-      <c r="R159" s="24"/>
-      <c r="S159" s="25"/>
-      <c r="T159" s="25"/>
-      <c r="U159" s="24"/>
-      <c r="V159" s="24"/>
-      <c r="W159" s="24"/>
-      <c r="X159" s="24"/>
-      <c r="Y159" s="24"/>
-      <c r="Z159" s="24"/>
-      <c r="AA159" s="24"/>
-      <c r="AB159" s="24"/>
-      <c r="AC159" s="24"/>
-      <c r="AD159" s="24"/>
-      <c r="AE159" s="24"/>
-      <c r="AF159" s="24"/>
-      <c r="AG159" s="24"/>
-      <c r="AH159" s="24"/>
-      <c r="AI159" s="24"/>
-      <c r="AJ159" s="25"/>
+      <c r="B159" s="25"/>
+      <c r="C159" s="25"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="25"/>
+      <c r="F159" s="25"/>
+      <c r="G159" s="25"/>
+      <c r="H159" s="25"/>
+      <c r="I159" s="26"/>
+      <c r="J159" s="26"/>
+      <c r="K159" s="25"/>
+      <c r="L159" s="25"/>
+      <c r="M159" s="25"/>
+      <c r="N159" s="26"/>
+      <c r="O159" s="26"/>
+      <c r="P159" s="27"/>
+      <c r="Q159" s="25"/>
+      <c r="R159" s="25"/>
+      <c r="S159" s="26"/>
+      <c r="T159" s="26"/>
+      <c r="U159" s="25"/>
+      <c r="V159" s="25"/>
+      <c r="W159" s="25"/>
+      <c r="X159" s="25"/>
+      <c r="Y159" s="25"/>
+      <c r="Z159" s="25"/>
+      <c r="AA159" s="25"/>
+      <c r="AB159" s="25"/>
+      <c r="AC159" s="25"/>
+      <c r="AD159" s="25"/>
+      <c r="AE159" s="25"/>
+      <c r="AF159" s="25"/>
+      <c r="AG159" s="25"/>
+      <c r="AH159" s="25"/>
+      <c r="AI159" s="25"/>
+      <c r="AJ159" s="26"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="24"/>
-      <c r="C160" s="24"/>
-      <c r="D160" s="24"/>
-      <c r="E160" s="24"/>
-      <c r="F160" s="24"/>
-      <c r="G160" s="24"/>
-      <c r="H160" s="24"/>
-      <c r="I160" s="25"/>
-      <c r="J160" s="25"/>
-      <c r="K160" s="24"/>
-      <c r="L160" s="24"/>
-      <c r="M160" s="24"/>
-      <c r="N160" s="25"/>
-      <c r="O160" s="25"/>
-      <c r="P160" s="26"/>
-      <c r="Q160" s="24"/>
-      <c r="R160" s="24"/>
-      <c r="S160" s="25"/>
-      <c r="T160" s="25"/>
-      <c r="U160" s="24"/>
-      <c r="V160" s="24"/>
-      <c r="W160" s="24"/>
-      <c r="X160" s="24"/>
-      <c r="Y160" s="24"/>
-      <c r="Z160" s="24"/>
-      <c r="AA160" s="24"/>
-      <c r="AB160" s="24"/>
-      <c r="AC160" s="24"/>
-      <c r="AD160" s="24"/>
-      <c r="AE160" s="24"/>
-      <c r="AF160" s="24"/>
-      <c r="AG160" s="24"/>
-      <c r="AH160" s="24"/>
-      <c r="AI160" s="24"/>
-      <c r="AJ160" s="25"/>
+      <c r="B160" s="25"/>
+      <c r="C160" s="25"/>
+      <c r="D160" s="25"/>
+      <c r="E160" s="25"/>
+      <c r="F160" s="25"/>
+      <c r="G160" s="25"/>
+      <c r="H160" s="25"/>
+      <c r="I160" s="26"/>
+      <c r="J160" s="26"/>
+      <c r="K160" s="25"/>
+      <c r="L160" s="25"/>
+      <c r="M160" s="25"/>
+      <c r="N160" s="26"/>
+      <c r="O160" s="26"/>
+      <c r="P160" s="27"/>
+      <c r="Q160" s="25"/>
+      <c r="R160" s="25"/>
+      <c r="S160" s="26"/>
+      <c r="T160" s="26"/>
+      <c r="U160" s="25"/>
+      <c r="V160" s="25"/>
+      <c r="W160" s="25"/>
+      <c r="X160" s="25"/>
+      <c r="Y160" s="25"/>
+      <c r="Z160" s="25"/>
+      <c r="AA160" s="25"/>
+      <c r="AB160" s="25"/>
+      <c r="AC160" s="25"/>
+      <c r="AD160" s="25"/>
+      <c r="AE160" s="25"/>
+      <c r="AF160" s="25"/>
+      <c r="AG160" s="25"/>
+      <c r="AH160" s="25"/>
+      <c r="AI160" s="25"/>
+      <c r="AJ160" s="26"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="24"/>
-      <c r="C161" s="24"/>
-      <c r="D161" s="24"/>
-      <c r="E161" s="24"/>
-      <c r="F161" s="24"/>
-      <c r="G161" s="24"/>
-      <c r="H161" s="24"/>
-      <c r="I161" s="25"/>
-      <c r="J161" s="25"/>
-      <c r="K161" s="24"/>
-      <c r="L161" s="24"/>
-      <c r="M161" s="24"/>
-      <c r="N161" s="25"/>
-      <c r="O161" s="25"/>
-      <c r="P161" s="26"/>
-      <c r="Q161" s="24"/>
-      <c r="R161" s="24"/>
-      <c r="S161" s="25"/>
-      <c r="T161" s="25"/>
-      <c r="U161" s="24"/>
-      <c r="V161" s="24"/>
-      <c r="W161" s="24"/>
-      <c r="X161" s="24"/>
-      <c r="Y161" s="24"/>
-      <c r="Z161" s="24"/>
-      <c r="AA161" s="24"/>
-      <c r="AB161" s="24"/>
-      <c r="AC161" s="24"/>
-      <c r="AD161" s="24"/>
-      <c r="AE161" s="24"/>
-      <c r="AF161" s="24"/>
-      <c r="AG161" s="24"/>
-      <c r="AH161" s="24"/>
-      <c r="AI161" s="24"/>
-      <c r="AJ161" s="25"/>
+      <c r="B161" s="25"/>
+      <c r="C161" s="25"/>
+      <c r="D161" s="25"/>
+      <c r="E161" s="25"/>
+      <c r="F161" s="25"/>
+      <c r="G161" s="25"/>
+      <c r="H161" s="25"/>
+      <c r="I161" s="26"/>
+      <c r="J161" s="26"/>
+      <c r="K161" s="25"/>
+      <c r="L161" s="25"/>
+      <c r="M161" s="25"/>
+      <c r="N161" s="26"/>
+      <c r="O161" s="26"/>
+      <c r="P161" s="27"/>
+      <c r="Q161" s="25"/>
+      <c r="R161" s="25"/>
+      <c r="S161" s="26"/>
+      <c r="T161" s="26"/>
+      <c r="U161" s="25"/>
+      <c r="V161" s="25"/>
+      <c r="W161" s="25"/>
+      <c r="X161" s="25"/>
+      <c r="Y161" s="25"/>
+      <c r="Z161" s="25"/>
+      <c r="AA161" s="25"/>
+      <c r="AB161" s="25"/>
+      <c r="AC161" s="25"/>
+      <c r="AD161" s="25"/>
+      <c r="AE161" s="25"/>
+      <c r="AF161" s="25"/>
+      <c r="AG161" s="25"/>
+      <c r="AH161" s="25"/>
+      <c r="AI161" s="25"/>
+      <c r="AJ161" s="26"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="24"/>
-      <c r="C162" s="24"/>
-      <c r="D162" s="24"/>
-      <c r="E162" s="24"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="24"/>
-      <c r="H162" s="24"/>
-      <c r="I162" s="25"/>
-      <c r="J162" s="25"/>
-      <c r="K162" s="24"/>
-      <c r="L162" s="24"/>
-      <c r="M162" s="24"/>
-      <c r="N162" s="25"/>
-      <c r="O162" s="25"/>
-      <c r="P162" s="26"/>
-      <c r="Q162" s="24"/>
-      <c r="R162" s="24"/>
-      <c r="S162" s="25"/>
-      <c r="T162" s="25"/>
-      <c r="U162" s="24"/>
-      <c r="V162" s="24"/>
-      <c r="W162" s="24"/>
-      <c r="X162" s="24"/>
-      <c r="Y162" s="24"/>
-      <c r="Z162" s="24"/>
-      <c r="AA162" s="24"/>
-      <c r="AB162" s="24"/>
-      <c r="AC162" s="24"/>
-      <c r="AD162" s="24"/>
-      <c r="AE162" s="24"/>
-      <c r="AF162" s="24"/>
-      <c r="AG162" s="24"/>
-      <c r="AH162" s="24"/>
-      <c r="AI162" s="24"/>
-      <c r="AJ162" s="25"/>
+      <c r="B162" s="25"/>
+      <c r="C162" s="25"/>
+      <c r="D162" s="25"/>
+      <c r="E162" s="25"/>
+      <c r="F162" s="25"/>
+      <c r="G162" s="25"/>
+      <c r="H162" s="25"/>
+      <c r="I162" s="26"/>
+      <c r="J162" s="26"/>
+      <c r="K162" s="25"/>
+      <c r="L162" s="25"/>
+      <c r="M162" s="25"/>
+      <c r="N162" s="26"/>
+      <c r="O162" s="26"/>
+      <c r="P162" s="27"/>
+      <c r="Q162" s="25"/>
+      <c r="R162" s="25"/>
+      <c r="S162" s="26"/>
+      <c r="T162" s="26"/>
+      <c r="U162" s="25"/>
+      <c r="V162" s="25"/>
+      <c r="W162" s="25"/>
+      <c r="X162" s="25"/>
+      <c r="Y162" s="25"/>
+      <c r="Z162" s="25"/>
+      <c r="AA162" s="25"/>
+      <c r="AB162" s="25"/>
+      <c r="AC162" s="25"/>
+      <c r="AD162" s="25"/>
+      <c r="AE162" s="25"/>
+      <c r="AF162" s="25"/>
+      <c r="AG162" s="25"/>
+      <c r="AH162" s="25"/>
+      <c r="AI162" s="25"/>
+      <c r="AJ162" s="26"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="24"/>
-      <c r="C163" s="24"/>
-      <c r="D163" s="24"/>
-      <c r="E163" s="24"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="24"/>
-      <c r="H163" s="24"/>
-      <c r="I163" s="25"/>
-      <c r="J163" s="25"/>
-      <c r="K163" s="24"/>
-      <c r="L163" s="24"/>
-      <c r="M163" s="24"/>
-      <c r="N163" s="25"/>
-      <c r="O163" s="25"/>
-      <c r="P163" s="26"/>
-      <c r="Q163" s="24"/>
-      <c r="R163" s="24"/>
-      <c r="S163" s="25"/>
-      <c r="T163" s="25"/>
-      <c r="U163" s="24"/>
-      <c r="V163" s="24"/>
-      <c r="W163" s="24"/>
-      <c r="X163" s="24"/>
-      <c r="Y163" s="24"/>
-      <c r="Z163" s="24"/>
-      <c r="AA163" s="24"/>
-      <c r="AB163" s="24"/>
-      <c r="AC163" s="24"/>
-      <c r="AD163" s="24"/>
-      <c r="AE163" s="24"/>
-      <c r="AF163" s="24"/>
-      <c r="AG163" s="24"/>
-      <c r="AH163" s="24"/>
-      <c r="AI163" s="24"/>
-      <c r="AJ163" s="25"/>
+      <c r="B163" s="25"/>
+      <c r="C163" s="25"/>
+      <c r="D163" s="25"/>
+      <c r="E163" s="25"/>
+      <c r="F163" s="25"/>
+      <c r="G163" s="25"/>
+      <c r="H163" s="25"/>
+      <c r="I163" s="26"/>
+      <c r="J163" s="26"/>
+      <c r="K163" s="25"/>
+      <c r="L163" s="25"/>
+      <c r="M163" s="25"/>
+      <c r="N163" s="26"/>
+      <c r="O163" s="26"/>
+      <c r="P163" s="27"/>
+      <c r="Q163" s="25"/>
+      <c r="R163" s="25"/>
+      <c r="S163" s="26"/>
+      <c r="T163" s="26"/>
+      <c r="U163" s="25"/>
+      <c r="V163" s="25"/>
+      <c r="W163" s="25"/>
+      <c r="X163" s="25"/>
+      <c r="Y163" s="25"/>
+      <c r="Z163" s="25"/>
+      <c r="AA163" s="25"/>
+      <c r="AB163" s="25"/>
+      <c r="AC163" s="25"/>
+      <c r="AD163" s="25"/>
+      <c r="AE163" s="25"/>
+      <c r="AF163" s="25"/>
+      <c r="AG163" s="25"/>
+      <c r="AH163" s="25"/>
+      <c r="AI163" s="25"/>
+      <c r="AJ163" s="26"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="24"/>
-      <c r="C164" s="24"/>
-      <c r="D164" s="24"/>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="25"/>
-      <c r="K164" s="24"/>
-      <c r="L164" s="24"/>
-      <c r="M164" s="24"/>
-      <c r="N164" s="25"/>
-      <c r="O164" s="25"/>
-      <c r="P164" s="26"/>
-      <c r="Q164" s="24"/>
-      <c r="R164" s="24"/>
-      <c r="S164" s="25"/>
-      <c r="T164" s="25"/>
-      <c r="U164" s="24"/>
-      <c r="V164" s="24"/>
-      <c r="W164" s="24"/>
-      <c r="X164" s="24"/>
-      <c r="Y164" s="24"/>
-      <c r="Z164" s="24"/>
-      <c r="AA164" s="24"/>
-      <c r="AB164" s="24"/>
-      <c r="AC164" s="24"/>
-      <c r="AD164" s="24"/>
-      <c r="AE164" s="24"/>
-      <c r="AF164" s="24"/>
-      <c r="AG164" s="24"/>
-      <c r="AH164" s="24"/>
-      <c r="AI164" s="24"/>
-      <c r="AJ164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+      <c r="D164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="26"/>
+      <c r="J164" s="26"/>
+      <c r="K164" s="25"/>
+      <c r="L164" s="25"/>
+      <c r="M164" s="25"/>
+      <c r="N164" s="26"/>
+      <c r="O164" s="26"/>
+      <c r="P164" s="27"/>
+      <c r="Q164" s="25"/>
+      <c r="R164" s="25"/>
+      <c r="S164" s="26"/>
+      <c r="T164" s="26"/>
+      <c r="U164" s="25"/>
+      <c r="V164" s="25"/>
+      <c r="W164" s="25"/>
+      <c r="X164" s="25"/>
+      <c r="Y164" s="25"/>
+      <c r="Z164" s="25"/>
+      <c r="AA164" s="25"/>
+      <c r="AB164" s="25"/>
+      <c r="AC164" s="25"/>
+      <c r="AD164" s="25"/>
+      <c r="AE164" s="25"/>
+      <c r="AF164" s="25"/>
+      <c r="AG164" s="25"/>
+      <c r="AH164" s="25"/>
+      <c r="AI164" s="25"/>
+      <c r="AJ164" s="26"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="24"/>
-      <c r="C165" s="24"/>
-      <c r="D165" s="24"/>
-      <c r="E165" s="24"/>
-      <c r="F165" s="24"/>
-      <c r="G165" s="24"/>
-      <c r="H165" s="24"/>
-      <c r="I165" s="25"/>
-      <c r="J165" s="25"/>
-      <c r="K165" s="24"/>
-      <c r="L165" s="24"/>
-      <c r="M165" s="24"/>
-      <c r="N165" s="25"/>
-      <c r="O165" s="25"/>
-      <c r="P165" s="26"/>
-      <c r="Q165" s="24"/>
-      <c r="R165" s="24"/>
-      <c r="S165" s="25"/>
-      <c r="T165" s="25"/>
-      <c r="U165" s="24"/>
-      <c r="V165" s="24"/>
-      <c r="W165" s="24"/>
-      <c r="X165" s="24"/>
-      <c r="Y165" s="24"/>
-      <c r="Z165" s="24"/>
-      <c r="AA165" s="24"/>
-      <c r="AB165" s="24"/>
-      <c r="AC165" s="24"/>
-      <c r="AD165" s="24"/>
-      <c r="AE165" s="24"/>
-      <c r="AF165" s="24"/>
-      <c r="AG165" s="24"/>
-      <c r="AH165" s="24"/>
-      <c r="AI165" s="24"/>
-      <c r="AJ165" s="25"/>
+      <c r="B165" s="25"/>
+      <c r="C165" s="25"/>
+      <c r="D165" s="25"/>
+      <c r="E165" s="25"/>
+      <c r="F165" s="25"/>
+      <c r="G165" s="25"/>
+      <c r="H165" s="25"/>
+      <c r="I165" s="26"/>
+      <c r="J165" s="26"/>
+      <c r="K165" s="25"/>
+      <c r="L165" s="25"/>
+      <c r="M165" s="25"/>
+      <c r="N165" s="26"/>
+      <c r="O165" s="26"/>
+      <c r="P165" s="27"/>
+      <c r="Q165" s="25"/>
+      <c r="R165" s="25"/>
+      <c r="S165" s="26"/>
+      <c r="T165" s="26"/>
+      <c r="U165" s="25"/>
+      <c r="V165" s="25"/>
+      <c r="W165" s="25"/>
+      <c r="X165" s="25"/>
+      <c r="Y165" s="25"/>
+      <c r="Z165" s="25"/>
+      <c r="AA165" s="25"/>
+      <c r="AB165" s="25"/>
+      <c r="AC165" s="25"/>
+      <c r="AD165" s="25"/>
+      <c r="AE165" s="25"/>
+      <c r="AF165" s="25"/>
+      <c r="AG165" s="25"/>
+      <c r="AH165" s="25"/>
+      <c r="AI165" s="25"/>
+      <c r="AJ165" s="26"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="24"/>
-      <c r="C166" s="24"/>
-      <c r="D166" s="24"/>
-      <c r="E166" s="24"/>
-      <c r="F166" s="24"/>
-      <c r="G166" s="24"/>
-      <c r="H166" s="24"/>
-      <c r="I166" s="25"/>
-      <c r="J166" s="25"/>
-      <c r="K166" s="24"/>
-      <c r="L166" s="24"/>
-      <c r="M166" s="24"/>
-      <c r="N166" s="25"/>
-      <c r="O166" s="25"/>
-      <c r="P166" s="26"/>
-      <c r="Q166" s="24"/>
-      <c r="R166" s="24"/>
-      <c r="S166" s="25"/>
-      <c r="T166" s="25"/>
-      <c r="U166" s="24"/>
-      <c r="V166" s="24"/>
-      <c r="W166" s="24"/>
-      <c r="X166" s="24"/>
-      <c r="Y166" s="24"/>
-      <c r="Z166" s="24"/>
-      <c r="AA166" s="24"/>
-      <c r="AB166" s="24"/>
-      <c r="AC166" s="24"/>
-      <c r="AD166" s="24"/>
-      <c r="AE166" s="24"/>
-      <c r="AF166" s="24"/>
-      <c r="AG166" s="24"/>
-      <c r="AH166" s="24"/>
-      <c r="AI166" s="24"/>
-      <c r="AJ166" s="25"/>
+      <c r="B166" s="25"/>
+      <c r="C166" s="25"/>
+      <c r="D166" s="25"/>
+      <c r="E166" s="25"/>
+      <c r="F166" s="25"/>
+      <c r="G166" s="25"/>
+      <c r="H166" s="25"/>
+      <c r="I166" s="26"/>
+      <c r="J166" s="26"/>
+      <c r="K166" s="25"/>
+      <c r="L166" s="25"/>
+      <c r="M166" s="25"/>
+      <c r="N166" s="26"/>
+      <c r="O166" s="26"/>
+      <c r="P166" s="27"/>
+      <c r="Q166" s="25"/>
+      <c r="R166" s="25"/>
+      <c r="S166" s="26"/>
+      <c r="T166" s="26"/>
+      <c r="U166" s="25"/>
+      <c r="V166" s="25"/>
+      <c r="W166" s="25"/>
+      <c r="X166" s="25"/>
+      <c r="Y166" s="25"/>
+      <c r="Z166" s="25"/>
+      <c r="AA166" s="25"/>
+      <c r="AB166" s="25"/>
+      <c r="AC166" s="25"/>
+      <c r="AD166" s="25"/>
+      <c r="AE166" s="25"/>
+      <c r="AF166" s="25"/>
+      <c r="AG166" s="25"/>
+      <c r="AH166" s="25"/>
+      <c r="AI166" s="25"/>
+      <c r="AJ166" s="26"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="24"/>
-      <c r="C167" s="24"/>
-      <c r="D167" s="24"/>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24"/>
-      <c r="I167" s="25"/>
-      <c r="J167" s="25"/>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="25"/>
-      <c r="O167" s="25"/>
-      <c r="P167" s="26"/>
-      <c r="Q167" s="24"/>
-      <c r="R167" s="24"/>
-      <c r="S167" s="25"/>
-      <c r="T167" s="25"/>
-      <c r="U167" s="24"/>
-      <c r="V167" s="24"/>
-      <c r="W167" s="24"/>
-      <c r="X167" s="24"/>
-      <c r="Y167" s="24"/>
-      <c r="Z167" s="24"/>
-      <c r="AA167" s="24"/>
-      <c r="AB167" s="24"/>
-      <c r="AC167" s="24"/>
-      <c r="AD167" s="24"/>
-      <c r="AE167" s="24"/>
-      <c r="AF167" s="24"/>
-      <c r="AG167" s="24"/>
-      <c r="AH167" s="24"/>
-      <c r="AI167" s="24"/>
-      <c r="AJ167" s="25"/>
+      <c r="B167" s="25"/>
+      <c r="C167" s="25"/>
+      <c r="D167" s="25"/>
+      <c r="E167" s="25"/>
+      <c r="F167" s="25"/>
+      <c r="G167" s="25"/>
+      <c r="H167" s="25"/>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+      <c r="K167" s="25"/>
+      <c r="L167" s="25"/>
+      <c r="M167" s="25"/>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="27"/>
+      <c r="Q167" s="25"/>
+      <c r="R167" s="25"/>
+      <c r="S167" s="26"/>
+      <c r="T167" s="26"/>
+      <c r="U167" s="25"/>
+      <c r="V167" s="25"/>
+      <c r="W167" s="25"/>
+      <c r="X167" s="25"/>
+      <c r="Y167" s="25"/>
+      <c r="Z167" s="25"/>
+      <c r="AA167" s="25"/>
+      <c r="AB167" s="25"/>
+      <c r="AC167" s="25"/>
+      <c r="AD167" s="25"/>
+      <c r="AE167" s="25"/>
+      <c r="AF167" s="25"/>
+      <c r="AG167" s="25"/>
+      <c r="AH167" s="25"/>
+      <c r="AI167" s="25"/>
+      <c r="AJ167" s="26"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="24"/>
-      <c r="C168" s="24"/>
-      <c r="D168" s="24"/>
-      <c r="E168" s="24"/>
-      <c r="F168" s="24"/>
-      <c r="G168" s="24"/>
-      <c r="H168" s="24"/>
-      <c r="I168" s="25"/>
-      <c r="J168" s="25"/>
-      <c r="K168" s="24"/>
-      <c r="L168" s="24"/>
-      <c r="M168" s="24"/>
-      <c r="N168" s="25"/>
-      <c r="O168" s="25"/>
-      <c r="P168" s="26"/>
-      <c r="Q168" s="24"/>
-      <c r="R168" s="24"/>
-      <c r="S168" s="25"/>
-      <c r="T168" s="25"/>
-      <c r="U168" s="24"/>
-      <c r="V168" s="24"/>
-      <c r="W168" s="24"/>
-      <c r="X168" s="24"/>
-      <c r="Y168" s="24"/>
-      <c r="Z168" s="24"/>
-      <c r="AA168" s="24"/>
-      <c r="AB168" s="24"/>
-      <c r="AC168" s="24"/>
-      <c r="AD168" s="24"/>
-      <c r="AE168" s="24"/>
-      <c r="AF168" s="24"/>
-      <c r="AG168" s="24"/>
-      <c r="AH168" s="24"/>
-      <c r="AI168" s="24"/>
-      <c r="AJ168" s="25"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="25"/>
+      <c r="D168" s="25"/>
+      <c r="E168" s="25"/>
+      <c r="F168" s="25"/>
+      <c r="G168" s="25"/>
+      <c r="H168" s="25"/>
+      <c r="I168" s="26"/>
+      <c r="J168" s="26"/>
+      <c r="K168" s="25"/>
+      <c r="L168" s="25"/>
+      <c r="M168" s="25"/>
+      <c r="N168" s="26"/>
+      <c r="O168" s="26"/>
+      <c r="P168" s="27"/>
+      <c r="Q168" s="25"/>
+      <c r="R168" s="25"/>
+      <c r="S168" s="26"/>
+      <c r="T168" s="26"/>
+      <c r="U168" s="25"/>
+      <c r="V168" s="25"/>
+      <c r="W168" s="25"/>
+      <c r="X168" s="25"/>
+      <c r="Y168" s="25"/>
+      <c r="Z168" s="25"/>
+      <c r="AA168" s="25"/>
+      <c r="AB168" s="25"/>
+      <c r="AC168" s="25"/>
+      <c r="AD168" s="25"/>
+      <c r="AE168" s="25"/>
+      <c r="AF168" s="25"/>
+      <c r="AG168" s="25"/>
+      <c r="AH168" s="25"/>
+      <c r="AI168" s="25"/>
+      <c r="AJ168" s="26"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="24"/>
-      <c r="C169" s="24"/>
-      <c r="D169" s="24"/>
-      <c r="E169" s="24"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="24"/>
-      <c r="H169" s="24"/>
-      <c r="I169" s="25"/>
-      <c r="J169" s="25"/>
-      <c r="K169" s="24"/>
-      <c r="L169" s="24"/>
-      <c r="M169" s="24"/>
-      <c r="N169" s="25"/>
-      <c r="O169" s="25"/>
-      <c r="P169" s="26"/>
-      <c r="Q169" s="24"/>
-      <c r="R169" s="24"/>
-      <c r="S169" s="25"/>
-      <c r="T169" s="25"/>
-      <c r="U169" s="24"/>
-      <c r="V169" s="24"/>
-      <c r="W169" s="24"/>
-      <c r="X169" s="24"/>
-      <c r="Y169" s="24"/>
-      <c r="Z169" s="24"/>
-      <c r="AA169" s="24"/>
-      <c r="AB169" s="24"/>
-      <c r="AC169" s="24"/>
-      <c r="AD169" s="24"/>
-      <c r="AE169" s="24"/>
-      <c r="AF169" s="24"/>
-      <c r="AG169" s="24"/>
-      <c r="AH169" s="24"/>
-      <c r="AI169" s="24"/>
-      <c r="AJ169" s="25"/>
+      <c r="B169" s="25"/>
+      <c r="C169" s="25"/>
+      <c r="D169" s="25"/>
+      <c r="E169" s="25"/>
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
+      <c r="H169" s="25"/>
+      <c r="I169" s="26"/>
+      <c r="J169" s="26"/>
+      <c r="K169" s="25"/>
+      <c r="L169" s="25"/>
+      <c r="M169" s="25"/>
+      <c r="N169" s="26"/>
+      <c r="O169" s="26"/>
+      <c r="P169" s="27"/>
+      <c r="Q169" s="25"/>
+      <c r="R169" s="25"/>
+      <c r="S169" s="26"/>
+      <c r="T169" s="26"/>
+      <c r="U169" s="25"/>
+      <c r="V169" s="25"/>
+      <c r="W169" s="25"/>
+      <c r="X169" s="25"/>
+      <c r="Y169" s="25"/>
+      <c r="Z169" s="25"/>
+      <c r="AA169" s="25"/>
+      <c r="AB169" s="25"/>
+      <c r="AC169" s="25"/>
+      <c r="AD169" s="25"/>
+      <c r="AE169" s="25"/>
+      <c r="AF169" s="25"/>
+      <c r="AG169" s="25"/>
+      <c r="AH169" s="25"/>
+      <c r="AI169" s="25"/>
+      <c r="AJ169" s="26"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="24"/>
-      <c r="C170" s="24"/>
-      <c r="D170" s="24"/>
-      <c r="E170" s="24"/>
-      <c r="F170" s="24"/>
-      <c r="G170" s="24"/>
-      <c r="H170" s="24"/>
-      <c r="I170" s="25"/>
-      <c r="J170" s="25"/>
-      <c r="K170" s="24"/>
-      <c r="L170" s="24"/>
-      <c r="M170" s="24"/>
-      <c r="N170" s="25"/>
-      <c r="O170" s="25"/>
-      <c r="P170" s="26"/>
-      <c r="Q170" s="24"/>
-      <c r="R170" s="24"/>
-      <c r="S170" s="25"/>
-      <c r="T170" s="25"/>
-      <c r="U170" s="24"/>
-      <c r="V170" s="24"/>
-      <c r="W170" s="24"/>
-      <c r="X170" s="24"/>
-      <c r="Y170" s="24"/>
-      <c r="Z170" s="24"/>
-      <c r="AA170" s="24"/>
-      <c r="AB170" s="24"/>
-      <c r="AC170" s="24"/>
-      <c r="AD170" s="24"/>
-      <c r="AE170" s="24"/>
-      <c r="AF170" s="24"/>
-      <c r="AG170" s="24"/>
-      <c r="AH170" s="24"/>
-      <c r="AI170" s="24"/>
-      <c r="AJ170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+      <c r="D170" s="25"/>
+      <c r="E170" s="25"/>
+      <c r="F170" s="25"/>
+      <c r="G170" s="25"/>
+      <c r="H170" s="25"/>
+      <c r="I170" s="26"/>
+      <c r="J170" s="26"/>
+      <c r="K170" s="25"/>
+      <c r="L170" s="25"/>
+      <c r="M170" s="25"/>
+      <c r="N170" s="26"/>
+      <c r="O170" s="26"/>
+      <c r="P170" s="27"/>
+      <c r="Q170" s="25"/>
+      <c r="R170" s="25"/>
+      <c r="S170" s="26"/>
+      <c r="T170" s="26"/>
+      <c r="U170" s="25"/>
+      <c r="V170" s="25"/>
+      <c r="W170" s="25"/>
+      <c r="X170" s="25"/>
+      <c r="Y170" s="25"/>
+      <c r="Z170" s="25"/>
+      <c r="AA170" s="25"/>
+      <c r="AB170" s="25"/>
+      <c r="AC170" s="25"/>
+      <c r="AD170" s="25"/>
+      <c r="AE170" s="25"/>
+      <c r="AF170" s="25"/>
+      <c r="AG170" s="25"/>
+      <c r="AH170" s="25"/>
+      <c r="AI170" s="25"/>
+      <c r="AJ170" s="26"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="24"/>
-      <c r="C171" s="24"/>
-      <c r="D171" s="24"/>
-      <c r="E171" s="24"/>
-      <c r="F171" s="24"/>
-      <c r="G171" s="24"/>
-      <c r="H171" s="24"/>
-      <c r="I171" s="25"/>
-      <c r="J171" s="25"/>
-      <c r="K171" s="24"/>
-      <c r="L171" s="24"/>
-      <c r="M171" s="24"/>
-      <c r="N171" s="25"/>
-      <c r="O171" s="25"/>
-      <c r="P171" s="26"/>
-      <c r="Q171" s="24"/>
-      <c r="R171" s="24"/>
-      <c r="S171" s="25"/>
-      <c r="T171" s="25"/>
-      <c r="U171" s="24"/>
-      <c r="V171" s="24"/>
-      <c r="W171" s="24"/>
-      <c r="X171" s="24"/>
-      <c r="Y171" s="24"/>
-      <c r="Z171" s="24"/>
-      <c r="AA171" s="24"/>
-      <c r="AB171" s="24"/>
-      <c r="AC171" s="24"/>
-      <c r="AD171" s="24"/>
-      <c r="AE171" s="24"/>
-      <c r="AF171" s="24"/>
-      <c r="AG171" s="24"/>
-      <c r="AH171" s="24"/>
-      <c r="AI171" s="24"/>
-      <c r="AJ171" s="25"/>
+      <c r="B171" s="25"/>
+      <c r="C171" s="25"/>
+      <c r="D171" s="25"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="25"/>
+      <c r="G171" s="25"/>
+      <c r="H171" s="25"/>
+      <c r="I171" s="26"/>
+      <c r="J171" s="26"/>
+      <c r="K171" s="25"/>
+      <c r="L171" s="25"/>
+      <c r="M171" s="25"/>
+      <c r="N171" s="26"/>
+      <c r="O171" s="26"/>
+      <c r="P171" s="27"/>
+      <c r="Q171" s="25"/>
+      <c r="R171" s="25"/>
+      <c r="S171" s="26"/>
+      <c r="T171" s="26"/>
+      <c r="U171" s="25"/>
+      <c r="V171" s="25"/>
+      <c r="W171" s="25"/>
+      <c r="X171" s="25"/>
+      <c r="Y171" s="25"/>
+      <c r="Z171" s="25"/>
+      <c r="AA171" s="25"/>
+      <c r="AB171" s="25"/>
+      <c r="AC171" s="25"/>
+      <c r="AD171" s="25"/>
+      <c r="AE171" s="25"/>
+      <c r="AF171" s="25"/>
+      <c r="AG171" s="25"/>
+      <c r="AH171" s="25"/>
+      <c r="AI171" s="25"/>
+      <c r="AJ171" s="26"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="24"/>
-      <c r="C172" s="24"/>
-      <c r="D172" s="24"/>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="25"/>
-      <c r="K172" s="24"/>
-      <c r="L172" s="24"/>
-      <c r="M172" s="24"/>
-      <c r="N172" s="25"/>
-      <c r="O172" s="25"/>
-      <c r="P172" s="26"/>
-      <c r="Q172" s="24"/>
-      <c r="R172" s="24"/>
-      <c r="S172" s="25"/>
-      <c r="T172" s="25"/>
-      <c r="U172" s="24"/>
-      <c r="V172" s="24"/>
-      <c r="W172" s="24"/>
-      <c r="X172" s="24"/>
-      <c r="Y172" s="24"/>
-      <c r="Z172" s="24"/>
-      <c r="AA172" s="24"/>
-      <c r="AB172" s="24"/>
-      <c r="AC172" s="24"/>
-      <c r="AD172" s="24"/>
-      <c r="AE172" s="24"/>
-      <c r="AF172" s="24"/>
-      <c r="AG172" s="24"/>
-      <c r="AH172" s="24"/>
-      <c r="AI172" s="24"/>
-      <c r="AJ172" s="25"/>
+      <c r="B172" s="25"/>
+      <c r="C172" s="25"/>
+      <c r="D172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="26"/>
+      <c r="J172" s="26"/>
+      <c r="K172" s="25"/>
+      <c r="L172" s="25"/>
+      <c r="M172" s="25"/>
+      <c r="N172" s="26"/>
+      <c r="O172" s="26"/>
+      <c r="P172" s="27"/>
+      <c r="Q172" s="25"/>
+      <c r="R172" s="25"/>
+      <c r="S172" s="26"/>
+      <c r="T172" s="26"/>
+      <c r="U172" s="25"/>
+      <c r="V172" s="25"/>
+      <c r="W172" s="25"/>
+      <c r="X172" s="25"/>
+      <c r="Y172" s="25"/>
+      <c r="Z172" s="25"/>
+      <c r="AA172" s="25"/>
+      <c r="AB172" s="25"/>
+      <c r="AC172" s="25"/>
+      <c r="AD172" s="25"/>
+      <c r="AE172" s="25"/>
+      <c r="AF172" s="25"/>
+      <c r="AG172" s="25"/>
+      <c r="AH172" s="25"/>
+      <c r="AI172" s="25"/>
+      <c r="AJ172" s="26"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="24"/>
-      <c r="C173" s="24"/>
-      <c r="D173" s="24"/>
-      <c r="E173" s="24"/>
-      <c r="F173" s="24"/>
-      <c r="G173" s="24"/>
-      <c r="H173" s="24"/>
-      <c r="I173" s="25"/>
-      <c r="J173" s="25"/>
-      <c r="K173" s="24"/>
-      <c r="L173" s="24"/>
-      <c r="M173" s="24"/>
-      <c r="N173" s="25"/>
-      <c r="O173" s="25"/>
-      <c r="P173" s="26"/>
-      <c r="Q173" s="24"/>
-      <c r="R173" s="24"/>
-      <c r="S173" s="25"/>
-      <c r="T173" s="25"/>
-      <c r="U173" s="24"/>
-      <c r="V173" s="24"/>
-      <c r="W173" s="24"/>
-      <c r="X173" s="24"/>
-      <c r="Y173" s="24"/>
-      <c r="Z173" s="24"/>
-      <c r="AA173" s="24"/>
-      <c r="AB173" s="24"/>
-      <c r="AC173" s="24"/>
-      <c r="AD173" s="24"/>
-      <c r="AE173" s="24"/>
-      <c r="AF173" s="24"/>
-      <c r="AG173" s="24"/>
-      <c r="AH173" s="24"/>
-      <c r="AI173" s="24"/>
-      <c r="AJ173" s="25"/>
+      <c r="B173" s="25"/>
+      <c r="C173" s="25"/>
+      <c r="D173" s="25"/>
+      <c r="E173" s="25"/>
+      <c r="F173" s="25"/>
+      <c r="G173" s="25"/>
+      <c r="H173" s="25"/>
+      <c r="I173" s="26"/>
+      <c r="J173" s="26"/>
+      <c r="K173" s="25"/>
+      <c r="L173" s="25"/>
+      <c r="M173" s="25"/>
+      <c r="N173" s="26"/>
+      <c r="O173" s="26"/>
+      <c r="P173" s="27"/>
+      <c r="Q173" s="25"/>
+      <c r="R173" s="25"/>
+      <c r="S173" s="26"/>
+      <c r="T173" s="26"/>
+      <c r="U173" s="25"/>
+      <c r="V173" s="25"/>
+      <c r="W173" s="25"/>
+      <c r="X173" s="25"/>
+      <c r="Y173" s="25"/>
+      <c r="Z173" s="25"/>
+      <c r="AA173" s="25"/>
+      <c r="AB173" s="25"/>
+      <c r="AC173" s="25"/>
+      <c r="AD173" s="25"/>
+      <c r="AE173" s="25"/>
+      <c r="AF173" s="25"/>
+      <c r="AG173" s="25"/>
+      <c r="AH173" s="25"/>
+      <c r="AI173" s="25"/>
+      <c r="AJ173" s="26"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="24"/>
-      <c r="C174" s="24"/>
-      <c r="D174" s="24"/>
-      <c r="E174" s="24"/>
-      <c r="F174" s="24"/>
-      <c r="G174" s="24"/>
-      <c r="H174" s="24"/>
-      <c r="I174" s="25"/>
-      <c r="J174" s="25"/>
-      <c r="K174" s="24"/>
-      <c r="L174" s="24"/>
-      <c r="M174" s="24"/>
-      <c r="N174" s="25"/>
-      <c r="O174" s="25"/>
-      <c r="P174" s="26"/>
-      <c r="Q174" s="24"/>
-      <c r="R174" s="24"/>
-      <c r="S174" s="25"/>
-      <c r="T174" s="25"/>
-      <c r="U174" s="24"/>
-      <c r="V174" s="24"/>
-      <c r="W174" s="24"/>
-      <c r="X174" s="24"/>
-      <c r="Y174" s="24"/>
-      <c r="Z174" s="24"/>
-      <c r="AA174" s="24"/>
-      <c r="AB174" s="24"/>
-      <c r="AC174" s="24"/>
-      <c r="AD174" s="24"/>
-      <c r="AE174" s="24"/>
-      <c r="AF174" s="24"/>
-      <c r="AG174" s="24"/>
-      <c r="AH174" s="24"/>
-      <c r="AI174" s="24"/>
-      <c r="AJ174" s="25"/>
+      <c r="B174" s="25"/>
+      <c r="C174" s="25"/>
+      <c r="D174" s="25"/>
+      <c r="E174" s="25"/>
+      <c r="F174" s="25"/>
+      <c r="G174" s="25"/>
+      <c r="H174" s="25"/>
+      <c r="I174" s="26"/>
+      <c r="J174" s="26"/>
+      <c r="K174" s="25"/>
+      <c r="L174" s="25"/>
+      <c r="M174" s="25"/>
+      <c r="N174" s="26"/>
+      <c r="O174" s="26"/>
+      <c r="P174" s="27"/>
+      <c r="Q174" s="25"/>
+      <c r="R174" s="25"/>
+      <c r="S174" s="26"/>
+      <c r="T174" s="26"/>
+      <c r="U174" s="25"/>
+      <c r="V174" s="25"/>
+      <c r="W174" s="25"/>
+      <c r="X174" s="25"/>
+      <c r="Y174" s="25"/>
+      <c r="Z174" s="25"/>
+      <c r="AA174" s="25"/>
+      <c r="AB174" s="25"/>
+      <c r="AC174" s="25"/>
+      <c r="AD174" s="25"/>
+      <c r="AE174" s="25"/>
+      <c r="AF174" s="25"/>
+      <c r="AG174" s="25"/>
+      <c r="AH174" s="25"/>
+      <c r="AI174" s="25"/>
+      <c r="AJ174" s="26"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="24"/>
-      <c r="C175" s="24"/>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24"/>
-      <c r="I175" s="25"/>
-      <c r="J175" s="25"/>
-      <c r="K175" s="24"/>
-      <c r="L175" s="24"/>
-      <c r="M175" s="24"/>
-      <c r="N175" s="25"/>
-      <c r="O175" s="25"/>
-      <c r="P175" s="26"/>
-      <c r="Q175" s="24"/>
-      <c r="R175" s="24"/>
-      <c r="S175" s="25"/>
-      <c r="T175" s="25"/>
-      <c r="U175" s="24"/>
-      <c r="V175" s="24"/>
-      <c r="W175" s="24"/>
-      <c r="X175" s="24"/>
-      <c r="Y175" s="24"/>
-      <c r="Z175" s="24"/>
-      <c r="AA175" s="24"/>
-      <c r="AB175" s="24"/>
-      <c r="AC175" s="24"/>
-      <c r="AD175" s="24"/>
-      <c r="AE175" s="24"/>
-      <c r="AF175" s="24"/>
-      <c r="AG175" s="24"/>
-      <c r="AH175" s="24"/>
-      <c r="AI175" s="24"/>
-      <c r="AJ175" s="25"/>
+      <c r="B175" s="25"/>
+      <c r="C175" s="25"/>
+      <c r="D175" s="25"/>
+      <c r="E175" s="25"/>
+      <c r="F175" s="25"/>
+      <c r="G175" s="25"/>
+      <c r="H175" s="25"/>
+      <c r="I175" s="26"/>
+      <c r="J175" s="26"/>
+      <c r="K175" s="25"/>
+      <c r="L175" s="25"/>
+      <c r="M175" s="25"/>
+      <c r="N175" s="26"/>
+      <c r="O175" s="26"/>
+      <c r="P175" s="27"/>
+      <c r="Q175" s="25"/>
+      <c r="R175" s="25"/>
+      <c r="S175" s="26"/>
+      <c r="T175" s="26"/>
+      <c r="U175" s="25"/>
+      <c r="V175" s="25"/>
+      <c r="W175" s="25"/>
+      <c r="X175" s="25"/>
+      <c r="Y175" s="25"/>
+      <c r="Z175" s="25"/>
+      <c r="AA175" s="25"/>
+      <c r="AB175" s="25"/>
+      <c r="AC175" s="25"/>
+      <c r="AD175" s="25"/>
+      <c r="AE175" s="25"/>
+      <c r="AF175" s="25"/>
+      <c r="AG175" s="25"/>
+      <c r="AH175" s="25"/>
+      <c r="AI175" s="25"/>
+      <c r="AJ175" s="26"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="24"/>
-      <c r="C176" s="24"/>
-      <c r="D176" s="24"/>
-      <c r="E176" s="24"/>
-      <c r="F176" s="24"/>
-      <c r="G176" s="24"/>
-      <c r="H176" s="24"/>
-      <c r="I176" s="25"/>
-      <c r="J176" s="25"/>
-      <c r="K176" s="24"/>
-      <c r="L176" s="24"/>
-      <c r="M176" s="24"/>
-      <c r="N176" s="25"/>
-      <c r="O176" s="25"/>
-      <c r="P176" s="26"/>
-      <c r="Q176" s="24"/>
-      <c r="R176" s="24"/>
-      <c r="S176" s="25"/>
-      <c r="T176" s="25"/>
-      <c r="U176" s="24"/>
-      <c r="V176" s="24"/>
-      <c r="W176" s="24"/>
-      <c r="X176" s="24"/>
-      <c r="Y176" s="24"/>
-      <c r="Z176" s="24"/>
-      <c r="AA176" s="24"/>
-      <c r="AB176" s="24"/>
-      <c r="AC176" s="24"/>
-      <c r="AD176" s="24"/>
-      <c r="AE176" s="24"/>
-      <c r="AF176" s="24"/>
-      <c r="AG176" s="24"/>
-      <c r="AH176" s="24"/>
-      <c r="AI176" s="24"/>
-      <c r="AJ176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+      <c r="D176" s="25"/>
+      <c r="E176" s="25"/>
+      <c r="F176" s="25"/>
+      <c r="G176" s="25"/>
+      <c r="H176" s="25"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
+      <c r="K176" s="25"/>
+      <c r="L176" s="25"/>
+      <c r="M176" s="25"/>
+      <c r="N176" s="26"/>
+      <c r="O176" s="26"/>
+      <c r="P176" s="27"/>
+      <c r="Q176" s="25"/>
+      <c r="R176" s="25"/>
+      <c r="S176" s="26"/>
+      <c r="T176" s="26"/>
+      <c r="U176" s="25"/>
+      <c r="V176" s="25"/>
+      <c r="W176" s="25"/>
+      <c r="X176" s="25"/>
+      <c r="Y176" s="25"/>
+      <c r="Z176" s="25"/>
+      <c r="AA176" s="25"/>
+      <c r="AB176" s="25"/>
+      <c r="AC176" s="25"/>
+      <c r="AD176" s="25"/>
+      <c r="AE176" s="25"/>
+      <c r="AF176" s="25"/>
+      <c r="AG176" s="25"/>
+      <c r="AH176" s="25"/>
+      <c r="AI176" s="25"/>
+      <c r="AJ176" s="26"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="24"/>
-      <c r="C177" s="24"/>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="25"/>
-      <c r="K177" s="24"/>
-      <c r="L177" s="24"/>
-      <c r="M177" s="24"/>
-      <c r="N177" s="25"/>
-      <c r="O177" s="25"/>
-      <c r="P177" s="26"/>
-      <c r="Q177" s="24"/>
-      <c r="R177" s="24"/>
-      <c r="S177" s="25"/>
-      <c r="T177" s="25"/>
-      <c r="U177" s="24"/>
-      <c r="V177" s="24"/>
-      <c r="W177" s="24"/>
-      <c r="X177" s="24"/>
-      <c r="Y177" s="24"/>
-      <c r="Z177" s="24"/>
-      <c r="AA177" s="24"/>
-      <c r="AB177" s="24"/>
-      <c r="AC177" s="24"/>
-      <c r="AD177" s="24"/>
-      <c r="AE177" s="24"/>
-      <c r="AF177" s="24"/>
-      <c r="AG177" s="24"/>
-      <c r="AH177" s="24"/>
-      <c r="AI177" s="24"/>
-      <c r="AJ177" s="25"/>
+      <c r="B177" s="25"/>
+      <c r="C177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="26"/>
+      <c r="J177" s="26"/>
+      <c r="K177" s="25"/>
+      <c r="L177" s="25"/>
+      <c r="M177" s="25"/>
+      <c r="N177" s="26"/>
+      <c r="O177" s="26"/>
+      <c r="P177" s="27"/>
+      <c r="Q177" s="25"/>
+      <c r="R177" s="25"/>
+      <c r="S177" s="26"/>
+      <c r="T177" s="26"/>
+      <c r="U177" s="25"/>
+      <c r="V177" s="25"/>
+      <c r="W177" s="25"/>
+      <c r="X177" s="25"/>
+      <c r="Y177" s="25"/>
+      <c r="Z177" s="25"/>
+      <c r="AA177" s="25"/>
+      <c r="AB177" s="25"/>
+      <c r="AC177" s="25"/>
+      <c r="AD177" s="25"/>
+      <c r="AE177" s="25"/>
+      <c r="AF177" s="25"/>
+      <c r="AG177" s="25"/>
+      <c r="AH177" s="25"/>
+      <c r="AI177" s="25"/>
+      <c r="AJ177" s="26"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="24"/>
-      <c r="C178" s="24"/>
-      <c r="D178" s="24"/>
-      <c r="E178" s="24"/>
-      <c r="F178" s="24"/>
-      <c r="G178" s="24"/>
-      <c r="H178" s="24"/>
-      <c r="I178" s="25"/>
-      <c r="J178" s="25"/>
-      <c r="K178" s="24"/>
-      <c r="L178" s="24"/>
-      <c r="M178" s="24"/>
-      <c r="N178" s="25"/>
-      <c r="O178" s="25"/>
-      <c r="P178" s="26"/>
-      <c r="Q178" s="24"/>
-      <c r="R178" s="24"/>
-      <c r="S178" s="25"/>
-      <c r="T178" s="25"/>
-      <c r="U178" s="24"/>
-      <c r="V178" s="24"/>
-      <c r="W178" s="24"/>
-      <c r="X178" s="24"/>
-      <c r="Y178" s="24"/>
-      <c r="Z178" s="24"/>
-      <c r="AA178" s="24"/>
-      <c r="AB178" s="24"/>
-      <c r="AC178" s="24"/>
-      <c r="AD178" s="24"/>
-      <c r="AE178" s="24"/>
-      <c r="AF178" s="24"/>
-      <c r="AG178" s="24"/>
-      <c r="AH178" s="24"/>
-      <c r="AI178" s="24"/>
-      <c r="AJ178" s="25"/>
+      <c r="B178" s="25"/>
+      <c r="C178" s="25"/>
+      <c r="D178" s="25"/>
+      <c r="E178" s="25"/>
+      <c r="F178" s="25"/>
+      <c r="G178" s="25"/>
+      <c r="H178" s="25"/>
+      <c r="I178" s="26"/>
+      <c r="J178" s="26"/>
+      <c r="K178" s="25"/>
+      <c r="L178" s="25"/>
+      <c r="M178" s="25"/>
+      <c r="N178" s="26"/>
+      <c r="O178" s="26"/>
+      <c r="P178" s="27"/>
+      <c r="Q178" s="25"/>
+      <c r="R178" s="25"/>
+      <c r="S178" s="26"/>
+      <c r="T178" s="26"/>
+      <c r="U178" s="25"/>
+      <c r="V178" s="25"/>
+      <c r="W178" s="25"/>
+      <c r="X178" s="25"/>
+      <c r="Y178" s="25"/>
+      <c r="Z178" s="25"/>
+      <c r="AA178" s="25"/>
+      <c r="AB178" s="25"/>
+      <c r="AC178" s="25"/>
+      <c r="AD178" s="25"/>
+      <c r="AE178" s="25"/>
+      <c r="AF178" s="25"/>
+      <c r="AG178" s="25"/>
+      <c r="AH178" s="25"/>
+      <c r="AI178" s="25"/>
+      <c r="AJ178" s="26"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="24"/>
-      <c r="C179" s="24"/>
-      <c r="D179" s="24"/>
-      <c r="E179" s="24"/>
-      <c r="F179" s="24"/>
-      <c r="G179" s="24"/>
-      <c r="H179" s="24"/>
-      <c r="I179" s="25"/>
-      <c r="J179" s="25"/>
-      <c r="K179" s="24"/>
-      <c r="L179" s="24"/>
-      <c r="M179" s="24"/>
-      <c r="N179" s="25"/>
-      <c r="O179" s="25"/>
-      <c r="P179" s="26"/>
-      <c r="Q179" s="24"/>
-      <c r="R179" s="24"/>
-      <c r="S179" s="25"/>
-      <c r="T179" s="25"/>
-      <c r="U179" s="24"/>
-      <c r="V179" s="24"/>
-      <c r="W179" s="24"/>
-      <c r="X179" s="24"/>
-      <c r="Y179" s="24"/>
-      <c r="Z179" s="24"/>
-      <c r="AA179" s="24"/>
-      <c r="AB179" s="24"/>
-      <c r="AC179" s="24"/>
-      <c r="AD179" s="24"/>
-      <c r="AE179" s="24"/>
-      <c r="AF179" s="24"/>
-      <c r="AG179" s="24"/>
-      <c r="AH179" s="24"/>
-      <c r="AI179" s="24"/>
-      <c r="AJ179" s="25"/>
+      <c r="B179" s="25"/>
+      <c r="C179" s="25"/>
+      <c r="D179" s="25"/>
+      <c r="E179" s="25"/>
+      <c r="F179" s="25"/>
+      <c r="G179" s="25"/>
+      <c r="H179" s="25"/>
+      <c r="I179" s="26"/>
+      <c r="J179" s="26"/>
+      <c r="K179" s="25"/>
+      <c r="L179" s="25"/>
+      <c r="M179" s="25"/>
+      <c r="N179" s="26"/>
+      <c r="O179" s="26"/>
+      <c r="P179" s="27"/>
+      <c r="Q179" s="25"/>
+      <c r="R179" s="25"/>
+      <c r="S179" s="26"/>
+      <c r="T179" s="26"/>
+      <c r="U179" s="25"/>
+      <c r="V179" s="25"/>
+      <c r="W179" s="25"/>
+      <c r="X179" s="25"/>
+      <c r="Y179" s="25"/>
+      <c r="Z179" s="25"/>
+      <c r="AA179" s="25"/>
+      <c r="AB179" s="25"/>
+      <c r="AC179" s="25"/>
+      <c r="AD179" s="25"/>
+      <c r="AE179" s="25"/>
+      <c r="AF179" s="25"/>
+      <c r="AG179" s="25"/>
+      <c r="AH179" s="25"/>
+      <c r="AI179" s="25"/>
+      <c r="AJ179" s="26"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="24"/>
-      <c r="C180" s="24"/>
-      <c r="D180" s="24"/>
-      <c r="E180" s="24"/>
-      <c r="F180" s="24"/>
-      <c r="G180" s="24"/>
-      <c r="H180" s="24"/>
-      <c r="I180" s="25"/>
-      <c r="J180" s="25"/>
-      <c r="K180" s="24"/>
-      <c r="L180" s="24"/>
-      <c r="M180" s="24"/>
-      <c r="N180" s="25"/>
-      <c r="O180" s="25"/>
-      <c r="P180" s="26"/>
-      <c r="Q180" s="24"/>
-      <c r="R180" s="24"/>
-      <c r="S180" s="25"/>
-      <c r="T180" s="25"/>
-      <c r="U180" s="24"/>
-      <c r="V180" s="24"/>
-      <c r="W180" s="24"/>
-      <c r="X180" s="24"/>
-      <c r="Y180" s="24"/>
-      <c r="Z180" s="24"/>
-      <c r="AA180" s="24"/>
-      <c r="AB180" s="24"/>
-      <c r="AC180" s="24"/>
-      <c r="AD180" s="24"/>
-      <c r="AE180" s="24"/>
-      <c r="AF180" s="24"/>
-      <c r="AG180" s="24"/>
-      <c r="AH180" s="24"/>
-      <c r="AI180" s="24"/>
-      <c r="AJ180" s="25"/>
+      <c r="B180" s="25"/>
+      <c r="C180" s="25"/>
+      <c r="D180" s="25"/>
+      <c r="E180" s="25"/>
+      <c r="F180" s="25"/>
+      <c r="G180" s="25"/>
+      <c r="H180" s="25"/>
+      <c r="I180" s="26"/>
+      <c r="J180" s="26"/>
+      <c r="K180" s="25"/>
+      <c r="L180" s="25"/>
+      <c r="M180" s="25"/>
+      <c r="N180" s="26"/>
+      <c r="O180" s="26"/>
+      <c r="P180" s="27"/>
+      <c r="Q180" s="25"/>
+      <c r="R180" s="25"/>
+      <c r="S180" s="26"/>
+      <c r="T180" s="26"/>
+      <c r="U180" s="25"/>
+      <c r="V180" s="25"/>
+      <c r="W180" s="25"/>
+      <c r="X180" s="25"/>
+      <c r="Y180" s="25"/>
+      <c r="Z180" s="25"/>
+      <c r="AA180" s="25"/>
+      <c r="AB180" s="25"/>
+      <c r="AC180" s="25"/>
+      <c r="AD180" s="25"/>
+      <c r="AE180" s="25"/>
+      <c r="AF180" s="25"/>
+      <c r="AG180" s="25"/>
+      <c r="AH180" s="25"/>
+      <c r="AI180" s="25"/>
+      <c r="AJ180" s="26"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="24"/>
-      <c r="C181" s="24"/>
-      <c r="D181" s="24"/>
-      <c r="E181" s="24"/>
-      <c r="F181" s="24"/>
-      <c r="G181" s="24"/>
-      <c r="H181" s="24"/>
-      <c r="I181" s="25"/>
-      <c r="J181" s="25"/>
-      <c r="K181" s="24"/>
-      <c r="L181" s="24"/>
-      <c r="M181" s="24"/>
-      <c r="N181" s="25"/>
-      <c r="O181" s="25"/>
-      <c r="P181" s="26"/>
-      <c r="Q181" s="24"/>
-      <c r="R181" s="24"/>
-      <c r="S181" s="25"/>
-      <c r="T181" s="25"/>
-      <c r="U181" s="24"/>
-      <c r="V181" s="24"/>
-      <c r="W181" s="24"/>
-      <c r="X181" s="24"/>
-      <c r="Y181" s="24"/>
-      <c r="Z181" s="24"/>
-      <c r="AA181" s="24"/>
-      <c r="AB181" s="24"/>
-      <c r="AC181" s="24"/>
-      <c r="AD181" s="24"/>
-      <c r="AE181" s="24"/>
-      <c r="AF181" s="24"/>
-      <c r="AG181" s="24"/>
-      <c r="AH181" s="24"/>
-      <c r="AI181" s="24"/>
-      <c r="AJ181" s="25"/>
+      <c r="B181" s="25"/>
+      <c r="C181" s="25"/>
+      <c r="D181" s="25"/>
+      <c r="E181" s="25"/>
+      <c r="F181" s="25"/>
+      <c r="G181" s="25"/>
+      <c r="H181" s="25"/>
+      <c r="I181" s="26"/>
+      <c r="J181" s="26"/>
+      <c r="K181" s="25"/>
+      <c r="L181" s="25"/>
+      <c r="M181" s="25"/>
+      <c r="N181" s="26"/>
+      <c r="O181" s="26"/>
+      <c r="P181" s="27"/>
+      <c r="Q181" s="25"/>
+      <c r="R181" s="25"/>
+      <c r="S181" s="26"/>
+      <c r="T181" s="26"/>
+      <c r="U181" s="25"/>
+      <c r="V181" s="25"/>
+      <c r="W181" s="25"/>
+      <c r="X181" s="25"/>
+      <c r="Y181" s="25"/>
+      <c r="Z181" s="25"/>
+      <c r="AA181" s="25"/>
+      <c r="AB181" s="25"/>
+      <c r="AC181" s="25"/>
+      <c r="AD181" s="25"/>
+      <c r="AE181" s="25"/>
+      <c r="AF181" s="25"/>
+      <c r="AG181" s="25"/>
+      <c r="AH181" s="25"/>
+      <c r="AI181" s="25"/>
+      <c r="AJ181" s="26"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="24"/>
-      <c r="C182" s="24"/>
-      <c r="D182" s="24"/>
-      <c r="E182" s="24"/>
-      <c r="F182" s="24"/>
-      <c r="G182" s="24"/>
-      <c r="H182" s="24"/>
-      <c r="I182" s="25"/>
-      <c r="J182" s="25"/>
-      <c r="K182" s="24"/>
-      <c r="L182" s="24"/>
-      <c r="M182" s="24"/>
-      <c r="N182" s="25"/>
-      <c r="O182" s="25"/>
-      <c r="P182" s="26"/>
-      <c r="Q182" s="24"/>
-      <c r="R182" s="24"/>
-      <c r="S182" s="25"/>
-      <c r="T182" s="25"/>
-      <c r="U182" s="24"/>
-      <c r="V182" s="24"/>
-      <c r="W182" s="24"/>
-      <c r="X182" s="24"/>
-      <c r="Y182" s="24"/>
-      <c r="Z182" s="24"/>
-      <c r="AA182" s="24"/>
-      <c r="AB182" s="24"/>
-      <c r="AC182" s="24"/>
-      <c r="AD182" s="24"/>
-      <c r="AE182" s="24"/>
-      <c r="AF182" s="24"/>
-      <c r="AG182" s="24"/>
-      <c r="AH182" s="24"/>
-      <c r="AI182" s="24"/>
-      <c r="AJ182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+      <c r="D182" s="25"/>
+      <c r="E182" s="25"/>
+      <c r="F182" s="25"/>
+      <c r="G182" s="25"/>
+      <c r="H182" s="25"/>
+      <c r="I182" s="26"/>
+      <c r="J182" s="26"/>
+      <c r="K182" s="25"/>
+      <c r="L182" s="25"/>
+      <c r="M182" s="25"/>
+      <c r="N182" s="26"/>
+      <c r="O182" s="26"/>
+      <c r="P182" s="27"/>
+      <c r="Q182" s="25"/>
+      <c r="R182" s="25"/>
+      <c r="S182" s="26"/>
+      <c r="T182" s="26"/>
+      <c r="U182" s="25"/>
+      <c r="V182" s="25"/>
+      <c r="W182" s="25"/>
+      <c r="X182" s="25"/>
+      <c r="Y182" s="25"/>
+      <c r="Z182" s="25"/>
+      <c r="AA182" s="25"/>
+      <c r="AB182" s="25"/>
+      <c r="AC182" s="25"/>
+      <c r="AD182" s="25"/>
+      <c r="AE182" s="25"/>
+      <c r="AF182" s="25"/>
+      <c r="AG182" s="25"/>
+      <c r="AH182" s="25"/>
+      <c r="AI182" s="25"/>
+      <c r="AJ182" s="26"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="24"/>
-      <c r="C183" s="24"/>
-      <c r="D183" s="24"/>
-      <c r="E183" s="24"/>
-      <c r="F183" s="24"/>
-      <c r="G183" s="24"/>
-      <c r="H183" s="24"/>
-      <c r="I183" s="25"/>
-      <c r="J183" s="25"/>
-      <c r="K183" s="24"/>
-      <c r="L183" s="24"/>
-      <c r="M183" s="24"/>
-      <c r="N183" s="25"/>
-      <c r="O183" s="25"/>
-      <c r="P183" s="26"/>
-      <c r="Q183" s="24"/>
-      <c r="R183" s="24"/>
-      <c r="S183" s="25"/>
-      <c r="T183" s="25"/>
-      <c r="U183" s="24"/>
-      <c r="V183" s="24"/>
-      <c r="W183" s="24"/>
-      <c r="X183" s="24"/>
-      <c r="Y183" s="24"/>
-      <c r="Z183" s="24"/>
-      <c r="AA183" s="24"/>
-      <c r="AB183" s="24"/>
-      <c r="AC183" s="24"/>
-      <c r="AD183" s="24"/>
-      <c r="AE183" s="24"/>
-      <c r="AF183" s="24"/>
-      <c r="AG183" s="24"/>
-      <c r="AH183" s="24"/>
-      <c r="AI183" s="24"/>
-      <c r="AJ183" s="25"/>
+      <c r="B183" s="25"/>
+      <c r="C183" s="25"/>
+      <c r="D183" s="25"/>
+      <c r="E183" s="25"/>
+      <c r="F183" s="25"/>
+      <c r="G183" s="25"/>
+      <c r="H183" s="25"/>
+      <c r="I183" s="26"/>
+      <c r="J183" s="26"/>
+      <c r="K183" s="25"/>
+      <c r="L183" s="25"/>
+      <c r="M183" s="25"/>
+      <c r="N183" s="26"/>
+      <c r="O183" s="26"/>
+      <c r="P183" s="27"/>
+      <c r="Q183" s="25"/>
+      <c r="R183" s="25"/>
+      <c r="S183" s="26"/>
+      <c r="T183" s="26"/>
+      <c r="U183" s="25"/>
+      <c r="V183" s="25"/>
+      <c r="W183" s="25"/>
+      <c r="X183" s="25"/>
+      <c r="Y183" s="25"/>
+      <c r="Z183" s="25"/>
+      <c r="AA183" s="25"/>
+      <c r="AB183" s="25"/>
+      <c r="AC183" s="25"/>
+      <c r="AD183" s="25"/>
+      <c r="AE183" s="25"/>
+      <c r="AF183" s="25"/>
+      <c r="AG183" s="25"/>
+      <c r="AH183" s="25"/>
+      <c r="AI183" s="25"/>
+      <c r="AJ183" s="26"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
-      <c r="I184" s="25"/>
-      <c r="J184" s="25"/>
-      <c r="K184" s="24"/>
-      <c r="L184" s="24"/>
-      <c r="M184" s="24"/>
-      <c r="N184" s="25"/>
-      <c r="O184" s="25"/>
-      <c r="P184" s="26"/>
-      <c r="Q184" s="24"/>
-      <c r="R184" s="24"/>
-      <c r="S184" s="25"/>
-      <c r="T184" s="25"/>
-      <c r="U184" s="24"/>
-      <c r="V184" s="24"/>
-      <c r="W184" s="24"/>
-      <c r="X184" s="24"/>
-      <c r="Y184" s="24"/>
-      <c r="Z184" s="24"/>
-      <c r="AA184" s="24"/>
-      <c r="AB184" s="24"/>
-      <c r="AC184" s="24"/>
-      <c r="AD184" s="24"/>
-      <c r="AE184" s="24"/>
-      <c r="AF184" s="24"/>
-      <c r="AG184" s="24"/>
-      <c r="AH184" s="24"/>
-      <c r="AI184" s="24"/>
-      <c r="AJ184" s="25"/>
+      <c r="B184" s="25"/>
+      <c r="C184" s="25"/>
+      <c r="D184" s="25"/>
+      <c r="E184" s="25"/>
+      <c r="F184" s="25"/>
+      <c r="G184" s="25"/>
+      <c r="H184" s="25"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
+      <c r="K184" s="25"/>
+      <c r="L184" s="25"/>
+      <c r="M184" s="25"/>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="27"/>
+      <c r="Q184" s="25"/>
+      <c r="R184" s="25"/>
+      <c r="S184" s="26"/>
+      <c r="T184" s="26"/>
+      <c r="U184" s="25"/>
+      <c r="V184" s="25"/>
+      <c r="W184" s="25"/>
+      <c r="X184" s="25"/>
+      <c r="Y184" s="25"/>
+      <c r="Z184" s="25"/>
+      <c r="AA184" s="25"/>
+      <c r="AB184" s="25"/>
+      <c r="AC184" s="25"/>
+      <c r="AD184" s="25"/>
+      <c r="AE184" s="25"/>
+      <c r="AF184" s="25"/>
+      <c r="AG184" s="25"/>
+      <c r="AH184" s="25"/>
+      <c r="AI184" s="25"/>
+      <c r="AJ184" s="26"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="24"/>
-      <c r="C185" s="24"/>
-      <c r="D185" s="24"/>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="25"/>
-      <c r="J185" s="25"/>
-      <c r="K185" s="24"/>
-      <c r="L185" s="24"/>
-      <c r="M185" s="24"/>
-      <c r="N185" s="25"/>
-      <c r="O185" s="25"/>
-      <c r="P185" s="26"/>
-      <c r="Q185" s="24"/>
-      <c r="R185" s="24"/>
-      <c r="S185" s="25"/>
-      <c r="T185" s="25"/>
-      <c r="U185" s="24"/>
-      <c r="V185" s="24"/>
-      <c r="W185" s="24"/>
-      <c r="X185" s="24"/>
-      <c r="Y185" s="24"/>
-      <c r="Z185" s="24"/>
-      <c r="AA185" s="24"/>
-      <c r="AB185" s="24"/>
-      <c r="AC185" s="24"/>
-      <c r="AD185" s="24"/>
-      <c r="AE185" s="24"/>
-      <c r="AF185" s="24"/>
-      <c r="AG185" s="24"/>
-      <c r="AH185" s="24"/>
-      <c r="AI185" s="24"/>
-      <c r="AJ185" s="25"/>
+      <c r="B185" s="25"/>
+      <c r="C185" s="25"/>
+      <c r="D185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="26"/>
+      <c r="J185" s="26"/>
+      <c r="K185" s="25"/>
+      <c r="L185" s="25"/>
+      <c r="M185" s="25"/>
+      <c r="N185" s="26"/>
+      <c r="O185" s="26"/>
+      <c r="P185" s="27"/>
+      <c r="Q185" s="25"/>
+      <c r="R185" s="25"/>
+      <c r="S185" s="26"/>
+      <c r="T185" s="26"/>
+      <c r="U185" s="25"/>
+      <c r="V185" s="25"/>
+      <c r="W185" s="25"/>
+      <c r="X185" s="25"/>
+      <c r="Y185" s="25"/>
+      <c r="Z185" s="25"/>
+      <c r="AA185" s="25"/>
+      <c r="AB185" s="25"/>
+      <c r="AC185" s="25"/>
+      <c r="AD185" s="25"/>
+      <c r="AE185" s="25"/>
+      <c r="AF185" s="25"/>
+      <c r="AG185" s="25"/>
+      <c r="AH185" s="25"/>
+      <c r="AI185" s="25"/>
+      <c r="AJ185" s="26"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="24"/>
-      <c r="C186" s="24"/>
-      <c r="D186" s="24"/>
-      <c r="E186" s="24"/>
-      <c r="F186" s="24"/>
-      <c r="G186" s="24"/>
-      <c r="H186" s="24"/>
-      <c r="I186" s="25"/>
-      <c r="J186" s="25"/>
-      <c r="K186" s="24"/>
-      <c r="L186" s="24"/>
-      <c r="M186" s="24"/>
-      <c r="N186" s="25"/>
-      <c r="O186" s="25"/>
-      <c r="P186" s="26"/>
-      <c r="Q186" s="24"/>
-      <c r="R186" s="24"/>
-      <c r="S186" s="25"/>
-      <c r="T186" s="25"/>
-      <c r="U186" s="24"/>
-      <c r="V186" s="24"/>
-      <c r="W186" s="24"/>
-      <c r="X186" s="24"/>
-      <c r="Y186" s="24"/>
-      <c r="Z186" s="24"/>
-      <c r="AA186" s="24"/>
-      <c r="AB186" s="24"/>
-      <c r="AC186" s="24"/>
-      <c r="AD186" s="24"/>
-      <c r="AE186" s="24"/>
-      <c r="AF186" s="24"/>
-      <c r="AG186" s="24"/>
-      <c r="AH186" s="24"/>
-      <c r="AI186" s="24"/>
-      <c r="AJ186" s="25"/>
+      <c r="B186" s="25"/>
+      <c r="C186" s="25"/>
+      <c r="D186" s="25"/>
+      <c r="E186" s="25"/>
+      <c r="F186" s="25"/>
+      <c r="G186" s="25"/>
+      <c r="H186" s="25"/>
+      <c r="I186" s="26"/>
+      <c r="J186" s="26"/>
+      <c r="K186" s="25"/>
+      <c r="L186" s="25"/>
+      <c r="M186" s="25"/>
+      <c r="N186" s="26"/>
+      <c r="O186" s="26"/>
+      <c r="P186" s="27"/>
+      <c r="Q186" s="25"/>
+      <c r="R186" s="25"/>
+      <c r="S186" s="26"/>
+      <c r="T186" s="26"/>
+      <c r="U186" s="25"/>
+      <c r="V186" s="25"/>
+      <c r="W186" s="25"/>
+      <c r="X186" s="25"/>
+      <c r="Y186" s="25"/>
+      <c r="Z186" s="25"/>
+      <c r="AA186" s="25"/>
+      <c r="AB186" s="25"/>
+      <c r="AC186" s="25"/>
+      <c r="AD186" s="25"/>
+      <c r="AE186" s="25"/>
+      <c r="AF186" s="25"/>
+      <c r="AG186" s="25"/>
+      <c r="AH186" s="25"/>
+      <c r="AI186" s="25"/>
+      <c r="AJ186" s="26"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="24"/>
-      <c r="C187" s="24"/>
-      <c r="D187" s="24"/>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="24"/>
-      <c r="H187" s="24"/>
-      <c r="I187" s="25"/>
-      <c r="J187" s="25"/>
-      <c r="K187" s="24"/>
-      <c r="L187" s="24"/>
-      <c r="M187" s="24"/>
-      <c r="N187" s="25"/>
-      <c r="O187" s="25"/>
-      <c r="P187" s="26"/>
-      <c r="Q187" s="24"/>
-      <c r="R187" s="24"/>
-      <c r="S187" s="25"/>
-      <c r="T187" s="25"/>
-      <c r="U187" s="24"/>
-      <c r="V187" s="24"/>
-      <c r="W187" s="24"/>
-      <c r="X187" s="24"/>
-      <c r="Y187" s="24"/>
-      <c r="Z187" s="24"/>
-      <c r="AA187" s="24"/>
-      <c r="AB187" s="24"/>
-      <c r="AC187" s="24"/>
-      <c r="AD187" s="24"/>
-      <c r="AE187" s="24"/>
-      <c r="AF187" s="24"/>
-      <c r="AG187" s="24"/>
-      <c r="AH187" s="24"/>
-      <c r="AI187" s="24"/>
-      <c r="AJ187" s="25"/>
+      <c r="B187" s="25"/>
+      <c r="C187" s="25"/>
+      <c r="D187" s="25"/>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="26"/>
+      <c r="J187" s="26"/>
+      <c r="K187" s="25"/>
+      <c r="L187" s="25"/>
+      <c r="M187" s="25"/>
+      <c r="N187" s="26"/>
+      <c r="O187" s="26"/>
+      <c r="P187" s="27"/>
+      <c r="Q187" s="25"/>
+      <c r="R187" s="25"/>
+      <c r="S187" s="26"/>
+      <c r="T187" s="26"/>
+      <c r="U187" s="25"/>
+      <c r="V187" s="25"/>
+      <c r="W187" s="25"/>
+      <c r="X187" s="25"/>
+      <c r="Y187" s="25"/>
+      <c r="Z187" s="25"/>
+      <c r="AA187" s="25"/>
+      <c r="AB187" s="25"/>
+      <c r="AC187" s="25"/>
+      <c r="AD187" s="25"/>
+      <c r="AE187" s="25"/>
+      <c r="AF187" s="25"/>
+      <c r="AG187" s="25"/>
+      <c r="AH187" s="25"/>
+      <c r="AI187" s="25"/>
+      <c r="AJ187" s="26"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="24"/>
-      <c r="C188" s="24"/>
-      <c r="D188" s="24"/>
-      <c r="E188" s="24"/>
-      <c r="F188" s="24"/>
-      <c r="G188" s="24"/>
-      <c r="H188" s="24"/>
-      <c r="I188" s="25"/>
-      <c r="J188" s="25"/>
-      <c r="K188" s="24"/>
-      <c r="L188" s="24"/>
-      <c r="M188" s="24"/>
-      <c r="N188" s="25"/>
-      <c r="O188" s="25"/>
-      <c r="P188" s="26"/>
-      <c r="Q188" s="24"/>
-      <c r="R188" s="24"/>
-      <c r="S188" s="25"/>
-      <c r="T188" s="25"/>
-      <c r="U188" s="24"/>
-      <c r="V188" s="24"/>
-      <c r="W188" s="24"/>
-      <c r="X188" s="24"/>
-      <c r="Y188" s="24"/>
-      <c r="Z188" s="24"/>
-      <c r="AA188" s="24"/>
-      <c r="AB188" s="24"/>
-      <c r="AC188" s="24"/>
-      <c r="AD188" s="24"/>
-      <c r="AE188" s="24"/>
-      <c r="AF188" s="24"/>
-      <c r="AG188" s="24"/>
-      <c r="AH188" s="24"/>
-      <c r="AI188" s="24"/>
-      <c r="AJ188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+      <c r="D188" s="25"/>
+      <c r="E188" s="25"/>
+      <c r="F188" s="25"/>
+      <c r="G188" s="25"/>
+      <c r="H188" s="25"/>
+      <c r="I188" s="26"/>
+      <c r="J188" s="26"/>
+      <c r="K188" s="25"/>
+      <c r="L188" s="25"/>
+      <c r="M188" s="25"/>
+      <c r="N188" s="26"/>
+      <c r="O188" s="26"/>
+      <c r="P188" s="27"/>
+      <c r="Q188" s="25"/>
+      <c r="R188" s="25"/>
+      <c r="S188" s="26"/>
+      <c r="T188" s="26"/>
+      <c r="U188" s="25"/>
+      <c r="V188" s="25"/>
+      <c r="W188" s="25"/>
+      <c r="X188" s="25"/>
+      <c r="Y188" s="25"/>
+      <c r="Z188" s="25"/>
+      <c r="AA188" s="25"/>
+      <c r="AB188" s="25"/>
+      <c r="AC188" s="25"/>
+      <c r="AD188" s="25"/>
+      <c r="AE188" s="25"/>
+      <c r="AF188" s="25"/>
+      <c r="AG188" s="25"/>
+      <c r="AH188" s="25"/>
+      <c r="AI188" s="25"/>
+      <c r="AJ188" s="26"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="24"/>
-      <c r="C189" s="24"/>
-      <c r="D189" s="24"/>
-      <c r="E189" s="24"/>
-      <c r="F189" s="24"/>
-      <c r="G189" s="24"/>
-      <c r="H189" s="24"/>
-      <c r="I189" s="25"/>
-      <c r="J189" s="25"/>
-      <c r="K189" s="24"/>
-      <c r="L189" s="24"/>
-      <c r="M189" s="24"/>
-      <c r="N189" s="25"/>
-      <c r="O189" s="25"/>
-      <c r="P189" s="26"/>
-      <c r="Q189" s="24"/>
-      <c r="R189" s="24"/>
-      <c r="S189" s="25"/>
-      <c r="T189" s="25"/>
-      <c r="U189" s="24"/>
-      <c r="V189" s="24"/>
-      <c r="W189" s="24"/>
-      <c r="X189" s="24"/>
-      <c r="Y189" s="24"/>
-      <c r="Z189" s="24"/>
-      <c r="AA189" s="24"/>
-      <c r="AB189" s="24"/>
-      <c r="AC189" s="24"/>
-      <c r="AD189" s="24"/>
-      <c r="AE189" s="24"/>
-      <c r="AF189" s="24"/>
-      <c r="AG189" s="24"/>
-      <c r="AH189" s="24"/>
-      <c r="AI189" s="24"/>
-      <c r="AJ189" s="25"/>
+      <c r="B189" s="25"/>
+      <c r="C189" s="25"/>
+      <c r="D189" s="25"/>
+      <c r="E189" s="25"/>
+      <c r="F189" s="25"/>
+      <c r="G189" s="25"/>
+      <c r="H189" s="25"/>
+      <c r="I189" s="26"/>
+      <c r="J189" s="26"/>
+      <c r="K189" s="25"/>
+      <c r="L189" s="25"/>
+      <c r="M189" s="25"/>
+      <c r="N189" s="26"/>
+      <c r="O189" s="26"/>
+      <c r="P189" s="27"/>
+      <c r="Q189" s="25"/>
+      <c r="R189" s="25"/>
+      <c r="S189" s="26"/>
+      <c r="T189" s="26"/>
+      <c r="U189" s="25"/>
+      <c r="V189" s="25"/>
+      <c r="W189" s="25"/>
+      <c r="X189" s="25"/>
+      <c r="Y189" s="25"/>
+      <c r="Z189" s="25"/>
+      <c r="AA189" s="25"/>
+      <c r="AB189" s="25"/>
+      <c r="AC189" s="25"/>
+      <c r="AD189" s="25"/>
+      <c r="AE189" s="25"/>
+      <c r="AF189" s="25"/>
+      <c r="AG189" s="25"/>
+      <c r="AH189" s="25"/>
+      <c r="AI189" s="25"/>
+      <c r="AJ189" s="26"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="24"/>
-      <c r="C190" s="24"/>
-      <c r="D190" s="24"/>
-      <c r="E190" s="24"/>
-      <c r="F190" s="24"/>
-      <c r="G190" s="24"/>
-      <c r="H190" s="24"/>
-      <c r="I190" s="25"/>
-      <c r="J190" s="25"/>
-      <c r="K190" s="24"/>
-      <c r="L190" s="24"/>
-      <c r="M190" s="24"/>
-      <c r="N190" s="25"/>
-      <c r="O190" s="25"/>
-      <c r="P190" s="26"/>
-      <c r="Q190" s="24"/>
-      <c r="R190" s="24"/>
-      <c r="S190" s="25"/>
-      <c r="T190" s="25"/>
-      <c r="U190" s="24"/>
-      <c r="V190" s="24"/>
-      <c r="W190" s="24"/>
-      <c r="X190" s="24"/>
-      <c r="Y190" s="24"/>
-      <c r="Z190" s="24"/>
-      <c r="AA190" s="24"/>
-      <c r="AB190" s="24"/>
-      <c r="AC190" s="24"/>
-      <c r="AD190" s="24"/>
-      <c r="AE190" s="24"/>
-      <c r="AF190" s="24"/>
-      <c r="AG190" s="24"/>
-      <c r="AH190" s="24"/>
-      <c r="AI190" s="24"/>
-      <c r="AJ190" s="25"/>
+      <c r="B190" s="25"/>
+      <c r="C190" s="25"/>
+      <c r="D190" s="25"/>
+      <c r="E190" s="25"/>
+      <c r="F190" s="25"/>
+      <c r="G190" s="25"/>
+      <c r="H190" s="25"/>
+      <c r="I190" s="26"/>
+      <c r="J190" s="26"/>
+      <c r="K190" s="25"/>
+      <c r="L190" s="25"/>
+      <c r="M190" s="25"/>
+      <c r="N190" s="26"/>
+      <c r="O190" s="26"/>
+      <c r="P190" s="27"/>
+      <c r="Q190" s="25"/>
+      <c r="R190" s="25"/>
+      <c r="S190" s="26"/>
+      <c r="T190" s="26"/>
+      <c r="U190" s="25"/>
+      <c r="V190" s="25"/>
+      <c r="W190" s="25"/>
+      <c r="X190" s="25"/>
+      <c r="Y190" s="25"/>
+      <c r="Z190" s="25"/>
+      <c r="AA190" s="25"/>
+      <c r="AB190" s="25"/>
+      <c r="AC190" s="25"/>
+      <c r="AD190" s="25"/>
+      <c r="AE190" s="25"/>
+      <c r="AF190" s="25"/>
+      <c r="AG190" s="25"/>
+      <c r="AH190" s="25"/>
+      <c r="AI190" s="25"/>
+      <c r="AJ190" s="26"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="24"/>
-      <c r="C191" s="24"/>
-      <c r="D191" s="24"/>
-      <c r="E191" s="24"/>
-      <c r="F191" s="24"/>
-      <c r="G191" s="24"/>
-      <c r="H191" s="24"/>
-      <c r="I191" s="25"/>
-      <c r="J191" s="25"/>
-      <c r="K191" s="24"/>
-      <c r="L191" s="24"/>
-      <c r="M191" s="24"/>
-      <c r="N191" s="25"/>
-      <c r="O191" s="25"/>
-      <c r="P191" s="26"/>
-      <c r="Q191" s="24"/>
-      <c r="R191" s="24"/>
-      <c r="S191" s="25"/>
-      <c r="T191" s="25"/>
-      <c r="U191" s="24"/>
-      <c r="V191" s="24"/>
-      <c r="W191" s="24"/>
-      <c r="X191" s="24"/>
-      <c r="Y191" s="24"/>
-      <c r="Z191" s="24"/>
-      <c r="AA191" s="24"/>
-      <c r="AB191" s="24"/>
-      <c r="AC191" s="24"/>
-      <c r="AD191" s="24"/>
-      <c r="AE191" s="24"/>
-      <c r="AF191" s="24"/>
-      <c r="AG191" s="24"/>
-      <c r="AH191" s="24"/>
-      <c r="AI191" s="24"/>
-      <c r="AJ191" s="25"/>
+      <c r="B191" s="25"/>
+      <c r="C191" s="25"/>
+      <c r="D191" s="25"/>
+      <c r="E191" s="25"/>
+      <c r="F191" s="25"/>
+      <c r="G191" s="25"/>
+      <c r="H191" s="25"/>
+      <c r="I191" s="26"/>
+      <c r="J191" s="26"/>
+      <c r="K191" s="25"/>
+      <c r="L191" s="25"/>
+      <c r="M191" s="25"/>
+      <c r="N191" s="26"/>
+      <c r="O191" s="26"/>
+      <c r="P191" s="27"/>
+      <c r="Q191" s="25"/>
+      <c r="R191" s="25"/>
+      <c r="S191" s="26"/>
+      <c r="T191" s="26"/>
+      <c r="U191" s="25"/>
+      <c r="V191" s="25"/>
+      <c r="W191" s="25"/>
+      <c r="X191" s="25"/>
+      <c r="Y191" s="25"/>
+      <c r="Z191" s="25"/>
+      <c r="AA191" s="25"/>
+      <c r="AB191" s="25"/>
+      <c r="AC191" s="25"/>
+      <c r="AD191" s="25"/>
+      <c r="AE191" s="25"/>
+      <c r="AF191" s="25"/>
+      <c r="AG191" s="25"/>
+      <c r="AH191" s="25"/>
+      <c r="AI191" s="25"/>
+      <c r="AJ191" s="26"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="24"/>
-      <c r="C192" s="24"/>
-      <c r="D192" s="24"/>
-      <c r="E192" s="24"/>
-      <c r="F192" s="24"/>
-      <c r="G192" s="24"/>
-      <c r="H192" s="24"/>
-      <c r="I192" s="25"/>
-      <c r="J192" s="25"/>
-      <c r="K192" s="24"/>
-      <c r="L192" s="24"/>
-      <c r="M192" s="24"/>
-      <c r="N192" s="25"/>
-      <c r="O192" s="25"/>
-      <c r="P192" s="26"/>
-      <c r="Q192" s="24"/>
-      <c r="R192" s="24"/>
-      <c r="S192" s="25"/>
-      <c r="T192" s="25"/>
-      <c r="U192" s="24"/>
-      <c r="V192" s="24"/>
-      <c r="W192" s="24"/>
-      <c r="X192" s="24"/>
-      <c r="Y192" s="24"/>
-      <c r="Z192" s="24"/>
-      <c r="AA192" s="24"/>
-      <c r="AB192" s="24"/>
-      <c r="AC192" s="24"/>
-      <c r="AD192" s="24"/>
-      <c r="AE192" s="24"/>
-      <c r="AF192" s="24"/>
-      <c r="AG192" s="24"/>
-      <c r="AH192" s="24"/>
-      <c r="AI192" s="24"/>
-      <c r="AJ192" s="25"/>
+      <c r="B192" s="25"/>
+      <c r="C192" s="25"/>
+      <c r="D192" s="25"/>
+      <c r="E192" s="25"/>
+      <c r="F192" s="25"/>
+      <c r="G192" s="25"/>
+      <c r="H192" s="25"/>
+      <c r="I192" s="26"/>
+      <c r="J192" s="26"/>
+      <c r="K192" s="25"/>
+      <c r="L192" s="25"/>
+      <c r="M192" s="25"/>
+      <c r="N192" s="26"/>
+      <c r="O192" s="26"/>
+      <c r="P192" s="27"/>
+      <c r="Q192" s="25"/>
+      <c r="R192" s="25"/>
+      <c r="S192" s="26"/>
+      <c r="T192" s="26"/>
+      <c r="U192" s="25"/>
+      <c r="V192" s="25"/>
+      <c r="W192" s="25"/>
+      <c r="X192" s="25"/>
+      <c r="Y192" s="25"/>
+      <c r="Z192" s="25"/>
+      <c r="AA192" s="25"/>
+      <c r="AB192" s="25"/>
+      <c r="AC192" s="25"/>
+      <c r="AD192" s="25"/>
+      <c r="AE192" s="25"/>
+      <c r="AF192" s="25"/>
+      <c r="AG192" s="25"/>
+      <c r="AH192" s="25"/>
+      <c r="AI192" s="25"/>
+      <c r="AJ192" s="26"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="24"/>
-      <c r="C193" s="24"/>
-      <c r="D193" s="24"/>
-      <c r="E193" s="24"/>
-      <c r="F193" s="24"/>
-      <c r="G193" s="24"/>
-      <c r="H193" s="24"/>
-      <c r="I193" s="25"/>
-      <c r="J193" s="25"/>
-      <c r="K193" s="24"/>
-      <c r="L193" s="24"/>
-      <c r="M193" s="24"/>
-      <c r="N193" s="25"/>
-      <c r="O193" s="25"/>
-      <c r="P193" s="26"/>
-      <c r="Q193" s="24"/>
-      <c r="R193" s="24"/>
-      <c r="S193" s="25"/>
-      <c r="T193" s="25"/>
-      <c r="U193" s="24"/>
-      <c r="V193" s="24"/>
-      <c r="W193" s="24"/>
-      <c r="X193" s="24"/>
-      <c r="Y193" s="24"/>
-      <c r="Z193" s="24"/>
-      <c r="AA193" s="24"/>
-      <c r="AB193" s="24"/>
-      <c r="AC193" s="24"/>
-      <c r="AD193" s="24"/>
-      <c r="AE193" s="24"/>
-      <c r="AF193" s="24"/>
-      <c r="AG193" s="24"/>
-      <c r="AH193" s="24"/>
-      <c r="AI193" s="24"/>
-      <c r="AJ193" s="25"/>
+      <c r="B193" s="25"/>
+      <c r="C193" s="25"/>
+      <c r="D193" s="25"/>
+      <c r="E193" s="25"/>
+      <c r="F193" s="25"/>
+      <c r="G193" s="25"/>
+      <c r="H193" s="25"/>
+      <c r="I193" s="26"/>
+      <c r="J193" s="26"/>
+      <c r="K193" s="25"/>
+      <c r="L193" s="25"/>
+      <c r="M193" s="25"/>
+      <c r="N193" s="26"/>
+      <c r="O193" s="26"/>
+      <c r="P193" s="27"/>
+      <c r="Q193" s="25"/>
+      <c r="R193" s="25"/>
+      <c r="S193" s="26"/>
+      <c r="T193" s="26"/>
+      <c r="U193" s="25"/>
+      <c r="V193" s="25"/>
+      <c r="W193" s="25"/>
+      <c r="X193" s="25"/>
+      <c r="Y193" s="25"/>
+      <c r="Z193" s="25"/>
+      <c r="AA193" s="25"/>
+      <c r="AB193" s="25"/>
+      <c r="AC193" s="25"/>
+      <c r="AD193" s="25"/>
+      <c r="AE193" s="25"/>
+      <c r="AF193" s="25"/>
+      <c r="AG193" s="25"/>
+      <c r="AH193" s="25"/>
+      <c r="AI193" s="25"/>
+      <c r="AJ193" s="26"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B194" s="24"/>
-      <c r="C194" s="24"/>
-      <c r="D194" s="24"/>
-      <c r="E194" s="24"/>
-      <c r="F194" s="24"/>
-      <c r="G194" s="24"/>
-      <c r="H194" s="24"/>
-      <c r="I194" s="25